--- a/20_設計書/化学物質データ申請画面.xlsx
+++ b/20_設計書/化学物質データ申請画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEF9EB40-5A33-4969-91AF-4CF01222CA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744A54B1-3BF6-4F52-AEB8-FA6E1D217B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31875" yWindow="225" windowWidth="25725" windowHeight="15975" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -3938,42 +3938,144 @@
     <xf numFmtId="0" fontId="69" fillId="0" borderId="14" xfId="188" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="61" fillId="14" borderId="0" xfId="48" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="48" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="48" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="22" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="17" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="3" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="17" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="21" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="22" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="20" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="54" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="22" fillId="0" borderId="3" xfId="50" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3992,107 +4094,11 @@
     <xf numFmtId="14" fontId="54" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="23" xfId="161" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="2" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="17" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="15" borderId="21" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="17" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="3" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="3" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="22" fillId="0" borderId="3" xfId="48" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="22" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="20" xfId="48" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="55" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="10" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="17" xfId="50" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="91" fillId="26" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4118,31 +4124,10 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="17" xfId="46" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="70" fillId="0" borderId="23" xfId="161" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="48" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="12" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="184" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="33" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4157,6 +4142,47 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="37" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="38" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4166,11 +4192,106 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="30" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="31" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="32" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="26" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="27" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="28" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="33" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="34" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="39" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="71" fillId="23" borderId="20" xfId="185" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4209,147 +4330,117 @@
     <xf numFmtId="0" fontId="71" fillId="22" borderId="14" xfId="185" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="26" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="15" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="12" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="7" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="8" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="12" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="184" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="23" borderId="20" xfId="188" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="23" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="15" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="12" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="13" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="7" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="8" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="22" borderId="14" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="27" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="28" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="15" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="12" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="7" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="8" xfId="184" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="33" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="34" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="39" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="30" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="31" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="32" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="37" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="38" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="78" fillId="23" borderId="20" xfId="188" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="15" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4393,105 +4484,14 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="41" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="63" fillId="0" borderId="3" xfId="187" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="63" fillId="0" borderId="3" xfId="187" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="88" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="86" fillId="0" borderId="3" xfId="187" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="64" fillId="14" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="23" borderId="3" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="15" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="12" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="13" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="7" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="8" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="22" borderId="14" xfId="187" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="189">
@@ -6027,8 +6027,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3036094" y="3940969"/>
-          <a:ext cx="3617380" cy="1508918"/>
+          <a:off x="3103563" y="3833813"/>
+          <a:ext cx="3699930" cy="1440656"/>
           <a:chOff x="3649663" y="3595688"/>
           <a:chExt cx="3620555" cy="1505743"/>
         </a:xfrm>
@@ -6932,8 +6932,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7147189" y="9058011"/>
-          <a:ext cx="797719" cy="277282"/>
+          <a:off x="7298796" y="8712730"/>
+          <a:ext cx="817562" cy="261407"/>
           <a:chOff x="13567834" y="4773083"/>
           <a:chExt cx="898525" cy="275168"/>
         </a:xfrm>
@@ -7230,123 +7230,6 @@
             <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
           </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>56</xdr:col>
-      <xdr:colOff>15876</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>47624</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>69</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>150812</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="吹き出し: 四角形 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AA57CCDB-CAB3-DFBA-12AC-BAC0DF9B8FC5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10239376" y="8485187"/>
-          <a:ext cx="2500312" cy="738188"/>
-        </a:xfrm>
-        <a:prstGeom prst="wedgeRectCallout">
-          <a:avLst>
-            <a:gd name="adj1" fmla="val -153301"/>
-            <a:gd name="adj2" fmla="val 74500"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:ln w="12700">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="lt1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>AA</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>古竹</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1050">
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l">
-            <a:lnSpc>
-              <a:spcPts val="900"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1050">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>ここに表示するお知らせは最新のお知らせ何件分に設定したほうがよいでしょうか。</a:t>
-          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -7724,16 +7607,16 @@
     <row r="20" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="21" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
-      <c r="B22" s="177" t="str">
+      <c r="B22" s="179" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
         <v>2026年 05月 20日 r1.2</v>
       </c>
-      <c r="C22" s="178"/>
-      <c r="D22" s="178"/>
-      <c r="E22" s="178"/>
-      <c r="F22" s="178"/>
-      <c r="G22" s="178"/>
-      <c r="H22" s="178"/>
+      <c r="C22" s="180"/>
+      <c r="D22" s="180"/>
+      <c r="E22" s="180"/>
+      <c r="F22" s="180"/>
+      <c r="G22" s="180"/>
+      <c r="H22" s="180"/>
     </row>
     <row r="23" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="24" spans="2:8" ht="14.25" customHeight="1"/>
@@ -7741,15 +7624,15 @@
     <row r="26" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="27" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="28" spans="2:8" ht="14.25" customHeight="1">
-      <c r="C28" s="180" t="s">
+      <c r="C28" s="181" t="s">
         <v>28</v>
       </c>
-      <c r="D28" s="180"/>
-      <c r="E28" s="180"/>
-      <c r="F28" s="180" t="s">
+      <c r="D28" s="181"/>
+      <c r="E28" s="181"/>
+      <c r="F28" s="181" t="s">
         <v>0</v>
       </c>
-      <c r="G28" s="180"/>
+      <c r="G28" s="181"/>
     </row>
     <row r="29" spans="2:8" ht="14.25" customHeight="1">
       <c r="C29" s="3" t="s">
@@ -7784,11 +7667,11 @@
     </row>
     <row r="32" spans="2:8" ht="14.25" customHeight="1"/>
     <row r="33" spans="3:20" ht="14.25" customHeight="1">
-      <c r="C33" s="181"/>
-      <c r="D33" s="181"/>
-      <c r="E33" s="181"/>
-      <c r="F33" s="181"/>
-      <c r="G33" s="181"/>
+      <c r="C33" s="182"/>
+      <c r="D33" s="182"/>
+      <c r="E33" s="182"/>
+      <c r="F33" s="182"/>
+      <c r="G33" s="182"/>
       <c r="H33" s="7"/>
       <c r="I33" s="7"/>
     </row>
@@ -7835,7 +7718,7 @@
       <c r="Q38" s="15"/>
       <c r="R38" s="14"/>
       <c r="S38" s="16"/>
-      <c r="T38" s="179"/>
+      <c r="T38" s="177"/>
     </row>
     <row r="39" spans="3:20" ht="14.25" customHeight="1">
       <c r="K39" s="17"/>
@@ -7847,7 +7730,7 @@
       <c r="Q39" s="8"/>
       <c r="R39" s="14"/>
       <c r="S39" s="19"/>
-      <c r="T39" s="182"/>
+      <c r="T39" s="178"/>
     </row>
     <row r="40" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="41" spans="3:20" ht="14.25" customHeight="1">
@@ -7871,7 +7754,7 @@
       <c r="Q42" s="15"/>
       <c r="R42" s="14"/>
       <c r="S42" s="16"/>
-      <c r="T42" s="179"/>
+      <c r="T42" s="177"/>
     </row>
     <row r="43" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K43" s="17"/>
@@ -7879,7 +7762,7 @@
       <c r="N43" s="12"/>
       <c r="R43" s="14"/>
       <c r="S43" s="19"/>
-      <c r="T43" s="179"/>
+      <c r="T43" s="177"/>
     </row>
     <row r="44" spans="3:20" s="8" customFormat="1" ht="14.25" customHeight="1">
       <c r="K44" s="1"/>
@@ -7915,7 +7798,7 @@
       <c r="Q46" s="15"/>
       <c r="R46" s="14"/>
       <c r="S46" s="16"/>
-      <c r="T46" s="179"/>
+      <c r="T46" s="177"/>
     </row>
     <row r="47" spans="3:20" ht="14.25" customHeight="1">
       <c r="K47" s="17"/>
@@ -7927,7 +7810,7 @@
       <c r="Q47" s="8"/>
       <c r="R47" s="14"/>
       <c r="S47" s="19"/>
-      <c r="T47" s="179"/>
+      <c r="T47" s="177"/>
     </row>
     <row r="48" spans="3:20" ht="14.25" customHeight="1"/>
     <row r="49" spans="11:20" ht="14.25" customHeight="1">
@@ -7952,7 +7835,7 @@
       <c r="Q50" s="15"/>
       <c r="R50" s="14"/>
       <c r="S50" s="16"/>
-      <c r="T50" s="179"/>
+      <c r="T50" s="177"/>
     </row>
     <row r="51" spans="11:20" ht="14.25" customHeight="1">
       <c r="K51" s="17"/>
@@ -7964,7 +7847,7 @@
       <c r="Q51" s="8"/>
       <c r="R51" s="14"/>
       <c r="S51" s="19"/>
-      <c r="T51" s="179"/>
+      <c r="T51" s="177"/>
     </row>
     <row r="52" spans="11:20" ht="14.25" customHeight="1"/>
     <row r="53" spans="11:20" ht="14.25" customHeight="1">
@@ -7989,7 +7872,7 @@
       <c r="Q54" s="15"/>
       <c r="R54" s="14"/>
       <c r="S54" s="16"/>
-      <c r="T54" s="179"/>
+      <c r="T54" s="177"/>
     </row>
     <row r="55" spans="11:20">
       <c r="K55" s="17"/>
@@ -8001,7 +7884,7 @@
       <c r="Q55" s="8"/>
       <c r="R55" s="14"/>
       <c r="S55" s="19"/>
-      <c r="T55" s="182"/>
+      <c r="T55" s="178"/>
     </row>
     <row r="57" spans="11:20">
       <c r="K57" s="11"/>
@@ -8025,7 +7908,7 @@
       <c r="Q58" s="15"/>
       <c r="R58" s="14"/>
       <c r="S58" s="16"/>
-      <c r="T58" s="179"/>
+      <c r="T58" s="177"/>
     </row>
     <row r="59" spans="11:20">
       <c r="K59" s="17"/>
@@ -8037,7 +7920,7 @@
       <c r="Q59" s="8"/>
       <c r="R59" s="14"/>
       <c r="S59" s="19"/>
-      <c r="T59" s="182"/>
+      <c r="T59" s="178"/>
     </row>
     <row r="61" spans="11:20">
       <c r="K61" s="11"/>
@@ -8061,7 +7944,7 @@
       <c r="Q62" s="15"/>
       <c r="R62" s="14"/>
       <c r="S62" s="16"/>
-      <c r="T62" s="179"/>
+      <c r="T62" s="177"/>
     </row>
     <row r="63" spans="11:20">
       <c r="K63" s="17"/>
@@ -8073,7 +7956,7 @@
       <c r="Q63" s="8"/>
       <c r="R63" s="14"/>
       <c r="S63" s="19"/>
-      <c r="T63" s="182"/>
+      <c r="T63" s="178"/>
     </row>
     <row r="65" spans="11:20">
       <c r="K65" s="11"/>
@@ -8097,7 +7980,7 @@
       <c r="Q66" s="15"/>
       <c r="R66" s="14"/>
       <c r="S66" s="16"/>
-      <c r="T66" s="179"/>
+      <c r="T66" s="177"/>
     </row>
     <row r="67" spans="11:20">
       <c r="K67" s="17"/>
@@ -8109,7 +7992,7 @@
       <c r="Q67" s="8"/>
       <c r="R67" s="14"/>
       <c r="S67" s="19"/>
-      <c r="T67" s="182"/>
+      <c r="T67" s="178"/>
     </row>
     <row r="69" spans="11:20">
       <c r="K69" s="11"/>
@@ -8133,7 +8016,7 @@
       <c r="Q70" s="15"/>
       <c r="R70" s="14"/>
       <c r="S70" s="16"/>
-      <c r="T70" s="179"/>
+      <c r="T70" s="177"/>
     </row>
     <row r="71" spans="11:20">
       <c r="K71" s="17"/>
@@ -8145,7 +8028,7 @@
       <c r="Q71" s="8"/>
       <c r="R71" s="14"/>
       <c r="S71" s="19"/>
-      <c r="T71" s="182"/>
+      <c r="T71" s="178"/>
     </row>
     <row r="73" spans="11:20">
       <c r="K73" s="11"/>
@@ -8169,7 +8052,7 @@
       <c r="Q74" s="15"/>
       <c r="R74" s="14"/>
       <c r="S74" s="16"/>
-      <c r="T74" s="179"/>
+      <c r="T74" s="177"/>
     </row>
     <row r="75" spans="11:20">
       <c r="K75" s="17"/>
@@ -8181,7 +8064,7 @@
       <c r="Q75" s="8"/>
       <c r="R75" s="14"/>
       <c r="S75" s="19"/>
-      <c r="T75" s="182"/>
+      <c r="T75" s="178"/>
     </row>
     <row r="77" spans="11:20">
       <c r="K77" s="11"/>
@@ -8205,7 +8088,7 @@
       <c r="Q78" s="15"/>
       <c r="R78" s="14"/>
       <c r="S78" s="16"/>
-      <c r="T78" s="179"/>
+      <c r="T78" s="177"/>
     </row>
     <row r="79" spans="11:20">
       <c r="K79" s="17"/>
@@ -8217,7 +8100,7 @@
       <c r="Q79" s="8"/>
       <c r="R79" s="14"/>
       <c r="S79" s="19"/>
-      <c r="T79" s="182"/>
+      <c r="T79" s="178"/>
     </row>
     <row r="81" spans="11:20">
       <c r="K81" s="11"/>
@@ -8241,7 +8124,7 @@
       <c r="Q82" s="15"/>
       <c r="R82" s="14"/>
       <c r="S82" s="16"/>
-      <c r="T82" s="179"/>
+      <c r="T82" s="177"/>
     </row>
     <row r="83" spans="11:20">
       <c r="K83" s="17"/>
@@ -8253,7 +8136,7 @@
       <c r="Q83" s="8"/>
       <c r="R83" s="14"/>
       <c r="S83" s="19"/>
-      <c r="T83" s="182"/>
+      <c r="T83" s="178"/>
     </row>
     <row r="85" spans="11:20">
       <c r="K85" s="11"/>
@@ -8277,7 +8160,7 @@
       <c r="Q86" s="15"/>
       <c r="R86" s="14"/>
       <c r="S86" s="16"/>
-      <c r="T86" s="179"/>
+      <c r="T86" s="177"/>
     </row>
     <row r="87" spans="11:20">
       <c r="K87" s="17"/>
@@ -8289,7 +8172,7 @@
       <c r="Q87" s="8"/>
       <c r="R87" s="14"/>
       <c r="S87" s="19"/>
-      <c r="T87" s="182"/>
+      <c r="T87" s="178"/>
     </row>
     <row r="89" spans="11:20">
       <c r="K89" s="11"/>
@@ -8313,7 +8196,7 @@
       <c r="Q90" s="15"/>
       <c r="R90" s="14"/>
       <c r="S90" s="16"/>
-      <c r="T90" s="179"/>
+      <c r="T90" s="177"/>
     </row>
     <row r="91" spans="11:20">
       <c r="K91" s="17"/>
@@ -8325,7 +8208,7 @@
       <c r="Q91" s="8"/>
       <c r="R91" s="14"/>
       <c r="S91" s="19"/>
-      <c r="T91" s="182"/>
+      <c r="T91" s="178"/>
     </row>
     <row r="93" spans="11:20">
       <c r="K93" s="11"/>
@@ -8349,7 +8232,7 @@
       <c r="Q94" s="15"/>
       <c r="R94" s="14"/>
       <c r="S94" s="16"/>
-      <c r="T94" s="179"/>
+      <c r="T94" s="177"/>
     </row>
     <row r="95" spans="11:20">
       <c r="K95" s="17"/>
@@ -8361,7 +8244,7 @@
       <c r="Q95" s="8"/>
       <c r="R95" s="14"/>
       <c r="S95" s="19"/>
-      <c r="T95" s="182"/>
+      <c r="T95" s="178"/>
     </row>
     <row r="97" spans="11:20">
       <c r="K97" s="11"/>
@@ -8385,7 +8268,7 @@
       <c r="Q98" s="15"/>
       <c r="R98" s="14"/>
       <c r="S98" s="16"/>
-      <c r="T98" s="179"/>
+      <c r="T98" s="177"/>
     </row>
     <row r="99" spans="11:20">
       <c r="K99" s="17"/>
@@ -8397,7 +8280,7 @@
       <c r="Q99" s="8"/>
       <c r="R99" s="14"/>
       <c r="S99" s="19"/>
-      <c r="T99" s="182"/>
+      <c r="T99" s="178"/>
     </row>
     <row r="101" spans="11:20">
       <c r="K101" s="11"/>
@@ -8421,7 +8304,7 @@
       <c r="Q102" s="15"/>
       <c r="R102" s="14"/>
       <c r="S102" s="16"/>
-      <c r="T102" s="179"/>
+      <c r="T102" s="177"/>
     </row>
     <row r="103" spans="11:20">
       <c r="K103" s="17"/>
@@ -8433,7 +8316,7 @@
       <c r="Q103" s="8"/>
       <c r="R103" s="14"/>
       <c r="S103" s="19"/>
-      <c r="T103" s="182"/>
+      <c r="T103" s="178"/>
     </row>
     <row r="105" spans="11:20">
       <c r="K105" s="11"/>
@@ -8457,7 +8340,7 @@
       <c r="Q106" s="15"/>
       <c r="R106" s="14"/>
       <c r="S106" s="16"/>
-      <c r="T106" s="179"/>
+      <c r="T106" s="177"/>
     </row>
     <row r="107" spans="11:20">
       <c r="K107" s="17"/>
@@ -8469,7 +8352,7 @@
       <c r="Q107" s="8"/>
       <c r="R107" s="14"/>
       <c r="S107" s="19"/>
-      <c r="T107" s="182"/>
+      <c r="T107" s="178"/>
     </row>
     <row r="109" spans="11:20">
       <c r="K109" s="11"/>
@@ -8493,7 +8376,7 @@
       <c r="Q110" s="15"/>
       <c r="R110" s="14"/>
       <c r="S110" s="16"/>
-      <c r="T110" s="179"/>
+      <c r="T110" s="177"/>
     </row>
     <row r="111" spans="11:20">
       <c r="K111" s="17"/>
@@ -8505,7 +8388,7 @@
       <c r="Q111" s="8"/>
       <c r="R111" s="14"/>
       <c r="S111" s="19"/>
-      <c r="T111" s="182"/>
+      <c r="T111" s="178"/>
     </row>
     <row r="113" spans="11:20">
       <c r="K113" s="11"/>
@@ -8529,7 +8412,7 @@
       <c r="Q114" s="15"/>
       <c r="R114" s="14"/>
       <c r="S114" s="16"/>
-      <c r="T114" s="179"/>
+      <c r="T114" s="177"/>
     </row>
     <row r="115" spans="11:20">
       <c r="K115" s="17"/>
@@ -8541,7 +8424,7 @@
       <c r="Q115" s="8"/>
       <c r="R115" s="14"/>
       <c r="S115" s="19"/>
-      <c r="T115" s="182"/>
+      <c r="T115" s="178"/>
     </row>
     <row r="117" spans="11:20">
       <c r="K117" s="11"/>
@@ -8565,7 +8448,7 @@
       <c r="Q118" s="15"/>
       <c r="R118" s="14"/>
       <c r="S118" s="16"/>
-      <c r="T118" s="179"/>
+      <c r="T118" s="177"/>
     </row>
     <row r="119" spans="11:20">
       <c r="K119" s="17"/>
@@ -8577,7 +8460,7 @@
       <c r="Q119" s="8"/>
       <c r="R119" s="14"/>
       <c r="S119" s="19"/>
-      <c r="T119" s="182"/>
+      <c r="T119" s="178"/>
     </row>
     <row r="121" spans="11:20">
       <c r="K121" s="11"/>
@@ -8601,7 +8484,7 @@
       <c r="Q122" s="15"/>
       <c r="R122" s="14"/>
       <c r="S122" s="16"/>
-      <c r="T122" s="179"/>
+      <c r="T122" s="177"/>
     </row>
     <row r="123" spans="11:20">
       <c r="K123" s="17"/>
@@ -8613,18 +8496,17 @@
       <c r="Q123" s="8"/>
       <c r="R123" s="14"/>
       <c r="S123" s="19"/>
-      <c r="T123" s="182"/>
+      <c r="T123" s="178"/>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="T118:T119"/>
-    <mergeCell ref="T122:T123"/>
-    <mergeCell ref="T94:T95"/>
-    <mergeCell ref="T98:T99"/>
-    <mergeCell ref="T102:T103"/>
-    <mergeCell ref="T106:T107"/>
-    <mergeCell ref="T110:T111"/>
-    <mergeCell ref="T114:T115"/>
+    <mergeCell ref="B22:H22"/>
+    <mergeCell ref="T42:T43"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="T38:T39"/>
     <mergeCell ref="T90:T91"/>
     <mergeCell ref="T46:T47"/>
     <mergeCell ref="T50:T51"/>
@@ -8637,13 +8519,14 @@
     <mergeCell ref="T78:T79"/>
     <mergeCell ref="T82:T83"/>
     <mergeCell ref="T86:T87"/>
-    <mergeCell ref="B22:H22"/>
-    <mergeCell ref="T42:T43"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="T38:T39"/>
+    <mergeCell ref="T118:T119"/>
+    <mergeCell ref="T122:T123"/>
+    <mergeCell ref="T94:T95"/>
+    <mergeCell ref="T98:T99"/>
+    <mergeCell ref="T102:T103"/>
+    <mergeCell ref="T106:T107"/>
+    <mergeCell ref="T110:T111"/>
+    <mergeCell ref="T114:T115"/>
   </mergeCells>
   <phoneticPr fontId="14"/>
   <printOptions horizontalCentered="1"/>
@@ -8666,1926 +8549,2113 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:53" ht="12" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="206" t="s">
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="221" t="s">
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="221"/>
-      <c r="S1" s="221"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="206" t="s">
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="225" t="s">
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="209" t="s">
         <v>122</v>
       </c>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="225"/>
-      <c r="AE1" s="225"/>
-      <c r="AF1" s="225"/>
-      <c r="AG1" s="225"/>
-      <c r="AH1" s="225"/>
-      <c r="AI1" s="225"/>
-      <c r="AJ1" s="225"/>
-      <c r="AK1" s="210" t="s">
+      <c r="AB1" s="209"/>
+      <c r="AC1" s="209"/>
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="209"/>
+      <c r="AG1" s="209"/>
+      <c r="AH1" s="209"/>
+      <c r="AI1" s="209"/>
+      <c r="AJ1" s="209"/>
+      <c r="AK1" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="210"/>
-      <c r="AM1" s="210"/>
-      <c r="AN1" s="211" t="s">
+      <c r="AL1" s="183"/>
+      <c r="AM1" s="183"/>
+      <c r="AN1" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="AO1" s="211"/>
-      <c r="AP1" s="211"/>
-      <c r="AQ1" s="210" t="s">
+      <c r="AO1" s="185"/>
+      <c r="AP1" s="185"/>
+      <c r="AQ1" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="AR1" s="210"/>
-      <c r="AS1" s="210"/>
-      <c r="AT1" s="213">
+      <c r="AR1" s="183"/>
+      <c r="AS1" s="183"/>
+      <c r="AT1" s="186">
         <f>AL7</f>
         <v>46125</v>
       </c>
-      <c r="AU1" s="213"/>
-      <c r="AV1" s="213"/>
-      <c r="AW1" s="213"/>
-      <c r="AX1" s="202" t="s">
+      <c r="AU1" s="186"/>
+      <c r="AV1" s="186"/>
+      <c r="AW1" s="186"/>
+      <c r="AX1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="AY1" s="203"/>
-      <c r="AZ1" s="203"/>
-      <c r="BA1" s="204"/>
+      <c r="AY1" s="191"/>
+      <c r="AZ1" s="191"/>
+      <c r="BA1" s="192"/>
     </row>
     <row r="2" spans="1:53">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="193" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="205"/>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="206"/>
-      <c r="L2" s="206"/>
-      <c r="M2" s="207" t="s">
+      <c r="J2" s="194"/>
+      <c r="K2" s="194"/>
+      <c r="L2" s="194"/>
+      <c r="M2" s="195" t="s">
         <v>29</v>
       </c>
-      <c r="N2" s="208"/>
-      <c r="O2" s="208"/>
-      <c r="P2" s="208"/>
-      <c r="Q2" s="208"/>
-      <c r="R2" s="208"/>
-      <c r="S2" s="208"/>
-      <c r="T2" s="208"/>
-      <c r="U2" s="208"/>
-      <c r="V2" s="208"/>
-      <c r="W2" s="209"/>
-      <c r="X2" s="206"/>
-      <c r="Y2" s="206"/>
-      <c r="Z2" s="206"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="225"/>
-      <c r="AC2" s="225"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="225"/>
-      <c r="AF2" s="225"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="225"/>
-      <c r="AI2" s="225"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="210" t="s">
+      <c r="N2" s="196"/>
+      <c r="O2" s="196"/>
+      <c r="P2" s="196"/>
+      <c r="Q2" s="196"/>
+      <c r="R2" s="196"/>
+      <c r="S2" s="196"/>
+      <c r="T2" s="196"/>
+      <c r="U2" s="196"/>
+      <c r="V2" s="196"/>
+      <c r="W2" s="197"/>
+      <c r="X2" s="194"/>
+      <c r="Y2" s="194"/>
+      <c r="Z2" s="194"/>
+      <c r="AA2" s="209"/>
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="209"/>
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="209"/>
+      <c r="AG2" s="209"/>
+      <c r="AH2" s="209"/>
+      <c r="AI2" s="209"/>
+      <c r="AJ2" s="209"/>
+      <c r="AK2" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="210"/>
-      <c r="AM2" s="210"/>
-      <c r="AN2" s="211" t="s">
+      <c r="AL2" s="183"/>
+      <c r="AM2" s="183"/>
+      <c r="AN2" s="185" t="s">
         <v>32</v>
       </c>
-      <c r="AO2" s="211"/>
-      <c r="AP2" s="211"/>
-      <c r="AQ2" s="210" t="s">
+      <c r="AO2" s="185"/>
+      <c r="AP2" s="185"/>
+      <c r="AQ2" s="183" t="s">
         <v>13</v>
       </c>
-      <c r="AR2" s="210"/>
-      <c r="AS2" s="210"/>
-      <c r="AT2" s="213">
+      <c r="AR2" s="183"/>
+      <c r="AS2" s="183"/>
+      <c r="AT2" s="186">
         <v>46162</v>
       </c>
-      <c r="AU2" s="213"/>
-      <c r="AV2" s="213"/>
-      <c r="AW2" s="213"/>
-      <c r="AX2" s="214" t="s">
+      <c r="AU2" s="186"/>
+      <c r="AV2" s="186"/>
+      <c r="AW2" s="186"/>
+      <c r="AX2" s="198" t="s">
         <v>30</v>
       </c>
-      <c r="AY2" s="215"/>
-      <c r="AZ2" s="215"/>
-      <c r="BA2" s="216"/>
+      <c r="AY2" s="199"/>
+      <c r="AZ2" s="199"/>
+      <c r="BA2" s="200"/>
     </row>
     <row r="3" spans="1:53" ht="12" customHeight="1">
-      <c r="A3" s="220" t="s">
+      <c r="A3" s="204" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="220"/>
-      <c r="F3" s="220"/>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="206" t="s">
+      <c r="B3" s="204"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="194" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="206"/>
-      <c r="K3" s="206"/>
-      <c r="L3" s="206"/>
-      <c r="M3" s="221"/>
-      <c r="N3" s="221"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="206" t="s">
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="194"/>
+      <c r="M3" s="205"/>
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="205"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="205"/>
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="205"/>
+      <c r="X3" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="206"/>
-      <c r="AA3" s="222" t="s">
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="206" t="s">
         <v>99</v>
       </c>
-      <c r="AB3" s="222"/>
-      <c r="AC3" s="222"/>
-      <c r="AD3" s="222"/>
-      <c r="AE3" s="222"/>
-      <c r="AF3" s="222"/>
-      <c r="AG3" s="222"/>
-      <c r="AH3" s="222"/>
-      <c r="AI3" s="222"/>
-      <c r="AJ3" s="222"/>
-      <c r="AK3" s="222"/>
-      <c r="AL3" s="222"/>
-      <c r="AM3" s="222"/>
-      <c r="AN3" s="222"/>
-      <c r="AO3" s="222"/>
-      <c r="AP3" s="222"/>
-      <c r="AQ3" s="210" t="s">
+      <c r="AB3" s="206"/>
+      <c r="AC3" s="206"/>
+      <c r="AD3" s="206"/>
+      <c r="AE3" s="206"/>
+      <c r="AF3" s="206"/>
+      <c r="AG3" s="206"/>
+      <c r="AH3" s="206"/>
+      <c r="AI3" s="206"/>
+      <c r="AJ3" s="206"/>
+      <c r="AK3" s="206"/>
+      <c r="AL3" s="206"/>
+      <c r="AM3" s="206"/>
+      <c r="AN3" s="206"/>
+      <c r="AO3" s="206"/>
+      <c r="AP3" s="206"/>
+      <c r="AQ3" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="AR3" s="210"/>
-      <c r="AS3" s="210"/>
-      <c r="AT3" s="226" t="str">
+      <c r="AR3" s="183"/>
+      <c r="AS3" s="183"/>
+      <c r="AT3" s="184" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
         <v>r1.2</v>
       </c>
-      <c r="AU3" s="226"/>
-      <c r="AV3" s="226"/>
-      <c r="AW3" s="226"/>
-      <c r="AX3" s="217"/>
-      <c r="AY3" s="218"/>
-      <c r="AZ3" s="218"/>
-      <c r="BA3" s="219"/>
+      <c r="AU3" s="184"/>
+      <c r="AV3" s="184"/>
+      <c r="AW3" s="184"/>
+      <c r="AX3" s="201"/>
+      <c r="AY3" s="202"/>
+      <c r="AZ3" s="202"/>
+      <c r="BA3" s="203"/>
     </row>
     <row r="4" spans="1:53" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:53" ht="14">
-      <c r="A5" s="224" t="s">
+      <c r="A5" s="208" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="224"/>
-      <c r="C5" s="224"/>
-      <c r="D5" s="224"/>
-      <c r="E5" s="224"/>
-      <c r="F5" s="224"/>
-      <c r="G5" s="224"/>
-      <c r="H5" s="224"/>
-      <c r="I5" s="224"/>
-      <c r="J5" s="224"/>
-      <c r="K5" s="224"/>
-      <c r="L5" s="224"/>
-      <c r="M5" s="224"/>
-      <c r="N5" s="224"/>
-      <c r="O5" s="224"/>
-      <c r="P5" s="224"/>
-      <c r="Q5" s="224"/>
-      <c r="R5" s="224"/>
-      <c r="S5" s="224"/>
-      <c r="T5" s="224"/>
-      <c r="U5" s="224"/>
-      <c r="V5" s="224"/>
-      <c r="W5" s="224"/>
-      <c r="X5" s="224"/>
-      <c r="Y5" s="224"/>
-      <c r="Z5" s="224"/>
-      <c r="AA5" s="224"/>
-      <c r="AB5" s="224"/>
-      <c r="AC5" s="224"/>
-      <c r="AD5" s="224"/>
-      <c r="AE5" s="224"/>
-      <c r="AF5" s="224"/>
-      <c r="AG5" s="224"/>
-      <c r="AH5" s="224"/>
-      <c r="AI5" s="224"/>
-      <c r="AJ5" s="224"/>
-      <c r="AK5" s="224"/>
-      <c r="AL5" s="224"/>
-      <c r="AM5" s="224"/>
-      <c r="AN5" s="224"/>
-      <c r="AO5" s="224"/>
-      <c r="AP5" s="224"/>
-      <c r="AQ5" s="224"/>
-      <c r="AR5" s="224"/>
-      <c r="AS5" s="224"/>
-      <c r="AT5" s="224"/>
-      <c r="AU5" s="224"/>
-      <c r="AV5" s="224"/>
-      <c r="AW5" s="224"/>
-      <c r="AX5" s="224"/>
-      <c r="AY5" s="224"/>
-      <c r="AZ5" s="224"/>
-      <c r="BA5" s="224"/>
+      <c r="B5" s="208"/>
+      <c r="C5" s="208"/>
+      <c r="D5" s="208"/>
+      <c r="E5" s="208"/>
+      <c r="F5" s="208"/>
+      <c r="G5" s="208"/>
+      <c r="H5" s="208"/>
+      <c r="I5" s="208"/>
+      <c r="J5" s="208"/>
+      <c r="K5" s="208"/>
+      <c r="L5" s="208"/>
+      <c r="M5" s="208"/>
+      <c r="N5" s="208"/>
+      <c r="O5" s="208"/>
+      <c r="P5" s="208"/>
+      <c r="Q5" s="208"/>
+      <c r="R5" s="208"/>
+      <c r="S5" s="208"/>
+      <c r="T5" s="208"/>
+      <c r="U5" s="208"/>
+      <c r="V5" s="208"/>
+      <c r="W5" s="208"/>
+      <c r="X5" s="208"/>
+      <c r="Y5" s="208"/>
+      <c r="Z5" s="208"/>
+      <c r="AA5" s="208"/>
+      <c r="AB5" s="208"/>
+      <c r="AC5" s="208"/>
+      <c r="AD5" s="208"/>
+      <c r="AE5" s="208"/>
+      <c r="AF5" s="208"/>
+      <c r="AG5" s="208"/>
+      <c r="AH5" s="208"/>
+      <c r="AI5" s="208"/>
+      <c r="AJ5" s="208"/>
+      <c r="AK5" s="208"/>
+      <c r="AL5" s="208"/>
+      <c r="AM5" s="208"/>
+      <c r="AN5" s="208"/>
+      <c r="AO5" s="208"/>
+      <c r="AP5" s="208"/>
+      <c r="AQ5" s="208"/>
+      <c r="AR5" s="208"/>
+      <c r="AS5" s="208"/>
+      <c r="AT5" s="208"/>
+      <c r="AU5" s="208"/>
+      <c r="AV5" s="208"/>
+      <c r="AW5" s="208"/>
+      <c r="AX5" s="208"/>
+      <c r="AY5" s="208"/>
+      <c r="AZ5" s="208"/>
+      <c r="BA5" s="208"/>
     </row>
     <row r="6" spans="1:53">
-      <c r="A6" s="227" t="s">
+      <c r="A6" s="187" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="228"/>
-      <c r="C6" s="212" t="s">
+      <c r="B6" s="188"/>
+      <c r="C6" s="189" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="212"/>
-      <c r="E6" s="212"/>
-      <c r="F6" s="212"/>
-      <c r="G6" s="212"/>
-      <c r="H6" s="212"/>
-      <c r="I6" s="212"/>
-      <c r="J6" s="212"/>
-      <c r="K6" s="212"/>
-      <c r="L6" s="212"/>
-      <c r="M6" s="212"/>
-      <c r="N6" s="212"/>
-      <c r="O6" s="212"/>
-      <c r="P6" s="212"/>
-      <c r="Q6" s="212" t="s">
+      <c r="D6" s="189"/>
+      <c r="E6" s="189"/>
+      <c r="F6" s="189"/>
+      <c r="G6" s="189"/>
+      <c r="H6" s="189"/>
+      <c r="I6" s="189"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="M6" s="189"/>
+      <c r="N6" s="189"/>
+      <c r="O6" s="189"/>
+      <c r="P6" s="189"/>
+      <c r="Q6" s="189" t="s">
         <v>18</v>
       </c>
-      <c r="R6" s="212"/>
-      <c r="S6" s="212"/>
-      <c r="T6" s="212"/>
-      <c r="U6" s="212"/>
-      <c r="V6" s="212"/>
-      <c r="W6" s="212"/>
-      <c r="X6" s="212"/>
-      <c r="Y6" s="212"/>
-      <c r="Z6" s="212"/>
-      <c r="AA6" s="212"/>
-      <c r="AB6" s="212"/>
-      <c r="AC6" s="212"/>
-      <c r="AD6" s="212"/>
-      <c r="AE6" s="212"/>
-      <c r="AF6" s="212"/>
-      <c r="AG6" s="212"/>
-      <c r="AH6" s="212"/>
-      <c r="AI6" s="212"/>
-      <c r="AJ6" s="212"/>
-      <c r="AK6" s="212"/>
-      <c r="AL6" s="212" t="s">
+      <c r="R6" s="189"/>
+      <c r="S6" s="189"/>
+      <c r="T6" s="189"/>
+      <c r="U6" s="189"/>
+      <c r="V6" s="189"/>
+      <c r="W6" s="189"/>
+      <c r="X6" s="189"/>
+      <c r="Y6" s="189"/>
+      <c r="Z6" s="189"/>
+      <c r="AA6" s="189"/>
+      <c r="AB6" s="189"/>
+      <c r="AC6" s="189"/>
+      <c r="AD6" s="189"/>
+      <c r="AE6" s="189"/>
+      <c r="AF6" s="189"/>
+      <c r="AG6" s="189"/>
+      <c r="AH6" s="189"/>
+      <c r="AI6" s="189"/>
+      <c r="AJ6" s="189"/>
+      <c r="AK6" s="189"/>
+      <c r="AL6" s="189" t="s">
         <v>19</v>
       </c>
-      <c r="AM6" s="212"/>
-      <c r="AN6" s="212"/>
-      <c r="AO6" s="212"/>
-      <c r="AP6" s="212" t="s">
+      <c r="AM6" s="189"/>
+      <c r="AN6" s="189"/>
+      <c r="AO6" s="189"/>
+      <c r="AP6" s="189" t="s">
         <v>20</v>
       </c>
-      <c r="AQ6" s="212"/>
-      <c r="AR6" s="212"/>
-      <c r="AS6" s="212" t="s">
+      <c r="AQ6" s="189"/>
+      <c r="AR6" s="189"/>
+      <c r="AS6" s="189" t="s">
         <v>21</v>
       </c>
-      <c r="AT6" s="212"/>
-      <c r="AU6" s="212"/>
-      <c r="AV6" s="212" t="s">
+      <c r="AT6" s="189"/>
+      <c r="AU6" s="189"/>
+      <c r="AV6" s="189" t="s">
         <v>22</v>
       </c>
-      <c r="AW6" s="212"/>
-      <c r="AX6" s="212"/>
-      <c r="AY6" s="212"/>
-      <c r="AZ6" s="212"/>
-      <c r="BA6" s="212"/>
+      <c r="AW6" s="189"/>
+      <c r="AX6" s="189"/>
+      <c r="AY6" s="189"/>
+      <c r="AZ6" s="189"/>
+      <c r="BA6" s="189"/>
     </row>
     <row r="7" spans="1:53">
-      <c r="A7" s="184" t="s">
+      <c r="A7" s="212" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="184"/>
-      <c r="C7" s="185" t="s">
+      <c r="B7" s="212"/>
+      <c r="C7" s="215" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="185"/>
-      <c r="E7" s="185"/>
-      <c r="F7" s="185"/>
-      <c r="G7" s="185"/>
-      <c r="H7" s="185"/>
-      <c r="I7" s="185"/>
-      <c r="J7" s="185"/>
-      <c r="K7" s="185"/>
-      <c r="L7" s="185"/>
-      <c r="M7" s="185"/>
-      <c r="N7" s="185"/>
-      <c r="O7" s="185"/>
-      <c r="P7" s="185"/>
-      <c r="Q7" s="185"/>
-      <c r="R7" s="185"/>
-      <c r="S7" s="185"/>
-      <c r="T7" s="185"/>
-      <c r="U7" s="185"/>
-      <c r="V7" s="185"/>
-      <c r="W7" s="185"/>
-      <c r="X7" s="185"/>
-      <c r="Y7" s="185"/>
-      <c r="Z7" s="185"/>
-      <c r="AA7" s="185"/>
-      <c r="AB7" s="185"/>
-      <c r="AC7" s="185"/>
-      <c r="AD7" s="185"/>
-      <c r="AE7" s="185"/>
-      <c r="AF7" s="185"/>
-      <c r="AG7" s="185"/>
-      <c r="AH7" s="185"/>
-      <c r="AI7" s="185"/>
-      <c r="AJ7" s="185"/>
-      <c r="AK7" s="185"/>
-      <c r="AL7" s="189">
+      <c r="D7" s="215"/>
+      <c r="E7" s="215"/>
+      <c r="F7" s="215"/>
+      <c r="G7" s="215"/>
+      <c r="H7" s="215"/>
+      <c r="I7" s="215"/>
+      <c r="J7" s="215"/>
+      <c r="K7" s="215"/>
+      <c r="L7" s="215"/>
+      <c r="M7" s="215"/>
+      <c r="N7" s="215"/>
+      <c r="O7" s="215"/>
+      <c r="P7" s="215"/>
+      <c r="Q7" s="215"/>
+      <c r="R7" s="215"/>
+      <c r="S7" s="215"/>
+      <c r="T7" s="215"/>
+      <c r="U7" s="215"/>
+      <c r="V7" s="215"/>
+      <c r="W7" s="215"/>
+      <c r="X7" s="215"/>
+      <c r="Y7" s="215"/>
+      <c r="Z7" s="215"/>
+      <c r="AA7" s="215"/>
+      <c r="AB7" s="215"/>
+      <c r="AC7" s="215"/>
+      <c r="AD7" s="215"/>
+      <c r="AE7" s="215"/>
+      <c r="AF7" s="215"/>
+      <c r="AG7" s="215"/>
+      <c r="AH7" s="215"/>
+      <c r="AI7" s="215"/>
+      <c r="AJ7" s="215"/>
+      <c r="AK7" s="215"/>
+      <c r="AL7" s="223">
         <v>46125</v>
       </c>
-      <c r="AM7" s="190"/>
-      <c r="AN7" s="190"/>
-      <c r="AO7" s="190"/>
-      <c r="AP7" s="185" t="s">
+      <c r="AM7" s="224"/>
+      <c r="AN7" s="224"/>
+      <c r="AO7" s="224"/>
+      <c r="AP7" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="AQ7" s="185"/>
-      <c r="AR7" s="185"/>
-      <c r="AS7" s="185"/>
-      <c r="AT7" s="185"/>
-      <c r="AU7" s="185"/>
-      <c r="AV7" s="185"/>
-      <c r="AW7" s="185"/>
-      <c r="AX7" s="185"/>
-      <c r="AY7" s="185"/>
-      <c r="AZ7" s="185"/>
-      <c r="BA7" s="185"/>
+      <c r="AQ7" s="215"/>
+      <c r="AR7" s="215"/>
+      <c r="AS7" s="215"/>
+      <c r="AT7" s="215"/>
+      <c r="AU7" s="215"/>
+      <c r="AV7" s="215"/>
+      <c r="AW7" s="215"/>
+      <c r="AX7" s="215"/>
+      <c r="AY7" s="215"/>
+      <c r="AZ7" s="215"/>
+      <c r="BA7" s="215"/>
     </row>
     <row r="8" spans="1:53" ht="25" customHeight="1">
-      <c r="A8" s="199" t="s">
+      <c r="A8" s="210" t="s">
         <v>96</v>
       </c>
-      <c r="B8" s="200"/>
-      <c r="C8" s="186" t="s">
+      <c r="B8" s="211"/>
+      <c r="C8" s="216" t="s">
         <v>119</v>
       </c>
-      <c r="D8" s="186"/>
-      <c r="E8" s="186"/>
-      <c r="F8" s="186"/>
-      <c r="G8" s="186"/>
-      <c r="H8" s="186"/>
-      <c r="I8" s="186"/>
-      <c r="J8" s="186"/>
-      <c r="K8" s="186"/>
-      <c r="L8" s="186"/>
-      <c r="M8" s="186"/>
-      <c r="N8" s="186"/>
-      <c r="O8" s="186"/>
-      <c r="P8" s="186"/>
-      <c r="Q8" s="196" t="s">
+      <c r="D8" s="216"/>
+      <c r="E8" s="216"/>
+      <c r="F8" s="216"/>
+      <c r="G8" s="216"/>
+      <c r="H8" s="216"/>
+      <c r="I8" s="216"/>
+      <c r="J8" s="216"/>
+      <c r="K8" s="216"/>
+      <c r="L8" s="216"/>
+      <c r="M8" s="216"/>
+      <c r="N8" s="216"/>
+      <c r="O8" s="216"/>
+      <c r="P8" s="216"/>
+      <c r="Q8" s="218" t="s">
         <v>98</v>
       </c>
-      <c r="R8" s="197"/>
-      <c r="S8" s="197"/>
-      <c r="T8" s="197"/>
-      <c r="U8" s="197"/>
-      <c r="V8" s="197"/>
-      <c r="W8" s="197"/>
-      <c r="X8" s="197"/>
-      <c r="Y8" s="197"/>
-      <c r="Z8" s="197"/>
-      <c r="AA8" s="197"/>
-      <c r="AB8" s="197"/>
-      <c r="AC8" s="197"/>
-      <c r="AD8" s="197"/>
-      <c r="AE8" s="197"/>
-      <c r="AF8" s="197"/>
-      <c r="AG8" s="197"/>
-      <c r="AH8" s="197"/>
-      <c r="AI8" s="197"/>
-      <c r="AJ8" s="197"/>
-      <c r="AK8" s="198"/>
-      <c r="AL8" s="191">
+      <c r="R8" s="219"/>
+      <c r="S8" s="219"/>
+      <c r="T8" s="219"/>
+      <c r="U8" s="219"/>
+      <c r="V8" s="219"/>
+      <c r="W8" s="219"/>
+      <c r="X8" s="219"/>
+      <c r="Y8" s="219"/>
+      <c r="Z8" s="219"/>
+      <c r="AA8" s="219"/>
+      <c r="AB8" s="219"/>
+      <c r="AC8" s="219"/>
+      <c r="AD8" s="219"/>
+      <c r="AE8" s="219"/>
+      <c r="AF8" s="219"/>
+      <c r="AG8" s="219"/>
+      <c r="AH8" s="219"/>
+      <c r="AI8" s="219"/>
+      <c r="AJ8" s="219"/>
+      <c r="AK8" s="220"/>
+      <c r="AL8" s="225">
         <v>46134</v>
       </c>
-      <c r="AM8" s="192"/>
-      <c r="AN8" s="192"/>
-      <c r="AO8" s="193"/>
-      <c r="AP8" s="185" t="s">
+      <c r="AM8" s="226"/>
+      <c r="AN8" s="226"/>
+      <c r="AO8" s="227"/>
+      <c r="AP8" s="215" t="s">
         <v>97</v>
       </c>
-      <c r="AQ8" s="185"/>
-      <c r="AR8" s="185"/>
-      <c r="AS8" s="185"/>
-      <c r="AT8" s="185"/>
-      <c r="AU8" s="185"/>
-      <c r="AV8" s="185"/>
-      <c r="AW8" s="185"/>
-      <c r="AX8" s="185"/>
-      <c r="AY8" s="185"/>
-      <c r="AZ8" s="185"/>
-      <c r="BA8" s="185"/>
+      <c r="AQ8" s="215"/>
+      <c r="AR8" s="215"/>
+      <c r="AS8" s="215"/>
+      <c r="AT8" s="215"/>
+      <c r="AU8" s="215"/>
+      <c r="AV8" s="215"/>
+      <c r="AW8" s="215"/>
+      <c r="AX8" s="215"/>
+      <c r="AY8" s="215"/>
+      <c r="AZ8" s="215"/>
+      <c r="BA8" s="215"/>
     </row>
     <row r="9" spans="1:53">
-      <c r="A9" s="199" t="s">
+      <c r="A9" s="210" t="s">
         <v>118</v>
       </c>
-      <c r="B9" s="200"/>
-      <c r="C9" s="186" t="s">
+      <c r="B9" s="211"/>
+      <c r="C9" s="216" t="s">
         <v>120</v>
       </c>
-      <c r="D9" s="186"/>
-      <c r="E9" s="186"/>
-      <c r="F9" s="186"/>
-      <c r="G9" s="186"/>
-      <c r="H9" s="186"/>
-      <c r="I9" s="186"/>
-      <c r="J9" s="186"/>
-      <c r="K9" s="186"/>
-      <c r="L9" s="186"/>
-      <c r="M9" s="186"/>
-      <c r="N9" s="186"/>
-      <c r="O9" s="186"/>
-      <c r="P9" s="186"/>
-      <c r="Q9" s="196" t="s">
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="216"/>
+      <c r="I9" s="216"/>
+      <c r="J9" s="216"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
+      <c r="M9" s="216"/>
+      <c r="N9" s="216"/>
+      <c r="O9" s="216"/>
+      <c r="P9" s="216"/>
+      <c r="Q9" s="218" t="s">
         <v>121</v>
       </c>
-      <c r="R9" s="197"/>
-      <c r="S9" s="197"/>
-      <c r="T9" s="197"/>
-      <c r="U9" s="197"/>
-      <c r="V9" s="197"/>
-      <c r="W9" s="197"/>
-      <c r="X9" s="197"/>
-      <c r="Y9" s="197"/>
-      <c r="Z9" s="197"/>
-      <c r="AA9" s="197"/>
-      <c r="AB9" s="197"/>
-      <c r="AC9" s="197"/>
-      <c r="AD9" s="197"/>
-      <c r="AE9" s="197"/>
-      <c r="AF9" s="197"/>
-      <c r="AG9" s="197"/>
-      <c r="AH9" s="197"/>
-      <c r="AI9" s="197"/>
-      <c r="AJ9" s="197"/>
-      <c r="AK9" s="198"/>
-      <c r="AL9" s="191">
+      <c r="R9" s="219"/>
+      <c r="S9" s="219"/>
+      <c r="T9" s="219"/>
+      <c r="U9" s="219"/>
+      <c r="V9" s="219"/>
+      <c r="W9" s="219"/>
+      <c r="X9" s="219"/>
+      <c r="Y9" s="219"/>
+      <c r="Z9" s="219"/>
+      <c r="AA9" s="219"/>
+      <c r="AB9" s="219"/>
+      <c r="AC9" s="219"/>
+      <c r="AD9" s="219"/>
+      <c r="AE9" s="219"/>
+      <c r="AF9" s="219"/>
+      <c r="AG9" s="219"/>
+      <c r="AH9" s="219"/>
+      <c r="AI9" s="219"/>
+      <c r="AJ9" s="219"/>
+      <c r="AK9" s="220"/>
+      <c r="AL9" s="225">
         <v>46162</v>
       </c>
-      <c r="AM9" s="192"/>
-      <c r="AN9" s="192"/>
-      <c r="AO9" s="193"/>
-      <c r="AP9" s="185" t="s">
+      <c r="AM9" s="226"/>
+      <c r="AN9" s="226"/>
+      <c r="AO9" s="227"/>
+      <c r="AP9" s="215" t="s">
         <v>32</v>
       </c>
-      <c r="AQ9" s="185"/>
-      <c r="AR9" s="185"/>
-      <c r="AS9" s="185"/>
-      <c r="AT9" s="185"/>
-      <c r="AU9" s="185"/>
-      <c r="AV9" s="185"/>
-      <c r="AW9" s="185"/>
-      <c r="AX9" s="185"/>
-      <c r="AY9" s="185"/>
-      <c r="AZ9" s="185"/>
-      <c r="BA9" s="185"/>
+      <c r="AQ9" s="215"/>
+      <c r="AR9" s="215"/>
+      <c r="AS9" s="215"/>
+      <c r="AT9" s="215"/>
+      <c r="AU9" s="215"/>
+      <c r="AV9" s="215"/>
+      <c r="AW9" s="215"/>
+      <c r="AX9" s="215"/>
+      <c r="AY9" s="215"/>
+      <c r="AZ9" s="215"/>
+      <c r="BA9" s="215"/>
     </row>
     <row r="10" spans="1:53">
-      <c r="A10" s="184"/>
-      <c r="B10" s="184"/>
-      <c r="C10" s="185"/>
-      <c r="D10" s="185"/>
-      <c r="E10" s="185"/>
-      <c r="F10" s="185"/>
-      <c r="G10" s="185"/>
-      <c r="H10" s="185"/>
-      <c r="I10" s="185"/>
-      <c r="J10" s="185"/>
-      <c r="K10" s="185"/>
-      <c r="L10" s="185"/>
-      <c r="M10" s="185"/>
-      <c r="N10" s="185"/>
-      <c r="O10" s="185"/>
-      <c r="P10" s="185"/>
-      <c r="Q10" s="186"/>
-      <c r="R10" s="185"/>
-      <c r="S10" s="185"/>
-      <c r="T10" s="185"/>
-      <c r="U10" s="185"/>
-      <c r="V10" s="185"/>
-      <c r="W10" s="185"/>
-      <c r="X10" s="185"/>
-      <c r="Y10" s="185"/>
-      <c r="Z10" s="185"/>
-      <c r="AA10" s="185"/>
-      <c r="AB10" s="185"/>
-      <c r="AC10" s="185"/>
-      <c r="AD10" s="185"/>
-      <c r="AE10" s="185"/>
-      <c r="AF10" s="185"/>
-      <c r="AG10" s="185"/>
-      <c r="AH10" s="185"/>
-      <c r="AI10" s="185"/>
-      <c r="AJ10" s="185"/>
-      <c r="AK10" s="185"/>
-      <c r="AL10" s="183"/>
-      <c r="AM10" s="184"/>
-      <c r="AN10" s="184"/>
-      <c r="AO10" s="184"/>
-      <c r="AP10" s="185"/>
-      <c r="AQ10" s="185"/>
-      <c r="AR10" s="185"/>
-      <c r="AS10" s="185"/>
-      <c r="AT10" s="185"/>
-      <c r="AU10" s="185"/>
-      <c r="AV10" s="185"/>
-      <c r="AW10" s="185"/>
-      <c r="AX10" s="185"/>
-      <c r="AY10" s="185"/>
-      <c r="AZ10" s="185"/>
-      <c r="BA10" s="185"/>
+      <c r="A10" s="212"/>
+      <c r="B10" s="212"/>
+      <c r="C10" s="215"/>
+      <c r="D10" s="215"/>
+      <c r="E10" s="215"/>
+      <c r="F10" s="215"/>
+      <c r="G10" s="215"/>
+      <c r="H10" s="215"/>
+      <c r="I10" s="215"/>
+      <c r="J10" s="215"/>
+      <c r="K10" s="215"/>
+      <c r="L10" s="215"/>
+      <c r="M10" s="215"/>
+      <c r="N10" s="215"/>
+      <c r="O10" s="215"/>
+      <c r="P10" s="215"/>
+      <c r="Q10" s="216"/>
+      <c r="R10" s="215"/>
+      <c r="S10" s="215"/>
+      <c r="T10" s="215"/>
+      <c r="U10" s="215"/>
+      <c r="V10" s="215"/>
+      <c r="W10" s="215"/>
+      <c r="X10" s="215"/>
+      <c r="Y10" s="215"/>
+      <c r="Z10" s="215"/>
+      <c r="AA10" s="215"/>
+      <c r="AB10" s="215"/>
+      <c r="AC10" s="215"/>
+      <c r="AD10" s="215"/>
+      <c r="AE10" s="215"/>
+      <c r="AF10" s="215"/>
+      <c r="AG10" s="215"/>
+      <c r="AH10" s="215"/>
+      <c r="AI10" s="215"/>
+      <c r="AJ10" s="215"/>
+      <c r="AK10" s="215"/>
+      <c r="AL10" s="222"/>
+      <c r="AM10" s="212"/>
+      <c r="AN10" s="212"/>
+      <c r="AO10" s="212"/>
+      <c r="AP10" s="215"/>
+      <c r="AQ10" s="215"/>
+      <c r="AR10" s="215"/>
+      <c r="AS10" s="215"/>
+      <c r="AT10" s="215"/>
+      <c r="AU10" s="215"/>
+      <c r="AV10" s="215"/>
+      <c r="AW10" s="215"/>
+      <c r="AX10" s="215"/>
+      <c r="AY10" s="215"/>
+      <c r="AZ10" s="215"/>
+      <c r="BA10" s="215"/>
     </row>
     <row r="11" spans="1:53">
-      <c r="A11" s="184"/>
-      <c r="B11" s="184"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="185"/>
-      <c r="E11" s="185"/>
-      <c r="F11" s="185"/>
-      <c r="G11" s="185"/>
-      <c r="H11" s="185"/>
-      <c r="I11" s="185"/>
-      <c r="J11" s="185"/>
-      <c r="K11" s="185"/>
-      <c r="L11" s="185"/>
-      <c r="M11" s="185"/>
-      <c r="N11" s="185"/>
-      <c r="O11" s="185"/>
-      <c r="P11" s="185"/>
-      <c r="Q11" s="186"/>
-      <c r="R11" s="185"/>
-      <c r="S11" s="185"/>
-      <c r="T11" s="185"/>
-      <c r="U11" s="185"/>
-      <c r="V11" s="185"/>
-      <c r="W11" s="185"/>
-      <c r="X11" s="185"/>
-      <c r="Y11" s="185"/>
-      <c r="Z11" s="185"/>
-      <c r="AA11" s="185"/>
-      <c r="AB11" s="185"/>
-      <c r="AC11" s="185"/>
-      <c r="AD11" s="185"/>
-      <c r="AE11" s="185"/>
-      <c r="AF11" s="185"/>
-      <c r="AG11" s="185"/>
-      <c r="AH11" s="185"/>
-      <c r="AI11" s="185"/>
-      <c r="AJ11" s="185"/>
-      <c r="AK11" s="185"/>
-      <c r="AL11" s="183"/>
-      <c r="AM11" s="184"/>
-      <c r="AN11" s="184"/>
-      <c r="AO11" s="184"/>
-      <c r="AP11" s="185"/>
-      <c r="AQ11" s="185"/>
-      <c r="AR11" s="185"/>
-      <c r="AS11" s="185"/>
-      <c r="AT11" s="185"/>
-      <c r="AU11" s="185"/>
-      <c r="AV11" s="185"/>
-      <c r="AW11" s="185"/>
-      <c r="AX11" s="185"/>
-      <c r="AY11" s="185"/>
-      <c r="AZ11" s="185"/>
-      <c r="BA11" s="185"/>
+      <c r="A11" s="212"/>
+      <c r="B11" s="212"/>
+      <c r="C11" s="216"/>
+      <c r="D11" s="215"/>
+      <c r="E11" s="215"/>
+      <c r="F11" s="215"/>
+      <c r="G11" s="215"/>
+      <c r="H11" s="215"/>
+      <c r="I11" s="215"/>
+      <c r="J11" s="215"/>
+      <c r="K11" s="215"/>
+      <c r="L11" s="215"/>
+      <c r="M11" s="215"/>
+      <c r="N11" s="215"/>
+      <c r="O11" s="215"/>
+      <c r="P11" s="215"/>
+      <c r="Q11" s="216"/>
+      <c r="R11" s="215"/>
+      <c r="S11" s="215"/>
+      <c r="T11" s="215"/>
+      <c r="U11" s="215"/>
+      <c r="V11" s="215"/>
+      <c r="W11" s="215"/>
+      <c r="X11" s="215"/>
+      <c r="Y11" s="215"/>
+      <c r="Z11" s="215"/>
+      <c r="AA11" s="215"/>
+      <c r="AB11" s="215"/>
+      <c r="AC11" s="215"/>
+      <c r="AD11" s="215"/>
+      <c r="AE11" s="215"/>
+      <c r="AF11" s="215"/>
+      <c r="AG11" s="215"/>
+      <c r="AH11" s="215"/>
+      <c r="AI11" s="215"/>
+      <c r="AJ11" s="215"/>
+      <c r="AK11" s="215"/>
+      <c r="AL11" s="222"/>
+      <c r="AM11" s="212"/>
+      <c r="AN11" s="212"/>
+      <c r="AO11" s="212"/>
+      <c r="AP11" s="215"/>
+      <c r="AQ11" s="215"/>
+      <c r="AR11" s="215"/>
+      <c r="AS11" s="215"/>
+      <c r="AT11" s="215"/>
+      <c r="AU11" s="215"/>
+      <c r="AV11" s="215"/>
+      <c r="AW11" s="215"/>
+      <c r="AX11" s="215"/>
+      <c r="AY11" s="215"/>
+      <c r="AZ11" s="215"/>
+      <c r="BA11" s="215"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="184"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
-      <c r="N12" s="185"/>
-      <c r="O12" s="185"/>
-      <c r="P12" s="185"/>
-      <c r="Q12" s="185"/>
-      <c r="R12" s="185"/>
-      <c r="S12" s="185"/>
-      <c r="T12" s="185"/>
-      <c r="U12" s="185"/>
-      <c r="V12" s="185"/>
-      <c r="W12" s="185"/>
-      <c r="X12" s="185"/>
-      <c r="Y12" s="185"/>
-      <c r="Z12" s="185"/>
-      <c r="AA12" s="185"/>
-      <c r="AB12" s="185"/>
-      <c r="AC12" s="185"/>
-      <c r="AD12" s="185"/>
-      <c r="AE12" s="185"/>
-      <c r="AF12" s="185"/>
-      <c r="AG12" s="185"/>
-      <c r="AH12" s="185"/>
-      <c r="AI12" s="185"/>
-      <c r="AJ12" s="185"/>
-      <c r="AK12" s="185"/>
-      <c r="AL12" s="183"/>
-      <c r="AM12" s="184"/>
-      <c r="AN12" s="184"/>
-      <c r="AO12" s="184"/>
-      <c r="AP12" s="185"/>
-      <c r="AQ12" s="185"/>
-      <c r="AR12" s="185"/>
-      <c r="AS12" s="185"/>
-      <c r="AT12" s="185"/>
-      <c r="AU12" s="185"/>
-      <c r="AV12" s="185"/>
-      <c r="AW12" s="185"/>
-      <c r="AX12" s="185"/>
-      <c r="AY12" s="185"/>
-      <c r="AZ12" s="185"/>
-      <c r="BA12" s="185"/>
+      <c r="A12" s="212"/>
+      <c r="B12" s="212"/>
+      <c r="C12" s="215"/>
+      <c r="D12" s="215"/>
+      <c r="E12" s="215"/>
+      <c r="F12" s="215"/>
+      <c r="G12" s="215"/>
+      <c r="H12" s="215"/>
+      <c r="I12" s="215"/>
+      <c r="J12" s="215"/>
+      <c r="K12" s="215"/>
+      <c r="L12" s="215"/>
+      <c r="M12" s="215"/>
+      <c r="N12" s="215"/>
+      <c r="O12" s="215"/>
+      <c r="P12" s="215"/>
+      <c r="Q12" s="215"/>
+      <c r="R12" s="215"/>
+      <c r="S12" s="215"/>
+      <c r="T12" s="215"/>
+      <c r="U12" s="215"/>
+      <c r="V12" s="215"/>
+      <c r="W12" s="215"/>
+      <c r="X12" s="215"/>
+      <c r="Y12" s="215"/>
+      <c r="Z12" s="215"/>
+      <c r="AA12" s="215"/>
+      <c r="AB12" s="215"/>
+      <c r="AC12" s="215"/>
+      <c r="AD12" s="215"/>
+      <c r="AE12" s="215"/>
+      <c r="AF12" s="215"/>
+      <c r="AG12" s="215"/>
+      <c r="AH12" s="215"/>
+      <c r="AI12" s="215"/>
+      <c r="AJ12" s="215"/>
+      <c r="AK12" s="215"/>
+      <c r="AL12" s="222"/>
+      <c r="AM12" s="212"/>
+      <c r="AN12" s="212"/>
+      <c r="AO12" s="212"/>
+      <c r="AP12" s="215"/>
+      <c r="AQ12" s="215"/>
+      <c r="AR12" s="215"/>
+      <c r="AS12" s="215"/>
+      <c r="AT12" s="215"/>
+      <c r="AU12" s="215"/>
+      <c r="AV12" s="215"/>
+      <c r="AW12" s="215"/>
+      <c r="AX12" s="215"/>
+      <c r="AY12" s="215"/>
+      <c r="AZ12" s="215"/>
+      <c r="BA12" s="215"/>
     </row>
     <row r="13" spans="1:53">
-      <c r="A13" s="195"/>
-      <c r="B13" s="195"/>
-      <c r="C13" s="187"/>
-      <c r="D13" s="187"/>
-      <c r="E13" s="187"/>
-      <c r="F13" s="187"/>
-      <c r="G13" s="187"/>
-      <c r="H13" s="187"/>
-      <c r="I13" s="187"/>
-      <c r="J13" s="187"/>
-      <c r="K13" s="187"/>
-      <c r="L13" s="187"/>
-      <c r="M13" s="187"/>
-      <c r="N13" s="187"/>
-      <c r="O13" s="187"/>
-      <c r="P13" s="187"/>
-      <c r="Q13" s="186"/>
-      <c r="R13" s="185"/>
-      <c r="S13" s="185"/>
-      <c r="T13" s="185"/>
-      <c r="U13" s="185"/>
-      <c r="V13" s="185"/>
-      <c r="W13" s="185"/>
-      <c r="X13" s="185"/>
-      <c r="Y13" s="185"/>
-      <c r="Z13" s="185"/>
-      <c r="AA13" s="185"/>
-      <c r="AB13" s="185"/>
-      <c r="AC13" s="185"/>
-      <c r="AD13" s="185"/>
-      <c r="AE13" s="185"/>
-      <c r="AF13" s="185"/>
-      <c r="AG13" s="185"/>
-      <c r="AH13" s="185"/>
-      <c r="AI13" s="185"/>
-      <c r="AJ13" s="185"/>
-      <c r="AK13" s="185"/>
-      <c r="AL13" s="194"/>
-      <c r="AM13" s="195"/>
-      <c r="AN13" s="195"/>
-      <c r="AO13" s="195"/>
-      <c r="AP13" s="185"/>
-      <c r="AQ13" s="185"/>
-      <c r="AR13" s="185"/>
-      <c r="AS13" s="187"/>
-      <c r="AT13" s="187"/>
-      <c r="AU13" s="187"/>
-      <c r="AV13" s="187"/>
-      <c r="AW13" s="187"/>
-      <c r="AX13" s="187"/>
-      <c r="AY13" s="187"/>
-      <c r="AZ13" s="187"/>
-      <c r="BA13" s="187"/>
+      <c r="A13" s="214"/>
+      <c r="B13" s="214"/>
+      <c r="C13" s="217"/>
+      <c r="D13" s="217"/>
+      <c r="E13" s="217"/>
+      <c r="F13" s="217"/>
+      <c r="G13" s="217"/>
+      <c r="H13" s="217"/>
+      <c r="I13" s="217"/>
+      <c r="J13" s="217"/>
+      <c r="K13" s="217"/>
+      <c r="L13" s="217"/>
+      <c r="M13" s="217"/>
+      <c r="N13" s="217"/>
+      <c r="O13" s="217"/>
+      <c r="P13" s="217"/>
+      <c r="Q13" s="216"/>
+      <c r="R13" s="215"/>
+      <c r="S13" s="215"/>
+      <c r="T13" s="215"/>
+      <c r="U13" s="215"/>
+      <c r="V13" s="215"/>
+      <c r="W13" s="215"/>
+      <c r="X13" s="215"/>
+      <c r="Y13" s="215"/>
+      <c r="Z13" s="215"/>
+      <c r="AA13" s="215"/>
+      <c r="AB13" s="215"/>
+      <c r="AC13" s="215"/>
+      <c r="AD13" s="215"/>
+      <c r="AE13" s="215"/>
+      <c r="AF13" s="215"/>
+      <c r="AG13" s="215"/>
+      <c r="AH13" s="215"/>
+      <c r="AI13" s="215"/>
+      <c r="AJ13" s="215"/>
+      <c r="AK13" s="215"/>
+      <c r="AL13" s="228"/>
+      <c r="AM13" s="214"/>
+      <c r="AN13" s="214"/>
+      <c r="AO13" s="214"/>
+      <c r="AP13" s="215"/>
+      <c r="AQ13" s="215"/>
+      <c r="AR13" s="215"/>
+      <c r="AS13" s="217"/>
+      <c r="AT13" s="217"/>
+      <c r="AU13" s="217"/>
+      <c r="AV13" s="217"/>
+      <c r="AW13" s="217"/>
+      <c r="AX13" s="217"/>
+      <c r="AY13" s="217"/>
+      <c r="AZ13" s="217"/>
+      <c r="BA13" s="217"/>
     </row>
     <row r="14" spans="1:53">
-      <c r="A14" s="184"/>
-      <c r="B14" s="184"/>
-      <c r="C14" s="185"/>
-      <c r="D14" s="185"/>
-      <c r="E14" s="185"/>
-      <c r="F14" s="185"/>
-      <c r="G14" s="185"/>
-      <c r="H14" s="185"/>
-      <c r="I14" s="185"/>
-      <c r="J14" s="185"/>
-      <c r="K14" s="185"/>
-      <c r="L14" s="185"/>
-      <c r="M14" s="185"/>
-      <c r="N14" s="185"/>
-      <c r="O14" s="185"/>
-      <c r="P14" s="185"/>
-      <c r="Q14" s="186"/>
-      <c r="R14" s="185"/>
-      <c r="S14" s="185"/>
-      <c r="T14" s="185"/>
-      <c r="U14" s="185"/>
-      <c r="V14" s="185"/>
-      <c r="W14" s="185"/>
-      <c r="X14" s="185"/>
-      <c r="Y14" s="185"/>
-      <c r="Z14" s="185"/>
-      <c r="AA14" s="185"/>
-      <c r="AB14" s="185"/>
-      <c r="AC14" s="185"/>
-      <c r="AD14" s="185"/>
-      <c r="AE14" s="185"/>
-      <c r="AF14" s="185"/>
-      <c r="AG14" s="185"/>
-      <c r="AH14" s="185"/>
-      <c r="AI14" s="185"/>
-      <c r="AJ14" s="185"/>
-      <c r="AK14" s="185"/>
-      <c r="AL14" s="183"/>
-      <c r="AM14" s="184"/>
-      <c r="AN14" s="184"/>
-      <c r="AO14" s="184"/>
-      <c r="AP14" s="185"/>
-      <c r="AQ14" s="185"/>
-      <c r="AR14" s="185"/>
-      <c r="AS14" s="185"/>
-      <c r="AT14" s="185"/>
-      <c r="AU14" s="185"/>
-      <c r="AV14" s="185"/>
-      <c r="AW14" s="185"/>
-      <c r="AX14" s="185"/>
-      <c r="AY14" s="185"/>
-      <c r="AZ14" s="185"/>
-      <c r="BA14" s="185"/>
+      <c r="A14" s="212"/>
+      <c r="B14" s="212"/>
+      <c r="C14" s="215"/>
+      <c r="D14" s="215"/>
+      <c r="E14" s="215"/>
+      <c r="F14" s="215"/>
+      <c r="G14" s="215"/>
+      <c r="H14" s="215"/>
+      <c r="I14" s="215"/>
+      <c r="J14" s="215"/>
+      <c r="K14" s="215"/>
+      <c r="L14" s="215"/>
+      <c r="M14" s="215"/>
+      <c r="N14" s="215"/>
+      <c r="O14" s="215"/>
+      <c r="P14" s="215"/>
+      <c r="Q14" s="216"/>
+      <c r="R14" s="215"/>
+      <c r="S14" s="215"/>
+      <c r="T14" s="215"/>
+      <c r="U14" s="215"/>
+      <c r="V14" s="215"/>
+      <c r="W14" s="215"/>
+      <c r="X14" s="215"/>
+      <c r="Y14" s="215"/>
+      <c r="Z14" s="215"/>
+      <c r="AA14" s="215"/>
+      <c r="AB14" s="215"/>
+      <c r="AC14" s="215"/>
+      <c r="AD14" s="215"/>
+      <c r="AE14" s="215"/>
+      <c r="AF14" s="215"/>
+      <c r="AG14" s="215"/>
+      <c r="AH14" s="215"/>
+      <c r="AI14" s="215"/>
+      <c r="AJ14" s="215"/>
+      <c r="AK14" s="215"/>
+      <c r="AL14" s="222"/>
+      <c r="AM14" s="212"/>
+      <c r="AN14" s="212"/>
+      <c r="AO14" s="212"/>
+      <c r="AP14" s="215"/>
+      <c r="AQ14" s="215"/>
+      <c r="AR14" s="215"/>
+      <c r="AS14" s="215"/>
+      <c r="AT14" s="215"/>
+      <c r="AU14" s="215"/>
+      <c r="AV14" s="215"/>
+      <c r="AW14" s="215"/>
+      <c r="AX14" s="215"/>
+      <c r="AY14" s="215"/>
+      <c r="AZ14" s="215"/>
+      <c r="BA14" s="215"/>
     </row>
     <row r="15" spans="1:53">
-      <c r="A15" s="184"/>
-      <c r="B15" s="184"/>
-      <c r="C15" s="185"/>
-      <c r="D15" s="185"/>
-      <c r="E15" s="185"/>
-      <c r="F15" s="185"/>
-      <c r="G15" s="185"/>
-      <c r="H15" s="185"/>
-      <c r="I15" s="185"/>
-      <c r="J15" s="185"/>
-      <c r="K15" s="185"/>
-      <c r="L15" s="185"/>
-      <c r="M15" s="185"/>
-      <c r="N15" s="185"/>
-      <c r="O15" s="185"/>
-      <c r="P15" s="185"/>
-      <c r="Q15" s="186"/>
-      <c r="R15" s="185"/>
-      <c r="S15" s="185"/>
-      <c r="T15" s="185"/>
-      <c r="U15" s="185"/>
-      <c r="V15" s="185"/>
-      <c r="W15" s="185"/>
-      <c r="X15" s="185"/>
-      <c r="Y15" s="185"/>
-      <c r="Z15" s="185"/>
-      <c r="AA15" s="185"/>
-      <c r="AB15" s="185"/>
-      <c r="AC15" s="185"/>
-      <c r="AD15" s="185"/>
-      <c r="AE15" s="185"/>
-      <c r="AF15" s="185"/>
-      <c r="AG15" s="185"/>
-      <c r="AH15" s="185"/>
-      <c r="AI15" s="185"/>
-      <c r="AJ15" s="185"/>
-      <c r="AK15" s="185"/>
-      <c r="AL15" s="183"/>
-      <c r="AM15" s="184"/>
-      <c r="AN15" s="184"/>
-      <c r="AO15" s="184"/>
-      <c r="AP15" s="185"/>
-      <c r="AQ15" s="185"/>
-      <c r="AR15" s="185"/>
-      <c r="AS15" s="185"/>
-      <c r="AT15" s="185"/>
-      <c r="AU15" s="185"/>
-      <c r="AV15" s="185"/>
-      <c r="AW15" s="185"/>
-      <c r="AX15" s="185"/>
-      <c r="AY15" s="185"/>
-      <c r="AZ15" s="185"/>
-      <c r="BA15" s="185"/>
+      <c r="A15" s="212"/>
+      <c r="B15" s="212"/>
+      <c r="C15" s="215"/>
+      <c r="D15" s="215"/>
+      <c r="E15" s="215"/>
+      <c r="F15" s="215"/>
+      <c r="G15" s="215"/>
+      <c r="H15" s="215"/>
+      <c r="I15" s="215"/>
+      <c r="J15" s="215"/>
+      <c r="K15" s="215"/>
+      <c r="L15" s="215"/>
+      <c r="M15" s="215"/>
+      <c r="N15" s="215"/>
+      <c r="O15" s="215"/>
+      <c r="P15" s="215"/>
+      <c r="Q15" s="216"/>
+      <c r="R15" s="215"/>
+      <c r="S15" s="215"/>
+      <c r="T15" s="215"/>
+      <c r="U15" s="215"/>
+      <c r="V15" s="215"/>
+      <c r="W15" s="215"/>
+      <c r="X15" s="215"/>
+      <c r="Y15" s="215"/>
+      <c r="Z15" s="215"/>
+      <c r="AA15" s="215"/>
+      <c r="AB15" s="215"/>
+      <c r="AC15" s="215"/>
+      <c r="AD15" s="215"/>
+      <c r="AE15" s="215"/>
+      <c r="AF15" s="215"/>
+      <c r="AG15" s="215"/>
+      <c r="AH15" s="215"/>
+      <c r="AI15" s="215"/>
+      <c r="AJ15" s="215"/>
+      <c r="AK15" s="215"/>
+      <c r="AL15" s="222"/>
+      <c r="AM15" s="212"/>
+      <c r="AN15" s="212"/>
+      <c r="AO15" s="212"/>
+      <c r="AP15" s="215"/>
+      <c r="AQ15" s="215"/>
+      <c r="AR15" s="215"/>
+      <c r="AS15" s="215"/>
+      <c r="AT15" s="215"/>
+      <c r="AU15" s="215"/>
+      <c r="AV15" s="215"/>
+      <c r="AW15" s="215"/>
+      <c r="AX15" s="215"/>
+      <c r="AY15" s="215"/>
+      <c r="AZ15" s="215"/>
+      <c r="BA15" s="215"/>
     </row>
     <row r="16" spans="1:53">
-      <c r="A16" s="184"/>
-      <c r="B16" s="184"/>
-      <c r="C16" s="185"/>
-      <c r="D16" s="185"/>
-      <c r="E16" s="185"/>
-      <c r="F16" s="185"/>
-      <c r="G16" s="185"/>
-      <c r="H16" s="185"/>
-      <c r="I16" s="185"/>
-      <c r="J16" s="185"/>
-      <c r="K16" s="185"/>
-      <c r="L16" s="185"/>
-      <c r="M16" s="185"/>
-      <c r="N16" s="185"/>
-      <c r="O16" s="185"/>
-      <c r="P16" s="185"/>
-      <c r="Q16" s="186"/>
-      <c r="R16" s="185"/>
-      <c r="S16" s="185"/>
-      <c r="T16" s="185"/>
-      <c r="U16" s="185"/>
-      <c r="V16" s="185"/>
-      <c r="W16" s="185"/>
-      <c r="X16" s="185"/>
-      <c r="Y16" s="185"/>
-      <c r="Z16" s="185"/>
-      <c r="AA16" s="185"/>
-      <c r="AB16" s="185"/>
-      <c r="AC16" s="185"/>
-      <c r="AD16" s="185"/>
-      <c r="AE16" s="185"/>
-      <c r="AF16" s="185"/>
-      <c r="AG16" s="185"/>
-      <c r="AH16" s="185"/>
-      <c r="AI16" s="185"/>
-      <c r="AJ16" s="185"/>
-      <c r="AK16" s="185"/>
-      <c r="AL16" s="183"/>
-      <c r="AM16" s="184"/>
-      <c r="AN16" s="184"/>
-      <c r="AO16" s="184"/>
-      <c r="AP16" s="185"/>
-      <c r="AQ16" s="185"/>
-      <c r="AR16" s="185"/>
-      <c r="AS16" s="185"/>
-      <c r="AT16" s="185"/>
-      <c r="AU16" s="185"/>
-      <c r="AV16" s="185"/>
-      <c r="AW16" s="185"/>
-      <c r="AX16" s="185"/>
-      <c r="AY16" s="185"/>
-      <c r="AZ16" s="185"/>
-      <c r="BA16" s="185"/>
+      <c r="A16" s="212"/>
+      <c r="B16" s="212"/>
+      <c r="C16" s="215"/>
+      <c r="D16" s="215"/>
+      <c r="E16" s="215"/>
+      <c r="F16" s="215"/>
+      <c r="G16" s="215"/>
+      <c r="H16" s="215"/>
+      <c r="I16" s="215"/>
+      <c r="J16" s="215"/>
+      <c r="K16" s="215"/>
+      <c r="L16" s="215"/>
+      <c r="M16" s="215"/>
+      <c r="N16" s="215"/>
+      <c r="O16" s="215"/>
+      <c r="P16" s="215"/>
+      <c r="Q16" s="216"/>
+      <c r="R16" s="215"/>
+      <c r="S16" s="215"/>
+      <c r="T16" s="215"/>
+      <c r="U16" s="215"/>
+      <c r="V16" s="215"/>
+      <c r="W16" s="215"/>
+      <c r="X16" s="215"/>
+      <c r="Y16" s="215"/>
+      <c r="Z16" s="215"/>
+      <c r="AA16" s="215"/>
+      <c r="AB16" s="215"/>
+      <c r="AC16" s="215"/>
+      <c r="AD16" s="215"/>
+      <c r="AE16" s="215"/>
+      <c r="AF16" s="215"/>
+      <c r="AG16" s="215"/>
+      <c r="AH16" s="215"/>
+      <c r="AI16" s="215"/>
+      <c r="AJ16" s="215"/>
+      <c r="AK16" s="215"/>
+      <c r="AL16" s="222"/>
+      <c r="AM16" s="212"/>
+      <c r="AN16" s="212"/>
+      <c r="AO16" s="212"/>
+      <c r="AP16" s="215"/>
+      <c r="AQ16" s="215"/>
+      <c r="AR16" s="215"/>
+      <c r="AS16" s="215"/>
+      <c r="AT16" s="215"/>
+      <c r="AU16" s="215"/>
+      <c r="AV16" s="215"/>
+      <c r="AW16" s="215"/>
+      <c r="AX16" s="215"/>
+      <c r="AY16" s="215"/>
+      <c r="AZ16" s="215"/>
+      <c r="BA16" s="215"/>
     </row>
     <row r="17" spans="1:53">
-      <c r="A17" s="201"/>
-      <c r="B17" s="201"/>
-      <c r="C17" s="185"/>
-      <c r="D17" s="185"/>
-      <c r="E17" s="185"/>
-      <c r="F17" s="185"/>
-      <c r="G17" s="185"/>
-      <c r="H17" s="185"/>
-      <c r="I17" s="185"/>
-      <c r="J17" s="185"/>
-      <c r="K17" s="185"/>
-      <c r="L17" s="185"/>
-      <c r="M17" s="185"/>
-      <c r="N17" s="185"/>
-      <c r="O17" s="185"/>
-      <c r="P17" s="185"/>
-      <c r="Q17" s="185"/>
-      <c r="R17" s="188"/>
-      <c r="S17" s="188"/>
-      <c r="T17" s="188"/>
-      <c r="U17" s="188"/>
-      <c r="V17" s="188"/>
-      <c r="W17" s="188"/>
-      <c r="X17" s="188"/>
-      <c r="Y17" s="188"/>
-      <c r="Z17" s="188"/>
-      <c r="AA17" s="188"/>
-      <c r="AB17" s="188"/>
-      <c r="AC17" s="188"/>
-      <c r="AD17" s="188"/>
-      <c r="AE17" s="188"/>
-      <c r="AF17" s="188"/>
-      <c r="AG17" s="188"/>
-      <c r="AH17" s="188"/>
-      <c r="AI17" s="188"/>
-      <c r="AJ17" s="188"/>
-      <c r="AK17" s="188"/>
-      <c r="AL17" s="183"/>
-      <c r="AM17" s="184"/>
-      <c r="AN17" s="184"/>
-      <c r="AO17" s="184"/>
-      <c r="AP17" s="185"/>
-      <c r="AQ17" s="188"/>
-      <c r="AR17" s="188"/>
-      <c r="AS17" s="188"/>
-      <c r="AT17" s="188"/>
-      <c r="AU17" s="188"/>
-      <c r="AV17" s="188"/>
-      <c r="AW17" s="188"/>
-      <c r="AX17" s="188"/>
-      <c r="AY17" s="188"/>
-      <c r="AZ17" s="188"/>
-      <c r="BA17" s="188"/>
+      <c r="A17" s="213"/>
+      <c r="B17" s="213"/>
+      <c r="C17" s="215"/>
+      <c r="D17" s="215"/>
+      <c r="E17" s="215"/>
+      <c r="F17" s="215"/>
+      <c r="G17" s="215"/>
+      <c r="H17" s="215"/>
+      <c r="I17" s="215"/>
+      <c r="J17" s="215"/>
+      <c r="K17" s="215"/>
+      <c r="L17" s="215"/>
+      <c r="M17" s="215"/>
+      <c r="N17" s="215"/>
+      <c r="O17" s="215"/>
+      <c r="P17" s="215"/>
+      <c r="Q17" s="215"/>
+      <c r="R17" s="221"/>
+      <c r="S17" s="221"/>
+      <c r="T17" s="221"/>
+      <c r="U17" s="221"/>
+      <c r="V17" s="221"/>
+      <c r="W17" s="221"/>
+      <c r="X17" s="221"/>
+      <c r="Y17" s="221"/>
+      <c r="Z17" s="221"/>
+      <c r="AA17" s="221"/>
+      <c r="AB17" s="221"/>
+      <c r="AC17" s="221"/>
+      <c r="AD17" s="221"/>
+      <c r="AE17" s="221"/>
+      <c r="AF17" s="221"/>
+      <c r="AG17" s="221"/>
+      <c r="AH17" s="221"/>
+      <c r="AI17" s="221"/>
+      <c r="AJ17" s="221"/>
+      <c r="AK17" s="221"/>
+      <c r="AL17" s="222"/>
+      <c r="AM17" s="212"/>
+      <c r="AN17" s="212"/>
+      <c r="AO17" s="212"/>
+      <c r="AP17" s="215"/>
+      <c r="AQ17" s="221"/>
+      <c r="AR17" s="221"/>
+      <c r="AS17" s="221"/>
+      <c r="AT17" s="221"/>
+      <c r="AU17" s="221"/>
+      <c r="AV17" s="221"/>
+      <c r="AW17" s="221"/>
+      <c r="AX17" s="221"/>
+      <c r="AY17" s="221"/>
+      <c r="AZ17" s="221"/>
+      <c r="BA17" s="221"/>
     </row>
     <row r="18" spans="1:53">
-      <c r="A18" s="201"/>
-      <c r="B18" s="201"/>
-      <c r="C18" s="185"/>
-      <c r="D18" s="185"/>
-      <c r="E18" s="185"/>
-      <c r="F18" s="185"/>
-      <c r="G18" s="185"/>
-      <c r="H18" s="185"/>
-      <c r="I18" s="185"/>
-      <c r="J18" s="185"/>
-      <c r="K18" s="185"/>
-      <c r="L18" s="185"/>
-      <c r="M18" s="185"/>
-      <c r="N18" s="185"/>
-      <c r="O18" s="185"/>
-      <c r="P18" s="185"/>
-      <c r="Q18" s="185"/>
-      <c r="R18" s="188"/>
-      <c r="S18" s="188"/>
-      <c r="T18" s="188"/>
-      <c r="U18" s="188"/>
-      <c r="V18" s="188"/>
-      <c r="W18" s="188"/>
-      <c r="X18" s="188"/>
-      <c r="Y18" s="188"/>
-      <c r="Z18" s="188"/>
-      <c r="AA18" s="188"/>
-      <c r="AB18" s="188"/>
-      <c r="AC18" s="188"/>
-      <c r="AD18" s="188"/>
-      <c r="AE18" s="188"/>
-      <c r="AF18" s="188"/>
-      <c r="AG18" s="188"/>
-      <c r="AH18" s="188"/>
-      <c r="AI18" s="188"/>
-      <c r="AJ18" s="188"/>
-      <c r="AK18" s="188"/>
-      <c r="AL18" s="183"/>
-      <c r="AM18" s="184"/>
-      <c r="AN18" s="184"/>
-      <c r="AO18" s="184"/>
-      <c r="AP18" s="185"/>
-      <c r="AQ18" s="188"/>
-      <c r="AR18" s="188"/>
-      <c r="AS18" s="188"/>
-      <c r="AT18" s="188"/>
-      <c r="AU18" s="188"/>
-      <c r="AV18" s="188"/>
-      <c r="AW18" s="188"/>
-      <c r="AX18" s="188"/>
-      <c r="AY18" s="188"/>
-      <c r="AZ18" s="188"/>
-      <c r="BA18" s="188"/>
+      <c r="A18" s="213"/>
+      <c r="B18" s="213"/>
+      <c r="C18" s="215"/>
+      <c r="D18" s="215"/>
+      <c r="E18" s="215"/>
+      <c r="F18" s="215"/>
+      <c r="G18" s="215"/>
+      <c r="H18" s="215"/>
+      <c r="I18" s="215"/>
+      <c r="J18" s="215"/>
+      <c r="K18" s="215"/>
+      <c r="L18" s="215"/>
+      <c r="M18" s="215"/>
+      <c r="N18" s="215"/>
+      <c r="O18" s="215"/>
+      <c r="P18" s="215"/>
+      <c r="Q18" s="215"/>
+      <c r="R18" s="221"/>
+      <c r="S18" s="221"/>
+      <c r="T18" s="221"/>
+      <c r="U18" s="221"/>
+      <c r="V18" s="221"/>
+      <c r="W18" s="221"/>
+      <c r="X18" s="221"/>
+      <c r="Y18" s="221"/>
+      <c r="Z18" s="221"/>
+      <c r="AA18" s="221"/>
+      <c r="AB18" s="221"/>
+      <c r="AC18" s="221"/>
+      <c r="AD18" s="221"/>
+      <c r="AE18" s="221"/>
+      <c r="AF18" s="221"/>
+      <c r="AG18" s="221"/>
+      <c r="AH18" s="221"/>
+      <c r="AI18" s="221"/>
+      <c r="AJ18" s="221"/>
+      <c r="AK18" s="221"/>
+      <c r="AL18" s="222"/>
+      <c r="AM18" s="212"/>
+      <c r="AN18" s="212"/>
+      <c r="AO18" s="212"/>
+      <c r="AP18" s="215"/>
+      <c r="AQ18" s="221"/>
+      <c r="AR18" s="221"/>
+      <c r="AS18" s="221"/>
+      <c r="AT18" s="221"/>
+      <c r="AU18" s="221"/>
+      <c r="AV18" s="221"/>
+      <c r="AW18" s="221"/>
+      <c r="AX18" s="221"/>
+      <c r="AY18" s="221"/>
+      <c r="AZ18" s="221"/>
+      <c r="BA18" s="221"/>
     </row>
     <row r="19" spans="1:53">
-      <c r="A19" s="184"/>
-      <c r="B19" s="184"/>
-      <c r="C19" s="185"/>
-      <c r="D19" s="185"/>
-      <c r="E19" s="185"/>
-      <c r="F19" s="185"/>
-      <c r="G19" s="185"/>
-      <c r="H19" s="185"/>
-      <c r="I19" s="185"/>
-      <c r="J19" s="185"/>
-      <c r="K19" s="185"/>
-      <c r="L19" s="185"/>
-      <c r="M19" s="185"/>
-      <c r="N19" s="185"/>
-      <c r="O19" s="185"/>
-      <c r="P19" s="185"/>
-      <c r="Q19" s="185"/>
-      <c r="R19" s="185"/>
-      <c r="S19" s="185"/>
-      <c r="T19" s="185"/>
-      <c r="U19" s="185"/>
-      <c r="V19" s="185"/>
-      <c r="W19" s="185"/>
-      <c r="X19" s="185"/>
-      <c r="Y19" s="185"/>
-      <c r="Z19" s="185"/>
-      <c r="AA19" s="185"/>
-      <c r="AB19" s="185"/>
-      <c r="AC19" s="185"/>
-      <c r="AD19" s="185"/>
-      <c r="AE19" s="185"/>
-      <c r="AF19" s="185"/>
-      <c r="AG19" s="185"/>
-      <c r="AH19" s="185"/>
-      <c r="AI19" s="185"/>
-      <c r="AJ19" s="185"/>
-      <c r="AK19" s="185"/>
-      <c r="AL19" s="183"/>
-      <c r="AM19" s="183"/>
-      <c r="AN19" s="183"/>
-      <c r="AO19" s="183"/>
-      <c r="AP19" s="185"/>
-      <c r="AQ19" s="185"/>
-      <c r="AR19" s="185"/>
-      <c r="AS19" s="185"/>
-      <c r="AT19" s="185"/>
-      <c r="AU19" s="185"/>
-      <c r="AV19" s="185"/>
-      <c r="AW19" s="185"/>
-      <c r="AX19" s="185"/>
-      <c r="AY19" s="185"/>
-      <c r="AZ19" s="185"/>
-      <c r="BA19" s="185"/>
+      <c r="A19" s="212"/>
+      <c r="B19" s="212"/>
+      <c r="C19" s="215"/>
+      <c r="D19" s="215"/>
+      <c r="E19" s="215"/>
+      <c r="F19" s="215"/>
+      <c r="G19" s="215"/>
+      <c r="H19" s="215"/>
+      <c r="I19" s="215"/>
+      <c r="J19" s="215"/>
+      <c r="K19" s="215"/>
+      <c r="L19" s="215"/>
+      <c r="M19" s="215"/>
+      <c r="N19" s="215"/>
+      <c r="O19" s="215"/>
+      <c r="P19" s="215"/>
+      <c r="Q19" s="215"/>
+      <c r="R19" s="215"/>
+      <c r="S19" s="215"/>
+      <c r="T19" s="215"/>
+      <c r="U19" s="215"/>
+      <c r="V19" s="215"/>
+      <c r="W19" s="215"/>
+      <c r="X19" s="215"/>
+      <c r="Y19" s="215"/>
+      <c r="Z19" s="215"/>
+      <c r="AA19" s="215"/>
+      <c r="AB19" s="215"/>
+      <c r="AC19" s="215"/>
+      <c r="AD19" s="215"/>
+      <c r="AE19" s="215"/>
+      <c r="AF19" s="215"/>
+      <c r="AG19" s="215"/>
+      <c r="AH19" s="215"/>
+      <c r="AI19" s="215"/>
+      <c r="AJ19" s="215"/>
+      <c r="AK19" s="215"/>
+      <c r="AL19" s="222"/>
+      <c r="AM19" s="222"/>
+      <c r="AN19" s="222"/>
+      <c r="AO19" s="222"/>
+      <c r="AP19" s="215"/>
+      <c r="AQ19" s="215"/>
+      <c r="AR19" s="215"/>
+      <c r="AS19" s="215"/>
+      <c r="AT19" s="215"/>
+      <c r="AU19" s="215"/>
+      <c r="AV19" s="215"/>
+      <c r="AW19" s="215"/>
+      <c r="AX19" s="215"/>
+      <c r="AY19" s="215"/>
+      <c r="AZ19" s="215"/>
+      <c r="BA19" s="215"/>
     </row>
     <row r="20" spans="1:53">
-      <c r="A20" s="184"/>
-      <c r="B20" s="184"/>
-      <c r="C20" s="185"/>
-      <c r="D20" s="185"/>
-      <c r="E20" s="185"/>
-      <c r="F20" s="185"/>
-      <c r="G20" s="185"/>
-      <c r="H20" s="185"/>
-      <c r="I20" s="185"/>
-      <c r="J20" s="185"/>
-      <c r="K20" s="185"/>
-      <c r="L20" s="185"/>
-      <c r="M20" s="185"/>
-      <c r="N20" s="185"/>
-      <c r="O20" s="185"/>
-      <c r="P20" s="185"/>
-      <c r="Q20" s="185"/>
-      <c r="R20" s="185"/>
-      <c r="S20" s="185"/>
-      <c r="T20" s="185"/>
-      <c r="U20" s="185"/>
-      <c r="V20" s="185"/>
-      <c r="W20" s="185"/>
-      <c r="X20" s="185"/>
-      <c r="Y20" s="185"/>
-      <c r="Z20" s="185"/>
-      <c r="AA20" s="185"/>
-      <c r="AB20" s="185"/>
-      <c r="AC20" s="185"/>
-      <c r="AD20" s="185"/>
-      <c r="AE20" s="185"/>
-      <c r="AF20" s="185"/>
-      <c r="AG20" s="185"/>
-      <c r="AH20" s="185"/>
-      <c r="AI20" s="185"/>
-      <c r="AJ20" s="185"/>
-      <c r="AK20" s="185"/>
-      <c r="AL20" s="183"/>
-      <c r="AM20" s="183"/>
-      <c r="AN20" s="183"/>
-      <c r="AO20" s="183"/>
-      <c r="AP20" s="185"/>
-      <c r="AQ20" s="185"/>
-      <c r="AR20" s="185"/>
-      <c r="AS20" s="185"/>
-      <c r="AT20" s="185"/>
-      <c r="AU20" s="185"/>
-      <c r="AV20" s="185"/>
-      <c r="AW20" s="185"/>
-      <c r="AX20" s="185"/>
-      <c r="AY20" s="185"/>
-      <c r="AZ20" s="185"/>
-      <c r="BA20" s="185"/>
+      <c r="A20" s="212"/>
+      <c r="B20" s="212"/>
+      <c r="C20" s="215"/>
+      <c r="D20" s="215"/>
+      <c r="E20" s="215"/>
+      <c r="F20" s="215"/>
+      <c r="G20" s="215"/>
+      <c r="H20" s="215"/>
+      <c r="I20" s="215"/>
+      <c r="J20" s="215"/>
+      <c r="K20" s="215"/>
+      <c r="L20" s="215"/>
+      <c r="M20" s="215"/>
+      <c r="N20" s="215"/>
+      <c r="O20" s="215"/>
+      <c r="P20" s="215"/>
+      <c r="Q20" s="215"/>
+      <c r="R20" s="215"/>
+      <c r="S20" s="215"/>
+      <c r="T20" s="215"/>
+      <c r="U20" s="215"/>
+      <c r="V20" s="215"/>
+      <c r="W20" s="215"/>
+      <c r="X20" s="215"/>
+      <c r="Y20" s="215"/>
+      <c r="Z20" s="215"/>
+      <c r="AA20" s="215"/>
+      <c r="AB20" s="215"/>
+      <c r="AC20" s="215"/>
+      <c r="AD20" s="215"/>
+      <c r="AE20" s="215"/>
+      <c r="AF20" s="215"/>
+      <c r="AG20" s="215"/>
+      <c r="AH20" s="215"/>
+      <c r="AI20" s="215"/>
+      <c r="AJ20" s="215"/>
+      <c r="AK20" s="215"/>
+      <c r="AL20" s="222"/>
+      <c r="AM20" s="222"/>
+      <c r="AN20" s="222"/>
+      <c r="AO20" s="222"/>
+      <c r="AP20" s="215"/>
+      <c r="AQ20" s="215"/>
+      <c r="AR20" s="215"/>
+      <c r="AS20" s="215"/>
+      <c r="AT20" s="215"/>
+      <c r="AU20" s="215"/>
+      <c r="AV20" s="215"/>
+      <c r="AW20" s="215"/>
+      <c r="AX20" s="215"/>
+      <c r="AY20" s="215"/>
+      <c r="AZ20" s="215"/>
+      <c r="BA20" s="215"/>
     </row>
     <row r="21" spans="1:53" ht="13.5" customHeight="1">
-      <c r="A21" s="184"/>
-      <c r="B21" s="184"/>
-      <c r="C21" s="185"/>
-      <c r="D21" s="185"/>
-      <c r="E21" s="185"/>
-      <c r="F21" s="185"/>
-      <c r="G21" s="185"/>
-      <c r="H21" s="185"/>
-      <c r="I21" s="185"/>
-      <c r="J21" s="185"/>
-      <c r="K21" s="185"/>
-      <c r="L21" s="185"/>
-      <c r="M21" s="185"/>
-      <c r="N21" s="185"/>
-      <c r="O21" s="185"/>
-      <c r="P21" s="185"/>
-      <c r="Q21" s="185"/>
-      <c r="R21" s="188"/>
-      <c r="S21" s="188"/>
-      <c r="T21" s="188"/>
-      <c r="U21" s="188"/>
-      <c r="V21" s="188"/>
-      <c r="W21" s="188"/>
-      <c r="X21" s="188"/>
-      <c r="Y21" s="188"/>
-      <c r="Z21" s="188"/>
-      <c r="AA21" s="188"/>
-      <c r="AB21" s="188"/>
-      <c r="AC21" s="188"/>
-      <c r="AD21" s="188"/>
-      <c r="AE21" s="188"/>
-      <c r="AF21" s="188"/>
-      <c r="AG21" s="188"/>
-      <c r="AH21" s="188"/>
-      <c r="AI21" s="188"/>
-      <c r="AJ21" s="188"/>
-      <c r="AK21" s="188"/>
-      <c r="AL21" s="183"/>
-      <c r="AM21" s="183"/>
-      <c r="AN21" s="183"/>
-      <c r="AO21" s="183"/>
-      <c r="AP21" s="185"/>
-      <c r="AQ21" s="185"/>
-      <c r="AR21" s="185"/>
-      <c r="AS21" s="185"/>
-      <c r="AT21" s="185"/>
-      <c r="AU21" s="185"/>
-      <c r="AV21" s="185"/>
-      <c r="AW21" s="185"/>
-      <c r="AX21" s="185"/>
-      <c r="AY21" s="185"/>
-      <c r="AZ21" s="185"/>
-      <c r="BA21" s="185"/>
+      <c r="A21" s="212"/>
+      <c r="B21" s="212"/>
+      <c r="C21" s="215"/>
+      <c r="D21" s="215"/>
+      <c r="E21" s="215"/>
+      <c r="F21" s="215"/>
+      <c r="G21" s="215"/>
+      <c r="H21" s="215"/>
+      <c r="I21" s="215"/>
+      <c r="J21" s="215"/>
+      <c r="K21" s="215"/>
+      <c r="L21" s="215"/>
+      <c r="M21" s="215"/>
+      <c r="N21" s="215"/>
+      <c r="O21" s="215"/>
+      <c r="P21" s="215"/>
+      <c r="Q21" s="215"/>
+      <c r="R21" s="221"/>
+      <c r="S21" s="221"/>
+      <c r="T21" s="221"/>
+      <c r="U21" s="221"/>
+      <c r="V21" s="221"/>
+      <c r="W21" s="221"/>
+      <c r="X21" s="221"/>
+      <c r="Y21" s="221"/>
+      <c r="Z21" s="221"/>
+      <c r="AA21" s="221"/>
+      <c r="AB21" s="221"/>
+      <c r="AC21" s="221"/>
+      <c r="AD21" s="221"/>
+      <c r="AE21" s="221"/>
+      <c r="AF21" s="221"/>
+      <c r="AG21" s="221"/>
+      <c r="AH21" s="221"/>
+      <c r="AI21" s="221"/>
+      <c r="AJ21" s="221"/>
+      <c r="AK21" s="221"/>
+      <c r="AL21" s="222"/>
+      <c r="AM21" s="222"/>
+      <c r="AN21" s="222"/>
+      <c r="AO21" s="222"/>
+      <c r="AP21" s="215"/>
+      <c r="AQ21" s="215"/>
+      <c r="AR21" s="215"/>
+      <c r="AS21" s="215"/>
+      <c r="AT21" s="215"/>
+      <c r="AU21" s="215"/>
+      <c r="AV21" s="215"/>
+      <c r="AW21" s="215"/>
+      <c r="AX21" s="215"/>
+      <c r="AY21" s="215"/>
+      <c r="AZ21" s="215"/>
+      <c r="BA21" s="215"/>
     </row>
     <row r="22" spans="1:53">
-      <c r="A22" s="184"/>
-      <c r="B22" s="184"/>
-      <c r="C22" s="185"/>
-      <c r="D22" s="185"/>
-      <c r="E22" s="185"/>
-      <c r="F22" s="185"/>
-      <c r="G22" s="185"/>
-      <c r="H22" s="185"/>
-      <c r="I22" s="185"/>
-      <c r="J22" s="185"/>
-      <c r="K22" s="185"/>
-      <c r="L22" s="185"/>
-      <c r="M22" s="185"/>
-      <c r="N22" s="185"/>
-      <c r="O22" s="185"/>
-      <c r="P22" s="185"/>
-      <c r="Q22" s="185"/>
-      <c r="R22" s="185"/>
-      <c r="S22" s="185"/>
-      <c r="T22" s="185"/>
-      <c r="U22" s="185"/>
-      <c r="V22" s="185"/>
-      <c r="W22" s="185"/>
-      <c r="X22" s="185"/>
-      <c r="Y22" s="185"/>
-      <c r="Z22" s="185"/>
-      <c r="AA22" s="185"/>
-      <c r="AB22" s="185"/>
-      <c r="AC22" s="185"/>
-      <c r="AD22" s="185"/>
-      <c r="AE22" s="185"/>
-      <c r="AF22" s="185"/>
-      <c r="AG22" s="185"/>
-      <c r="AH22" s="185"/>
-      <c r="AI22" s="185"/>
-      <c r="AJ22" s="185"/>
-      <c r="AK22" s="185"/>
-      <c r="AL22" s="183"/>
-      <c r="AM22" s="183"/>
-      <c r="AN22" s="183"/>
-      <c r="AO22" s="183"/>
-      <c r="AP22" s="185"/>
-      <c r="AQ22" s="185"/>
-      <c r="AR22" s="185"/>
-      <c r="AS22" s="185"/>
-      <c r="AT22" s="185"/>
-      <c r="AU22" s="185"/>
-      <c r="AV22" s="185"/>
-      <c r="AW22" s="185"/>
-      <c r="AX22" s="185"/>
-      <c r="AY22" s="185"/>
-      <c r="AZ22" s="185"/>
-      <c r="BA22" s="185"/>
+      <c r="A22" s="212"/>
+      <c r="B22" s="212"/>
+      <c r="C22" s="215"/>
+      <c r="D22" s="215"/>
+      <c r="E22" s="215"/>
+      <c r="F22" s="215"/>
+      <c r="G22" s="215"/>
+      <c r="H22" s="215"/>
+      <c r="I22" s="215"/>
+      <c r="J22" s="215"/>
+      <c r="K22" s="215"/>
+      <c r="L22" s="215"/>
+      <c r="M22" s="215"/>
+      <c r="N22" s="215"/>
+      <c r="O22" s="215"/>
+      <c r="P22" s="215"/>
+      <c r="Q22" s="215"/>
+      <c r="R22" s="215"/>
+      <c r="S22" s="215"/>
+      <c r="T22" s="215"/>
+      <c r="U22" s="215"/>
+      <c r="V22" s="215"/>
+      <c r="W22" s="215"/>
+      <c r="X22" s="215"/>
+      <c r="Y22" s="215"/>
+      <c r="Z22" s="215"/>
+      <c r="AA22" s="215"/>
+      <c r="AB22" s="215"/>
+      <c r="AC22" s="215"/>
+      <c r="AD22" s="215"/>
+      <c r="AE22" s="215"/>
+      <c r="AF22" s="215"/>
+      <c r="AG22" s="215"/>
+      <c r="AH22" s="215"/>
+      <c r="AI22" s="215"/>
+      <c r="AJ22" s="215"/>
+      <c r="AK22" s="215"/>
+      <c r="AL22" s="222"/>
+      <c r="AM22" s="222"/>
+      <c r="AN22" s="222"/>
+      <c r="AO22" s="222"/>
+      <c r="AP22" s="215"/>
+      <c r="AQ22" s="215"/>
+      <c r="AR22" s="215"/>
+      <c r="AS22" s="215"/>
+      <c r="AT22" s="215"/>
+      <c r="AU22" s="215"/>
+      <c r="AV22" s="215"/>
+      <c r="AW22" s="215"/>
+      <c r="AX22" s="215"/>
+      <c r="AY22" s="215"/>
+      <c r="AZ22" s="215"/>
+      <c r="BA22" s="215"/>
     </row>
     <row r="23" spans="1:53">
-      <c r="A23" s="184"/>
-      <c r="B23" s="184"/>
-      <c r="C23" s="185"/>
-      <c r="D23" s="185"/>
-      <c r="E23" s="185"/>
-      <c r="F23" s="185"/>
-      <c r="G23" s="185"/>
-      <c r="H23" s="185"/>
-      <c r="I23" s="185"/>
-      <c r="J23" s="185"/>
-      <c r="K23" s="185"/>
-      <c r="L23" s="185"/>
-      <c r="M23" s="185"/>
-      <c r="N23" s="185"/>
-      <c r="O23" s="185"/>
-      <c r="P23" s="185"/>
-      <c r="Q23" s="185"/>
-      <c r="R23" s="188"/>
-      <c r="S23" s="188"/>
-      <c r="T23" s="188"/>
-      <c r="U23" s="188"/>
-      <c r="V23" s="188"/>
-      <c r="W23" s="188"/>
-      <c r="X23" s="188"/>
-      <c r="Y23" s="188"/>
-      <c r="Z23" s="188"/>
-      <c r="AA23" s="188"/>
-      <c r="AB23" s="188"/>
-      <c r="AC23" s="188"/>
-      <c r="AD23" s="188"/>
-      <c r="AE23" s="188"/>
-      <c r="AF23" s="188"/>
-      <c r="AG23" s="188"/>
-      <c r="AH23" s="188"/>
-      <c r="AI23" s="188"/>
-      <c r="AJ23" s="188"/>
-      <c r="AK23" s="188"/>
-      <c r="AL23" s="183"/>
-      <c r="AM23" s="183"/>
-      <c r="AN23" s="183"/>
-      <c r="AO23" s="183"/>
-      <c r="AP23" s="185"/>
-      <c r="AQ23" s="185"/>
-      <c r="AR23" s="185"/>
-      <c r="AS23" s="185"/>
-      <c r="AT23" s="185"/>
-      <c r="AU23" s="185"/>
-      <c r="AV23" s="185"/>
-      <c r="AW23" s="185"/>
-      <c r="AX23" s="185"/>
-      <c r="AY23" s="185"/>
-      <c r="AZ23" s="185"/>
-      <c r="BA23" s="185"/>
+      <c r="A23" s="212"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="215"/>
+      <c r="D23" s="215"/>
+      <c r="E23" s="215"/>
+      <c r="F23" s="215"/>
+      <c r="G23" s="215"/>
+      <c r="H23" s="215"/>
+      <c r="I23" s="215"/>
+      <c r="J23" s="215"/>
+      <c r="K23" s="215"/>
+      <c r="L23" s="215"/>
+      <c r="M23" s="215"/>
+      <c r="N23" s="215"/>
+      <c r="O23" s="215"/>
+      <c r="P23" s="215"/>
+      <c r="Q23" s="215"/>
+      <c r="R23" s="221"/>
+      <c r="S23" s="221"/>
+      <c r="T23" s="221"/>
+      <c r="U23" s="221"/>
+      <c r="V23" s="221"/>
+      <c r="W23" s="221"/>
+      <c r="X23" s="221"/>
+      <c r="Y23" s="221"/>
+      <c r="Z23" s="221"/>
+      <c r="AA23" s="221"/>
+      <c r="AB23" s="221"/>
+      <c r="AC23" s="221"/>
+      <c r="AD23" s="221"/>
+      <c r="AE23" s="221"/>
+      <c r="AF23" s="221"/>
+      <c r="AG23" s="221"/>
+      <c r="AH23" s="221"/>
+      <c r="AI23" s="221"/>
+      <c r="AJ23" s="221"/>
+      <c r="AK23" s="221"/>
+      <c r="AL23" s="222"/>
+      <c r="AM23" s="222"/>
+      <c r="AN23" s="222"/>
+      <c r="AO23" s="222"/>
+      <c r="AP23" s="215"/>
+      <c r="AQ23" s="215"/>
+      <c r="AR23" s="215"/>
+      <c r="AS23" s="215"/>
+      <c r="AT23" s="215"/>
+      <c r="AU23" s="215"/>
+      <c r="AV23" s="215"/>
+      <c r="AW23" s="215"/>
+      <c r="AX23" s="215"/>
+      <c r="AY23" s="215"/>
+      <c r="AZ23" s="215"/>
+      <c r="BA23" s="215"/>
     </row>
     <row r="24" spans="1:53">
-      <c r="A24" s="184"/>
-      <c r="B24" s="184"/>
-      <c r="C24" s="185"/>
-      <c r="D24" s="185"/>
-      <c r="E24" s="185"/>
-      <c r="F24" s="185"/>
-      <c r="G24" s="185"/>
-      <c r="H24" s="185"/>
-      <c r="I24" s="185"/>
-      <c r="J24" s="185"/>
-      <c r="K24" s="185"/>
-      <c r="L24" s="185"/>
-      <c r="M24" s="185"/>
-      <c r="N24" s="185"/>
-      <c r="O24" s="185"/>
-      <c r="P24" s="185"/>
-      <c r="Q24" s="185"/>
-      <c r="R24" s="185"/>
-      <c r="S24" s="185"/>
-      <c r="T24" s="185"/>
-      <c r="U24" s="185"/>
-      <c r="V24" s="185"/>
-      <c r="W24" s="185"/>
-      <c r="X24" s="185"/>
-      <c r="Y24" s="185"/>
-      <c r="Z24" s="185"/>
-      <c r="AA24" s="185"/>
-      <c r="AB24" s="185"/>
-      <c r="AC24" s="185"/>
-      <c r="AD24" s="185"/>
-      <c r="AE24" s="185"/>
-      <c r="AF24" s="185"/>
-      <c r="AG24" s="185"/>
-      <c r="AH24" s="185"/>
-      <c r="AI24" s="185"/>
-      <c r="AJ24" s="185"/>
-      <c r="AK24" s="185"/>
-      <c r="AL24" s="183"/>
-      <c r="AM24" s="183"/>
-      <c r="AN24" s="183"/>
-      <c r="AO24" s="183"/>
-      <c r="AP24" s="185"/>
-      <c r="AQ24" s="185"/>
-      <c r="AR24" s="185"/>
-      <c r="AS24" s="185"/>
-      <c r="AT24" s="185"/>
-      <c r="AU24" s="185"/>
-      <c r="AV24" s="185"/>
-      <c r="AW24" s="185"/>
-      <c r="AX24" s="185"/>
-      <c r="AY24" s="185"/>
-      <c r="AZ24" s="185"/>
-      <c r="BA24" s="185"/>
+      <c r="A24" s="212"/>
+      <c r="B24" s="212"/>
+      <c r="C24" s="215"/>
+      <c r="D24" s="215"/>
+      <c r="E24" s="215"/>
+      <c r="F24" s="215"/>
+      <c r="G24" s="215"/>
+      <c r="H24" s="215"/>
+      <c r="I24" s="215"/>
+      <c r="J24" s="215"/>
+      <c r="K24" s="215"/>
+      <c r="L24" s="215"/>
+      <c r="M24" s="215"/>
+      <c r="N24" s="215"/>
+      <c r="O24" s="215"/>
+      <c r="P24" s="215"/>
+      <c r="Q24" s="215"/>
+      <c r="R24" s="215"/>
+      <c r="S24" s="215"/>
+      <c r="T24" s="215"/>
+      <c r="U24" s="215"/>
+      <c r="V24" s="215"/>
+      <c r="W24" s="215"/>
+      <c r="X24" s="215"/>
+      <c r="Y24" s="215"/>
+      <c r="Z24" s="215"/>
+      <c r="AA24" s="215"/>
+      <c r="AB24" s="215"/>
+      <c r="AC24" s="215"/>
+      <c r="AD24" s="215"/>
+      <c r="AE24" s="215"/>
+      <c r="AF24" s="215"/>
+      <c r="AG24" s="215"/>
+      <c r="AH24" s="215"/>
+      <c r="AI24" s="215"/>
+      <c r="AJ24" s="215"/>
+      <c r="AK24" s="215"/>
+      <c r="AL24" s="222"/>
+      <c r="AM24" s="222"/>
+      <c r="AN24" s="222"/>
+      <c r="AO24" s="222"/>
+      <c r="AP24" s="215"/>
+      <c r="AQ24" s="215"/>
+      <c r="AR24" s="215"/>
+      <c r="AS24" s="215"/>
+      <c r="AT24" s="215"/>
+      <c r="AU24" s="215"/>
+      <c r="AV24" s="215"/>
+      <c r="AW24" s="215"/>
+      <c r="AX24" s="215"/>
+      <c r="AY24" s="215"/>
+      <c r="AZ24" s="215"/>
+      <c r="BA24" s="215"/>
     </row>
     <row r="25" spans="1:53">
-      <c r="A25" s="184"/>
-      <c r="B25" s="184"/>
-      <c r="C25" s="185"/>
-      <c r="D25" s="185"/>
-      <c r="E25" s="185"/>
-      <c r="F25" s="185"/>
-      <c r="G25" s="185"/>
-      <c r="H25" s="185"/>
-      <c r="I25" s="185"/>
-      <c r="J25" s="185"/>
-      <c r="K25" s="185"/>
-      <c r="L25" s="185"/>
-      <c r="M25" s="185"/>
-      <c r="N25" s="185"/>
-      <c r="O25" s="185"/>
-      <c r="P25" s="185"/>
-      <c r="Q25" s="185"/>
-      <c r="R25" s="185"/>
-      <c r="S25" s="185"/>
-      <c r="T25" s="185"/>
-      <c r="U25" s="185"/>
-      <c r="V25" s="185"/>
-      <c r="W25" s="185"/>
-      <c r="X25" s="185"/>
-      <c r="Y25" s="185"/>
-      <c r="Z25" s="185"/>
-      <c r="AA25" s="185"/>
-      <c r="AB25" s="185"/>
-      <c r="AC25" s="185"/>
-      <c r="AD25" s="185"/>
-      <c r="AE25" s="185"/>
-      <c r="AF25" s="185"/>
-      <c r="AG25" s="185"/>
-      <c r="AH25" s="185"/>
-      <c r="AI25" s="185"/>
-      <c r="AJ25" s="185"/>
-      <c r="AK25" s="185"/>
-      <c r="AL25" s="183"/>
-      <c r="AM25" s="184"/>
-      <c r="AN25" s="184"/>
-      <c r="AO25" s="184"/>
-      <c r="AP25" s="185"/>
-      <c r="AQ25" s="185"/>
-      <c r="AR25" s="185"/>
-      <c r="AS25" s="185"/>
-      <c r="AT25" s="185"/>
-      <c r="AU25" s="185"/>
-      <c r="AV25" s="185"/>
-      <c r="AW25" s="185"/>
-      <c r="AX25" s="185"/>
-      <c r="AY25" s="185"/>
-      <c r="AZ25" s="185"/>
-      <c r="BA25" s="185"/>
+      <c r="A25" s="212"/>
+      <c r="B25" s="212"/>
+      <c r="C25" s="215"/>
+      <c r="D25" s="215"/>
+      <c r="E25" s="215"/>
+      <c r="F25" s="215"/>
+      <c r="G25" s="215"/>
+      <c r="H25" s="215"/>
+      <c r="I25" s="215"/>
+      <c r="J25" s="215"/>
+      <c r="K25" s="215"/>
+      <c r="L25" s="215"/>
+      <c r="M25" s="215"/>
+      <c r="N25" s="215"/>
+      <c r="O25" s="215"/>
+      <c r="P25" s="215"/>
+      <c r="Q25" s="215"/>
+      <c r="R25" s="215"/>
+      <c r="S25" s="215"/>
+      <c r="T25" s="215"/>
+      <c r="U25" s="215"/>
+      <c r="V25" s="215"/>
+      <c r="W25" s="215"/>
+      <c r="X25" s="215"/>
+      <c r="Y25" s="215"/>
+      <c r="Z25" s="215"/>
+      <c r="AA25" s="215"/>
+      <c r="AB25" s="215"/>
+      <c r="AC25" s="215"/>
+      <c r="AD25" s="215"/>
+      <c r="AE25" s="215"/>
+      <c r="AF25" s="215"/>
+      <c r="AG25" s="215"/>
+      <c r="AH25" s="215"/>
+      <c r="AI25" s="215"/>
+      <c r="AJ25" s="215"/>
+      <c r="AK25" s="215"/>
+      <c r="AL25" s="222"/>
+      <c r="AM25" s="212"/>
+      <c r="AN25" s="212"/>
+      <c r="AO25" s="212"/>
+      <c r="AP25" s="215"/>
+      <c r="AQ25" s="215"/>
+      <c r="AR25" s="215"/>
+      <c r="AS25" s="215"/>
+      <c r="AT25" s="215"/>
+      <c r="AU25" s="215"/>
+      <c r="AV25" s="215"/>
+      <c r="AW25" s="215"/>
+      <c r="AX25" s="215"/>
+      <c r="AY25" s="215"/>
+      <c r="AZ25" s="215"/>
+      <c r="BA25" s="215"/>
     </row>
     <row r="26" spans="1:53">
-      <c r="A26" s="184"/>
-      <c r="B26" s="184"/>
-      <c r="C26" s="185"/>
-      <c r="D26" s="185"/>
-      <c r="E26" s="185"/>
-      <c r="F26" s="185"/>
-      <c r="G26" s="185"/>
-      <c r="H26" s="185"/>
-      <c r="I26" s="185"/>
-      <c r="J26" s="185"/>
-      <c r="K26" s="185"/>
-      <c r="L26" s="185"/>
-      <c r="M26" s="185"/>
-      <c r="N26" s="185"/>
-      <c r="O26" s="185"/>
-      <c r="P26" s="185"/>
-      <c r="Q26" s="185"/>
-      <c r="R26" s="185"/>
-      <c r="S26" s="185"/>
-      <c r="T26" s="185"/>
-      <c r="U26" s="185"/>
-      <c r="V26" s="185"/>
-      <c r="W26" s="185"/>
-      <c r="X26" s="185"/>
-      <c r="Y26" s="185"/>
-      <c r="Z26" s="185"/>
-      <c r="AA26" s="185"/>
-      <c r="AB26" s="185"/>
-      <c r="AC26" s="185"/>
-      <c r="AD26" s="185"/>
-      <c r="AE26" s="185"/>
-      <c r="AF26" s="185"/>
-      <c r="AG26" s="185"/>
-      <c r="AH26" s="185"/>
-      <c r="AI26" s="185"/>
-      <c r="AJ26" s="185"/>
-      <c r="AK26" s="185"/>
-      <c r="AL26" s="183"/>
-      <c r="AM26" s="184"/>
-      <c r="AN26" s="184"/>
-      <c r="AO26" s="184"/>
-      <c r="AP26" s="185"/>
-      <c r="AQ26" s="185"/>
-      <c r="AR26" s="185"/>
-      <c r="AS26" s="185"/>
-      <c r="AT26" s="185"/>
-      <c r="AU26" s="185"/>
-      <c r="AV26" s="185"/>
-      <c r="AW26" s="185"/>
-      <c r="AX26" s="185"/>
-      <c r="AY26" s="185"/>
-      <c r="AZ26" s="185"/>
-      <c r="BA26" s="185"/>
+      <c r="A26" s="212"/>
+      <c r="B26" s="212"/>
+      <c r="C26" s="215"/>
+      <c r="D26" s="215"/>
+      <c r="E26" s="215"/>
+      <c r="F26" s="215"/>
+      <c r="G26" s="215"/>
+      <c r="H26" s="215"/>
+      <c r="I26" s="215"/>
+      <c r="J26" s="215"/>
+      <c r="K26" s="215"/>
+      <c r="L26" s="215"/>
+      <c r="M26" s="215"/>
+      <c r="N26" s="215"/>
+      <c r="O26" s="215"/>
+      <c r="P26" s="215"/>
+      <c r="Q26" s="215"/>
+      <c r="R26" s="215"/>
+      <c r="S26" s="215"/>
+      <c r="T26" s="215"/>
+      <c r="U26" s="215"/>
+      <c r="V26" s="215"/>
+      <c r="W26" s="215"/>
+      <c r="X26" s="215"/>
+      <c r="Y26" s="215"/>
+      <c r="Z26" s="215"/>
+      <c r="AA26" s="215"/>
+      <c r="AB26" s="215"/>
+      <c r="AC26" s="215"/>
+      <c r="AD26" s="215"/>
+      <c r="AE26" s="215"/>
+      <c r="AF26" s="215"/>
+      <c r="AG26" s="215"/>
+      <c r="AH26" s="215"/>
+      <c r="AI26" s="215"/>
+      <c r="AJ26" s="215"/>
+      <c r="AK26" s="215"/>
+      <c r="AL26" s="222"/>
+      <c r="AM26" s="212"/>
+      <c r="AN26" s="212"/>
+      <c r="AO26" s="212"/>
+      <c r="AP26" s="215"/>
+      <c r="AQ26" s="215"/>
+      <c r="AR26" s="215"/>
+      <c r="AS26" s="215"/>
+      <c r="AT26" s="215"/>
+      <c r="AU26" s="215"/>
+      <c r="AV26" s="215"/>
+      <c r="AW26" s="215"/>
+      <c r="AX26" s="215"/>
+      <c r="AY26" s="215"/>
+      <c r="AZ26" s="215"/>
+      <c r="BA26" s="215"/>
     </row>
     <row r="27" spans="1:53">
-      <c r="A27" s="184"/>
-      <c r="B27" s="184"/>
-      <c r="C27" s="185"/>
-      <c r="D27" s="185"/>
-      <c r="E27" s="185"/>
-      <c r="F27" s="185"/>
-      <c r="G27" s="185"/>
-      <c r="H27" s="185"/>
-      <c r="I27" s="185"/>
-      <c r="J27" s="185"/>
-      <c r="K27" s="185"/>
-      <c r="L27" s="185"/>
-      <c r="M27" s="185"/>
-      <c r="N27" s="185"/>
-      <c r="O27" s="185"/>
-      <c r="P27" s="185"/>
-      <c r="Q27" s="185"/>
-      <c r="R27" s="185"/>
-      <c r="S27" s="185"/>
-      <c r="T27" s="185"/>
-      <c r="U27" s="185"/>
-      <c r="V27" s="185"/>
-      <c r="W27" s="185"/>
-      <c r="X27" s="185"/>
-      <c r="Y27" s="185"/>
-      <c r="Z27" s="185"/>
-      <c r="AA27" s="185"/>
-      <c r="AB27" s="185"/>
-      <c r="AC27" s="185"/>
-      <c r="AD27" s="185"/>
-      <c r="AE27" s="185"/>
-      <c r="AF27" s="185"/>
-      <c r="AG27" s="185"/>
-      <c r="AH27" s="185"/>
-      <c r="AI27" s="185"/>
-      <c r="AJ27" s="185"/>
-      <c r="AK27" s="185"/>
-      <c r="AL27" s="183"/>
-      <c r="AM27" s="184"/>
-      <c r="AN27" s="184"/>
-      <c r="AO27" s="184"/>
-      <c r="AP27" s="185"/>
-      <c r="AQ27" s="185"/>
-      <c r="AR27" s="185"/>
-      <c r="AS27" s="185"/>
-      <c r="AT27" s="185"/>
-      <c r="AU27" s="185"/>
-      <c r="AV27" s="185"/>
-      <c r="AW27" s="185"/>
-      <c r="AX27" s="185"/>
-      <c r="AY27" s="185"/>
-      <c r="AZ27" s="185"/>
-      <c r="BA27" s="185"/>
+      <c r="A27" s="212"/>
+      <c r="B27" s="212"/>
+      <c r="C27" s="215"/>
+      <c r="D27" s="215"/>
+      <c r="E27" s="215"/>
+      <c r="F27" s="215"/>
+      <c r="G27" s="215"/>
+      <c r="H27" s="215"/>
+      <c r="I27" s="215"/>
+      <c r="J27" s="215"/>
+      <c r="K27" s="215"/>
+      <c r="L27" s="215"/>
+      <c r="M27" s="215"/>
+      <c r="N27" s="215"/>
+      <c r="O27" s="215"/>
+      <c r="P27" s="215"/>
+      <c r="Q27" s="215"/>
+      <c r="R27" s="215"/>
+      <c r="S27" s="215"/>
+      <c r="T27" s="215"/>
+      <c r="U27" s="215"/>
+      <c r="V27" s="215"/>
+      <c r="W27" s="215"/>
+      <c r="X27" s="215"/>
+      <c r="Y27" s="215"/>
+      <c r="Z27" s="215"/>
+      <c r="AA27" s="215"/>
+      <c r="AB27" s="215"/>
+      <c r="AC27" s="215"/>
+      <c r="AD27" s="215"/>
+      <c r="AE27" s="215"/>
+      <c r="AF27" s="215"/>
+      <c r="AG27" s="215"/>
+      <c r="AH27" s="215"/>
+      <c r="AI27" s="215"/>
+      <c r="AJ27" s="215"/>
+      <c r="AK27" s="215"/>
+      <c r="AL27" s="222"/>
+      <c r="AM27" s="212"/>
+      <c r="AN27" s="212"/>
+      <c r="AO27" s="212"/>
+      <c r="AP27" s="215"/>
+      <c r="AQ27" s="215"/>
+      <c r="AR27" s="215"/>
+      <c r="AS27" s="215"/>
+      <c r="AT27" s="215"/>
+      <c r="AU27" s="215"/>
+      <c r="AV27" s="215"/>
+      <c r="AW27" s="215"/>
+      <c r="AX27" s="215"/>
+      <c r="AY27" s="215"/>
+      <c r="AZ27" s="215"/>
+      <c r="BA27" s="215"/>
     </row>
     <row r="28" spans="1:53">
-      <c r="A28" s="184"/>
-      <c r="B28" s="184"/>
-      <c r="C28" s="185"/>
-      <c r="D28" s="185"/>
-      <c r="E28" s="185"/>
-      <c r="F28" s="185"/>
-      <c r="G28" s="185"/>
-      <c r="H28" s="185"/>
-      <c r="I28" s="185"/>
-      <c r="J28" s="185"/>
-      <c r="K28" s="185"/>
-      <c r="L28" s="185"/>
-      <c r="M28" s="185"/>
-      <c r="N28" s="185"/>
-      <c r="O28" s="185"/>
-      <c r="P28" s="185"/>
-      <c r="Q28" s="185"/>
-      <c r="R28" s="185"/>
-      <c r="S28" s="185"/>
-      <c r="T28" s="185"/>
-      <c r="U28" s="185"/>
-      <c r="V28" s="185"/>
-      <c r="W28" s="185"/>
-      <c r="X28" s="185"/>
-      <c r="Y28" s="185"/>
-      <c r="Z28" s="185"/>
-      <c r="AA28" s="185"/>
-      <c r="AB28" s="185"/>
-      <c r="AC28" s="185"/>
-      <c r="AD28" s="185"/>
-      <c r="AE28" s="185"/>
-      <c r="AF28" s="185"/>
-      <c r="AG28" s="185"/>
-      <c r="AH28" s="185"/>
-      <c r="AI28" s="185"/>
-      <c r="AJ28" s="185"/>
-      <c r="AK28" s="185"/>
-      <c r="AL28" s="183"/>
-      <c r="AM28" s="184"/>
-      <c r="AN28" s="184"/>
-      <c r="AO28" s="184"/>
-      <c r="AP28" s="185"/>
-      <c r="AQ28" s="185"/>
-      <c r="AR28" s="185"/>
-      <c r="AS28" s="185"/>
-      <c r="AT28" s="185"/>
-      <c r="AU28" s="185"/>
-      <c r="AV28" s="185"/>
-      <c r="AW28" s="185"/>
-      <c r="AX28" s="185"/>
-      <c r="AY28" s="185"/>
-      <c r="AZ28" s="185"/>
-      <c r="BA28" s="185"/>
+      <c r="A28" s="212"/>
+      <c r="B28" s="212"/>
+      <c r="C28" s="215"/>
+      <c r="D28" s="215"/>
+      <c r="E28" s="215"/>
+      <c r="F28" s="215"/>
+      <c r="G28" s="215"/>
+      <c r="H28" s="215"/>
+      <c r="I28" s="215"/>
+      <c r="J28" s="215"/>
+      <c r="K28" s="215"/>
+      <c r="L28" s="215"/>
+      <c r="M28" s="215"/>
+      <c r="N28" s="215"/>
+      <c r="O28" s="215"/>
+      <c r="P28" s="215"/>
+      <c r="Q28" s="215"/>
+      <c r="R28" s="215"/>
+      <c r="S28" s="215"/>
+      <c r="T28" s="215"/>
+      <c r="U28" s="215"/>
+      <c r="V28" s="215"/>
+      <c r="W28" s="215"/>
+      <c r="X28" s="215"/>
+      <c r="Y28" s="215"/>
+      <c r="Z28" s="215"/>
+      <c r="AA28" s="215"/>
+      <c r="AB28" s="215"/>
+      <c r="AC28" s="215"/>
+      <c r="AD28" s="215"/>
+      <c r="AE28" s="215"/>
+      <c r="AF28" s="215"/>
+      <c r="AG28" s="215"/>
+      <c r="AH28" s="215"/>
+      <c r="AI28" s="215"/>
+      <c r="AJ28" s="215"/>
+      <c r="AK28" s="215"/>
+      <c r="AL28" s="222"/>
+      <c r="AM28" s="212"/>
+      <c r="AN28" s="212"/>
+      <c r="AO28" s="212"/>
+      <c r="AP28" s="215"/>
+      <c r="AQ28" s="215"/>
+      <c r="AR28" s="215"/>
+      <c r="AS28" s="215"/>
+      <c r="AT28" s="215"/>
+      <c r="AU28" s="215"/>
+      <c r="AV28" s="215"/>
+      <c r="AW28" s="215"/>
+      <c r="AX28" s="215"/>
+      <c r="AY28" s="215"/>
+      <c r="AZ28" s="215"/>
+      <c r="BA28" s="215"/>
     </row>
     <row r="29" spans="1:53">
-      <c r="A29" s="184"/>
-      <c r="B29" s="184"/>
-      <c r="C29" s="185"/>
-      <c r="D29" s="185"/>
-      <c r="E29" s="185"/>
-      <c r="F29" s="185"/>
-      <c r="G29" s="185"/>
-      <c r="H29" s="185"/>
-      <c r="I29" s="185"/>
-      <c r="J29" s="185"/>
-      <c r="K29" s="185"/>
-      <c r="L29" s="185"/>
-      <c r="M29" s="185"/>
-      <c r="N29" s="185"/>
-      <c r="O29" s="185"/>
-      <c r="P29" s="185"/>
-      <c r="Q29" s="185"/>
-      <c r="R29" s="185"/>
-      <c r="S29" s="185"/>
-      <c r="T29" s="185"/>
-      <c r="U29" s="185"/>
-      <c r="V29" s="185"/>
-      <c r="W29" s="185"/>
-      <c r="X29" s="185"/>
-      <c r="Y29" s="185"/>
-      <c r="Z29" s="185"/>
-      <c r="AA29" s="185"/>
-      <c r="AB29" s="185"/>
-      <c r="AC29" s="185"/>
-      <c r="AD29" s="185"/>
-      <c r="AE29" s="185"/>
-      <c r="AF29" s="185"/>
-      <c r="AG29" s="185"/>
-      <c r="AH29" s="185"/>
-      <c r="AI29" s="185"/>
-      <c r="AJ29" s="185"/>
-      <c r="AK29" s="185"/>
-      <c r="AL29" s="183"/>
-      <c r="AM29" s="184"/>
-      <c r="AN29" s="184"/>
-      <c r="AO29" s="184"/>
-      <c r="AP29" s="185"/>
-      <c r="AQ29" s="185"/>
-      <c r="AR29" s="185"/>
-      <c r="AS29" s="185"/>
-      <c r="AT29" s="185"/>
-      <c r="AU29" s="185"/>
-      <c r="AV29" s="185"/>
-      <c r="AW29" s="185"/>
-      <c r="AX29" s="185"/>
-      <c r="AY29" s="185"/>
-      <c r="AZ29" s="185"/>
-      <c r="BA29" s="185"/>
+      <c r="A29" s="212"/>
+      <c r="B29" s="212"/>
+      <c r="C29" s="215"/>
+      <c r="D29" s="215"/>
+      <c r="E29" s="215"/>
+      <c r="F29" s="215"/>
+      <c r="G29" s="215"/>
+      <c r="H29" s="215"/>
+      <c r="I29" s="215"/>
+      <c r="J29" s="215"/>
+      <c r="K29" s="215"/>
+      <c r="L29" s="215"/>
+      <c r="M29" s="215"/>
+      <c r="N29" s="215"/>
+      <c r="O29" s="215"/>
+      <c r="P29" s="215"/>
+      <c r="Q29" s="215"/>
+      <c r="R29" s="215"/>
+      <c r="S29" s="215"/>
+      <c r="T29" s="215"/>
+      <c r="U29" s="215"/>
+      <c r="V29" s="215"/>
+      <c r="W29" s="215"/>
+      <c r="X29" s="215"/>
+      <c r="Y29" s="215"/>
+      <c r="Z29" s="215"/>
+      <c r="AA29" s="215"/>
+      <c r="AB29" s="215"/>
+      <c r="AC29" s="215"/>
+      <c r="AD29" s="215"/>
+      <c r="AE29" s="215"/>
+      <c r="AF29" s="215"/>
+      <c r="AG29" s="215"/>
+      <c r="AH29" s="215"/>
+      <c r="AI29" s="215"/>
+      <c r="AJ29" s="215"/>
+      <c r="AK29" s="215"/>
+      <c r="AL29" s="222"/>
+      <c r="AM29" s="212"/>
+      <c r="AN29" s="212"/>
+      <c r="AO29" s="212"/>
+      <c r="AP29" s="215"/>
+      <c r="AQ29" s="215"/>
+      <c r="AR29" s="215"/>
+      <c r="AS29" s="215"/>
+      <c r="AT29" s="215"/>
+      <c r="AU29" s="215"/>
+      <c r="AV29" s="215"/>
+      <c r="AW29" s="215"/>
+      <c r="AX29" s="215"/>
+      <c r="AY29" s="215"/>
+      <c r="AZ29" s="215"/>
+      <c r="BA29" s="215"/>
     </row>
     <row r="30" spans="1:53">
-      <c r="A30" s="184"/>
-      <c r="B30" s="184"/>
-      <c r="C30" s="185"/>
-      <c r="D30" s="185"/>
-      <c r="E30" s="185"/>
-      <c r="F30" s="185"/>
-      <c r="G30" s="185"/>
-      <c r="H30" s="185"/>
-      <c r="I30" s="185"/>
-      <c r="J30" s="185"/>
-      <c r="K30" s="185"/>
-      <c r="L30" s="185"/>
-      <c r="M30" s="185"/>
-      <c r="N30" s="185"/>
-      <c r="O30" s="185"/>
-      <c r="P30" s="185"/>
-      <c r="Q30" s="185"/>
-      <c r="R30" s="185"/>
-      <c r="S30" s="185"/>
-      <c r="T30" s="185"/>
-      <c r="U30" s="185"/>
-      <c r="V30" s="185"/>
-      <c r="W30" s="185"/>
-      <c r="X30" s="185"/>
-      <c r="Y30" s="185"/>
-      <c r="Z30" s="185"/>
-      <c r="AA30" s="185"/>
-      <c r="AB30" s="185"/>
-      <c r="AC30" s="185"/>
-      <c r="AD30" s="185"/>
-      <c r="AE30" s="185"/>
-      <c r="AF30" s="185"/>
-      <c r="AG30" s="185"/>
-      <c r="AH30" s="185"/>
-      <c r="AI30" s="185"/>
-      <c r="AJ30" s="185"/>
-      <c r="AK30" s="185"/>
-      <c r="AL30" s="184"/>
-      <c r="AM30" s="184"/>
-      <c r="AN30" s="184"/>
-      <c r="AO30" s="184"/>
-      <c r="AP30" s="185"/>
-      <c r="AQ30" s="185"/>
-      <c r="AR30" s="185"/>
-      <c r="AS30" s="185"/>
-      <c r="AT30" s="185"/>
-      <c r="AU30" s="185"/>
-      <c r="AV30" s="185"/>
-      <c r="AW30" s="185"/>
-      <c r="AX30" s="185"/>
-      <c r="AY30" s="185"/>
-      <c r="AZ30" s="185"/>
-      <c r="BA30" s="185"/>
+      <c r="A30" s="212"/>
+      <c r="B30" s="212"/>
+      <c r="C30" s="215"/>
+      <c r="D30" s="215"/>
+      <c r="E30" s="215"/>
+      <c r="F30" s="215"/>
+      <c r="G30" s="215"/>
+      <c r="H30" s="215"/>
+      <c r="I30" s="215"/>
+      <c r="J30" s="215"/>
+      <c r="K30" s="215"/>
+      <c r="L30" s="215"/>
+      <c r="M30" s="215"/>
+      <c r="N30" s="215"/>
+      <c r="O30" s="215"/>
+      <c r="P30" s="215"/>
+      <c r="Q30" s="215"/>
+      <c r="R30" s="215"/>
+      <c r="S30" s="215"/>
+      <c r="T30" s="215"/>
+      <c r="U30" s="215"/>
+      <c r="V30" s="215"/>
+      <c r="W30" s="215"/>
+      <c r="X30" s="215"/>
+      <c r="Y30" s="215"/>
+      <c r="Z30" s="215"/>
+      <c r="AA30" s="215"/>
+      <c r="AB30" s="215"/>
+      <c r="AC30" s="215"/>
+      <c r="AD30" s="215"/>
+      <c r="AE30" s="215"/>
+      <c r="AF30" s="215"/>
+      <c r="AG30" s="215"/>
+      <c r="AH30" s="215"/>
+      <c r="AI30" s="215"/>
+      <c r="AJ30" s="215"/>
+      <c r="AK30" s="215"/>
+      <c r="AL30" s="212"/>
+      <c r="AM30" s="212"/>
+      <c r="AN30" s="212"/>
+      <c r="AO30" s="212"/>
+      <c r="AP30" s="215"/>
+      <c r="AQ30" s="215"/>
+      <c r="AR30" s="215"/>
+      <c r="AS30" s="215"/>
+      <c r="AT30" s="215"/>
+      <c r="AU30" s="215"/>
+      <c r="AV30" s="215"/>
+      <c r="AW30" s="215"/>
+      <c r="AX30" s="215"/>
+      <c r="AY30" s="215"/>
+      <c r="AZ30" s="215"/>
+      <c r="BA30" s="215"/>
     </row>
     <row r="31" spans="1:53">
-      <c r="A31" s="184"/>
-      <c r="B31" s="184"/>
-      <c r="C31" s="185"/>
-      <c r="D31" s="185"/>
-      <c r="E31" s="185"/>
-      <c r="F31" s="185"/>
-      <c r="G31" s="185"/>
-      <c r="H31" s="185"/>
-      <c r="I31" s="185"/>
-      <c r="J31" s="185"/>
-      <c r="K31" s="185"/>
-      <c r="L31" s="185"/>
-      <c r="M31" s="185"/>
-      <c r="N31" s="185"/>
-      <c r="O31" s="185"/>
-      <c r="P31" s="185"/>
-      <c r="Q31" s="185"/>
-      <c r="R31" s="185"/>
-      <c r="S31" s="185"/>
-      <c r="T31" s="185"/>
-      <c r="U31" s="185"/>
-      <c r="V31" s="185"/>
-      <c r="W31" s="185"/>
-      <c r="X31" s="185"/>
-      <c r="Y31" s="185"/>
-      <c r="Z31" s="185"/>
-      <c r="AA31" s="185"/>
-      <c r="AB31" s="185"/>
-      <c r="AC31" s="185"/>
-      <c r="AD31" s="185"/>
-      <c r="AE31" s="185"/>
-      <c r="AF31" s="185"/>
-      <c r="AG31" s="185"/>
-      <c r="AH31" s="185"/>
-      <c r="AI31" s="185"/>
-      <c r="AJ31" s="185"/>
-      <c r="AK31" s="185"/>
-      <c r="AL31" s="184"/>
-      <c r="AM31" s="184"/>
-      <c r="AN31" s="184"/>
-      <c r="AO31" s="184"/>
-      <c r="AP31" s="185"/>
-      <c r="AQ31" s="185"/>
-      <c r="AR31" s="185"/>
-      <c r="AS31" s="185"/>
-      <c r="AT31" s="185"/>
-      <c r="AU31" s="185"/>
-      <c r="AV31" s="185"/>
-      <c r="AW31" s="185"/>
-      <c r="AX31" s="185"/>
-      <c r="AY31" s="185"/>
-      <c r="AZ31" s="185"/>
-      <c r="BA31" s="185"/>
+      <c r="A31" s="212"/>
+      <c r="B31" s="212"/>
+      <c r="C31" s="215"/>
+      <c r="D31" s="215"/>
+      <c r="E31" s="215"/>
+      <c r="F31" s="215"/>
+      <c r="G31" s="215"/>
+      <c r="H31" s="215"/>
+      <c r="I31" s="215"/>
+      <c r="J31" s="215"/>
+      <c r="K31" s="215"/>
+      <c r="L31" s="215"/>
+      <c r="M31" s="215"/>
+      <c r="N31" s="215"/>
+      <c r="O31" s="215"/>
+      <c r="P31" s="215"/>
+      <c r="Q31" s="215"/>
+      <c r="R31" s="215"/>
+      <c r="S31" s="215"/>
+      <c r="T31" s="215"/>
+      <c r="U31" s="215"/>
+      <c r="V31" s="215"/>
+      <c r="W31" s="215"/>
+      <c r="X31" s="215"/>
+      <c r="Y31" s="215"/>
+      <c r="Z31" s="215"/>
+      <c r="AA31" s="215"/>
+      <c r="AB31" s="215"/>
+      <c r="AC31" s="215"/>
+      <c r="AD31" s="215"/>
+      <c r="AE31" s="215"/>
+      <c r="AF31" s="215"/>
+      <c r="AG31" s="215"/>
+      <c r="AH31" s="215"/>
+      <c r="AI31" s="215"/>
+      <c r="AJ31" s="215"/>
+      <c r="AK31" s="215"/>
+      <c r="AL31" s="212"/>
+      <c r="AM31" s="212"/>
+      <c r="AN31" s="212"/>
+      <c r="AO31" s="212"/>
+      <c r="AP31" s="215"/>
+      <c r="AQ31" s="215"/>
+      <c r="AR31" s="215"/>
+      <c r="AS31" s="215"/>
+      <c r="AT31" s="215"/>
+      <c r="AU31" s="215"/>
+      <c r="AV31" s="215"/>
+      <c r="AW31" s="215"/>
+      <c r="AX31" s="215"/>
+      <c r="AY31" s="215"/>
+      <c r="AZ31" s="215"/>
+      <c r="BA31" s="215"/>
     </row>
     <row r="32" spans="1:53">
-      <c r="A32" s="184"/>
-      <c r="B32" s="184"/>
-      <c r="C32" s="185"/>
-      <c r="D32" s="185"/>
-      <c r="E32" s="185"/>
-      <c r="F32" s="185"/>
-      <c r="G32" s="185"/>
-      <c r="H32" s="185"/>
-      <c r="I32" s="185"/>
-      <c r="J32" s="185"/>
-      <c r="K32" s="185"/>
-      <c r="L32" s="185"/>
-      <c r="M32" s="185"/>
-      <c r="N32" s="185"/>
-      <c r="O32" s="185"/>
-      <c r="P32" s="185"/>
-      <c r="Q32" s="185"/>
-      <c r="R32" s="185"/>
-      <c r="S32" s="185"/>
-      <c r="T32" s="185"/>
-      <c r="U32" s="185"/>
-      <c r="V32" s="185"/>
-      <c r="W32" s="185"/>
-      <c r="X32" s="185"/>
-      <c r="Y32" s="185"/>
-      <c r="Z32" s="185"/>
-      <c r="AA32" s="185"/>
-      <c r="AB32" s="185"/>
-      <c r="AC32" s="185"/>
-      <c r="AD32" s="185"/>
-      <c r="AE32" s="185"/>
-      <c r="AF32" s="185"/>
-      <c r="AG32" s="185"/>
-      <c r="AH32" s="185"/>
-      <c r="AI32" s="185"/>
-      <c r="AJ32" s="185"/>
-      <c r="AK32" s="185"/>
-      <c r="AL32" s="184"/>
-      <c r="AM32" s="184"/>
-      <c r="AN32" s="184"/>
-      <c r="AO32" s="184"/>
-      <c r="AP32" s="185"/>
-      <c r="AQ32" s="185"/>
-      <c r="AR32" s="185"/>
-      <c r="AS32" s="185"/>
-      <c r="AT32" s="185"/>
-      <c r="AU32" s="185"/>
-      <c r="AV32" s="185"/>
-      <c r="AW32" s="185"/>
-      <c r="AX32" s="185"/>
-      <c r="AY32" s="185"/>
-      <c r="AZ32" s="185"/>
-      <c r="BA32" s="185"/>
+      <c r="A32" s="212"/>
+      <c r="B32" s="212"/>
+      <c r="C32" s="215"/>
+      <c r="D32" s="215"/>
+      <c r="E32" s="215"/>
+      <c r="F32" s="215"/>
+      <c r="G32" s="215"/>
+      <c r="H32" s="215"/>
+      <c r="I32" s="215"/>
+      <c r="J32" s="215"/>
+      <c r="K32" s="215"/>
+      <c r="L32" s="215"/>
+      <c r="M32" s="215"/>
+      <c r="N32" s="215"/>
+      <c r="O32" s="215"/>
+      <c r="P32" s="215"/>
+      <c r="Q32" s="215"/>
+      <c r="R32" s="215"/>
+      <c r="S32" s="215"/>
+      <c r="T32" s="215"/>
+      <c r="U32" s="215"/>
+      <c r="V32" s="215"/>
+      <c r="W32" s="215"/>
+      <c r="X32" s="215"/>
+      <c r="Y32" s="215"/>
+      <c r="Z32" s="215"/>
+      <c r="AA32" s="215"/>
+      <c r="AB32" s="215"/>
+      <c r="AC32" s="215"/>
+      <c r="AD32" s="215"/>
+      <c r="AE32" s="215"/>
+      <c r="AF32" s="215"/>
+      <c r="AG32" s="215"/>
+      <c r="AH32" s="215"/>
+      <c r="AI32" s="215"/>
+      <c r="AJ32" s="215"/>
+      <c r="AK32" s="215"/>
+      <c r="AL32" s="212"/>
+      <c r="AM32" s="212"/>
+      <c r="AN32" s="212"/>
+      <c r="AO32" s="212"/>
+      <c r="AP32" s="215"/>
+      <c r="AQ32" s="215"/>
+      <c r="AR32" s="215"/>
+      <c r="AS32" s="215"/>
+      <c r="AT32" s="215"/>
+      <c r="AU32" s="215"/>
+      <c r="AV32" s="215"/>
+      <c r="AW32" s="215"/>
+      <c r="AX32" s="215"/>
+      <c r="AY32" s="215"/>
+      <c r="AZ32" s="215"/>
+      <c r="BA32" s="215"/>
     </row>
     <row r="33" spans="1:53">
-      <c r="A33" s="184"/>
-      <c r="B33" s="184"/>
-      <c r="C33" s="185"/>
-      <c r="D33" s="185"/>
-      <c r="E33" s="185"/>
-      <c r="F33" s="185"/>
-      <c r="G33" s="185"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="185"/>
-      <c r="K33" s="185"/>
-      <c r="L33" s="185"/>
-      <c r="M33" s="185"/>
-      <c r="N33" s="185"/>
-      <c r="O33" s="185"/>
-      <c r="P33" s="185"/>
-      <c r="Q33" s="185"/>
-      <c r="R33" s="185"/>
-      <c r="S33" s="185"/>
-      <c r="T33" s="185"/>
-      <c r="U33" s="185"/>
-      <c r="V33" s="185"/>
-      <c r="W33" s="185"/>
-      <c r="X33" s="185"/>
-      <c r="Y33" s="185"/>
-      <c r="Z33" s="185"/>
-      <c r="AA33" s="185"/>
-      <c r="AB33" s="185"/>
-      <c r="AC33" s="185"/>
-      <c r="AD33" s="185"/>
-      <c r="AE33" s="185"/>
-      <c r="AF33" s="185"/>
-      <c r="AG33" s="185"/>
-      <c r="AH33" s="185"/>
-      <c r="AI33" s="185"/>
-      <c r="AJ33" s="185"/>
-      <c r="AK33" s="185"/>
-      <c r="AL33" s="184"/>
-      <c r="AM33" s="184"/>
-      <c r="AN33" s="184"/>
-      <c r="AO33" s="184"/>
-      <c r="AP33" s="185"/>
-      <c r="AQ33" s="185"/>
-      <c r="AR33" s="185"/>
-      <c r="AS33" s="185"/>
-      <c r="AT33" s="185"/>
-      <c r="AU33" s="185"/>
-      <c r="AV33" s="185"/>
-      <c r="AW33" s="185"/>
-      <c r="AX33" s="185"/>
-      <c r="AY33" s="185"/>
-      <c r="AZ33" s="185"/>
-      <c r="BA33" s="185"/>
+      <c r="A33" s="212"/>
+      <c r="B33" s="212"/>
+      <c r="C33" s="215"/>
+      <c r="D33" s="215"/>
+      <c r="E33" s="215"/>
+      <c r="F33" s="215"/>
+      <c r="G33" s="215"/>
+      <c r="H33" s="215"/>
+      <c r="I33" s="215"/>
+      <c r="J33" s="215"/>
+      <c r="K33" s="215"/>
+      <c r="L33" s="215"/>
+      <c r="M33" s="215"/>
+      <c r="N33" s="215"/>
+      <c r="O33" s="215"/>
+      <c r="P33" s="215"/>
+      <c r="Q33" s="215"/>
+      <c r="R33" s="215"/>
+      <c r="S33" s="215"/>
+      <c r="T33" s="215"/>
+      <c r="U33" s="215"/>
+      <c r="V33" s="215"/>
+      <c r="W33" s="215"/>
+      <c r="X33" s="215"/>
+      <c r="Y33" s="215"/>
+      <c r="Z33" s="215"/>
+      <c r="AA33" s="215"/>
+      <c r="AB33" s="215"/>
+      <c r="AC33" s="215"/>
+      <c r="AD33" s="215"/>
+      <c r="AE33" s="215"/>
+      <c r="AF33" s="215"/>
+      <c r="AG33" s="215"/>
+      <c r="AH33" s="215"/>
+      <c r="AI33" s="215"/>
+      <c r="AJ33" s="215"/>
+      <c r="AK33" s="215"/>
+      <c r="AL33" s="212"/>
+      <c r="AM33" s="212"/>
+      <c r="AN33" s="212"/>
+      <c r="AO33" s="212"/>
+      <c r="AP33" s="215"/>
+      <c r="AQ33" s="215"/>
+      <c r="AR33" s="215"/>
+      <c r="AS33" s="215"/>
+      <c r="AT33" s="215"/>
+      <c r="AU33" s="215"/>
+      <c r="AV33" s="215"/>
+      <c r="AW33" s="215"/>
+      <c r="AX33" s="215"/>
+      <c r="AY33" s="215"/>
+      <c r="AZ33" s="215"/>
+      <c r="BA33" s="215"/>
     </row>
     <row r="34" spans="1:53">
-      <c r="A34" s="184"/>
-      <c r="B34" s="184"/>
-      <c r="C34" s="185"/>
-      <c r="D34" s="185"/>
-      <c r="E34" s="185"/>
-      <c r="F34" s="185"/>
-      <c r="G34" s="185"/>
-      <c r="H34" s="185"/>
-      <c r="I34" s="185"/>
-      <c r="J34" s="185"/>
-      <c r="K34" s="185"/>
-      <c r="L34" s="185"/>
-      <c r="M34" s="185"/>
-      <c r="N34" s="185"/>
-      <c r="O34" s="185"/>
-      <c r="P34" s="185"/>
-      <c r="Q34" s="185"/>
-      <c r="R34" s="185"/>
-      <c r="S34" s="185"/>
-      <c r="T34" s="185"/>
-      <c r="U34" s="185"/>
-      <c r="V34" s="185"/>
-      <c r="W34" s="185"/>
-      <c r="X34" s="185"/>
-      <c r="Y34" s="185"/>
-      <c r="Z34" s="185"/>
-      <c r="AA34" s="185"/>
-      <c r="AB34" s="185"/>
-      <c r="AC34" s="185"/>
-      <c r="AD34" s="185"/>
-      <c r="AE34" s="185"/>
-      <c r="AF34" s="185"/>
-      <c r="AG34" s="185"/>
-      <c r="AH34" s="185"/>
-      <c r="AI34" s="185"/>
-      <c r="AJ34" s="185"/>
-      <c r="AK34" s="185"/>
-      <c r="AL34" s="184"/>
-      <c r="AM34" s="184"/>
-      <c r="AN34" s="184"/>
-      <c r="AO34" s="184"/>
-      <c r="AP34" s="185"/>
-      <c r="AQ34" s="185"/>
-      <c r="AR34" s="185"/>
-      <c r="AS34" s="185"/>
-      <c r="AT34" s="185"/>
-      <c r="AU34" s="185"/>
-      <c r="AV34" s="185"/>
-      <c r="AW34" s="185"/>
-      <c r="AX34" s="185"/>
-      <c r="AY34" s="185"/>
-      <c r="AZ34" s="185"/>
-      <c r="BA34" s="185"/>
+      <c r="A34" s="212"/>
+      <c r="B34" s="212"/>
+      <c r="C34" s="215"/>
+      <c r="D34" s="215"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="215"/>
+      <c r="G34" s="215"/>
+      <c r="H34" s="215"/>
+      <c r="I34" s="215"/>
+      <c r="J34" s="215"/>
+      <c r="K34" s="215"/>
+      <c r="L34" s="215"/>
+      <c r="M34" s="215"/>
+      <c r="N34" s="215"/>
+      <c r="O34" s="215"/>
+      <c r="P34" s="215"/>
+      <c r="Q34" s="215"/>
+      <c r="R34" s="215"/>
+      <c r="S34" s="215"/>
+      <c r="T34" s="215"/>
+      <c r="U34" s="215"/>
+      <c r="V34" s="215"/>
+      <c r="W34" s="215"/>
+      <c r="X34" s="215"/>
+      <c r="Y34" s="215"/>
+      <c r="Z34" s="215"/>
+      <c r="AA34" s="215"/>
+      <c r="AB34" s="215"/>
+      <c r="AC34" s="215"/>
+      <c r="AD34" s="215"/>
+      <c r="AE34" s="215"/>
+      <c r="AF34" s="215"/>
+      <c r="AG34" s="215"/>
+      <c r="AH34" s="215"/>
+      <c r="AI34" s="215"/>
+      <c r="AJ34" s="215"/>
+      <c r="AK34" s="215"/>
+      <c r="AL34" s="212"/>
+      <c r="AM34" s="212"/>
+      <c r="AN34" s="212"/>
+      <c r="AO34" s="212"/>
+      <c r="AP34" s="215"/>
+      <c r="AQ34" s="215"/>
+      <c r="AR34" s="215"/>
+      <c r="AS34" s="215"/>
+      <c r="AT34" s="215"/>
+      <c r="AU34" s="215"/>
+      <c r="AV34" s="215"/>
+      <c r="AW34" s="215"/>
+      <c r="AX34" s="215"/>
+      <c r="AY34" s="215"/>
+      <c r="AZ34" s="215"/>
+      <c r="BA34" s="215"/>
     </row>
   </sheetData>
   <mergeCells count="229">
-    <mergeCell ref="AK1:AM1"/>
-    <mergeCell ref="AT3:AW3"/>
-    <mergeCell ref="AN1:AP1"/>
-    <mergeCell ref="AQ1:AS1"/>
-    <mergeCell ref="AT1:AW1"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:P6"/>
-    <mergeCell ref="Q6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AL22:AO22"/>
+    <mergeCell ref="AL23:AO23"/>
+    <mergeCell ref="AL24:AO24"/>
+    <mergeCell ref="AL25:AO25"/>
+    <mergeCell ref="AL26:AO26"/>
+    <mergeCell ref="Q24:AK24"/>
+    <mergeCell ref="Q25:AK25"/>
+    <mergeCell ref="Q26:AK26"/>
+    <mergeCell ref="AP14:AR14"/>
+    <mergeCell ref="Q16:AK16"/>
+    <mergeCell ref="AL16:AO16"/>
+    <mergeCell ref="AP16:AR16"/>
+    <mergeCell ref="AV20:BA20"/>
+    <mergeCell ref="AV21:BA21"/>
+    <mergeCell ref="AV14:BA14"/>
+    <mergeCell ref="AV15:BA15"/>
+    <mergeCell ref="AS28:AU28"/>
+    <mergeCell ref="AS30:AU30"/>
+    <mergeCell ref="AS31:AU31"/>
+    <mergeCell ref="AS25:AU25"/>
+    <mergeCell ref="AP31:AR31"/>
+    <mergeCell ref="AP27:AR27"/>
+    <mergeCell ref="AP28:AR28"/>
+    <mergeCell ref="AS16:AU16"/>
+    <mergeCell ref="AP15:AR15"/>
+    <mergeCell ref="AS26:AU26"/>
+    <mergeCell ref="AS14:AU14"/>
+    <mergeCell ref="AS15:AU15"/>
+    <mergeCell ref="AV7:BA7"/>
+    <mergeCell ref="AV8:BA8"/>
+    <mergeCell ref="AV9:BA9"/>
+    <mergeCell ref="AV10:BA10"/>
+    <mergeCell ref="AV11:BA11"/>
+    <mergeCell ref="AV12:BA12"/>
+    <mergeCell ref="AV34:BA34"/>
+    <mergeCell ref="AV24:BA24"/>
+    <mergeCell ref="AV25:BA25"/>
+    <mergeCell ref="AV26:BA26"/>
+    <mergeCell ref="AV29:BA29"/>
+    <mergeCell ref="AV30:BA30"/>
+    <mergeCell ref="AV31:BA31"/>
+    <mergeCell ref="AV27:BA27"/>
+    <mergeCell ref="AV28:BA28"/>
+    <mergeCell ref="AV32:BA32"/>
+    <mergeCell ref="AV33:BA33"/>
+    <mergeCell ref="AV13:BA13"/>
+    <mergeCell ref="AV22:BA22"/>
+    <mergeCell ref="AV23:BA23"/>
+    <mergeCell ref="AV17:BA17"/>
+    <mergeCell ref="AV18:BA18"/>
+    <mergeCell ref="AV19:BA19"/>
+    <mergeCell ref="AV16:BA16"/>
+    <mergeCell ref="AS34:AU34"/>
+    <mergeCell ref="AP34:AR34"/>
+    <mergeCell ref="AS7:AU7"/>
+    <mergeCell ref="AS8:AU8"/>
+    <mergeCell ref="AS9:AU9"/>
+    <mergeCell ref="AS10:AU10"/>
+    <mergeCell ref="AS11:AU11"/>
+    <mergeCell ref="AS12:AU12"/>
+    <mergeCell ref="AS19:AU19"/>
+    <mergeCell ref="AS20:AU20"/>
+    <mergeCell ref="AS21:AU21"/>
+    <mergeCell ref="AS13:AU13"/>
+    <mergeCell ref="AS17:AU17"/>
+    <mergeCell ref="AS18:AU18"/>
+    <mergeCell ref="AS22:AU22"/>
+    <mergeCell ref="AS23:AU23"/>
+    <mergeCell ref="AS24:AU24"/>
+    <mergeCell ref="AS29:AU29"/>
+    <mergeCell ref="AS27:AU27"/>
+    <mergeCell ref="AS32:AU32"/>
+    <mergeCell ref="AS33:AU33"/>
+    <mergeCell ref="AP24:AR24"/>
+    <mergeCell ref="AP25:AR25"/>
+    <mergeCell ref="AP32:AR32"/>
+    <mergeCell ref="AL32:AO32"/>
+    <mergeCell ref="AL33:AO33"/>
+    <mergeCell ref="AL34:AO34"/>
+    <mergeCell ref="AP7:AR7"/>
+    <mergeCell ref="AP8:AR8"/>
+    <mergeCell ref="AP9:AR9"/>
+    <mergeCell ref="AP10:AR10"/>
+    <mergeCell ref="AP18:AR18"/>
+    <mergeCell ref="AP19:AR19"/>
+    <mergeCell ref="AP20:AR20"/>
+    <mergeCell ref="AP21:AR21"/>
+    <mergeCell ref="AP11:AR11"/>
+    <mergeCell ref="AP12:AR12"/>
+    <mergeCell ref="AP13:AR13"/>
+    <mergeCell ref="AP17:AR17"/>
+    <mergeCell ref="AP22:AR22"/>
+    <mergeCell ref="AP23:AR23"/>
+    <mergeCell ref="AL30:AO30"/>
+    <mergeCell ref="AL31:AO31"/>
+    <mergeCell ref="AL20:AO20"/>
+    <mergeCell ref="AP26:AR26"/>
+    <mergeCell ref="AP29:AR29"/>
+    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP33:AR33"/>
+    <mergeCell ref="AL29:AO29"/>
+    <mergeCell ref="AL27:AO27"/>
+    <mergeCell ref="AL28:AO28"/>
+    <mergeCell ref="Q29:AK29"/>
+    <mergeCell ref="Q27:AK27"/>
+    <mergeCell ref="Q28:AK28"/>
+    <mergeCell ref="AL7:AO7"/>
+    <mergeCell ref="AL8:AO8"/>
+    <mergeCell ref="AL17:AO17"/>
+    <mergeCell ref="AL18:AO18"/>
+    <mergeCell ref="AL19:AO19"/>
+    <mergeCell ref="AL9:AO9"/>
+    <mergeCell ref="AL10:AO10"/>
+    <mergeCell ref="AL11:AO11"/>
+    <mergeCell ref="AL12:AO12"/>
+    <mergeCell ref="AL13:AO13"/>
+    <mergeCell ref="AL21:AO21"/>
+    <mergeCell ref="Q17:AK17"/>
+    <mergeCell ref="Q18:AK18"/>
+    <mergeCell ref="Q22:AK22"/>
+    <mergeCell ref="Q14:AK14"/>
+    <mergeCell ref="AL14:AO14"/>
+    <mergeCell ref="Q15:AK15"/>
+    <mergeCell ref="AL15:AO15"/>
+    <mergeCell ref="C34:P34"/>
+    <mergeCell ref="Q7:AK7"/>
+    <mergeCell ref="Q8:AK8"/>
+    <mergeCell ref="Q9:AK9"/>
+    <mergeCell ref="Q10:AK10"/>
+    <mergeCell ref="Q11:AK11"/>
+    <mergeCell ref="Q12:AK12"/>
+    <mergeCell ref="Q19:AK19"/>
+    <mergeCell ref="Q20:AK20"/>
+    <mergeCell ref="Q21:AK21"/>
+    <mergeCell ref="Q13:AK13"/>
+    <mergeCell ref="Q34:AK34"/>
+    <mergeCell ref="Q30:AK30"/>
+    <mergeCell ref="Q31:AK31"/>
+    <mergeCell ref="Q32:AK32"/>
+    <mergeCell ref="Q33:AK33"/>
+    <mergeCell ref="Q23:AK23"/>
+    <mergeCell ref="C17:P17"/>
+    <mergeCell ref="C14:P14"/>
+    <mergeCell ref="C15:P15"/>
+    <mergeCell ref="C16:P16"/>
+    <mergeCell ref="C30:P30"/>
+    <mergeCell ref="C31:P31"/>
+    <mergeCell ref="C32:P32"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C33:P33"/>
+    <mergeCell ref="C27:P27"/>
+    <mergeCell ref="C28:P28"/>
+    <mergeCell ref="C24:P24"/>
+    <mergeCell ref="C25:P25"/>
+    <mergeCell ref="C26:P26"/>
+    <mergeCell ref="C29:P29"/>
+    <mergeCell ref="C22:P22"/>
+    <mergeCell ref="C23:P23"/>
+    <mergeCell ref="C7:P7"/>
+    <mergeCell ref="C8:P8"/>
+    <mergeCell ref="C9:P9"/>
+    <mergeCell ref="C10:P10"/>
+    <mergeCell ref="C18:P18"/>
+    <mergeCell ref="C19:P19"/>
+    <mergeCell ref="C20:P20"/>
+    <mergeCell ref="C21:P21"/>
+    <mergeCell ref="C11:P11"/>
+    <mergeCell ref="C12:P12"/>
+    <mergeCell ref="C13:P13"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A10:B10"/>
     <mergeCell ref="AX1:BA1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="I2:L2"/>
@@ -10610,202 +10680,15 @@
     <mergeCell ref="M1:W1"/>
     <mergeCell ref="X1:Z2"/>
     <mergeCell ref="AA1:AJ2"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C33:P33"/>
-    <mergeCell ref="C27:P27"/>
-    <mergeCell ref="C28:P28"/>
-    <mergeCell ref="C24:P24"/>
-    <mergeCell ref="C25:P25"/>
-    <mergeCell ref="C26:P26"/>
-    <mergeCell ref="C29:P29"/>
-    <mergeCell ref="C22:P22"/>
-    <mergeCell ref="C23:P23"/>
-    <mergeCell ref="C7:P7"/>
-    <mergeCell ref="C8:P8"/>
-    <mergeCell ref="C9:P9"/>
-    <mergeCell ref="C10:P10"/>
-    <mergeCell ref="C18:P18"/>
-    <mergeCell ref="C19:P19"/>
-    <mergeCell ref="C20:P20"/>
-    <mergeCell ref="C21:P21"/>
-    <mergeCell ref="C11:P11"/>
-    <mergeCell ref="C12:P12"/>
-    <mergeCell ref="C13:P13"/>
-    <mergeCell ref="C34:P34"/>
-    <mergeCell ref="Q7:AK7"/>
-    <mergeCell ref="Q8:AK8"/>
-    <mergeCell ref="Q9:AK9"/>
-    <mergeCell ref="Q10:AK10"/>
-    <mergeCell ref="Q11:AK11"/>
-    <mergeCell ref="Q12:AK12"/>
-    <mergeCell ref="Q19:AK19"/>
-    <mergeCell ref="Q20:AK20"/>
-    <mergeCell ref="Q21:AK21"/>
-    <mergeCell ref="Q13:AK13"/>
-    <mergeCell ref="Q34:AK34"/>
-    <mergeCell ref="Q30:AK30"/>
-    <mergeCell ref="Q31:AK31"/>
-    <mergeCell ref="Q32:AK32"/>
-    <mergeCell ref="Q33:AK33"/>
-    <mergeCell ref="Q23:AK23"/>
-    <mergeCell ref="C17:P17"/>
-    <mergeCell ref="C14:P14"/>
-    <mergeCell ref="C15:P15"/>
-    <mergeCell ref="C16:P16"/>
-    <mergeCell ref="C30:P30"/>
-    <mergeCell ref="C31:P31"/>
-    <mergeCell ref="C32:P32"/>
-    <mergeCell ref="AL29:AO29"/>
-    <mergeCell ref="AL27:AO27"/>
-    <mergeCell ref="AL28:AO28"/>
-    <mergeCell ref="Q29:AK29"/>
-    <mergeCell ref="Q27:AK27"/>
-    <mergeCell ref="Q28:AK28"/>
-    <mergeCell ref="AL7:AO7"/>
-    <mergeCell ref="AL8:AO8"/>
-    <mergeCell ref="AL17:AO17"/>
-    <mergeCell ref="AL18:AO18"/>
-    <mergeCell ref="AL19:AO19"/>
-    <mergeCell ref="AL9:AO9"/>
-    <mergeCell ref="AL10:AO10"/>
-    <mergeCell ref="AL11:AO11"/>
-    <mergeCell ref="AL12:AO12"/>
-    <mergeCell ref="AL13:AO13"/>
-    <mergeCell ref="AL21:AO21"/>
-    <mergeCell ref="Q17:AK17"/>
-    <mergeCell ref="Q18:AK18"/>
-    <mergeCell ref="Q22:AK22"/>
-    <mergeCell ref="Q14:AK14"/>
-    <mergeCell ref="AL14:AO14"/>
-    <mergeCell ref="Q15:AK15"/>
-    <mergeCell ref="AL15:AO15"/>
-    <mergeCell ref="AL32:AO32"/>
-    <mergeCell ref="AL33:AO33"/>
-    <mergeCell ref="AL34:AO34"/>
-    <mergeCell ref="AP7:AR7"/>
-    <mergeCell ref="AP8:AR8"/>
-    <mergeCell ref="AP9:AR9"/>
-    <mergeCell ref="AP10:AR10"/>
-    <mergeCell ref="AP18:AR18"/>
-    <mergeCell ref="AP19:AR19"/>
-    <mergeCell ref="AP20:AR20"/>
-    <mergeCell ref="AP21:AR21"/>
-    <mergeCell ref="AP11:AR11"/>
-    <mergeCell ref="AP12:AR12"/>
-    <mergeCell ref="AP13:AR13"/>
-    <mergeCell ref="AP17:AR17"/>
-    <mergeCell ref="AP22:AR22"/>
-    <mergeCell ref="AP23:AR23"/>
-    <mergeCell ref="AL30:AO30"/>
-    <mergeCell ref="AL31:AO31"/>
-    <mergeCell ref="AL20:AO20"/>
-    <mergeCell ref="AP26:AR26"/>
-    <mergeCell ref="AP29:AR29"/>
-    <mergeCell ref="AP30:AR30"/>
-    <mergeCell ref="AP33:AR33"/>
-    <mergeCell ref="AS34:AU34"/>
-    <mergeCell ref="AP34:AR34"/>
-    <mergeCell ref="AS7:AU7"/>
-    <mergeCell ref="AS8:AU8"/>
-    <mergeCell ref="AS9:AU9"/>
-    <mergeCell ref="AS10:AU10"/>
-    <mergeCell ref="AS11:AU11"/>
-    <mergeCell ref="AS12:AU12"/>
-    <mergeCell ref="AS19:AU19"/>
-    <mergeCell ref="AS20:AU20"/>
-    <mergeCell ref="AS21:AU21"/>
-    <mergeCell ref="AS13:AU13"/>
-    <mergeCell ref="AS17:AU17"/>
-    <mergeCell ref="AS18:AU18"/>
-    <mergeCell ref="AS22:AU22"/>
-    <mergeCell ref="AS23:AU23"/>
-    <mergeCell ref="AS24:AU24"/>
-    <mergeCell ref="AS29:AU29"/>
-    <mergeCell ref="AS27:AU27"/>
-    <mergeCell ref="AS32:AU32"/>
-    <mergeCell ref="AS33:AU33"/>
-    <mergeCell ref="AP24:AR24"/>
-    <mergeCell ref="AP25:AR25"/>
-    <mergeCell ref="AP32:AR32"/>
-    <mergeCell ref="AV7:BA7"/>
-    <mergeCell ref="AV8:BA8"/>
-    <mergeCell ref="AV9:BA9"/>
-    <mergeCell ref="AV10:BA10"/>
-    <mergeCell ref="AV11:BA11"/>
-    <mergeCell ref="AV12:BA12"/>
-    <mergeCell ref="AV34:BA34"/>
-    <mergeCell ref="AV24:BA24"/>
-    <mergeCell ref="AV25:BA25"/>
-    <mergeCell ref="AV26:BA26"/>
-    <mergeCell ref="AV29:BA29"/>
-    <mergeCell ref="AV30:BA30"/>
-    <mergeCell ref="AV31:BA31"/>
-    <mergeCell ref="AV27:BA27"/>
-    <mergeCell ref="AV28:BA28"/>
-    <mergeCell ref="AV32:BA32"/>
-    <mergeCell ref="AV33:BA33"/>
-    <mergeCell ref="AV13:BA13"/>
-    <mergeCell ref="AV22:BA22"/>
-    <mergeCell ref="AV23:BA23"/>
-    <mergeCell ref="AV17:BA17"/>
-    <mergeCell ref="AV18:BA18"/>
-    <mergeCell ref="AV19:BA19"/>
-    <mergeCell ref="AV16:BA16"/>
-    <mergeCell ref="AV20:BA20"/>
-    <mergeCell ref="AV21:BA21"/>
-    <mergeCell ref="AV14:BA14"/>
-    <mergeCell ref="AV15:BA15"/>
-    <mergeCell ref="AS28:AU28"/>
-    <mergeCell ref="AS30:AU30"/>
-    <mergeCell ref="AS31:AU31"/>
-    <mergeCell ref="AS25:AU25"/>
-    <mergeCell ref="AP31:AR31"/>
-    <mergeCell ref="AP27:AR27"/>
-    <mergeCell ref="AP28:AR28"/>
-    <mergeCell ref="AS16:AU16"/>
-    <mergeCell ref="AP15:AR15"/>
-    <mergeCell ref="AS26:AU26"/>
-    <mergeCell ref="AS14:AU14"/>
-    <mergeCell ref="AS15:AU15"/>
-    <mergeCell ref="AL22:AO22"/>
-    <mergeCell ref="AL23:AO23"/>
-    <mergeCell ref="AL24:AO24"/>
-    <mergeCell ref="AL25:AO25"/>
-    <mergeCell ref="AL26:AO26"/>
-    <mergeCell ref="Q24:AK24"/>
-    <mergeCell ref="Q25:AK25"/>
-    <mergeCell ref="Q26:AK26"/>
-    <mergeCell ref="AP14:AR14"/>
-    <mergeCell ref="Q16:AK16"/>
-    <mergeCell ref="AL16:AO16"/>
-    <mergeCell ref="AP16:AR16"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="AT3:AW3"/>
+    <mergeCell ref="AN1:AP1"/>
+    <mergeCell ref="AQ1:AS1"/>
+    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:P6"/>
+    <mergeCell ref="Q6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
   </mergeCells>
   <phoneticPr fontId="52"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -10833,300 +10716,300 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:75" ht="12" customHeight="1">
-      <c r="A1" s="223" t="s">
+      <c r="A1" s="207" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="223"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="206" t="s">
+      <c r="B1" s="207"/>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
+      <c r="E1" s="207"/>
+      <c r="F1" s="207"/>
+      <c r="G1" s="207"/>
+      <c r="H1" s="207"/>
+      <c r="I1" s="194" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="206"/>
-      <c r="K1" s="206"/>
-      <c r="L1" s="206"/>
-      <c r="M1" s="221" t="str">
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="194"/>
+      <c r="M1" s="205" t="str">
         <f>変更来歴!M1</f>
         <v>ヒロセ電機株式会社</v>
       </c>
-      <c r="N1" s="221"/>
-      <c r="O1" s="221"/>
-      <c r="P1" s="221"/>
-      <c r="Q1" s="221"/>
-      <c r="R1" s="221"/>
-      <c r="S1" s="221"/>
-      <c r="T1" s="221"/>
-      <c r="U1" s="221"/>
-      <c r="V1" s="221"/>
-      <c r="W1" s="221"/>
-      <c r="X1" s="206" t="s">
+      <c r="N1" s="205"/>
+      <c r="O1" s="205"/>
+      <c r="P1" s="205"/>
+      <c r="Q1" s="205"/>
+      <c r="R1" s="205"/>
+      <c r="S1" s="205"/>
+      <c r="T1" s="205"/>
+      <c r="U1" s="205"/>
+      <c r="V1" s="205"/>
+      <c r="W1" s="205"/>
+      <c r="X1" s="194" t="s">
         <v>7</v>
       </c>
-      <c r="Y1" s="206"/>
-      <c r="Z1" s="206"/>
-      <c r="AA1" s="225" t="str">
+      <c r="Y1" s="194"/>
+      <c r="Z1" s="194"/>
+      <c r="AA1" s="209" t="str">
         <f>変更来歴!AA1</f>
         <v>化学物質データ申請</v>
       </c>
-      <c r="AB1" s="225"/>
-      <c r="AC1" s="225"/>
-      <c r="AD1" s="225"/>
-      <c r="AE1" s="225"/>
-      <c r="AF1" s="225"/>
-      <c r="AG1" s="225"/>
-      <c r="AH1" s="225"/>
-      <c r="AI1" s="225"/>
-      <c r="AJ1" s="225"/>
-      <c r="AK1" s="210" t="s">
+      <c r="AB1" s="209"/>
+      <c r="AC1" s="209"/>
+      <c r="AD1" s="209"/>
+      <c r="AE1" s="209"/>
+      <c r="AF1" s="209"/>
+      <c r="AG1" s="209"/>
+      <c r="AH1" s="209"/>
+      <c r="AI1" s="209"/>
+      <c r="AJ1" s="209"/>
+      <c r="AK1" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="AL1" s="210"/>
-      <c r="AM1" s="210"/>
-      <c r="AN1" s="211" t="str">
+      <c r="AL1" s="183"/>
+      <c r="AM1" s="183"/>
+      <c r="AN1" s="185" t="str">
         <f>変更来歴!AP7</f>
         <v>古竹</v>
       </c>
-      <c r="AO1" s="211"/>
-      <c r="AP1" s="211"/>
-      <c r="AQ1" s="211"/>
-      <c r="AR1" s="211"/>
-      <c r="AS1" s="210" t="s">
+      <c r="AO1" s="185"/>
+      <c r="AP1" s="185"/>
+      <c r="AQ1" s="185"/>
+      <c r="AR1" s="185"/>
+      <c r="AS1" s="183" t="s">
         <v>9</v>
       </c>
-      <c r="AT1" s="210"/>
-      <c r="AU1" s="210"/>
-      <c r="AV1" s="213">
+      <c r="AT1" s="183"/>
+      <c r="AU1" s="183"/>
+      <c r="AV1" s="186">
         <f>変更来歴!AL7</f>
         <v>46125</v>
       </c>
-      <c r="AW1" s="226"/>
-      <c r="AX1" s="226"/>
-      <c r="AY1" s="226"/>
-      <c r="AZ1" s="202" t="s">
+      <c r="AW1" s="184"/>
+      <c r="AX1" s="184"/>
+      <c r="AY1" s="184"/>
+      <c r="AZ1" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="BA1" s="203"/>
-      <c r="BB1" s="203"/>
-      <c r="BC1" s="204"/>
+      <c r="BA1" s="191"/>
+      <c r="BB1" s="191"/>
+      <c r="BC1" s="192"/>
     </row>
     <row r="2" spans="1:75">
-      <c r="A2" s="205" t="s">
+      <c r="A2" s="193" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="205"/>
-      <c r="C2" s="205"/>
-      <c r="D2" s="205"/>
-      <c r="E2" s="205"/>
-      <c r="F2" s="205"/>
-      <c r="G2" s="205"/>
-      <c r="H2" s="205"/>
-      <c r="I2" s="206" t="s">
+      <c r="B2" s="193"/>
+      <c r="C2" s="193"/>
+      <c r="D2" s="193"/>
+      <c r="E2" s="193"/>
+      <c r="F2" s="193"/>
+      <c r="G2" s="193"/>
+      <c r="H2" s="193"/>
+      <c r="I2" s="194" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="206"/>
-      <c r="K2" s="206"/>
-      <c r="L2" s="206"/>
-      <c r="M2" s="238" t="str">
+      <c r="J2" s="194"/>
+      <c r="K2" s="194"/>
+      <c r="L2" s="194"/>
+      <c r="M2" s="230" t="str">
         <f>変更来歴!M2</f>
         <v>　</v>
       </c>
-      <c r="N2" s="238"/>
-      <c r="O2" s="238"/>
-      <c r="P2" s="238"/>
-      <c r="Q2" s="238"/>
-      <c r="R2" s="238"/>
-      <c r="S2" s="238"/>
-      <c r="T2" s="238"/>
-      <c r="U2" s="238"/>
-      <c r="V2" s="238"/>
-      <c r="W2" s="238"/>
-      <c r="X2" s="206"/>
-      <c r="Y2" s="206"/>
-      <c r="Z2" s="206"/>
-      <c r="AA2" s="225"/>
-      <c r="AB2" s="225"/>
-      <c r="AC2" s="225"/>
-      <c r="AD2" s="225"/>
-      <c r="AE2" s="225"/>
-      <c r="AF2" s="225"/>
-      <c r="AG2" s="225"/>
-      <c r="AH2" s="225"/>
-      <c r="AI2" s="225"/>
-      <c r="AJ2" s="225"/>
-      <c r="AK2" s="210" t="s">
+      <c r="N2" s="230"/>
+      <c r="O2" s="230"/>
+      <c r="P2" s="230"/>
+      <c r="Q2" s="230"/>
+      <c r="R2" s="230"/>
+      <c r="S2" s="230"/>
+      <c r="T2" s="230"/>
+      <c r="U2" s="230"/>
+      <c r="V2" s="230"/>
+      <c r="W2" s="230"/>
+      <c r="X2" s="194"/>
+      <c r="Y2" s="194"/>
+      <c r="Z2" s="194"/>
+      <c r="AA2" s="209"/>
+      <c r="AB2" s="209"/>
+      <c r="AC2" s="209"/>
+      <c r="AD2" s="209"/>
+      <c r="AE2" s="209"/>
+      <c r="AF2" s="209"/>
+      <c r="AG2" s="209"/>
+      <c r="AH2" s="209"/>
+      <c r="AI2" s="209"/>
+      <c r="AJ2" s="209"/>
+      <c r="AK2" s="183" t="s">
         <v>12</v>
       </c>
-      <c r="AL2" s="210"/>
-      <c r="AM2" s="210"/>
-      <c r="AN2" s="211" t="str">
+      <c r="AL2" s="183"/>
+      <c r="AM2" s="183"/>
+      <c r="AN2" s="185" t="str">
         <f ca="1">INDIRECT("変更来歴!AP" &amp; COUNTA(変更来歴!AP7:'変更来歴'!AP39) + 6)</f>
         <v>古竹</v>
       </c>
-      <c r="AO2" s="211"/>
-      <c r="AP2" s="211"/>
-      <c r="AQ2" s="211"/>
-      <c r="AR2" s="211"/>
-      <c r="AS2" s="210" t="s">
+      <c r="AO2" s="185"/>
+      <c r="AP2" s="185"/>
+      <c r="AQ2" s="185"/>
+      <c r="AR2" s="185"/>
+      <c r="AS2" s="183" t="s">
         <v>13</v>
       </c>
-      <c r="AT2" s="210"/>
-      <c r="AU2" s="210"/>
-      <c r="AV2" s="213">
+      <c r="AT2" s="183"/>
+      <c r="AU2" s="183"/>
+      <c r="AV2" s="186">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
         <v>46162</v>
       </c>
-      <c r="AW2" s="226"/>
-      <c r="AX2" s="226"/>
-      <c r="AY2" s="226"/>
-      <c r="AZ2" s="214" t="str">
+      <c r="AW2" s="184"/>
+      <c r="AX2" s="184"/>
+      <c r="AY2" s="184"/>
+      <c r="AZ2" s="198" t="str">
         <f>変更来歴!AX2</f>
         <v>IMWF-53</v>
       </c>
-      <c r="BA2" s="215"/>
-      <c r="BB2" s="215"/>
-      <c r="BC2" s="216"/>
+      <c r="BA2" s="199"/>
+      <c r="BB2" s="199"/>
+      <c r="BC2" s="200"/>
     </row>
     <row r="3" spans="1:75" ht="12" customHeight="1">
-      <c r="A3" s="220" t="str">
+      <c r="A3" s="204" t="str">
         <f>変更来歴!A3</f>
         <v>画面設計書</v>
       </c>
-      <c r="B3" s="220"/>
-      <c r="C3" s="220"/>
-      <c r="D3" s="220"/>
-      <c r="E3" s="220"/>
-      <c r="F3" s="220"/>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="206" t="s">
+      <c r="B3" s="204"/>
+      <c r="C3" s="204"/>
+      <c r="D3" s="204"/>
+      <c r="E3" s="204"/>
+      <c r="F3" s="204"/>
+      <c r="G3" s="204"/>
+      <c r="H3" s="204"/>
+      <c r="I3" s="194" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="206"/>
-      <c r="K3" s="206"/>
-      <c r="L3" s="206"/>
-      <c r="M3" s="221" t="str">
+      <c r="J3" s="194"/>
+      <c r="K3" s="194"/>
+      <c r="L3" s="194"/>
+      <c r="M3" s="205" t="str">
         <f ca="1">RIGHT(CELL("filename",A1),LEN(CELL("filename",A1))-FIND("]",CELL("filename",A1)))</f>
         <v>化学物質データ申請画面(日英併記)</v>
       </c>
-      <c r="N3" s="221"/>
-      <c r="O3" s="221"/>
-      <c r="P3" s="221"/>
-      <c r="Q3" s="221"/>
-      <c r="R3" s="221"/>
-      <c r="S3" s="221"/>
-      <c r="T3" s="221"/>
-      <c r="U3" s="221"/>
-      <c r="V3" s="221"/>
-      <c r="W3" s="221"/>
-      <c r="X3" s="206" t="s">
+      <c r="N3" s="205"/>
+      <c r="O3" s="205"/>
+      <c r="P3" s="205"/>
+      <c r="Q3" s="205"/>
+      <c r="R3" s="205"/>
+      <c r="S3" s="205"/>
+      <c r="T3" s="205"/>
+      <c r="U3" s="205"/>
+      <c r="V3" s="205"/>
+      <c r="W3" s="205"/>
+      <c r="X3" s="194" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="206"/>
-      <c r="Z3" s="206"/>
-      <c r="AA3" s="222" t="str">
+      <c r="Y3" s="194"/>
+      <c r="Z3" s="194"/>
+      <c r="AA3" s="206" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
         <v>表紙画面</v>
       </c>
-      <c r="AB3" s="222"/>
-      <c r="AC3" s="222"/>
-      <c r="AD3" s="222"/>
-      <c r="AE3" s="222"/>
-      <c r="AF3" s="222"/>
-      <c r="AG3" s="222"/>
-      <c r="AH3" s="222"/>
-      <c r="AI3" s="222"/>
-      <c r="AJ3" s="222"/>
-      <c r="AK3" s="222"/>
-      <c r="AL3" s="222"/>
-      <c r="AM3" s="222"/>
-      <c r="AN3" s="222"/>
-      <c r="AO3" s="222"/>
-      <c r="AP3" s="222"/>
-      <c r="AQ3" s="222"/>
-      <c r="AR3" s="222"/>
-      <c r="AS3" s="210" t="s">
+      <c r="AB3" s="206"/>
+      <c r="AC3" s="206"/>
+      <c r="AD3" s="206"/>
+      <c r="AE3" s="206"/>
+      <c r="AF3" s="206"/>
+      <c r="AG3" s="206"/>
+      <c r="AH3" s="206"/>
+      <c r="AI3" s="206"/>
+      <c r="AJ3" s="206"/>
+      <c r="AK3" s="206"/>
+      <c r="AL3" s="206"/>
+      <c r="AM3" s="206"/>
+      <c r="AN3" s="206"/>
+      <c r="AO3" s="206"/>
+      <c r="AP3" s="206"/>
+      <c r="AQ3" s="206"/>
+      <c r="AR3" s="206"/>
+      <c r="AS3" s="183" t="s">
         <v>15</v>
       </c>
-      <c r="AT3" s="210"/>
-      <c r="AU3" s="210"/>
-      <c r="AV3" s="226" t="str">
+      <c r="AT3" s="183"/>
+      <c r="AU3" s="183"/>
+      <c r="AV3" s="184" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
         <v>r1.2</v>
       </c>
-      <c r="AW3" s="226"/>
-      <c r="AX3" s="226"/>
-      <c r="AY3" s="226"/>
-      <c r="AZ3" s="217"/>
-      <c r="BA3" s="218"/>
-      <c r="BB3" s="218"/>
-      <c r="BC3" s="219"/>
+      <c r="AW3" s="184"/>
+      <c r="AX3" s="184"/>
+      <c r="AY3" s="184"/>
+      <c r="AZ3" s="201"/>
+      <c r="BA3" s="202"/>
+      <c r="BB3" s="202"/>
+      <c r="BC3" s="203"/>
     </row>
     <row r="4" spans="1:75" ht="5.9" customHeight="1"/>
     <row r="5" spans="1:75" ht="13.5" customHeight="1">
-      <c r="A5" s="232" t="str">
+      <c r="A5" s="234" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
         <v>画面レイアウト(表紙)</v>
       </c>
-      <c r="B5" s="233"/>
-      <c r="C5" s="233"/>
-      <c r="D5" s="233"/>
-      <c r="E5" s="233"/>
-      <c r="F5" s="233"/>
-      <c r="G5" s="233"/>
-      <c r="H5" s="233"/>
-      <c r="I5" s="233"/>
-      <c r="J5" s="233"/>
-      <c r="K5" s="233"/>
-      <c r="L5" s="233"/>
-      <c r="M5" s="233"/>
-      <c r="N5" s="233"/>
-      <c r="O5" s="233"/>
-      <c r="P5" s="233"/>
-      <c r="Q5" s="233"/>
-      <c r="R5" s="233"/>
-      <c r="S5" s="233"/>
-      <c r="T5" s="233"/>
-      <c r="U5" s="233"/>
-      <c r="V5" s="233"/>
-      <c r="W5" s="233"/>
-      <c r="X5" s="233"/>
-      <c r="Y5" s="233"/>
-      <c r="Z5" s="233"/>
-      <c r="AA5" s="233"/>
-      <c r="AB5" s="233"/>
-      <c r="AC5" s="233"/>
-      <c r="AD5" s="233"/>
-      <c r="AE5" s="233"/>
-      <c r="AF5" s="233"/>
-      <c r="AG5" s="233"/>
-      <c r="AH5" s="233"/>
-      <c r="AI5" s="233"/>
-      <c r="AJ5" s="233"/>
-      <c r="AK5" s="233"/>
-      <c r="AL5" s="233"/>
-      <c r="AM5" s="233"/>
-      <c r="AN5" s="233"/>
-      <c r="AO5" s="233"/>
-      <c r="AP5" s="233"/>
-      <c r="AQ5" s="233"/>
-      <c r="AR5" s="233"/>
-      <c r="AS5" s="233"/>
-      <c r="AT5" s="233"/>
-      <c r="AU5" s="233"/>
-      <c r="AV5" s="233"/>
-      <c r="AW5" s="233"/>
-      <c r="AX5" s="233"/>
-      <c r="AY5" s="233"/>
-      <c r="AZ5" s="233"/>
-      <c r="BA5" s="234"/>
-      <c r="BB5" s="235" t="s">
+      <c r="B5" s="235"/>
+      <c r="C5" s="235"/>
+      <c r="D5" s="235"/>
+      <c r="E5" s="235"/>
+      <c r="F5" s="235"/>
+      <c r="G5" s="235"/>
+      <c r="H5" s="235"/>
+      <c r="I5" s="235"/>
+      <c r="J5" s="235"/>
+      <c r="K5" s="235"/>
+      <c r="L5" s="235"/>
+      <c r="M5" s="235"/>
+      <c r="N5" s="235"/>
+      <c r="O5" s="235"/>
+      <c r="P5" s="235"/>
+      <c r="Q5" s="235"/>
+      <c r="R5" s="235"/>
+      <c r="S5" s="235"/>
+      <c r="T5" s="235"/>
+      <c r="U5" s="235"/>
+      <c r="V5" s="235"/>
+      <c r="W5" s="235"/>
+      <c r="X5" s="235"/>
+      <c r="Y5" s="235"/>
+      <c r="Z5" s="235"/>
+      <c r="AA5" s="235"/>
+      <c r="AB5" s="235"/>
+      <c r="AC5" s="235"/>
+      <c r="AD5" s="235"/>
+      <c r="AE5" s="235"/>
+      <c r="AF5" s="235"/>
+      <c r="AG5" s="235"/>
+      <c r="AH5" s="235"/>
+      <c r="AI5" s="235"/>
+      <c r="AJ5" s="235"/>
+      <c r="AK5" s="235"/>
+      <c r="AL5" s="235"/>
+      <c r="AM5" s="235"/>
+      <c r="AN5" s="235"/>
+      <c r="AO5" s="235"/>
+      <c r="AP5" s="235"/>
+      <c r="AQ5" s="235"/>
+      <c r="AR5" s="235"/>
+      <c r="AS5" s="235"/>
+      <c r="AT5" s="235"/>
+      <c r="AU5" s="235"/>
+      <c r="AV5" s="235"/>
+      <c r="AW5" s="235"/>
+      <c r="AX5" s="235"/>
+      <c r="AY5" s="235"/>
+      <c r="AZ5" s="235"/>
+      <c r="BA5" s="236"/>
+      <c r="BB5" s="237" t="s">
         <v>24</v>
       </c>
-      <c r="BC5" s="236"/>
+      <c r="BC5" s="238"/>
       <c r="BD5" s="24"/>
     </row>
     <row r="6" spans="1:75" ht="13.5" customHeight="1">
@@ -11406,12 +11289,12 @@
       <c r="BB8" s="49"/>
       <c r="BC8" s="50"/>
       <c r="BD8" s="34"/>
-      <c r="BE8" s="229" t="s">
+      <c r="BE8" s="231" t="s">
         <v>131</v>
       </c>
-      <c r="BF8" s="230"/>
-      <c r="BG8" s="230"/>
-      <c r="BH8" s="231"/>
+      <c r="BF8" s="232"/>
+      <c r="BG8" s="232"/>
+      <c r="BH8" s="233"/>
     </row>
     <row r="9" spans="1:75" ht="24" customHeight="1">
       <c r="A9" s="36"/>
@@ -11421,46 +11304,46 @@
       <c r="E9" s="40"/>
       <c r="F9" s="38"/>
       <c r="G9" s="38"/>
-      <c r="H9" s="237" t="s">
+      <c r="H9" s="229" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="237"/>
-      <c r="J9" s="237"/>
-      <c r="K9" s="237"/>
-      <c r="L9" s="237"/>
-      <c r="M9" s="237"/>
-      <c r="N9" s="237"/>
-      <c r="O9" s="237"/>
-      <c r="P9" s="237"/>
-      <c r="Q9" s="237"/>
-      <c r="R9" s="237"/>
-      <c r="S9" s="237"/>
-      <c r="T9" s="237"/>
-      <c r="U9" s="237"/>
-      <c r="V9" s="237"/>
-      <c r="W9" s="237"/>
-      <c r="X9" s="237"/>
-      <c r="Y9" s="237"/>
-      <c r="Z9" s="237"/>
-      <c r="AA9" s="237"/>
-      <c r="AB9" s="237"/>
-      <c r="AC9" s="237"/>
-      <c r="AD9" s="237"/>
-      <c r="AE9" s="237"/>
-      <c r="AF9" s="237"/>
-      <c r="AG9" s="237"/>
-      <c r="AH9" s="237"/>
-      <c r="AI9" s="237"/>
-      <c r="AJ9" s="237"/>
-      <c r="AK9" s="237"/>
-      <c r="AL9" s="237"/>
-      <c r="AM9" s="237"/>
-      <c r="AN9" s="237"/>
-      <c r="AO9" s="237"/>
-      <c r="AP9" s="237"/>
-      <c r="AQ9" s="237"/>
-      <c r="AR9" s="237"/>
-      <c r="AS9" s="237"/>
+      <c r="I9" s="229"/>
+      <c r="J9" s="229"/>
+      <c r="K9" s="229"/>
+      <c r="L9" s="229"/>
+      <c r="M9" s="229"/>
+      <c r="N9" s="229"/>
+      <c r="O9" s="229"/>
+      <c r="P9" s="229"/>
+      <c r="Q9" s="229"/>
+      <c r="R9" s="229"/>
+      <c r="S9" s="229"/>
+      <c r="T9" s="229"/>
+      <c r="U9" s="229"/>
+      <c r="V9" s="229"/>
+      <c r="W9" s="229"/>
+      <c r="X9" s="229"/>
+      <c r="Y9" s="229"/>
+      <c r="Z9" s="229"/>
+      <c r="AA9" s="229"/>
+      <c r="AB9" s="229"/>
+      <c r="AC9" s="229"/>
+      <c r="AD9" s="229"/>
+      <c r="AE9" s="229"/>
+      <c r="AF9" s="229"/>
+      <c r="AG9" s="229"/>
+      <c r="AH9" s="229"/>
+      <c r="AI9" s="229"/>
+      <c r="AJ9" s="229"/>
+      <c r="AK9" s="229"/>
+      <c r="AL9" s="229"/>
+      <c r="AM9" s="229"/>
+      <c r="AN9" s="229"/>
+      <c r="AO9" s="229"/>
+      <c r="AP9" s="229"/>
+      <c r="AQ9" s="229"/>
+      <c r="AR9" s="229"/>
+      <c r="AS9" s="229"/>
       <c r="AT9" s="43"/>
       <c r="AU9" s="41"/>
       <c r="AV9" s="44"/>
@@ -26703,6 +26586,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="BE8:BH8"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="A5:BA5"/>
+    <mergeCell ref="BB5:BC5"/>
+    <mergeCell ref="AV2:AY2"/>
+    <mergeCell ref="AZ2:BC3"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="I3:L3"/>
+    <mergeCell ref="M3:W3"/>
+    <mergeCell ref="X3:Z3"/>
+    <mergeCell ref="AA3:AR3"/>
+    <mergeCell ref="AS3:AU3"/>
+    <mergeCell ref="AV3:AY3"/>
     <mergeCell ref="H9:AS9"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AU1"/>
@@ -26719,19 +26615,6 @@
     <mergeCell ref="M1:W1"/>
     <mergeCell ref="X1:Z2"/>
     <mergeCell ref="AA1:AJ2"/>
-    <mergeCell ref="BE8:BH8"/>
-    <mergeCell ref="AK1:AM1"/>
-    <mergeCell ref="A5:BA5"/>
-    <mergeCell ref="BB5:BC5"/>
-    <mergeCell ref="AV2:AY2"/>
-    <mergeCell ref="AZ2:BC3"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="I3:L3"/>
-    <mergeCell ref="M3:W3"/>
-    <mergeCell ref="X3:Z3"/>
-    <mergeCell ref="AA3:AR3"/>
-    <mergeCell ref="AS3:AU3"/>
-    <mergeCell ref="AV3:AY3"/>
   </mergeCells>
   <phoneticPr fontId="56"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0.19685039370078741" footer="0.19685039370078741"/>
@@ -27013,17 +26896,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="12.75" customHeight="1">
-      <c r="A1" s="254" t="s">
+      <c r="A1" s="286" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="254"/>
-      <c r="C1" s="254"/>
-      <c r="D1" s="254"/>
-      <c r="E1" s="254"/>
-      <c r="F1" s="254"/>
-      <c r="G1" s="254"/>
-      <c r="H1" s="254"/>
-      <c r="I1" s="254"/>
+      <c r="B1" s="286"/>
+      <c r="C1" s="286"/>
+      <c r="D1" s="286"/>
+      <c r="E1" s="286"/>
+      <c r="F1" s="286"/>
+      <c r="G1" s="286"/>
+      <c r="H1" s="286"/>
+      <c r="I1" s="286"/>
       <c r="J1" s="128"/>
       <c r="K1" s="128"/>
       <c r="L1" s="128"/>
@@ -27088,719 +26971,719 @@
       <c r="BS1" s="129"/>
     </row>
     <row r="2" spans="1:71" ht="12.75" customHeight="1">
-      <c r="A2" s="255" t="s">
+      <c r="A2" s="287" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
-      <c r="K2" s="255"/>
-      <c r="L2" s="255"/>
-      <c r="M2" s="255"/>
-      <c r="N2" s="255"/>
-      <c r="O2" s="255"/>
-      <c r="P2" s="255"/>
-      <c r="Q2" s="256"/>
-      <c r="R2" s="256"/>
-      <c r="S2" s="256"/>
-      <c r="T2" s="256"/>
-      <c r="U2" s="256"/>
-      <c r="V2" s="256"/>
-      <c r="W2" s="256"/>
-      <c r="X2" s="256"/>
-      <c r="Y2" s="256"/>
-      <c r="Z2" s="256"/>
-      <c r="AA2" s="256"/>
-      <c r="AB2" s="256"/>
-      <c r="AC2" s="256"/>
-      <c r="AD2" s="256"/>
-      <c r="AE2" s="256"/>
-      <c r="AF2" s="256"/>
-      <c r="AG2" s="256"/>
-      <c r="AH2" s="256"/>
-      <c r="AI2" s="256"/>
-      <c r="AJ2" s="256"/>
-      <c r="AK2" s="256"/>
-      <c r="AL2" s="256"/>
-      <c r="AM2" s="256"/>
-      <c r="AN2" s="256"/>
-      <c r="AO2" s="256"/>
-      <c r="AP2" s="256"/>
-      <c r="AQ2" s="256"/>
-      <c r="AR2" s="256"/>
-      <c r="AS2" s="256"/>
-      <c r="AT2" s="256"/>
-      <c r="AU2" s="256"/>
-      <c r="AV2" s="256"/>
-      <c r="AW2" s="256"/>
-      <c r="AX2" s="256"/>
-      <c r="AY2" s="256"/>
-      <c r="AZ2" s="256"/>
-      <c r="BA2" s="256"/>
-      <c r="BB2" s="256"/>
-      <c r="BC2" s="256"/>
-      <c r="BD2" s="256"/>
-      <c r="BE2" s="256"/>
-      <c r="BF2" s="256"/>
-      <c r="BG2" s="256"/>
-      <c r="BH2" s="256"/>
-      <c r="BI2" s="256"/>
-      <c r="BJ2" s="256"/>
-      <c r="BK2" s="256"/>
-      <c r="BL2" s="256"/>
-      <c r="BM2" s="256"/>
-      <c r="BN2" s="256"/>
-      <c r="BO2" s="256"/>
-      <c r="BP2" s="256"/>
-      <c r="BQ2" s="256"/>
-      <c r="BR2" s="256"/>
-      <c r="BS2" s="256"/>
+      <c r="B2" s="287"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="287"/>
+      <c r="E2" s="287"/>
+      <c r="F2" s="287"/>
+      <c r="G2" s="287"/>
+      <c r="H2" s="287"/>
+      <c r="I2" s="287"/>
+      <c r="J2" s="287"/>
+      <c r="K2" s="287"/>
+      <c r="L2" s="287"/>
+      <c r="M2" s="287"/>
+      <c r="N2" s="287"/>
+      <c r="O2" s="287"/>
+      <c r="P2" s="287"/>
+      <c r="Q2" s="288"/>
+      <c r="R2" s="288"/>
+      <c r="S2" s="288"/>
+      <c r="T2" s="288"/>
+      <c r="U2" s="288"/>
+      <c r="V2" s="288"/>
+      <c r="W2" s="288"/>
+      <c r="X2" s="288"/>
+      <c r="Y2" s="288"/>
+      <c r="Z2" s="288"/>
+      <c r="AA2" s="288"/>
+      <c r="AB2" s="288"/>
+      <c r="AC2" s="288"/>
+      <c r="AD2" s="288"/>
+      <c r="AE2" s="288"/>
+      <c r="AF2" s="288"/>
+      <c r="AG2" s="288"/>
+      <c r="AH2" s="288"/>
+      <c r="AI2" s="288"/>
+      <c r="AJ2" s="288"/>
+      <c r="AK2" s="288"/>
+      <c r="AL2" s="288"/>
+      <c r="AM2" s="288"/>
+      <c r="AN2" s="288"/>
+      <c r="AO2" s="288"/>
+      <c r="AP2" s="288"/>
+      <c r="AQ2" s="288"/>
+      <c r="AR2" s="288"/>
+      <c r="AS2" s="288"/>
+      <c r="AT2" s="288"/>
+      <c r="AU2" s="288"/>
+      <c r="AV2" s="288"/>
+      <c r="AW2" s="288"/>
+      <c r="AX2" s="288"/>
+      <c r="AY2" s="288"/>
+      <c r="AZ2" s="288"/>
+      <c r="BA2" s="288"/>
+      <c r="BB2" s="288"/>
+      <c r="BC2" s="288"/>
+      <c r="BD2" s="288"/>
+      <c r="BE2" s="288"/>
+      <c r="BF2" s="288"/>
+      <c r="BG2" s="288"/>
+      <c r="BH2" s="288"/>
+      <c r="BI2" s="288"/>
+      <c r="BJ2" s="288"/>
+      <c r="BK2" s="288"/>
+      <c r="BL2" s="288"/>
+      <c r="BM2" s="288"/>
+      <c r="BN2" s="288"/>
+      <c r="BO2" s="288"/>
+      <c r="BP2" s="288"/>
+      <c r="BQ2" s="288"/>
+      <c r="BR2" s="288"/>
+      <c r="BS2" s="288"/>
     </row>
     <row r="3" spans="1:71" ht="27.75" customHeight="1">
-      <c r="A3" s="257" t="s">
+      <c r="A3" s="289" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="258"/>
-      <c r="C3" s="258" t="s">
+      <c r="B3" s="290"/>
+      <c r="C3" s="290" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="258"/>
-      <c r="E3" s="258"/>
-      <c r="F3" s="258"/>
-      <c r="G3" s="258"/>
-      <c r="H3" s="258"/>
-      <c r="I3" s="258"/>
-      <c r="J3" s="258"/>
-      <c r="K3" s="258"/>
-      <c r="L3" s="258"/>
-      <c r="M3" s="258"/>
-      <c r="N3" s="258"/>
-      <c r="O3" s="258"/>
-      <c r="P3" s="258"/>
-      <c r="Q3" s="260" t="s">
+      <c r="D3" s="290"/>
+      <c r="E3" s="290"/>
+      <c r="F3" s="290"/>
+      <c r="G3" s="290"/>
+      <c r="H3" s="290"/>
+      <c r="I3" s="290"/>
+      <c r="J3" s="290"/>
+      <c r="K3" s="290"/>
+      <c r="L3" s="290"/>
+      <c r="M3" s="290"/>
+      <c r="N3" s="290"/>
+      <c r="O3" s="290"/>
+      <c r="P3" s="290"/>
+      <c r="Q3" s="292" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="261"/>
-      <c r="S3" s="261"/>
-      <c r="T3" s="261"/>
-      <c r="U3" s="261"/>
-      <c r="V3" s="261"/>
-      <c r="W3" s="261"/>
-      <c r="X3" s="261"/>
-      <c r="Y3" s="261"/>
-      <c r="Z3" s="261"/>
-      <c r="AA3" s="262"/>
-      <c r="AB3" s="272" t="s">
+      <c r="R3" s="293"/>
+      <c r="S3" s="293"/>
+      <c r="T3" s="293"/>
+      <c r="U3" s="293"/>
+      <c r="V3" s="293"/>
+      <c r="W3" s="293"/>
+      <c r="X3" s="293"/>
+      <c r="Y3" s="293"/>
+      <c r="Z3" s="293"/>
+      <c r="AA3" s="294"/>
+      <c r="AB3" s="298" t="s">
         <v>126</v>
       </c>
-      <c r="AC3" s="273"/>
-      <c r="AD3" s="273"/>
-      <c r="AE3" s="273"/>
-      <c r="AF3" s="273"/>
-      <c r="AG3" s="273"/>
-      <c r="AH3" s="273"/>
-      <c r="AI3" s="273"/>
-      <c r="AJ3" s="273"/>
-      <c r="AK3" s="257" t="s">
+      <c r="AC3" s="299"/>
+      <c r="AD3" s="299"/>
+      <c r="AE3" s="299"/>
+      <c r="AF3" s="299"/>
+      <c r="AG3" s="299"/>
+      <c r="AH3" s="299"/>
+      <c r="AI3" s="299"/>
+      <c r="AJ3" s="299"/>
+      <c r="AK3" s="289" t="s">
         <v>40</v>
       </c>
-      <c r="AL3" s="257"/>
-      <c r="AM3" s="257"/>
-      <c r="AN3" s="257"/>
-      <c r="AO3" s="257"/>
-      <c r="AP3" s="257"/>
-      <c r="AQ3" s="257"/>
-      <c r="AR3" s="257"/>
-      <c r="AS3" s="257"/>
-      <c r="AT3" s="257"/>
-      <c r="AU3" s="257"/>
-      <c r="AV3" s="257"/>
-      <c r="AW3" s="257"/>
-      <c r="AX3" s="257"/>
-      <c r="AY3" s="257"/>
-      <c r="AZ3" s="257"/>
-      <c r="BA3" s="257"/>
-      <c r="BB3" s="257"/>
-      <c r="BC3" s="257"/>
-      <c r="BD3" s="257"/>
-      <c r="BE3" s="257"/>
-      <c r="BF3" s="257"/>
-      <c r="BG3" s="257"/>
-      <c r="BH3" s="257"/>
-      <c r="BI3" s="257"/>
-      <c r="BJ3" s="257"/>
-      <c r="BK3" s="257"/>
-      <c r="BL3" s="257"/>
-      <c r="BM3" s="257"/>
-      <c r="BN3" s="257"/>
-      <c r="BO3" s="257"/>
-      <c r="BP3" s="257"/>
-      <c r="BQ3" s="257"/>
-      <c r="BR3" s="257"/>
-      <c r="BS3" s="257"/>
+      <c r="AL3" s="289"/>
+      <c r="AM3" s="289"/>
+      <c r="AN3" s="289"/>
+      <c r="AO3" s="289"/>
+      <c r="AP3" s="289"/>
+      <c r="AQ3" s="289"/>
+      <c r="AR3" s="289"/>
+      <c r="AS3" s="289"/>
+      <c r="AT3" s="289"/>
+      <c r="AU3" s="289"/>
+      <c r="AV3" s="289"/>
+      <c r="AW3" s="289"/>
+      <c r="AX3" s="289"/>
+      <c r="AY3" s="289"/>
+      <c r="AZ3" s="289"/>
+      <c r="BA3" s="289"/>
+      <c r="BB3" s="289"/>
+      <c r="BC3" s="289"/>
+      <c r="BD3" s="289"/>
+      <c r="BE3" s="289"/>
+      <c r="BF3" s="289"/>
+      <c r="BG3" s="289"/>
+      <c r="BH3" s="289"/>
+      <c r="BI3" s="289"/>
+      <c r="BJ3" s="289"/>
+      <c r="BK3" s="289"/>
+      <c r="BL3" s="289"/>
+      <c r="BM3" s="289"/>
+      <c r="BN3" s="289"/>
+      <c r="BO3" s="289"/>
+      <c r="BP3" s="289"/>
+      <c r="BQ3" s="289"/>
+      <c r="BR3" s="289"/>
+      <c r="BS3" s="289"/>
     </row>
     <row r="4" spans="1:71" ht="27.75" customHeight="1">
-      <c r="A4" s="258"/>
-      <c r="B4" s="258"/>
-      <c r="C4" s="259" t="s">
+      <c r="A4" s="290"/>
+      <c r="B4" s="290"/>
+      <c r="C4" s="291" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="259"/>
-      <c r="E4" s="259"/>
-      <c r="F4" s="259"/>
-      <c r="G4" s="259"/>
-      <c r="H4" s="259"/>
-      <c r="I4" s="259"/>
-      <c r="J4" s="259" t="s">
+      <c r="D4" s="291"/>
+      <c r="E4" s="291"/>
+      <c r="F4" s="291"/>
+      <c r="G4" s="291"/>
+      <c r="H4" s="291"/>
+      <c r="I4" s="291"/>
+      <c r="J4" s="291" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="259"/>
-      <c r="L4" s="259"/>
-      <c r="M4" s="259"/>
-      <c r="N4" s="259"/>
-      <c r="O4" s="259"/>
-      <c r="P4" s="259"/>
-      <c r="Q4" s="263"/>
-      <c r="R4" s="264"/>
-      <c r="S4" s="264"/>
-      <c r="T4" s="264"/>
-      <c r="U4" s="264"/>
-      <c r="V4" s="264"/>
-      <c r="W4" s="264"/>
-      <c r="X4" s="264"/>
-      <c r="Y4" s="264"/>
-      <c r="Z4" s="264"/>
-      <c r="AA4" s="265"/>
-      <c r="AB4" s="274"/>
-      <c r="AC4" s="275"/>
-      <c r="AD4" s="275"/>
-      <c r="AE4" s="275"/>
-      <c r="AF4" s="275"/>
-      <c r="AG4" s="275"/>
-      <c r="AH4" s="275"/>
-      <c r="AI4" s="275"/>
-      <c r="AJ4" s="275"/>
-      <c r="AK4" s="257"/>
-      <c r="AL4" s="257"/>
-      <c r="AM4" s="257"/>
-      <c r="AN4" s="257"/>
-      <c r="AO4" s="257"/>
-      <c r="AP4" s="257"/>
-      <c r="AQ4" s="257"/>
-      <c r="AR4" s="257"/>
-      <c r="AS4" s="257"/>
-      <c r="AT4" s="257"/>
-      <c r="AU4" s="257"/>
-      <c r="AV4" s="257"/>
-      <c r="AW4" s="257"/>
-      <c r="AX4" s="257"/>
-      <c r="AY4" s="257"/>
-      <c r="AZ4" s="257"/>
-      <c r="BA4" s="257"/>
-      <c r="BB4" s="257"/>
-      <c r="BC4" s="257"/>
-      <c r="BD4" s="257"/>
-      <c r="BE4" s="257"/>
-      <c r="BF4" s="257"/>
-      <c r="BG4" s="257"/>
-      <c r="BH4" s="257"/>
-      <c r="BI4" s="257"/>
-      <c r="BJ4" s="257"/>
-      <c r="BK4" s="257"/>
-      <c r="BL4" s="257"/>
-      <c r="BM4" s="257"/>
-      <c r="BN4" s="257"/>
-      <c r="BO4" s="257"/>
-      <c r="BP4" s="257"/>
-      <c r="BQ4" s="257"/>
-      <c r="BR4" s="257"/>
-      <c r="BS4" s="257"/>
+      <c r="K4" s="291"/>
+      <c r="L4" s="291"/>
+      <c r="M4" s="291"/>
+      <c r="N4" s="291"/>
+      <c r="O4" s="291"/>
+      <c r="P4" s="291"/>
+      <c r="Q4" s="295"/>
+      <c r="R4" s="296"/>
+      <c r="S4" s="296"/>
+      <c r="T4" s="296"/>
+      <c r="U4" s="296"/>
+      <c r="V4" s="296"/>
+      <c r="W4" s="296"/>
+      <c r="X4" s="296"/>
+      <c r="Y4" s="296"/>
+      <c r="Z4" s="296"/>
+      <c r="AA4" s="297"/>
+      <c r="AB4" s="300"/>
+      <c r="AC4" s="301"/>
+      <c r="AD4" s="301"/>
+      <c r="AE4" s="301"/>
+      <c r="AF4" s="301"/>
+      <c r="AG4" s="301"/>
+      <c r="AH4" s="301"/>
+      <c r="AI4" s="301"/>
+      <c r="AJ4" s="301"/>
+      <c r="AK4" s="289"/>
+      <c r="AL4" s="289"/>
+      <c r="AM4" s="289"/>
+      <c r="AN4" s="289"/>
+      <c r="AO4" s="289"/>
+      <c r="AP4" s="289"/>
+      <c r="AQ4" s="289"/>
+      <c r="AR4" s="289"/>
+      <c r="AS4" s="289"/>
+      <c r="AT4" s="289"/>
+      <c r="AU4" s="289"/>
+      <c r="AV4" s="289"/>
+      <c r="AW4" s="289"/>
+      <c r="AX4" s="289"/>
+      <c r="AY4" s="289"/>
+      <c r="AZ4" s="289"/>
+      <c r="BA4" s="289"/>
+      <c r="BB4" s="289"/>
+      <c r="BC4" s="289"/>
+      <c r="BD4" s="289"/>
+      <c r="BE4" s="289"/>
+      <c r="BF4" s="289"/>
+      <c r="BG4" s="289"/>
+      <c r="BH4" s="289"/>
+      <c r="BI4" s="289"/>
+      <c r="BJ4" s="289"/>
+      <c r="BK4" s="289"/>
+      <c r="BL4" s="289"/>
+      <c r="BM4" s="289"/>
+      <c r="BN4" s="289"/>
+      <c r="BO4" s="289"/>
+      <c r="BP4" s="289"/>
+      <c r="BQ4" s="289"/>
+      <c r="BR4" s="289"/>
+      <c r="BS4" s="289"/>
     </row>
     <row r="5" spans="1:71">
-      <c r="A5" s="244" t="s">
+      <c r="A5" s="259" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="245"/>
-      <c r="C5" s="266" t="s">
+      <c r="B5" s="260"/>
+      <c r="C5" s="277" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="267"/>
-      <c r="E5" s="267"/>
-      <c r="F5" s="267"/>
-      <c r="G5" s="267"/>
-      <c r="H5" s="267"/>
-      <c r="I5" s="268"/>
-      <c r="J5" s="269"/>
-      <c r="K5" s="270"/>
-      <c r="L5" s="270"/>
-      <c r="M5" s="270"/>
-      <c r="N5" s="270"/>
-      <c r="O5" s="270"/>
-      <c r="P5" s="271"/>
-      <c r="Q5" s="249"/>
-      <c r="R5" s="250"/>
-      <c r="S5" s="250"/>
-      <c r="T5" s="250"/>
-      <c r="U5" s="250"/>
-      <c r="V5" s="250"/>
-      <c r="W5" s="250"/>
-      <c r="X5" s="250"/>
-      <c r="Y5" s="250"/>
-      <c r="Z5" s="250"/>
-      <c r="AA5" s="251"/>
-      <c r="AB5" s="252"/>
-      <c r="AC5" s="253"/>
-      <c r="AD5" s="253"/>
-      <c r="AE5" s="253"/>
-      <c r="AF5" s="253"/>
-      <c r="AG5" s="253"/>
-      <c r="AH5" s="253"/>
-      <c r="AI5" s="253"/>
-      <c r="AJ5" s="253"/>
-      <c r="AK5" s="241"/>
-      <c r="AL5" s="242"/>
-      <c r="AM5" s="242"/>
-      <c r="AN5" s="242"/>
-      <c r="AO5" s="242"/>
-      <c r="AP5" s="242"/>
-      <c r="AQ5" s="242"/>
-      <c r="AR5" s="242"/>
-      <c r="AS5" s="242"/>
-      <c r="AT5" s="242"/>
-      <c r="AU5" s="242"/>
-      <c r="AV5" s="242"/>
-      <c r="AW5" s="242"/>
-      <c r="AX5" s="242"/>
-      <c r="AY5" s="242"/>
-      <c r="AZ5" s="242"/>
-      <c r="BA5" s="242"/>
-      <c r="BB5" s="242"/>
-      <c r="BC5" s="242"/>
-      <c r="BD5" s="242"/>
-      <c r="BE5" s="242"/>
-      <c r="BF5" s="242"/>
-      <c r="BG5" s="242"/>
-      <c r="BH5" s="242"/>
-      <c r="BI5" s="242"/>
-      <c r="BJ5" s="242"/>
-      <c r="BK5" s="242"/>
-      <c r="BL5" s="242"/>
-      <c r="BM5" s="242"/>
-      <c r="BN5" s="242"/>
-      <c r="BO5" s="242"/>
-      <c r="BP5" s="242"/>
-      <c r="BQ5" s="242"/>
-      <c r="BR5" s="242"/>
-      <c r="BS5" s="243"/>
+      <c r="D5" s="278"/>
+      <c r="E5" s="278"/>
+      <c r="F5" s="278"/>
+      <c r="G5" s="278"/>
+      <c r="H5" s="278"/>
+      <c r="I5" s="279"/>
+      <c r="J5" s="271"/>
+      <c r="K5" s="272"/>
+      <c r="L5" s="272"/>
+      <c r="M5" s="272"/>
+      <c r="N5" s="272"/>
+      <c r="O5" s="272"/>
+      <c r="P5" s="273"/>
+      <c r="Q5" s="256"/>
+      <c r="R5" s="257"/>
+      <c r="S5" s="257"/>
+      <c r="T5" s="257"/>
+      <c r="U5" s="257"/>
+      <c r="V5" s="257"/>
+      <c r="W5" s="257"/>
+      <c r="X5" s="257"/>
+      <c r="Y5" s="257"/>
+      <c r="Z5" s="257"/>
+      <c r="AA5" s="258"/>
+      <c r="AB5" s="249"/>
+      <c r="AC5" s="250"/>
+      <c r="AD5" s="250"/>
+      <c r="AE5" s="250"/>
+      <c r="AF5" s="250"/>
+      <c r="AG5" s="250"/>
+      <c r="AH5" s="250"/>
+      <c r="AI5" s="250"/>
+      <c r="AJ5" s="250"/>
+      <c r="AK5" s="251"/>
+      <c r="AL5" s="247"/>
+      <c r="AM5" s="247"/>
+      <c r="AN5" s="247"/>
+      <c r="AO5" s="247"/>
+      <c r="AP5" s="247"/>
+      <c r="AQ5" s="247"/>
+      <c r="AR5" s="247"/>
+      <c r="AS5" s="247"/>
+      <c r="AT5" s="247"/>
+      <c r="AU5" s="247"/>
+      <c r="AV5" s="247"/>
+      <c r="AW5" s="247"/>
+      <c r="AX5" s="247"/>
+      <c r="AY5" s="247"/>
+      <c r="AZ5" s="247"/>
+      <c r="BA5" s="247"/>
+      <c r="BB5" s="247"/>
+      <c r="BC5" s="247"/>
+      <c r="BD5" s="247"/>
+      <c r="BE5" s="247"/>
+      <c r="BF5" s="247"/>
+      <c r="BG5" s="247"/>
+      <c r="BH5" s="247"/>
+      <c r="BI5" s="247"/>
+      <c r="BJ5" s="247"/>
+      <c r="BK5" s="247"/>
+      <c r="BL5" s="247"/>
+      <c r="BM5" s="247"/>
+      <c r="BN5" s="247"/>
+      <c r="BO5" s="247"/>
+      <c r="BP5" s="247"/>
+      <c r="BQ5" s="247"/>
+      <c r="BR5" s="247"/>
+      <c r="BS5" s="252"/>
     </row>
     <row r="6" spans="1:71">
-      <c r="A6" s="244" t="s">
+      <c r="A6" s="259" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="245"/>
-      <c r="C6" s="266"/>
-      <c r="D6" s="267"/>
-      <c r="E6" s="267"/>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="267"/>
-      <c r="I6" s="268"/>
-      <c r="J6" s="269" t="s">
+      <c r="B6" s="260"/>
+      <c r="C6" s="277"/>
+      <c r="D6" s="278"/>
+      <c r="E6" s="278"/>
+      <c r="F6" s="278"/>
+      <c r="G6" s="278"/>
+      <c r="H6" s="278"/>
+      <c r="I6" s="279"/>
+      <c r="J6" s="271" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="270"/>
-      <c r="L6" s="270"/>
-      <c r="M6" s="270"/>
-      <c r="N6" s="270"/>
-      <c r="O6" s="270"/>
-      <c r="P6" s="271"/>
-      <c r="Q6" s="249"/>
-      <c r="R6" s="250"/>
-      <c r="S6" s="250"/>
-      <c r="T6" s="250"/>
-      <c r="U6" s="250"/>
-      <c r="V6" s="250"/>
-      <c r="W6" s="250"/>
-      <c r="X6" s="250"/>
-      <c r="Y6" s="250"/>
-      <c r="Z6" s="250"/>
-      <c r="AA6" s="251"/>
-      <c r="AB6" s="252"/>
-      <c r="AC6" s="253"/>
-      <c r="AD6" s="253"/>
-      <c r="AE6" s="253"/>
-      <c r="AF6" s="253"/>
-      <c r="AG6" s="253"/>
-      <c r="AH6" s="253"/>
-      <c r="AI6" s="253"/>
-      <c r="AJ6" s="253"/>
-      <c r="AK6" s="241"/>
-      <c r="AL6" s="242"/>
-      <c r="AM6" s="242"/>
-      <c r="AN6" s="242"/>
-      <c r="AO6" s="242"/>
-      <c r="AP6" s="242"/>
-      <c r="AQ6" s="242"/>
-      <c r="AR6" s="242"/>
-      <c r="AS6" s="242"/>
-      <c r="AT6" s="242"/>
-      <c r="AU6" s="242"/>
-      <c r="AV6" s="242"/>
-      <c r="AW6" s="242"/>
-      <c r="AX6" s="242"/>
-      <c r="AY6" s="242"/>
-      <c r="AZ6" s="242"/>
-      <c r="BA6" s="242"/>
-      <c r="BB6" s="242"/>
-      <c r="BC6" s="242"/>
-      <c r="BD6" s="242"/>
-      <c r="BE6" s="242"/>
-      <c r="BF6" s="242"/>
-      <c r="BG6" s="242"/>
-      <c r="BH6" s="242"/>
-      <c r="BI6" s="242"/>
-      <c r="BJ6" s="242"/>
-      <c r="BK6" s="242"/>
-      <c r="BL6" s="242"/>
-      <c r="BM6" s="242"/>
-      <c r="BN6" s="242"/>
-      <c r="BO6" s="242"/>
-      <c r="BP6" s="242"/>
-      <c r="BQ6" s="242"/>
-      <c r="BR6" s="242"/>
-      <c r="BS6" s="243"/>
+      <c r="K6" s="272"/>
+      <c r="L6" s="272"/>
+      <c r="M6" s="272"/>
+      <c r="N6" s="272"/>
+      <c r="O6" s="272"/>
+      <c r="P6" s="273"/>
+      <c r="Q6" s="256"/>
+      <c r="R6" s="257"/>
+      <c r="S6" s="257"/>
+      <c r="T6" s="257"/>
+      <c r="U6" s="257"/>
+      <c r="V6" s="257"/>
+      <c r="W6" s="257"/>
+      <c r="X6" s="257"/>
+      <c r="Y6" s="257"/>
+      <c r="Z6" s="257"/>
+      <c r="AA6" s="258"/>
+      <c r="AB6" s="249"/>
+      <c r="AC6" s="250"/>
+      <c r="AD6" s="250"/>
+      <c r="AE6" s="250"/>
+      <c r="AF6" s="250"/>
+      <c r="AG6" s="250"/>
+      <c r="AH6" s="250"/>
+      <c r="AI6" s="250"/>
+      <c r="AJ6" s="250"/>
+      <c r="AK6" s="251"/>
+      <c r="AL6" s="247"/>
+      <c r="AM6" s="247"/>
+      <c r="AN6" s="247"/>
+      <c r="AO6" s="247"/>
+      <c r="AP6" s="247"/>
+      <c r="AQ6" s="247"/>
+      <c r="AR6" s="247"/>
+      <c r="AS6" s="247"/>
+      <c r="AT6" s="247"/>
+      <c r="AU6" s="247"/>
+      <c r="AV6" s="247"/>
+      <c r="AW6" s="247"/>
+      <c r="AX6" s="247"/>
+      <c r="AY6" s="247"/>
+      <c r="AZ6" s="247"/>
+      <c r="BA6" s="247"/>
+      <c r="BB6" s="247"/>
+      <c r="BC6" s="247"/>
+      <c r="BD6" s="247"/>
+      <c r="BE6" s="247"/>
+      <c r="BF6" s="247"/>
+      <c r="BG6" s="247"/>
+      <c r="BH6" s="247"/>
+      <c r="BI6" s="247"/>
+      <c r="BJ6" s="247"/>
+      <c r="BK6" s="247"/>
+      <c r="BL6" s="247"/>
+      <c r="BM6" s="247"/>
+      <c r="BN6" s="247"/>
+      <c r="BO6" s="247"/>
+      <c r="BP6" s="247"/>
+      <c r="BQ6" s="247"/>
+      <c r="BR6" s="247"/>
+      <c r="BS6" s="252"/>
     </row>
     <row r="7" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A7" s="244" t="s">
+      <c r="A7" s="259" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="245"/>
-      <c r="C7" s="279" t="s">
+      <c r="B7" s="260"/>
+      <c r="C7" s="282" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="280"/>
-      <c r="E7" s="280"/>
-      <c r="F7" s="280"/>
-      <c r="G7" s="280"/>
-      <c r="H7" s="280"/>
-      <c r="I7" s="281"/>
-      <c r="J7" s="282"/>
-      <c r="K7" s="282"/>
-      <c r="L7" s="282"/>
-      <c r="M7" s="282"/>
-      <c r="N7" s="282"/>
-      <c r="O7" s="282"/>
-      <c r="P7" s="282"/>
-      <c r="Q7" s="249"/>
-      <c r="R7" s="250"/>
-      <c r="S7" s="250"/>
-      <c r="T7" s="250"/>
-      <c r="U7" s="250"/>
-      <c r="V7" s="250"/>
-      <c r="W7" s="250"/>
-      <c r="X7" s="250"/>
-      <c r="Y7" s="250"/>
-      <c r="Z7" s="250"/>
-      <c r="AA7" s="251"/>
-      <c r="AB7" s="252"/>
-      <c r="AC7" s="253"/>
-      <c r="AD7" s="253"/>
-      <c r="AE7" s="253"/>
-      <c r="AF7" s="253"/>
-      <c r="AG7" s="253"/>
-      <c r="AH7" s="253"/>
-      <c r="AI7" s="253"/>
-      <c r="AJ7" s="253"/>
-      <c r="AK7" s="276"/>
-      <c r="AL7" s="277"/>
-      <c r="AM7" s="277"/>
-      <c r="AN7" s="277"/>
-      <c r="AO7" s="277"/>
-      <c r="AP7" s="277"/>
-      <c r="AQ7" s="277"/>
-      <c r="AR7" s="277"/>
-      <c r="AS7" s="277"/>
-      <c r="AT7" s="277"/>
-      <c r="AU7" s="277"/>
-      <c r="AV7" s="277"/>
-      <c r="AW7" s="277"/>
-      <c r="AX7" s="277"/>
-      <c r="AY7" s="277"/>
-      <c r="AZ7" s="277"/>
-      <c r="BA7" s="277"/>
-      <c r="BB7" s="277"/>
-      <c r="BC7" s="277"/>
-      <c r="BD7" s="277"/>
-      <c r="BE7" s="277"/>
-      <c r="BF7" s="277"/>
-      <c r="BG7" s="277"/>
-      <c r="BH7" s="277"/>
-      <c r="BI7" s="277"/>
-      <c r="BJ7" s="277"/>
-      <c r="BK7" s="277"/>
-      <c r="BL7" s="277"/>
-      <c r="BM7" s="277"/>
-      <c r="BN7" s="277"/>
-      <c r="BO7" s="277"/>
-      <c r="BP7" s="277"/>
-      <c r="BQ7" s="277"/>
-      <c r="BR7" s="277"/>
-      <c r="BS7" s="278"/>
+      <c r="D7" s="283"/>
+      <c r="E7" s="283"/>
+      <c r="F7" s="283"/>
+      <c r="G7" s="283"/>
+      <c r="H7" s="283"/>
+      <c r="I7" s="284"/>
+      <c r="J7" s="285"/>
+      <c r="K7" s="285"/>
+      <c r="L7" s="285"/>
+      <c r="M7" s="285"/>
+      <c r="N7" s="285"/>
+      <c r="O7" s="285"/>
+      <c r="P7" s="285"/>
+      <c r="Q7" s="256"/>
+      <c r="R7" s="257"/>
+      <c r="S7" s="257"/>
+      <c r="T7" s="257"/>
+      <c r="U7" s="257"/>
+      <c r="V7" s="257"/>
+      <c r="W7" s="257"/>
+      <c r="X7" s="257"/>
+      <c r="Y7" s="257"/>
+      <c r="Z7" s="257"/>
+      <c r="AA7" s="258"/>
+      <c r="AB7" s="249"/>
+      <c r="AC7" s="250"/>
+      <c r="AD7" s="250"/>
+      <c r="AE7" s="250"/>
+      <c r="AF7" s="250"/>
+      <c r="AG7" s="250"/>
+      <c r="AH7" s="250"/>
+      <c r="AI7" s="250"/>
+      <c r="AJ7" s="250"/>
+      <c r="AK7" s="239"/>
+      <c r="AL7" s="280"/>
+      <c r="AM7" s="280"/>
+      <c r="AN7" s="280"/>
+      <c r="AO7" s="280"/>
+      <c r="AP7" s="280"/>
+      <c r="AQ7" s="280"/>
+      <c r="AR7" s="280"/>
+      <c r="AS7" s="280"/>
+      <c r="AT7" s="280"/>
+      <c r="AU7" s="280"/>
+      <c r="AV7" s="280"/>
+      <c r="AW7" s="280"/>
+      <c r="AX7" s="280"/>
+      <c r="AY7" s="280"/>
+      <c r="AZ7" s="280"/>
+      <c r="BA7" s="280"/>
+      <c r="BB7" s="280"/>
+      <c r="BC7" s="280"/>
+      <c r="BD7" s="280"/>
+      <c r="BE7" s="280"/>
+      <c r="BF7" s="280"/>
+      <c r="BG7" s="280"/>
+      <c r="BH7" s="280"/>
+      <c r="BI7" s="280"/>
+      <c r="BJ7" s="280"/>
+      <c r="BK7" s="280"/>
+      <c r="BL7" s="280"/>
+      <c r="BM7" s="280"/>
+      <c r="BN7" s="280"/>
+      <c r="BO7" s="280"/>
+      <c r="BP7" s="280"/>
+      <c r="BQ7" s="280"/>
+      <c r="BR7" s="280"/>
+      <c r="BS7" s="281"/>
     </row>
     <row r="8" spans="1:71" ht="25.5" customHeight="1">
-      <c r="A8" s="244">
+      <c r="A8" s="259">
         <v>2.1</v>
       </c>
-      <c r="B8" s="245"/>
-      <c r="C8" s="266"/>
-      <c r="D8" s="267"/>
-      <c r="E8" s="267"/>
-      <c r="F8" s="267"/>
-      <c r="G8" s="267"/>
-      <c r="H8" s="267"/>
-      <c r="I8" s="268"/>
-      <c r="J8" s="286" t="s">
+      <c r="B8" s="260"/>
+      <c r="C8" s="277"/>
+      <c r="D8" s="278"/>
+      <c r="E8" s="278"/>
+      <c r="F8" s="278"/>
+      <c r="G8" s="278"/>
+      <c r="H8" s="278"/>
+      <c r="I8" s="279"/>
+      <c r="J8" s="274" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="287"/>
-      <c r="L8" s="287"/>
-      <c r="M8" s="287"/>
-      <c r="N8" s="287"/>
-      <c r="O8" s="287"/>
-      <c r="P8" s="288"/>
-      <c r="Q8" s="289" t="s">
+      <c r="K8" s="275"/>
+      <c r="L8" s="275"/>
+      <c r="M8" s="275"/>
+      <c r="N8" s="275"/>
+      <c r="O8" s="275"/>
+      <c r="P8" s="276"/>
+      <c r="Q8" s="253" t="s">
         <v>139</v>
       </c>
-      <c r="R8" s="290"/>
-      <c r="S8" s="290"/>
-      <c r="T8" s="290"/>
-      <c r="U8" s="290"/>
-      <c r="V8" s="290"/>
-      <c r="W8" s="290"/>
-      <c r="X8" s="290"/>
-      <c r="Y8" s="290"/>
-      <c r="Z8" s="290"/>
-      <c r="AA8" s="291"/>
-      <c r="AB8" s="292"/>
-      <c r="AC8" s="293"/>
-      <c r="AD8" s="293"/>
-      <c r="AE8" s="293"/>
-      <c r="AF8" s="293"/>
-      <c r="AG8" s="293"/>
-      <c r="AH8" s="293"/>
-      <c r="AI8" s="293"/>
-      <c r="AJ8" s="293"/>
-      <c r="AK8" s="283" t="s">
+      <c r="R8" s="254"/>
+      <c r="S8" s="254"/>
+      <c r="T8" s="254"/>
+      <c r="U8" s="254"/>
+      <c r="V8" s="254"/>
+      <c r="W8" s="254"/>
+      <c r="X8" s="254"/>
+      <c r="Y8" s="254"/>
+      <c r="Z8" s="254"/>
+      <c r="AA8" s="255"/>
+      <c r="AB8" s="264"/>
+      <c r="AC8" s="265"/>
+      <c r="AD8" s="265"/>
+      <c r="AE8" s="265"/>
+      <c r="AF8" s="265"/>
+      <c r="AG8" s="265"/>
+      <c r="AH8" s="265"/>
+      <c r="AI8" s="265"/>
+      <c r="AJ8" s="265"/>
+      <c r="AK8" s="269" t="s">
         <v>130</v>
       </c>
-      <c r="AL8" s="284"/>
-      <c r="AM8" s="284"/>
-      <c r="AN8" s="284"/>
-      <c r="AO8" s="284"/>
-      <c r="AP8" s="284"/>
-      <c r="AQ8" s="284"/>
-      <c r="AR8" s="284"/>
-      <c r="AS8" s="284"/>
-      <c r="AT8" s="284"/>
-      <c r="AU8" s="284"/>
-      <c r="AV8" s="284"/>
-      <c r="AW8" s="284"/>
-      <c r="AX8" s="284"/>
-      <c r="AY8" s="284"/>
-      <c r="AZ8" s="284"/>
-      <c r="BA8" s="284"/>
-      <c r="BB8" s="284"/>
-      <c r="BC8" s="284"/>
-      <c r="BD8" s="284"/>
-      <c r="BE8" s="284"/>
-      <c r="BF8" s="284"/>
-      <c r="BG8" s="284"/>
-      <c r="BH8" s="284"/>
-      <c r="BI8" s="284"/>
-      <c r="BJ8" s="284"/>
-      <c r="BK8" s="284"/>
-      <c r="BL8" s="284"/>
-      <c r="BM8" s="284"/>
-      <c r="BN8" s="284"/>
-      <c r="BO8" s="284"/>
-      <c r="BP8" s="284"/>
-      <c r="BQ8" s="284"/>
-      <c r="BR8" s="284"/>
-      <c r="BS8" s="285"/>
+      <c r="AL8" s="262"/>
+      <c r="AM8" s="262"/>
+      <c r="AN8" s="262"/>
+      <c r="AO8" s="262"/>
+      <c r="AP8" s="262"/>
+      <c r="AQ8" s="262"/>
+      <c r="AR8" s="262"/>
+      <c r="AS8" s="262"/>
+      <c r="AT8" s="262"/>
+      <c r="AU8" s="262"/>
+      <c r="AV8" s="262"/>
+      <c r="AW8" s="262"/>
+      <c r="AX8" s="262"/>
+      <c r="AY8" s="262"/>
+      <c r="AZ8" s="262"/>
+      <c r="BA8" s="262"/>
+      <c r="BB8" s="262"/>
+      <c r="BC8" s="262"/>
+      <c r="BD8" s="262"/>
+      <c r="BE8" s="262"/>
+      <c r="BF8" s="262"/>
+      <c r="BG8" s="262"/>
+      <c r="BH8" s="262"/>
+      <c r="BI8" s="262"/>
+      <c r="BJ8" s="262"/>
+      <c r="BK8" s="262"/>
+      <c r="BL8" s="262"/>
+      <c r="BM8" s="262"/>
+      <c r="BN8" s="262"/>
+      <c r="BO8" s="262"/>
+      <c r="BP8" s="262"/>
+      <c r="BQ8" s="262"/>
+      <c r="BR8" s="262"/>
+      <c r="BS8" s="270"/>
     </row>
     <row r="9" spans="1:71" ht="54.75" customHeight="1">
-      <c r="A9" s="244" t="s">
+      <c r="A9" s="259" t="s">
         <v>70</v>
       </c>
-      <c r="B9" s="245"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="247"/>
-      <c r="E9" s="247"/>
-      <c r="F9" s="247"/>
-      <c r="G9" s="247"/>
-      <c r="H9" s="247"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="286" t="s">
+      <c r="B9" s="260"/>
+      <c r="C9" s="241"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
+      <c r="G9" s="242"/>
+      <c r="H9" s="242"/>
+      <c r="I9" s="243"/>
+      <c r="J9" s="274" t="s">
         <v>47</v>
       </c>
-      <c r="K9" s="287"/>
-      <c r="L9" s="287"/>
-      <c r="M9" s="287"/>
-      <c r="N9" s="287"/>
-      <c r="O9" s="287"/>
-      <c r="P9" s="288"/>
-      <c r="Q9" s="249" t="s">
+      <c r="K9" s="275"/>
+      <c r="L9" s="275"/>
+      <c r="M9" s="275"/>
+      <c r="N9" s="275"/>
+      <c r="O9" s="275"/>
+      <c r="P9" s="276"/>
+      <c r="Q9" s="256" t="s">
         <v>139</v>
       </c>
-      <c r="R9" s="250"/>
-      <c r="S9" s="250"/>
-      <c r="T9" s="250"/>
-      <c r="U9" s="250"/>
-      <c r="V9" s="250"/>
-      <c r="W9" s="250"/>
-      <c r="X9" s="250"/>
-      <c r="Y9" s="250"/>
-      <c r="Z9" s="250"/>
-      <c r="AA9" s="251"/>
-      <c r="AB9" s="292"/>
-      <c r="AC9" s="293"/>
-      <c r="AD9" s="293"/>
-      <c r="AE9" s="293"/>
-      <c r="AF9" s="293"/>
-      <c r="AG9" s="293"/>
-      <c r="AH9" s="293"/>
-      <c r="AI9" s="293"/>
-      <c r="AJ9" s="293"/>
-      <c r="AK9" s="241" t="s">
+      <c r="R9" s="257"/>
+      <c r="S9" s="257"/>
+      <c r="T9" s="257"/>
+      <c r="U9" s="257"/>
+      <c r="V9" s="257"/>
+      <c r="W9" s="257"/>
+      <c r="X9" s="257"/>
+      <c r="Y9" s="257"/>
+      <c r="Z9" s="257"/>
+      <c r="AA9" s="258"/>
+      <c r="AB9" s="264"/>
+      <c r="AC9" s="265"/>
+      <c r="AD9" s="265"/>
+      <c r="AE9" s="265"/>
+      <c r="AF9" s="265"/>
+      <c r="AG9" s="265"/>
+      <c r="AH9" s="265"/>
+      <c r="AI9" s="265"/>
+      <c r="AJ9" s="265"/>
+      <c r="AK9" s="251" t="s">
         <v>123</v>
       </c>
-      <c r="AL9" s="242"/>
-      <c r="AM9" s="242"/>
-      <c r="AN9" s="242"/>
-      <c r="AO9" s="242"/>
-      <c r="AP9" s="242"/>
-      <c r="AQ9" s="242"/>
-      <c r="AR9" s="242"/>
-      <c r="AS9" s="242"/>
-      <c r="AT9" s="242"/>
-      <c r="AU9" s="242"/>
-      <c r="AV9" s="242"/>
-      <c r="AW9" s="242"/>
-      <c r="AX9" s="242"/>
-      <c r="AY9" s="242"/>
-      <c r="AZ9" s="242"/>
-      <c r="BA9" s="242"/>
-      <c r="BB9" s="242"/>
-      <c r="BC9" s="242"/>
-      <c r="BD9" s="242"/>
-      <c r="BE9" s="242"/>
-      <c r="BF9" s="242"/>
-      <c r="BG9" s="242"/>
-      <c r="BH9" s="242"/>
-      <c r="BI9" s="242"/>
-      <c r="BJ9" s="242"/>
-      <c r="BK9" s="242"/>
-      <c r="BL9" s="242"/>
-      <c r="BM9" s="242"/>
-      <c r="BN9" s="242"/>
-      <c r="BO9" s="242"/>
-      <c r="BP9" s="242"/>
-      <c r="BQ9" s="242"/>
-      <c r="BR9" s="242"/>
-      <c r="BS9" s="243"/>
+      <c r="AL9" s="247"/>
+      <c r="AM9" s="247"/>
+      <c r="AN9" s="247"/>
+      <c r="AO9" s="247"/>
+      <c r="AP9" s="247"/>
+      <c r="AQ9" s="247"/>
+      <c r="AR9" s="247"/>
+      <c r="AS9" s="247"/>
+      <c r="AT9" s="247"/>
+      <c r="AU9" s="247"/>
+      <c r="AV9" s="247"/>
+      <c r="AW9" s="247"/>
+      <c r="AX9" s="247"/>
+      <c r="AY9" s="247"/>
+      <c r="AZ9" s="247"/>
+      <c r="BA9" s="247"/>
+      <c r="BB9" s="247"/>
+      <c r="BC9" s="247"/>
+      <c r="BD9" s="247"/>
+      <c r="BE9" s="247"/>
+      <c r="BF9" s="247"/>
+      <c r="BG9" s="247"/>
+      <c r="BH9" s="247"/>
+      <c r="BI9" s="247"/>
+      <c r="BJ9" s="247"/>
+      <c r="BK9" s="247"/>
+      <c r="BL9" s="247"/>
+      <c r="BM9" s="247"/>
+      <c r="BN9" s="247"/>
+      <c r="BO9" s="247"/>
+      <c r="BP9" s="247"/>
+      <c r="BQ9" s="247"/>
+      <c r="BR9" s="247"/>
+      <c r="BS9" s="252"/>
     </row>
     <row r="10" spans="1:71" ht="141" customHeight="1">
-      <c r="A10" s="244" t="s">
+      <c r="A10" s="259" t="s">
         <v>77</v>
       </c>
-      <c r="B10" s="245"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="248"/>
-      <c r="J10" s="269" t="s">
+      <c r="B10" s="260"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="242"/>
+      <c r="E10" s="242"/>
+      <c r="F10" s="242"/>
+      <c r="G10" s="242"/>
+      <c r="H10" s="242"/>
+      <c r="I10" s="243"/>
+      <c r="J10" s="271" t="s">
         <v>71</v>
       </c>
-      <c r="K10" s="270"/>
-      <c r="L10" s="270"/>
-      <c r="M10" s="270"/>
-      <c r="N10" s="270"/>
-      <c r="O10" s="270"/>
-      <c r="P10" s="271"/>
-      <c r="Q10" s="296" t="s">
+      <c r="K10" s="272"/>
+      <c r="L10" s="272"/>
+      <c r="M10" s="272"/>
+      <c r="N10" s="272"/>
+      <c r="O10" s="272"/>
+      <c r="P10" s="273"/>
+      <c r="Q10" s="266" t="s">
         <v>139</v>
       </c>
-      <c r="R10" s="297"/>
-      <c r="S10" s="297"/>
-      <c r="T10" s="297"/>
-      <c r="U10" s="297"/>
-      <c r="V10" s="297"/>
-      <c r="W10" s="297"/>
-      <c r="X10" s="297"/>
-      <c r="Y10" s="297"/>
-      <c r="Z10" s="297"/>
-      <c r="AA10" s="298"/>
-      <c r="AB10" s="252"/>
-      <c r="AC10" s="253"/>
-      <c r="AD10" s="253"/>
-      <c r="AE10" s="253"/>
-      <c r="AF10" s="253"/>
-      <c r="AG10" s="253"/>
-      <c r="AH10" s="253"/>
-      <c r="AI10" s="253"/>
-      <c r="AJ10" s="253"/>
-      <c r="AK10" s="241" t="s">
+      <c r="R10" s="267"/>
+      <c r="S10" s="267"/>
+      <c r="T10" s="267"/>
+      <c r="U10" s="267"/>
+      <c r="V10" s="267"/>
+      <c r="W10" s="267"/>
+      <c r="X10" s="267"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="267"/>
+      <c r="AA10" s="268"/>
+      <c r="AB10" s="249"/>
+      <c r="AC10" s="250"/>
+      <c r="AD10" s="250"/>
+      <c r="AE10" s="250"/>
+      <c r="AF10" s="250"/>
+      <c r="AG10" s="250"/>
+      <c r="AH10" s="250"/>
+      <c r="AI10" s="250"/>
+      <c r="AJ10" s="250"/>
+      <c r="AK10" s="251" t="s">
         <v>125</v>
       </c>
-      <c r="AL10" s="242"/>
-      <c r="AM10" s="242"/>
-      <c r="AN10" s="242"/>
-      <c r="AO10" s="242"/>
-      <c r="AP10" s="242"/>
-      <c r="AQ10" s="242"/>
-      <c r="AR10" s="242"/>
-      <c r="AS10" s="242"/>
-      <c r="AT10" s="242"/>
-      <c r="AU10" s="242"/>
-      <c r="AV10" s="242"/>
-      <c r="AW10" s="242"/>
-      <c r="AX10" s="242"/>
-      <c r="AY10" s="242"/>
-      <c r="AZ10" s="242"/>
-      <c r="BA10" s="242"/>
-      <c r="BB10" s="242"/>
-      <c r="BC10" s="242"/>
-      <c r="BD10" s="242"/>
-      <c r="BE10" s="242"/>
-      <c r="BF10" s="242"/>
-      <c r="BG10" s="242"/>
-      <c r="BH10" s="242"/>
-      <c r="BI10" s="242"/>
-      <c r="BJ10" s="242"/>
-      <c r="BK10" s="242"/>
-      <c r="BL10" s="242"/>
-      <c r="BM10" s="242"/>
-      <c r="BN10" s="242"/>
-      <c r="BO10" s="242"/>
-      <c r="BP10" s="242"/>
-      <c r="BQ10" s="242"/>
-      <c r="BR10" s="242"/>
-      <c r="BS10" s="243"/>
+      <c r="AL10" s="247"/>
+      <c r="AM10" s="247"/>
+      <c r="AN10" s="247"/>
+      <c r="AO10" s="247"/>
+      <c r="AP10" s="247"/>
+      <c r="AQ10" s="247"/>
+      <c r="AR10" s="247"/>
+      <c r="AS10" s="247"/>
+      <c r="AT10" s="247"/>
+      <c r="AU10" s="247"/>
+      <c r="AV10" s="247"/>
+      <c r="AW10" s="247"/>
+      <c r="AX10" s="247"/>
+      <c r="AY10" s="247"/>
+      <c r="AZ10" s="247"/>
+      <c r="BA10" s="247"/>
+      <c r="BB10" s="247"/>
+      <c r="BC10" s="247"/>
+      <c r="BD10" s="247"/>
+      <c r="BE10" s="247"/>
+      <c r="BF10" s="247"/>
+      <c r="BG10" s="247"/>
+      <c r="BH10" s="247"/>
+      <c r="BI10" s="247"/>
+      <c r="BJ10" s="247"/>
+      <c r="BK10" s="247"/>
+      <c r="BL10" s="247"/>
+      <c r="BM10" s="247"/>
+      <c r="BN10" s="247"/>
+      <c r="BO10" s="247"/>
+      <c r="BP10" s="247"/>
+      <c r="BQ10" s="247"/>
+      <c r="BR10" s="247"/>
+      <c r="BS10" s="252"/>
     </row>
     <row r="11" spans="1:71" ht="33.75" customHeight="1">
-      <c r="A11" s="244" t="s">
+      <c r="A11" s="259" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="245"/>
+      <c r="B11" s="260"/>
       <c r="C11" s="131"/>
       <c r="D11" s="132"/>
       <c r="E11" s="132"/>
@@ -27808,485 +27691,485 @@
       <c r="G11" s="132"/>
       <c r="H11" s="132"/>
       <c r="I11" s="133"/>
-      <c r="J11" s="294" t="s">
+      <c r="J11" s="261" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="284"/>
-      <c r="L11" s="284"/>
-      <c r="M11" s="284"/>
-      <c r="N11" s="284"/>
-      <c r="O11" s="284"/>
-      <c r="P11" s="295"/>
-      <c r="Q11" s="249" t="s">
+      <c r="K11" s="262"/>
+      <c r="L11" s="262"/>
+      <c r="M11" s="262"/>
+      <c r="N11" s="262"/>
+      <c r="O11" s="262"/>
+      <c r="P11" s="263"/>
+      <c r="Q11" s="256" t="s">
         <v>140</v>
       </c>
-      <c r="R11" s="250"/>
-      <c r="S11" s="250"/>
-      <c r="T11" s="250"/>
-      <c r="U11" s="250"/>
-      <c r="V11" s="250"/>
-      <c r="W11" s="250"/>
-      <c r="X11" s="250"/>
-      <c r="Y11" s="250"/>
-      <c r="Z11" s="250"/>
-      <c r="AA11" s="251"/>
-      <c r="AB11" s="292"/>
-      <c r="AC11" s="293"/>
-      <c r="AD11" s="293"/>
-      <c r="AE11" s="293"/>
-      <c r="AF11" s="293"/>
-      <c r="AG11" s="293"/>
-      <c r="AH11" s="293"/>
-      <c r="AI11" s="293"/>
-      <c r="AJ11" s="293"/>
-      <c r="AK11" s="241" t="s">
+      <c r="R11" s="257"/>
+      <c r="S11" s="257"/>
+      <c r="T11" s="257"/>
+      <c r="U11" s="257"/>
+      <c r="V11" s="257"/>
+      <c r="W11" s="257"/>
+      <c r="X11" s="257"/>
+      <c r="Y11" s="257"/>
+      <c r="Z11" s="257"/>
+      <c r="AA11" s="258"/>
+      <c r="AB11" s="264"/>
+      <c r="AC11" s="265"/>
+      <c r="AD11" s="265"/>
+      <c r="AE11" s="265"/>
+      <c r="AF11" s="265"/>
+      <c r="AG11" s="265"/>
+      <c r="AH11" s="265"/>
+      <c r="AI11" s="265"/>
+      <c r="AJ11" s="265"/>
+      <c r="AK11" s="251" t="s">
         <v>73</v>
       </c>
-      <c r="AL11" s="242"/>
-      <c r="AM11" s="242"/>
-      <c r="AN11" s="242"/>
-      <c r="AO11" s="242"/>
-      <c r="AP11" s="242"/>
-      <c r="AQ11" s="242"/>
-      <c r="AR11" s="242"/>
-      <c r="AS11" s="242"/>
-      <c r="AT11" s="242"/>
-      <c r="AU11" s="242"/>
-      <c r="AV11" s="242"/>
-      <c r="AW11" s="242"/>
-      <c r="AX11" s="242"/>
-      <c r="AY11" s="242"/>
-      <c r="AZ11" s="242"/>
-      <c r="BA11" s="242"/>
-      <c r="BB11" s="242"/>
-      <c r="BC11" s="242"/>
-      <c r="BD11" s="242"/>
-      <c r="BE11" s="242"/>
-      <c r="BF11" s="242"/>
-      <c r="BG11" s="242"/>
-      <c r="BH11" s="242"/>
-      <c r="BI11" s="242"/>
-      <c r="BJ11" s="242"/>
-      <c r="BK11" s="242"/>
-      <c r="BL11" s="242"/>
-      <c r="BM11" s="242"/>
-      <c r="BN11" s="242"/>
-      <c r="BO11" s="242"/>
-      <c r="BP11" s="242"/>
-      <c r="BQ11" s="242"/>
-      <c r="BR11" s="242"/>
-      <c r="BS11" s="243"/>
+      <c r="AL11" s="247"/>
+      <c r="AM11" s="247"/>
+      <c r="AN11" s="247"/>
+      <c r="AO11" s="247"/>
+      <c r="AP11" s="247"/>
+      <c r="AQ11" s="247"/>
+      <c r="AR11" s="247"/>
+      <c r="AS11" s="247"/>
+      <c r="AT11" s="247"/>
+      <c r="AU11" s="247"/>
+      <c r="AV11" s="247"/>
+      <c r="AW11" s="247"/>
+      <c r="AX11" s="247"/>
+      <c r="AY11" s="247"/>
+      <c r="AZ11" s="247"/>
+      <c r="BA11" s="247"/>
+      <c r="BB11" s="247"/>
+      <c r="BC11" s="247"/>
+      <c r="BD11" s="247"/>
+      <c r="BE11" s="247"/>
+      <c r="BF11" s="247"/>
+      <c r="BG11" s="247"/>
+      <c r="BH11" s="247"/>
+      <c r="BI11" s="247"/>
+      <c r="BJ11" s="247"/>
+      <c r="BK11" s="247"/>
+      <c r="BL11" s="247"/>
+      <c r="BM11" s="247"/>
+      <c r="BN11" s="247"/>
+      <c r="BO11" s="247"/>
+      <c r="BP11" s="247"/>
+      <c r="BQ11" s="247"/>
+      <c r="BR11" s="247"/>
+      <c r="BS11" s="252"/>
     </row>
     <row r="12" spans="1:71" ht="45.75" customHeight="1">
-      <c r="A12" s="244" t="s">
+      <c r="A12" s="259" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="245"/>
-      <c r="C12" s="246"/>
-      <c r="D12" s="247"/>
-      <c r="E12" s="247"/>
-      <c r="F12" s="247"/>
-      <c r="G12" s="247"/>
-      <c r="H12" s="247"/>
-      <c r="I12" s="248"/>
-      <c r="J12" s="294" t="s">
+      <c r="B12" s="260"/>
+      <c r="C12" s="241"/>
+      <c r="D12" s="242"/>
+      <c r="E12" s="242"/>
+      <c r="F12" s="242"/>
+      <c r="G12" s="242"/>
+      <c r="H12" s="242"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="261" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="284"/>
-      <c r="L12" s="284"/>
-      <c r="M12" s="284"/>
-      <c r="N12" s="284"/>
-      <c r="O12" s="284"/>
-      <c r="P12" s="295"/>
-      <c r="Q12" s="289"/>
-      <c r="R12" s="290"/>
-      <c r="S12" s="290"/>
-      <c r="T12" s="290"/>
-      <c r="U12" s="290"/>
-      <c r="V12" s="290"/>
-      <c r="W12" s="290"/>
-      <c r="X12" s="290"/>
-      <c r="Y12" s="290"/>
-      <c r="Z12" s="290"/>
-      <c r="AA12" s="291"/>
-      <c r="AB12" s="292" t="s">
+      <c r="K12" s="262"/>
+      <c r="L12" s="262"/>
+      <c r="M12" s="262"/>
+      <c r="N12" s="262"/>
+      <c r="O12" s="262"/>
+      <c r="P12" s="263"/>
+      <c r="Q12" s="253"/>
+      <c r="R12" s="254"/>
+      <c r="S12" s="254"/>
+      <c r="T12" s="254"/>
+      <c r="U12" s="254"/>
+      <c r="V12" s="254"/>
+      <c r="W12" s="254"/>
+      <c r="X12" s="254"/>
+      <c r="Y12" s="254"/>
+      <c r="Z12" s="254"/>
+      <c r="AA12" s="255"/>
+      <c r="AB12" s="264" t="s">
         <v>142</v>
       </c>
-      <c r="AC12" s="293"/>
-      <c r="AD12" s="293"/>
-      <c r="AE12" s="293"/>
-      <c r="AF12" s="293"/>
-      <c r="AG12" s="293"/>
-      <c r="AH12" s="293"/>
-      <c r="AI12" s="293"/>
-      <c r="AJ12" s="293"/>
-      <c r="AK12" s="241" t="s">
+      <c r="AC12" s="265"/>
+      <c r="AD12" s="265"/>
+      <c r="AE12" s="265"/>
+      <c r="AF12" s="265"/>
+      <c r="AG12" s="265"/>
+      <c r="AH12" s="265"/>
+      <c r="AI12" s="265"/>
+      <c r="AJ12" s="265"/>
+      <c r="AK12" s="251" t="s">
         <v>124</v>
       </c>
-      <c r="AL12" s="242"/>
-      <c r="AM12" s="242"/>
-      <c r="AN12" s="242"/>
-      <c r="AO12" s="242"/>
-      <c r="AP12" s="242"/>
-      <c r="AQ12" s="242"/>
-      <c r="AR12" s="242"/>
-      <c r="AS12" s="242"/>
-      <c r="AT12" s="242"/>
-      <c r="AU12" s="242"/>
-      <c r="AV12" s="242"/>
-      <c r="AW12" s="242"/>
-      <c r="AX12" s="242"/>
-      <c r="AY12" s="242"/>
-      <c r="AZ12" s="242"/>
-      <c r="BA12" s="242"/>
-      <c r="BB12" s="242"/>
-      <c r="BC12" s="242"/>
-      <c r="BD12" s="242"/>
-      <c r="BE12" s="242"/>
-      <c r="BF12" s="242"/>
-      <c r="BG12" s="242"/>
-      <c r="BH12" s="242"/>
-      <c r="BI12" s="242"/>
-      <c r="BJ12" s="242"/>
-      <c r="BK12" s="242"/>
-      <c r="BL12" s="242"/>
-      <c r="BM12" s="242"/>
-      <c r="BN12" s="242"/>
-      <c r="BO12" s="242"/>
-      <c r="BP12" s="242"/>
-      <c r="BQ12" s="242"/>
-      <c r="BR12" s="242"/>
-      <c r="BS12" s="243"/>
+      <c r="AL12" s="247"/>
+      <c r="AM12" s="247"/>
+      <c r="AN12" s="247"/>
+      <c r="AO12" s="247"/>
+      <c r="AP12" s="247"/>
+      <c r="AQ12" s="247"/>
+      <c r="AR12" s="247"/>
+      <c r="AS12" s="247"/>
+      <c r="AT12" s="247"/>
+      <c r="AU12" s="247"/>
+      <c r="AV12" s="247"/>
+      <c r="AW12" s="247"/>
+      <c r="AX12" s="247"/>
+      <c r="AY12" s="247"/>
+      <c r="AZ12" s="247"/>
+      <c r="BA12" s="247"/>
+      <c r="BB12" s="247"/>
+      <c r="BC12" s="247"/>
+      <c r="BD12" s="247"/>
+      <c r="BE12" s="247"/>
+      <c r="BF12" s="247"/>
+      <c r="BG12" s="247"/>
+      <c r="BH12" s="247"/>
+      <c r="BI12" s="247"/>
+      <c r="BJ12" s="247"/>
+      <c r="BK12" s="247"/>
+      <c r="BL12" s="247"/>
+      <c r="BM12" s="247"/>
+      <c r="BN12" s="247"/>
+      <c r="BO12" s="247"/>
+      <c r="BP12" s="247"/>
+      <c r="BQ12" s="247"/>
+      <c r="BR12" s="247"/>
+      <c r="BS12" s="252"/>
     </row>
     <row r="13" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A13" s="244" t="s">
+      <c r="A13" s="259" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="245"/>
-      <c r="C13" s="246"/>
-      <c r="D13" s="247"/>
-      <c r="E13" s="247"/>
-      <c r="F13" s="247"/>
-      <c r="G13" s="247"/>
-      <c r="H13" s="247"/>
-      <c r="I13" s="248"/>
-      <c r="J13" s="246" t="s">
+      <c r="B13" s="260"/>
+      <c r="C13" s="241"/>
+      <c r="D13" s="242"/>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="243"/>
+      <c r="J13" s="241" t="s">
         <v>141</v>
       </c>
-      <c r="K13" s="247"/>
-      <c r="L13" s="247"/>
-      <c r="M13" s="247"/>
-      <c r="N13" s="247"/>
-      <c r="O13" s="247"/>
-      <c r="P13" s="248"/>
-      <c r="Q13" s="249"/>
-      <c r="R13" s="250"/>
-      <c r="S13" s="250"/>
-      <c r="T13" s="250"/>
-      <c r="U13" s="250"/>
-      <c r="V13" s="250"/>
-      <c r="W13" s="250"/>
-      <c r="X13" s="250"/>
-      <c r="Y13" s="250"/>
-      <c r="Z13" s="250"/>
-      <c r="AA13" s="251"/>
-      <c r="AB13" s="252"/>
-      <c r="AC13" s="253"/>
-      <c r="AD13" s="253"/>
-      <c r="AE13" s="253"/>
-      <c r="AF13" s="253"/>
-      <c r="AG13" s="253"/>
-      <c r="AH13" s="253"/>
-      <c r="AI13" s="253"/>
-      <c r="AJ13" s="253"/>
-      <c r="AK13" s="241" t="s">
+      <c r="K13" s="242"/>
+      <c r="L13" s="242"/>
+      <c r="M13" s="242"/>
+      <c r="N13" s="242"/>
+      <c r="O13" s="242"/>
+      <c r="P13" s="243"/>
+      <c r="Q13" s="256"/>
+      <c r="R13" s="257"/>
+      <c r="S13" s="257"/>
+      <c r="T13" s="257"/>
+      <c r="U13" s="257"/>
+      <c r="V13" s="257"/>
+      <c r="W13" s="257"/>
+      <c r="X13" s="257"/>
+      <c r="Y13" s="257"/>
+      <c r="Z13" s="257"/>
+      <c r="AA13" s="258"/>
+      <c r="AB13" s="249"/>
+      <c r="AC13" s="250"/>
+      <c r="AD13" s="250"/>
+      <c r="AE13" s="250"/>
+      <c r="AF13" s="250"/>
+      <c r="AG13" s="250"/>
+      <c r="AH13" s="250"/>
+      <c r="AI13" s="250"/>
+      <c r="AJ13" s="250"/>
+      <c r="AK13" s="251" t="s">
         <v>129</v>
       </c>
-      <c r="AL13" s="242"/>
-      <c r="AM13" s="242"/>
-      <c r="AN13" s="242"/>
-      <c r="AO13" s="242"/>
-      <c r="AP13" s="242"/>
-      <c r="AQ13" s="242"/>
-      <c r="AR13" s="242"/>
-      <c r="AS13" s="242"/>
-      <c r="AT13" s="242"/>
-      <c r="AU13" s="242"/>
-      <c r="AV13" s="242"/>
-      <c r="AW13" s="242"/>
-      <c r="AX13" s="242"/>
-      <c r="AY13" s="242"/>
-      <c r="AZ13" s="242"/>
-      <c r="BA13" s="242"/>
-      <c r="BB13" s="242"/>
-      <c r="BC13" s="242"/>
-      <c r="BD13" s="242"/>
-      <c r="BE13" s="242"/>
-      <c r="BF13" s="242"/>
-      <c r="BG13" s="242"/>
-      <c r="BH13" s="242"/>
-      <c r="BI13" s="242"/>
-      <c r="BJ13" s="242"/>
-      <c r="BK13" s="242"/>
-      <c r="BL13" s="242"/>
-      <c r="BM13" s="242"/>
-      <c r="BN13" s="242"/>
-      <c r="BO13" s="242"/>
-      <c r="BP13" s="242"/>
-      <c r="BQ13" s="242"/>
-      <c r="BR13" s="242"/>
-      <c r="BS13" s="243"/>
+      <c r="AL13" s="247"/>
+      <c r="AM13" s="247"/>
+      <c r="AN13" s="247"/>
+      <c r="AO13" s="247"/>
+      <c r="AP13" s="247"/>
+      <c r="AQ13" s="247"/>
+      <c r="AR13" s="247"/>
+      <c r="AS13" s="247"/>
+      <c r="AT13" s="247"/>
+      <c r="AU13" s="247"/>
+      <c r="AV13" s="247"/>
+      <c r="AW13" s="247"/>
+      <c r="AX13" s="247"/>
+      <c r="AY13" s="247"/>
+      <c r="AZ13" s="247"/>
+      <c r="BA13" s="247"/>
+      <c r="BB13" s="247"/>
+      <c r="BC13" s="247"/>
+      <c r="BD13" s="247"/>
+      <c r="BE13" s="247"/>
+      <c r="BF13" s="247"/>
+      <c r="BG13" s="247"/>
+      <c r="BH13" s="247"/>
+      <c r="BI13" s="247"/>
+      <c r="BJ13" s="247"/>
+      <c r="BK13" s="247"/>
+      <c r="BL13" s="247"/>
+      <c r="BM13" s="247"/>
+      <c r="BN13" s="247"/>
+      <c r="BO13" s="247"/>
+      <c r="BP13" s="247"/>
+      <c r="BQ13" s="247"/>
+      <c r="BR13" s="247"/>
+      <c r="BS13" s="252"/>
     </row>
     <row r="14" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A14" s="244" t="s">
+      <c r="A14" s="259" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="245"/>
-      <c r="C14" s="246"/>
-      <c r="D14" s="247"/>
-      <c r="E14" s="247"/>
-      <c r="F14" s="247"/>
-      <c r="G14" s="247"/>
-      <c r="H14" s="247"/>
-      <c r="I14" s="248"/>
-      <c r="J14" s="246" t="s">
+      <c r="B14" s="260"/>
+      <c r="C14" s="241"/>
+      <c r="D14" s="242"/>
+      <c r="E14" s="242"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="242"/>
+      <c r="H14" s="242"/>
+      <c r="I14" s="243"/>
+      <c r="J14" s="241" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="247"/>
-      <c r="L14" s="247"/>
-      <c r="M14" s="247"/>
-      <c r="N14" s="247"/>
-      <c r="O14" s="247"/>
-      <c r="P14" s="248"/>
-      <c r="Q14" s="249"/>
-      <c r="R14" s="250"/>
-      <c r="S14" s="250"/>
-      <c r="T14" s="250"/>
-      <c r="U14" s="250"/>
-      <c r="V14" s="250"/>
-      <c r="W14" s="250"/>
-      <c r="X14" s="250"/>
-      <c r="Y14" s="250"/>
-      <c r="Z14" s="250"/>
-      <c r="AA14" s="251"/>
-      <c r="AB14" s="252"/>
-      <c r="AC14" s="253"/>
-      <c r="AD14" s="253"/>
-      <c r="AE14" s="253"/>
-      <c r="AF14" s="253"/>
-      <c r="AG14" s="253"/>
-      <c r="AH14" s="253"/>
-      <c r="AI14" s="253"/>
-      <c r="AJ14" s="253"/>
-      <c r="AK14" s="241" t="s">
+      <c r="K14" s="242"/>
+      <c r="L14" s="242"/>
+      <c r="M14" s="242"/>
+      <c r="N14" s="242"/>
+      <c r="O14" s="242"/>
+      <c r="P14" s="243"/>
+      <c r="Q14" s="256"/>
+      <c r="R14" s="257"/>
+      <c r="S14" s="257"/>
+      <c r="T14" s="257"/>
+      <c r="U14" s="257"/>
+      <c r="V14" s="257"/>
+      <c r="W14" s="257"/>
+      <c r="X14" s="257"/>
+      <c r="Y14" s="257"/>
+      <c r="Z14" s="257"/>
+      <c r="AA14" s="258"/>
+      <c r="AB14" s="249"/>
+      <c r="AC14" s="250"/>
+      <c r="AD14" s="250"/>
+      <c r="AE14" s="250"/>
+      <c r="AF14" s="250"/>
+      <c r="AG14" s="250"/>
+      <c r="AH14" s="250"/>
+      <c r="AI14" s="250"/>
+      <c r="AJ14" s="250"/>
+      <c r="AK14" s="251" t="s">
         <v>67</v>
       </c>
-      <c r="AL14" s="242"/>
-      <c r="AM14" s="242"/>
-      <c r="AN14" s="242"/>
-      <c r="AO14" s="242"/>
-      <c r="AP14" s="242"/>
-      <c r="AQ14" s="242"/>
-      <c r="AR14" s="242"/>
-      <c r="AS14" s="242"/>
-      <c r="AT14" s="242"/>
-      <c r="AU14" s="242"/>
-      <c r="AV14" s="242"/>
-      <c r="AW14" s="242"/>
-      <c r="AX14" s="242"/>
-      <c r="AY14" s="242"/>
-      <c r="AZ14" s="242"/>
-      <c r="BA14" s="242"/>
-      <c r="BB14" s="242"/>
-      <c r="BC14" s="242"/>
-      <c r="BD14" s="242"/>
-      <c r="BE14" s="242"/>
-      <c r="BF14" s="242"/>
-      <c r="BG14" s="242"/>
-      <c r="BH14" s="242"/>
-      <c r="BI14" s="242"/>
-      <c r="BJ14" s="242"/>
-      <c r="BK14" s="242"/>
-      <c r="BL14" s="242"/>
-      <c r="BM14" s="242"/>
-      <c r="BN14" s="242"/>
-      <c r="BO14" s="242"/>
-      <c r="BP14" s="242"/>
-      <c r="BQ14" s="242"/>
-      <c r="BR14" s="242"/>
-      <c r="BS14" s="243"/>
+      <c r="AL14" s="247"/>
+      <c r="AM14" s="247"/>
+      <c r="AN14" s="247"/>
+      <c r="AO14" s="247"/>
+      <c r="AP14" s="247"/>
+      <c r="AQ14" s="247"/>
+      <c r="AR14" s="247"/>
+      <c r="AS14" s="247"/>
+      <c r="AT14" s="247"/>
+      <c r="AU14" s="247"/>
+      <c r="AV14" s="247"/>
+      <c r="AW14" s="247"/>
+      <c r="AX14" s="247"/>
+      <c r="AY14" s="247"/>
+      <c r="AZ14" s="247"/>
+      <c r="BA14" s="247"/>
+      <c r="BB14" s="247"/>
+      <c r="BC14" s="247"/>
+      <c r="BD14" s="247"/>
+      <c r="BE14" s="247"/>
+      <c r="BF14" s="247"/>
+      <c r="BG14" s="247"/>
+      <c r="BH14" s="247"/>
+      <c r="BI14" s="247"/>
+      <c r="BJ14" s="247"/>
+      <c r="BK14" s="247"/>
+      <c r="BL14" s="247"/>
+      <c r="BM14" s="247"/>
+      <c r="BN14" s="247"/>
+      <c r="BO14" s="247"/>
+      <c r="BP14" s="247"/>
+      <c r="BQ14" s="247"/>
+      <c r="BR14" s="247"/>
+      <c r="BS14" s="252"/>
     </row>
     <row r="15" spans="1:71" ht="46" customHeight="1">
-      <c r="A15" s="244" t="s">
+      <c r="A15" s="259" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="245"/>
-      <c r="C15" s="246"/>
-      <c r="D15" s="247"/>
-      <c r="E15" s="247"/>
-      <c r="F15" s="247"/>
-      <c r="G15" s="247"/>
-      <c r="H15" s="247"/>
-      <c r="I15" s="248"/>
-      <c r="J15" s="246" t="s">
+      <c r="B15" s="260"/>
+      <c r="C15" s="241"/>
+      <c r="D15" s="242"/>
+      <c r="E15" s="242"/>
+      <c r="F15" s="242"/>
+      <c r="G15" s="242"/>
+      <c r="H15" s="242"/>
+      <c r="I15" s="243"/>
+      <c r="J15" s="241" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="247"/>
-      <c r="L15" s="247"/>
-      <c r="M15" s="247"/>
-      <c r="N15" s="247"/>
-      <c r="O15" s="247"/>
-      <c r="P15" s="248"/>
-      <c r="Q15" s="249"/>
-      <c r="R15" s="250"/>
-      <c r="S15" s="250"/>
-      <c r="T15" s="250"/>
-      <c r="U15" s="250"/>
-      <c r="V15" s="250"/>
-      <c r="W15" s="250"/>
-      <c r="X15" s="250"/>
-      <c r="Y15" s="250"/>
-      <c r="Z15" s="250"/>
-      <c r="AA15" s="251"/>
-      <c r="AB15" s="252"/>
-      <c r="AC15" s="253"/>
-      <c r="AD15" s="253"/>
-      <c r="AE15" s="253"/>
-      <c r="AF15" s="253"/>
-      <c r="AG15" s="253"/>
-      <c r="AH15" s="253"/>
-      <c r="AI15" s="253"/>
-      <c r="AJ15" s="253"/>
-      <c r="AK15" s="241"/>
-      <c r="AL15" s="242"/>
-      <c r="AM15" s="242"/>
-      <c r="AN15" s="242"/>
-      <c r="AO15" s="242"/>
-      <c r="AP15" s="242"/>
-      <c r="AQ15" s="242"/>
-      <c r="AR15" s="242"/>
-      <c r="AS15" s="242"/>
-      <c r="AT15" s="242"/>
-      <c r="AU15" s="242"/>
-      <c r="AV15" s="242"/>
-      <c r="AW15" s="242"/>
-      <c r="AX15" s="242"/>
-      <c r="AY15" s="242"/>
-      <c r="AZ15" s="242"/>
-      <c r="BA15" s="242"/>
-      <c r="BB15" s="242"/>
-      <c r="BC15" s="242"/>
-      <c r="BD15" s="242"/>
-      <c r="BE15" s="242"/>
-      <c r="BF15" s="242"/>
-      <c r="BG15" s="242"/>
-      <c r="BH15" s="242"/>
-      <c r="BI15" s="242"/>
-      <c r="BJ15" s="242"/>
-      <c r="BK15" s="242"/>
-      <c r="BL15" s="242"/>
-      <c r="BM15" s="242"/>
-      <c r="BN15" s="242"/>
-      <c r="BO15" s="242"/>
-      <c r="BP15" s="242"/>
-      <c r="BQ15" s="242"/>
-      <c r="BR15" s="242"/>
-      <c r="BS15" s="243"/>
+      <c r="K15" s="242"/>
+      <c r="L15" s="242"/>
+      <c r="M15" s="242"/>
+      <c r="N15" s="242"/>
+      <c r="O15" s="242"/>
+      <c r="P15" s="243"/>
+      <c r="Q15" s="256"/>
+      <c r="R15" s="257"/>
+      <c r="S15" s="257"/>
+      <c r="T15" s="257"/>
+      <c r="U15" s="257"/>
+      <c r="V15" s="257"/>
+      <c r="W15" s="257"/>
+      <c r="X15" s="257"/>
+      <c r="Y15" s="257"/>
+      <c r="Z15" s="257"/>
+      <c r="AA15" s="258"/>
+      <c r="AB15" s="249"/>
+      <c r="AC15" s="250"/>
+      <c r="AD15" s="250"/>
+      <c r="AE15" s="250"/>
+      <c r="AF15" s="250"/>
+      <c r="AG15" s="250"/>
+      <c r="AH15" s="250"/>
+      <c r="AI15" s="250"/>
+      <c r="AJ15" s="250"/>
+      <c r="AK15" s="251"/>
+      <c r="AL15" s="247"/>
+      <c r="AM15" s="247"/>
+      <c r="AN15" s="247"/>
+      <c r="AO15" s="247"/>
+      <c r="AP15" s="247"/>
+      <c r="AQ15" s="247"/>
+      <c r="AR15" s="247"/>
+      <c r="AS15" s="247"/>
+      <c r="AT15" s="247"/>
+      <c r="AU15" s="247"/>
+      <c r="AV15" s="247"/>
+      <c r="AW15" s="247"/>
+      <c r="AX15" s="247"/>
+      <c r="AY15" s="247"/>
+      <c r="AZ15" s="247"/>
+      <c r="BA15" s="247"/>
+      <c r="BB15" s="247"/>
+      <c r="BC15" s="247"/>
+      <c r="BD15" s="247"/>
+      <c r="BE15" s="247"/>
+      <c r="BF15" s="247"/>
+      <c r="BG15" s="247"/>
+      <c r="BH15" s="247"/>
+      <c r="BI15" s="247"/>
+      <c r="BJ15" s="247"/>
+      <c r="BK15" s="247"/>
+      <c r="BL15" s="247"/>
+      <c r="BM15" s="247"/>
+      <c r="BN15" s="247"/>
+      <c r="BO15" s="247"/>
+      <c r="BP15" s="247"/>
+      <c r="BQ15" s="247"/>
+      <c r="BR15" s="247"/>
+      <c r="BS15" s="252"/>
     </row>
     <row r="16" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A16" s="276"/>
-      <c r="B16" s="299"/>
-      <c r="C16" s="246"/>
-      <c r="D16" s="247"/>
-      <c r="E16" s="247"/>
-      <c r="F16" s="247"/>
-      <c r="G16" s="247"/>
-      <c r="H16" s="247"/>
-      <c r="I16" s="248"/>
+      <c r="A16" s="239"/>
+      <c r="B16" s="240"/>
+      <c r="C16" s="241"/>
+      <c r="D16" s="242"/>
+      <c r="E16" s="242"/>
+      <c r="F16" s="242"/>
+      <c r="G16" s="242"/>
+      <c r="H16" s="242"/>
+      <c r="I16" s="243"/>
       <c r="J16" s="134"/>
-      <c r="K16" s="300"/>
-      <c r="L16" s="300"/>
-      <c r="M16" s="300"/>
-      <c r="N16" s="300"/>
-      <c r="O16" s="300"/>
-      <c r="P16" s="301"/>
-      <c r="Q16" s="302"/>
-      <c r="R16" s="242"/>
-      <c r="S16" s="242"/>
-      <c r="T16" s="242"/>
-      <c r="U16" s="242"/>
-      <c r="V16" s="242"/>
-      <c r="W16" s="242"/>
-      <c r="X16" s="242"/>
-      <c r="Y16" s="242"/>
-      <c r="Z16" s="242"/>
-      <c r="AA16" s="303"/>
-      <c r="AB16" s="252"/>
-      <c r="AC16" s="253"/>
-      <c r="AD16" s="253"/>
-      <c r="AE16" s="253"/>
-      <c r="AF16" s="253"/>
-      <c r="AG16" s="253"/>
-      <c r="AH16" s="253"/>
-      <c r="AI16" s="253"/>
-      <c r="AJ16" s="253"/>
-      <c r="AK16" s="241"/>
-      <c r="AL16" s="242"/>
-      <c r="AM16" s="242"/>
-      <c r="AN16" s="242"/>
-      <c r="AO16" s="242"/>
-      <c r="AP16" s="242"/>
-      <c r="AQ16" s="242"/>
-      <c r="AR16" s="242"/>
-      <c r="AS16" s="242"/>
-      <c r="AT16" s="242"/>
-      <c r="AU16" s="242"/>
-      <c r="AV16" s="242"/>
-      <c r="AW16" s="242"/>
-      <c r="AX16" s="242"/>
-      <c r="AY16" s="242"/>
-      <c r="AZ16" s="242"/>
-      <c r="BA16" s="242"/>
-      <c r="BB16" s="242"/>
-      <c r="BC16" s="242"/>
-      <c r="BD16" s="242"/>
-      <c r="BE16" s="242"/>
-      <c r="BF16" s="242"/>
-      <c r="BG16" s="242"/>
-      <c r="BH16" s="242"/>
-      <c r="BI16" s="242"/>
-      <c r="BJ16" s="242"/>
-      <c r="BK16" s="242"/>
-      <c r="BL16" s="242"/>
-      <c r="BM16" s="242"/>
-      <c r="BN16" s="242"/>
-      <c r="BO16" s="242"/>
-      <c r="BP16" s="242"/>
-      <c r="BQ16" s="242"/>
-      <c r="BR16" s="242"/>
-      <c r="BS16" s="243"/>
+      <c r="K16" s="244"/>
+      <c r="L16" s="244"/>
+      <c r="M16" s="244"/>
+      <c r="N16" s="244"/>
+      <c r="O16" s="244"/>
+      <c r="P16" s="245"/>
+      <c r="Q16" s="246"/>
+      <c r="R16" s="247"/>
+      <c r="S16" s="247"/>
+      <c r="T16" s="247"/>
+      <c r="U16" s="247"/>
+      <c r="V16" s="247"/>
+      <c r="W16" s="247"/>
+      <c r="X16" s="247"/>
+      <c r="Y16" s="247"/>
+      <c r="Z16" s="247"/>
+      <c r="AA16" s="248"/>
+      <c r="AB16" s="249"/>
+      <c r="AC16" s="250"/>
+      <c r="AD16" s="250"/>
+      <c r="AE16" s="250"/>
+      <c r="AF16" s="250"/>
+      <c r="AG16" s="250"/>
+      <c r="AH16" s="250"/>
+      <c r="AI16" s="250"/>
+      <c r="AJ16" s="250"/>
+      <c r="AK16" s="251"/>
+      <c r="AL16" s="247"/>
+      <c r="AM16" s="247"/>
+      <c r="AN16" s="247"/>
+      <c r="AO16" s="247"/>
+      <c r="AP16" s="247"/>
+      <c r="AQ16" s="247"/>
+      <c r="AR16" s="247"/>
+      <c r="AS16" s="247"/>
+      <c r="AT16" s="247"/>
+      <c r="AU16" s="247"/>
+      <c r="AV16" s="247"/>
+      <c r="AW16" s="247"/>
+      <c r="AX16" s="247"/>
+      <c r="AY16" s="247"/>
+      <c r="AZ16" s="247"/>
+      <c r="BA16" s="247"/>
+      <c r="BB16" s="247"/>
+      <c r="BC16" s="247"/>
+      <c r="BD16" s="247"/>
+      <c r="BE16" s="247"/>
+      <c r="BF16" s="247"/>
+      <c r="BG16" s="247"/>
+      <c r="BH16" s="247"/>
+      <c r="BI16" s="247"/>
+      <c r="BJ16" s="247"/>
+      <c r="BK16" s="247"/>
+      <c r="BL16" s="247"/>
+      <c r="BM16" s="247"/>
+      <c r="BN16" s="247"/>
+      <c r="BO16" s="247"/>
+      <c r="BP16" s="247"/>
+      <c r="BQ16" s="247"/>
+      <c r="BR16" s="247"/>
+      <c r="BS16" s="252"/>
     </row>
     <row r="17" spans="28:36">
-      <c r="AB17" s="239"/>
-      <c r="AC17" s="239"/>
-      <c r="AD17" s="239"/>
-      <c r="AE17" s="239"/>
-      <c r="AF17" s="239"/>
-      <c r="AG17" s="239"/>
-      <c r="AH17" s="239"/>
-      <c r="AI17" s="239"/>
-      <c r="AJ17" s="239"/>
+      <c r="AB17" s="302"/>
+      <c r="AC17" s="302"/>
+      <c r="AD17" s="302"/>
+      <c r="AE17" s="302"/>
+      <c r="AF17" s="302"/>
+      <c r="AG17" s="302"/>
+      <c r="AH17" s="302"/>
+      <c r="AI17" s="302"/>
+      <c r="AJ17" s="302"/>
     </row>
     <row r="18" spans="28:36">
-      <c r="AB18" s="240"/>
-      <c r="AC18" s="240"/>
-      <c r="AD18" s="240"/>
-      <c r="AE18" s="240"/>
-      <c r="AF18" s="240"/>
-      <c r="AG18" s="240"/>
-      <c r="AH18" s="240"/>
-      <c r="AI18" s="240"/>
-      <c r="AJ18" s="240"/>
+      <c r="AB18" s="303"/>
+      <c r="AC18" s="303"/>
+      <c r="AD18" s="303"/>
+      <c r="AE18" s="303"/>
+      <c r="AF18" s="303"/>
+      <c r="AG18" s="303"/>
+      <c r="AH18" s="303"/>
+      <c r="AI18" s="303"/>
+      <c r="AJ18" s="303"/>
     </row>
     <row r="19" spans="28:36">
       <c r="AB19" s="152"/>
@@ -28301,29 +28184,50 @@
     </row>
   </sheetData>
   <mergeCells count="83">
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="K16:P16"/>
-    <mergeCell ref="Q16:AA16"/>
-    <mergeCell ref="AB16:AJ16"/>
-    <mergeCell ref="C14:I14"/>
-    <mergeCell ref="J14:P14"/>
-    <mergeCell ref="AB14:AJ14"/>
-    <mergeCell ref="AB15:AJ15"/>
-    <mergeCell ref="AK16:BS16"/>
-    <mergeCell ref="Q12:AA12"/>
-    <mergeCell ref="Q9:AA9"/>
-    <mergeCell ref="Q11:AA11"/>
-    <mergeCell ref="AK11:BS11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="J12:P12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="J11:P11"/>
-    <mergeCell ref="AK12:BS12"/>
-    <mergeCell ref="AB11:AJ11"/>
-    <mergeCell ref="AB12:AJ12"/>
-    <mergeCell ref="Q10:AA10"/>
+    <mergeCell ref="AB17:AJ17"/>
+    <mergeCell ref="AB18:AJ18"/>
+    <mergeCell ref="AK13:BS13"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="C13:I13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="Q13:AA13"/>
+    <mergeCell ref="AB13:AJ13"/>
+    <mergeCell ref="AK14:BS14"/>
+    <mergeCell ref="AK15:BS15"/>
+    <mergeCell ref="Q15:AA15"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="C15:I15"/>
+    <mergeCell ref="J15:P15"/>
+    <mergeCell ref="Q14:AA14"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="AK5:BS5"/>
+    <mergeCell ref="Q5:AA5"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="Q2:BS2"/>
+    <mergeCell ref="A3:B4"/>
+    <mergeCell ref="C3:P3"/>
+    <mergeCell ref="C4:I4"/>
+    <mergeCell ref="J4:P4"/>
+    <mergeCell ref="Q3:AA4"/>
+    <mergeCell ref="AK3:BS4"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="J5:P5"/>
+    <mergeCell ref="AB3:AJ4"/>
+    <mergeCell ref="AB5:AJ5"/>
+    <mergeCell ref="AK6:BS6"/>
+    <mergeCell ref="AK7:BS7"/>
+    <mergeCell ref="Q6:AA6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="J7:P7"/>
+    <mergeCell ref="Q7:AA7"/>
+    <mergeCell ref="AB6:AJ6"/>
+    <mergeCell ref="AB7:AJ7"/>
     <mergeCell ref="AK8:BS8"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:I10"/>
@@ -28340,50 +28244,29 @@
     <mergeCell ref="AB8:AJ8"/>
     <mergeCell ref="AB9:AJ9"/>
     <mergeCell ref="AB10:AJ10"/>
-    <mergeCell ref="AK6:BS6"/>
-    <mergeCell ref="AK7:BS7"/>
-    <mergeCell ref="Q6:AA6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AA7"/>
-    <mergeCell ref="AB6:AJ6"/>
-    <mergeCell ref="AB7:AJ7"/>
-    <mergeCell ref="AK5:BS5"/>
-    <mergeCell ref="Q5:AA5"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="Q2:BS2"/>
-    <mergeCell ref="A3:B4"/>
-    <mergeCell ref="C3:P3"/>
-    <mergeCell ref="C4:I4"/>
-    <mergeCell ref="J4:P4"/>
-    <mergeCell ref="Q3:AA4"/>
-    <mergeCell ref="AK3:BS4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="J5:P5"/>
-    <mergeCell ref="AB3:AJ4"/>
-    <mergeCell ref="AB5:AJ5"/>
-    <mergeCell ref="AB17:AJ17"/>
-    <mergeCell ref="AB18:AJ18"/>
-    <mergeCell ref="AK13:BS13"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AA13"/>
-    <mergeCell ref="AB13:AJ13"/>
-    <mergeCell ref="AK14:BS14"/>
-    <mergeCell ref="AK15:BS15"/>
-    <mergeCell ref="Q15:AA15"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q14:AA14"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="Q12:AA12"/>
+    <mergeCell ref="Q9:AA9"/>
+    <mergeCell ref="Q11:AA11"/>
+    <mergeCell ref="AK11:BS11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:I12"/>
+    <mergeCell ref="J12:P12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="J11:P11"/>
+    <mergeCell ref="AK12:BS12"/>
+    <mergeCell ref="AB11:AJ11"/>
+    <mergeCell ref="AB12:AJ12"/>
+    <mergeCell ref="Q10:AA10"/>
+    <mergeCell ref="C14:I14"/>
+    <mergeCell ref="J14:P14"/>
+    <mergeCell ref="AB14:AJ14"/>
+    <mergeCell ref="AB15:AJ15"/>
+    <mergeCell ref="AK16:BS16"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:I16"/>
+    <mergeCell ref="K16:P16"/>
+    <mergeCell ref="Q16:AA16"/>
+    <mergeCell ref="AB16:AJ16"/>
   </mergeCells>
   <phoneticPr fontId="56"/>
   <conditionalFormatting sqref="Q5:Q9">
@@ -28804,15 +28687,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="13.75" customHeight="1">
-      <c r="A1" s="341" t="s">
+      <c r="A1" s="307" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="341"/>
-      <c r="C1" s="341"/>
-      <c r="D1" s="341"/>
-      <c r="E1" s="341"/>
-      <c r="F1" s="341"/>
-      <c r="G1" s="341"/>
+      <c r="B1" s="307"/>
+      <c r="C1" s="307"/>
+      <c r="D1" s="307"/>
+      <c r="E1" s="307"/>
+      <c r="F1" s="307"/>
+      <c r="G1" s="307"/>
       <c r="H1" s="142"/>
       <c r="I1" s="142"/>
       <c r="J1" s="142"/>
@@ -28884,57 +28767,57 @@
       <c r="BX1" s="143"/>
     </row>
     <row r="2" spans="1:76" ht="13.75" customHeight="1">
-      <c r="A2" s="339" t="s">
+      <c r="A2" s="305" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="340"/>
-      <c r="C2" s="342" t="s">
+      <c r="B2" s="306"/>
+      <c r="C2" s="308" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="343"/>
-      <c r="E2" s="343"/>
-      <c r="F2" s="343"/>
-      <c r="G2" s="343"/>
-      <c r="H2" s="343"/>
-      <c r="I2" s="344"/>
-      <c r="J2" s="339" t="s">
+      <c r="D2" s="309"/>
+      <c r="E2" s="309"/>
+      <c r="F2" s="309"/>
+      <c r="G2" s="309"/>
+      <c r="H2" s="309"/>
+      <c r="I2" s="310"/>
+      <c r="J2" s="305" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="340"/>
-      <c r="L2" s="340"/>
-      <c r="M2" s="340"/>
-      <c r="N2" s="340"/>
-      <c r="O2" s="340"/>
-      <c r="P2" s="339" t="s">
+      <c r="K2" s="306"/>
+      <c r="L2" s="306"/>
+      <c r="M2" s="306"/>
+      <c r="N2" s="306"/>
+      <c r="O2" s="306"/>
+      <c r="P2" s="305" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="340"/>
-      <c r="R2" s="340"/>
-      <c r="S2" s="340"/>
-      <c r="T2" s="340"/>
-      <c r="U2" s="340"/>
-      <c r="V2" s="340"/>
-      <c r="W2" s="340"/>
-      <c r="X2" s="339" t="s">
+      <c r="Q2" s="306"/>
+      <c r="R2" s="306"/>
+      <c r="S2" s="306"/>
+      <c r="T2" s="306"/>
+      <c r="U2" s="306"/>
+      <c r="V2" s="306"/>
+      <c r="W2" s="306"/>
+      <c r="X2" s="305" t="s">
         <v>146</v>
       </c>
-      <c r="Y2" s="340"/>
-      <c r="Z2" s="340"/>
-      <c r="AA2" s="340"/>
-      <c r="AB2" s="340"/>
-      <c r="AC2" s="340"/>
-      <c r="AD2" s="340"/>
-      <c r="AE2" s="340"/>
-      <c r="AF2" s="339" t="s">
+      <c r="Y2" s="306"/>
+      <c r="Z2" s="306"/>
+      <c r="AA2" s="306"/>
+      <c r="AB2" s="306"/>
+      <c r="AC2" s="306"/>
+      <c r="AD2" s="306"/>
+      <c r="AE2" s="306"/>
+      <c r="AF2" s="305" t="s">
         <v>40</v>
       </c>
-      <c r="AG2" s="340"/>
-      <c r="AH2" s="340"/>
-      <c r="AI2" s="340"/>
-      <c r="AJ2" s="340"/>
-      <c r="AK2" s="340"/>
-      <c r="AL2" s="340"/>
-      <c r="AM2" s="340"/>
+      <c r="AG2" s="306"/>
+      <c r="AH2" s="306"/>
+      <c r="AI2" s="306"/>
+      <c r="AJ2" s="306"/>
+      <c r="AK2" s="306"/>
+      <c r="AL2" s="306"/>
+      <c r="AM2" s="306"/>
       <c r="AN2" s="143"/>
       <c r="AO2" s="143"/>
       <c r="AP2" s="143"/>
@@ -28974,45 +28857,45 @@
       <c r="BX2" s="143"/>
     </row>
     <row r="3" spans="1:76" ht="48.75" customHeight="1">
-      <c r="A3" s="340"/>
-      <c r="B3" s="340"/>
-      <c r="C3" s="345"/>
-      <c r="D3" s="346"/>
-      <c r="E3" s="346"/>
-      <c r="F3" s="346"/>
-      <c r="G3" s="346"/>
-      <c r="H3" s="346"/>
-      <c r="I3" s="347"/>
-      <c r="J3" s="340"/>
-      <c r="K3" s="340"/>
-      <c r="L3" s="340"/>
-      <c r="M3" s="340"/>
-      <c r="N3" s="340"/>
-      <c r="O3" s="340"/>
-      <c r="P3" s="340"/>
-      <c r="Q3" s="340"/>
-      <c r="R3" s="340"/>
-      <c r="S3" s="340"/>
-      <c r="T3" s="340"/>
-      <c r="U3" s="340"/>
-      <c r="V3" s="340"/>
-      <c r="W3" s="340"/>
-      <c r="X3" s="340"/>
-      <c r="Y3" s="340"/>
-      <c r="Z3" s="340"/>
-      <c r="AA3" s="340"/>
-      <c r="AB3" s="340"/>
-      <c r="AC3" s="340"/>
-      <c r="AD3" s="340"/>
-      <c r="AE3" s="340"/>
-      <c r="AF3" s="340"/>
-      <c r="AG3" s="340"/>
-      <c r="AH3" s="340"/>
-      <c r="AI3" s="340"/>
-      <c r="AJ3" s="340"/>
-      <c r="AK3" s="340"/>
-      <c r="AL3" s="340"/>
-      <c r="AM3" s="340"/>
+      <c r="A3" s="306"/>
+      <c r="B3" s="306"/>
+      <c r="C3" s="311"/>
+      <c r="D3" s="312"/>
+      <c r="E3" s="312"/>
+      <c r="F3" s="312"/>
+      <c r="G3" s="312"/>
+      <c r="H3" s="312"/>
+      <c r="I3" s="313"/>
+      <c r="J3" s="306"/>
+      <c r="K3" s="306"/>
+      <c r="L3" s="306"/>
+      <c r="M3" s="306"/>
+      <c r="N3" s="306"/>
+      <c r="O3" s="306"/>
+      <c r="P3" s="306"/>
+      <c r="Q3" s="306"/>
+      <c r="R3" s="306"/>
+      <c r="S3" s="306"/>
+      <c r="T3" s="306"/>
+      <c r="U3" s="306"/>
+      <c r="V3" s="306"/>
+      <c r="W3" s="306"/>
+      <c r="X3" s="306"/>
+      <c r="Y3" s="306"/>
+      <c r="Z3" s="306"/>
+      <c r="AA3" s="306"/>
+      <c r="AB3" s="306"/>
+      <c r="AC3" s="306"/>
+      <c r="AD3" s="306"/>
+      <c r="AE3" s="306"/>
+      <c r="AF3" s="306"/>
+      <c r="AG3" s="306"/>
+      <c r="AH3" s="306"/>
+      <c r="AI3" s="306"/>
+      <c r="AJ3" s="306"/>
+      <c r="AK3" s="306"/>
+      <c r="AL3" s="306"/>
+      <c r="AM3" s="306"/>
       <c r="AN3" s="143"/>
       <c r="AO3" s="143"/>
       <c r="AP3" s="143"/>
@@ -29052,57 +28935,57 @@
       <c r="BX3" s="143"/>
     </row>
     <row r="4" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A4" s="311">
+      <c r="A4" s="339">
         <v>1</v>
       </c>
-      <c r="B4" s="312"/>
-      <c r="C4" s="305" t="s">
+      <c r="B4" s="340"/>
+      <c r="C4" s="333" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="306"/>
-      <c r="E4" s="306"/>
-      <c r="F4" s="306"/>
-      <c r="G4" s="306"/>
-      <c r="H4" s="306"/>
-      <c r="I4" s="307"/>
-      <c r="J4" s="322" t="s">
+      <c r="D4" s="334"/>
+      <c r="E4" s="334"/>
+      <c r="F4" s="334"/>
+      <c r="G4" s="334"/>
+      <c r="H4" s="334"/>
+      <c r="I4" s="335"/>
+      <c r="J4" s="315" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="322"/>
-      <c r="L4" s="322"/>
-      <c r="M4" s="322"/>
-      <c r="N4" s="322"/>
-      <c r="O4" s="322"/>
-      <c r="P4" s="336" t="s">
+      <c r="K4" s="315"/>
+      <c r="L4" s="315"/>
+      <c r="M4" s="315"/>
+      <c r="N4" s="315"/>
+      <c r="O4" s="315"/>
+      <c r="P4" s="321" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="336"/>
-      <c r="R4" s="336"/>
-      <c r="S4" s="336"/>
-      <c r="T4" s="336"/>
-      <c r="U4" s="333" t="s">
+      <c r="Q4" s="321"/>
+      <c r="R4" s="321"/>
+      <c r="S4" s="321"/>
+      <c r="T4" s="321"/>
+      <c r="U4" s="322" t="s">
         <v>34</v>
       </c>
-      <c r="V4" s="333"/>
-      <c r="W4" s="333"/>
-      <c r="X4" s="325" t="s">
+      <c r="V4" s="322"/>
+      <c r="W4" s="322"/>
+      <c r="X4" s="318" t="s">
         <v>149</v>
       </c>
-      <c r="Y4" s="326"/>
-      <c r="Z4" s="326"/>
-      <c r="AA4" s="326"/>
-      <c r="AB4" s="326"/>
-      <c r="AC4" s="326"/>
-      <c r="AD4" s="326"/>
-      <c r="AE4" s="327"/>
-      <c r="AF4" s="337"/>
-      <c r="AG4" s="337"/>
-      <c r="AH4" s="337"/>
-      <c r="AI4" s="337"/>
-      <c r="AJ4" s="337"/>
-      <c r="AK4" s="337"/>
-      <c r="AL4" s="337"/>
-      <c r="AM4" s="337"/>
+      <c r="Y4" s="319"/>
+      <c r="Z4" s="319"/>
+      <c r="AA4" s="319"/>
+      <c r="AB4" s="319"/>
+      <c r="AC4" s="319"/>
+      <c r="AD4" s="319"/>
+      <c r="AE4" s="320"/>
+      <c r="AF4" s="314"/>
+      <c r="AG4" s="314"/>
+      <c r="AH4" s="314"/>
+      <c r="AI4" s="314"/>
+      <c r="AJ4" s="314"/>
+      <c r="AK4" s="314"/>
+      <c r="AL4" s="314"/>
+      <c r="AM4" s="314"/>
       <c r="AN4" s="145"/>
       <c r="AO4" s="145"/>
       <c r="AP4" s="145"/>
@@ -29142,53 +29025,53 @@
       <c r="BX4" s="145"/>
     </row>
     <row r="5" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A5" s="313"/>
-      <c r="B5" s="314"/>
-      <c r="C5" s="308"/>
-      <c r="D5" s="309"/>
-      <c r="E5" s="309"/>
-      <c r="F5" s="309"/>
-      <c r="G5" s="309"/>
-      <c r="H5" s="309"/>
-      <c r="I5" s="310"/>
-      <c r="J5" s="322" t="s">
+      <c r="A5" s="341"/>
+      <c r="B5" s="342"/>
+      <c r="C5" s="336"/>
+      <c r="D5" s="337"/>
+      <c r="E5" s="337"/>
+      <c r="F5" s="337"/>
+      <c r="G5" s="337"/>
+      <c r="H5" s="337"/>
+      <c r="I5" s="338"/>
+      <c r="J5" s="315" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="322"/>
-      <c r="L5" s="322"/>
-      <c r="M5" s="322"/>
-      <c r="N5" s="322"/>
-      <c r="O5" s="322"/>
-      <c r="P5" s="323" t="s">
+      <c r="K5" s="315"/>
+      <c r="L5" s="315"/>
+      <c r="M5" s="315"/>
+      <c r="N5" s="315"/>
+      <c r="O5" s="315"/>
+      <c r="P5" s="316" t="s">
         <v>87</v>
       </c>
-      <c r="Q5" s="323"/>
-      <c r="R5" s="323"/>
-      <c r="S5" s="323"/>
-      <c r="T5" s="323"/>
-      <c r="U5" s="338">
+      <c r="Q5" s="316"/>
+      <c r="R5" s="316"/>
+      <c r="S5" s="316"/>
+      <c r="T5" s="316"/>
+      <c r="U5" s="317">
         <v>255</v>
       </c>
-      <c r="V5" s="338"/>
-      <c r="W5" s="338"/>
-      <c r="X5" s="325" t="s">
+      <c r="V5" s="317"/>
+      <c r="W5" s="317"/>
+      <c r="X5" s="318" t="s">
         <v>147</v>
       </c>
-      <c r="Y5" s="326"/>
-      <c r="Z5" s="326"/>
-      <c r="AA5" s="326"/>
-      <c r="AB5" s="326"/>
-      <c r="AC5" s="326"/>
-      <c r="AD5" s="326"/>
-      <c r="AE5" s="327"/>
-      <c r="AF5" s="337"/>
-      <c r="AG5" s="337"/>
-      <c r="AH5" s="337"/>
-      <c r="AI5" s="337"/>
-      <c r="AJ5" s="337"/>
-      <c r="AK5" s="337"/>
-      <c r="AL5" s="337"/>
-      <c r="AM5" s="337"/>
+      <c r="Y5" s="319"/>
+      <c r="Z5" s="319"/>
+      <c r="AA5" s="319"/>
+      <c r="AB5" s="319"/>
+      <c r="AC5" s="319"/>
+      <c r="AD5" s="319"/>
+      <c r="AE5" s="320"/>
+      <c r="AF5" s="314"/>
+      <c r="AG5" s="314"/>
+      <c r="AH5" s="314"/>
+      <c r="AI5" s="314"/>
+      <c r="AJ5" s="314"/>
+      <c r="AK5" s="314"/>
+      <c r="AL5" s="314"/>
+      <c r="AM5" s="314"/>
       <c r="AN5" s="145"/>
       <c r="AO5" s="145"/>
       <c r="AP5" s="145"/>
@@ -29228,57 +29111,57 @@
       <c r="BX5" s="145"/>
     </row>
     <row r="6" spans="1:76" ht="27" customHeight="1">
-      <c r="A6" s="317">
+      <c r="A6" s="323">
         <v>2</v>
       </c>
-      <c r="B6" s="317"/>
-      <c r="C6" s="319" t="s">
+      <c r="B6" s="323"/>
+      <c r="C6" s="324" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="320"/>
-      <c r="E6" s="320"/>
-      <c r="F6" s="320"/>
-      <c r="G6" s="320"/>
-      <c r="H6" s="320"/>
-      <c r="I6" s="321"/>
-      <c r="J6" s="322" t="s">
+      <c r="D6" s="325"/>
+      <c r="E6" s="325"/>
+      <c r="F6" s="325"/>
+      <c r="G6" s="325"/>
+      <c r="H6" s="325"/>
+      <c r="I6" s="326"/>
+      <c r="J6" s="315" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="322"/>
-      <c r="L6" s="322"/>
-      <c r="M6" s="322"/>
-      <c r="N6" s="322"/>
-      <c r="O6" s="322"/>
-      <c r="P6" s="323" t="s">
+      <c r="K6" s="315"/>
+      <c r="L6" s="315"/>
+      <c r="M6" s="315"/>
+      <c r="N6" s="315"/>
+      <c r="O6" s="315"/>
+      <c r="P6" s="316" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="323"/>
-      <c r="R6" s="323"/>
-      <c r="S6" s="323"/>
-      <c r="T6" s="323"/>
-      <c r="U6" s="324">
+      <c r="Q6" s="316"/>
+      <c r="R6" s="316"/>
+      <c r="S6" s="316"/>
+      <c r="T6" s="316"/>
+      <c r="U6" s="327">
         <v>100</v>
       </c>
-      <c r="V6" s="324"/>
-      <c r="W6" s="324"/>
-      <c r="X6" s="325" t="s">
+      <c r="V6" s="327"/>
+      <c r="W6" s="327"/>
+      <c r="X6" s="318" t="s">
         <v>148</v>
       </c>
-      <c r="Y6" s="326"/>
-      <c r="Z6" s="326"/>
-      <c r="AA6" s="326"/>
-      <c r="AB6" s="326"/>
-      <c r="AC6" s="326"/>
-      <c r="AD6" s="326"/>
-      <c r="AE6" s="327"/>
-      <c r="AF6" s="317"/>
-      <c r="AG6" s="317"/>
-      <c r="AH6" s="317"/>
-      <c r="AI6" s="317"/>
-      <c r="AJ6" s="317"/>
-      <c r="AK6" s="317"/>
-      <c r="AL6" s="317"/>
-      <c r="AM6" s="317"/>
+      <c r="Y6" s="319"/>
+      <c r="Z6" s="319"/>
+      <c r="AA6" s="319"/>
+      <c r="AB6" s="319"/>
+      <c r="AC6" s="319"/>
+      <c r="AD6" s="319"/>
+      <c r="AE6" s="320"/>
+      <c r="AF6" s="323"/>
+      <c r="AG6" s="323"/>
+      <c r="AH6" s="323"/>
+      <c r="AI6" s="323"/>
+      <c r="AJ6" s="323"/>
+      <c r="AK6" s="323"/>
+      <c r="AL6" s="323"/>
+      <c r="AM6" s="323"/>
       <c r="AN6" s="143"/>
       <c r="AO6" s="143"/>
       <c r="AP6" s="143"/>
@@ -29318,57 +29201,57 @@
       <c r="BX6" s="143"/>
     </row>
     <row r="7" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A7" s="311">
+      <c r="A7" s="339">
         <v>3</v>
       </c>
-      <c r="B7" s="312"/>
-      <c r="C7" s="319" t="s">
+      <c r="B7" s="340"/>
+      <c r="C7" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="320"/>
-      <c r="E7" s="320"/>
-      <c r="F7" s="320"/>
-      <c r="G7" s="320"/>
-      <c r="H7" s="320"/>
-      <c r="I7" s="321"/>
-      <c r="J7" s="322" t="s">
+      <c r="D7" s="325"/>
+      <c r="E7" s="325"/>
+      <c r="F7" s="325"/>
+      <c r="G7" s="325"/>
+      <c r="H7" s="325"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="315" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="322"/>
-      <c r="L7" s="322"/>
-      <c r="M7" s="322"/>
-      <c r="N7" s="322"/>
-      <c r="O7" s="322"/>
-      <c r="P7" s="336" t="s">
+      <c r="K7" s="315"/>
+      <c r="L7" s="315"/>
+      <c r="M7" s="315"/>
+      <c r="N7" s="315"/>
+      <c r="O7" s="315"/>
+      <c r="P7" s="321" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="336"/>
-      <c r="R7" s="336"/>
-      <c r="S7" s="336"/>
-      <c r="T7" s="336"/>
-      <c r="U7" s="333" t="s">
+      <c r="Q7" s="321"/>
+      <c r="R7" s="321"/>
+      <c r="S7" s="321"/>
+      <c r="T7" s="321"/>
+      <c r="U7" s="322" t="s">
         <v>34</v>
       </c>
-      <c r="V7" s="333"/>
-      <c r="W7" s="333"/>
-      <c r="X7" s="325" t="s">
+      <c r="V7" s="322"/>
+      <c r="W7" s="322"/>
+      <c r="X7" s="318" t="s">
         <v>150</v>
       </c>
-      <c r="Y7" s="326"/>
-      <c r="Z7" s="326"/>
-      <c r="AA7" s="326"/>
-      <c r="AB7" s="326"/>
-      <c r="AC7" s="326"/>
-      <c r="AD7" s="326"/>
-      <c r="AE7" s="327"/>
-      <c r="AF7" s="334"/>
-      <c r="AG7" s="334"/>
-      <c r="AH7" s="334"/>
-      <c r="AI7" s="334"/>
-      <c r="AJ7" s="334"/>
-      <c r="AK7" s="334"/>
-      <c r="AL7" s="334"/>
-      <c r="AM7" s="334"/>
+      <c r="Y7" s="319"/>
+      <c r="Z7" s="319"/>
+      <c r="AA7" s="319"/>
+      <c r="AB7" s="319"/>
+      <c r="AC7" s="319"/>
+      <c r="AD7" s="319"/>
+      <c r="AE7" s="320"/>
+      <c r="AF7" s="328"/>
+      <c r="AG7" s="328"/>
+      <c r="AH7" s="328"/>
+      <c r="AI7" s="328"/>
+      <c r="AJ7" s="328"/>
+      <c r="AK7" s="328"/>
+      <c r="AL7" s="328"/>
+      <c r="AM7" s="328"/>
       <c r="AN7" s="147"/>
       <c r="AO7" s="147"/>
       <c r="AP7" s="147"/>
@@ -29408,55 +29291,55 @@
       <c r="BX7" s="145"/>
     </row>
     <row r="8" spans="1:76" s="146" customFormat="1" ht="26" customHeight="1">
-      <c r="A8" s="315"/>
-      <c r="B8" s="316"/>
-      <c r="C8" s="319" t="s">
+      <c r="A8" s="343"/>
+      <c r="B8" s="344"/>
+      <c r="C8" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="320"/>
-      <c r="E8" s="320"/>
-      <c r="F8" s="320"/>
-      <c r="G8" s="320"/>
-      <c r="H8" s="320"/>
-      <c r="I8" s="321"/>
-      <c r="J8" s="322" t="s">
+      <c r="D8" s="325"/>
+      <c r="E8" s="325"/>
+      <c r="F8" s="325"/>
+      <c r="G8" s="325"/>
+      <c r="H8" s="325"/>
+      <c r="I8" s="326"/>
+      <c r="J8" s="315" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="322"/>
-      <c r="L8" s="322"/>
-      <c r="M8" s="322"/>
-      <c r="N8" s="322"/>
-      <c r="O8" s="322"/>
-      <c r="P8" s="323" t="s">
+      <c r="K8" s="315"/>
+      <c r="L8" s="315"/>
+      <c r="M8" s="315"/>
+      <c r="N8" s="315"/>
+      <c r="O8" s="315"/>
+      <c r="P8" s="316" t="s">
         <v>85</v>
       </c>
-      <c r="Q8" s="323"/>
-      <c r="R8" s="323"/>
-      <c r="S8" s="323"/>
-      <c r="T8" s="323"/>
-      <c r="U8" s="333" t="s">
+      <c r="Q8" s="316"/>
+      <c r="R8" s="316"/>
+      <c r="S8" s="316"/>
+      <c r="T8" s="316"/>
+      <c r="U8" s="322" t="s">
         <v>34</v>
       </c>
-      <c r="V8" s="333"/>
-      <c r="W8" s="333"/>
-      <c r="X8" s="325" t="s">
+      <c r="V8" s="322"/>
+      <c r="W8" s="322"/>
+      <c r="X8" s="318" t="s">
         <v>151</v>
       </c>
-      <c r="Y8" s="326"/>
-      <c r="Z8" s="326"/>
-      <c r="AA8" s="326"/>
-      <c r="AB8" s="326"/>
-      <c r="AC8" s="326"/>
-      <c r="AD8" s="326"/>
-      <c r="AE8" s="327"/>
-      <c r="AF8" s="317"/>
-      <c r="AG8" s="334"/>
-      <c r="AH8" s="334"/>
-      <c r="AI8" s="334"/>
-      <c r="AJ8" s="334"/>
-      <c r="AK8" s="334"/>
-      <c r="AL8" s="334"/>
-      <c r="AM8" s="334"/>
+      <c r="Y8" s="319"/>
+      <c r="Z8" s="319"/>
+      <c r="AA8" s="319"/>
+      <c r="AB8" s="319"/>
+      <c r="AC8" s="319"/>
+      <c r="AD8" s="319"/>
+      <c r="AE8" s="320"/>
+      <c r="AF8" s="323"/>
+      <c r="AG8" s="328"/>
+      <c r="AH8" s="328"/>
+      <c r="AI8" s="328"/>
+      <c r="AJ8" s="328"/>
+      <c r="AK8" s="328"/>
+      <c r="AL8" s="328"/>
+      <c r="AM8" s="328"/>
       <c r="AN8" s="147"/>
       <c r="AO8" s="147"/>
       <c r="AP8" s="147"/>
@@ -29496,55 +29379,55 @@
       <c r="BX8" s="145"/>
     </row>
     <row r="9" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A9" s="313"/>
-      <c r="B9" s="314"/>
-      <c r="C9" s="319" t="s">
+      <c r="A9" s="341"/>
+      <c r="B9" s="342"/>
+      <c r="C9" s="324" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="320"/>
-      <c r="E9" s="320"/>
-      <c r="F9" s="320"/>
-      <c r="G9" s="320"/>
-      <c r="H9" s="320"/>
-      <c r="I9" s="321"/>
-      <c r="J9" s="322" t="s">
+      <c r="D9" s="325"/>
+      <c r="E9" s="325"/>
+      <c r="F9" s="325"/>
+      <c r="G9" s="325"/>
+      <c r="H9" s="325"/>
+      <c r="I9" s="326"/>
+      <c r="J9" s="315" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="322"/>
-      <c r="L9" s="322"/>
-      <c r="M9" s="322"/>
-      <c r="N9" s="322"/>
-      <c r="O9" s="322"/>
-      <c r="P9" s="323" t="s">
+      <c r="K9" s="315"/>
+      <c r="L9" s="315"/>
+      <c r="M9" s="315"/>
+      <c r="N9" s="315"/>
+      <c r="O9" s="315"/>
+      <c r="P9" s="316" t="s">
         <v>87</v>
       </c>
-      <c r="Q9" s="323"/>
-      <c r="R9" s="323"/>
-      <c r="S9" s="323"/>
-      <c r="T9" s="323"/>
-      <c r="U9" s="335">
+      <c r="Q9" s="316"/>
+      <c r="R9" s="316"/>
+      <c r="S9" s="316"/>
+      <c r="T9" s="316"/>
+      <c r="U9" s="329">
         <v>3000</v>
       </c>
-      <c r="V9" s="335"/>
-      <c r="W9" s="335"/>
-      <c r="X9" s="325" t="s">
+      <c r="V9" s="329"/>
+      <c r="W9" s="329"/>
+      <c r="X9" s="318" t="s">
         <v>152</v>
       </c>
-      <c r="Y9" s="326"/>
-      <c r="Z9" s="326"/>
-      <c r="AA9" s="326"/>
-      <c r="AB9" s="326"/>
-      <c r="AC9" s="326"/>
-      <c r="AD9" s="326"/>
-      <c r="AE9" s="327"/>
-      <c r="AF9" s="334"/>
-      <c r="AG9" s="334"/>
-      <c r="AH9" s="334"/>
-      <c r="AI9" s="334"/>
-      <c r="AJ9" s="334"/>
-      <c r="AK9" s="334"/>
-      <c r="AL9" s="334"/>
-      <c r="AM9" s="334"/>
+      <c r="Y9" s="319"/>
+      <c r="Z9" s="319"/>
+      <c r="AA9" s="319"/>
+      <c r="AB9" s="319"/>
+      <c r="AC9" s="319"/>
+      <c r="AD9" s="319"/>
+      <c r="AE9" s="320"/>
+      <c r="AF9" s="328"/>
+      <c r="AG9" s="328"/>
+      <c r="AH9" s="328"/>
+      <c r="AI9" s="328"/>
+      <c r="AJ9" s="328"/>
+      <c r="AK9" s="328"/>
+      <c r="AL9" s="328"/>
+      <c r="AM9" s="328"/>
       <c r="AN9" s="147"/>
       <c r="AO9" s="147"/>
       <c r="AP9" s="147"/>
@@ -29584,19 +29467,19 @@
       <c r="BX9" s="145"/>
     </row>
     <row r="10" spans="1:76" ht="81" customHeight="1">
-      <c r="A10" s="317">
+      <c r="A10" s="323">
         <v>4</v>
       </c>
-      <c r="B10" s="317"/>
-      <c r="C10" s="319" t="s">
+      <c r="B10" s="323"/>
+      <c r="C10" s="324" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="320"/>
-      <c r="E10" s="320"/>
-      <c r="F10" s="320"/>
-      <c r="G10" s="320"/>
-      <c r="H10" s="320"/>
-      <c r="I10" s="321"/>
+      <c r="D10" s="325"/>
+      <c r="E10" s="325"/>
+      <c r="F10" s="325"/>
+      <c r="G10" s="325"/>
+      <c r="H10" s="325"/>
+      <c r="I10" s="326"/>
       <c r="J10" s="330" t="s">
         <v>89</v>
       </c>
@@ -29605,38 +29488,38 @@
       <c r="M10" s="331"/>
       <c r="N10" s="331"/>
       <c r="O10" s="332"/>
-      <c r="P10" s="323" t="s">
+      <c r="P10" s="316" t="s">
         <v>90</v>
       </c>
-      <c r="Q10" s="323"/>
-      <c r="R10" s="323"/>
-      <c r="S10" s="323"/>
-      <c r="T10" s="323"/>
-      <c r="U10" s="333" t="s">
+      <c r="Q10" s="316"/>
+      <c r="R10" s="316"/>
+      <c r="S10" s="316"/>
+      <c r="T10" s="316"/>
+      <c r="U10" s="322" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="333"/>
-      <c r="W10" s="333"/>
-      <c r="X10" s="325" t="s">
+      <c r="V10" s="322"/>
+      <c r="W10" s="322"/>
+      <c r="X10" s="318" t="s">
         <v>153</v>
       </c>
-      <c r="Y10" s="326"/>
-      <c r="Z10" s="326"/>
-      <c r="AA10" s="326"/>
-      <c r="AB10" s="326"/>
-      <c r="AC10" s="326"/>
-      <c r="AD10" s="326"/>
-      <c r="AE10" s="327"/>
-      <c r="AF10" s="317" t="s">
+      <c r="Y10" s="319"/>
+      <c r="Z10" s="319"/>
+      <c r="AA10" s="319"/>
+      <c r="AB10" s="319"/>
+      <c r="AC10" s="319"/>
+      <c r="AD10" s="319"/>
+      <c r="AE10" s="320"/>
+      <c r="AF10" s="323" t="s">
         <v>91</v>
       </c>
-      <c r="AG10" s="317"/>
-      <c r="AH10" s="317"/>
-      <c r="AI10" s="317"/>
-      <c r="AJ10" s="317"/>
-      <c r="AK10" s="317"/>
-      <c r="AL10" s="317"/>
-      <c r="AM10" s="317"/>
+      <c r="AG10" s="323"/>
+      <c r="AH10" s="323"/>
+      <c r="AI10" s="323"/>
+      <c r="AJ10" s="323"/>
+      <c r="AK10" s="323"/>
+      <c r="AL10" s="323"/>
+      <c r="AM10" s="323"/>
       <c r="AN10" s="143"/>
       <c r="AO10" s="143"/>
       <c r="AP10" s="143"/>
@@ -29676,59 +29559,59 @@
       <c r="BX10" s="143"/>
     </row>
     <row r="11" spans="1:76" ht="27.75" customHeight="1">
-      <c r="A11" s="328" t="s">
+      <c r="A11" s="346" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="329"/>
-      <c r="C11" s="319" t="s">
+      <c r="B11" s="347"/>
+      <c r="C11" s="324" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="320"/>
-      <c r="E11" s="320"/>
-      <c r="F11" s="320"/>
-      <c r="G11" s="320"/>
-      <c r="H11" s="320"/>
-      <c r="I11" s="321"/>
-      <c r="J11" s="322" t="s">
+      <c r="D11" s="325"/>
+      <c r="E11" s="325"/>
+      <c r="F11" s="325"/>
+      <c r="G11" s="325"/>
+      <c r="H11" s="325"/>
+      <c r="I11" s="326"/>
+      <c r="J11" s="315" t="s">
         <v>144</v>
       </c>
-      <c r="K11" s="322"/>
-      <c r="L11" s="322"/>
-      <c r="M11" s="322"/>
-      <c r="N11" s="322"/>
-      <c r="O11" s="322"/>
-      <c r="P11" s="323" t="s">
+      <c r="K11" s="315"/>
+      <c r="L11" s="315"/>
+      <c r="M11" s="315"/>
+      <c r="N11" s="315"/>
+      <c r="O11" s="315"/>
+      <c r="P11" s="316" t="s">
         <v>145</v>
       </c>
-      <c r="Q11" s="323"/>
-      <c r="R11" s="323"/>
-      <c r="S11" s="323"/>
-      <c r="T11" s="323"/>
-      <c r="U11" s="324">
+      <c r="Q11" s="316"/>
+      <c r="R11" s="316"/>
+      <c r="S11" s="316"/>
+      <c r="T11" s="316"/>
+      <c r="U11" s="327">
         <v>100</v>
       </c>
-      <c r="V11" s="324"/>
-      <c r="W11" s="324"/>
-      <c r="X11" s="325" t="s">
+      <c r="V11" s="327"/>
+      <c r="W11" s="327"/>
+      <c r="X11" s="318" t="s">
         <v>156</v>
       </c>
-      <c r="Y11" s="326"/>
-      <c r="Z11" s="326"/>
-      <c r="AA11" s="326"/>
-      <c r="AB11" s="326"/>
-      <c r="AC11" s="326"/>
-      <c r="AD11" s="326"/>
-      <c r="AE11" s="327"/>
-      <c r="AF11" s="317" t="s">
+      <c r="Y11" s="319"/>
+      <c r="Z11" s="319"/>
+      <c r="AA11" s="319"/>
+      <c r="AB11" s="319"/>
+      <c r="AC11" s="319"/>
+      <c r="AD11" s="319"/>
+      <c r="AE11" s="320"/>
+      <c r="AF11" s="323" t="s">
         <v>154</v>
       </c>
-      <c r="AG11" s="317"/>
-      <c r="AH11" s="317"/>
-      <c r="AI11" s="317"/>
-      <c r="AJ11" s="317"/>
-      <c r="AK11" s="317"/>
-      <c r="AL11" s="317"/>
-      <c r="AM11" s="317"/>
+      <c r="AG11" s="323"/>
+      <c r="AH11" s="323"/>
+      <c r="AI11" s="323"/>
+      <c r="AJ11" s="323"/>
+      <c r="AK11" s="323"/>
+      <c r="AL11" s="323"/>
+      <c r="AM11" s="323"/>
       <c r="AN11" s="143"/>
       <c r="AO11" s="143"/>
       <c r="AP11" s="143"/>
@@ -29768,45 +29651,45 @@
       <c r="BX11" s="143"/>
     </row>
     <row r="12" spans="1:76" ht="27.75" customHeight="1">
-      <c r="A12" s="318"/>
-      <c r="B12" s="317"/>
-      <c r="C12" s="319"/>
-      <c r="D12" s="320"/>
-      <c r="E12" s="320"/>
-      <c r="F12" s="320"/>
-      <c r="G12" s="320"/>
-      <c r="H12" s="320"/>
-      <c r="I12" s="321"/>
-      <c r="J12" s="322"/>
-      <c r="K12" s="322"/>
-      <c r="L12" s="322"/>
-      <c r="M12" s="322"/>
-      <c r="N12" s="322"/>
-      <c r="O12" s="322"/>
-      <c r="P12" s="323"/>
-      <c r="Q12" s="323"/>
-      <c r="R12" s="323"/>
-      <c r="S12" s="323"/>
-      <c r="T12" s="323"/>
-      <c r="U12" s="324"/>
-      <c r="V12" s="324"/>
-      <c r="W12" s="324"/>
-      <c r="X12" s="325"/>
-      <c r="Y12" s="326"/>
-      <c r="Z12" s="326"/>
-      <c r="AA12" s="326"/>
-      <c r="AB12" s="326"/>
-      <c r="AC12" s="326"/>
-      <c r="AD12" s="326"/>
-      <c r="AE12" s="327"/>
-      <c r="AF12" s="317"/>
-      <c r="AG12" s="317"/>
-      <c r="AH12" s="317"/>
-      <c r="AI12" s="317"/>
-      <c r="AJ12" s="317"/>
-      <c r="AK12" s="317"/>
-      <c r="AL12" s="317"/>
-      <c r="AM12" s="317"/>
+      <c r="A12" s="345"/>
+      <c r="B12" s="323"/>
+      <c r="C12" s="324"/>
+      <c r="D12" s="325"/>
+      <c r="E12" s="325"/>
+      <c r="F12" s="325"/>
+      <c r="G12" s="325"/>
+      <c r="H12" s="325"/>
+      <c r="I12" s="326"/>
+      <c r="J12" s="315"/>
+      <c r="K12" s="315"/>
+      <c r="L12" s="315"/>
+      <c r="M12" s="315"/>
+      <c r="N12" s="315"/>
+      <c r="O12" s="315"/>
+      <c r="P12" s="316"/>
+      <c r="Q12" s="316"/>
+      <c r="R12" s="316"/>
+      <c r="S12" s="316"/>
+      <c r="T12" s="316"/>
+      <c r="U12" s="327"/>
+      <c r="V12" s="327"/>
+      <c r="W12" s="327"/>
+      <c r="X12" s="318"/>
+      <c r="Y12" s="319"/>
+      <c r="Z12" s="319"/>
+      <c r="AA12" s="319"/>
+      <c r="AB12" s="319"/>
+      <c r="AC12" s="319"/>
+      <c r="AD12" s="319"/>
+      <c r="AE12" s="320"/>
+      <c r="AF12" s="323"/>
+      <c r="AG12" s="323"/>
+      <c r="AH12" s="323"/>
+      <c r="AI12" s="323"/>
+      <c r="AJ12" s="323"/>
+      <c r="AK12" s="323"/>
+      <c r="AL12" s="323"/>
+      <c r="AM12" s="323"/>
       <c r="AN12" s="143"/>
       <c r="AO12" s="143"/>
       <c r="AP12" s="143"/>
@@ -30028,56 +29911,6 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="AF2:AM3"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:B3"/>
-    <mergeCell ref="C2:I3"/>
-    <mergeCell ref="J2:O3"/>
-    <mergeCell ref="P2:W3"/>
-    <mergeCell ref="X2:AE3"/>
-    <mergeCell ref="AF4:AM4"/>
-    <mergeCell ref="J5:O5"/>
-    <mergeCell ref="P5:T5"/>
-    <mergeCell ref="U5:W5"/>
-    <mergeCell ref="X5:AE5"/>
-    <mergeCell ref="AF5:AM5"/>
-    <mergeCell ref="J4:O4"/>
-    <mergeCell ref="P4:T4"/>
-    <mergeCell ref="U4:W4"/>
-    <mergeCell ref="X4:AE4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="J6:O6"/>
-    <mergeCell ref="P6:T6"/>
-    <mergeCell ref="U6:W6"/>
-    <mergeCell ref="AF8:AM8"/>
-    <mergeCell ref="AF6:AM6"/>
-    <mergeCell ref="C7:I7"/>
-    <mergeCell ref="J7:O7"/>
-    <mergeCell ref="P7:T7"/>
-    <mergeCell ref="U7:W7"/>
-    <mergeCell ref="AF7:AM7"/>
-    <mergeCell ref="X7:AE7"/>
-    <mergeCell ref="X6:AE6"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="J8:O8"/>
-    <mergeCell ref="P8:T8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="X8:AE8"/>
-    <mergeCell ref="X10:AE10"/>
-    <mergeCell ref="AF9:AM9"/>
-    <mergeCell ref="X9:AE9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:O9"/>
-    <mergeCell ref="P9:T9"/>
-    <mergeCell ref="U9:W9"/>
-    <mergeCell ref="P11:T11"/>
-    <mergeCell ref="U11:W11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="J10:O10"/>
-    <mergeCell ref="P10:T10"/>
-    <mergeCell ref="U10:W10"/>
     <mergeCell ref="C4:I5"/>
     <mergeCell ref="A4:B5"/>
     <mergeCell ref="A7:B9"/>
@@ -30094,6 +29927,56 @@
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="C11:I11"/>
     <mergeCell ref="J11:O11"/>
+    <mergeCell ref="P11:T11"/>
+    <mergeCell ref="U11:W11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="J10:O10"/>
+    <mergeCell ref="P10:T10"/>
+    <mergeCell ref="U10:W10"/>
+    <mergeCell ref="X10:AE10"/>
+    <mergeCell ref="AF9:AM9"/>
+    <mergeCell ref="X9:AE9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:O9"/>
+    <mergeCell ref="P9:T9"/>
+    <mergeCell ref="U9:W9"/>
+    <mergeCell ref="AF8:AM8"/>
+    <mergeCell ref="AF6:AM6"/>
+    <mergeCell ref="C7:I7"/>
+    <mergeCell ref="J7:O7"/>
+    <mergeCell ref="P7:T7"/>
+    <mergeCell ref="U7:W7"/>
+    <mergeCell ref="AF7:AM7"/>
+    <mergeCell ref="X7:AE7"/>
+    <mergeCell ref="X6:AE6"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="P8:T8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="X8:AE8"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="J6:O6"/>
+    <mergeCell ref="P6:T6"/>
+    <mergeCell ref="U6:W6"/>
+    <mergeCell ref="AF4:AM4"/>
+    <mergeCell ref="J5:O5"/>
+    <mergeCell ref="P5:T5"/>
+    <mergeCell ref="U5:W5"/>
+    <mergeCell ref="X5:AE5"/>
+    <mergeCell ref="AF5:AM5"/>
+    <mergeCell ref="J4:O4"/>
+    <mergeCell ref="P4:T4"/>
+    <mergeCell ref="U4:W4"/>
+    <mergeCell ref="X4:AE4"/>
+    <mergeCell ref="AF2:AM3"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:B3"/>
+    <mergeCell ref="C2:I3"/>
+    <mergeCell ref="J2:O3"/>
+    <mergeCell ref="P2:W3"/>
+    <mergeCell ref="X2:AE3"/>
   </mergeCells>
   <phoneticPr fontId="56"/>
   <dataValidations count="1">

--- a/20_設計書/化学物質データ申請画面.xlsx
+++ b/20_設計書/化学物質データ申請画面.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744A54B1-3BF6-4F52-AEB8-FA6E1D217B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27BB215-9CC5-421D-9A65-1BE89730FC92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30285" yWindow="1515" windowWidth="20595" windowHeight="12375" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -86,8 +86,8 @@
     <definedName name="ooo" localSheetId="4" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ooo" localSheetId="5" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
     <definedName name="ooo" hidden="1">{"'Sheet1'!$A$3:$I$11"}</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'化学物質データ申請画面(日英併記)'!$A$1:$BC$68</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">画面項目!$A$1:$BT$17</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'化学物質データ申請画面(日英併記)'!$A$1:$BC$69</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">画面項目!$A$1:$BT$19</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">処理詳細!$A$1:$CH$35</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">入力チェック!$A$1:$AN$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">表紙!$A$1:$I$36</definedName>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="165">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -1582,6 +1582,103 @@
     </rPh>
     <phoneticPr fontId="56"/>
   </si>
+  <si>
+    <t>r1.3</t>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>「化学物質データ画面(日英併記)」シート、「画面項目シート」</t>
+    <rPh sb="22" eb="26">
+      <t>ガメンコウモク</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>レビュー指摘により以下を修正
+・共通ヘッダーを追加</t>
+    <rPh sb="4" eb="6">
+      <t>シテキ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="14"/>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="56"/>
+  </si>
+  <si>
+    <t>共通ヘッダー</t>
+    <rPh sb="0" eb="2">
+      <t>キョウツウ</t>
+    </rPh>
+    <phoneticPr fontId="56"/>
+  </si>
+  <si>
+    <t>0.1</t>
+    <phoneticPr fontId="56"/>
+  </si>
+  <si>
+    <t>ヒロセ電機ロゴ</t>
+    <rPh sb="3" eb="5">
+      <t>デンキ</t>
+    </rPh>
+    <phoneticPr fontId="56"/>
+  </si>
+  <si>
+    <t>「化学物質データ画面」～「化学物質データ申請完了画面」共通
+ロゴを押下すると「化学物質データ画面」に遷移する。</t>
+    <rPh sb="1" eb="3">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ブッシツ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>カガク</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ブッシツ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>カンリョウ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>キョウツウ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="39" eb="43">
+      <t>カガクブッシツ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="50" eb="52">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="56"/>
+  </si>
 </sst>
 </file>
 
@@ -3408,7 +3505,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="348">
+  <cellXfs count="356">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4124,6 +4221,66 @@
     <xf numFmtId="0" fontId="22" fillId="10" borderId="17" xfId="46" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="63" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="26" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="27" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="28" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="45" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -4153,22 +4310,7 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="184" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="10" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="17" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -4182,21 +4324,6 @@
     <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="2" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="25" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="10" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="63" fillId="0" borderId="25" xfId="45" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="29" xfId="185" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5158,13 +5285,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>80433</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>82550</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
       <xdr:colOff>100311</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>99172</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5223,13 +5350,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
       <xdr:colOff>57978</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>153147</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5288,13 +5415,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>38</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5361,13 +5488,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>39</xdr:row>
+      <xdr:row>40</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5434,13 +5561,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>41</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5507,13 +5634,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>43</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5580,13 +5707,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>45</xdr:row>
+      <xdr:row>46</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5653,13 +5780,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>47</xdr:row>
+      <xdr:row>48</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5726,13 +5853,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>144552</xdr:colOff>
-      <xdr:row>49</xdr:row>
+      <xdr:row>50</xdr:row>
       <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5799,13 +5926,13 @@
     <xdr:from>
       <xdr:col>18</xdr:col>
       <xdr:colOff>15875</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>16329</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>131803</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>97918</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -5903,13 +6030,13 @@
     <xdr:from>
       <xdr:col>25</xdr:col>
       <xdr:colOff>48372</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>31</xdr:col>
       <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>95251</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6005,13 +6132,13 @@
     <xdr:from>
       <xdr:col>17</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>37</xdr:col>
       <xdr:colOff>48680</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>11906</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -6027,8 +6154,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="3103563" y="3833813"/>
-          <a:ext cx="3699930" cy="1440656"/>
+          <a:off x="3036094" y="4345781"/>
+          <a:ext cx="3617380" cy="1508919"/>
           <a:chOff x="3649663" y="3595688"/>
           <a:chExt cx="3620555" cy="1505743"/>
         </a:xfrm>
@@ -6121,16 +6248,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>178593</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>169332</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>125412</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>15081</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>246062</xdr:rowOff>
+      <xdr:colOff>154781</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6145,8 +6272,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1977760" y="857249"/>
-          <a:ext cx="376238" cy="246063"/>
+          <a:off x="2089943" y="1332971"/>
+          <a:ext cx="386557" cy="262467"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6209,13 +6336,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>130176</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>113771</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>95251</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>258234</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6308,13 +6435,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>161397</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>98425</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>52653</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>68526</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6394,13 +6521,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>71438</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>55826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>157691</xdr:colOff>
-      <xdr:row>18</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>14551</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6480,13 +6607,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>38630</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>22</xdr:row>
       <xdr:rowOff>151076</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>109008</xdr:colOff>
-      <xdr:row>23</xdr:row>
+      <xdr:row>24</xdr:row>
       <xdr:rowOff>106626</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6566,13 +6693,13 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>119064</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>47360</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
       <xdr:colOff>28576</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>158485</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6652,13 +6779,13 @@
     <xdr:from>
       <xdr:col>20</xdr:col>
       <xdr:colOff>107422</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>143139</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>10584</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>93926</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6738,13 +6865,13 @@
     <xdr:from>
       <xdr:col>27</xdr:col>
       <xdr:colOff>61120</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>146314</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
       <xdr:colOff>141024</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>93926</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6824,13 +6951,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>74083</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>105834</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>160338</xdr:colOff>
-      <xdr:row>54</xdr:row>
+      <xdr:row>55</xdr:row>
       <xdr:rowOff>62972</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -6910,13 +7037,13 @@
     <xdr:from>
       <xdr:col>39</xdr:col>
       <xdr:colOff>178858</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>116417</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>44</xdr:col>
       <xdr:colOff>83608</xdr:colOff>
-      <xdr:row>55</xdr:row>
+      <xdr:row>56</xdr:row>
       <xdr:rowOff>60324</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
@@ -6932,8 +7059,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="7298796" y="8712730"/>
-          <a:ext cx="817562" cy="261407"/>
+          <a:off x="7147189" y="9462823"/>
+          <a:ext cx="797719" cy="277282"/>
           <a:chOff x="13567834" y="4773083"/>
           <a:chExt cx="898525" cy="275168"/>
         </a:xfrm>
@@ -7153,13 +7280,13 @@
     <xdr:from>
       <xdr:col>37</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
-      <xdr:row>52</xdr:row>
+      <xdr:row>53</xdr:row>
       <xdr:rowOff>25401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>39</xdr:col>
       <xdr:colOff>137584</xdr:colOff>
-      <xdr:row>53</xdr:row>
+      <xdr:row>54</xdr:row>
       <xdr:rowOff>92076</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7221,6 +7348,210 @@
               <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
             </a:rPr>
             <a:t>2.6</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>62006</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>39614</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="34" name="図 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5D984BD2-BB2B-454A-B6E7-D1678D5C8E26}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="178594" y="881063"/>
+          <a:ext cx="3633881" cy="444426"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>64295</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>52</xdr:col>
+      <xdr:colOff>11907</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>48653</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="正方形/長方形 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99B4D9A7-EF54-47BD-8CF3-C92801E47A70}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3636170" y="890588"/>
+          <a:ext cx="5662612" cy="443940"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" lIns="36000" tIns="36000" rIns="36000" bIns="36000" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l">
+            <a:lnSpc>
+              <a:spcPts val="900"/>
+            </a:lnSpc>
+          </a:pPr>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="800">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>98424</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>26458</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>137318</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>282575</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="正方形/長方形 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE220CF4-AD21-48C2-A069-6777A0EBAC69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1348580" y="907521"/>
+          <a:ext cx="396082" cy="256117"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FFFF66"/>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:sysClr val="windowText" lastClr="000000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>0.1</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
             <a:solidFill>
@@ -7609,7 +7940,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="179" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 05月 20日 r1.2</v>
+        <v>2026年 05月 20日 r1.3</v>
       </c>
       <c r="C22" s="180"/>
       <c r="D22" s="180"/>
@@ -8753,7 +9084,7 @@
       <c r="AS3" s="183"/>
       <c r="AT3" s="184" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>r1.2</v>
+        <v>r1.3</v>
       </c>
       <c r="AU3" s="184"/>
       <c r="AV3" s="184"/>
@@ -9083,24 +9414,30 @@
       <c r="AZ9" s="215"/>
       <c r="BA9" s="215"/>
     </row>
-    <row r="10" spans="1:53">
-      <c r="A10" s="212"/>
-      <c r="B10" s="212"/>
-      <c r="C10" s="215"/>
-      <c r="D10" s="215"/>
-      <c r="E10" s="215"/>
-      <c r="F10" s="215"/>
-      <c r="G10" s="215"/>
-      <c r="H10" s="215"/>
-      <c r="I10" s="215"/>
-      <c r="J10" s="215"/>
-      <c r="K10" s="215"/>
-      <c r="L10" s="215"/>
-      <c r="M10" s="215"/>
-      <c r="N10" s="215"/>
-      <c r="O10" s="215"/>
-      <c r="P10" s="215"/>
-      <c r="Q10" s="216"/>
+    <row r="10" spans="1:53" ht="27.5" customHeight="1">
+      <c r="A10" s="210" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="211"/>
+      <c r="C10" s="216" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="216"/>
+      <c r="E10" s="216"/>
+      <c r="F10" s="216"/>
+      <c r="G10" s="216"/>
+      <c r="H10" s="216"/>
+      <c r="I10" s="216"/>
+      <c r="J10" s="216"/>
+      <c r="K10" s="216"/>
+      <c r="L10" s="216"/>
+      <c r="M10" s="216"/>
+      <c r="N10" s="216"/>
+      <c r="O10" s="216"/>
+      <c r="P10" s="216"/>
+      <c r="Q10" s="216" t="s">
+        <v>159</v>
+      </c>
       <c r="R10" s="215"/>
       <c r="S10" s="215"/>
       <c r="T10" s="215"/>
@@ -9121,11 +9458,15 @@
       <c r="AI10" s="215"/>
       <c r="AJ10" s="215"/>
       <c r="AK10" s="215"/>
-      <c r="AL10" s="222"/>
+      <c r="AL10" s="222">
+        <v>46176</v>
+      </c>
       <c r="AM10" s="212"/>
       <c r="AN10" s="212"/>
       <c r="AO10" s="212"/>
-      <c r="AP10" s="215"/>
+      <c r="AP10" s="215" t="s">
+        <v>97</v>
+      </c>
       <c r="AQ10" s="215"/>
       <c r="AR10" s="215"/>
       <c r="AS10" s="215"/>
@@ -10701,7 +11042,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D71D2C-D985-4695-8A8E-E0DDD89A760E}">
-  <dimension ref="A1:DX214"/>
+  <dimension ref="A1:DX215"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="18" width="2.6328125" style="25" customWidth="1"/>
@@ -10860,7 +11201,7 @@
       <c r="AU2" s="183"/>
       <c r="AV2" s="186">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46162</v>
+        <v>46176</v>
       </c>
       <c r="AW2" s="184"/>
       <c r="AX2" s="184"/>
@@ -10938,7 +11279,7 @@
       <c r="AU3" s="183"/>
       <c r="AV3" s="184" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>r1.2</v>
+        <v>r1.3</v>
       </c>
       <c r="AW3" s="184"/>
       <c r="AX3" s="184"/>
@@ -11172,350 +11513,349 @@
       <c r="BC6" s="26"/>
       <c r="BD6" s="24"/>
     </row>
-    <row r="7" spans="1:75" ht="21" customHeight="1">
+    <row r="7" spans="1:75" s="80" customFormat="1" ht="31.5" customHeight="1">
       <c r="A7" s="36"/>
-      <c r="B7" s="74"/>
-      <c r="C7" s="79" t="s">
-        <v>50</v>
-      </c>
-      <c r="D7" s="75"/>
-      <c r="E7" s="76"/>
-      <c r="F7" s="76"/>
-      <c r="G7" s="76"/>
-      <c r="H7" s="70"/>
-      <c r="I7" s="70"/>
-      <c r="J7" s="136"/>
-      <c r="K7" s="136"/>
-      <c r="L7" s="136"/>
-      <c r="M7" s="136"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="70"/>
-      <c r="R7" s="70"/>
-      <c r="S7" s="70"/>
-      <c r="T7" s="71"/>
-      <c r="U7" s="71"/>
-      <c r="V7" s="71"/>
-      <c r="W7" s="71"/>
-      <c r="X7" s="71"/>
-      <c r="Y7" s="72"/>
-      <c r="Z7" s="71"/>
-      <c r="AA7" s="70"/>
-      <c r="AB7" s="72"/>
-      <c r="AC7" s="71"/>
-      <c r="AD7" s="70"/>
-      <c r="AE7" s="72"/>
-      <c r="AF7" s="70"/>
-      <c r="AG7" s="70"/>
-      <c r="AH7" s="72"/>
-      <c r="AI7" s="70"/>
-      <c r="AJ7" s="70"/>
-      <c r="AK7" s="77"/>
-      <c r="AL7" s="70"/>
-      <c r="AM7" s="70"/>
-      <c r="AN7" s="70"/>
-      <c r="AO7" s="70"/>
-      <c r="AP7" s="70"/>
-      <c r="AQ7" s="70"/>
-      <c r="AR7" s="70"/>
-      <c r="AS7" s="70"/>
-      <c r="AT7" s="76"/>
-      <c r="AU7" s="76"/>
-      <c r="AV7" s="76"/>
-      <c r="AW7" s="76"/>
-      <c r="AX7" s="76"/>
-      <c r="AY7" s="76"/>
-      <c r="AZ7" s="78"/>
+      <c r="B7" s="55"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="67"/>
+      <c r="P7" s="67"/>
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="67"/>
+      <c r="X7" s="67"/>
+      <c r="Y7" s="67"/>
+      <c r="Z7" s="67"/>
+      <c r="AA7" s="67"/>
+      <c r="AB7" s="67"/>
+      <c r="AC7" s="67"/>
+      <c r="AD7" s="67"/>
+      <c r="AE7" s="67"/>
+      <c r="AF7" s="67"/>
+      <c r="AG7" s="67"/>
+      <c r="AH7" s="67"/>
+      <c r="AI7" s="67"/>
+      <c r="AJ7" s="67"/>
+      <c r="AK7" s="67"/>
+      <c r="AL7" s="67"/>
+      <c r="AM7" s="67"/>
+      <c r="AN7" s="67"/>
+      <c r="AO7" s="67"/>
+      <c r="AP7" s="67"/>
+      <c r="AQ7" s="67"/>
+      <c r="AR7" s="67"/>
+      <c r="AS7" s="68"/>
+      <c r="AT7" s="61"/>
+      <c r="AU7" s="54"/>
+      <c r="AV7" s="58"/>
+      <c r="AW7" s="58"/>
+      <c r="AX7" s="58"/>
+      <c r="AY7" s="54"/>
+      <c r="AZ7" s="59"/>
       <c r="BA7" s="59"/>
       <c r="BB7" s="49"/>
       <c r="BC7" s="50"/>
-      <c r="BD7" s="34"/>
-    </row>
-    <row r="8" spans="1:75" ht="12.5" customHeight="1">
+      <c r="BD7" s="35"/>
+      <c r="BE7" s="81"/>
+      <c r="BF7" s="81"/>
+      <c r="BG7" s="81"/>
+      <c r="BH7" s="84"/>
+      <c r="BI7" s="81"/>
+      <c r="BJ7" s="81"/>
+      <c r="BK7" s="81"/>
+      <c r="BL7" s="81"/>
+      <c r="BM7" s="81"/>
+      <c r="BN7" s="81"/>
+      <c r="BO7" s="81"/>
+      <c r="BP7" s="81"/>
+      <c r="BQ7" s="81"/>
+      <c r="BR7" s="81"/>
+      <c r="BS7" s="81"/>
+      <c r="BT7" s="81"/>
+    </row>
+    <row r="8" spans="1:75" ht="21" customHeight="1">
       <c r="A8" s="36"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="63"/>
-      <c r="D8" s="64"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-      <c r="J8" s="67"/>
-      <c r="K8" s="67"/>
-      <c r="L8" s="67"/>
-      <c r="M8" s="67"/>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="67"/>
-      <c r="V8" s="67"/>
-      <c r="W8" s="67"/>
-      <c r="X8" s="67"/>
-      <c r="Y8" s="67"/>
-      <c r="Z8" s="67"/>
-      <c r="AA8" s="67"/>
-      <c r="AB8" s="67"/>
-      <c r="AC8" s="67"/>
-      <c r="AD8" s="67"/>
-      <c r="AE8" s="67"/>
-      <c r="AF8" s="67"/>
-      <c r="AG8" s="67"/>
-      <c r="AH8" s="67"/>
-      <c r="AI8" s="67"/>
-      <c r="AJ8" s="67"/>
-      <c r="AK8" s="67"/>
-      <c r="AL8" s="67"/>
-      <c r="AM8" s="67"/>
-      <c r="AN8" s="67"/>
-      <c r="AO8" s="67"/>
-      <c r="AP8" s="67"/>
-      <c r="AQ8" s="67"/>
-      <c r="AR8" s="67"/>
-      <c r="AS8" s="69"/>
-      <c r="AT8" s="65"/>
-      <c r="AU8" s="65"/>
-      <c r="AV8" s="65"/>
-      <c r="AW8" s="65"/>
-      <c r="AX8" s="65"/>
-      <c r="AY8" s="65"/>
-      <c r="AZ8" s="59"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="79" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="75"/>
+      <c r="E8" s="76"/>
+      <c r="F8" s="76"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="70"/>
+      <c r="I8" s="70"/>
+      <c r="J8" s="136"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="136"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="72"/>
+      <c r="P8" s="73"/>
+      <c r="Q8" s="70"/>
+      <c r="R8" s="70"/>
+      <c r="S8" s="70"/>
+      <c r="T8" s="71"/>
+      <c r="U8" s="71"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="71"/>
+      <c r="X8" s="71"/>
+      <c r="Y8" s="72"/>
+      <c r="Z8" s="71"/>
+      <c r="AA8" s="70"/>
+      <c r="AB8" s="72"/>
+      <c r="AC8" s="71"/>
+      <c r="AD8" s="70"/>
+      <c r="AE8" s="72"/>
+      <c r="AF8" s="70"/>
+      <c r="AG8" s="70"/>
+      <c r="AH8" s="72"/>
+      <c r="AI8" s="70"/>
+      <c r="AJ8" s="70"/>
+      <c r="AK8" s="77"/>
+      <c r="AL8" s="70"/>
+      <c r="AM8" s="70"/>
+      <c r="AN8" s="70"/>
+      <c r="AO8" s="70"/>
+      <c r="AP8" s="70"/>
+      <c r="AQ8" s="70"/>
+      <c r="AR8" s="70"/>
+      <c r="AS8" s="70"/>
+      <c r="AT8" s="76"/>
+      <c r="AU8" s="76"/>
+      <c r="AV8" s="76"/>
+      <c r="AW8" s="76"/>
+      <c r="AX8" s="76"/>
+      <c r="AY8" s="76"/>
+      <c r="AZ8" s="78"/>
       <c r="BA8" s="59"/>
       <c r="BB8" s="49"/>
       <c r="BC8" s="50"/>
       <c r="BD8" s="34"/>
-      <c r="BE8" s="231" t="s">
+    </row>
+    <row r="9" spans="1:75" ht="12.5" customHeight="1">
+      <c r="A9" s="36"/>
+      <c r="B9" s="55"/>
+      <c r="C9" s="63"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+      <c r="K9" s="67"/>
+      <c r="L9" s="67"/>
+      <c r="M9" s="67"/>
+      <c r="N9" s="67"/>
+      <c r="O9" s="67"/>
+      <c r="P9" s="67"/>
+      <c r="Q9" s="67"/>
+      <c r="R9" s="67"/>
+      <c r="S9" s="67"/>
+      <c r="T9" s="67"/>
+      <c r="U9" s="67"/>
+      <c r="V9" s="67"/>
+      <c r="W9" s="67"/>
+      <c r="X9" s="67"/>
+      <c r="Y9" s="67"/>
+      <c r="Z9" s="67"/>
+      <c r="AA9" s="67"/>
+      <c r="AB9" s="67"/>
+      <c r="AC9" s="67"/>
+      <c r="AD9" s="67"/>
+      <c r="AE9" s="67"/>
+      <c r="AF9" s="67"/>
+      <c r="AG9" s="67"/>
+      <c r="AH9" s="67"/>
+      <c r="AI9" s="67"/>
+      <c r="AJ9" s="67"/>
+      <c r="AK9" s="67"/>
+      <c r="AL9" s="67"/>
+      <c r="AM9" s="67"/>
+      <c r="AN9" s="67"/>
+      <c r="AO9" s="67"/>
+      <c r="AP9" s="67"/>
+      <c r="AQ9" s="67"/>
+      <c r="AR9" s="67"/>
+      <c r="AS9" s="69"/>
+      <c r="AT9" s="65"/>
+      <c r="AU9" s="65"/>
+      <c r="AV9" s="65"/>
+      <c r="AW9" s="65"/>
+      <c r="AX9" s="65"/>
+      <c r="AY9" s="65"/>
+      <c r="AZ9" s="59"/>
+      <c r="BA9" s="59"/>
+      <c r="BB9" s="49"/>
+      <c r="BC9" s="50"/>
+      <c r="BD9" s="34"/>
+      <c r="BE9" s="231" t="s">
         <v>131</v>
       </c>
-      <c r="BF8" s="232"/>
-      <c r="BG8" s="232"/>
-      <c r="BH8" s="233"/>
-    </row>
-    <row r="9" spans="1:75" ht="24" customHeight="1">
-      <c r="A9" s="36"/>
-      <c r="B9" s="37"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="229" t="s">
+      <c r="BF9" s="232"/>
+      <c r="BG9" s="232"/>
+      <c r="BH9" s="233"/>
+    </row>
+    <row r="10" spans="1:75" ht="24" customHeight="1">
+      <c r="A10" s="36"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="38"/>
+      <c r="H10" s="229" t="s">
         <v>117</v>
       </c>
-      <c r="I9" s="229"/>
-      <c r="J9" s="229"/>
-      <c r="K9" s="229"/>
-      <c r="L9" s="229"/>
-      <c r="M9" s="229"/>
-      <c r="N9" s="229"/>
-      <c r="O9" s="229"/>
-      <c r="P9" s="229"/>
-      <c r="Q9" s="229"/>
-      <c r="R9" s="229"/>
-      <c r="S9" s="229"/>
-      <c r="T9" s="229"/>
-      <c r="U9" s="229"/>
-      <c r="V9" s="229"/>
-      <c r="W9" s="229"/>
-      <c r="X9" s="229"/>
-      <c r="Y9" s="229"/>
-      <c r="Z9" s="229"/>
-      <c r="AA9" s="229"/>
-      <c r="AB9" s="229"/>
-      <c r="AC9" s="229"/>
-      <c r="AD9" s="229"/>
-      <c r="AE9" s="229"/>
-      <c r="AF9" s="229"/>
-      <c r="AG9" s="229"/>
-      <c r="AH9" s="229"/>
-      <c r="AI9" s="229"/>
-      <c r="AJ9" s="229"/>
-      <c r="AK9" s="229"/>
-      <c r="AL9" s="229"/>
-      <c r="AM9" s="229"/>
-      <c r="AN9" s="229"/>
-      <c r="AO9" s="229"/>
-      <c r="AP9" s="229"/>
-      <c r="AQ9" s="229"/>
-      <c r="AR9" s="229"/>
-      <c r="AS9" s="229"/>
-      <c r="AT9" s="43"/>
-      <c r="AU9" s="41"/>
-      <c r="AV9" s="44"/>
-      <c r="AW9" s="44"/>
-      <c r="AX9" s="44"/>
-      <c r="AY9" s="38"/>
-      <c r="AZ9" s="39"/>
-      <c r="BA9" s="39"/>
-      <c r="BB9" s="32"/>
-      <c r="BC9" s="33"/>
-      <c r="BD9" s="34"/>
-      <c r="BE9" s="154"/>
-      <c r="BF9" s="155" t="s">
+      <c r="I10" s="229"/>
+      <c r="J10" s="229"/>
+      <c r="K10" s="229"/>
+      <c r="L10" s="229"/>
+      <c r="M10" s="229"/>
+      <c r="N10" s="229"/>
+      <c r="O10" s="229"/>
+      <c r="P10" s="229"/>
+      <c r="Q10" s="229"/>
+      <c r="R10" s="229"/>
+      <c r="S10" s="229"/>
+      <c r="T10" s="229"/>
+      <c r="U10" s="229"/>
+      <c r="V10" s="229"/>
+      <c r="W10" s="229"/>
+      <c r="X10" s="229"/>
+      <c r="Y10" s="229"/>
+      <c r="Z10" s="229"/>
+      <c r="AA10" s="229"/>
+      <c r="AB10" s="229"/>
+      <c r="AC10" s="229"/>
+      <c r="AD10" s="229"/>
+      <c r="AE10" s="229"/>
+      <c r="AF10" s="229"/>
+      <c r="AG10" s="229"/>
+      <c r="AH10" s="229"/>
+      <c r="AI10" s="229"/>
+      <c r="AJ10" s="229"/>
+      <c r="AK10" s="229"/>
+      <c r="AL10" s="229"/>
+      <c r="AM10" s="229"/>
+      <c r="AN10" s="229"/>
+      <c r="AO10" s="229"/>
+      <c r="AP10" s="229"/>
+      <c r="AQ10" s="229"/>
+      <c r="AR10" s="229"/>
+      <c r="AS10" s="229"/>
+      <c r="AT10" s="43"/>
+      <c r="AU10" s="41"/>
+      <c r="AV10" s="44"/>
+      <c r="AW10" s="44"/>
+      <c r="AX10" s="44"/>
+      <c r="AY10" s="38"/>
+      <c r="AZ10" s="39"/>
+      <c r="BA10" s="39"/>
+      <c r="BB10" s="32"/>
+      <c r="BC10" s="33"/>
+      <c r="BD10" s="34"/>
+      <c r="BE10" s="154"/>
+      <c r="BF10" s="155" t="s">
         <v>113</v>
       </c>
-      <c r="BG9" s="155"/>
-      <c r="BH9" s="156"/>
-      <c r="BI9" s="155"/>
-      <c r="BJ9" s="157"/>
-      <c r="BK9" s="157"/>
-      <c r="BL9" s="157"/>
-      <c r="BM9" s="157"/>
-      <c r="BN9" s="157"/>
-      <c r="BO9" s="157"/>
-      <c r="BP9" s="157"/>
-      <c r="BQ9" s="158"/>
-      <c r="BR9" s="158"/>
-      <c r="BS9" s="158"/>
-      <c r="BT9" s="158"/>
-      <c r="BU9" s="159"/>
-      <c r="BV9" s="159"/>
-      <c r="BW9" s="160"/>
-    </row>
-    <row r="10" spans="1:75" ht="12.5" customHeight="1">
-      <c r="A10" s="36"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="57"/>
-      <c r="D10" s="57"/>
-      <c r="E10" s="57"/>
-      <c r="F10" s="57"/>
-      <c r="G10" s="57"/>
-      <c r="H10" s="89" t="s">
+      <c r="BG10" s="155"/>
+      <c r="BH10" s="156"/>
+      <c r="BI10" s="155"/>
+      <c r="BJ10" s="157"/>
+      <c r="BK10" s="157"/>
+      <c r="BL10" s="157"/>
+      <c r="BM10" s="157"/>
+      <c r="BN10" s="157"/>
+      <c r="BO10" s="157"/>
+      <c r="BP10" s="157"/>
+      <c r="BQ10" s="158"/>
+      <c r="BR10" s="158"/>
+      <c r="BS10" s="158"/>
+      <c r="BT10" s="158"/>
+      <c r="BU10" s="159"/>
+      <c r="BV10" s="159"/>
+      <c r="BW10" s="160"/>
+    </row>
+    <row r="11" spans="1:75" ht="12.5" customHeight="1">
+      <c r="A11" s="36"/>
+      <c r="B11" s="55"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="89" t="s">
         <v>93</v>
       </c>
-      <c r="I10" s="57"/>
-      <c r="J10" s="57"/>
-      <c r="K10" s="57"/>
-      <c r="L10" s="57"/>
-      <c r="M10" s="57"/>
-      <c r="N10" s="57"/>
-      <c r="O10" s="57"/>
-      <c r="P10" s="57"/>
-      <c r="Q10" s="57"/>
-      <c r="R10" s="57"/>
-      <c r="S10" s="57"/>
-      <c r="T10" s="57"/>
-      <c r="U10" s="57"/>
-      <c r="V10" s="57"/>
-      <c r="W10" s="57"/>
-      <c r="X10" s="57"/>
-      <c r="Y10" s="57"/>
-      <c r="Z10" s="57"/>
-      <c r="AA10" s="57"/>
-      <c r="AB10" s="57"/>
-      <c r="AC10" s="57"/>
-      <c r="AD10" s="57"/>
-      <c r="AE10" s="57"/>
-      <c r="AF10" s="57"/>
-      <c r="AG10" s="57"/>
-      <c r="AH10" s="57"/>
-      <c r="AI10" s="57"/>
-      <c r="AJ10" s="57"/>
-      <c r="AK10" s="57"/>
-      <c r="AL10" s="57"/>
-      <c r="AM10" s="57"/>
-      <c r="AN10" s="57"/>
-      <c r="AO10" s="57"/>
-      <c r="AP10" s="57"/>
-      <c r="AQ10" s="57"/>
-      <c r="AR10" s="57"/>
-      <c r="AS10" s="57"/>
-      <c r="AT10" s="57"/>
-      <c r="AU10" s="57"/>
-      <c r="AV10" s="57"/>
-      <c r="AW10" s="57"/>
-      <c r="AX10" s="57"/>
-      <c r="AY10" s="57"/>
-      <c r="AZ10" s="59"/>
-      <c r="BA10" s="59"/>
-      <c r="BB10" s="49"/>
-      <c r="BC10" s="50"/>
-      <c r="BD10" s="34"/>
-      <c r="BE10" s="161"/>
-      <c r="BF10" s="81"/>
-      <c r="BG10" s="84" t="s">
+      <c r="I11" s="57"/>
+      <c r="J11" s="57"/>
+      <c r="K11" s="57"/>
+      <c r="L11" s="57"/>
+      <c r="M11" s="57"/>
+      <c r="N11" s="57"/>
+      <c r="O11" s="57"/>
+      <c r="P11" s="57"/>
+      <c r="Q11" s="57"/>
+      <c r="R11" s="57"/>
+      <c r="S11" s="57"/>
+      <c r="T11" s="57"/>
+      <c r="U11" s="57"/>
+      <c r="V11" s="57"/>
+      <c r="W11" s="57"/>
+      <c r="X11" s="57"/>
+      <c r="Y11" s="57"/>
+      <c r="Z11" s="57"/>
+      <c r="AA11" s="57"/>
+      <c r="AB11" s="57"/>
+      <c r="AC11" s="57"/>
+      <c r="AD11" s="57"/>
+      <c r="AE11" s="57"/>
+      <c r="AF11" s="57"/>
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="57"/>
+      <c r="AI11" s="57"/>
+      <c r="AJ11" s="57"/>
+      <c r="AK11" s="57"/>
+      <c r="AL11" s="57"/>
+      <c r="AM11" s="57"/>
+      <c r="AN11" s="57"/>
+      <c r="AO11" s="57"/>
+      <c r="AP11" s="57"/>
+      <c r="AQ11" s="57"/>
+      <c r="AR11" s="57"/>
+      <c r="AS11" s="57"/>
+      <c r="AT11" s="57"/>
+      <c r="AU11" s="57"/>
+      <c r="AV11" s="57"/>
+      <c r="AW11" s="57"/>
+      <c r="AX11" s="57"/>
+      <c r="AY11" s="57"/>
+      <c r="AZ11" s="59"/>
+      <c r="BA11" s="59"/>
+      <c r="BB11" s="49"/>
+      <c r="BC11" s="50"/>
+      <c r="BD11" s="34"/>
+      <c r="BE11" s="161"/>
+      <c r="BF11" s="81"/>
+      <c r="BG11" s="84" t="s">
         <v>114</v>
       </c>
-      <c r="BH10" s="81"/>
-      <c r="BI10" s="81"/>
-      <c r="BJ10" s="81"/>
-      <c r="BK10" s="81"/>
-      <c r="BL10" s="81"/>
-      <c r="BM10" s="81"/>
-      <c r="BN10" s="81"/>
-      <c r="BO10" s="81"/>
-      <c r="BP10" s="81"/>
-      <c r="BQ10" s="81"/>
-      <c r="BR10" s="81"/>
-      <c r="BS10" s="81"/>
-      <c r="BT10" s="81"/>
-      <c r="BW10" s="162"/>
-    </row>
-    <row r="11" spans="1:75" ht="12" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" s="45"/>
-      <c r="C11" s="46"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
-      <c r="F11" s="34"/>
-      <c r="G11" s="34"/>
-      <c r="H11" s="47"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="48"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="44"/>
-      <c r="P11" s="48"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="48"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-      <c r="X11" s="34"/>
-      <c r="Y11" s="47"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="41"/>
-      <c r="AB11" s="42"/>
-      <c r="AC11" s="41"/>
-      <c r="AD11" s="48"/>
-      <c r="AE11" s="48"/>
-      <c r="AF11" s="44"/>
-      <c r="AG11" s="48"/>
-      <c r="AH11" s="48"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="48"/>
-      <c r="AK11" s="44"/>
-      <c r="AL11" s="34"/>
-      <c r="AM11" s="34"/>
-      <c r="AN11" s="34"/>
-      <c r="AO11" s="34"/>
-      <c r="AP11" s="34"/>
-      <c r="AQ11" s="34"/>
-      <c r="AR11" s="34"/>
-      <c r="AS11" s="41"/>
-      <c r="AT11" s="43"/>
-      <c r="AU11" s="41"/>
-      <c r="AV11" s="44"/>
-      <c r="AW11" s="44"/>
-      <c r="AX11" s="44"/>
-      <c r="AY11" s="38"/>
-      <c r="AZ11" s="39"/>
-      <c r="BA11" s="39"/>
-      <c r="BB11" s="32"/>
-      <c r="BC11" s="33"/>
-      <c r="BD11" s="34"/>
-      <c r="BE11" s="163"/>
-      <c r="BF11" s="81"/>
-      <c r="BG11" s="81"/>
       <c r="BH11" s="81"/>
       <c r="BI11" s="81"/>
       <c r="BJ11" s="81"/>
@@ -11531,52 +11871,52 @@
       <c r="BT11" s="81"/>
       <c r="BW11" s="162"/>
     </row>
-    <row r="12" spans="1:75" ht="12.5" customHeight="1">
+    <row r="12" spans="1:75" ht="12" customHeight="1">
       <c r="A12" s="36"/>
-      <c r="B12" s="37"/>
-      <c r="C12" s="34"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="46"/>
       <c r="D12" s="34"/>
       <c r="E12" s="34"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="40"/>
-      <c r="H12" s="90"/>
-      <c r="I12" s="90"/>
-      <c r="J12" s="90"/>
-      <c r="K12" s="90"/>
-      <c r="L12" s="90"/>
-      <c r="M12" s="90"/>
-      <c r="N12" s="90"/>
-      <c r="O12" s="90"/>
-      <c r="P12" s="90"/>
-      <c r="Q12" s="90"/>
-      <c r="R12" s="90"/>
-      <c r="S12" s="90"/>
-      <c r="T12" s="91"/>
-      <c r="U12" s="91"/>
-      <c r="V12" s="91"/>
-      <c r="W12" s="91"/>
-      <c r="X12" s="92"/>
-      <c r="Y12" s="91"/>
-      <c r="Z12" s="91"/>
-      <c r="AA12" s="91"/>
-      <c r="AB12" s="93"/>
-      <c r="AC12" s="91"/>
-      <c r="AD12" s="94"/>
-      <c r="AE12" s="94"/>
-      <c r="AF12" s="94"/>
-      <c r="AG12" s="94"/>
-      <c r="AH12" s="94"/>
-      <c r="AI12" s="90"/>
-      <c r="AJ12" s="91"/>
-      <c r="AK12" s="91"/>
-      <c r="AL12" s="91"/>
-      <c r="AM12" s="91"/>
-      <c r="AN12" s="95"/>
-      <c r="AO12" s="92"/>
-      <c r="AP12" s="92"/>
-      <c r="AQ12" s="91"/>
-      <c r="AR12" s="91"/>
-      <c r="AS12" s="91"/>
+      <c r="F12" s="34"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="47"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="41"/>
+      <c r="K12" s="42"/>
+      <c r="L12" s="41"/>
+      <c r="M12" s="48"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="44"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="44"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
+      <c r="X12" s="34"/>
+      <c r="Y12" s="47"/>
+      <c r="Z12" s="42"/>
+      <c r="AA12" s="41"/>
+      <c r="AB12" s="42"/>
+      <c r="AC12" s="41"/>
+      <c r="AD12" s="48"/>
+      <c r="AE12" s="48"/>
+      <c r="AF12" s="44"/>
+      <c r="AG12" s="48"/>
+      <c r="AH12" s="48"/>
+      <c r="AI12" s="43"/>
+      <c r="AJ12" s="48"/>
+      <c r="AK12" s="44"/>
+      <c r="AL12" s="34"/>
+      <c r="AM12" s="34"/>
+      <c r="AN12" s="34"/>
+      <c r="AO12" s="34"/>
+      <c r="AP12" s="34"/>
+      <c r="AQ12" s="34"/>
+      <c r="AR12" s="34"/>
+      <c r="AS12" s="41"/>
       <c r="AT12" s="43"/>
       <c r="AU12" s="41"/>
       <c r="AV12" s="44"/>
@@ -11588,11 +11928,9 @@
       <c r="BB12" s="32"/>
       <c r="BC12" s="33"/>
       <c r="BD12" s="34"/>
-      <c r="BE12" s="161"/>
-      <c r="BF12" s="81" t="s">
-        <v>65</v>
-      </c>
-      <c r="BG12" s="84"/>
+      <c r="BE12" s="163"/>
+      <c r="BF12" s="81"/>
+      <c r="BG12" s="81"/>
       <c r="BH12" s="81"/>
       <c r="BI12" s="81"/>
       <c r="BJ12" s="81"/>
@@ -11610,16 +11948,14 @@
     </row>
     <row r="13" spans="1:75" ht="12.5" customHeight="1">
       <c r="A13" s="36"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="54"/>
+      <c r="B13" s="37"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="34"/>
+      <c r="E13" s="34"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="40"/>
       <c r="H13" s="90"/>
-      <c r="I13" s="105" t="s">
-        <v>51</v>
-      </c>
+      <c r="I13" s="90"/>
       <c r="J13" s="90"/>
       <c r="K13" s="90"/>
       <c r="L13" s="90"/>
@@ -11636,42 +11972,42 @@
       <c r="W13" s="91"/>
       <c r="X13" s="92"/>
       <c r="Y13" s="91"/>
-      <c r="Z13" s="90"/>
-      <c r="AA13" s="90"/>
-      <c r="AB13" s="90"/>
-      <c r="AC13" s="90"/>
-      <c r="AD13" s="90"/>
-      <c r="AE13" s="90"/>
-      <c r="AF13" s="90"/>
-      <c r="AG13" s="90"/>
-      <c r="AH13" s="90"/>
+      <c r="Z13" s="91"/>
+      <c r="AA13" s="91"/>
+      <c r="AB13" s="93"/>
+      <c r="AC13" s="91"/>
+      <c r="AD13" s="94"/>
+      <c r="AE13" s="94"/>
+      <c r="AF13" s="94"/>
+      <c r="AG13" s="94"/>
+      <c r="AH13" s="94"/>
       <c r="AI13" s="90"/>
-      <c r="AJ13" s="90"/>
-      <c r="AK13" s="90"/>
-      <c r="AL13" s="90"/>
-      <c r="AM13" s="90"/>
-      <c r="AN13" s="90"/>
-      <c r="AO13" s="90"/>
-      <c r="AP13" s="90"/>
-      <c r="AQ13" s="90"/>
-      <c r="AR13" s="90"/>
-      <c r="AS13" s="90"/>
-      <c r="AT13" s="54"/>
-      <c r="AU13" s="54"/>
-      <c r="AV13" s="54"/>
-      <c r="AW13" s="54"/>
-      <c r="AX13" s="58"/>
-      <c r="AY13" s="54"/>
-      <c r="AZ13" s="59"/>
-      <c r="BA13" s="59"/>
+      <c r="AJ13" s="91"/>
+      <c r="AK13" s="91"/>
+      <c r="AL13" s="91"/>
+      <c r="AM13" s="91"/>
+      <c r="AN13" s="95"/>
+      <c r="AO13" s="92"/>
+      <c r="AP13" s="92"/>
+      <c r="AQ13" s="91"/>
+      <c r="AR13" s="91"/>
+      <c r="AS13" s="91"/>
+      <c r="AT13" s="43"/>
+      <c r="AU13" s="41"/>
+      <c r="AV13" s="44"/>
+      <c r="AW13" s="44"/>
+      <c r="AX13" s="44"/>
+      <c r="AY13" s="38"/>
+      <c r="AZ13" s="39"/>
+      <c r="BA13" s="39"/>
       <c r="BB13" s="32"/>
       <c r="BC13" s="33"/>
       <c r="BD13" s="34"/>
-      <c r="BE13" s="163"/>
-      <c r="BF13" s="64"/>
-      <c r="BG13" s="64" t="s">
-        <v>66</v>
+      <c r="BE13" s="161"/>
+      <c r="BF13" s="81" t="s">
+        <v>65</v>
       </c>
+      <c r="BG13" s="84"/>
       <c r="BH13" s="81"/>
       <c r="BI13" s="81"/>
       <c r="BJ13" s="81"/>
@@ -11690,55 +12026,55 @@
     <row r="14" spans="1:75" ht="12.5" customHeight="1">
       <c r="A14" s="36"/>
       <c r="B14" s="55"/>
-      <c r="C14" s="60"/>
+      <c r="C14" s="54"/>
       <c r="D14" s="56"/>
       <c r="E14" s="56"/>
       <c r="F14" s="56"/>
-      <c r="G14" s="58"/>
+      <c r="G14" s="54"/>
       <c r="H14" s="90"/>
-      <c r="I14" s="137" t="s">
-        <v>100</v>
+      <c r="I14" s="105" t="s">
+        <v>51</v>
       </c>
-      <c r="J14" s="97"/>
-      <c r="K14" s="96"/>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
-      <c r="N14" s="96"/>
-      <c r="O14" s="96"/>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="96"/>
-      <c r="W14" s="96"/>
-      <c r="X14" s="98"/>
-      <c r="Y14" s="90"/>
+      <c r="J14" s="90"/>
+      <c r="K14" s="90"/>
+      <c r="L14" s="90"/>
+      <c r="M14" s="90"/>
+      <c r="N14" s="90"/>
+      <c r="O14" s="90"/>
+      <c r="P14" s="90"/>
+      <c r="Q14" s="90"/>
+      <c r="R14" s="90"/>
+      <c r="S14" s="90"/>
+      <c r="T14" s="91"/>
+      <c r="U14" s="91"/>
+      <c r="V14" s="91"/>
+      <c r="W14" s="91"/>
+      <c r="X14" s="92"/>
+      <c r="Y14" s="91"/>
       <c r="Z14" s="90"/>
-      <c r="AA14" s="99"/>
+      <c r="AA14" s="90"/>
       <c r="AB14" s="90"/>
-      <c r="AC14" s="100"/>
-      <c r="AD14" s="100"/>
-      <c r="AE14" s="101"/>
-      <c r="AF14" s="100"/>
-      <c r="AG14" s="101"/>
-      <c r="AH14" s="100"/>
-      <c r="AI14" s="102"/>
-      <c r="AJ14" s="100"/>
-      <c r="AK14" s="101"/>
-      <c r="AL14" s="101"/>
-      <c r="AM14" s="101"/>
-      <c r="AN14" s="101"/>
-      <c r="AO14" s="101"/>
-      <c r="AP14" s="101"/>
-      <c r="AQ14" s="101"/>
-      <c r="AR14" s="101"/>
-      <c r="AS14" s="101"/>
-      <c r="AT14" s="58"/>
-      <c r="AU14" s="58"/>
-      <c r="AV14" s="58"/>
-      <c r="AW14" s="58"/>
+      <c r="AC14" s="90"/>
+      <c r="AD14" s="90"/>
+      <c r="AE14" s="90"/>
+      <c r="AF14" s="90"/>
+      <c r="AG14" s="90"/>
+      <c r="AH14" s="90"/>
+      <c r="AI14" s="90"/>
+      <c r="AJ14" s="90"/>
+      <c r="AK14" s="90"/>
+      <c r="AL14" s="90"/>
+      <c r="AM14" s="90"/>
+      <c r="AN14" s="90"/>
+      <c r="AO14" s="90"/>
+      <c r="AP14" s="90"/>
+      <c r="AQ14" s="90"/>
+      <c r="AR14" s="90"/>
+      <c r="AS14" s="90"/>
+      <c r="AT14" s="54"/>
+      <c r="AU14" s="54"/>
+      <c r="AV14" s="54"/>
+      <c r="AW14" s="54"/>
       <c r="AX14" s="58"/>
       <c r="AY14" s="54"/>
       <c r="AZ14" s="59"/>
@@ -11748,10 +12084,10 @@
       <c r="BD14" s="34"/>
       <c r="BE14" s="163"/>
       <c r="BF14" s="64"/>
-      <c r="BG14" s="64"/>
-      <c r="BH14" s="81" t="s">
-        <v>115</v>
+      <c r="BG14" s="64" t="s">
+        <v>66</v>
       </c>
+      <c r="BH14" s="81"/>
       <c r="BI14" s="81"/>
       <c r="BJ14" s="81"/>
       <c r="BK14" s="81"/>
@@ -11769,15 +12105,17 @@
     <row r="15" spans="1:75" ht="12.5" customHeight="1">
       <c r="A15" s="36"/>
       <c r="B15" s="55"/>
-      <c r="C15" s="62"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
+      <c r="C15" s="60"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
+      <c r="F15" s="56"/>
       <c r="G15" s="58"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="98"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="98"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="137" t="s">
+        <v>100</v>
+      </c>
+      <c r="J15" s="97"/>
+      <c r="K15" s="96"/>
       <c r="L15" s="96"/>
       <c r="M15" s="96"/>
       <c r="N15" s="96"/>
@@ -11792,14 +12130,14 @@
       <c r="W15" s="96"/>
       <c r="X15" s="98"/>
       <c r="Y15" s="90"/>
-      <c r="Z15" s="99"/>
-      <c r="AA15" s="90"/>
-      <c r="AB15" s="99"/>
-      <c r="AC15" s="90"/>
+      <c r="Z15" s="90"/>
+      <c r="AA15" s="99"/>
+      <c r="AB15" s="90"/>
+      <c r="AC15" s="100"/>
       <c r="AD15" s="100"/>
-      <c r="AE15" s="100"/>
-      <c r="AF15" s="101"/>
-      <c r="AG15" s="100"/>
+      <c r="AE15" s="101"/>
+      <c r="AF15" s="100"/>
+      <c r="AG15" s="101"/>
       <c r="AH15" s="100"/>
       <c r="AI15" s="102"/>
       <c r="AJ15" s="100"/>
@@ -11811,9 +12149,9 @@
       <c r="AP15" s="101"/>
       <c r="AQ15" s="101"/>
       <c r="AR15" s="101"/>
-      <c r="AS15" s="90"/>
-      <c r="AT15" s="61"/>
-      <c r="AU15" s="54"/>
+      <c r="AS15" s="101"/>
+      <c r="AT15" s="58"/>
+      <c r="AU15" s="58"/>
       <c r="AV15" s="58"/>
       <c r="AW15" s="58"/>
       <c r="AX15" s="58"/>
@@ -11827,7 +12165,7 @@
       <c r="BF15" s="64"/>
       <c r="BG15" s="64"/>
       <c r="BH15" s="81" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="BI15" s="81"/>
       <c r="BJ15" s="81"/>
@@ -11846,7 +12184,7 @@
     <row r="16" spans="1:75" ht="12.5" customHeight="1">
       <c r="A16" s="36"/>
       <c r="B16" s="55"/>
-      <c r="C16" s="54"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="58"/>
       <c r="E16" s="58"/>
       <c r="F16" s="58"/>
@@ -11869,30 +12207,30 @@
       <c r="W16" s="96"/>
       <c r="X16" s="98"/>
       <c r="Y16" s="90"/>
-      <c r="Z16" s="101"/>
-      <c r="AA16" s="101"/>
-      <c r="AB16" s="101"/>
-      <c r="AC16" s="101"/>
-      <c r="AD16" s="101"/>
-      <c r="AE16" s="101"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="90"/>
+      <c r="AB16" s="99"/>
+      <c r="AC16" s="90"/>
+      <c r="AD16" s="100"/>
+      <c r="AE16" s="100"/>
       <c r="AF16" s="101"/>
-      <c r="AG16" s="101"/>
-      <c r="AH16" s="101"/>
-      <c r="AI16" s="101"/>
-      <c r="AJ16" s="101"/>
+      <c r="AG16" s="100"/>
+      <c r="AH16" s="100"/>
+      <c r="AI16" s="102"/>
+      <c r="AJ16" s="100"/>
       <c r="AK16" s="101"/>
       <c r="AL16" s="101"/>
-      <c r="AM16" s="90"/>
-      <c r="AN16" s="90"/>
-      <c r="AO16" s="90"/>
-      <c r="AP16" s="90"/>
-      <c r="AQ16" s="90"/>
-      <c r="AR16" s="90"/>
+      <c r="AM16" s="101"/>
+      <c r="AN16" s="101"/>
+      <c r="AO16" s="101"/>
+      <c r="AP16" s="101"/>
+      <c r="AQ16" s="101"/>
+      <c r="AR16" s="101"/>
       <c r="AS16" s="90"/>
-      <c r="AT16" s="54"/>
+      <c r="AT16" s="61"/>
       <c r="AU16" s="54"/>
-      <c r="AV16" s="54"/>
-      <c r="AW16" s="54"/>
+      <c r="AV16" s="58"/>
+      <c r="AW16" s="58"/>
       <c r="AX16" s="58"/>
       <c r="AY16" s="54"/>
       <c r="AZ16" s="59"/>
@@ -11900,111 +12238,113 @@
       <c r="BB16" s="32"/>
       <c r="BC16" s="33"/>
       <c r="BD16" s="34"/>
-      <c r="BE16" s="164"/>
-      <c r="BF16" s="165"/>
-      <c r="BG16" s="165"/>
-      <c r="BH16" s="165"/>
-      <c r="BI16" s="165"/>
-      <c r="BJ16" s="165"/>
-      <c r="BK16" s="165"/>
-      <c r="BL16" s="165"/>
-      <c r="BM16" s="165"/>
-      <c r="BN16" s="165"/>
-      <c r="BO16" s="165"/>
-      <c r="BP16" s="165"/>
-      <c r="BQ16" s="165"/>
-      <c r="BR16" s="165"/>
-      <c r="BS16" s="165"/>
-      <c r="BT16" s="165"/>
-      <c r="BU16" s="166"/>
-      <c r="BV16" s="166"/>
-      <c r="BW16" s="167"/>
-    </row>
-    <row r="17" spans="1:72" ht="12.5" customHeight="1">
+      <c r="BE16" s="163"/>
+      <c r="BF16" s="64"/>
+      <c r="BG16" s="64"/>
+      <c r="BH16" s="81" t="s">
+        <v>116</v>
+      </c>
+      <c r="BI16" s="81"/>
+      <c r="BJ16" s="81"/>
+      <c r="BK16" s="81"/>
+      <c r="BL16" s="81"/>
+      <c r="BM16" s="81"/>
+      <c r="BN16" s="81"/>
+      <c r="BO16" s="81"/>
+      <c r="BP16" s="81"/>
+      <c r="BQ16" s="81"/>
+      <c r="BR16" s="81"/>
+      <c r="BS16" s="81"/>
+      <c r="BT16" s="81"/>
+      <c r="BW16" s="162"/>
+    </row>
+    <row r="17" spans="1:75" ht="12.5" customHeight="1">
       <c r="A17" s="36"/>
-      <c r="B17" s="37"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="106"/>
-      <c r="I17" s="106"/>
-      <c r="J17" s="106"/>
-      <c r="K17" s="106"/>
-      <c r="L17" s="106"/>
-      <c r="M17" s="106"/>
-      <c r="N17" s="106"/>
-      <c r="O17" s="106"/>
-      <c r="P17" s="106"/>
-      <c r="Q17" s="106"/>
-      <c r="R17" s="106"/>
-      <c r="S17" s="106"/>
-      <c r="T17" s="107"/>
-      <c r="U17" s="107"/>
-      <c r="V17" s="107"/>
-      <c r="W17" s="107"/>
-      <c r="X17" s="108"/>
-      <c r="Y17" s="107"/>
-      <c r="Z17" s="107"/>
-      <c r="AA17" s="107"/>
-      <c r="AB17" s="109"/>
-      <c r="AC17" s="107"/>
-      <c r="AD17" s="110"/>
-      <c r="AE17" s="110"/>
-      <c r="AF17" s="110"/>
-      <c r="AG17" s="110"/>
-      <c r="AH17" s="110"/>
-      <c r="AI17" s="106"/>
-      <c r="AJ17" s="107"/>
-      <c r="AK17" s="107"/>
-      <c r="AL17" s="107"/>
-      <c r="AM17" s="107"/>
-      <c r="AN17" s="111"/>
-      <c r="AO17" s="108"/>
-      <c r="AP17" s="108"/>
-      <c r="AQ17" s="107"/>
-      <c r="AR17" s="107"/>
-      <c r="AS17" s="107"/>
-      <c r="AT17" s="43"/>
-      <c r="AU17" s="41"/>
-      <c r="AV17" s="44"/>
-      <c r="AW17" s="44"/>
-      <c r="AX17" s="44"/>
-      <c r="AY17" s="38"/>
-      <c r="AZ17" s="39"/>
-      <c r="BA17" s="39"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="54"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="103"/>
+      <c r="I17" s="98"/>
+      <c r="J17" s="96"/>
+      <c r="K17" s="98"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="96"/>
+      <c r="O17" s="96"/>
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="96"/>
+      <c r="W17" s="96"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="90"/>
+      <c r="Z17" s="101"/>
+      <c r="AA17" s="101"/>
+      <c r="AB17" s="101"/>
+      <c r="AC17" s="101"/>
+      <c r="AD17" s="101"/>
+      <c r="AE17" s="101"/>
+      <c r="AF17" s="101"/>
+      <c r="AG17" s="101"/>
+      <c r="AH17" s="101"/>
+      <c r="AI17" s="101"/>
+      <c r="AJ17" s="101"/>
+      <c r="AK17" s="101"/>
+      <c r="AL17" s="101"/>
+      <c r="AM17" s="90"/>
+      <c r="AN17" s="90"/>
+      <c r="AO17" s="90"/>
+      <c r="AP17" s="90"/>
+      <c r="AQ17" s="90"/>
+      <c r="AR17" s="90"/>
+      <c r="AS17" s="90"/>
+      <c r="AT17" s="54"/>
+      <c r="AU17" s="54"/>
+      <c r="AV17" s="54"/>
+      <c r="AW17" s="54"/>
+      <c r="AX17" s="58"/>
+      <c r="AY17" s="54"/>
+      <c r="AZ17" s="59"/>
+      <c r="BA17" s="59"/>
       <c r="BB17" s="32"/>
       <c r="BC17" s="33"/>
       <c r="BD17" s="34"/>
-      <c r="BF17" s="64"/>
-      <c r="BG17" s="64"/>
-      <c r="BH17" s="81"/>
-      <c r="BI17" s="81"/>
-      <c r="BJ17" s="81"/>
-      <c r="BK17" s="81"/>
-      <c r="BL17" s="81"/>
-      <c r="BM17" s="81"/>
-      <c r="BN17" s="81"/>
-      <c r="BO17" s="81"/>
-      <c r="BP17" s="81"/>
-      <c r="BQ17" s="81"/>
-      <c r="BR17" s="81"/>
-      <c r="BS17" s="81"/>
-      <c r="BT17" s="81"/>
-    </row>
-    <row r="18" spans="1:72" ht="12.5" customHeight="1">
+      <c r="BE17" s="164"/>
+      <c r="BF17" s="165"/>
+      <c r="BG17" s="165"/>
+      <c r="BH17" s="165"/>
+      <c r="BI17" s="165"/>
+      <c r="BJ17" s="165"/>
+      <c r="BK17" s="165"/>
+      <c r="BL17" s="165"/>
+      <c r="BM17" s="165"/>
+      <c r="BN17" s="165"/>
+      <c r="BO17" s="165"/>
+      <c r="BP17" s="165"/>
+      <c r="BQ17" s="165"/>
+      <c r="BR17" s="165"/>
+      <c r="BS17" s="165"/>
+      <c r="BT17" s="165"/>
+      <c r="BU17" s="166"/>
+      <c r="BV17" s="166"/>
+      <c r="BW17" s="167"/>
+    </row>
+    <row r="18" spans="1:75" ht="12.5" customHeight="1">
       <c r="A18" s="36"/>
-      <c r="B18" s="55"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="54"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="34"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="40"/>
       <c r="H18" s="106"/>
-      <c r="I18" s="120" t="s">
-        <v>33</v>
-      </c>
+      <c r="I18" s="106"/>
       <c r="J18" s="106"/>
       <c r="K18" s="106"/>
       <c r="L18" s="106"/>
@@ -12021,38 +12361,37 @@
       <c r="W18" s="107"/>
       <c r="X18" s="108"/>
       <c r="Y18" s="107"/>
-      <c r="Z18" s="106"/>
-      <c r="AA18" s="106"/>
-      <c r="AB18" s="106"/>
-      <c r="AC18" s="106"/>
-      <c r="AD18" s="106"/>
-      <c r="AE18" s="106"/>
-      <c r="AF18" s="106"/>
-      <c r="AG18" s="106"/>
-      <c r="AH18" s="106"/>
+      <c r="Z18" s="107"/>
+      <c r="AA18" s="107"/>
+      <c r="AB18" s="109"/>
+      <c r="AC18" s="107"/>
+      <c r="AD18" s="110"/>
+      <c r="AE18" s="110"/>
+      <c r="AF18" s="110"/>
+      <c r="AG18" s="110"/>
+      <c r="AH18" s="110"/>
       <c r="AI18" s="106"/>
-      <c r="AJ18" s="106"/>
-      <c r="AK18" s="106"/>
-      <c r="AL18" s="106"/>
-      <c r="AM18" s="106"/>
-      <c r="AN18" s="106"/>
-      <c r="AO18" s="106"/>
-      <c r="AP18" s="106"/>
-      <c r="AQ18" s="106"/>
-      <c r="AR18" s="106"/>
-      <c r="AS18" s="106"/>
-      <c r="AT18" s="54"/>
-      <c r="AU18" s="54"/>
-      <c r="AV18" s="54"/>
-      <c r="AW18" s="54"/>
-      <c r="AX18" s="58"/>
-      <c r="AY18" s="54"/>
-      <c r="AZ18" s="59"/>
-      <c r="BA18" s="59"/>
+      <c r="AJ18" s="107"/>
+      <c r="AK18" s="107"/>
+      <c r="AL18" s="107"/>
+      <c r="AM18" s="107"/>
+      <c r="AN18" s="111"/>
+      <c r="AO18" s="108"/>
+      <c r="AP18" s="108"/>
+      <c r="AQ18" s="107"/>
+      <c r="AR18" s="107"/>
+      <c r="AS18" s="107"/>
+      <c r="AT18" s="43"/>
+      <c r="AU18" s="41"/>
+      <c r="AV18" s="44"/>
+      <c r="AW18" s="44"/>
+      <c r="AX18" s="44"/>
+      <c r="AY18" s="38"/>
+      <c r="AZ18" s="39"/>
+      <c r="BA18" s="39"/>
       <c r="BB18" s="32"/>
       <c r="BC18" s="33"/>
       <c r="BD18" s="34"/>
-      <c r="BE18" s="81"/>
       <c r="BF18" s="64"/>
       <c r="BG18" s="64"/>
       <c r="BH18" s="81"/>
@@ -12069,58 +12408,58 @@
       <c r="BS18" s="81"/>
       <c r="BT18" s="81"/>
     </row>
-    <row r="19" spans="1:72" ht="12.5" customHeight="1">
+    <row r="19" spans="1:75" ht="12.5" customHeight="1">
       <c r="A19" s="36"/>
       <c r="B19" s="55"/>
-      <c r="C19" s="60"/>
+      <c r="C19" s="54"/>
       <c r="D19" s="56"/>
       <c r="E19" s="56"/>
       <c r="F19" s="56"/>
-      <c r="G19" s="58"/>
+      <c r="G19" s="54"/>
       <c r="H19" s="106"/>
-      <c r="I19" s="106" t="s">
-        <v>101</v>
+      <c r="I19" s="120" t="s">
+        <v>33</v>
       </c>
-      <c r="J19" s="113"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112"/>
-      <c r="M19" s="112"/>
-      <c r="N19" s="112"/>
-      <c r="O19" s="112"/>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
-      <c r="S19" s="112"/>
-      <c r="T19" s="112"/>
-      <c r="U19" s="112"/>
-      <c r="V19" s="112"/>
-      <c r="W19" s="112"/>
-      <c r="X19" s="114"/>
-      <c r="Y19" s="106"/>
+      <c r="J19" s="106"/>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
+      <c r="M19" s="106"/>
+      <c r="N19" s="106"/>
+      <c r="O19" s="106"/>
+      <c r="P19" s="106"/>
+      <c r="Q19" s="106"/>
+      <c r="R19" s="106"/>
+      <c r="S19" s="106"/>
+      <c r="T19" s="107"/>
+      <c r="U19" s="107"/>
+      <c r="V19" s="107"/>
+      <c r="W19" s="107"/>
+      <c r="X19" s="108"/>
+      <c r="Y19" s="107"/>
       <c r="Z19" s="106"/>
-      <c r="AA19" s="115"/>
+      <c r="AA19" s="106"/>
       <c r="AB19" s="106"/>
-      <c r="AC19" s="116"/>
-      <c r="AD19" s="116"/>
-      <c r="AE19" s="117"/>
-      <c r="AF19" s="116"/>
-      <c r="AG19" s="117"/>
-      <c r="AH19" s="116"/>
-      <c r="AI19" s="118"/>
-      <c r="AJ19" s="116"/>
-      <c r="AK19" s="117"/>
-      <c r="AL19" s="117"/>
-      <c r="AM19" s="117"/>
-      <c r="AN19" s="117"/>
-      <c r="AO19" s="117"/>
-      <c r="AP19" s="117"/>
-      <c r="AQ19" s="117"/>
-      <c r="AR19" s="117"/>
-      <c r="AS19" s="117"/>
-      <c r="AT19" s="58"/>
-      <c r="AU19" s="58"/>
-      <c r="AV19" s="58"/>
-      <c r="AW19" s="58"/>
+      <c r="AC19" s="106"/>
+      <c r="AD19" s="106"/>
+      <c r="AE19" s="106"/>
+      <c r="AF19" s="106"/>
+      <c r="AG19" s="106"/>
+      <c r="AH19" s="106"/>
+      <c r="AI19" s="106"/>
+      <c r="AJ19" s="106"/>
+      <c r="AK19" s="106"/>
+      <c r="AL19" s="106"/>
+      <c r="AM19" s="106"/>
+      <c r="AN19" s="106"/>
+      <c r="AO19" s="106"/>
+      <c r="AP19" s="106"/>
+      <c r="AQ19" s="106"/>
+      <c r="AR19" s="106"/>
+      <c r="AS19" s="106"/>
+      <c r="AT19" s="54"/>
+      <c r="AU19" s="54"/>
+      <c r="AV19" s="54"/>
+      <c r="AW19" s="54"/>
       <c r="AX19" s="58"/>
       <c r="AY19" s="54"/>
       <c r="AZ19" s="59"/>
@@ -12128,9 +12467,9 @@
       <c r="BB19" s="32"/>
       <c r="BC19" s="33"/>
       <c r="BD19" s="34"/>
-      <c r="BE19" s="84"/>
-      <c r="BF19" s="81"/>
-      <c r="BG19" s="81"/>
+      <c r="BE19" s="81"/>
+      <c r="BF19" s="64"/>
+      <c r="BG19" s="64"/>
       <c r="BH19" s="81"/>
       <c r="BI19" s="81"/>
       <c r="BJ19" s="81"/>
@@ -12145,27 +12484,27 @@
       <c r="BS19" s="81"/>
       <c r="BT19" s="81"/>
     </row>
-    <row r="20" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="20" spans="1:75" ht="12.5" customHeight="1">
       <c r="A20" s="36"/>
       <c r="B20" s="55"/>
-      <c r="C20" s="62"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="56"/>
+      <c r="E20" s="56"/>
+      <c r="F20" s="56"/>
       <c r="G20" s="58"/>
-      <c r="H20" s="119"/>
-      <c r="I20" s="114"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="114"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106" t="s">
+        <v>101</v>
+      </c>
+      <c r="J20" s="113"/>
+      <c r="K20" s="112"/>
       <c r="L20" s="112"/>
       <c r="M20" s="112"/>
       <c r="N20" s="112"/>
       <c r="O20" s="112"/>
       <c r="P20" s="112"/>
       <c r="Q20" s="112"/>
-      <c r="R20" s="106" t="s">
-        <v>52</v>
-      </c>
+      <c r="R20" s="112"/>
       <c r="S20" s="112"/>
       <c r="T20" s="112"/>
       <c r="U20" s="112"/>
@@ -12173,14 +12512,14 @@
       <c r="W20" s="112"/>
       <c r="X20" s="114"/>
       <c r="Y20" s="106"/>
-      <c r="Z20" s="115"/>
-      <c r="AA20" s="106"/>
-      <c r="AB20" s="115"/>
-      <c r="AC20" s="106"/>
+      <c r="Z20" s="106"/>
+      <c r="AA20" s="115"/>
+      <c r="AB20" s="106"/>
+      <c r="AC20" s="116"/>
       <c r="AD20" s="116"/>
-      <c r="AE20" s="116"/>
-      <c r="AF20" s="117"/>
-      <c r="AG20" s="116"/>
+      <c r="AE20" s="117"/>
+      <c r="AF20" s="116"/>
+      <c r="AG20" s="117"/>
       <c r="AH20" s="116"/>
       <c r="AI20" s="118"/>
       <c r="AJ20" s="116"/>
@@ -12192,9 +12531,9 @@
       <c r="AP20" s="117"/>
       <c r="AQ20" s="117"/>
       <c r="AR20" s="117"/>
-      <c r="AS20" s="106"/>
-      <c r="AT20" s="61"/>
-      <c r="AU20" s="54"/>
+      <c r="AS20" s="117"/>
+      <c r="AT20" s="58"/>
+      <c r="AU20" s="58"/>
       <c r="AV20" s="58"/>
       <c r="AW20" s="58"/>
       <c r="AX20" s="58"/>
@@ -12204,9 +12543,9 @@
       <c r="BB20" s="32"/>
       <c r="BC20" s="33"/>
       <c r="BD20" s="34"/>
-      <c r="BE20" s="81"/>
+      <c r="BE20" s="84"/>
       <c r="BF20" s="81"/>
-      <c r="BG20" s="64"/>
+      <c r="BG20" s="81"/>
       <c r="BH20" s="81"/>
       <c r="BI20" s="81"/>
       <c r="BJ20" s="81"/>
@@ -12221,10 +12560,10 @@
       <c r="BS20" s="81"/>
       <c r="BT20" s="81"/>
     </row>
-    <row r="21" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="21" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A21" s="36"/>
       <c r="B21" s="55"/>
-      <c r="C21" s="54"/>
+      <c r="C21" s="62"/>
       <c r="D21" s="58"/>
       <c r="E21" s="58"/>
       <c r="F21" s="58"/>
@@ -12239,8 +12578,8 @@
       <c r="O21" s="112"/>
       <c r="P21" s="112"/>
       <c r="Q21" s="112"/>
-      <c r="R21" s="138" t="s">
-        <v>102</v>
+      <c r="R21" s="106" t="s">
+        <v>52</v>
       </c>
       <c r="S21" s="112"/>
       <c r="T21" s="112"/>
@@ -12249,30 +12588,30 @@
       <c r="W21" s="112"/>
       <c r="X21" s="114"/>
       <c r="Y21" s="106"/>
-      <c r="Z21" s="117"/>
-      <c r="AA21" s="117"/>
-      <c r="AB21" s="117"/>
-      <c r="AC21" s="117"/>
-      <c r="AD21" s="117"/>
-      <c r="AE21" s="117"/>
+      <c r="Z21" s="115"/>
+      <c r="AA21" s="106"/>
+      <c r="AB21" s="115"/>
+      <c r="AC21" s="106"/>
+      <c r="AD21" s="116"/>
+      <c r="AE21" s="116"/>
       <c r="AF21" s="117"/>
-      <c r="AG21" s="117"/>
-      <c r="AH21" s="117"/>
-      <c r="AI21" s="117"/>
-      <c r="AJ21" s="117"/>
+      <c r="AG21" s="116"/>
+      <c r="AH21" s="116"/>
+      <c r="AI21" s="118"/>
+      <c r="AJ21" s="116"/>
       <c r="AK21" s="117"/>
       <c r="AL21" s="117"/>
-      <c r="AM21" s="106"/>
-      <c r="AN21" s="106"/>
-      <c r="AO21" s="106"/>
-      <c r="AP21" s="106"/>
-      <c r="AQ21" s="106"/>
-      <c r="AR21" s="106"/>
+      <c r="AM21" s="117"/>
+      <c r="AN21" s="117"/>
+      <c r="AO21" s="117"/>
+      <c r="AP21" s="117"/>
+      <c r="AQ21" s="117"/>
+      <c r="AR21" s="117"/>
       <c r="AS21" s="106"/>
-      <c r="AT21" s="54"/>
+      <c r="AT21" s="61"/>
       <c r="AU21" s="54"/>
-      <c r="AV21" s="54"/>
-      <c r="AW21" s="54"/>
+      <c r="AV21" s="58"/>
+      <c r="AW21" s="58"/>
       <c r="AX21" s="58"/>
       <c r="AY21" s="54"/>
       <c r="AZ21" s="59"/>
@@ -12281,7 +12620,7 @@
       <c r="BC21" s="33"/>
       <c r="BD21" s="34"/>
       <c r="BE21" s="81"/>
-      <c r="BF21" s="64"/>
+      <c r="BF21" s="81"/>
       <c r="BG21" s="64"/>
       <c r="BH21" s="81"/>
       <c r="BI21" s="81"/>
@@ -12297,7 +12636,7 @@
       <c r="BS21" s="81"/>
       <c r="BT21" s="81"/>
     </row>
-    <row r="22" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="22" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A22" s="36"/>
       <c r="B22" s="55"/>
       <c r="C22" s="54"/>
@@ -12315,7 +12654,9 @@
       <c r="O22" s="112"/>
       <c r="P22" s="112"/>
       <c r="Q22" s="112"/>
-      <c r="R22" s="122"/>
+      <c r="R22" s="138" t="s">
+        <v>102</v>
+      </c>
       <c r="S22" s="112"/>
       <c r="T22" s="112"/>
       <c r="U22" s="112"/>
@@ -12356,7 +12697,7 @@
       <c r="BD22" s="34"/>
       <c r="BE22" s="81"/>
       <c r="BF22" s="64"/>
-      <c r="BG22" s="81"/>
+      <c r="BG22" s="64"/>
       <c r="BH22" s="81"/>
       <c r="BI22" s="81"/>
       <c r="BJ22" s="81"/>
@@ -12371,65 +12712,65 @@
       <c r="BS22" s="81"/>
       <c r="BT22" s="81"/>
     </row>
-    <row r="23" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="23" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="35"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="90"/>
-      <c r="I23" s="90"/>
-      <c r="J23" s="90"/>
-      <c r="K23" s="90"/>
-      <c r="L23" s="90"/>
-      <c r="M23" s="90"/>
-      <c r="N23" s="90"/>
-      <c r="O23" s="90"/>
-      <c r="P23" s="90"/>
-      <c r="Q23" s="90"/>
-      <c r="R23" s="90"/>
-      <c r="S23" s="90"/>
-      <c r="T23" s="91"/>
-      <c r="U23" s="91"/>
-      <c r="V23" s="91"/>
-      <c r="W23" s="91"/>
-      <c r="X23" s="92"/>
-      <c r="Y23" s="91"/>
-      <c r="Z23" s="91"/>
-      <c r="AA23" s="91"/>
-      <c r="AB23" s="93"/>
-      <c r="AC23" s="91"/>
-      <c r="AD23" s="94"/>
-      <c r="AE23" s="94"/>
-      <c r="AF23" s="94"/>
-      <c r="AG23" s="94"/>
-      <c r="AH23" s="94"/>
-      <c r="AI23" s="90"/>
-      <c r="AJ23" s="91"/>
-      <c r="AK23" s="91"/>
-      <c r="AL23" s="91"/>
-      <c r="AM23" s="91"/>
-      <c r="AN23" s="95"/>
-      <c r="AO23" s="92"/>
-      <c r="AP23" s="92"/>
-      <c r="AQ23" s="91"/>
-      <c r="AR23" s="91"/>
-      <c r="AS23" s="91"/>
-      <c r="AT23" s="43"/>
-      <c r="AU23" s="41"/>
-      <c r="AV23" s="44"/>
-      <c r="AW23" s="44"/>
-      <c r="AX23" s="44"/>
-      <c r="AY23" s="38"/>
-      <c r="AZ23" s="39"/>
-      <c r="BA23" s="39"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="114"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="112"/>
+      <c r="R23" s="122"/>
+      <c r="S23" s="112"/>
+      <c r="T23" s="112"/>
+      <c r="U23" s="112"/>
+      <c r="V23" s="112"/>
+      <c r="W23" s="112"/>
+      <c r="X23" s="114"/>
+      <c r="Y23" s="106"/>
+      <c r="Z23" s="117"/>
+      <c r="AA23" s="117"/>
+      <c r="AB23" s="117"/>
+      <c r="AC23" s="117"/>
+      <c r="AD23" s="117"/>
+      <c r="AE23" s="117"/>
+      <c r="AF23" s="117"/>
+      <c r="AG23" s="117"/>
+      <c r="AH23" s="117"/>
+      <c r="AI23" s="117"/>
+      <c r="AJ23" s="117"/>
+      <c r="AK23" s="117"/>
+      <c r="AL23" s="117"/>
+      <c r="AM23" s="106"/>
+      <c r="AN23" s="106"/>
+      <c r="AO23" s="106"/>
+      <c r="AP23" s="106"/>
+      <c r="AQ23" s="106"/>
+      <c r="AR23" s="106"/>
+      <c r="AS23" s="106"/>
+      <c r="AT23" s="54"/>
+      <c r="AU23" s="54"/>
+      <c r="AV23" s="54"/>
+      <c r="AW23" s="54"/>
+      <c r="AX23" s="58"/>
+      <c r="AY23" s="54"/>
+      <c r="AZ23" s="59"/>
+      <c r="BA23" s="59"/>
       <c r="BB23" s="32"/>
       <c r="BC23" s="33"/>
       <c r="BD23" s="34"/>
-      <c r="BE23" s="84"/>
-      <c r="BF23" s="81"/>
+      <c r="BE23" s="81"/>
+      <c r="BF23" s="64"/>
       <c r="BG23" s="81"/>
       <c r="BH23" s="81"/>
       <c r="BI23" s="81"/>
@@ -12445,18 +12786,16 @@
       <c r="BS23" s="81"/>
       <c r="BT23" s="81"/>
     </row>
-    <row r="24" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="24" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A24" s="36"/>
-      <c r="B24" s="55"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="56"/>
-      <c r="E24" s="56"/>
-      <c r="F24" s="56"/>
-      <c r="G24" s="54"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="34"/>
+      <c r="D24" s="34"/>
+      <c r="E24" s="34"/>
+      <c r="F24" s="35"/>
+      <c r="G24" s="40"/>
       <c r="H24" s="90"/>
-      <c r="I24" s="104" t="s">
-        <v>53</v>
-      </c>
+      <c r="I24" s="90"/>
       <c r="J24" s="90"/>
       <c r="K24" s="90"/>
       <c r="L24" s="90"/>
@@ -12473,38 +12812,38 @@
       <c r="W24" s="91"/>
       <c r="X24" s="92"/>
       <c r="Y24" s="91"/>
-      <c r="Z24" s="90"/>
-      <c r="AA24" s="90"/>
-      <c r="AB24" s="90"/>
-      <c r="AC24" s="90"/>
-      <c r="AD24" s="90"/>
-      <c r="AE24" s="90"/>
-      <c r="AF24" s="90"/>
-      <c r="AG24" s="90"/>
-      <c r="AH24" s="90"/>
+      <c r="Z24" s="91"/>
+      <c r="AA24" s="91"/>
+      <c r="AB24" s="93"/>
+      <c r="AC24" s="91"/>
+      <c r="AD24" s="94"/>
+      <c r="AE24" s="94"/>
+      <c r="AF24" s="94"/>
+      <c r="AG24" s="94"/>
+      <c r="AH24" s="94"/>
       <c r="AI24" s="90"/>
-      <c r="AJ24" s="90"/>
-      <c r="AK24" s="90"/>
-      <c r="AL24" s="90"/>
-      <c r="AM24" s="90"/>
-      <c r="AN24" s="90"/>
-      <c r="AO24" s="90"/>
-      <c r="AP24" s="90"/>
-      <c r="AQ24" s="90"/>
-      <c r="AR24" s="90"/>
-      <c r="AS24" s="90"/>
-      <c r="AT24" s="54"/>
-      <c r="AU24" s="54"/>
-      <c r="AV24" s="54"/>
-      <c r="AW24" s="54"/>
-      <c r="AX24" s="58"/>
-      <c r="AY24" s="54"/>
-      <c r="AZ24" s="59"/>
-      <c r="BA24" s="59"/>
+      <c r="AJ24" s="91"/>
+      <c r="AK24" s="91"/>
+      <c r="AL24" s="91"/>
+      <c r="AM24" s="91"/>
+      <c r="AN24" s="95"/>
+      <c r="AO24" s="92"/>
+      <c r="AP24" s="92"/>
+      <c r="AQ24" s="91"/>
+      <c r="AR24" s="91"/>
+      <c r="AS24" s="91"/>
+      <c r="AT24" s="43"/>
+      <c r="AU24" s="41"/>
+      <c r="AV24" s="44"/>
+      <c r="AW24" s="44"/>
+      <c r="AX24" s="44"/>
+      <c r="AY24" s="38"/>
+      <c r="AZ24" s="39"/>
+      <c r="BA24" s="39"/>
       <c r="BB24" s="32"/>
       <c r="BC24" s="33"/>
       <c r="BD24" s="34"/>
-      <c r="BE24" s="81"/>
+      <c r="BE24" s="84"/>
       <c r="BF24" s="81"/>
       <c r="BG24" s="81"/>
       <c r="BH24" s="81"/>
@@ -12521,58 +12860,58 @@
       <c r="BS24" s="81"/>
       <c r="BT24" s="81"/>
     </row>
-    <row r="25" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="25" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A25" s="36"/>
       <c r="B25" s="55"/>
-      <c r="C25" s="60"/>
+      <c r="C25" s="54"/>
       <c r="D25" s="56"/>
       <c r="E25" s="56"/>
       <c r="F25" s="56"/>
-      <c r="G25" s="58"/>
+      <c r="G25" s="54"/>
       <c r="H25" s="90"/>
-      <c r="I25" s="90" t="s">
-        <v>94</v>
+      <c r="I25" s="104" t="s">
+        <v>53</v>
       </c>
-      <c r="J25" s="97"/>
-      <c r="K25" s="96"/>
-      <c r="L25" s="96"/>
-      <c r="M25" s="96"/>
-      <c r="N25" s="96"/>
-      <c r="O25" s="96"/>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="96"/>
-      <c r="S25" s="96"/>
-      <c r="T25" s="96"/>
-      <c r="U25" s="96"/>
-      <c r="V25" s="96"/>
-      <c r="W25" s="96"/>
-      <c r="X25" s="98"/>
-      <c r="Y25" s="90"/>
+      <c r="J25" s="90"/>
+      <c r="K25" s="90"/>
+      <c r="L25" s="90"/>
+      <c r="M25" s="90"/>
+      <c r="N25" s="90"/>
+      <c r="O25" s="90"/>
+      <c r="P25" s="90"/>
+      <c r="Q25" s="90"/>
+      <c r="R25" s="90"/>
+      <c r="S25" s="90"/>
+      <c r="T25" s="91"/>
+      <c r="U25" s="91"/>
+      <c r="V25" s="91"/>
+      <c r="W25" s="91"/>
+      <c r="X25" s="92"/>
+      <c r="Y25" s="91"/>
       <c r="Z25" s="90"/>
-      <c r="AA25" s="99"/>
+      <c r="AA25" s="90"/>
       <c r="AB25" s="90"/>
-      <c r="AC25" s="100"/>
-      <c r="AD25" s="100"/>
-      <c r="AE25" s="101"/>
-      <c r="AF25" s="100"/>
-      <c r="AG25" s="101"/>
-      <c r="AH25" s="100"/>
-      <c r="AI25" s="102"/>
-      <c r="AJ25" s="100"/>
-      <c r="AK25" s="101"/>
-      <c r="AL25" s="101"/>
-      <c r="AM25" s="101"/>
-      <c r="AN25" s="101"/>
-      <c r="AO25" s="101"/>
-      <c r="AP25" s="101"/>
-      <c r="AQ25" s="101"/>
-      <c r="AR25" s="101"/>
-      <c r="AS25" s="101"/>
-      <c r="AT25" s="58"/>
-      <c r="AU25" s="58"/>
-      <c r="AV25" s="58"/>
-      <c r="AW25" s="58"/>
+      <c r="AC25" s="90"/>
+      <c r="AD25" s="90"/>
+      <c r="AE25" s="90"/>
+      <c r="AF25" s="90"/>
+      <c r="AG25" s="90"/>
+      <c r="AH25" s="90"/>
+      <c r="AI25" s="90"/>
+      <c r="AJ25" s="90"/>
+      <c r="AK25" s="90"/>
+      <c r="AL25" s="90"/>
+      <c r="AM25" s="90"/>
+      <c r="AN25" s="90"/>
+      <c r="AO25" s="90"/>
+      <c r="AP25" s="90"/>
+      <c r="AQ25" s="90"/>
+      <c r="AR25" s="90"/>
+      <c r="AS25" s="90"/>
+      <c r="AT25" s="54"/>
+      <c r="AU25" s="54"/>
+      <c r="AV25" s="54"/>
+      <c r="AW25" s="54"/>
       <c r="AX25" s="58"/>
       <c r="AY25" s="54"/>
       <c r="AZ25" s="59"/>
@@ -12597,18 +12936,20 @@
       <c r="BS25" s="81"/>
       <c r="BT25" s="81"/>
     </row>
-    <row r="26" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="26" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A26" s="36"/>
       <c r="B26" s="55"/>
-      <c r="C26" s="62"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
       <c r="G26" s="58"/>
-      <c r="H26" s="103"/>
-      <c r="I26" s="98"/>
-      <c r="J26" s="96"/>
-      <c r="K26" s="98"/>
+      <c r="H26" s="90"/>
+      <c r="I26" s="90" t="s">
+        <v>94</v>
+      </c>
+      <c r="J26" s="97"/>
+      <c r="K26" s="96"/>
       <c r="L26" s="96"/>
       <c r="M26" s="96"/>
       <c r="N26" s="96"/>
@@ -12623,14 +12964,14 @@
       <c r="W26" s="96"/>
       <c r="X26" s="98"/>
       <c r="Y26" s="90"/>
-      <c r="Z26" s="99"/>
-      <c r="AA26" s="90"/>
-      <c r="AB26" s="99"/>
-      <c r="AC26" s="90"/>
+      <c r="Z26" s="90"/>
+      <c r="AA26" s="99"/>
+      <c r="AB26" s="90"/>
+      <c r="AC26" s="100"/>
       <c r="AD26" s="100"/>
-      <c r="AE26" s="100"/>
-      <c r="AF26" s="101"/>
-      <c r="AG26" s="100"/>
+      <c r="AE26" s="101"/>
+      <c r="AF26" s="100"/>
+      <c r="AG26" s="101"/>
       <c r="AH26" s="100"/>
       <c r="AI26" s="102"/>
       <c r="AJ26" s="100"/>
@@ -12642,9 +12983,9 @@
       <c r="AP26" s="101"/>
       <c r="AQ26" s="101"/>
       <c r="AR26" s="101"/>
-      <c r="AS26" s="90"/>
-      <c r="AT26" s="61"/>
-      <c r="AU26" s="54"/>
+      <c r="AS26" s="101"/>
+      <c r="AT26" s="58"/>
+      <c r="AU26" s="58"/>
       <c r="AV26" s="58"/>
       <c r="AW26" s="58"/>
       <c r="AX26" s="58"/>
@@ -12671,10 +13012,10 @@
       <c r="BS26" s="81"/>
       <c r="BT26" s="81"/>
     </row>
-    <row r="27" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="27" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A27" s="36"/>
       <c r="B27" s="55"/>
-      <c r="C27" s="54"/>
+      <c r="C27" s="62"/>
       <c r="D27" s="58"/>
       <c r="E27" s="58"/>
       <c r="F27" s="58"/>
@@ -12697,30 +13038,30 @@
       <c r="W27" s="96"/>
       <c r="X27" s="98"/>
       <c r="Y27" s="90"/>
-      <c r="Z27" s="101"/>
-      <c r="AA27" s="101"/>
-      <c r="AB27" s="101"/>
-      <c r="AC27" s="101"/>
-      <c r="AD27" s="101"/>
-      <c r="AE27" s="101"/>
+      <c r="Z27" s="99"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="99"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="100"/>
+      <c r="AE27" s="100"/>
       <c r="AF27" s="101"/>
-      <c r="AG27" s="101"/>
-      <c r="AH27" s="101"/>
-      <c r="AI27" s="101"/>
-      <c r="AJ27" s="101"/>
+      <c r="AG27" s="100"/>
+      <c r="AH27" s="100"/>
+      <c r="AI27" s="102"/>
+      <c r="AJ27" s="100"/>
       <c r="AK27" s="101"/>
       <c r="AL27" s="101"/>
-      <c r="AM27" s="90"/>
-      <c r="AN27" s="90"/>
-      <c r="AO27" s="90"/>
-      <c r="AP27" s="90"/>
-      <c r="AQ27" s="90"/>
-      <c r="AR27" s="90"/>
+      <c r="AM27" s="101"/>
+      <c r="AN27" s="101"/>
+      <c r="AO27" s="101"/>
+      <c r="AP27" s="101"/>
+      <c r="AQ27" s="101"/>
+      <c r="AR27" s="101"/>
       <c r="AS27" s="90"/>
-      <c r="AT27" s="54"/>
+      <c r="AT27" s="61"/>
       <c r="AU27" s="54"/>
-      <c r="AV27" s="54"/>
-      <c r="AW27" s="54"/>
+      <c r="AV27" s="58"/>
+      <c r="AW27" s="58"/>
       <c r="AX27" s="58"/>
       <c r="AY27" s="54"/>
       <c r="AZ27" s="59"/>
@@ -12745,7 +13086,7 @@
       <c r="BS27" s="81"/>
       <c r="BT27" s="81"/>
     </row>
-    <row r="28" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="28" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A28" s="36"/>
       <c r="B28" s="55"/>
       <c r="C28" s="54"/>
@@ -12819,7 +13160,7 @@
       <c r="BS28" s="81"/>
       <c r="BT28" s="81"/>
     </row>
-    <row r="29" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="29" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A29" s="36"/>
       <c r="B29" s="55"/>
       <c r="C29" s="54"/>
@@ -12893,7 +13234,7 @@
       <c r="BS29" s="81"/>
       <c r="BT29" s="81"/>
     </row>
-    <row r="30" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="30" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A30" s="36"/>
       <c r="B30" s="55"/>
       <c r="C30" s="54"/>
@@ -12952,7 +13293,7 @@
       <c r="BD30" s="34"/>
       <c r="BE30" s="81"/>
       <c r="BF30" s="81"/>
-      <c r="BG30" s="64"/>
+      <c r="BG30" s="81"/>
       <c r="BH30" s="81"/>
       <c r="BI30" s="81"/>
       <c r="BJ30" s="81"/>
@@ -12967,7 +13308,7 @@
       <c r="BS30" s="81"/>
       <c r="BT30" s="81"/>
     </row>
-    <row r="31" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="31" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A31" s="36"/>
       <c r="B31" s="55"/>
       <c r="C31" s="54"/>
@@ -13041,7 +13382,7 @@
       <c r="BS31" s="81"/>
       <c r="BT31" s="81"/>
     </row>
-    <row r="32" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+    <row r="32" spans="1:75" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A32" s="36"/>
       <c r="B32" s="55"/>
       <c r="C32" s="54"/>
@@ -13100,7 +13441,7 @@
       <c r="BD32" s="34"/>
       <c r="BE32" s="81"/>
       <c r="BF32" s="81"/>
-      <c r="BG32" s="81"/>
+      <c r="BG32" s="64"/>
       <c r="BH32" s="81"/>
       <c r="BI32" s="81"/>
       <c r="BJ32" s="81"/>
@@ -13133,9 +13474,7 @@
       <c r="O33" s="96"/>
       <c r="P33" s="96"/>
       <c r="Q33" s="96"/>
-      <c r="R33" s="121" t="s">
-        <v>54</v>
-      </c>
+      <c r="R33" s="96"/>
       <c r="S33" s="96"/>
       <c r="T33" s="96"/>
       <c r="U33" s="96"/>
@@ -13175,7 +13514,7 @@
       <c r="BC33" s="33"/>
       <c r="BD33" s="34"/>
       <c r="BE33" s="81"/>
-      <c r="BF33" s="64"/>
+      <c r="BF33" s="81"/>
       <c r="BG33" s="81"/>
       <c r="BH33" s="81"/>
       <c r="BI33" s="81"/>
@@ -13210,7 +13549,7 @@
       <c r="P34" s="96"/>
       <c r="Q34" s="96"/>
       <c r="R34" s="121" t="s">
-        <v>103</v>
+        <v>54</v>
       </c>
       <c r="S34" s="96"/>
       <c r="T34" s="96"/>
@@ -13252,7 +13591,7 @@
       <c r="BD34" s="34"/>
       <c r="BE34" s="81"/>
       <c r="BF34" s="64"/>
-      <c r="BG34" s="64"/>
+      <c r="BG34" s="81"/>
       <c r="BH34" s="81"/>
       <c r="BI34" s="81"/>
       <c r="BJ34" s="81"/>
@@ -13286,7 +13625,7 @@
       <c r="P35" s="96"/>
       <c r="Q35" s="96"/>
       <c r="R35" s="121" t="s">
-        <v>55</v>
+        <v>103</v>
       </c>
       <c r="S35" s="96"/>
       <c r="T35" s="96"/>
@@ -13326,9 +13665,9 @@
       <c r="BB35" s="32"/>
       <c r="BC35" s="33"/>
       <c r="BD35" s="34"/>
-      <c r="BE35" s="84"/>
-      <c r="BF35" s="81"/>
-      <c r="BG35" s="81"/>
+      <c r="BE35" s="81"/>
+      <c r="BF35" s="64"/>
+      <c r="BG35" s="64"/>
       <c r="BH35" s="81"/>
       <c r="BI35" s="81"/>
       <c r="BJ35" s="81"/>
@@ -13362,7 +13701,7 @@
       <c r="P36" s="96"/>
       <c r="Q36" s="96"/>
       <c r="R36" s="121" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="S36" s="96"/>
       <c r="T36" s="96"/>
@@ -13402,7 +13741,7 @@
       <c r="BB36" s="32"/>
       <c r="BC36" s="33"/>
       <c r="BD36" s="34"/>
-      <c r="BE36" s="81"/>
+      <c r="BE36" s="84"/>
       <c r="BF36" s="81"/>
       <c r="BG36" s="81"/>
       <c r="BH36" s="81"/>
@@ -13421,58 +13760,60 @@
     </row>
     <row r="37" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A37" s="36"/>
-      <c r="B37" s="37"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="35"/>
-      <c r="G37" s="40"/>
-      <c r="H37" s="106"/>
-      <c r="I37" s="106"/>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="106"/>
-      <c r="O37" s="106"/>
-      <c r="P37" s="106"/>
-      <c r="Q37" s="106"/>
-      <c r="R37" s="106"/>
-      <c r="S37" s="106"/>
-      <c r="T37" s="107"/>
-      <c r="U37" s="107"/>
-      <c r="V37" s="107"/>
-      <c r="W37" s="107"/>
-      <c r="X37" s="108"/>
-      <c r="Y37" s="107"/>
-      <c r="Z37" s="107"/>
-      <c r="AA37" s="107"/>
-      <c r="AB37" s="109"/>
-      <c r="AC37" s="107"/>
-      <c r="AD37" s="110"/>
-      <c r="AE37" s="110"/>
-      <c r="AF37" s="110"/>
-      <c r="AG37" s="110"/>
-      <c r="AH37" s="110"/>
-      <c r="AI37" s="106"/>
-      <c r="AJ37" s="107"/>
-      <c r="AK37" s="107"/>
-      <c r="AL37" s="107"/>
-      <c r="AM37" s="107"/>
-      <c r="AN37" s="111"/>
-      <c r="AO37" s="108"/>
-      <c r="AP37" s="108"/>
-      <c r="AQ37" s="107"/>
-      <c r="AR37" s="107"/>
-      <c r="AS37" s="107"/>
-      <c r="AT37" s="43"/>
-      <c r="AU37" s="41"/>
-      <c r="AV37" s="44"/>
-      <c r="AW37" s="44"/>
-      <c r="AX37" s="44"/>
-      <c r="AY37" s="38"/>
-      <c r="AZ37" s="39"/>
-      <c r="BA37" s="39"/>
+      <c r="B37" s="55"/>
+      <c r="C37" s="54"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="103"/>
+      <c r="I37" s="98"/>
+      <c r="J37" s="96"/>
+      <c r="K37" s="98"/>
+      <c r="L37" s="96"/>
+      <c r="M37" s="96"/>
+      <c r="N37" s="96"/>
+      <c r="O37" s="96"/>
+      <c r="P37" s="96"/>
+      <c r="Q37" s="96"/>
+      <c r="R37" s="121" t="s">
+        <v>104</v>
+      </c>
+      <c r="S37" s="96"/>
+      <c r="T37" s="96"/>
+      <c r="U37" s="96"/>
+      <c r="V37" s="96"/>
+      <c r="W37" s="96"/>
+      <c r="X37" s="98"/>
+      <c r="Y37" s="90"/>
+      <c r="Z37" s="101"/>
+      <c r="AA37" s="101"/>
+      <c r="AB37" s="101"/>
+      <c r="AC37" s="101"/>
+      <c r="AD37" s="101"/>
+      <c r="AE37" s="101"/>
+      <c r="AF37" s="101"/>
+      <c r="AG37" s="101"/>
+      <c r="AH37" s="101"/>
+      <c r="AI37" s="101"/>
+      <c r="AJ37" s="101"/>
+      <c r="AK37" s="101"/>
+      <c r="AL37" s="101"/>
+      <c r="AM37" s="90"/>
+      <c r="AN37" s="90"/>
+      <c r="AO37" s="90"/>
+      <c r="AP37" s="90"/>
+      <c r="AQ37" s="90"/>
+      <c r="AR37" s="90"/>
+      <c r="AS37" s="90"/>
+      <c r="AT37" s="54"/>
+      <c r="AU37" s="54"/>
+      <c r="AV37" s="54"/>
+      <c r="AW37" s="54"/>
+      <c r="AX37" s="58"/>
+      <c r="AY37" s="54"/>
+      <c r="AZ37" s="59"/>
+      <c r="BA37" s="59"/>
       <c r="BB37" s="32"/>
       <c r="BC37" s="33"/>
       <c r="BD37" s="34"/>
@@ -13495,16 +13836,14 @@
     </row>
     <row r="38" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A38" s="36"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="54"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="56"/>
-      <c r="G38" s="54"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="34"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="40"/>
       <c r="H38" s="106"/>
-      <c r="I38" s="123" t="s">
-        <v>56</v>
-      </c>
+      <c r="I38" s="106"/>
       <c r="J38" s="106"/>
       <c r="K38" s="106"/>
       <c r="L38" s="106"/>
@@ -13514,43 +13853,41 @@
       <c r="P38" s="106"/>
       <c r="Q38" s="106"/>
       <c r="R38" s="106"/>
-      <c r="S38" s="124" t="s">
-        <v>57</v>
-      </c>
+      <c r="S38" s="106"/>
       <c r="T38" s="107"/>
       <c r="U38" s="107"/>
       <c r="V38" s="107"/>
       <c r="W38" s="107"/>
       <c r="X38" s="108"/>
       <c r="Y38" s="107"/>
-      <c r="Z38" s="106"/>
-      <c r="AA38" s="106"/>
-      <c r="AB38" s="106"/>
-      <c r="AC38" s="106"/>
-      <c r="AD38" s="106"/>
-      <c r="AE38" s="106"/>
-      <c r="AF38" s="106"/>
-      <c r="AG38" s="106"/>
-      <c r="AH38" s="106"/>
+      <c r="Z38" s="107"/>
+      <c r="AA38" s="107"/>
+      <c r="AB38" s="109"/>
+      <c r="AC38" s="107"/>
+      <c r="AD38" s="110"/>
+      <c r="AE38" s="110"/>
+      <c r="AF38" s="110"/>
+      <c r="AG38" s="110"/>
+      <c r="AH38" s="110"/>
       <c r="AI38" s="106"/>
-      <c r="AJ38" s="106"/>
-      <c r="AK38" s="106"/>
-      <c r="AL38" s="106"/>
-      <c r="AM38" s="106"/>
-      <c r="AN38" s="106"/>
-      <c r="AO38" s="106"/>
-      <c r="AP38" s="106"/>
-      <c r="AQ38" s="106"/>
-      <c r="AR38" s="106"/>
-      <c r="AS38" s="106"/>
-      <c r="AT38" s="54"/>
-      <c r="AU38" s="54"/>
-      <c r="AV38" s="54"/>
-      <c r="AW38" s="54"/>
-      <c r="AX38" s="58"/>
-      <c r="AY38" s="54"/>
-      <c r="AZ38" s="59"/>
-      <c r="BA38" s="59"/>
+      <c r="AJ38" s="107"/>
+      <c r="AK38" s="107"/>
+      <c r="AL38" s="107"/>
+      <c r="AM38" s="107"/>
+      <c r="AN38" s="111"/>
+      <c r="AO38" s="108"/>
+      <c r="AP38" s="108"/>
+      <c r="AQ38" s="107"/>
+      <c r="AR38" s="107"/>
+      <c r="AS38" s="107"/>
+      <c r="AT38" s="43"/>
+      <c r="AU38" s="41"/>
+      <c r="AV38" s="44"/>
+      <c r="AW38" s="44"/>
+      <c r="AX38" s="44"/>
+      <c r="AY38" s="38"/>
+      <c r="AZ38" s="39"/>
+      <c r="BA38" s="39"/>
       <c r="BB38" s="32"/>
       <c r="BC38" s="33"/>
       <c r="BD38" s="34"/>
@@ -13575,45 +13912,45 @@
       <c r="A39" s="36"/>
       <c r="B39" s="55"/>
       <c r="C39" s="54"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="119"/>
-      <c r="I39" s="139" t="s">
-        <v>105</v>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="54"/>
+      <c r="H39" s="106"/>
+      <c r="I39" s="123" t="s">
+        <v>56</v>
       </c>
-      <c r="J39" s="112"/>
-      <c r="K39" s="114"/>
-      <c r="L39" s="112"/>
-      <c r="M39" s="112"/>
-      <c r="N39" s="112"/>
-      <c r="O39" s="112"/>
-      <c r="P39" s="112"/>
-      <c r="Q39" s="112"/>
-      <c r="R39" s="112"/>
-      <c r="S39" s="140" t="s">
-        <v>106</v>
+      <c r="J39" s="106"/>
+      <c r="K39" s="106"/>
+      <c r="L39" s="106"/>
+      <c r="M39" s="106"/>
+      <c r="N39" s="106"/>
+      <c r="O39" s="106"/>
+      <c r="P39" s="106"/>
+      <c r="Q39" s="106"/>
+      <c r="R39" s="106"/>
+      <c r="S39" s="124" t="s">
+        <v>57</v>
       </c>
-      <c r="T39" s="112"/>
-      <c r="U39" s="112"/>
-      <c r="V39" s="112"/>
-      <c r="W39" s="112"/>
-      <c r="X39" s="114"/>
-      <c r="Y39" s="106"/>
-      <c r="Z39" s="117"/>
-      <c r="AA39" s="117"/>
-      <c r="AB39" s="117"/>
-      <c r="AC39" s="117"/>
-      <c r="AD39" s="117"/>
-      <c r="AE39" s="117"/>
-      <c r="AF39" s="117"/>
-      <c r="AG39" s="117"/>
-      <c r="AH39" s="117"/>
-      <c r="AI39" s="117"/>
-      <c r="AJ39" s="117"/>
-      <c r="AK39" s="117"/>
-      <c r="AL39" s="117"/>
+      <c r="T39" s="107"/>
+      <c r="U39" s="107"/>
+      <c r="V39" s="107"/>
+      <c r="W39" s="107"/>
+      <c r="X39" s="108"/>
+      <c r="Y39" s="107"/>
+      <c r="Z39" s="106"/>
+      <c r="AA39" s="106"/>
+      <c r="AB39" s="106"/>
+      <c r="AC39" s="106"/>
+      <c r="AD39" s="106"/>
+      <c r="AE39" s="106"/>
+      <c r="AF39" s="106"/>
+      <c r="AG39" s="106"/>
+      <c r="AH39" s="106"/>
+      <c r="AI39" s="106"/>
+      <c r="AJ39" s="106"/>
+      <c r="AK39" s="106"/>
+      <c r="AL39" s="106"/>
       <c r="AM39" s="106"/>
       <c r="AN39" s="106"/>
       <c r="AO39" s="106"/>
@@ -13652,24 +13989,26 @@
     <row r="40" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A40" s="36"/>
       <c r="B40" s="55"/>
-      <c r="C40" s="60"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
       <c r="G40" s="58"/>
-      <c r="H40" s="106"/>
-      <c r="I40" s="112"/>
-      <c r="J40" s="113"/>
-      <c r="K40" s="112"/>
+      <c r="H40" s="119"/>
+      <c r="I40" s="139" t="s">
+        <v>105</v>
+      </c>
+      <c r="J40" s="112"/>
+      <c r="K40" s="114"/>
       <c r="L40" s="112"/>
       <c r="M40" s="112"/>
       <c r="N40" s="112"/>
       <c r="O40" s="112"/>
       <c r="P40" s="112"/>
       <c r="Q40" s="112"/>
-      <c r="R40" s="106"/>
-      <c r="S40" s="124" t="s">
-        <v>58</v>
+      <c r="R40" s="112"/>
+      <c r="S40" s="140" t="s">
+        <v>106</v>
       </c>
       <c r="T40" s="112"/>
       <c r="U40" s="112"/>
@@ -13677,30 +14016,30 @@
       <c r="W40" s="112"/>
       <c r="X40" s="114"/>
       <c r="Y40" s="106"/>
-      <c r="Z40" s="106"/>
-      <c r="AA40" s="115"/>
-      <c r="AB40" s="106"/>
-      <c r="AC40" s="116"/>
-      <c r="AD40" s="116"/>
+      <c r="Z40" s="117"/>
+      <c r="AA40" s="117"/>
+      <c r="AB40" s="117"/>
+      <c r="AC40" s="117"/>
+      <c r="AD40" s="117"/>
       <c r="AE40" s="117"/>
-      <c r="AF40" s="116"/>
+      <c r="AF40" s="117"/>
       <c r="AG40" s="117"/>
-      <c r="AH40" s="116"/>
-      <c r="AI40" s="118"/>
-      <c r="AJ40" s="116"/>
+      <c r="AH40" s="117"/>
+      <c r="AI40" s="117"/>
+      <c r="AJ40" s="117"/>
       <c r="AK40" s="117"/>
       <c r="AL40" s="117"/>
-      <c r="AM40" s="117"/>
-      <c r="AN40" s="117"/>
-      <c r="AO40" s="117"/>
-      <c r="AP40" s="117"/>
-      <c r="AQ40" s="117"/>
-      <c r="AR40" s="117"/>
-      <c r="AS40" s="117"/>
-      <c r="AT40" s="58"/>
-      <c r="AU40" s="58"/>
-      <c r="AV40" s="58"/>
-      <c r="AW40" s="58"/>
+      <c r="AM40" s="106"/>
+      <c r="AN40" s="106"/>
+      <c r="AO40" s="106"/>
+      <c r="AP40" s="106"/>
+      <c r="AQ40" s="106"/>
+      <c r="AR40" s="106"/>
+      <c r="AS40" s="106"/>
+      <c r="AT40" s="54"/>
+      <c r="AU40" s="54"/>
+      <c r="AV40" s="54"/>
+      <c r="AW40" s="54"/>
       <c r="AX40" s="58"/>
       <c r="AY40" s="54"/>
       <c r="AZ40" s="59"/>
@@ -13728,24 +14067,24 @@
     <row r="41" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A41" s="36"/>
       <c r="B41" s="55"/>
-      <c r="C41" s="54"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
       <c r="G41" s="58"/>
-      <c r="H41" s="119"/>
-      <c r="I41" s="139"/>
-      <c r="J41" s="112"/>
-      <c r="K41" s="114"/>
+      <c r="H41" s="106"/>
+      <c r="I41" s="112"/>
+      <c r="J41" s="113"/>
+      <c r="K41" s="112"/>
       <c r="L41" s="112"/>
       <c r="M41" s="112"/>
       <c r="N41" s="112"/>
       <c r="O41" s="112"/>
       <c r="P41" s="112"/>
       <c r="Q41" s="112"/>
-      <c r="R41" s="112"/>
-      <c r="S41" s="140" t="s">
-        <v>107</v>
+      <c r="R41" s="106"/>
+      <c r="S41" s="124" t="s">
+        <v>58</v>
       </c>
       <c r="T41" s="112"/>
       <c r="U41" s="112"/>
@@ -13753,30 +14092,30 @@
       <c r="W41" s="112"/>
       <c r="X41" s="114"/>
       <c r="Y41" s="106"/>
-      <c r="Z41" s="117"/>
-      <c r="AA41" s="117"/>
-      <c r="AB41" s="117"/>
-      <c r="AC41" s="117"/>
-      <c r="AD41" s="117"/>
+      <c r="Z41" s="106"/>
+      <c r="AA41" s="115"/>
+      <c r="AB41" s="106"/>
+      <c r="AC41" s="116"/>
+      <c r="AD41" s="116"/>
       <c r="AE41" s="117"/>
-      <c r="AF41" s="117"/>
+      <c r="AF41" s="116"/>
       <c r="AG41" s="117"/>
-      <c r="AH41" s="117"/>
-      <c r="AI41" s="117"/>
-      <c r="AJ41" s="117"/>
+      <c r="AH41" s="116"/>
+      <c r="AI41" s="118"/>
+      <c r="AJ41" s="116"/>
       <c r="AK41" s="117"/>
       <c r="AL41" s="117"/>
-      <c r="AM41" s="106"/>
-      <c r="AN41" s="106"/>
-      <c r="AO41" s="106"/>
-      <c r="AP41" s="106"/>
-      <c r="AQ41" s="106"/>
-      <c r="AR41" s="106"/>
-      <c r="AS41" s="106"/>
-      <c r="AT41" s="54"/>
-      <c r="AU41" s="54"/>
-      <c r="AV41" s="54"/>
-      <c r="AW41" s="54"/>
+      <c r="AM41" s="117"/>
+      <c r="AN41" s="117"/>
+      <c r="AO41" s="117"/>
+      <c r="AP41" s="117"/>
+      <c r="AQ41" s="117"/>
+      <c r="AR41" s="117"/>
+      <c r="AS41" s="117"/>
+      <c r="AT41" s="58"/>
+      <c r="AU41" s="58"/>
+      <c r="AV41" s="58"/>
+      <c r="AW41" s="58"/>
       <c r="AX41" s="58"/>
       <c r="AY41" s="54"/>
       <c r="AZ41" s="59"/>
@@ -13804,13 +14143,13 @@
     <row r="42" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A42" s="36"/>
       <c r="B42" s="55"/>
-      <c r="C42" s="62"/>
+      <c r="C42" s="54"/>
       <c r="D42" s="58"/>
       <c r="E42" s="58"/>
       <c r="F42" s="58"/>
       <c r="G42" s="58"/>
       <c r="H42" s="119"/>
-      <c r="I42" s="114"/>
+      <c r="I42" s="139"/>
       <c r="J42" s="112"/>
       <c r="K42" s="114"/>
       <c r="L42" s="112"/>
@@ -13819,40 +14158,40 @@
       <c r="O42" s="112"/>
       <c r="P42" s="112"/>
       <c r="Q42" s="112"/>
-      <c r="R42" s="106"/>
-      <c r="S42" s="124" t="s">
-        <v>59</v>
+      <c r="R42" s="112"/>
+      <c r="S42" s="140" t="s">
+        <v>107</v>
       </c>
       <c r="T42" s="112"/>
       <c r="U42" s="112"/>
-      <c r="V42" s="25"/>
+      <c r="V42" s="112"/>
       <c r="W42" s="112"/>
       <c r="X42" s="114"/>
       <c r="Y42" s="106"/>
-      <c r="Z42" s="115"/>
-      <c r="AA42" s="106"/>
-      <c r="AB42" s="115"/>
-      <c r="AC42" s="106"/>
-      <c r="AD42" s="116"/>
-      <c r="AE42" s="116"/>
+      <c r="Z42" s="117"/>
+      <c r="AA42" s="117"/>
+      <c r="AB42" s="117"/>
+      <c r="AC42" s="117"/>
+      <c r="AD42" s="117"/>
+      <c r="AE42" s="117"/>
       <c r="AF42" s="117"/>
-      <c r="AG42" s="116"/>
-      <c r="AH42" s="116"/>
-      <c r="AI42" s="118"/>
-      <c r="AJ42" s="116"/>
+      <c r="AG42" s="117"/>
+      <c r="AH42" s="117"/>
+      <c r="AI42" s="117"/>
+      <c r="AJ42" s="117"/>
       <c r="AK42" s="117"/>
       <c r="AL42" s="117"/>
-      <c r="AM42" s="117"/>
-      <c r="AN42" s="117"/>
-      <c r="AO42" s="117"/>
-      <c r="AP42" s="117"/>
-      <c r="AQ42" s="117"/>
-      <c r="AR42" s="117"/>
+      <c r="AM42" s="106"/>
+      <c r="AN42" s="106"/>
+      <c r="AO42" s="106"/>
+      <c r="AP42" s="106"/>
+      <c r="AQ42" s="106"/>
+      <c r="AR42" s="106"/>
       <c r="AS42" s="106"/>
-      <c r="AT42" s="61"/>
+      <c r="AT42" s="54"/>
       <c r="AU42" s="54"/>
-      <c r="AV42" s="58"/>
-      <c r="AW42" s="58"/>
+      <c r="AV42" s="54"/>
+      <c r="AW42" s="54"/>
       <c r="AX42" s="58"/>
       <c r="AY42" s="54"/>
       <c r="AZ42" s="59"/>
@@ -13880,13 +14219,13 @@
     <row r="43" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A43" s="36"/>
       <c r="B43" s="55"/>
-      <c r="C43" s="54"/>
+      <c r="C43" s="62"/>
       <c r="D43" s="58"/>
       <c r="E43" s="58"/>
       <c r="F43" s="58"/>
       <c r="G43" s="58"/>
       <c r="H43" s="119"/>
-      <c r="I43" s="139"/>
+      <c r="I43" s="114"/>
       <c r="J43" s="112"/>
       <c r="K43" s="114"/>
       <c r="L43" s="112"/>
@@ -13895,40 +14234,40 @@
       <c r="O43" s="112"/>
       <c r="P43" s="112"/>
       <c r="Q43" s="112"/>
-      <c r="R43" s="112"/>
-      <c r="S43" s="140" t="s">
-        <v>108</v>
+      <c r="R43" s="106"/>
+      <c r="S43" s="124" t="s">
+        <v>59</v>
       </c>
       <c r="T43" s="112"/>
       <c r="U43" s="112"/>
-      <c r="V43" s="112"/>
+      <c r="V43" s="25"/>
       <c r="W43" s="112"/>
       <c r="X43" s="114"/>
       <c r="Y43" s="106"/>
-      <c r="Z43" s="117"/>
-      <c r="AA43" s="117"/>
-      <c r="AB43" s="117"/>
-      <c r="AC43" s="117"/>
-      <c r="AD43" s="117"/>
-      <c r="AE43" s="117"/>
+      <c r="Z43" s="115"/>
+      <c r="AA43" s="106"/>
+      <c r="AB43" s="115"/>
+      <c r="AC43" s="106"/>
+      <c r="AD43" s="116"/>
+      <c r="AE43" s="116"/>
       <c r="AF43" s="117"/>
-      <c r="AG43" s="117"/>
-      <c r="AH43" s="117"/>
-      <c r="AI43" s="117"/>
-      <c r="AJ43" s="117"/>
+      <c r="AG43" s="116"/>
+      <c r="AH43" s="116"/>
+      <c r="AI43" s="118"/>
+      <c r="AJ43" s="116"/>
       <c r="AK43" s="117"/>
       <c r="AL43" s="117"/>
-      <c r="AM43" s="106"/>
-      <c r="AN43" s="106"/>
-      <c r="AO43" s="106"/>
-      <c r="AP43" s="106"/>
-      <c r="AQ43" s="106"/>
-      <c r="AR43" s="106"/>
+      <c r="AM43" s="117"/>
+      <c r="AN43" s="117"/>
+      <c r="AO43" s="117"/>
+      <c r="AP43" s="117"/>
+      <c r="AQ43" s="117"/>
+      <c r="AR43" s="117"/>
       <c r="AS43" s="106"/>
-      <c r="AT43" s="54"/>
+      <c r="AT43" s="61"/>
       <c r="AU43" s="54"/>
-      <c r="AV43" s="54"/>
-      <c r="AW43" s="54"/>
+      <c r="AV43" s="58"/>
+      <c r="AW43" s="58"/>
       <c r="AX43" s="58"/>
       <c r="AY43" s="54"/>
       <c r="AZ43" s="59"/>
@@ -13937,7 +14276,7 @@
       <c r="BC43" s="33"/>
       <c r="BD43" s="34"/>
       <c r="BE43" s="81"/>
-      <c r="BF43" s="64"/>
+      <c r="BF43" s="81"/>
       <c r="BG43" s="81"/>
       <c r="BH43" s="81"/>
       <c r="BI43" s="81"/>
@@ -13962,7 +14301,7 @@
       <c r="F44" s="58"/>
       <c r="G44" s="58"/>
       <c r="H44" s="119"/>
-      <c r="I44" s="114"/>
+      <c r="I44" s="139"/>
       <c r="J44" s="112"/>
       <c r="K44" s="114"/>
       <c r="L44" s="112"/>
@@ -13971,9 +14310,9 @@
       <c r="O44" s="112"/>
       <c r="P44" s="112"/>
       <c r="Q44" s="112"/>
-      <c r="R44" s="106"/>
-      <c r="S44" s="124" t="s">
-        <v>60</v>
+      <c r="R44" s="112"/>
+      <c r="S44" s="140" t="s">
+        <v>108</v>
       </c>
       <c r="T44" s="112"/>
       <c r="U44" s="112"/>
@@ -14014,7 +14353,7 @@
       <c r="BD44" s="34"/>
       <c r="BE44" s="81"/>
       <c r="BF44" s="64"/>
-      <c r="BG44" s="84"/>
+      <c r="BG44" s="81"/>
       <c r="BH44" s="81"/>
       <c r="BI44" s="81"/>
       <c r="BJ44" s="81"/>
@@ -14038,7 +14377,7 @@
       <c r="F45" s="58"/>
       <c r="G45" s="58"/>
       <c r="H45" s="119"/>
-      <c r="I45" s="139"/>
+      <c r="I45" s="114"/>
       <c r="J45" s="112"/>
       <c r="K45" s="114"/>
       <c r="L45" s="112"/>
@@ -14047,9 +14386,9 @@
       <c r="O45" s="112"/>
       <c r="P45" s="112"/>
       <c r="Q45" s="112"/>
-      <c r="R45" s="112"/>
-      <c r="S45" s="140" t="s">
-        <v>109</v>
+      <c r="R45" s="106"/>
+      <c r="S45" s="124" t="s">
+        <v>60</v>
       </c>
       <c r="T45" s="112"/>
       <c r="U45" s="112"/>
@@ -14088,9 +14427,9 @@
       <c r="BB45" s="32"/>
       <c r="BC45" s="33"/>
       <c r="BD45" s="34"/>
-      <c r="BE45" s="84"/>
-      <c r="BF45" s="81"/>
-      <c r="BG45" s="81"/>
+      <c r="BE45" s="81"/>
+      <c r="BF45" s="64"/>
+      <c r="BG45" s="84"/>
       <c r="BH45" s="81"/>
       <c r="BI45" s="81"/>
       <c r="BJ45" s="81"/>
@@ -14114,7 +14453,7 @@
       <c r="F46" s="58"/>
       <c r="G46" s="58"/>
       <c r="H46" s="119"/>
-      <c r="I46" s="114"/>
+      <c r="I46" s="139"/>
       <c r="J46" s="112"/>
       <c r="K46" s="114"/>
       <c r="L46" s="112"/>
@@ -14123,9 +14462,9 @@
       <c r="O46" s="112"/>
       <c r="P46" s="112"/>
       <c r="Q46" s="112"/>
-      <c r="R46" s="106"/>
-      <c r="S46" s="124" t="s">
-        <v>61</v>
+      <c r="R46" s="112"/>
+      <c r="S46" s="140" t="s">
+        <v>109</v>
       </c>
       <c r="T46" s="112"/>
       <c r="U46" s="112"/>
@@ -14164,7 +14503,7 @@
       <c r="BB46" s="32"/>
       <c r="BC46" s="33"/>
       <c r="BD46" s="34"/>
-      <c r="BE46" s="81"/>
+      <c r="BE46" s="84"/>
       <c r="BF46" s="81"/>
       <c r="BG46" s="81"/>
       <c r="BH46" s="81"/>
@@ -14190,7 +14529,7 @@
       <c r="F47" s="58"/>
       <c r="G47" s="58"/>
       <c r="H47" s="119"/>
-      <c r="I47" s="139"/>
+      <c r="I47" s="114"/>
       <c r="J47" s="112"/>
       <c r="K47" s="114"/>
       <c r="L47" s="112"/>
@@ -14199,8 +14538,10 @@
       <c r="O47" s="112"/>
       <c r="P47" s="112"/>
       <c r="Q47" s="112"/>
-      <c r="R47" s="112"/>
-      <c r="S47" s="140"/>
+      <c r="R47" s="106"/>
+      <c r="S47" s="124" t="s">
+        <v>61</v>
+      </c>
       <c r="T47" s="112"/>
       <c r="U47" s="112"/>
       <c r="V47" s="112"/>
@@ -14264,7 +14605,7 @@
       <c r="F48" s="58"/>
       <c r="G48" s="58"/>
       <c r="H48" s="119"/>
-      <c r="I48" s="114"/>
+      <c r="I48" s="139"/>
       <c r="J48" s="112"/>
       <c r="K48" s="114"/>
       <c r="L48" s="112"/>
@@ -14273,10 +14614,8 @@
       <c r="O48" s="112"/>
       <c r="P48" s="112"/>
       <c r="Q48" s="112"/>
-      <c r="R48" s="106"/>
-      <c r="S48" s="124" t="s">
-        <v>62</v>
-      </c>
+      <c r="R48" s="112"/>
+      <c r="S48" s="140"/>
       <c r="T48" s="112"/>
       <c r="U48" s="112"/>
       <c r="V48" s="112"/>
@@ -14340,7 +14679,7 @@
       <c r="F49" s="58"/>
       <c r="G49" s="58"/>
       <c r="H49" s="119"/>
-      <c r="I49" s="139"/>
+      <c r="I49" s="114"/>
       <c r="J49" s="112"/>
       <c r="K49" s="114"/>
       <c r="L49" s="112"/>
@@ -14349,8 +14688,10 @@
       <c r="O49" s="112"/>
       <c r="P49" s="112"/>
       <c r="Q49" s="112"/>
-      <c r="R49" s="112"/>
-      <c r="S49" s="140"/>
+      <c r="R49" s="106"/>
+      <c r="S49" s="124" t="s">
+        <v>62</v>
+      </c>
       <c r="T49" s="112"/>
       <c r="U49" s="112"/>
       <c r="V49" s="112"/>
@@ -14414,7 +14755,7 @@
       <c r="F50" s="58"/>
       <c r="G50" s="58"/>
       <c r="H50" s="119"/>
-      <c r="I50" s="114"/>
+      <c r="I50" s="139"/>
       <c r="J50" s="112"/>
       <c r="K50" s="114"/>
       <c r="L50" s="112"/>
@@ -14423,10 +14764,8 @@
       <c r="O50" s="112"/>
       <c r="P50" s="112"/>
       <c r="Q50" s="112"/>
-      <c r="R50" s="106"/>
-      <c r="S50" s="124" t="s">
-        <v>63</v>
-      </c>
+      <c r="R50" s="112"/>
+      <c r="S50" s="140"/>
       <c r="T50" s="112"/>
       <c r="U50" s="112"/>
       <c r="V50" s="112"/>
@@ -14467,6 +14806,7 @@
       <c r="BE50" s="81"/>
       <c r="BF50" s="81"/>
       <c r="BG50" s="81"/>
+      <c r="BH50" s="81"/>
       <c r="BI50" s="81"/>
       <c r="BJ50" s="81"/>
       <c r="BK50" s="81"/>
@@ -14498,9 +14838,9 @@
       <c r="O51" s="112"/>
       <c r="P51" s="112"/>
       <c r="Q51" s="112"/>
-      <c r="R51" s="112"/>
-      <c r="S51" s="141" t="s">
-        <v>95</v>
+      <c r="R51" s="106"/>
+      <c r="S51" s="124" t="s">
+        <v>63</v>
       </c>
       <c r="T51" s="112"/>
       <c r="U51" s="112"/>
@@ -14541,6 +14881,19 @@
       <c r="BD51" s="34"/>
       <c r="BE51" s="81"/>
       <c r="BF51" s="81"/>
+      <c r="BG51" s="81"/>
+      <c r="BI51" s="81"/>
+      <c r="BJ51" s="81"/>
+      <c r="BK51" s="81"/>
+      <c r="BL51" s="81"/>
+      <c r="BM51" s="81"/>
+      <c r="BN51" s="81"/>
+      <c r="BO51" s="81"/>
+      <c r="BP51" s="81"/>
+      <c r="BQ51" s="81"/>
+      <c r="BR51" s="81"/>
+      <c r="BS51" s="81"/>
+      <c r="BT51" s="81"/>
     </row>
     <row r="52" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A52" s="36"/>
@@ -14560,8 +14913,10 @@
       <c r="O52" s="112"/>
       <c r="P52" s="112"/>
       <c r="Q52" s="112"/>
-      <c r="R52" s="122"/>
-      <c r="S52" s="112"/>
+      <c r="R52" s="112"/>
+      <c r="S52" s="141" t="s">
+        <v>95</v>
+      </c>
       <c r="T52" s="112"/>
       <c r="U52" s="112"/>
       <c r="V52" s="112"/>
@@ -14601,20 +14956,6 @@
       <c r="BD52" s="34"/>
       <c r="BE52" s="81"/>
       <c r="BF52" s="81"/>
-      <c r="BG52" s="81"/>
-      <c r="BH52" s="81"/>
-      <c r="BI52" s="81"/>
-      <c r="BJ52" s="81"/>
-      <c r="BK52" s="81"/>
-      <c r="BL52" s="81"/>
-      <c r="BM52" s="81"/>
-      <c r="BN52" s="81"/>
-      <c r="BO52" s="81"/>
-      <c r="BP52" s="81"/>
-      <c r="BQ52" s="81"/>
-      <c r="BR52" s="81"/>
-      <c r="BS52" s="81"/>
-      <c r="BT52" s="81"/>
     </row>
     <row r="53" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A53" s="36"/>
@@ -14692,58 +15033,58 @@
     </row>
     <row r="54" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A54" s="36"/>
-      <c r="B54" s="37"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="54"/>
-      <c r="D54" s="54"/>
-      <c r="E54" s="54"/>
-      <c r="F54" s="54"/>
-      <c r="G54" s="54"/>
-      <c r="H54" s="90"/>
-      <c r="I54" s="90"/>
-      <c r="J54" s="90"/>
-      <c r="K54" s="90"/>
-      <c r="L54" s="90"/>
-      <c r="M54" s="90"/>
-      <c r="N54" s="90"/>
-      <c r="O54" s="90"/>
-      <c r="P54" s="90"/>
-      <c r="Q54" s="90"/>
-      <c r="R54" s="90"/>
-      <c r="S54" s="90"/>
-      <c r="T54" s="91"/>
-      <c r="U54" s="91"/>
-      <c r="V54" s="91"/>
-      <c r="W54" s="91"/>
-      <c r="X54" s="92"/>
-      <c r="Y54" s="91"/>
-      <c r="Z54" s="91"/>
-      <c r="AA54" s="91"/>
-      <c r="AB54" s="93"/>
-      <c r="AC54" s="91"/>
-      <c r="AD54" s="94"/>
-      <c r="AE54" s="94"/>
-      <c r="AF54" s="94"/>
-      <c r="AG54" s="94"/>
-      <c r="AH54" s="94"/>
-      <c r="AI54" s="90"/>
-      <c r="AJ54" s="91"/>
-      <c r="AK54" s="91"/>
-      <c r="AL54" s="91"/>
-      <c r="AM54" s="91"/>
-      <c r="AN54" s="95"/>
-      <c r="AO54" s="92"/>
-      <c r="AP54" s="92"/>
-      <c r="AQ54" s="91"/>
-      <c r="AR54" s="91"/>
-      <c r="AS54" s="91"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="119"/>
+      <c r="I54" s="114"/>
+      <c r="J54" s="112"/>
+      <c r="K54" s="114"/>
+      <c r="L54" s="112"/>
+      <c r="M54" s="112"/>
+      <c r="N54" s="112"/>
+      <c r="O54" s="112"/>
+      <c r="P54" s="112"/>
+      <c r="Q54" s="112"/>
+      <c r="R54" s="122"/>
+      <c r="S54" s="112"/>
+      <c r="T54" s="112"/>
+      <c r="U54" s="112"/>
+      <c r="V54" s="112"/>
+      <c r="W54" s="112"/>
+      <c r="X54" s="114"/>
+      <c r="Y54" s="106"/>
+      <c r="Z54" s="117"/>
+      <c r="AA54" s="117"/>
+      <c r="AB54" s="117"/>
+      <c r="AC54" s="117"/>
+      <c r="AD54" s="117"/>
+      <c r="AE54" s="117"/>
+      <c r="AF54" s="117"/>
+      <c r="AG54" s="117"/>
+      <c r="AH54" s="117"/>
+      <c r="AI54" s="117"/>
+      <c r="AJ54" s="117"/>
+      <c r="AK54" s="117"/>
+      <c r="AL54" s="117"/>
+      <c r="AM54" s="106"/>
+      <c r="AN54" s="106"/>
+      <c r="AO54" s="106"/>
+      <c r="AP54" s="106"/>
+      <c r="AQ54" s="106"/>
+      <c r="AR54" s="106"/>
+      <c r="AS54" s="106"/>
       <c r="AT54" s="54"/>
       <c r="AU54" s="54"/>
       <c r="AV54" s="54"/>
       <c r="AW54" s="54"/>
-      <c r="AX54" s="54"/>
+      <c r="AX54" s="58"/>
       <c r="AY54" s="54"/>
-      <c r="AZ54" s="39"/>
-      <c r="BA54" s="39"/>
+      <c r="AZ54" s="59"/>
+      <c r="BA54" s="59"/>
       <c r="BB54" s="32"/>
       <c r="BC54" s="33"/>
       <c r="BD54" s="34"/>
@@ -14766,16 +15107,14 @@
     </row>
     <row r="55" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
       <c r="A55" s="36"/>
-      <c r="B55" s="55"/>
+      <c r="B55" s="37"/>
       <c r="C55" s="54"/>
       <c r="D55" s="54"/>
       <c r="E55" s="54"/>
       <c r="F55" s="54"/>
       <c r="G55" s="54"/>
       <c r="H55" s="90"/>
-      <c r="I55" s="125" t="s">
-        <v>110</v>
-      </c>
+      <c r="I55" s="90"/>
       <c r="J55" s="90"/>
       <c r="K55" s="90"/>
       <c r="L55" s="90"/>
@@ -14792,34 +15131,34 @@
       <c r="W55" s="91"/>
       <c r="X55" s="92"/>
       <c r="Y55" s="91"/>
-      <c r="Z55" s="90"/>
-      <c r="AA55" s="90"/>
-      <c r="AB55" s="90"/>
-      <c r="AC55" s="90"/>
-      <c r="AD55" s="90"/>
-      <c r="AE55" s="90"/>
-      <c r="AF55" s="90"/>
-      <c r="AG55" s="90"/>
-      <c r="AH55" s="90"/>
+      <c r="Z55" s="91"/>
+      <c r="AA55" s="91"/>
+      <c r="AB55" s="93"/>
+      <c r="AC55" s="91"/>
+      <c r="AD55" s="94"/>
+      <c r="AE55" s="94"/>
+      <c r="AF55" s="94"/>
+      <c r="AG55" s="94"/>
+      <c r="AH55" s="94"/>
       <c r="AI55" s="90"/>
-      <c r="AJ55" s="90"/>
-      <c r="AK55" s="90"/>
-      <c r="AL55" s="90"/>
-      <c r="AM55" s="90"/>
-      <c r="AN55" s="90"/>
-      <c r="AO55" s="90"/>
-      <c r="AP55" s="90"/>
-      <c r="AQ55" s="90"/>
-      <c r="AR55" s="90"/>
-      <c r="AS55" s="90"/>
+      <c r="AJ55" s="91"/>
+      <c r="AK55" s="91"/>
+      <c r="AL55" s="91"/>
+      <c r="AM55" s="91"/>
+      <c r="AN55" s="95"/>
+      <c r="AO55" s="92"/>
+      <c r="AP55" s="92"/>
+      <c r="AQ55" s="91"/>
+      <c r="AR55" s="91"/>
+      <c r="AS55" s="91"/>
       <c r="AT55" s="54"/>
       <c r="AU55" s="54"/>
       <c r="AV55" s="54"/>
       <c r="AW55" s="54"/>
       <c r="AX55" s="54"/>
       <c r="AY55" s="54"/>
-      <c r="AZ55" s="59"/>
-      <c r="BA55" s="59"/>
+      <c r="AZ55" s="39"/>
+      <c r="BA55" s="39"/>
       <c r="BB55" s="32"/>
       <c r="BC55" s="33"/>
       <c r="BD55" s="34"/>
@@ -14850,44 +15189,44 @@
       <c r="G56" s="54"/>
       <c r="H56" s="90"/>
       <c r="I56" s="125" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
-      <c r="J56" s="97"/>
-      <c r="K56" s="96"/>
-      <c r="L56" s="96"/>
-      <c r="M56" s="96"/>
-      <c r="N56" s="96"/>
-      <c r="O56" s="96"/>
-      <c r="P56" s="96"/>
-      <c r="Q56" s="96"/>
-      <c r="R56" s="96"/>
-      <c r="S56" s="96"/>
-      <c r="T56" s="96"/>
-      <c r="U56" s="96"/>
-      <c r="V56" s="96"/>
-      <c r="W56" s="96"/>
-      <c r="X56" s="98"/>
-      <c r="Y56" s="90"/>
+      <c r="J56" s="90"/>
+      <c r="K56" s="90"/>
+      <c r="L56" s="90"/>
+      <c r="M56" s="90"/>
+      <c r="N56" s="90"/>
+      <c r="O56" s="90"/>
+      <c r="P56" s="90"/>
+      <c r="Q56" s="90"/>
+      <c r="R56" s="90"/>
+      <c r="S56" s="90"/>
+      <c r="T56" s="91"/>
+      <c r="U56" s="91"/>
+      <c r="V56" s="91"/>
+      <c r="W56" s="91"/>
+      <c r="X56" s="92"/>
+      <c r="Y56" s="91"/>
       <c r="Z56" s="90"/>
-      <c r="AA56" s="99"/>
+      <c r="AA56" s="90"/>
       <c r="AB56" s="90"/>
-      <c r="AC56" s="100"/>
-      <c r="AD56" s="100"/>
-      <c r="AE56" s="101"/>
-      <c r="AF56" s="100"/>
-      <c r="AG56" s="101"/>
-      <c r="AH56" s="100"/>
-      <c r="AI56" s="102"/>
-      <c r="AJ56" s="100"/>
-      <c r="AK56" s="101"/>
-      <c r="AL56" s="101"/>
-      <c r="AM56" s="101"/>
-      <c r="AN56" s="101"/>
-      <c r="AO56" s="101"/>
-      <c r="AP56" s="101"/>
-      <c r="AQ56" s="101"/>
-      <c r="AR56" s="101"/>
-      <c r="AS56" s="101"/>
+      <c r="AC56" s="90"/>
+      <c r="AD56" s="90"/>
+      <c r="AE56" s="90"/>
+      <c r="AF56" s="90"/>
+      <c r="AG56" s="90"/>
+      <c r="AH56" s="90"/>
+      <c r="AI56" s="90"/>
+      <c r="AJ56" s="90"/>
+      <c r="AK56" s="90"/>
+      <c r="AL56" s="90"/>
+      <c r="AM56" s="90"/>
+      <c r="AN56" s="90"/>
+      <c r="AO56" s="90"/>
+      <c r="AP56" s="90"/>
+      <c r="AQ56" s="90"/>
+      <c r="AR56" s="90"/>
+      <c r="AS56" s="90"/>
       <c r="AT56" s="54"/>
       <c r="AU56" s="54"/>
       <c r="AV56" s="54"/>
@@ -14924,12 +15263,12 @@
       <c r="E57" s="54"/>
       <c r="F57" s="54"/>
       <c r="G57" s="54"/>
-      <c r="H57" s="103"/>
-      <c r="I57" s="126" t="s">
-        <v>64</v>
+      <c r="H57" s="90"/>
+      <c r="I57" s="125" t="s">
+        <v>111</v>
       </c>
-      <c r="J57" s="96"/>
-      <c r="K57" s="98"/>
+      <c r="J57" s="97"/>
+      <c r="K57" s="96"/>
       <c r="L57" s="96"/>
       <c r="M57" s="96"/>
       <c r="N57" s="96"/>
@@ -14944,14 +15283,14 @@
       <c r="W57" s="96"/>
       <c r="X57" s="98"/>
       <c r="Y57" s="90"/>
-      <c r="Z57" s="99"/>
-      <c r="AA57" s="90"/>
-      <c r="AB57" s="99"/>
-      <c r="AC57" s="90"/>
+      <c r="Z57" s="90"/>
+      <c r="AA57" s="99"/>
+      <c r="AB57" s="90"/>
+      <c r="AC57" s="100"/>
       <c r="AD57" s="100"/>
-      <c r="AE57" s="100"/>
-      <c r="AF57" s="101"/>
-      <c r="AG57" s="100"/>
+      <c r="AE57" s="101"/>
+      <c r="AF57" s="100"/>
+      <c r="AG57" s="101"/>
       <c r="AH57" s="100"/>
       <c r="AI57" s="102"/>
       <c r="AJ57" s="100"/>
@@ -14963,7 +15302,7 @@
       <c r="AP57" s="101"/>
       <c r="AQ57" s="101"/>
       <c r="AR57" s="101"/>
-      <c r="AS57" s="90"/>
+      <c r="AS57" s="101"/>
       <c r="AT57" s="54"/>
       <c r="AU57" s="54"/>
       <c r="AV57" s="54"/>
@@ -15002,7 +15341,7 @@
       <c r="G58" s="54"/>
       <c r="H58" s="103"/>
       <c r="I58" s="126" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="J58" s="96"/>
       <c r="K58" s="98"/>
@@ -15020,25 +15359,25 @@
       <c r="W58" s="96"/>
       <c r="X58" s="98"/>
       <c r="Y58" s="90"/>
-      <c r="Z58" s="101"/>
-      <c r="AA58" s="101"/>
-      <c r="AB58" s="101"/>
-      <c r="AC58" s="101"/>
-      <c r="AD58" s="101"/>
-      <c r="AE58" s="101"/>
+      <c r="Z58" s="99"/>
+      <c r="AA58" s="90"/>
+      <c r="AB58" s="99"/>
+      <c r="AC58" s="90"/>
+      <c r="AD58" s="100"/>
+      <c r="AE58" s="100"/>
       <c r="AF58" s="101"/>
-      <c r="AG58" s="101"/>
-      <c r="AH58" s="101"/>
-      <c r="AI58" s="101"/>
-      <c r="AJ58" s="101"/>
+      <c r="AG58" s="100"/>
+      <c r="AH58" s="100"/>
+      <c r="AI58" s="102"/>
+      <c r="AJ58" s="100"/>
       <c r="AK58" s="101"/>
       <c r="AL58" s="101"/>
-      <c r="AM58" s="90"/>
-      <c r="AN58" s="90"/>
-      <c r="AO58" s="90"/>
-      <c r="AP58" s="90"/>
-      <c r="AQ58" s="90"/>
-      <c r="AR58" s="90"/>
+      <c r="AM58" s="101"/>
+      <c r="AN58" s="101"/>
+      <c r="AO58" s="101"/>
+      <c r="AP58" s="101"/>
+      <c r="AQ58" s="101"/>
+      <c r="AR58" s="101"/>
       <c r="AS58" s="90"/>
       <c r="AT58" s="54"/>
       <c r="AU58" s="54"/>
@@ -15077,7 +15416,9 @@
       <c r="F59" s="54"/>
       <c r="G59" s="54"/>
       <c r="H59" s="103"/>
-      <c r="I59" s="98"/>
+      <c r="I59" s="126" t="s">
+        <v>112</v>
+      </c>
       <c r="J59" s="96"/>
       <c r="K59" s="98"/>
       <c r="L59" s="96"/>
@@ -15094,25 +15435,25 @@
       <c r="W59" s="96"/>
       <c r="X59" s="98"/>
       <c r="Y59" s="90"/>
-      <c r="Z59" s="99"/>
-      <c r="AA59" s="90"/>
-      <c r="AB59" s="99"/>
-      <c r="AC59" s="90"/>
-      <c r="AD59" s="100"/>
-      <c r="AE59" s="100"/>
+      <c r="Z59" s="101"/>
+      <c r="AA59" s="101"/>
+      <c r="AB59" s="101"/>
+      <c r="AC59" s="101"/>
+      <c r="AD59" s="101"/>
+      <c r="AE59" s="101"/>
       <c r="AF59" s="101"/>
-      <c r="AG59" s="100"/>
-      <c r="AH59" s="100"/>
-      <c r="AI59" s="102"/>
-      <c r="AJ59" s="100"/>
+      <c r="AG59" s="101"/>
+      <c r="AH59" s="101"/>
+      <c r="AI59" s="101"/>
+      <c r="AJ59" s="101"/>
       <c r="AK59" s="101"/>
       <c r="AL59" s="101"/>
-      <c r="AM59" s="101"/>
-      <c r="AN59" s="101"/>
-      <c r="AO59" s="101"/>
-      <c r="AP59" s="101"/>
-      <c r="AQ59" s="101"/>
-      <c r="AR59" s="101"/>
+      <c r="AM59" s="90"/>
+      <c r="AN59" s="90"/>
+      <c r="AO59" s="90"/>
+      <c r="AP59" s="90"/>
+      <c r="AQ59" s="90"/>
+      <c r="AR59" s="90"/>
       <c r="AS59" s="90"/>
       <c r="AT59" s="54"/>
       <c r="AU59" s="54"/>
@@ -15127,6 +15468,19 @@
       <c r="BD59" s="34"/>
       <c r="BE59" s="81"/>
       <c r="BF59" s="81"/>
+      <c r="BG59" s="81"/>
+      <c r="BH59" s="81"/>
+      <c r="BI59" s="81"/>
+      <c r="BJ59" s="81"/>
+      <c r="BK59" s="81"/>
+      <c r="BL59" s="81"/>
+      <c r="BM59" s="81"/>
+      <c r="BN59" s="81"/>
+      <c r="BO59" s="81"/>
+      <c r="BP59" s="81"/>
+      <c r="BQ59" s="81"/>
+      <c r="BR59" s="81"/>
+      <c r="BS59" s="81"/>
       <c r="BT59" s="81"/>
     </row>
     <row r="60" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
@@ -15155,25 +15509,25 @@
       <c r="W60" s="96"/>
       <c r="X60" s="98"/>
       <c r="Y60" s="90"/>
-      <c r="Z60" s="101"/>
-      <c r="AA60" s="101"/>
-      <c r="AB60" s="101"/>
-      <c r="AC60" s="101"/>
-      <c r="AD60" s="101"/>
-      <c r="AE60" s="101"/>
+      <c r="Z60" s="99"/>
+      <c r="AA60" s="90"/>
+      <c r="AB60" s="99"/>
+      <c r="AC60" s="90"/>
+      <c r="AD60" s="100"/>
+      <c r="AE60" s="100"/>
       <c r="AF60" s="101"/>
-      <c r="AG60" s="101"/>
-      <c r="AH60" s="101"/>
-      <c r="AI60" s="101"/>
-      <c r="AJ60" s="101"/>
+      <c r="AG60" s="100"/>
+      <c r="AH60" s="100"/>
+      <c r="AI60" s="102"/>
+      <c r="AJ60" s="100"/>
       <c r="AK60" s="101"/>
       <c r="AL60" s="101"/>
-      <c r="AM60" s="90"/>
-      <c r="AN60" s="90"/>
-      <c r="AO60" s="90"/>
-      <c r="AP60" s="90"/>
-      <c r="AQ60" s="90"/>
-      <c r="AR60" s="90"/>
+      <c r="AM60" s="101"/>
+      <c r="AN60" s="101"/>
+      <c r="AO60" s="101"/>
+      <c r="AP60" s="101"/>
+      <c r="AQ60" s="101"/>
+      <c r="AR60" s="101"/>
       <c r="AS60" s="90"/>
       <c r="AT60" s="54"/>
       <c r="AU60" s="54"/>
@@ -15188,19 +15542,6 @@
       <c r="BD60" s="34"/>
       <c r="BE60" s="81"/>
       <c r="BF60" s="81"/>
-      <c r="BG60" s="64"/>
-      <c r="BH60" s="64"/>
-      <c r="BI60" s="83"/>
-      <c r="BJ60" s="82"/>
-      <c r="BK60" s="82"/>
-      <c r="BL60" s="82"/>
-      <c r="BM60" s="82"/>
-      <c r="BN60" s="82"/>
-      <c r="BO60" s="82"/>
-      <c r="BP60" s="82"/>
-      <c r="BQ60" s="82"/>
-      <c r="BR60" s="81"/>
-      <c r="BS60" s="81"/>
       <c r="BT60" s="81"/>
     </row>
     <row r="61" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
@@ -15211,61 +15552,61 @@
       <c r="E61" s="54"/>
       <c r="F61" s="54"/>
       <c r="G61" s="54"/>
-      <c r="H61" s="67"/>
-      <c r="I61" s="67"/>
-      <c r="J61" s="67"/>
-      <c r="K61" s="67"/>
-      <c r="L61" s="67"/>
-      <c r="M61" s="67"/>
-      <c r="N61" s="67"/>
-      <c r="O61" s="67"/>
-      <c r="P61" s="67"/>
-      <c r="Q61" s="67"/>
-      <c r="R61" s="67"/>
-      <c r="S61" s="67"/>
-      <c r="T61" s="67"/>
-      <c r="U61" s="67"/>
-      <c r="V61" s="67"/>
-      <c r="W61" s="67"/>
-      <c r="X61" s="67"/>
-      <c r="Y61" s="67"/>
-      <c r="Z61" s="67"/>
-      <c r="AA61" s="67"/>
-      <c r="AB61" s="67"/>
-      <c r="AC61" s="67"/>
-      <c r="AD61" s="67"/>
-      <c r="AE61" s="67"/>
-      <c r="AF61" s="67"/>
-      <c r="AG61" s="67"/>
-      <c r="AH61" s="67"/>
-      <c r="AI61" s="67"/>
-      <c r="AJ61" s="67"/>
-      <c r="AK61" s="67"/>
-      <c r="AL61" s="67"/>
-      <c r="AM61" s="67"/>
-      <c r="AN61" s="67"/>
-      <c r="AO61" s="67"/>
-      <c r="AP61" s="67"/>
-      <c r="AQ61" s="67"/>
-      <c r="AR61" s="67"/>
-      <c r="AS61" s="68"/>
-      <c r="AT61" s="61"/>
+      <c r="H61" s="103"/>
+      <c r="I61" s="98"/>
+      <c r="J61" s="96"/>
+      <c r="K61" s="98"/>
+      <c r="L61" s="96"/>
+      <c r="M61" s="96"/>
+      <c r="N61" s="96"/>
+      <c r="O61" s="96"/>
+      <c r="P61" s="96"/>
+      <c r="Q61" s="96"/>
+      <c r="R61" s="96"/>
+      <c r="S61" s="96"/>
+      <c r="T61" s="96"/>
+      <c r="U61" s="96"/>
+      <c r="V61" s="96"/>
+      <c r="W61" s="96"/>
+      <c r="X61" s="98"/>
+      <c r="Y61" s="90"/>
+      <c r="Z61" s="101"/>
+      <c r="AA61" s="101"/>
+      <c r="AB61" s="101"/>
+      <c r="AC61" s="101"/>
+      <c r="AD61" s="101"/>
+      <c r="AE61" s="101"/>
+      <c r="AF61" s="101"/>
+      <c r="AG61" s="101"/>
+      <c r="AH61" s="101"/>
+      <c r="AI61" s="101"/>
+      <c r="AJ61" s="101"/>
+      <c r="AK61" s="101"/>
+      <c r="AL61" s="101"/>
+      <c r="AM61" s="90"/>
+      <c r="AN61" s="90"/>
+      <c r="AO61" s="90"/>
+      <c r="AP61" s="90"/>
+      <c r="AQ61" s="90"/>
+      <c r="AR61" s="90"/>
+      <c r="AS61" s="90"/>
+      <c r="AT61" s="54"/>
       <c r="AU61" s="54"/>
-      <c r="AV61" s="58"/>
-      <c r="AW61" s="58"/>
-      <c r="AX61" s="58"/>
+      <c r="AV61" s="54"/>
+      <c r="AW61" s="54"/>
+      <c r="AX61" s="54"/>
       <c r="AY61" s="54"/>
       <c r="AZ61" s="59"/>
       <c r="BA61" s="59"/>
-      <c r="BB61" s="49"/>
-      <c r="BC61" s="50"/>
-      <c r="BD61" s="35"/>
+      <c r="BB61" s="32"/>
+      <c r="BC61" s="33"/>
+      <c r="BD61" s="34"/>
       <c r="BE61" s="81"/>
       <c r="BF61" s="81"/>
       <c r="BG61" s="64"/>
       <c r="BH61" s="64"/>
       <c r="BI61" s="83"/>
-      <c r="BJ61" s="64"/>
+      <c r="BJ61" s="82"/>
       <c r="BK61" s="82"/>
       <c r="BL61" s="82"/>
       <c r="BM61" s="82"/>
@@ -15336,17 +15677,17 @@
       <c r="BD62" s="35"/>
       <c r="BE62" s="81"/>
       <c r="BF62" s="81"/>
-      <c r="BG62" s="81"/>
-      <c r="BH62" s="84"/>
-      <c r="BI62" s="81"/>
-      <c r="BJ62" s="81"/>
-      <c r="BK62" s="81"/>
-      <c r="BL62" s="81"/>
-      <c r="BM62" s="81"/>
-      <c r="BN62" s="81"/>
-      <c r="BO62" s="81"/>
-      <c r="BP62" s="81"/>
-      <c r="BQ62" s="81"/>
+      <c r="BG62" s="64"/>
+      <c r="BH62" s="64"/>
+      <c r="BI62" s="83"/>
+      <c r="BJ62" s="64"/>
+      <c r="BK62" s="82"/>
+      <c r="BL62" s="82"/>
+      <c r="BM62" s="82"/>
+      <c r="BN62" s="82"/>
+      <c r="BO62" s="82"/>
+      <c r="BP62" s="82"/>
+      <c r="BQ62" s="82"/>
       <c r="BR62" s="81"/>
       <c r="BS62" s="81"/>
       <c r="BT62" s="81"/>
@@ -15355,63 +15696,63 @@
       <c r="A63" s="36"/>
       <c r="B63" s="55"/>
       <c r="C63" s="54"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="119"/>
-      <c r="I63" s="114"/>
-      <c r="J63" s="112"/>
-      <c r="K63" s="114"/>
-      <c r="L63" s="112"/>
-      <c r="M63" s="112"/>
-      <c r="N63" s="112"/>
-      <c r="O63" s="112"/>
-      <c r="P63" s="112"/>
-      <c r="Q63" s="112"/>
-      <c r="R63" s="112"/>
-      <c r="S63" s="112"/>
-      <c r="T63" s="112"/>
-      <c r="U63" s="112"/>
-      <c r="V63" s="112"/>
-      <c r="W63" s="112"/>
-      <c r="X63" s="114"/>
-      <c r="Y63" s="106"/>
-      <c r="Z63" s="117"/>
-      <c r="AA63" s="117"/>
-      <c r="AB63" s="117"/>
-      <c r="AC63" s="117"/>
-      <c r="AD63" s="117"/>
-      <c r="AE63" s="117"/>
-      <c r="AF63" s="117"/>
-      <c r="AG63" s="117"/>
-      <c r="AH63" s="117"/>
-      <c r="AI63" s="117"/>
-      <c r="AJ63" s="117"/>
-      <c r="AK63" s="117"/>
-      <c r="AL63" s="117"/>
-      <c r="AM63" s="106"/>
-      <c r="AN63" s="106"/>
-      <c r="AO63" s="106"/>
-      <c r="AP63" s="106"/>
-      <c r="AQ63" s="106"/>
-      <c r="AR63" s="106"/>
-      <c r="AS63" s="106"/>
-      <c r="AT63" s="54"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="54"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="54"/>
+      <c r="H63" s="67"/>
+      <c r="I63" s="67"/>
+      <c r="J63" s="67"/>
+      <c r="K63" s="67"/>
+      <c r="L63" s="67"/>
+      <c r="M63" s="67"/>
+      <c r="N63" s="67"/>
+      <c r="O63" s="67"/>
+      <c r="P63" s="67"/>
+      <c r="Q63" s="67"/>
+      <c r="R63" s="67"/>
+      <c r="S63" s="67"/>
+      <c r="T63" s="67"/>
+      <c r="U63" s="67"/>
+      <c r="V63" s="67"/>
+      <c r="W63" s="67"/>
+      <c r="X63" s="67"/>
+      <c r="Y63" s="67"/>
+      <c r="Z63" s="67"/>
+      <c r="AA63" s="67"/>
+      <c r="AB63" s="67"/>
+      <c r="AC63" s="67"/>
+      <c r="AD63" s="67"/>
+      <c r="AE63" s="67"/>
+      <c r="AF63" s="67"/>
+      <c r="AG63" s="67"/>
+      <c r="AH63" s="67"/>
+      <c r="AI63" s="67"/>
+      <c r="AJ63" s="67"/>
+      <c r="AK63" s="67"/>
+      <c r="AL63" s="67"/>
+      <c r="AM63" s="67"/>
+      <c r="AN63" s="67"/>
+      <c r="AO63" s="67"/>
+      <c r="AP63" s="67"/>
+      <c r="AQ63" s="67"/>
+      <c r="AR63" s="67"/>
+      <c r="AS63" s="68"/>
+      <c r="AT63" s="61"/>
       <c r="AU63" s="54"/>
-      <c r="AV63" s="54"/>
-      <c r="AW63" s="54"/>
+      <c r="AV63" s="58"/>
+      <c r="AW63" s="58"/>
       <c r="AX63" s="58"/>
       <c r="AY63" s="54"/>
       <c r="AZ63" s="59"/>
       <c r="BA63" s="59"/>
-      <c r="BB63" s="32"/>
-      <c r="BC63" s="33"/>
-      <c r="BD63" s="34"/>
+      <c r="BB63" s="49"/>
+      <c r="BC63" s="50"/>
+      <c r="BD63" s="35"/>
       <c r="BE63" s="81"/>
       <c r="BF63" s="81"/>
       <c r="BG63" s="81"/>
-      <c r="BH63" s="81"/>
+      <c r="BH63" s="84"/>
       <c r="BI63" s="81"/>
       <c r="BJ63" s="81"/>
       <c r="BK63" s="81"/>
@@ -15485,7 +15826,7 @@
       <c r="BE64" s="81"/>
       <c r="BF64" s="81"/>
       <c r="BG64" s="81"/>
-      <c r="BH64" s="84"/>
+      <c r="BH64" s="81"/>
       <c r="BI64" s="81"/>
       <c r="BJ64" s="81"/>
       <c r="BK64" s="81"/>
@@ -15517,7 +15858,7 @@
       <c r="O65" s="112"/>
       <c r="P65" s="112"/>
       <c r="Q65" s="112"/>
-      <c r="R65" s="122"/>
+      <c r="R65" s="112"/>
       <c r="S65" s="112"/>
       <c r="T65" s="112"/>
       <c r="U65" s="112"/>
@@ -15558,8 +15899,8 @@
       <c r="BD65" s="34"/>
       <c r="BE65" s="81"/>
       <c r="BF65" s="81"/>
-      <c r="BG65" s="64"/>
-      <c r="BH65" s="64"/>
+      <c r="BG65" s="81"/>
+      <c r="BH65" s="84"/>
       <c r="BI65" s="81"/>
       <c r="BJ65" s="81"/>
       <c r="BK65" s="81"/>
@@ -15665,7 +16006,7 @@
       <c r="O67" s="112"/>
       <c r="P67" s="112"/>
       <c r="Q67" s="112"/>
-      <c r="R67" s="112"/>
+      <c r="R67" s="122"/>
       <c r="S67" s="112"/>
       <c r="T67" s="112"/>
       <c r="U67" s="112"/>
@@ -15725,63 +16066,63 @@
       <c r="A68" s="36"/>
       <c r="B68" s="55"/>
       <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="67"/>
-      <c r="I68" s="67"/>
-      <c r="J68" s="67"/>
-      <c r="K68" s="67"/>
-      <c r="L68" s="67"/>
-      <c r="M68" s="67"/>
-      <c r="N68" s="67"/>
-      <c r="O68" s="67"/>
-      <c r="P68" s="67"/>
-      <c r="Q68" s="67"/>
-      <c r="R68" s="67"/>
-      <c r="S68" s="67"/>
-      <c r="T68" s="67"/>
-      <c r="U68" s="67"/>
-      <c r="V68" s="67"/>
-      <c r="W68" s="67"/>
-      <c r="X68" s="67"/>
-      <c r="Y68" s="67"/>
-      <c r="Z68" s="67"/>
-      <c r="AA68" s="67"/>
-      <c r="AB68" s="67"/>
-      <c r="AC68" s="67"/>
-      <c r="AD68" s="67"/>
-      <c r="AE68" s="67"/>
-      <c r="AF68" s="67"/>
-      <c r="AG68" s="67"/>
-      <c r="AH68" s="67"/>
-      <c r="AI68" s="67"/>
-      <c r="AJ68" s="67"/>
-      <c r="AK68" s="67"/>
-      <c r="AL68" s="67"/>
-      <c r="AM68" s="67"/>
-      <c r="AN68" s="67"/>
-      <c r="AO68" s="67"/>
-      <c r="AP68" s="67"/>
-      <c r="AQ68" s="67"/>
-      <c r="AR68" s="67"/>
-      <c r="AS68" s="68"/>
-      <c r="AT68" s="61"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="119"/>
+      <c r="I68" s="114"/>
+      <c r="J68" s="112"/>
+      <c r="K68" s="114"/>
+      <c r="L68" s="112"/>
+      <c r="M68" s="112"/>
+      <c r="N68" s="112"/>
+      <c r="O68" s="112"/>
+      <c r="P68" s="112"/>
+      <c r="Q68" s="112"/>
+      <c r="R68" s="112"/>
+      <c r="S68" s="112"/>
+      <c r="T68" s="112"/>
+      <c r="U68" s="112"/>
+      <c r="V68" s="112"/>
+      <c r="W68" s="112"/>
+      <c r="X68" s="114"/>
+      <c r="Y68" s="106"/>
+      <c r="Z68" s="117"/>
+      <c r="AA68" s="117"/>
+      <c r="AB68" s="117"/>
+      <c r="AC68" s="117"/>
+      <c r="AD68" s="117"/>
+      <c r="AE68" s="117"/>
+      <c r="AF68" s="117"/>
+      <c r="AG68" s="117"/>
+      <c r="AH68" s="117"/>
+      <c r="AI68" s="117"/>
+      <c r="AJ68" s="117"/>
+      <c r="AK68" s="117"/>
+      <c r="AL68" s="117"/>
+      <c r="AM68" s="106"/>
+      <c r="AN68" s="106"/>
+      <c r="AO68" s="106"/>
+      <c r="AP68" s="106"/>
+      <c r="AQ68" s="106"/>
+      <c r="AR68" s="106"/>
+      <c r="AS68" s="106"/>
+      <c r="AT68" s="54"/>
       <c r="AU68" s="54"/>
-      <c r="AV68" s="58"/>
-      <c r="AW68" s="58"/>
+      <c r="AV68" s="54"/>
+      <c r="AW68" s="54"/>
       <c r="AX68" s="58"/>
       <c r="AY68" s="54"/>
       <c r="AZ68" s="59"/>
       <c r="BA68" s="59"/>
-      <c r="BB68" s="49"/>
-      <c r="BC68" s="50"/>
-      <c r="BD68" s="35"/>
+      <c r="BB68" s="32"/>
+      <c r="BC68" s="33"/>
+      <c r="BD68" s="34"/>
       <c r="BE68" s="81"/>
       <c r="BF68" s="81"/>
-      <c r="BG68" s="81"/>
-      <c r="BH68" s="81"/>
+      <c r="BG68" s="64"/>
+      <c r="BH68" s="64"/>
       <c r="BI68" s="81"/>
       <c r="BJ68" s="81"/>
       <c r="BK68" s="81"/>
@@ -15795,63 +16136,63 @@
       <c r="BS68" s="81"/>
       <c r="BT68" s="81"/>
     </row>
-    <row r="69" spans="1:72" s="80" customFormat="1" ht="15">
-      <c r="A69" s="52"/>
-      <c r="B69" s="135"/>
-      <c r="C69" s="86"/>
-      <c r="D69" s="86"/>
-      <c r="E69" s="86"/>
-      <c r="F69" s="86"/>
-      <c r="G69" s="86"/>
-      <c r="H69" s="86"/>
-      <c r="I69" s="86"/>
-      <c r="J69" s="86"/>
-      <c r="K69" s="86"/>
-      <c r="L69" s="86"/>
-      <c r="M69" s="86"/>
-      <c r="N69" s="86"/>
-      <c r="O69" s="86"/>
-      <c r="P69" s="86"/>
-      <c r="Q69" s="86"/>
-      <c r="R69" s="86"/>
-      <c r="S69" s="87"/>
-      <c r="T69" s="87"/>
-      <c r="U69" s="87"/>
-      <c r="V69" s="87"/>
-      <c r="W69" s="86"/>
-      <c r="X69" s="86"/>
-      <c r="Y69" s="87"/>
-      <c r="Z69" s="87"/>
-      <c r="AA69" s="86"/>
-      <c r="AB69" s="86"/>
-      <c r="AC69" s="86"/>
-      <c r="AD69" s="87"/>
-      <c r="AE69" s="87"/>
-      <c r="AF69" s="87"/>
-      <c r="AG69" s="87"/>
-      <c r="AH69" s="87"/>
-      <c r="AI69" s="87"/>
-      <c r="AJ69" s="87"/>
-      <c r="AK69" s="87"/>
-      <c r="AL69" s="87"/>
-      <c r="AM69" s="87"/>
-      <c r="AN69" s="87"/>
-      <c r="AO69" s="87"/>
-      <c r="AP69" s="87"/>
-      <c r="AQ69" s="87"/>
-      <c r="AR69" s="87"/>
-      <c r="AS69" s="87"/>
-      <c r="AT69" s="87"/>
-      <c r="AU69" s="87"/>
-      <c r="AV69" s="87"/>
-      <c r="AW69" s="87"/>
-      <c r="AX69" s="87"/>
-      <c r="AY69" s="85"/>
-      <c r="AZ69" s="66"/>
-      <c r="BA69" s="66"/>
-      <c r="BB69" s="88"/>
+    <row r="69" spans="1:72" s="80" customFormat="1" ht="12.5" customHeight="1">
+      <c r="A69" s="36"/>
+      <c r="B69" s="55"/>
+      <c r="C69" s="54"/>
+      <c r="D69" s="54"/>
+      <c r="E69" s="54"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="54"/>
+      <c r="H69" s="67"/>
+      <c r="I69" s="67"/>
+      <c r="J69" s="67"/>
+      <c r="K69" s="67"/>
+      <c r="L69" s="67"/>
+      <c r="M69" s="67"/>
+      <c r="N69" s="67"/>
+      <c r="O69" s="67"/>
+      <c r="P69" s="67"/>
+      <c r="Q69" s="67"/>
+      <c r="R69" s="67"/>
+      <c r="S69" s="67"/>
+      <c r="T69" s="67"/>
+      <c r="U69" s="67"/>
+      <c r="V69" s="67"/>
+      <c r="W69" s="67"/>
+      <c r="X69" s="67"/>
+      <c r="Y69" s="67"/>
+      <c r="Z69" s="67"/>
+      <c r="AA69" s="67"/>
+      <c r="AB69" s="67"/>
+      <c r="AC69" s="67"/>
+      <c r="AD69" s="67"/>
+      <c r="AE69" s="67"/>
+      <c r="AF69" s="67"/>
+      <c r="AG69" s="67"/>
+      <c r="AH69" s="67"/>
+      <c r="AI69" s="67"/>
+      <c r="AJ69" s="67"/>
+      <c r="AK69" s="67"/>
+      <c r="AL69" s="67"/>
+      <c r="AM69" s="67"/>
+      <c r="AN69" s="67"/>
+      <c r="AO69" s="67"/>
+      <c r="AP69" s="67"/>
+      <c r="AQ69" s="67"/>
+      <c r="AR69" s="67"/>
+      <c r="AS69" s="68"/>
+      <c r="AT69" s="61"/>
+      <c r="AU69" s="54"/>
+      <c r="AV69" s="58"/>
+      <c r="AW69" s="58"/>
+      <c r="AX69" s="58"/>
+      <c r="AY69" s="54"/>
+      <c r="AZ69" s="59"/>
+      <c r="BA69" s="59"/>
+      <c r="BB69" s="49"/>
       <c r="BC69" s="50"/>
-      <c r="BD69" s="51"/>
+      <c r="BD69" s="35"/>
       <c r="BE69" s="81"/>
       <c r="BF69" s="81"/>
       <c r="BG69" s="81"/>
@@ -15870,66 +16211,66 @@
       <c r="BT69" s="81"/>
     </row>
     <row r="70" spans="1:72" s="80" customFormat="1" ht="15">
-      <c r="A70" s="35"/>
-      <c r="B70" s="35"/>
-      <c r="C70" s="35"/>
-      <c r="D70" s="35"/>
-      <c r="E70" s="35"/>
-      <c r="F70" s="35"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="35"/>
-      <c r="I70" s="35"/>
-      <c r="J70" s="35"/>
-      <c r="K70" s="35"/>
-      <c r="L70" s="35"/>
-      <c r="M70" s="35"/>
-      <c r="N70" s="35"/>
-      <c r="O70" s="35"/>
-      <c r="P70" s="35"/>
-      <c r="Q70" s="35"/>
-      <c r="R70" s="35"/>
-      <c r="S70" s="53"/>
-      <c r="T70" s="53"/>
-      <c r="U70" s="53"/>
-      <c r="V70" s="53"/>
-      <c r="W70" s="35"/>
-      <c r="X70" s="35"/>
-      <c r="Y70" s="53"/>
-      <c r="Z70" s="53"/>
-      <c r="AA70" s="35"/>
-      <c r="AB70" s="35"/>
-      <c r="AC70" s="35"/>
-      <c r="AD70" s="53"/>
-      <c r="AE70" s="53"/>
-      <c r="AF70" s="53"/>
-      <c r="AG70" s="53"/>
-      <c r="AH70" s="53"/>
-      <c r="AI70" s="53"/>
-      <c r="AJ70" s="53"/>
-      <c r="AK70" s="53"/>
-      <c r="AL70" s="53"/>
-      <c r="AM70" s="53"/>
-      <c r="AN70" s="53"/>
-      <c r="AO70" s="53"/>
-      <c r="AP70" s="53"/>
-      <c r="AQ70" s="53"/>
-      <c r="AR70" s="53"/>
-      <c r="AS70" s="53"/>
-      <c r="AT70" s="53"/>
-      <c r="AU70" s="53"/>
-      <c r="AV70" s="53"/>
-      <c r="AW70" s="53"/>
-      <c r="AX70" s="53"/>
-      <c r="AY70" s="53"/>
-      <c r="AZ70" s="53"/>
-      <c r="BA70" s="53"/>
-      <c r="BB70" s="53"/>
-      <c r="BC70" s="53"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="135"/>
+      <c r="C70" s="86"/>
+      <c r="D70" s="86"/>
+      <c r="E70" s="86"/>
+      <c r="F70" s="86"/>
+      <c r="G70" s="86"/>
+      <c r="H70" s="86"/>
+      <c r="I70" s="86"/>
+      <c r="J70" s="86"/>
+      <c r="K70" s="86"/>
+      <c r="L70" s="86"/>
+      <c r="M70" s="86"/>
+      <c r="N70" s="86"/>
+      <c r="O70" s="86"/>
+      <c r="P70" s="86"/>
+      <c r="Q70" s="86"/>
+      <c r="R70" s="86"/>
+      <c r="S70" s="87"/>
+      <c r="T70" s="87"/>
+      <c r="U70" s="87"/>
+      <c r="V70" s="87"/>
+      <c r="W70" s="86"/>
+      <c r="X70" s="86"/>
+      <c r="Y70" s="87"/>
+      <c r="Z70" s="87"/>
+      <c r="AA70" s="86"/>
+      <c r="AB70" s="86"/>
+      <c r="AC70" s="86"/>
+      <c r="AD70" s="87"/>
+      <c r="AE70" s="87"/>
+      <c r="AF70" s="87"/>
+      <c r="AG70" s="87"/>
+      <c r="AH70" s="87"/>
+      <c r="AI70" s="87"/>
+      <c r="AJ70" s="87"/>
+      <c r="AK70" s="87"/>
+      <c r="AL70" s="87"/>
+      <c r="AM70" s="87"/>
+      <c r="AN70" s="87"/>
+      <c r="AO70" s="87"/>
+      <c r="AP70" s="87"/>
+      <c r="AQ70" s="87"/>
+      <c r="AR70" s="87"/>
+      <c r="AS70" s="87"/>
+      <c r="AT70" s="87"/>
+      <c r="AU70" s="87"/>
+      <c r="AV70" s="87"/>
+      <c r="AW70" s="87"/>
+      <c r="AX70" s="87"/>
+      <c r="AY70" s="85"/>
+      <c r="AZ70" s="66"/>
+      <c r="BA70" s="66"/>
+      <c r="BB70" s="88"/>
+      <c r="BC70" s="50"/>
       <c r="BD70" s="51"/>
       <c r="BE70" s="81"/>
       <c r="BF70" s="81"/>
       <c r="BG70" s="81"/>
-      <c r="BH70" s="127"/>
+      <c r="BH70" s="81"/>
       <c r="BI70" s="81"/>
       <c r="BJ70" s="81"/>
       <c r="BK70" s="81"/>
@@ -16001,18 +16342,18 @@
       <c r="BC71" s="53"/>
       <c r="BD71" s="51"/>
       <c r="BE71" s="81"/>
-      <c r="BF71" s="64"/>
-      <c r="BG71" s="64"/>
-      <c r="BH71" s="64"/>
-      <c r="BI71" s="83"/>
-      <c r="BJ71" s="64"/>
-      <c r="BK71" s="82"/>
-      <c r="BL71" s="82"/>
-      <c r="BM71" s="82"/>
-      <c r="BN71" s="82"/>
-      <c r="BO71" s="82"/>
-      <c r="BP71" s="82"/>
-      <c r="BQ71" s="82"/>
+      <c r="BF71" s="81"/>
+      <c r="BG71" s="81"/>
+      <c r="BH71" s="127"/>
+      <c r="BI71" s="81"/>
+      <c r="BJ71" s="81"/>
+      <c r="BK71" s="81"/>
+      <c r="BL71" s="81"/>
+      <c r="BM71" s="81"/>
+      <c r="BN71" s="81"/>
+      <c r="BO71" s="81"/>
+      <c r="BP71" s="81"/>
+      <c r="BQ71" s="81"/>
       <c r="BR71" s="81"/>
       <c r="BS71" s="81"/>
       <c r="BT71" s="81"/>
@@ -16075,18 +16416,18 @@
       <c r="BC72" s="53"/>
       <c r="BD72" s="51"/>
       <c r="BE72" s="81"/>
-      <c r="BF72" s="81"/>
-      <c r="BG72" s="81"/>
-      <c r="BH72" s="84"/>
-      <c r="BI72" s="81"/>
-      <c r="BJ72" s="81"/>
-      <c r="BK72" s="81"/>
-      <c r="BL72" s="81"/>
-      <c r="BM72" s="81"/>
-      <c r="BN72" s="81"/>
-      <c r="BO72" s="81"/>
-      <c r="BP72" s="81"/>
-      <c r="BQ72" s="81"/>
+      <c r="BF72" s="64"/>
+      <c r="BG72" s="64"/>
+      <c r="BH72" s="64"/>
+      <c r="BI72" s="83"/>
+      <c r="BJ72" s="64"/>
+      <c r="BK72" s="82"/>
+      <c r="BL72" s="82"/>
+      <c r="BM72" s="82"/>
+      <c r="BN72" s="82"/>
+      <c r="BO72" s="82"/>
+      <c r="BP72" s="82"/>
+      <c r="BQ72" s="82"/>
       <c r="BR72" s="81"/>
       <c r="BS72" s="81"/>
       <c r="BT72" s="81"/>
@@ -16149,9 +16490,9 @@
       <c r="BC73" s="53"/>
       <c r="BD73" s="51"/>
       <c r="BE73" s="81"/>
-      <c r="BF73" s="64"/>
+      <c r="BF73" s="81"/>
       <c r="BG73" s="81"/>
-      <c r="BH73" s="81"/>
+      <c r="BH73" s="84"/>
       <c r="BI73" s="81"/>
       <c r="BJ73" s="81"/>
       <c r="BK73" s="81"/>
@@ -16223,9 +16564,9 @@
       <c r="BC74" s="53"/>
       <c r="BD74" s="51"/>
       <c r="BE74" s="81"/>
-      <c r="BF74" s="81"/>
+      <c r="BF74" s="64"/>
       <c r="BG74" s="81"/>
-      <c r="BH74" s="84"/>
+      <c r="BH74" s="81"/>
       <c r="BI74" s="81"/>
       <c r="BJ74" s="81"/>
       <c r="BK74" s="81"/>
@@ -16298,8 +16639,8 @@
       <c r="BD75" s="51"/>
       <c r="BE75" s="81"/>
       <c r="BF75" s="81"/>
-      <c r="BG75" s="64"/>
-      <c r="BH75" s="64"/>
+      <c r="BG75" s="81"/>
+      <c r="BH75" s="84"/>
       <c r="BI75" s="81"/>
       <c r="BJ75" s="81"/>
       <c r="BK75" s="81"/>
@@ -16445,7 +16786,7 @@
       <c r="BC77" s="53"/>
       <c r="BD77" s="51"/>
       <c r="BE77" s="81"/>
-      <c r="BF77" s="84"/>
+      <c r="BF77" s="81"/>
       <c r="BG77" s="64"/>
       <c r="BH77" s="64"/>
       <c r="BI77" s="81"/>
@@ -16519,9 +16860,9 @@
       <c r="BC78" s="53"/>
       <c r="BD78" s="51"/>
       <c r="BE78" s="81"/>
-      <c r="BF78" s="81"/>
-      <c r="BG78" s="81"/>
-      <c r="BH78" s="81"/>
+      <c r="BF78" s="84"/>
+      <c r="BG78" s="64"/>
+      <c r="BH78" s="64"/>
       <c r="BI78" s="81"/>
       <c r="BJ78" s="81"/>
       <c r="BK78" s="81"/>
@@ -16669,7 +17010,7 @@
       <c r="BE80" s="81"/>
       <c r="BF80" s="81"/>
       <c r="BG80" s="81"/>
-      <c r="BH80" s="127"/>
+      <c r="BH80" s="81"/>
       <c r="BI80" s="81"/>
       <c r="BJ80" s="81"/>
       <c r="BK80" s="81"/>
@@ -16742,8 +17083,8 @@
       <c r="BD81" s="51"/>
       <c r="BE81" s="81"/>
       <c r="BF81" s="81"/>
-      <c r="BG81" s="64"/>
-      <c r="BH81" s="64"/>
+      <c r="BG81" s="81"/>
+      <c r="BH81" s="127"/>
       <c r="BI81" s="81"/>
       <c r="BJ81" s="81"/>
       <c r="BK81" s="81"/>
@@ -16815,7 +17156,7 @@
       <c r="BC82" s="53"/>
       <c r="BD82" s="51"/>
       <c r="BE82" s="81"/>
-      <c r="BF82" s="84"/>
+      <c r="BF82" s="81"/>
       <c r="BG82" s="64"/>
       <c r="BH82" s="64"/>
       <c r="BI82" s="81"/>
@@ -16889,9 +17230,9 @@
       <c r="BC83" s="53"/>
       <c r="BD83" s="51"/>
       <c r="BE83" s="81"/>
-      <c r="BF83" s="81"/>
-      <c r="BG83" s="81"/>
-      <c r="BH83" s="81"/>
+      <c r="BF83" s="84"/>
+      <c r="BG83" s="64"/>
+      <c r="BH83" s="64"/>
       <c r="BI83" s="81"/>
       <c r="BJ83" s="81"/>
       <c r="BK83" s="81"/>
@@ -17038,8 +17379,8 @@
       <c r="BD85" s="51"/>
       <c r="BE85" s="81"/>
       <c r="BF85" s="81"/>
-      <c r="BG85" s="64"/>
-      <c r="BH85" s="64"/>
+      <c r="BG85" s="81"/>
+      <c r="BH85" s="81"/>
       <c r="BI85" s="81"/>
       <c r="BJ85" s="81"/>
       <c r="BK85" s="81"/>
@@ -17111,7 +17452,7 @@
       <c r="BC86" s="53"/>
       <c r="BD86" s="51"/>
       <c r="BE86" s="81"/>
-      <c r="BF86" s="84"/>
+      <c r="BF86" s="81"/>
       <c r="BG86" s="64"/>
       <c r="BH86" s="64"/>
       <c r="BI86" s="81"/>
@@ -17185,9 +17526,9 @@
       <c r="BC87" s="53"/>
       <c r="BD87" s="51"/>
       <c r="BE87" s="81"/>
-      <c r="BF87" s="81"/>
-      <c r="BG87" s="81"/>
-      <c r="BH87" s="81"/>
+      <c r="BF87" s="84"/>
+      <c r="BG87" s="64"/>
+      <c r="BH87" s="64"/>
       <c r="BI87" s="81"/>
       <c r="BJ87" s="81"/>
       <c r="BK87" s="81"/>
@@ -17926,8 +18267,8 @@
       <c r="BD97" s="51"/>
       <c r="BE97" s="81"/>
       <c r="BF97" s="81"/>
-      <c r="BG97" s="64"/>
-      <c r="BH97" s="64"/>
+      <c r="BG97" s="81"/>
+      <c r="BH97" s="81"/>
       <c r="BI97" s="81"/>
       <c r="BJ97" s="81"/>
       <c r="BK97" s="81"/>
@@ -17999,9 +18340,9 @@
       <c r="BC98" s="53"/>
       <c r="BD98" s="51"/>
       <c r="BE98" s="81"/>
-      <c r="BF98" s="84"/>
+      <c r="BF98" s="81"/>
       <c r="BG98" s="64"/>
-      <c r="BH98" s="81"/>
+      <c r="BH98" s="64"/>
       <c r="BI98" s="81"/>
       <c r="BJ98" s="81"/>
       <c r="BK98" s="81"/>
@@ -18073,8 +18414,8 @@
       <c r="BC99" s="53"/>
       <c r="BD99" s="51"/>
       <c r="BE99" s="81"/>
-      <c r="BF99" s="81"/>
-      <c r="BG99" s="81"/>
+      <c r="BF99" s="84"/>
+      <c r="BG99" s="64"/>
       <c r="BH99" s="81"/>
       <c r="BI99" s="81"/>
       <c r="BJ99" s="81"/>
@@ -18593,7 +18934,7 @@
       <c r="BE106" s="81"/>
       <c r="BF106" s="81"/>
       <c r="BG106" s="81"/>
-      <c r="BH106" s="64"/>
+      <c r="BH106" s="81"/>
       <c r="BI106" s="81"/>
       <c r="BJ106" s="81"/>
       <c r="BK106" s="81"/>
@@ -18666,7 +19007,7 @@
       <c r="BD107" s="51"/>
       <c r="BE107" s="81"/>
       <c r="BF107" s="81"/>
-      <c r="BG107" s="64"/>
+      <c r="BG107" s="81"/>
       <c r="BH107" s="64"/>
       <c r="BI107" s="81"/>
       <c r="BJ107" s="81"/>
@@ -18739,9 +19080,9 @@
       <c r="BC108" s="53"/>
       <c r="BD108" s="51"/>
       <c r="BE108" s="81"/>
-      <c r="BF108" s="84"/>
+      <c r="BF108" s="81"/>
       <c r="BG108" s="64"/>
-      <c r="BH108" s="81"/>
+      <c r="BH108" s="64"/>
       <c r="BI108" s="81"/>
       <c r="BJ108" s="81"/>
       <c r="BK108" s="81"/>
@@ -18813,8 +19154,8 @@
       <c r="BC109" s="53"/>
       <c r="BD109" s="51"/>
       <c r="BE109" s="81"/>
-      <c r="BF109" s="81"/>
-      <c r="BG109" s="81"/>
+      <c r="BF109" s="84"/>
+      <c r="BG109" s="64"/>
       <c r="BH109" s="81"/>
       <c r="BI109" s="81"/>
       <c r="BJ109" s="81"/>
@@ -19629,7 +19970,7 @@
       <c r="BE120" s="81"/>
       <c r="BF120" s="81"/>
       <c r="BG120" s="81"/>
-      <c r="BH120" s="84"/>
+      <c r="BH120" s="81"/>
       <c r="BI120" s="81"/>
       <c r="BJ120" s="81"/>
       <c r="BK120" s="81"/>
@@ -19703,7 +20044,7 @@
       <c r="BE121" s="81"/>
       <c r="BF121" s="81"/>
       <c r="BG121" s="81"/>
-      <c r="BH121" s="81"/>
+      <c r="BH121" s="84"/>
       <c r="BI121" s="81"/>
       <c r="BJ121" s="81"/>
       <c r="BK121" s="81"/>
@@ -26583,10 +26924,84 @@
       <c r="BC214" s="53"/>
       <c r="BD214" s="51"/>
       <c r="BE214" s="81"/>
+      <c r="BF214" s="81"/>
+      <c r="BG214" s="81"/>
+      <c r="BH214" s="81"/>
+      <c r="BI214" s="81"/>
+      <c r="BJ214" s="81"/>
+      <c r="BK214" s="81"/>
+      <c r="BL214" s="81"/>
+      <c r="BM214" s="81"/>
+      <c r="BN214" s="81"/>
+      <c r="BO214" s="81"/>
+      <c r="BP214" s="81"/>
+      <c r="BQ214" s="81"/>
+      <c r="BR214" s="81"/>
+      <c r="BS214" s="81"/>
+      <c r="BT214" s="81"/>
+    </row>
+    <row r="215" spans="1:72" s="80" customFormat="1" ht="15">
+      <c r="A215" s="35"/>
+      <c r="B215" s="35"/>
+      <c r="C215" s="35"/>
+      <c r="D215" s="35"/>
+      <c r="E215" s="35"/>
+      <c r="F215" s="35"/>
+      <c r="G215" s="35"/>
+      <c r="H215" s="35"/>
+      <c r="I215" s="35"/>
+      <c r="J215" s="35"/>
+      <c r="K215" s="35"/>
+      <c r="L215" s="35"/>
+      <c r="M215" s="35"/>
+      <c r="N215" s="35"/>
+      <c r="O215" s="35"/>
+      <c r="P215" s="35"/>
+      <c r="Q215" s="35"/>
+      <c r="R215" s="35"/>
+      <c r="S215" s="53"/>
+      <c r="T215" s="53"/>
+      <c r="U215" s="53"/>
+      <c r="V215" s="53"/>
+      <c r="W215" s="35"/>
+      <c r="X215" s="35"/>
+      <c r="Y215" s="53"/>
+      <c r="Z215" s="53"/>
+      <c r="AA215" s="35"/>
+      <c r="AB215" s="35"/>
+      <c r="AC215" s="35"/>
+      <c r="AD215" s="53"/>
+      <c r="AE215" s="53"/>
+      <c r="AF215" s="53"/>
+      <c r="AG215" s="53"/>
+      <c r="AH215" s="53"/>
+      <c r="AI215" s="53"/>
+      <c r="AJ215" s="53"/>
+      <c r="AK215" s="53"/>
+      <c r="AL215" s="53"/>
+      <c r="AM215" s="53"/>
+      <c r="AN215" s="53"/>
+      <c r="AO215" s="53"/>
+      <c r="AP215" s="53"/>
+      <c r="AQ215" s="53"/>
+      <c r="AR215" s="53"/>
+      <c r="AS215" s="53"/>
+      <c r="AT215" s="53"/>
+      <c r="AU215" s="53"/>
+      <c r="AV215" s="53"/>
+      <c r="AW215" s="53"/>
+      <c r="AX215" s="53"/>
+      <c r="AY215" s="53"/>
+      <c r="AZ215" s="53"/>
+      <c r="BA215" s="53"/>
+      <c r="BB215" s="53"/>
+      <c r="BC215" s="53"/>
+      <c r="BD215" s="51"/>
+      <c r="BE215" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="BE8:BH8"/>
+    <mergeCell ref="BE9:BH9"/>
     <mergeCell ref="AK1:AM1"/>
     <mergeCell ref="A5:BA5"/>
     <mergeCell ref="BB5:BC5"/>
@@ -26599,7 +27014,7 @@
     <mergeCell ref="AA3:AR3"/>
     <mergeCell ref="AS3:AU3"/>
     <mergeCell ref="AV3:AY3"/>
-    <mergeCell ref="H9:AS9"/>
+    <mergeCell ref="H10:AS10"/>
     <mergeCell ref="AN1:AR1"/>
     <mergeCell ref="AS1:AU1"/>
     <mergeCell ref="AV1:AY1"/>
@@ -26631,7 +27046,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:BS19"/>
+  <dimension ref="A1:BS21"/>
   <sheetFormatPr defaultColWidth="2.54296875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="10" width="2.54296875" style="130" customWidth="1"/>
@@ -26896,17 +27311,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="12.75" customHeight="1">
-      <c r="A1" s="286" t="s">
+      <c r="A1" s="294" t="s">
         <v>35</v>
       </c>
-      <c r="B1" s="286"/>
-      <c r="C1" s="286"/>
-      <c r="D1" s="286"/>
-      <c r="E1" s="286"/>
-      <c r="F1" s="286"/>
-      <c r="G1" s="286"/>
-      <c r="H1" s="286"/>
-      <c r="I1" s="286"/>
+      <c r="B1" s="294"/>
+      <c r="C1" s="294"/>
+      <c r="D1" s="294"/>
+      <c r="E1" s="294"/>
+      <c r="F1" s="294"/>
+      <c r="G1" s="294"/>
+      <c r="H1" s="294"/>
+      <c r="I1" s="294"/>
       <c r="J1" s="128"/>
       <c r="K1" s="128"/>
       <c r="L1" s="128"/>
@@ -26971,654 +27386,648 @@
       <c r="BS1" s="129"/>
     </row>
     <row r="2" spans="1:71" ht="12.75" customHeight="1">
-      <c r="A2" s="287" t="s">
+      <c r="A2" s="295" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="287"/>
-      <c r="C2" s="287"/>
-      <c r="D2" s="287"/>
-      <c r="E2" s="287"/>
-      <c r="F2" s="287"/>
-      <c r="G2" s="287"/>
-      <c r="H2" s="287"/>
-      <c r="I2" s="287"/>
-      <c r="J2" s="287"/>
-      <c r="K2" s="287"/>
-      <c r="L2" s="287"/>
-      <c r="M2" s="287"/>
-      <c r="N2" s="287"/>
-      <c r="O2" s="287"/>
-      <c r="P2" s="287"/>
-      <c r="Q2" s="288"/>
-      <c r="R2" s="288"/>
-      <c r="S2" s="288"/>
-      <c r="T2" s="288"/>
-      <c r="U2" s="288"/>
-      <c r="V2" s="288"/>
-      <c r="W2" s="288"/>
-      <c r="X2" s="288"/>
-      <c r="Y2" s="288"/>
-      <c r="Z2" s="288"/>
-      <c r="AA2" s="288"/>
-      <c r="AB2" s="288"/>
-      <c r="AC2" s="288"/>
-      <c r="AD2" s="288"/>
-      <c r="AE2" s="288"/>
-      <c r="AF2" s="288"/>
-      <c r="AG2" s="288"/>
-      <c r="AH2" s="288"/>
-      <c r="AI2" s="288"/>
-      <c r="AJ2" s="288"/>
-      <c r="AK2" s="288"/>
-      <c r="AL2" s="288"/>
-      <c r="AM2" s="288"/>
-      <c r="AN2" s="288"/>
-      <c r="AO2" s="288"/>
-      <c r="AP2" s="288"/>
-      <c r="AQ2" s="288"/>
-      <c r="AR2" s="288"/>
-      <c r="AS2" s="288"/>
-      <c r="AT2" s="288"/>
-      <c r="AU2" s="288"/>
-      <c r="AV2" s="288"/>
-      <c r="AW2" s="288"/>
-      <c r="AX2" s="288"/>
-      <c r="AY2" s="288"/>
-      <c r="AZ2" s="288"/>
-      <c r="BA2" s="288"/>
-      <c r="BB2" s="288"/>
-      <c r="BC2" s="288"/>
-      <c r="BD2" s="288"/>
-      <c r="BE2" s="288"/>
-      <c r="BF2" s="288"/>
-      <c r="BG2" s="288"/>
-      <c r="BH2" s="288"/>
-      <c r="BI2" s="288"/>
-      <c r="BJ2" s="288"/>
-      <c r="BK2" s="288"/>
-      <c r="BL2" s="288"/>
-      <c r="BM2" s="288"/>
-      <c r="BN2" s="288"/>
-      <c r="BO2" s="288"/>
-      <c r="BP2" s="288"/>
-      <c r="BQ2" s="288"/>
-      <c r="BR2" s="288"/>
-      <c r="BS2" s="288"/>
+      <c r="B2" s="295"/>
+      <c r="C2" s="295"/>
+      <c r="D2" s="295"/>
+      <c r="E2" s="295"/>
+      <c r="F2" s="295"/>
+      <c r="G2" s="295"/>
+      <c r="H2" s="295"/>
+      <c r="I2" s="295"/>
+      <c r="J2" s="295"/>
+      <c r="K2" s="295"/>
+      <c r="L2" s="295"/>
+      <c r="M2" s="295"/>
+      <c r="N2" s="295"/>
+      <c r="O2" s="295"/>
+      <c r="P2" s="295"/>
+      <c r="Q2" s="296"/>
+      <c r="R2" s="296"/>
+      <c r="S2" s="296"/>
+      <c r="T2" s="296"/>
+      <c r="U2" s="296"/>
+      <c r="V2" s="296"/>
+      <c r="W2" s="296"/>
+      <c r="X2" s="296"/>
+      <c r="Y2" s="296"/>
+      <c r="Z2" s="296"/>
+      <c r="AA2" s="296"/>
+      <c r="AB2" s="296"/>
+      <c r="AC2" s="296"/>
+      <c r="AD2" s="296"/>
+      <c r="AE2" s="296"/>
+      <c r="AF2" s="296"/>
+      <c r="AG2" s="296"/>
+      <c r="AH2" s="296"/>
+      <c r="AI2" s="296"/>
+      <c r="AJ2" s="296"/>
+      <c r="AK2" s="296"/>
+      <c r="AL2" s="296"/>
+      <c r="AM2" s="296"/>
+      <c r="AN2" s="296"/>
+      <c r="AO2" s="296"/>
+      <c r="AP2" s="296"/>
+      <c r="AQ2" s="296"/>
+      <c r="AR2" s="296"/>
+      <c r="AS2" s="296"/>
+      <c r="AT2" s="296"/>
+      <c r="AU2" s="296"/>
+      <c r="AV2" s="296"/>
+      <c r="AW2" s="296"/>
+      <c r="AX2" s="296"/>
+      <c r="AY2" s="296"/>
+      <c r="AZ2" s="296"/>
+      <c r="BA2" s="296"/>
+      <c r="BB2" s="296"/>
+      <c r="BC2" s="296"/>
+      <c r="BD2" s="296"/>
+      <c r="BE2" s="296"/>
+      <c r="BF2" s="296"/>
+      <c r="BG2" s="296"/>
+      <c r="BH2" s="296"/>
+      <c r="BI2" s="296"/>
+      <c r="BJ2" s="296"/>
+      <c r="BK2" s="296"/>
+      <c r="BL2" s="296"/>
+      <c r="BM2" s="296"/>
+      <c r="BN2" s="296"/>
+      <c r="BO2" s="296"/>
+      <c r="BP2" s="296"/>
+      <c r="BQ2" s="296"/>
+      <c r="BR2" s="296"/>
+      <c r="BS2" s="296"/>
     </row>
     <row r="3" spans="1:71" ht="27.75" customHeight="1">
-      <c r="A3" s="289" t="s">
+      <c r="A3" s="297" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="290"/>
-      <c r="C3" s="290" t="s">
+      <c r="B3" s="298"/>
+      <c r="C3" s="298" t="s">
         <v>38</v>
       </c>
-      <c r="D3" s="290"/>
-      <c r="E3" s="290"/>
-      <c r="F3" s="290"/>
-      <c r="G3" s="290"/>
-      <c r="H3" s="290"/>
-      <c r="I3" s="290"/>
-      <c r="J3" s="290"/>
-      <c r="K3" s="290"/>
-      <c r="L3" s="290"/>
-      <c r="M3" s="290"/>
-      <c r="N3" s="290"/>
-      <c r="O3" s="290"/>
-      <c r="P3" s="290"/>
-      <c r="Q3" s="292" t="s">
+      <c r="D3" s="298"/>
+      <c r="E3" s="298"/>
+      <c r="F3" s="298"/>
+      <c r="G3" s="298"/>
+      <c r="H3" s="298"/>
+      <c r="I3" s="298"/>
+      <c r="J3" s="298"/>
+      <c r="K3" s="298"/>
+      <c r="L3" s="298"/>
+      <c r="M3" s="298"/>
+      <c r="N3" s="298"/>
+      <c r="O3" s="298"/>
+      <c r="P3" s="298"/>
+      <c r="Q3" s="300" t="s">
         <v>39</v>
       </c>
-      <c r="R3" s="293"/>
-      <c r="S3" s="293"/>
-      <c r="T3" s="293"/>
-      <c r="U3" s="293"/>
-      <c r="V3" s="293"/>
-      <c r="W3" s="293"/>
-      <c r="X3" s="293"/>
-      <c r="Y3" s="293"/>
-      <c r="Z3" s="293"/>
-      <c r="AA3" s="294"/>
-      <c r="AB3" s="298" t="s">
+      <c r="R3" s="301"/>
+      <c r="S3" s="301"/>
+      <c r="T3" s="301"/>
+      <c r="U3" s="301"/>
+      <c r="V3" s="301"/>
+      <c r="W3" s="301"/>
+      <c r="X3" s="301"/>
+      <c r="Y3" s="301"/>
+      <c r="Z3" s="301"/>
+      <c r="AA3" s="302"/>
+      <c r="AB3" s="306" t="s">
         <v>126</v>
       </c>
-      <c r="AC3" s="299"/>
-      <c r="AD3" s="299"/>
-      <c r="AE3" s="299"/>
-      <c r="AF3" s="299"/>
-      <c r="AG3" s="299"/>
-      <c r="AH3" s="299"/>
-      <c r="AI3" s="299"/>
-      <c r="AJ3" s="299"/>
-      <c r="AK3" s="289" t="s">
+      <c r="AC3" s="307"/>
+      <c r="AD3" s="307"/>
+      <c r="AE3" s="307"/>
+      <c r="AF3" s="307"/>
+      <c r="AG3" s="307"/>
+      <c r="AH3" s="307"/>
+      <c r="AI3" s="307"/>
+      <c r="AJ3" s="307"/>
+      <c r="AK3" s="297" t="s">
         <v>40</v>
       </c>
-      <c r="AL3" s="289"/>
-      <c r="AM3" s="289"/>
-      <c r="AN3" s="289"/>
-      <c r="AO3" s="289"/>
-      <c r="AP3" s="289"/>
-      <c r="AQ3" s="289"/>
-      <c r="AR3" s="289"/>
-      <c r="AS3" s="289"/>
-      <c r="AT3" s="289"/>
-      <c r="AU3" s="289"/>
-      <c r="AV3" s="289"/>
-      <c r="AW3" s="289"/>
-      <c r="AX3" s="289"/>
-      <c r="AY3" s="289"/>
-      <c r="AZ3" s="289"/>
-      <c r="BA3" s="289"/>
-      <c r="BB3" s="289"/>
-      <c r="BC3" s="289"/>
-      <c r="BD3" s="289"/>
-      <c r="BE3" s="289"/>
-      <c r="BF3" s="289"/>
-      <c r="BG3" s="289"/>
-      <c r="BH3" s="289"/>
-      <c r="BI3" s="289"/>
-      <c r="BJ3" s="289"/>
-      <c r="BK3" s="289"/>
-      <c r="BL3" s="289"/>
-      <c r="BM3" s="289"/>
-      <c r="BN3" s="289"/>
-      <c r="BO3" s="289"/>
-      <c r="BP3" s="289"/>
-      <c r="BQ3" s="289"/>
-      <c r="BR3" s="289"/>
-      <c r="BS3" s="289"/>
+      <c r="AL3" s="297"/>
+      <c r="AM3" s="297"/>
+      <c r="AN3" s="297"/>
+      <c r="AO3" s="297"/>
+      <c r="AP3" s="297"/>
+      <c r="AQ3" s="297"/>
+      <c r="AR3" s="297"/>
+      <c r="AS3" s="297"/>
+      <c r="AT3" s="297"/>
+      <c r="AU3" s="297"/>
+      <c r="AV3" s="297"/>
+      <c r="AW3" s="297"/>
+      <c r="AX3" s="297"/>
+      <c r="AY3" s="297"/>
+      <c r="AZ3" s="297"/>
+      <c r="BA3" s="297"/>
+      <c r="BB3" s="297"/>
+      <c r="BC3" s="297"/>
+      <c r="BD3" s="297"/>
+      <c r="BE3" s="297"/>
+      <c r="BF3" s="297"/>
+      <c r="BG3" s="297"/>
+      <c r="BH3" s="297"/>
+      <c r="BI3" s="297"/>
+      <c r="BJ3" s="297"/>
+      <c r="BK3" s="297"/>
+      <c r="BL3" s="297"/>
+      <c r="BM3" s="297"/>
+      <c r="BN3" s="297"/>
+      <c r="BO3" s="297"/>
+      <c r="BP3" s="297"/>
+      <c r="BQ3" s="297"/>
+      <c r="BR3" s="297"/>
+      <c r="BS3" s="297"/>
     </row>
     <row r="4" spans="1:71" ht="27.75" customHeight="1">
-      <c r="A4" s="290"/>
-      <c r="B4" s="290"/>
-      <c r="C4" s="291" t="s">
+      <c r="A4" s="298"/>
+      <c r="B4" s="298"/>
+      <c r="C4" s="299" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="291"/>
-      <c r="E4" s="291"/>
-      <c r="F4" s="291"/>
-      <c r="G4" s="291"/>
-      <c r="H4" s="291"/>
-      <c r="I4" s="291"/>
-      <c r="J4" s="291" t="s">
+      <c r="D4" s="299"/>
+      <c r="E4" s="299"/>
+      <c r="F4" s="299"/>
+      <c r="G4" s="299"/>
+      <c r="H4" s="299"/>
+      <c r="I4" s="299"/>
+      <c r="J4" s="299" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="291"/>
-      <c r="L4" s="291"/>
-      <c r="M4" s="291"/>
-      <c r="N4" s="291"/>
-      <c r="O4" s="291"/>
-      <c r="P4" s="291"/>
-      <c r="Q4" s="295"/>
-      <c r="R4" s="296"/>
-      <c r="S4" s="296"/>
-      <c r="T4" s="296"/>
-      <c r="U4" s="296"/>
-      <c r="V4" s="296"/>
-      <c r="W4" s="296"/>
-      <c r="X4" s="296"/>
-      <c r="Y4" s="296"/>
-      <c r="Z4" s="296"/>
-      <c r="AA4" s="297"/>
-      <c r="AB4" s="300"/>
-      <c r="AC4" s="301"/>
-      <c r="AD4" s="301"/>
-      <c r="AE4" s="301"/>
-      <c r="AF4" s="301"/>
-      <c r="AG4" s="301"/>
-      <c r="AH4" s="301"/>
-      <c r="AI4" s="301"/>
-      <c r="AJ4" s="301"/>
-      <c r="AK4" s="289"/>
-      <c r="AL4" s="289"/>
-      <c r="AM4" s="289"/>
-      <c r="AN4" s="289"/>
-      <c r="AO4" s="289"/>
-      <c r="AP4" s="289"/>
-      <c r="AQ4" s="289"/>
-      <c r="AR4" s="289"/>
-      <c r="AS4" s="289"/>
-      <c r="AT4" s="289"/>
-      <c r="AU4" s="289"/>
-      <c r="AV4" s="289"/>
-      <c r="AW4" s="289"/>
-      <c r="AX4" s="289"/>
-      <c r="AY4" s="289"/>
-      <c r="AZ4" s="289"/>
-      <c r="BA4" s="289"/>
-      <c r="BB4" s="289"/>
-      <c r="BC4" s="289"/>
-      <c r="BD4" s="289"/>
-      <c r="BE4" s="289"/>
-      <c r="BF4" s="289"/>
-      <c r="BG4" s="289"/>
-      <c r="BH4" s="289"/>
-      <c r="BI4" s="289"/>
-      <c r="BJ4" s="289"/>
-      <c r="BK4" s="289"/>
-      <c r="BL4" s="289"/>
-      <c r="BM4" s="289"/>
-      <c r="BN4" s="289"/>
-      <c r="BO4" s="289"/>
-      <c r="BP4" s="289"/>
-      <c r="BQ4" s="289"/>
-      <c r="BR4" s="289"/>
-      <c r="BS4" s="289"/>
-    </row>
-    <row r="5" spans="1:71">
-      <c r="A5" s="259" t="s">
+      <c r="K4" s="299"/>
+      <c r="L4" s="299"/>
+      <c r="M4" s="299"/>
+      <c r="N4" s="299"/>
+      <c r="O4" s="299"/>
+      <c r="P4" s="299"/>
+      <c r="Q4" s="303"/>
+      <c r="R4" s="304"/>
+      <c r="S4" s="304"/>
+      <c r="T4" s="304"/>
+      <c r="U4" s="304"/>
+      <c r="V4" s="304"/>
+      <c r="W4" s="304"/>
+      <c r="X4" s="304"/>
+      <c r="Y4" s="304"/>
+      <c r="Z4" s="304"/>
+      <c r="AA4" s="305"/>
+      <c r="AB4" s="308"/>
+      <c r="AC4" s="309"/>
+      <c r="AD4" s="309"/>
+      <c r="AE4" s="309"/>
+      <c r="AF4" s="309"/>
+      <c r="AG4" s="309"/>
+      <c r="AH4" s="309"/>
+      <c r="AI4" s="309"/>
+      <c r="AJ4" s="309"/>
+      <c r="AK4" s="297"/>
+      <c r="AL4" s="297"/>
+      <c r="AM4" s="297"/>
+      <c r="AN4" s="297"/>
+      <c r="AO4" s="297"/>
+      <c r="AP4" s="297"/>
+      <c r="AQ4" s="297"/>
+      <c r="AR4" s="297"/>
+      <c r="AS4" s="297"/>
+      <c r="AT4" s="297"/>
+      <c r="AU4" s="297"/>
+      <c r="AV4" s="297"/>
+      <c r="AW4" s="297"/>
+      <c r="AX4" s="297"/>
+      <c r="AY4" s="297"/>
+      <c r="AZ4" s="297"/>
+      <c r="BA4" s="297"/>
+      <c r="BB4" s="297"/>
+      <c r="BC4" s="297"/>
+      <c r="BD4" s="297"/>
+      <c r="BE4" s="297"/>
+      <c r="BF4" s="297"/>
+      <c r="BG4" s="297"/>
+      <c r="BH4" s="297"/>
+      <c r="BI4" s="297"/>
+      <c r="BJ4" s="297"/>
+      <c r="BK4" s="297"/>
+      <c r="BL4" s="297"/>
+      <c r="BM4" s="297"/>
+      <c r="BN4" s="297"/>
+      <c r="BO4" s="297"/>
+      <c r="BP4" s="297"/>
+      <c r="BQ4" s="297"/>
+      <c r="BR4" s="297"/>
+      <c r="BS4" s="297"/>
+    </row>
+    <row r="5" spans="1:71" ht="15" customHeight="1">
+      <c r="A5" s="239" t="s">
+        <v>160</v>
+      </c>
+      <c r="B5" s="240"/>
+      <c r="C5" s="241" t="s">
+        <v>161</v>
+      </c>
+      <c r="D5" s="242"/>
+      <c r="E5" s="242"/>
+      <c r="F5" s="242"/>
+      <c r="G5" s="242"/>
+      <c r="H5" s="242"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="244"/>
+      <c r="K5" s="245"/>
+      <c r="L5" s="245"/>
+      <c r="M5" s="245"/>
+      <c r="N5" s="245"/>
+      <c r="O5" s="245"/>
+      <c r="P5" s="246"/>
+      <c r="Q5" s="247"/>
+      <c r="R5" s="248"/>
+      <c r="S5" s="248"/>
+      <c r="T5" s="248"/>
+      <c r="U5" s="248"/>
+      <c r="V5" s="248"/>
+      <c r="W5" s="248"/>
+      <c r="X5" s="248"/>
+      <c r="Y5" s="248"/>
+      <c r="Z5" s="248"/>
+      <c r="AA5" s="249"/>
+      <c r="AB5" s="250"/>
+      <c r="AC5" s="251"/>
+      <c r="AD5" s="251"/>
+      <c r="AE5" s="251"/>
+      <c r="AF5" s="251"/>
+      <c r="AG5" s="251"/>
+      <c r="AH5" s="251"/>
+      <c r="AI5" s="251"/>
+      <c r="AJ5" s="251"/>
+      <c r="AK5" s="252"/>
+      <c r="AL5" s="253"/>
+      <c r="AM5" s="253"/>
+      <c r="AN5" s="253"/>
+      <c r="AO5" s="253"/>
+      <c r="AP5" s="253"/>
+      <c r="AQ5" s="253"/>
+      <c r="AR5" s="253"/>
+      <c r="AS5" s="253"/>
+      <c r="AT5" s="253"/>
+      <c r="AU5" s="253"/>
+      <c r="AV5" s="253"/>
+      <c r="AW5" s="253"/>
+      <c r="AX5" s="253"/>
+      <c r="AY5" s="253"/>
+      <c r="AZ5" s="253"/>
+      <c r="BA5" s="253"/>
+      <c r="BB5" s="253"/>
+      <c r="BC5" s="253"/>
+      <c r="BD5" s="253"/>
+      <c r="BE5" s="253"/>
+      <c r="BF5" s="253"/>
+      <c r="BG5" s="253"/>
+      <c r="BH5" s="253"/>
+      <c r="BI5" s="253"/>
+      <c r="BJ5" s="253"/>
+      <c r="BK5" s="253"/>
+      <c r="BL5" s="253"/>
+      <c r="BM5" s="253"/>
+      <c r="BN5" s="253"/>
+      <c r="BO5" s="253"/>
+      <c r="BP5" s="253"/>
+      <c r="BQ5" s="253"/>
+      <c r="BR5" s="253"/>
+      <c r="BS5" s="254"/>
+    </row>
+    <row r="6" spans="1:71" ht="33" customHeight="1">
+      <c r="A6" s="239" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="240"/>
+      <c r="C6" s="241"/>
+      <c r="D6" s="242"/>
+      <c r="E6" s="242"/>
+      <c r="F6" s="242"/>
+      <c r="G6" s="242"/>
+      <c r="H6" s="242"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="244" t="s">
+        <v>163</v>
+      </c>
+      <c r="K6" s="245"/>
+      <c r="L6" s="245"/>
+      <c r="M6" s="245"/>
+      <c r="N6" s="245"/>
+      <c r="O6" s="245"/>
+      <c r="P6" s="246"/>
+      <c r="Q6" s="247"/>
+      <c r="R6" s="248"/>
+      <c r="S6" s="248"/>
+      <c r="T6" s="248"/>
+      <c r="U6" s="248"/>
+      <c r="V6" s="248"/>
+      <c r="W6" s="248"/>
+      <c r="X6" s="248"/>
+      <c r="Y6" s="248"/>
+      <c r="Z6" s="248"/>
+      <c r="AA6" s="249"/>
+      <c r="AB6" s="250"/>
+      <c r="AC6" s="251"/>
+      <c r="AD6" s="251"/>
+      <c r="AE6" s="251"/>
+      <c r="AF6" s="251"/>
+      <c r="AG6" s="251"/>
+      <c r="AH6" s="251"/>
+      <c r="AI6" s="251"/>
+      <c r="AJ6" s="251"/>
+      <c r="AK6" s="255" t="s">
+        <v>164</v>
+      </c>
+      <c r="AL6" s="251"/>
+      <c r="AM6" s="251"/>
+      <c r="AN6" s="251"/>
+      <c r="AO6" s="251"/>
+      <c r="AP6" s="251"/>
+      <c r="AQ6" s="251"/>
+      <c r="AR6" s="251"/>
+      <c r="AS6" s="251"/>
+      <c r="AT6" s="251"/>
+      <c r="AU6" s="251"/>
+      <c r="AV6" s="251"/>
+      <c r="AW6" s="251"/>
+      <c r="AX6" s="251"/>
+      <c r="AY6" s="251"/>
+      <c r="AZ6" s="251"/>
+      <c r="BA6" s="251"/>
+      <c r="BB6" s="251"/>
+      <c r="BC6" s="251"/>
+      <c r="BD6" s="251"/>
+      <c r="BE6" s="251"/>
+      <c r="BF6" s="251"/>
+      <c r="BG6" s="251"/>
+      <c r="BH6" s="251"/>
+      <c r="BI6" s="251"/>
+      <c r="BJ6" s="251"/>
+      <c r="BK6" s="251"/>
+      <c r="BL6" s="251"/>
+      <c r="BM6" s="251"/>
+      <c r="BN6" s="251"/>
+      <c r="BO6" s="251"/>
+      <c r="BP6" s="251"/>
+      <c r="BQ6" s="251"/>
+      <c r="BR6" s="251"/>
+      <c r="BS6" s="256"/>
+    </row>
+    <row r="7" spans="1:71">
+      <c r="A7" s="239" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="260"/>
-      <c r="C5" s="277" t="s">
+      <c r="B7" s="240"/>
+      <c r="C7" s="285" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="278"/>
-      <c r="E5" s="278"/>
-      <c r="F5" s="278"/>
-      <c r="G5" s="278"/>
-      <c r="H5" s="278"/>
-      <c r="I5" s="279"/>
-      <c r="J5" s="271"/>
-      <c r="K5" s="272"/>
-      <c r="L5" s="272"/>
-      <c r="M5" s="272"/>
-      <c r="N5" s="272"/>
-      <c r="O5" s="272"/>
-      <c r="P5" s="273"/>
-      <c r="Q5" s="256"/>
-      <c r="R5" s="257"/>
-      <c r="S5" s="257"/>
-      <c r="T5" s="257"/>
-      <c r="U5" s="257"/>
-      <c r="V5" s="257"/>
-      <c r="W5" s="257"/>
-      <c r="X5" s="257"/>
-      <c r="Y5" s="257"/>
-      <c r="Z5" s="257"/>
-      <c r="AA5" s="258"/>
-      <c r="AB5" s="249"/>
-      <c r="AC5" s="250"/>
-      <c r="AD5" s="250"/>
-      <c r="AE5" s="250"/>
-      <c r="AF5" s="250"/>
-      <c r="AG5" s="250"/>
-      <c r="AH5" s="250"/>
-      <c r="AI5" s="250"/>
-      <c r="AJ5" s="250"/>
-      <c r="AK5" s="251"/>
-      <c r="AL5" s="247"/>
-      <c r="AM5" s="247"/>
-      <c r="AN5" s="247"/>
-      <c r="AO5" s="247"/>
-      <c r="AP5" s="247"/>
-      <c r="AQ5" s="247"/>
-      <c r="AR5" s="247"/>
-      <c r="AS5" s="247"/>
-      <c r="AT5" s="247"/>
-      <c r="AU5" s="247"/>
-      <c r="AV5" s="247"/>
-      <c r="AW5" s="247"/>
-      <c r="AX5" s="247"/>
-      <c r="AY5" s="247"/>
-      <c r="AZ5" s="247"/>
-      <c r="BA5" s="247"/>
-      <c r="BB5" s="247"/>
-      <c r="BC5" s="247"/>
-      <c r="BD5" s="247"/>
-      <c r="BE5" s="247"/>
-      <c r="BF5" s="247"/>
-      <c r="BG5" s="247"/>
-      <c r="BH5" s="247"/>
-      <c r="BI5" s="247"/>
-      <c r="BJ5" s="247"/>
-      <c r="BK5" s="247"/>
-      <c r="BL5" s="247"/>
-      <c r="BM5" s="247"/>
-      <c r="BN5" s="247"/>
-      <c r="BO5" s="247"/>
-      <c r="BP5" s="247"/>
-      <c r="BQ5" s="247"/>
-      <c r="BR5" s="247"/>
-      <c r="BS5" s="252"/>
-    </row>
-    <row r="6" spans="1:71">
-      <c r="A6" s="259" t="s">
+      <c r="D7" s="286"/>
+      <c r="E7" s="286"/>
+      <c r="F7" s="286"/>
+      <c r="G7" s="286"/>
+      <c r="H7" s="286"/>
+      <c r="I7" s="287"/>
+      <c r="J7" s="279"/>
+      <c r="K7" s="280"/>
+      <c r="L7" s="280"/>
+      <c r="M7" s="280"/>
+      <c r="N7" s="280"/>
+      <c r="O7" s="280"/>
+      <c r="P7" s="281"/>
+      <c r="Q7" s="247"/>
+      <c r="R7" s="248"/>
+      <c r="S7" s="248"/>
+      <c r="T7" s="248"/>
+      <c r="U7" s="248"/>
+      <c r="V7" s="248"/>
+      <c r="W7" s="248"/>
+      <c r="X7" s="248"/>
+      <c r="Y7" s="248"/>
+      <c r="Z7" s="248"/>
+      <c r="AA7" s="249"/>
+      <c r="AB7" s="250"/>
+      <c r="AC7" s="251"/>
+      <c r="AD7" s="251"/>
+      <c r="AE7" s="251"/>
+      <c r="AF7" s="251"/>
+      <c r="AG7" s="251"/>
+      <c r="AH7" s="251"/>
+      <c r="AI7" s="251"/>
+      <c r="AJ7" s="251"/>
+      <c r="AK7" s="252"/>
+      <c r="AL7" s="253"/>
+      <c r="AM7" s="253"/>
+      <c r="AN7" s="253"/>
+      <c r="AO7" s="253"/>
+      <c r="AP7" s="253"/>
+      <c r="AQ7" s="253"/>
+      <c r="AR7" s="253"/>
+      <c r="AS7" s="253"/>
+      <c r="AT7" s="253"/>
+      <c r="AU7" s="253"/>
+      <c r="AV7" s="253"/>
+      <c r="AW7" s="253"/>
+      <c r="AX7" s="253"/>
+      <c r="AY7" s="253"/>
+      <c r="AZ7" s="253"/>
+      <c r="BA7" s="253"/>
+      <c r="BB7" s="253"/>
+      <c r="BC7" s="253"/>
+      <c r="BD7" s="253"/>
+      <c r="BE7" s="253"/>
+      <c r="BF7" s="253"/>
+      <c r="BG7" s="253"/>
+      <c r="BH7" s="253"/>
+      <c r="BI7" s="253"/>
+      <c r="BJ7" s="253"/>
+      <c r="BK7" s="253"/>
+      <c r="BL7" s="253"/>
+      <c r="BM7" s="253"/>
+      <c r="BN7" s="253"/>
+      <c r="BO7" s="253"/>
+      <c r="BP7" s="253"/>
+      <c r="BQ7" s="253"/>
+      <c r="BR7" s="253"/>
+      <c r="BS7" s="254"/>
+    </row>
+    <row r="8" spans="1:71">
+      <c r="A8" s="239" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="260"/>
-      <c r="C6" s="277"/>
-      <c r="D6" s="278"/>
-      <c r="E6" s="278"/>
-      <c r="F6" s="278"/>
-      <c r="G6" s="278"/>
-      <c r="H6" s="278"/>
-      <c r="I6" s="279"/>
-      <c r="J6" s="271" t="s">
+      <c r="B8" s="240"/>
+      <c r="C8" s="285"/>
+      <c r="D8" s="286"/>
+      <c r="E8" s="286"/>
+      <c r="F8" s="286"/>
+      <c r="G8" s="286"/>
+      <c r="H8" s="286"/>
+      <c r="I8" s="287"/>
+      <c r="J8" s="279" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="272"/>
-      <c r="L6" s="272"/>
-      <c r="M6" s="272"/>
-      <c r="N6" s="272"/>
-      <c r="O6" s="272"/>
-      <c r="P6" s="273"/>
-      <c r="Q6" s="256"/>
-      <c r="R6" s="257"/>
-      <c r="S6" s="257"/>
-      <c r="T6" s="257"/>
-      <c r="U6" s="257"/>
-      <c r="V6" s="257"/>
-      <c r="W6" s="257"/>
-      <c r="X6" s="257"/>
-      <c r="Y6" s="257"/>
-      <c r="Z6" s="257"/>
-      <c r="AA6" s="258"/>
-      <c r="AB6" s="249"/>
-      <c r="AC6" s="250"/>
-      <c r="AD6" s="250"/>
-      <c r="AE6" s="250"/>
-      <c r="AF6" s="250"/>
-      <c r="AG6" s="250"/>
-      <c r="AH6" s="250"/>
-      <c r="AI6" s="250"/>
-      <c r="AJ6" s="250"/>
-      <c r="AK6" s="251"/>
-      <c r="AL6" s="247"/>
-      <c r="AM6" s="247"/>
-      <c r="AN6" s="247"/>
-      <c r="AO6" s="247"/>
-      <c r="AP6" s="247"/>
-      <c r="AQ6" s="247"/>
-      <c r="AR6" s="247"/>
-      <c r="AS6" s="247"/>
-      <c r="AT6" s="247"/>
-      <c r="AU6" s="247"/>
-      <c r="AV6" s="247"/>
-      <c r="AW6" s="247"/>
-      <c r="AX6" s="247"/>
-      <c r="AY6" s="247"/>
-      <c r="AZ6" s="247"/>
-      <c r="BA6" s="247"/>
-      <c r="BB6" s="247"/>
-      <c r="BC6" s="247"/>
-      <c r="BD6" s="247"/>
-      <c r="BE6" s="247"/>
-      <c r="BF6" s="247"/>
-      <c r="BG6" s="247"/>
-      <c r="BH6" s="247"/>
-      <c r="BI6" s="247"/>
-      <c r="BJ6" s="247"/>
-      <c r="BK6" s="247"/>
-      <c r="BL6" s="247"/>
-      <c r="BM6" s="247"/>
-      <c r="BN6" s="247"/>
-      <c r="BO6" s="247"/>
-      <c r="BP6" s="247"/>
-      <c r="BQ6" s="247"/>
-      <c r="BR6" s="247"/>
-      <c r="BS6" s="252"/>
-    </row>
-    <row r="7" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A7" s="259" t="s">
+      <c r="K8" s="280"/>
+      <c r="L8" s="280"/>
+      <c r="M8" s="280"/>
+      <c r="N8" s="280"/>
+      <c r="O8" s="280"/>
+      <c r="P8" s="281"/>
+      <c r="Q8" s="247"/>
+      <c r="R8" s="248"/>
+      <c r="S8" s="248"/>
+      <c r="T8" s="248"/>
+      <c r="U8" s="248"/>
+      <c r="V8" s="248"/>
+      <c r="W8" s="248"/>
+      <c r="X8" s="248"/>
+      <c r="Y8" s="248"/>
+      <c r="Z8" s="248"/>
+      <c r="AA8" s="249"/>
+      <c r="AB8" s="250"/>
+      <c r="AC8" s="251"/>
+      <c r="AD8" s="251"/>
+      <c r="AE8" s="251"/>
+      <c r="AF8" s="251"/>
+      <c r="AG8" s="251"/>
+      <c r="AH8" s="251"/>
+      <c r="AI8" s="251"/>
+      <c r="AJ8" s="251"/>
+      <c r="AK8" s="252"/>
+      <c r="AL8" s="253"/>
+      <c r="AM8" s="253"/>
+      <c r="AN8" s="253"/>
+      <c r="AO8" s="253"/>
+      <c r="AP8" s="253"/>
+      <c r="AQ8" s="253"/>
+      <c r="AR8" s="253"/>
+      <c r="AS8" s="253"/>
+      <c r="AT8" s="253"/>
+      <c r="AU8" s="253"/>
+      <c r="AV8" s="253"/>
+      <c r="AW8" s="253"/>
+      <c r="AX8" s="253"/>
+      <c r="AY8" s="253"/>
+      <c r="AZ8" s="253"/>
+      <c r="BA8" s="253"/>
+      <c r="BB8" s="253"/>
+      <c r="BC8" s="253"/>
+      <c r="BD8" s="253"/>
+      <c r="BE8" s="253"/>
+      <c r="BF8" s="253"/>
+      <c r="BG8" s="253"/>
+      <c r="BH8" s="253"/>
+      <c r="BI8" s="253"/>
+      <c r="BJ8" s="253"/>
+      <c r="BK8" s="253"/>
+      <c r="BL8" s="253"/>
+      <c r="BM8" s="253"/>
+      <c r="BN8" s="253"/>
+      <c r="BO8" s="253"/>
+      <c r="BP8" s="253"/>
+      <c r="BQ8" s="253"/>
+      <c r="BR8" s="253"/>
+      <c r="BS8" s="254"/>
+    </row>
+    <row r="9" spans="1:71" ht="15.75" customHeight="1">
+      <c r="A9" s="239" t="s">
         <v>68</v>
       </c>
-      <c r="B7" s="260"/>
-      <c r="C7" s="282" t="s">
+      <c r="B9" s="240"/>
+      <c r="C9" s="290" t="s">
         <v>69</v>
       </c>
-      <c r="D7" s="283"/>
-      <c r="E7" s="283"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="283"/>
-      <c r="H7" s="283"/>
-      <c r="I7" s="284"/>
-      <c r="J7" s="285"/>
-      <c r="K7" s="285"/>
-      <c r="L7" s="285"/>
-      <c r="M7" s="285"/>
-      <c r="N7" s="285"/>
-      <c r="O7" s="285"/>
-      <c r="P7" s="285"/>
-      <c r="Q7" s="256"/>
-      <c r="R7" s="257"/>
-      <c r="S7" s="257"/>
-      <c r="T7" s="257"/>
-      <c r="U7" s="257"/>
-      <c r="V7" s="257"/>
-      <c r="W7" s="257"/>
-      <c r="X7" s="257"/>
-      <c r="Y7" s="257"/>
-      <c r="Z7" s="257"/>
-      <c r="AA7" s="258"/>
-      <c r="AB7" s="249"/>
-      <c r="AC7" s="250"/>
-      <c r="AD7" s="250"/>
-      <c r="AE7" s="250"/>
-      <c r="AF7" s="250"/>
-      <c r="AG7" s="250"/>
-      <c r="AH7" s="250"/>
-      <c r="AI7" s="250"/>
-      <c r="AJ7" s="250"/>
-      <c r="AK7" s="239"/>
-      <c r="AL7" s="280"/>
-      <c r="AM7" s="280"/>
-      <c r="AN7" s="280"/>
-      <c r="AO7" s="280"/>
-      <c r="AP7" s="280"/>
-      <c r="AQ7" s="280"/>
-      <c r="AR7" s="280"/>
-      <c r="AS7" s="280"/>
-      <c r="AT7" s="280"/>
-      <c r="AU7" s="280"/>
-      <c r="AV7" s="280"/>
-      <c r="AW7" s="280"/>
-      <c r="AX7" s="280"/>
-      <c r="AY7" s="280"/>
-      <c r="AZ7" s="280"/>
-      <c r="BA7" s="280"/>
-      <c r="BB7" s="280"/>
-      <c r="BC7" s="280"/>
-      <c r="BD7" s="280"/>
-      <c r="BE7" s="280"/>
-      <c r="BF7" s="280"/>
-      <c r="BG7" s="280"/>
-      <c r="BH7" s="280"/>
-      <c r="BI7" s="280"/>
-      <c r="BJ7" s="280"/>
-      <c r="BK7" s="280"/>
-      <c r="BL7" s="280"/>
-      <c r="BM7" s="280"/>
-      <c r="BN7" s="280"/>
-      <c r="BO7" s="280"/>
-      <c r="BP7" s="280"/>
-      <c r="BQ7" s="280"/>
-      <c r="BR7" s="280"/>
-      <c r="BS7" s="281"/>
-    </row>
-    <row r="8" spans="1:71" ht="25.5" customHeight="1">
-      <c r="A8" s="259">
+      <c r="D9" s="291"/>
+      <c r="E9" s="291"/>
+      <c r="F9" s="291"/>
+      <c r="G9" s="291"/>
+      <c r="H9" s="291"/>
+      <c r="I9" s="292"/>
+      <c r="J9" s="293"/>
+      <c r="K9" s="293"/>
+      <c r="L9" s="293"/>
+      <c r="M9" s="293"/>
+      <c r="N9" s="293"/>
+      <c r="O9" s="293"/>
+      <c r="P9" s="293"/>
+      <c r="Q9" s="247"/>
+      <c r="R9" s="248"/>
+      <c r="S9" s="248"/>
+      <c r="T9" s="248"/>
+      <c r="U9" s="248"/>
+      <c r="V9" s="248"/>
+      <c r="W9" s="248"/>
+      <c r="X9" s="248"/>
+      <c r="Y9" s="248"/>
+      <c r="Z9" s="248"/>
+      <c r="AA9" s="249"/>
+      <c r="AB9" s="250"/>
+      <c r="AC9" s="251"/>
+      <c r="AD9" s="251"/>
+      <c r="AE9" s="251"/>
+      <c r="AF9" s="251"/>
+      <c r="AG9" s="251"/>
+      <c r="AH9" s="251"/>
+      <c r="AI9" s="251"/>
+      <c r="AJ9" s="251"/>
+      <c r="AK9" s="257"/>
+      <c r="AL9" s="288"/>
+      <c r="AM9" s="288"/>
+      <c r="AN9" s="288"/>
+      <c r="AO9" s="288"/>
+      <c r="AP9" s="288"/>
+      <c r="AQ9" s="288"/>
+      <c r="AR9" s="288"/>
+      <c r="AS9" s="288"/>
+      <c r="AT9" s="288"/>
+      <c r="AU9" s="288"/>
+      <c r="AV9" s="288"/>
+      <c r="AW9" s="288"/>
+      <c r="AX9" s="288"/>
+      <c r="AY9" s="288"/>
+      <c r="AZ9" s="288"/>
+      <c r="BA9" s="288"/>
+      <c r="BB9" s="288"/>
+      <c r="BC9" s="288"/>
+      <c r="BD9" s="288"/>
+      <c r="BE9" s="288"/>
+      <c r="BF9" s="288"/>
+      <c r="BG9" s="288"/>
+      <c r="BH9" s="288"/>
+      <c r="BI9" s="288"/>
+      <c r="BJ9" s="288"/>
+      <c r="BK9" s="288"/>
+      <c r="BL9" s="288"/>
+      <c r="BM9" s="288"/>
+      <c r="BN9" s="288"/>
+      <c r="BO9" s="288"/>
+      <c r="BP9" s="288"/>
+      <c r="BQ9" s="288"/>
+      <c r="BR9" s="288"/>
+      <c r="BS9" s="289"/>
+    </row>
+    <row r="10" spans="1:71" ht="25.5" customHeight="1">
+      <c r="A10" s="239">
         <v>2.1</v>
       </c>
-      <c r="B8" s="260"/>
-      <c r="C8" s="277"/>
-      <c r="D8" s="278"/>
-      <c r="E8" s="278"/>
-      <c r="F8" s="278"/>
-      <c r="G8" s="278"/>
-      <c r="H8" s="278"/>
-      <c r="I8" s="279"/>
-      <c r="J8" s="274" t="s">
+      <c r="B10" s="240"/>
+      <c r="C10" s="285"/>
+      <c r="D10" s="286"/>
+      <c r="E10" s="286"/>
+      <c r="F10" s="286"/>
+      <c r="G10" s="286"/>
+      <c r="H10" s="286"/>
+      <c r="I10" s="287"/>
+      <c r="J10" s="282" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="275"/>
-      <c r="L8" s="275"/>
-      <c r="M8" s="275"/>
-      <c r="N8" s="275"/>
-      <c r="O8" s="275"/>
-      <c r="P8" s="276"/>
-      <c r="Q8" s="253" t="s">
-        <v>139</v>
-      </c>
-      <c r="R8" s="254"/>
-      <c r="S8" s="254"/>
-      <c r="T8" s="254"/>
-      <c r="U8" s="254"/>
-      <c r="V8" s="254"/>
-      <c r="W8" s="254"/>
-      <c r="X8" s="254"/>
-      <c r="Y8" s="254"/>
-      <c r="Z8" s="254"/>
-      <c r="AA8" s="255"/>
-      <c r="AB8" s="264"/>
-      <c r="AC8" s="265"/>
-      <c r="AD8" s="265"/>
-      <c r="AE8" s="265"/>
-      <c r="AF8" s="265"/>
-      <c r="AG8" s="265"/>
-      <c r="AH8" s="265"/>
-      <c r="AI8" s="265"/>
-      <c r="AJ8" s="265"/>
-      <c r="AK8" s="269" t="s">
-        <v>130</v>
-      </c>
-      <c r="AL8" s="262"/>
-      <c r="AM8" s="262"/>
-      <c r="AN8" s="262"/>
-      <c r="AO8" s="262"/>
-      <c r="AP8" s="262"/>
-      <c r="AQ8" s="262"/>
-      <c r="AR8" s="262"/>
-      <c r="AS8" s="262"/>
-      <c r="AT8" s="262"/>
-      <c r="AU8" s="262"/>
-      <c r="AV8" s="262"/>
-      <c r="AW8" s="262"/>
-      <c r="AX8" s="262"/>
-      <c r="AY8" s="262"/>
-      <c r="AZ8" s="262"/>
-      <c r="BA8" s="262"/>
-      <c r="BB8" s="262"/>
-      <c r="BC8" s="262"/>
-      <c r="BD8" s="262"/>
-      <c r="BE8" s="262"/>
-      <c r="BF8" s="262"/>
-      <c r="BG8" s="262"/>
-      <c r="BH8" s="262"/>
-      <c r="BI8" s="262"/>
-      <c r="BJ8" s="262"/>
-      <c r="BK8" s="262"/>
-      <c r="BL8" s="262"/>
-      <c r="BM8" s="262"/>
-      <c r="BN8" s="262"/>
-      <c r="BO8" s="262"/>
-      <c r="BP8" s="262"/>
-      <c r="BQ8" s="262"/>
-      <c r="BR8" s="262"/>
-      <c r="BS8" s="270"/>
-    </row>
-    <row r="9" spans="1:71" ht="54.75" customHeight="1">
-      <c r="A9" s="259" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="260"/>
-      <c r="C9" s="241"/>
-      <c r="D9" s="242"/>
-      <c r="E9" s="242"/>
-      <c r="F9" s="242"/>
-      <c r="G9" s="242"/>
-      <c r="H9" s="242"/>
-      <c r="I9" s="243"/>
-      <c r="J9" s="274" t="s">
-        <v>47</v>
-      </c>
-      <c r="K9" s="275"/>
-      <c r="L9" s="275"/>
-      <c r="M9" s="275"/>
-      <c r="N9" s="275"/>
-      <c r="O9" s="275"/>
-      <c r="P9" s="276"/>
-      <c r="Q9" s="256" t="s">
-        <v>139</v>
-      </c>
-      <c r="R9" s="257"/>
-      <c r="S9" s="257"/>
-      <c r="T9" s="257"/>
-      <c r="U9" s="257"/>
-      <c r="V9" s="257"/>
-      <c r="W9" s="257"/>
-      <c r="X9" s="257"/>
-      <c r="Y9" s="257"/>
-      <c r="Z9" s="257"/>
-      <c r="AA9" s="258"/>
-      <c r="AB9" s="264"/>
-      <c r="AC9" s="265"/>
-      <c r="AD9" s="265"/>
-      <c r="AE9" s="265"/>
-      <c r="AF9" s="265"/>
-      <c r="AG9" s="265"/>
-      <c r="AH9" s="265"/>
-      <c r="AI9" s="265"/>
-      <c r="AJ9" s="265"/>
-      <c r="AK9" s="251" t="s">
-        <v>123</v>
-      </c>
-      <c r="AL9" s="247"/>
-      <c r="AM9" s="247"/>
-      <c r="AN9" s="247"/>
-      <c r="AO9" s="247"/>
-      <c r="AP9" s="247"/>
-      <c r="AQ9" s="247"/>
-      <c r="AR9" s="247"/>
-      <c r="AS9" s="247"/>
-      <c r="AT9" s="247"/>
-      <c r="AU9" s="247"/>
-      <c r="AV9" s="247"/>
-      <c r="AW9" s="247"/>
-      <c r="AX9" s="247"/>
-      <c r="AY9" s="247"/>
-      <c r="AZ9" s="247"/>
-      <c r="BA9" s="247"/>
-      <c r="BB9" s="247"/>
-      <c r="BC9" s="247"/>
-      <c r="BD9" s="247"/>
-      <c r="BE9" s="247"/>
-      <c r="BF9" s="247"/>
-      <c r="BG9" s="247"/>
-      <c r="BH9" s="247"/>
-      <c r="BI9" s="247"/>
-      <c r="BJ9" s="247"/>
-      <c r="BK9" s="247"/>
-      <c r="BL9" s="247"/>
-      <c r="BM9" s="247"/>
-      <c r="BN9" s="247"/>
-      <c r="BO9" s="247"/>
-      <c r="BP9" s="247"/>
-      <c r="BQ9" s="247"/>
-      <c r="BR9" s="247"/>
-      <c r="BS9" s="252"/>
-    </row>
-    <row r="10" spans="1:71" ht="141" customHeight="1">
-      <c r="A10" s="259" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="260"/>
-      <c r="C10" s="241"/>
-      <c r="D10" s="242"/>
-      <c r="E10" s="242"/>
-      <c r="F10" s="242"/>
-      <c r="G10" s="242"/>
-      <c r="H10" s="242"/>
-      <c r="I10" s="243"/>
-      <c r="J10" s="271" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="272"/>
-      <c r="L10" s="272"/>
-      <c r="M10" s="272"/>
-      <c r="N10" s="272"/>
-      <c r="O10" s="272"/>
-      <c r="P10" s="273"/>
+      <c r="K10" s="283"/>
+      <c r="L10" s="283"/>
+      <c r="M10" s="283"/>
+      <c r="N10" s="283"/>
+      <c r="O10" s="283"/>
+      <c r="P10" s="284"/>
       <c r="Q10" s="266" t="s">
         <v>139</v>
       </c>
@@ -27632,577 +28041,739 @@
       <c r="Y10" s="267"/>
       <c r="Z10" s="267"/>
       <c r="AA10" s="268"/>
-      <c r="AB10" s="249"/>
-      <c r="AC10" s="250"/>
-      <c r="AD10" s="250"/>
-      <c r="AE10" s="250"/>
-      <c r="AF10" s="250"/>
-      <c r="AG10" s="250"/>
-      <c r="AH10" s="250"/>
-      <c r="AI10" s="250"/>
-      <c r="AJ10" s="250"/>
-      <c r="AK10" s="251" t="s">
+      <c r="AB10" s="272"/>
+      <c r="AC10" s="273"/>
+      <c r="AD10" s="273"/>
+      <c r="AE10" s="273"/>
+      <c r="AF10" s="273"/>
+      <c r="AG10" s="273"/>
+      <c r="AH10" s="273"/>
+      <c r="AI10" s="273"/>
+      <c r="AJ10" s="273"/>
+      <c r="AK10" s="277" t="s">
+        <v>130</v>
+      </c>
+      <c r="AL10" s="270"/>
+      <c r="AM10" s="270"/>
+      <c r="AN10" s="270"/>
+      <c r="AO10" s="270"/>
+      <c r="AP10" s="270"/>
+      <c r="AQ10" s="270"/>
+      <c r="AR10" s="270"/>
+      <c r="AS10" s="270"/>
+      <c r="AT10" s="270"/>
+      <c r="AU10" s="270"/>
+      <c r="AV10" s="270"/>
+      <c r="AW10" s="270"/>
+      <c r="AX10" s="270"/>
+      <c r="AY10" s="270"/>
+      <c r="AZ10" s="270"/>
+      <c r="BA10" s="270"/>
+      <c r="BB10" s="270"/>
+      <c r="BC10" s="270"/>
+      <c r="BD10" s="270"/>
+      <c r="BE10" s="270"/>
+      <c r="BF10" s="270"/>
+      <c r="BG10" s="270"/>
+      <c r="BH10" s="270"/>
+      <c r="BI10" s="270"/>
+      <c r="BJ10" s="270"/>
+      <c r="BK10" s="270"/>
+      <c r="BL10" s="270"/>
+      <c r="BM10" s="270"/>
+      <c r="BN10" s="270"/>
+      <c r="BO10" s="270"/>
+      <c r="BP10" s="270"/>
+      <c r="BQ10" s="270"/>
+      <c r="BR10" s="270"/>
+      <c r="BS10" s="278"/>
+    </row>
+    <row r="11" spans="1:71" ht="54.75" customHeight="1">
+      <c r="A11" s="239" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="240"/>
+      <c r="C11" s="259"/>
+      <c r="D11" s="260"/>
+      <c r="E11" s="260"/>
+      <c r="F11" s="260"/>
+      <c r="G11" s="260"/>
+      <c r="H11" s="260"/>
+      <c r="I11" s="261"/>
+      <c r="J11" s="282" t="s">
+        <v>47</v>
+      </c>
+      <c r="K11" s="283"/>
+      <c r="L11" s="283"/>
+      <c r="M11" s="283"/>
+      <c r="N11" s="283"/>
+      <c r="O11" s="283"/>
+      <c r="P11" s="284"/>
+      <c r="Q11" s="247" t="s">
+        <v>139</v>
+      </c>
+      <c r="R11" s="248"/>
+      <c r="S11" s="248"/>
+      <c r="T11" s="248"/>
+      <c r="U11" s="248"/>
+      <c r="V11" s="248"/>
+      <c r="W11" s="248"/>
+      <c r="X11" s="248"/>
+      <c r="Y11" s="248"/>
+      <c r="Z11" s="248"/>
+      <c r="AA11" s="249"/>
+      <c r="AB11" s="272"/>
+      <c r="AC11" s="273"/>
+      <c r="AD11" s="273"/>
+      <c r="AE11" s="273"/>
+      <c r="AF11" s="273"/>
+      <c r="AG11" s="273"/>
+      <c r="AH11" s="273"/>
+      <c r="AI11" s="273"/>
+      <c r="AJ11" s="273"/>
+      <c r="AK11" s="252" t="s">
+        <v>123</v>
+      </c>
+      <c r="AL11" s="253"/>
+      <c r="AM11" s="253"/>
+      <c r="AN11" s="253"/>
+      <c r="AO11" s="253"/>
+      <c r="AP11" s="253"/>
+      <c r="AQ11" s="253"/>
+      <c r="AR11" s="253"/>
+      <c r="AS11" s="253"/>
+      <c r="AT11" s="253"/>
+      <c r="AU11" s="253"/>
+      <c r="AV11" s="253"/>
+      <c r="AW11" s="253"/>
+      <c r="AX11" s="253"/>
+      <c r="AY11" s="253"/>
+      <c r="AZ11" s="253"/>
+      <c r="BA11" s="253"/>
+      <c r="BB11" s="253"/>
+      <c r="BC11" s="253"/>
+      <c r="BD11" s="253"/>
+      <c r="BE11" s="253"/>
+      <c r="BF11" s="253"/>
+      <c r="BG11" s="253"/>
+      <c r="BH11" s="253"/>
+      <c r="BI11" s="253"/>
+      <c r="BJ11" s="253"/>
+      <c r="BK11" s="253"/>
+      <c r="BL11" s="253"/>
+      <c r="BM11" s="253"/>
+      <c r="BN11" s="253"/>
+      <c r="BO11" s="253"/>
+      <c r="BP11" s="253"/>
+      <c r="BQ11" s="253"/>
+      <c r="BR11" s="253"/>
+      <c r="BS11" s="254"/>
+    </row>
+    <row r="12" spans="1:71" ht="141" customHeight="1">
+      <c r="A12" s="239" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="240"/>
+      <c r="C12" s="259"/>
+      <c r="D12" s="260"/>
+      <c r="E12" s="260"/>
+      <c r="F12" s="260"/>
+      <c r="G12" s="260"/>
+      <c r="H12" s="260"/>
+      <c r="I12" s="261"/>
+      <c r="J12" s="279" t="s">
+        <v>71</v>
+      </c>
+      <c r="K12" s="280"/>
+      <c r="L12" s="280"/>
+      <c r="M12" s="280"/>
+      <c r="N12" s="280"/>
+      <c r="O12" s="280"/>
+      <c r="P12" s="281"/>
+      <c r="Q12" s="274" t="s">
+        <v>139</v>
+      </c>
+      <c r="R12" s="275"/>
+      <c r="S12" s="275"/>
+      <c r="T12" s="275"/>
+      <c r="U12" s="275"/>
+      <c r="V12" s="275"/>
+      <c r="W12" s="275"/>
+      <c r="X12" s="275"/>
+      <c r="Y12" s="275"/>
+      <c r="Z12" s="275"/>
+      <c r="AA12" s="276"/>
+      <c r="AB12" s="250"/>
+      <c r="AC12" s="251"/>
+      <c r="AD12" s="251"/>
+      <c r="AE12" s="251"/>
+      <c r="AF12" s="251"/>
+      <c r="AG12" s="251"/>
+      <c r="AH12" s="251"/>
+      <c r="AI12" s="251"/>
+      <c r="AJ12" s="251"/>
+      <c r="AK12" s="252" t="s">
         <v>125</v>
       </c>
-      <c r="AL10" s="247"/>
-      <c r="AM10" s="247"/>
-      <c r="AN10" s="247"/>
-      <c r="AO10" s="247"/>
-      <c r="AP10" s="247"/>
-      <c r="AQ10" s="247"/>
-      <c r="AR10" s="247"/>
-      <c r="AS10" s="247"/>
-      <c r="AT10" s="247"/>
-      <c r="AU10" s="247"/>
-      <c r="AV10" s="247"/>
-      <c r="AW10" s="247"/>
-      <c r="AX10" s="247"/>
-      <c r="AY10" s="247"/>
-      <c r="AZ10" s="247"/>
-      <c r="BA10" s="247"/>
-      <c r="BB10" s="247"/>
-      <c r="BC10" s="247"/>
-      <c r="BD10" s="247"/>
-      <c r="BE10" s="247"/>
-      <c r="BF10" s="247"/>
-      <c r="BG10" s="247"/>
-      <c r="BH10" s="247"/>
-      <c r="BI10" s="247"/>
-      <c r="BJ10" s="247"/>
-      <c r="BK10" s="247"/>
-      <c r="BL10" s="247"/>
-      <c r="BM10" s="247"/>
-      <c r="BN10" s="247"/>
-      <c r="BO10" s="247"/>
-      <c r="BP10" s="247"/>
-      <c r="BQ10" s="247"/>
-      <c r="BR10" s="247"/>
-      <c r="BS10" s="252"/>
-    </row>
-    <row r="11" spans="1:71" ht="33.75" customHeight="1">
-      <c r="A11" s="259" t="s">
+      <c r="AL12" s="253"/>
+      <c r="AM12" s="253"/>
+      <c r="AN12" s="253"/>
+      <c r="AO12" s="253"/>
+      <c r="AP12" s="253"/>
+      <c r="AQ12" s="253"/>
+      <c r="AR12" s="253"/>
+      <c r="AS12" s="253"/>
+      <c r="AT12" s="253"/>
+      <c r="AU12" s="253"/>
+      <c r="AV12" s="253"/>
+      <c r="AW12" s="253"/>
+      <c r="AX12" s="253"/>
+      <c r="AY12" s="253"/>
+      <c r="AZ12" s="253"/>
+      <c r="BA12" s="253"/>
+      <c r="BB12" s="253"/>
+      <c r="BC12" s="253"/>
+      <c r="BD12" s="253"/>
+      <c r="BE12" s="253"/>
+      <c r="BF12" s="253"/>
+      <c r="BG12" s="253"/>
+      <c r="BH12" s="253"/>
+      <c r="BI12" s="253"/>
+      <c r="BJ12" s="253"/>
+      <c r="BK12" s="253"/>
+      <c r="BL12" s="253"/>
+      <c r="BM12" s="253"/>
+      <c r="BN12" s="253"/>
+      <c r="BO12" s="253"/>
+      <c r="BP12" s="253"/>
+      <c r="BQ12" s="253"/>
+      <c r="BR12" s="253"/>
+      <c r="BS12" s="254"/>
+    </row>
+    <row r="13" spans="1:71" ht="33.75" customHeight="1">
+      <c r="A13" s="239" t="s">
         <v>78</v>
       </c>
-      <c r="B11" s="260"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
-      <c r="H11" s="132"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="261" t="s">
+      <c r="B13" s="240"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="132"/>
+      <c r="E13" s="132"/>
+      <c r="F13" s="132"/>
+      <c r="G13" s="132"/>
+      <c r="H13" s="132"/>
+      <c r="I13" s="133"/>
+      <c r="J13" s="269" t="s">
         <v>72</v>
       </c>
-      <c r="K11" s="262"/>
-      <c r="L11" s="262"/>
-      <c r="M11" s="262"/>
-      <c r="N11" s="262"/>
-      <c r="O11" s="262"/>
-      <c r="P11" s="263"/>
-      <c r="Q11" s="256" t="s">
+      <c r="K13" s="270"/>
+      <c r="L13" s="270"/>
+      <c r="M13" s="270"/>
+      <c r="N13" s="270"/>
+      <c r="O13" s="270"/>
+      <c r="P13" s="271"/>
+      <c r="Q13" s="247" t="s">
         <v>140</v>
       </c>
-      <c r="R11" s="257"/>
-      <c r="S11" s="257"/>
-      <c r="T11" s="257"/>
-      <c r="U11" s="257"/>
-      <c r="V11" s="257"/>
-      <c r="W11" s="257"/>
-      <c r="X11" s="257"/>
-      <c r="Y11" s="257"/>
-      <c r="Z11" s="257"/>
-      <c r="AA11" s="258"/>
-      <c r="AB11" s="264"/>
-      <c r="AC11" s="265"/>
-      <c r="AD11" s="265"/>
-      <c r="AE11" s="265"/>
-      <c r="AF11" s="265"/>
-      <c r="AG11" s="265"/>
-      <c r="AH11" s="265"/>
-      <c r="AI11" s="265"/>
-      <c r="AJ11" s="265"/>
-      <c r="AK11" s="251" t="s">
+      <c r="R13" s="248"/>
+      <c r="S13" s="248"/>
+      <c r="T13" s="248"/>
+      <c r="U13" s="248"/>
+      <c r="V13" s="248"/>
+      <c r="W13" s="248"/>
+      <c r="X13" s="248"/>
+      <c r="Y13" s="248"/>
+      <c r="Z13" s="248"/>
+      <c r="AA13" s="249"/>
+      <c r="AB13" s="272"/>
+      <c r="AC13" s="273"/>
+      <c r="AD13" s="273"/>
+      <c r="AE13" s="273"/>
+      <c r="AF13" s="273"/>
+      <c r="AG13" s="273"/>
+      <c r="AH13" s="273"/>
+      <c r="AI13" s="273"/>
+      <c r="AJ13" s="273"/>
+      <c r="AK13" s="252" t="s">
         <v>73</v>
       </c>
-      <c r="AL11" s="247"/>
-      <c r="AM11" s="247"/>
-      <c r="AN11" s="247"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="247"/>
-      <c r="AQ11" s="247"/>
-      <c r="AR11" s="247"/>
-      <c r="AS11" s="247"/>
-      <c r="AT11" s="247"/>
-      <c r="AU11" s="247"/>
-      <c r="AV11" s="247"/>
-      <c r="AW11" s="247"/>
-      <c r="AX11" s="247"/>
-      <c r="AY11" s="247"/>
-      <c r="AZ11" s="247"/>
-      <c r="BA11" s="247"/>
-      <c r="BB11" s="247"/>
-      <c r="BC11" s="247"/>
-      <c r="BD11" s="247"/>
-      <c r="BE11" s="247"/>
-      <c r="BF11" s="247"/>
-      <c r="BG11" s="247"/>
-      <c r="BH11" s="247"/>
-      <c r="BI11" s="247"/>
-      <c r="BJ11" s="247"/>
-      <c r="BK11" s="247"/>
-      <c r="BL11" s="247"/>
-      <c r="BM11" s="247"/>
-      <c r="BN11" s="247"/>
-      <c r="BO11" s="247"/>
-      <c r="BP11" s="247"/>
-      <c r="BQ11" s="247"/>
-      <c r="BR11" s="247"/>
-      <c r="BS11" s="252"/>
-    </row>
-    <row r="12" spans="1:71" ht="45.75" customHeight="1">
-      <c r="A12" s="259" t="s">
+      <c r="AL13" s="253"/>
+      <c r="AM13" s="253"/>
+      <c r="AN13" s="253"/>
+      <c r="AO13" s="253"/>
+      <c r="AP13" s="253"/>
+      <c r="AQ13" s="253"/>
+      <c r="AR13" s="253"/>
+      <c r="AS13" s="253"/>
+      <c r="AT13" s="253"/>
+      <c r="AU13" s="253"/>
+      <c r="AV13" s="253"/>
+      <c r="AW13" s="253"/>
+      <c r="AX13" s="253"/>
+      <c r="AY13" s="253"/>
+      <c r="AZ13" s="253"/>
+      <c r="BA13" s="253"/>
+      <c r="BB13" s="253"/>
+      <c r="BC13" s="253"/>
+      <c r="BD13" s="253"/>
+      <c r="BE13" s="253"/>
+      <c r="BF13" s="253"/>
+      <c r="BG13" s="253"/>
+      <c r="BH13" s="253"/>
+      <c r="BI13" s="253"/>
+      <c r="BJ13" s="253"/>
+      <c r="BK13" s="253"/>
+      <c r="BL13" s="253"/>
+      <c r="BM13" s="253"/>
+      <c r="BN13" s="253"/>
+      <c r="BO13" s="253"/>
+      <c r="BP13" s="253"/>
+      <c r="BQ13" s="253"/>
+      <c r="BR13" s="253"/>
+      <c r="BS13" s="254"/>
+    </row>
+    <row r="14" spans="1:71" ht="45.75" customHeight="1">
+      <c r="A14" s="239" t="s">
         <v>79</v>
       </c>
-      <c r="B12" s="260"/>
-      <c r="C12" s="241"/>
-      <c r="D12" s="242"/>
-      <c r="E12" s="242"/>
-      <c r="F12" s="242"/>
-      <c r="G12" s="242"/>
-      <c r="H12" s="242"/>
-      <c r="I12" s="243"/>
-      <c r="J12" s="261" t="s">
+      <c r="B14" s="240"/>
+      <c r="C14" s="259"/>
+      <c r="D14" s="260"/>
+      <c r="E14" s="260"/>
+      <c r="F14" s="260"/>
+      <c r="G14" s="260"/>
+      <c r="H14" s="260"/>
+      <c r="I14" s="261"/>
+      <c r="J14" s="269" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="262"/>
-      <c r="L12" s="262"/>
-      <c r="M12" s="262"/>
-      <c r="N12" s="262"/>
-      <c r="O12" s="262"/>
-      <c r="P12" s="263"/>
-      <c r="Q12" s="253"/>
-      <c r="R12" s="254"/>
-      <c r="S12" s="254"/>
-      <c r="T12" s="254"/>
-      <c r="U12" s="254"/>
-      <c r="V12" s="254"/>
-      <c r="W12" s="254"/>
-      <c r="X12" s="254"/>
-      <c r="Y12" s="254"/>
-      <c r="Z12" s="254"/>
-      <c r="AA12" s="255"/>
-      <c r="AB12" s="264" t="s">
+      <c r="K14" s="270"/>
+      <c r="L14" s="270"/>
+      <c r="M14" s="270"/>
+      <c r="N14" s="270"/>
+      <c r="O14" s="270"/>
+      <c r="P14" s="271"/>
+      <c r="Q14" s="266"/>
+      <c r="R14" s="267"/>
+      <c r="S14" s="267"/>
+      <c r="T14" s="267"/>
+      <c r="U14" s="267"/>
+      <c r="V14" s="267"/>
+      <c r="W14" s="267"/>
+      <c r="X14" s="267"/>
+      <c r="Y14" s="267"/>
+      <c r="Z14" s="267"/>
+      <c r="AA14" s="268"/>
+      <c r="AB14" s="272" t="s">
         <v>142</v>
       </c>
-      <c r="AC12" s="265"/>
-      <c r="AD12" s="265"/>
-      <c r="AE12" s="265"/>
-      <c r="AF12" s="265"/>
-      <c r="AG12" s="265"/>
-      <c r="AH12" s="265"/>
-      <c r="AI12" s="265"/>
-      <c r="AJ12" s="265"/>
-      <c r="AK12" s="251" t="s">
+      <c r="AC14" s="273"/>
+      <c r="AD14" s="273"/>
+      <c r="AE14" s="273"/>
+      <c r="AF14" s="273"/>
+      <c r="AG14" s="273"/>
+      <c r="AH14" s="273"/>
+      <c r="AI14" s="273"/>
+      <c r="AJ14" s="273"/>
+      <c r="AK14" s="252" t="s">
         <v>124</v>
       </c>
-      <c r="AL12" s="247"/>
-      <c r="AM12" s="247"/>
-      <c r="AN12" s="247"/>
-      <c r="AO12" s="247"/>
-      <c r="AP12" s="247"/>
-      <c r="AQ12" s="247"/>
-      <c r="AR12" s="247"/>
-      <c r="AS12" s="247"/>
-      <c r="AT12" s="247"/>
-      <c r="AU12" s="247"/>
-      <c r="AV12" s="247"/>
-      <c r="AW12" s="247"/>
-      <c r="AX12" s="247"/>
-      <c r="AY12" s="247"/>
-      <c r="AZ12" s="247"/>
-      <c r="BA12" s="247"/>
-      <c r="BB12" s="247"/>
-      <c r="BC12" s="247"/>
-      <c r="BD12" s="247"/>
-      <c r="BE12" s="247"/>
-      <c r="BF12" s="247"/>
-      <c r="BG12" s="247"/>
-      <c r="BH12" s="247"/>
-      <c r="BI12" s="247"/>
-      <c r="BJ12" s="247"/>
-      <c r="BK12" s="247"/>
-      <c r="BL12" s="247"/>
-      <c r="BM12" s="247"/>
-      <c r="BN12" s="247"/>
-      <c r="BO12" s="247"/>
-      <c r="BP12" s="247"/>
-      <c r="BQ12" s="247"/>
-      <c r="BR12" s="247"/>
-      <c r="BS12" s="252"/>
-    </row>
-    <row r="13" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A13" s="259" t="s">
+      <c r="AL14" s="253"/>
+      <c r="AM14" s="253"/>
+      <c r="AN14" s="253"/>
+      <c r="AO14" s="253"/>
+      <c r="AP14" s="253"/>
+      <c r="AQ14" s="253"/>
+      <c r="AR14" s="253"/>
+      <c r="AS14" s="253"/>
+      <c r="AT14" s="253"/>
+      <c r="AU14" s="253"/>
+      <c r="AV14" s="253"/>
+      <c r="AW14" s="253"/>
+      <c r="AX14" s="253"/>
+      <c r="AY14" s="253"/>
+      <c r="AZ14" s="253"/>
+      <c r="BA14" s="253"/>
+      <c r="BB14" s="253"/>
+      <c r="BC14" s="253"/>
+      <c r="BD14" s="253"/>
+      <c r="BE14" s="253"/>
+      <c r="BF14" s="253"/>
+      <c r="BG14" s="253"/>
+      <c r="BH14" s="253"/>
+      <c r="BI14" s="253"/>
+      <c r="BJ14" s="253"/>
+      <c r="BK14" s="253"/>
+      <c r="BL14" s="253"/>
+      <c r="BM14" s="253"/>
+      <c r="BN14" s="253"/>
+      <c r="BO14" s="253"/>
+      <c r="BP14" s="253"/>
+      <c r="BQ14" s="253"/>
+      <c r="BR14" s="253"/>
+      <c r="BS14" s="254"/>
+    </row>
+    <row r="15" spans="1:71" ht="15.75" customHeight="1">
+      <c r="A15" s="239" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="260"/>
-      <c r="C13" s="241"/>
-      <c r="D13" s="242"/>
-      <c r="E13" s="242"/>
-      <c r="F13" s="242"/>
-      <c r="G13" s="242"/>
-      <c r="H13" s="242"/>
-      <c r="I13" s="243"/>
-      <c r="J13" s="241" t="s">
+      <c r="B15" s="240"/>
+      <c r="C15" s="259"/>
+      <c r="D15" s="260"/>
+      <c r="E15" s="260"/>
+      <c r="F15" s="260"/>
+      <c r="G15" s="260"/>
+      <c r="H15" s="260"/>
+      <c r="I15" s="261"/>
+      <c r="J15" s="259" t="s">
         <v>141</v>
       </c>
-      <c r="K13" s="242"/>
-      <c r="L13" s="242"/>
-      <c r="M13" s="242"/>
-      <c r="N13" s="242"/>
-      <c r="O13" s="242"/>
-      <c r="P13" s="243"/>
-      <c r="Q13" s="256"/>
-      <c r="R13" s="257"/>
-      <c r="S13" s="257"/>
-      <c r="T13" s="257"/>
-      <c r="U13" s="257"/>
-      <c r="V13" s="257"/>
-      <c r="W13" s="257"/>
-      <c r="X13" s="257"/>
-      <c r="Y13" s="257"/>
-      <c r="Z13" s="257"/>
-      <c r="AA13" s="258"/>
-      <c r="AB13" s="249"/>
-      <c r="AC13" s="250"/>
-      <c r="AD13" s="250"/>
-      <c r="AE13" s="250"/>
-      <c r="AF13" s="250"/>
-      <c r="AG13" s="250"/>
-      <c r="AH13" s="250"/>
-      <c r="AI13" s="250"/>
-      <c r="AJ13" s="250"/>
-      <c r="AK13" s="251" t="s">
+      <c r="K15" s="260"/>
+      <c r="L15" s="260"/>
+      <c r="M15" s="260"/>
+      <c r="N15" s="260"/>
+      <c r="O15" s="260"/>
+      <c r="P15" s="261"/>
+      <c r="Q15" s="247"/>
+      <c r="R15" s="248"/>
+      <c r="S15" s="248"/>
+      <c r="T15" s="248"/>
+      <c r="U15" s="248"/>
+      <c r="V15" s="248"/>
+      <c r="W15" s="248"/>
+      <c r="X15" s="248"/>
+      <c r="Y15" s="248"/>
+      <c r="Z15" s="248"/>
+      <c r="AA15" s="249"/>
+      <c r="AB15" s="250"/>
+      <c r="AC15" s="251"/>
+      <c r="AD15" s="251"/>
+      <c r="AE15" s="251"/>
+      <c r="AF15" s="251"/>
+      <c r="AG15" s="251"/>
+      <c r="AH15" s="251"/>
+      <c r="AI15" s="251"/>
+      <c r="AJ15" s="251"/>
+      <c r="AK15" s="252" t="s">
         <v>129</v>
       </c>
-      <c r="AL13" s="247"/>
-      <c r="AM13" s="247"/>
-      <c r="AN13" s="247"/>
-      <c r="AO13" s="247"/>
-      <c r="AP13" s="247"/>
-      <c r="AQ13" s="247"/>
-      <c r="AR13" s="247"/>
-      <c r="AS13" s="247"/>
-      <c r="AT13" s="247"/>
-      <c r="AU13" s="247"/>
-      <c r="AV13" s="247"/>
-      <c r="AW13" s="247"/>
-      <c r="AX13" s="247"/>
-      <c r="AY13" s="247"/>
-      <c r="AZ13" s="247"/>
-      <c r="BA13" s="247"/>
-      <c r="BB13" s="247"/>
-      <c r="BC13" s="247"/>
-      <c r="BD13" s="247"/>
-      <c r="BE13" s="247"/>
-      <c r="BF13" s="247"/>
-      <c r="BG13" s="247"/>
-      <c r="BH13" s="247"/>
-      <c r="BI13" s="247"/>
-      <c r="BJ13" s="247"/>
-      <c r="BK13" s="247"/>
-      <c r="BL13" s="247"/>
-      <c r="BM13" s="247"/>
-      <c r="BN13" s="247"/>
-      <c r="BO13" s="247"/>
-      <c r="BP13" s="247"/>
-      <c r="BQ13" s="247"/>
-      <c r="BR13" s="247"/>
-      <c r="BS13" s="252"/>
-    </row>
-    <row r="14" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A14" s="259" t="s">
+      <c r="AL15" s="253"/>
+      <c r="AM15" s="253"/>
+      <c r="AN15" s="253"/>
+      <c r="AO15" s="253"/>
+      <c r="AP15" s="253"/>
+      <c r="AQ15" s="253"/>
+      <c r="AR15" s="253"/>
+      <c r="AS15" s="253"/>
+      <c r="AT15" s="253"/>
+      <c r="AU15" s="253"/>
+      <c r="AV15" s="253"/>
+      <c r="AW15" s="253"/>
+      <c r="AX15" s="253"/>
+      <c r="AY15" s="253"/>
+      <c r="AZ15" s="253"/>
+      <c r="BA15" s="253"/>
+      <c r="BB15" s="253"/>
+      <c r="BC15" s="253"/>
+      <c r="BD15" s="253"/>
+      <c r="BE15" s="253"/>
+      <c r="BF15" s="253"/>
+      <c r="BG15" s="253"/>
+      <c r="BH15" s="253"/>
+      <c r="BI15" s="253"/>
+      <c r="BJ15" s="253"/>
+      <c r="BK15" s="253"/>
+      <c r="BL15" s="253"/>
+      <c r="BM15" s="253"/>
+      <c r="BN15" s="253"/>
+      <c r="BO15" s="253"/>
+      <c r="BP15" s="253"/>
+      <c r="BQ15" s="253"/>
+      <c r="BR15" s="253"/>
+      <c r="BS15" s="254"/>
+    </row>
+    <row r="16" spans="1:71" ht="15.75" customHeight="1">
+      <c r="A16" s="239" t="s">
         <v>92</v>
       </c>
-      <c r="B14" s="260"/>
-      <c r="C14" s="241"/>
-      <c r="D14" s="242"/>
-      <c r="E14" s="242"/>
-      <c r="F14" s="242"/>
-      <c r="G14" s="242"/>
-      <c r="H14" s="242"/>
-      <c r="I14" s="243"/>
-      <c r="J14" s="241" t="s">
+      <c r="B16" s="240"/>
+      <c r="C16" s="259"/>
+      <c r="D16" s="260"/>
+      <c r="E16" s="260"/>
+      <c r="F16" s="260"/>
+      <c r="G16" s="260"/>
+      <c r="H16" s="260"/>
+      <c r="I16" s="261"/>
+      <c r="J16" s="259" t="s">
         <v>75</v>
       </c>
-      <c r="K14" s="242"/>
-      <c r="L14" s="242"/>
-      <c r="M14" s="242"/>
-      <c r="N14" s="242"/>
-      <c r="O14" s="242"/>
-      <c r="P14" s="243"/>
-      <c r="Q14" s="256"/>
-      <c r="R14" s="257"/>
-      <c r="S14" s="257"/>
-      <c r="T14" s="257"/>
-      <c r="U14" s="257"/>
-      <c r="V14" s="257"/>
-      <c r="W14" s="257"/>
-      <c r="X14" s="257"/>
-      <c r="Y14" s="257"/>
-      <c r="Z14" s="257"/>
-      <c r="AA14" s="258"/>
-      <c r="AB14" s="249"/>
-      <c r="AC14" s="250"/>
-      <c r="AD14" s="250"/>
-      <c r="AE14" s="250"/>
-      <c r="AF14" s="250"/>
-      <c r="AG14" s="250"/>
-      <c r="AH14" s="250"/>
-      <c r="AI14" s="250"/>
-      <c r="AJ14" s="250"/>
-      <c r="AK14" s="251" t="s">
+      <c r="K16" s="260"/>
+      <c r="L16" s="260"/>
+      <c r="M16" s="260"/>
+      <c r="N16" s="260"/>
+      <c r="O16" s="260"/>
+      <c r="P16" s="261"/>
+      <c r="Q16" s="247"/>
+      <c r="R16" s="248"/>
+      <c r="S16" s="248"/>
+      <c r="T16" s="248"/>
+      <c r="U16" s="248"/>
+      <c r="V16" s="248"/>
+      <c r="W16" s="248"/>
+      <c r="X16" s="248"/>
+      <c r="Y16" s="248"/>
+      <c r="Z16" s="248"/>
+      <c r="AA16" s="249"/>
+      <c r="AB16" s="250"/>
+      <c r="AC16" s="251"/>
+      <c r="AD16" s="251"/>
+      <c r="AE16" s="251"/>
+      <c r="AF16" s="251"/>
+      <c r="AG16" s="251"/>
+      <c r="AH16" s="251"/>
+      <c r="AI16" s="251"/>
+      <c r="AJ16" s="251"/>
+      <c r="AK16" s="252" t="s">
         <v>67</v>
       </c>
-      <c r="AL14" s="247"/>
-      <c r="AM14" s="247"/>
-      <c r="AN14" s="247"/>
-      <c r="AO14" s="247"/>
-      <c r="AP14" s="247"/>
-      <c r="AQ14" s="247"/>
-      <c r="AR14" s="247"/>
-      <c r="AS14" s="247"/>
-      <c r="AT14" s="247"/>
-      <c r="AU14" s="247"/>
-      <c r="AV14" s="247"/>
-      <c r="AW14" s="247"/>
-      <c r="AX14" s="247"/>
-      <c r="AY14" s="247"/>
-      <c r="AZ14" s="247"/>
-      <c r="BA14" s="247"/>
-      <c r="BB14" s="247"/>
-      <c r="BC14" s="247"/>
-      <c r="BD14" s="247"/>
-      <c r="BE14" s="247"/>
-      <c r="BF14" s="247"/>
-      <c r="BG14" s="247"/>
-      <c r="BH14" s="247"/>
-      <c r="BI14" s="247"/>
-      <c r="BJ14" s="247"/>
-      <c r="BK14" s="247"/>
-      <c r="BL14" s="247"/>
-      <c r="BM14" s="247"/>
-      <c r="BN14" s="247"/>
-      <c r="BO14" s="247"/>
-      <c r="BP14" s="247"/>
-      <c r="BQ14" s="247"/>
-      <c r="BR14" s="247"/>
-      <c r="BS14" s="252"/>
-    </row>
-    <row r="15" spans="1:71" ht="46" customHeight="1">
-      <c r="A15" s="259" t="s">
+      <c r="AL16" s="253"/>
+      <c r="AM16" s="253"/>
+      <c r="AN16" s="253"/>
+      <c r="AO16" s="253"/>
+      <c r="AP16" s="253"/>
+      <c r="AQ16" s="253"/>
+      <c r="AR16" s="253"/>
+      <c r="AS16" s="253"/>
+      <c r="AT16" s="253"/>
+      <c r="AU16" s="253"/>
+      <c r="AV16" s="253"/>
+      <c r="AW16" s="253"/>
+      <c r="AX16" s="253"/>
+      <c r="AY16" s="253"/>
+      <c r="AZ16" s="253"/>
+      <c r="BA16" s="253"/>
+      <c r="BB16" s="253"/>
+      <c r="BC16" s="253"/>
+      <c r="BD16" s="253"/>
+      <c r="BE16" s="253"/>
+      <c r="BF16" s="253"/>
+      <c r="BG16" s="253"/>
+      <c r="BH16" s="253"/>
+      <c r="BI16" s="253"/>
+      <c r="BJ16" s="253"/>
+      <c r="BK16" s="253"/>
+      <c r="BL16" s="253"/>
+      <c r="BM16" s="253"/>
+      <c r="BN16" s="253"/>
+      <c r="BO16" s="253"/>
+      <c r="BP16" s="253"/>
+      <c r="BQ16" s="253"/>
+      <c r="BR16" s="253"/>
+      <c r="BS16" s="254"/>
+    </row>
+    <row r="17" spans="1:71" ht="46" customHeight="1">
+      <c r="A17" s="239" t="s">
         <v>128</v>
       </c>
-      <c r="B15" s="260"/>
-      <c r="C15" s="241"/>
-      <c r="D15" s="242"/>
-      <c r="E15" s="242"/>
-      <c r="F15" s="242"/>
-      <c r="G15" s="242"/>
-      <c r="H15" s="242"/>
-      <c r="I15" s="243"/>
-      <c r="J15" s="241" t="s">
+      <c r="B17" s="240"/>
+      <c r="C17" s="259"/>
+      <c r="D17" s="260"/>
+      <c r="E17" s="260"/>
+      <c r="F17" s="260"/>
+      <c r="G17" s="260"/>
+      <c r="H17" s="260"/>
+      <c r="I17" s="261"/>
+      <c r="J17" s="259" t="s">
         <v>76</v>
       </c>
-      <c r="K15" s="242"/>
-      <c r="L15" s="242"/>
-      <c r="M15" s="242"/>
-      <c r="N15" s="242"/>
-      <c r="O15" s="242"/>
-      <c r="P15" s="243"/>
-      <c r="Q15" s="256"/>
-      <c r="R15" s="257"/>
-      <c r="S15" s="257"/>
-      <c r="T15" s="257"/>
-      <c r="U15" s="257"/>
-      <c r="V15" s="257"/>
-      <c r="W15" s="257"/>
-      <c r="X15" s="257"/>
-      <c r="Y15" s="257"/>
-      <c r="Z15" s="257"/>
-      <c r="AA15" s="258"/>
-      <c r="AB15" s="249"/>
-      <c r="AC15" s="250"/>
-      <c r="AD15" s="250"/>
-      <c r="AE15" s="250"/>
-      <c r="AF15" s="250"/>
-      <c r="AG15" s="250"/>
-      <c r="AH15" s="250"/>
-      <c r="AI15" s="250"/>
-      <c r="AJ15" s="250"/>
-      <c r="AK15" s="251"/>
-      <c r="AL15" s="247"/>
-      <c r="AM15" s="247"/>
-      <c r="AN15" s="247"/>
-      <c r="AO15" s="247"/>
-      <c r="AP15" s="247"/>
-      <c r="AQ15" s="247"/>
-      <c r="AR15" s="247"/>
-      <c r="AS15" s="247"/>
-      <c r="AT15" s="247"/>
-      <c r="AU15" s="247"/>
-      <c r="AV15" s="247"/>
-      <c r="AW15" s="247"/>
-      <c r="AX15" s="247"/>
-      <c r="AY15" s="247"/>
-      <c r="AZ15" s="247"/>
-      <c r="BA15" s="247"/>
-      <c r="BB15" s="247"/>
-      <c r="BC15" s="247"/>
-      <c r="BD15" s="247"/>
-      <c r="BE15" s="247"/>
-      <c r="BF15" s="247"/>
-      <c r="BG15" s="247"/>
-      <c r="BH15" s="247"/>
-      <c r="BI15" s="247"/>
-      <c r="BJ15" s="247"/>
-      <c r="BK15" s="247"/>
-      <c r="BL15" s="247"/>
-      <c r="BM15" s="247"/>
-      <c r="BN15" s="247"/>
-      <c r="BO15" s="247"/>
-      <c r="BP15" s="247"/>
-      <c r="BQ15" s="247"/>
-      <c r="BR15" s="247"/>
-      <c r="BS15" s="252"/>
-    </row>
-    <row r="16" spans="1:71" ht="15.75" customHeight="1">
-      <c r="A16" s="239"/>
-      <c r="B16" s="240"/>
-      <c r="C16" s="241"/>
-      <c r="D16" s="242"/>
-      <c r="E16" s="242"/>
-      <c r="F16" s="242"/>
-      <c r="G16" s="242"/>
-      <c r="H16" s="242"/>
-      <c r="I16" s="243"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="244"/>
-      <c r="L16" s="244"/>
-      <c r="M16" s="244"/>
-      <c r="N16" s="244"/>
-      <c r="O16" s="244"/>
-      <c r="P16" s="245"/>
-      <c r="Q16" s="246"/>
-      <c r="R16" s="247"/>
-      <c r="S16" s="247"/>
-      <c r="T16" s="247"/>
-      <c r="U16" s="247"/>
-      <c r="V16" s="247"/>
-      <c r="W16" s="247"/>
-      <c r="X16" s="247"/>
-      <c r="Y16" s="247"/>
-      <c r="Z16" s="247"/>
-      <c r="AA16" s="248"/>
-      <c r="AB16" s="249"/>
-      <c r="AC16" s="250"/>
-      <c r="AD16" s="250"/>
-      <c r="AE16" s="250"/>
-      <c r="AF16" s="250"/>
-      <c r="AG16" s="250"/>
-      <c r="AH16" s="250"/>
-      <c r="AI16" s="250"/>
-      <c r="AJ16" s="250"/>
-      <c r="AK16" s="251"/>
-      <c r="AL16" s="247"/>
-      <c r="AM16" s="247"/>
-      <c r="AN16" s="247"/>
-      <c r="AO16" s="247"/>
-      <c r="AP16" s="247"/>
-      <c r="AQ16" s="247"/>
-      <c r="AR16" s="247"/>
-      <c r="AS16" s="247"/>
-      <c r="AT16" s="247"/>
-      <c r="AU16" s="247"/>
-      <c r="AV16" s="247"/>
-      <c r="AW16" s="247"/>
-      <c r="AX16" s="247"/>
-      <c r="AY16" s="247"/>
-      <c r="AZ16" s="247"/>
-      <c r="BA16" s="247"/>
-      <c r="BB16" s="247"/>
-      <c r="BC16" s="247"/>
-      <c r="BD16" s="247"/>
-      <c r="BE16" s="247"/>
-      <c r="BF16" s="247"/>
-      <c r="BG16" s="247"/>
-      <c r="BH16" s="247"/>
-      <c r="BI16" s="247"/>
-      <c r="BJ16" s="247"/>
-      <c r="BK16" s="247"/>
-      <c r="BL16" s="247"/>
-      <c r="BM16" s="247"/>
-      <c r="BN16" s="247"/>
-      <c r="BO16" s="247"/>
-      <c r="BP16" s="247"/>
-      <c r="BQ16" s="247"/>
-      <c r="BR16" s="247"/>
-      <c r="BS16" s="252"/>
-    </row>
-    <row r="17" spans="28:36">
-      <c r="AB17" s="302"/>
-      <c r="AC17" s="302"/>
-      <c r="AD17" s="302"/>
-      <c r="AE17" s="302"/>
-      <c r="AF17" s="302"/>
-      <c r="AG17" s="302"/>
-      <c r="AH17" s="302"/>
-      <c r="AI17" s="302"/>
-      <c r="AJ17" s="302"/>
-    </row>
-    <row r="18" spans="28:36">
-      <c r="AB18" s="303"/>
-      <c r="AC18" s="303"/>
-      <c r="AD18" s="303"/>
-      <c r="AE18" s="303"/>
-      <c r="AF18" s="303"/>
-      <c r="AG18" s="303"/>
-      <c r="AH18" s="303"/>
-      <c r="AI18" s="303"/>
-      <c r="AJ18" s="303"/>
-    </row>
-    <row r="19" spans="28:36">
-      <c r="AB19" s="152"/>
-      <c r="AC19" s="152"/>
-      <c r="AD19" s="152"/>
-      <c r="AE19" s="152"/>
-      <c r="AF19" s="153"/>
-      <c r="AG19" s="152"/>
-      <c r="AH19" s="152"/>
-      <c r="AI19" s="153"/>
-      <c r="AJ19" s="153"/>
+      <c r="K17" s="260"/>
+      <c r="L17" s="260"/>
+      <c r="M17" s="260"/>
+      <c r="N17" s="260"/>
+      <c r="O17" s="260"/>
+      <c r="P17" s="261"/>
+      <c r="Q17" s="247"/>
+      <c r="R17" s="248"/>
+      <c r="S17" s="248"/>
+      <c r="T17" s="248"/>
+      <c r="U17" s="248"/>
+      <c r="V17" s="248"/>
+      <c r="W17" s="248"/>
+      <c r="X17" s="248"/>
+      <c r="Y17" s="248"/>
+      <c r="Z17" s="248"/>
+      <c r="AA17" s="249"/>
+      <c r="AB17" s="250"/>
+      <c r="AC17" s="251"/>
+      <c r="AD17" s="251"/>
+      <c r="AE17" s="251"/>
+      <c r="AF17" s="251"/>
+      <c r="AG17" s="251"/>
+      <c r="AH17" s="251"/>
+      <c r="AI17" s="251"/>
+      <c r="AJ17" s="251"/>
+      <c r="AK17" s="252"/>
+      <c r="AL17" s="253"/>
+      <c r="AM17" s="253"/>
+      <c r="AN17" s="253"/>
+      <c r="AO17" s="253"/>
+      <c r="AP17" s="253"/>
+      <c r="AQ17" s="253"/>
+      <c r="AR17" s="253"/>
+      <c r="AS17" s="253"/>
+      <c r="AT17" s="253"/>
+      <c r="AU17" s="253"/>
+      <c r="AV17" s="253"/>
+      <c r="AW17" s="253"/>
+      <c r="AX17" s="253"/>
+      <c r="AY17" s="253"/>
+      <c r="AZ17" s="253"/>
+      <c r="BA17" s="253"/>
+      <c r="BB17" s="253"/>
+      <c r="BC17" s="253"/>
+      <c r="BD17" s="253"/>
+      <c r="BE17" s="253"/>
+      <c r="BF17" s="253"/>
+      <c r="BG17" s="253"/>
+      <c r="BH17" s="253"/>
+      <c r="BI17" s="253"/>
+      <c r="BJ17" s="253"/>
+      <c r="BK17" s="253"/>
+      <c r="BL17" s="253"/>
+      <c r="BM17" s="253"/>
+      <c r="BN17" s="253"/>
+      <c r="BO17" s="253"/>
+      <c r="BP17" s="253"/>
+      <c r="BQ17" s="253"/>
+      <c r="BR17" s="253"/>
+      <c r="BS17" s="254"/>
+    </row>
+    <row r="18" spans="1:71" ht="15.75" customHeight="1">
+      <c r="A18" s="257"/>
+      <c r="B18" s="258"/>
+      <c r="C18" s="259"/>
+      <c r="D18" s="260"/>
+      <c r="E18" s="260"/>
+      <c r="F18" s="260"/>
+      <c r="G18" s="260"/>
+      <c r="H18" s="260"/>
+      <c r="I18" s="261"/>
+      <c r="J18" s="134"/>
+      <c r="K18" s="262"/>
+      <c r="L18" s="262"/>
+      <c r="M18" s="262"/>
+      <c r="N18" s="262"/>
+      <c r="O18" s="262"/>
+      <c r="P18" s="263"/>
+      <c r="Q18" s="264"/>
+      <c r="R18" s="253"/>
+      <c r="S18" s="253"/>
+      <c r="T18" s="253"/>
+      <c r="U18" s="253"/>
+      <c r="V18" s="253"/>
+      <c r="W18" s="253"/>
+      <c r="X18" s="253"/>
+      <c r="Y18" s="253"/>
+      <c r="Z18" s="253"/>
+      <c r="AA18" s="265"/>
+      <c r="AB18" s="250"/>
+      <c r="AC18" s="251"/>
+      <c r="AD18" s="251"/>
+      <c r="AE18" s="251"/>
+      <c r="AF18" s="251"/>
+      <c r="AG18" s="251"/>
+      <c r="AH18" s="251"/>
+      <c r="AI18" s="251"/>
+      <c r="AJ18" s="251"/>
+      <c r="AK18" s="252"/>
+      <c r="AL18" s="253"/>
+      <c r="AM18" s="253"/>
+      <c r="AN18" s="253"/>
+      <c r="AO18" s="253"/>
+      <c r="AP18" s="253"/>
+      <c r="AQ18" s="253"/>
+      <c r="AR18" s="253"/>
+      <c r="AS18" s="253"/>
+      <c r="AT18" s="253"/>
+      <c r="AU18" s="253"/>
+      <c r="AV18" s="253"/>
+      <c r="AW18" s="253"/>
+      <c r="AX18" s="253"/>
+      <c r="AY18" s="253"/>
+      <c r="AZ18" s="253"/>
+      <c r="BA18" s="253"/>
+      <c r="BB18" s="253"/>
+      <c r="BC18" s="253"/>
+      <c r="BD18" s="253"/>
+      <c r="BE18" s="253"/>
+      <c r="BF18" s="253"/>
+      <c r="BG18" s="253"/>
+      <c r="BH18" s="253"/>
+      <c r="BI18" s="253"/>
+      <c r="BJ18" s="253"/>
+      <c r="BK18" s="253"/>
+      <c r="BL18" s="253"/>
+      <c r="BM18" s="253"/>
+      <c r="BN18" s="253"/>
+      <c r="BO18" s="253"/>
+      <c r="BP18" s="253"/>
+      <c r="BQ18" s="253"/>
+      <c r="BR18" s="253"/>
+      <c r="BS18" s="254"/>
+    </row>
+    <row r="19" spans="1:71">
+      <c r="AB19" s="310"/>
+      <c r="AC19" s="310"/>
+      <c r="AD19" s="310"/>
+      <c r="AE19" s="310"/>
+      <c r="AF19" s="310"/>
+      <c r="AG19" s="310"/>
+      <c r="AH19" s="310"/>
+      <c r="AI19" s="310"/>
+      <c r="AJ19" s="310"/>
+    </row>
+    <row r="20" spans="1:71">
+      <c r="AB20" s="311"/>
+      <c r="AC20" s="311"/>
+      <c r="AD20" s="311"/>
+      <c r="AE20" s="311"/>
+      <c r="AF20" s="311"/>
+      <c r="AG20" s="311"/>
+      <c r="AH20" s="311"/>
+      <c r="AI20" s="311"/>
+      <c r="AJ20" s="311"/>
+    </row>
+    <row r="21" spans="1:71">
+      <c r="AB21" s="152"/>
+      <c r="AC21" s="152"/>
+      <c r="AD21" s="152"/>
+      <c r="AE21" s="152"/>
+      <c r="AF21" s="153"/>
+      <c r="AG21" s="152"/>
+      <c r="AH21" s="152"/>
+      <c r="AI21" s="153"/>
+      <c r="AJ21" s="153"/>
     </row>
   </sheetData>
-  <mergeCells count="83">
-    <mergeCell ref="AB17:AJ17"/>
-    <mergeCell ref="AB18:AJ18"/>
-    <mergeCell ref="AK13:BS13"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="J13:P13"/>
-    <mergeCell ref="Q13:AA13"/>
-    <mergeCell ref="AB13:AJ13"/>
-    <mergeCell ref="AK14:BS14"/>
+  <mergeCells count="95">
+    <mergeCell ref="AB19:AJ19"/>
+    <mergeCell ref="AB20:AJ20"/>
     <mergeCell ref="AK15:BS15"/>
-    <mergeCell ref="Q15:AA15"/>
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="J15:P15"/>
-    <mergeCell ref="Q14:AA14"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="AK5:BS5"/>
-    <mergeCell ref="Q5:AA5"/>
-    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="Q15:AA15"/>
+    <mergeCell ref="AB15:AJ15"/>
+    <mergeCell ref="AK16:BS16"/>
+    <mergeCell ref="AK17:BS17"/>
+    <mergeCell ref="Q17:AA17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="C17:I17"/>
+    <mergeCell ref="J17:P17"/>
+    <mergeCell ref="Q16:AA16"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="AK7:BS7"/>
+    <mergeCell ref="Q7:AA7"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="Q2:BS2"/>
@@ -28212,94 +28783,106 @@
     <mergeCell ref="J4:P4"/>
     <mergeCell ref="Q3:AA4"/>
     <mergeCell ref="AK3:BS4"/>
-    <mergeCell ref="C5:I5"/>
-    <mergeCell ref="J5:P5"/>
-    <mergeCell ref="AB3:AJ4"/>
-    <mergeCell ref="AB5:AJ5"/>
-    <mergeCell ref="AK6:BS6"/>
-    <mergeCell ref="AK7:BS7"/>
-    <mergeCell ref="Q6:AA6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:I6"/>
-    <mergeCell ref="J6:P6"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="C7:I7"/>
     <mergeCell ref="J7:P7"/>
-    <mergeCell ref="Q7:AA7"/>
-    <mergeCell ref="AB6:AJ6"/>
+    <mergeCell ref="AB3:AJ4"/>
     <mergeCell ref="AB7:AJ7"/>
     <mergeCell ref="AK8:BS8"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:I10"/>
-    <mergeCell ref="J10:P10"/>
     <mergeCell ref="AK9:BS9"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:I9"/>
-    <mergeCell ref="J9:P9"/>
-    <mergeCell ref="AK10:BS10"/>
     <mergeCell ref="Q8:AA8"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="C8:I8"/>
     <mergeCell ref="J8:P8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:I9"/>
+    <mergeCell ref="J9:P9"/>
+    <mergeCell ref="Q9:AA9"/>
     <mergeCell ref="AB8:AJ8"/>
     <mergeCell ref="AB9:AJ9"/>
-    <mergeCell ref="AB10:AJ10"/>
-    <mergeCell ref="Q12:AA12"/>
-    <mergeCell ref="Q9:AA9"/>
-    <mergeCell ref="Q11:AA11"/>
-    <mergeCell ref="AK11:BS11"/>
+    <mergeCell ref="AK10:BS10"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="C12:I12"/>
     <mergeCell ref="J12:P12"/>
+    <mergeCell ref="AK11:BS11"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="C11:I11"/>
     <mergeCell ref="J11:P11"/>
     <mergeCell ref="AK12:BS12"/>
+    <mergeCell ref="Q10:AA10"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:I10"/>
+    <mergeCell ref="J10:P10"/>
+    <mergeCell ref="AB10:AJ10"/>
     <mergeCell ref="AB11:AJ11"/>
     <mergeCell ref="AB12:AJ12"/>
-    <mergeCell ref="Q10:AA10"/>
+    <mergeCell ref="Q14:AA14"/>
+    <mergeCell ref="Q11:AA11"/>
+    <mergeCell ref="Q13:AA13"/>
+    <mergeCell ref="AK13:BS13"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="C14:I14"/>
     <mergeCell ref="J14:P14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="J13:P13"/>
+    <mergeCell ref="AK14:BS14"/>
+    <mergeCell ref="AB13:AJ13"/>
     <mergeCell ref="AB14:AJ14"/>
-    <mergeCell ref="AB15:AJ15"/>
-    <mergeCell ref="AK16:BS16"/>
-    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="Q12:AA12"/>
     <mergeCell ref="C16:I16"/>
-    <mergeCell ref="K16:P16"/>
-    <mergeCell ref="Q16:AA16"/>
+    <mergeCell ref="J16:P16"/>
     <mergeCell ref="AB16:AJ16"/>
+    <mergeCell ref="AB17:AJ17"/>
+    <mergeCell ref="AK18:BS18"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:I18"/>
+    <mergeCell ref="K18:P18"/>
+    <mergeCell ref="Q18:AA18"/>
+    <mergeCell ref="AB18:AJ18"/>
+    <mergeCell ref="AK5:BS5"/>
+    <mergeCell ref="AB6:AJ6"/>
+    <mergeCell ref="AK6:BS6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:I5"/>
+    <mergeCell ref="J5:P5"/>
+    <mergeCell ref="Q5:AA5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:I6"/>
+    <mergeCell ref="J6:P6"/>
+    <mergeCell ref="Q6:AA6"/>
+    <mergeCell ref="AB5:AJ5"/>
   </mergeCells>
   <phoneticPr fontId="56"/>
-  <conditionalFormatting sqref="Q5:Q9">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="Q5:Q11">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>FIND("○",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:Q16">
-    <cfRule type="expression" dxfId="2" priority="8" stopIfTrue="1">
+  <conditionalFormatting sqref="Q13:Q18">
+    <cfRule type="expression" dxfId="2" priority="9" stopIfTrue="1">
       <formula>FIND("○",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB5:AB18">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="AB5:AB20">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>FIND("○",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK5:AK16">
-    <cfRule type="expression" dxfId="0" priority="7" stopIfTrue="1">
+  <conditionalFormatting sqref="AK5:AK18">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>FIND("○",#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="VZW982988:WAK983025 HC5:HQ16 QY5:RM16 AAU5:ABI16 AKQ5:ALE16 AUM5:AVA16 BEI5:BEW16 BOE5:BOS16 BYA5:BYO16 CHW5:CIK16 CRS5:CSG16 DBO5:DCC16 DLK5:DLY16 DVG5:DVU16 EFC5:EFQ16 EOY5:EPM16 EYU5:EZI16 FIQ5:FJE16 FSM5:FTA16 GCI5:GCW16 GME5:GMS16 GWA5:GWO16 HFW5:HGK16 HPS5:HQG16 HZO5:IAC16 IJK5:IJY16 ITG5:ITU16 JDC5:JDQ16 JMY5:JNM16 JWU5:JXI16 KGQ5:KHE16 KQM5:KRA16 LAI5:LAW16 LKE5:LKS16 LUA5:LUO16 MDW5:MEK16 MNS5:MOG16 MXO5:MYC16 NHK5:NHY16 NRG5:NRU16 OBC5:OBQ16 OKY5:OLM16 OUU5:OVI16 PEQ5:PFE16 POM5:PPA16 PYI5:PYW16 QIE5:QIS16 QSA5:QSO16 RBW5:RCK16 RLS5:RMG16 RVO5:RWC16 SFK5:SFY16 SPG5:SPU16 SZC5:SZQ16 TIY5:TJM16 TSU5:TTI16 UCQ5:UDE16 UMM5:UNA16 UWI5:UWW16 VGE5:VGS16 VQA5:VQO16 VZW5:WAK16 WTO5:WUC16 WJS982988:WKG983025 HC65484:HQ65521 QY65484:RM65521 AAU65484:ABI65521 AKQ65484:ALE65521 AUM65484:AVA65521 BEI65484:BEW65521 BOE65484:BOS65521 BYA65484:BYO65521 CHW65484:CIK65521 CRS65484:CSG65521 DBO65484:DCC65521 DLK65484:DLY65521 DVG65484:DVU65521 EFC65484:EFQ65521 EOY65484:EPM65521 EYU65484:EZI65521 FIQ65484:FJE65521 FSM65484:FTA65521 GCI65484:GCW65521 GME65484:GMS65521 GWA65484:GWO65521 HFW65484:HGK65521 HPS65484:HQG65521 HZO65484:IAC65521 IJK65484:IJY65521 ITG65484:ITU65521 JDC65484:JDQ65521 JMY65484:JNM65521 JWU65484:JXI65521 KGQ65484:KHE65521 KQM65484:KRA65521 LAI65484:LAW65521 LKE65484:LKS65521 LUA65484:LUO65521 MDW65484:MEK65521 MNS65484:MOG65521 MXO65484:MYC65521 NHK65484:NHY65521 NRG65484:NRU65521 OBC65484:OBQ65521 OKY65484:OLM65521 OUU65484:OVI65521 PEQ65484:PFE65521 POM65484:PPA65521 PYI65484:PYW65521 QIE65484:QIS65521 QSA65484:QSO65521 RBW65484:RCK65521 RLS65484:RMG65521 RVO65484:RWC65521 SFK65484:SFY65521 SPG65484:SPU65521 SZC65484:SZQ65521 TIY65484:TJM65521 TSU65484:TTI65521 UCQ65484:UDE65521 UMM65484:UNA65521 UWI65484:UWW65521 VGE65484:VGS65521 VQA65484:VQO65521 VZW65484:WAK65521 WJS65484:WKG65521 WTO65484:WUC65521 HC131020:HQ131057 QY131020:RM131057 AAU131020:ABI131057 AKQ131020:ALE131057 AUM131020:AVA131057 BEI131020:BEW131057 BOE131020:BOS131057 BYA131020:BYO131057 CHW131020:CIK131057 CRS131020:CSG131057 DBO131020:DCC131057 DLK131020:DLY131057 DVG131020:DVU131057 EFC131020:EFQ131057 EOY131020:EPM131057 EYU131020:EZI131057 FIQ131020:FJE131057 FSM131020:FTA131057 GCI131020:GCW131057 GME131020:GMS131057 GWA131020:GWO131057 HFW131020:HGK131057 HPS131020:HQG131057 HZO131020:IAC131057 IJK131020:IJY131057 ITG131020:ITU131057 JDC131020:JDQ131057 JMY131020:JNM131057 JWU131020:JXI131057 KGQ131020:KHE131057 KQM131020:KRA131057 LAI131020:LAW131057 LKE131020:LKS131057 LUA131020:LUO131057 MDW131020:MEK131057 MNS131020:MOG131057 MXO131020:MYC131057 NHK131020:NHY131057 NRG131020:NRU131057 OBC131020:OBQ131057 OKY131020:OLM131057 OUU131020:OVI131057 PEQ131020:PFE131057 POM131020:PPA131057 PYI131020:PYW131057 QIE131020:QIS131057 QSA131020:QSO131057 RBW131020:RCK131057 RLS131020:RMG131057 RVO131020:RWC131057 SFK131020:SFY131057 SPG131020:SPU131057 SZC131020:SZQ131057 TIY131020:TJM131057 TSU131020:TTI131057 UCQ131020:UDE131057 UMM131020:UNA131057 UWI131020:UWW131057 VGE131020:VGS131057 VQA131020:VQO131057 VZW131020:WAK131057 WJS131020:WKG131057 WTO131020:WUC131057 HC196556:HQ196593 QY196556:RM196593 AAU196556:ABI196593 AKQ196556:ALE196593 AUM196556:AVA196593 BEI196556:BEW196593 BOE196556:BOS196593 BYA196556:BYO196593 CHW196556:CIK196593 CRS196556:CSG196593 DBO196556:DCC196593 DLK196556:DLY196593 DVG196556:DVU196593 EFC196556:EFQ196593 EOY196556:EPM196593 EYU196556:EZI196593 FIQ196556:FJE196593 FSM196556:FTA196593 GCI196556:GCW196593 GME196556:GMS196593 GWA196556:GWO196593 HFW196556:HGK196593 HPS196556:HQG196593 HZO196556:IAC196593 IJK196556:IJY196593 ITG196556:ITU196593 JDC196556:JDQ196593 JMY196556:JNM196593 JWU196556:JXI196593 KGQ196556:KHE196593 KQM196556:KRA196593 LAI196556:LAW196593 LKE196556:LKS196593 LUA196556:LUO196593 MDW196556:MEK196593 MNS196556:MOG196593 MXO196556:MYC196593 NHK196556:NHY196593 NRG196556:NRU196593 OBC196556:OBQ196593 OKY196556:OLM196593 OUU196556:OVI196593 PEQ196556:PFE196593 POM196556:PPA196593 PYI196556:PYW196593 QIE196556:QIS196593 QSA196556:QSO196593 RBW196556:RCK196593 RLS196556:RMG196593 RVO196556:RWC196593 SFK196556:SFY196593 SPG196556:SPU196593 SZC196556:SZQ196593 TIY196556:TJM196593 TSU196556:TTI196593 UCQ196556:UDE196593 UMM196556:UNA196593 UWI196556:UWW196593 VGE196556:VGS196593 VQA196556:VQO196593 VZW196556:WAK196593 WJS196556:WKG196593 WTO196556:WUC196593 HC262092:HQ262129 QY262092:RM262129 AAU262092:ABI262129 AKQ262092:ALE262129 AUM262092:AVA262129 BEI262092:BEW262129 BOE262092:BOS262129 BYA262092:BYO262129 CHW262092:CIK262129 CRS262092:CSG262129 DBO262092:DCC262129 DLK262092:DLY262129 DVG262092:DVU262129 EFC262092:EFQ262129 EOY262092:EPM262129 EYU262092:EZI262129 FIQ262092:FJE262129 FSM262092:FTA262129 GCI262092:GCW262129 GME262092:GMS262129 GWA262092:GWO262129 HFW262092:HGK262129 HPS262092:HQG262129 HZO262092:IAC262129 IJK262092:IJY262129 ITG262092:ITU262129 JDC262092:JDQ262129 JMY262092:JNM262129 JWU262092:JXI262129 KGQ262092:KHE262129 KQM262092:KRA262129 LAI262092:LAW262129 LKE262092:LKS262129 LUA262092:LUO262129 MDW262092:MEK262129 MNS262092:MOG262129 MXO262092:MYC262129 NHK262092:NHY262129 NRG262092:NRU262129 OBC262092:OBQ262129 OKY262092:OLM262129 OUU262092:OVI262129 PEQ262092:PFE262129 POM262092:PPA262129 PYI262092:PYW262129 QIE262092:QIS262129 QSA262092:QSO262129 RBW262092:RCK262129 RLS262092:RMG262129 RVO262092:RWC262129 SFK262092:SFY262129 SPG262092:SPU262129 SZC262092:SZQ262129 TIY262092:TJM262129 TSU262092:TTI262129 UCQ262092:UDE262129 UMM262092:UNA262129 UWI262092:UWW262129 VGE262092:VGS262129 VQA262092:VQO262129 VZW262092:WAK262129 WJS262092:WKG262129 WTO262092:WUC262129 HC327628:HQ327665 QY327628:RM327665 AAU327628:ABI327665 AKQ327628:ALE327665 AUM327628:AVA327665 BEI327628:BEW327665 BOE327628:BOS327665 BYA327628:BYO327665 CHW327628:CIK327665 CRS327628:CSG327665 DBO327628:DCC327665 DLK327628:DLY327665 DVG327628:DVU327665 EFC327628:EFQ327665 EOY327628:EPM327665 EYU327628:EZI327665 FIQ327628:FJE327665 FSM327628:FTA327665 GCI327628:GCW327665 GME327628:GMS327665 GWA327628:GWO327665 HFW327628:HGK327665 HPS327628:HQG327665 HZO327628:IAC327665 IJK327628:IJY327665 ITG327628:ITU327665 JDC327628:JDQ327665 JMY327628:JNM327665 JWU327628:JXI327665 KGQ327628:KHE327665 KQM327628:KRA327665 LAI327628:LAW327665 LKE327628:LKS327665 LUA327628:LUO327665 MDW327628:MEK327665 MNS327628:MOG327665 MXO327628:MYC327665 NHK327628:NHY327665 NRG327628:NRU327665 OBC327628:OBQ327665 OKY327628:OLM327665 OUU327628:OVI327665 PEQ327628:PFE327665 POM327628:PPA327665 PYI327628:PYW327665 QIE327628:QIS327665 QSA327628:QSO327665 RBW327628:RCK327665 RLS327628:RMG327665 RVO327628:RWC327665 SFK327628:SFY327665 SPG327628:SPU327665 SZC327628:SZQ327665 TIY327628:TJM327665 TSU327628:TTI327665 UCQ327628:UDE327665 UMM327628:UNA327665 UWI327628:UWW327665 VGE327628:VGS327665 VQA327628:VQO327665 VZW327628:WAK327665 WJS327628:WKG327665 WTO327628:WUC327665 HC393164:HQ393201 QY393164:RM393201 AAU393164:ABI393201 AKQ393164:ALE393201 AUM393164:AVA393201 BEI393164:BEW393201 BOE393164:BOS393201 BYA393164:BYO393201 CHW393164:CIK393201 CRS393164:CSG393201 DBO393164:DCC393201 DLK393164:DLY393201 DVG393164:DVU393201 EFC393164:EFQ393201 EOY393164:EPM393201 EYU393164:EZI393201 FIQ393164:FJE393201 FSM393164:FTA393201 GCI393164:GCW393201 GME393164:GMS393201 GWA393164:GWO393201 HFW393164:HGK393201 HPS393164:HQG393201 HZO393164:IAC393201 IJK393164:IJY393201 ITG393164:ITU393201 JDC393164:JDQ393201 JMY393164:JNM393201 JWU393164:JXI393201 KGQ393164:KHE393201 KQM393164:KRA393201 LAI393164:LAW393201 LKE393164:LKS393201 LUA393164:LUO393201 MDW393164:MEK393201 MNS393164:MOG393201 MXO393164:MYC393201 NHK393164:NHY393201 NRG393164:NRU393201 OBC393164:OBQ393201 OKY393164:OLM393201 OUU393164:OVI393201 PEQ393164:PFE393201 POM393164:PPA393201 PYI393164:PYW393201 QIE393164:QIS393201 QSA393164:QSO393201 RBW393164:RCK393201 RLS393164:RMG393201 RVO393164:RWC393201 SFK393164:SFY393201 SPG393164:SPU393201 SZC393164:SZQ393201 TIY393164:TJM393201 TSU393164:TTI393201 UCQ393164:UDE393201 UMM393164:UNA393201 UWI393164:UWW393201 VGE393164:VGS393201 VQA393164:VQO393201 VZW393164:WAK393201 WJS393164:WKG393201 WTO393164:WUC393201 HC458700:HQ458737 QY458700:RM458737 AAU458700:ABI458737 AKQ458700:ALE458737 AUM458700:AVA458737 BEI458700:BEW458737 BOE458700:BOS458737 BYA458700:BYO458737 CHW458700:CIK458737 CRS458700:CSG458737 DBO458700:DCC458737 DLK458700:DLY458737 DVG458700:DVU458737 EFC458700:EFQ458737 EOY458700:EPM458737 EYU458700:EZI458737 FIQ458700:FJE458737 FSM458700:FTA458737 GCI458700:GCW458737 GME458700:GMS458737 GWA458700:GWO458737 HFW458700:HGK458737 HPS458700:HQG458737 HZO458700:IAC458737 IJK458700:IJY458737 ITG458700:ITU458737 JDC458700:JDQ458737 JMY458700:JNM458737 JWU458700:JXI458737 KGQ458700:KHE458737 KQM458700:KRA458737 LAI458700:LAW458737 LKE458700:LKS458737 LUA458700:LUO458737 MDW458700:MEK458737 MNS458700:MOG458737 MXO458700:MYC458737 NHK458700:NHY458737 NRG458700:NRU458737 OBC458700:OBQ458737 OKY458700:OLM458737 OUU458700:OVI458737 PEQ458700:PFE458737 POM458700:PPA458737 PYI458700:PYW458737 QIE458700:QIS458737 QSA458700:QSO458737 RBW458700:RCK458737 RLS458700:RMG458737 RVO458700:RWC458737 SFK458700:SFY458737 SPG458700:SPU458737 SZC458700:SZQ458737 TIY458700:TJM458737 TSU458700:TTI458737 UCQ458700:UDE458737 UMM458700:UNA458737 UWI458700:UWW458737 VGE458700:VGS458737 VQA458700:VQO458737 VZW458700:WAK458737 WJS458700:WKG458737 WTO458700:WUC458737 HC524236:HQ524273 QY524236:RM524273 AAU524236:ABI524273 AKQ524236:ALE524273 AUM524236:AVA524273 BEI524236:BEW524273 BOE524236:BOS524273 BYA524236:BYO524273 CHW524236:CIK524273 CRS524236:CSG524273 DBO524236:DCC524273 DLK524236:DLY524273 DVG524236:DVU524273 EFC524236:EFQ524273 EOY524236:EPM524273 EYU524236:EZI524273 FIQ524236:FJE524273 FSM524236:FTA524273 GCI524236:GCW524273 GME524236:GMS524273 GWA524236:GWO524273 HFW524236:HGK524273 HPS524236:HQG524273 HZO524236:IAC524273 IJK524236:IJY524273 ITG524236:ITU524273 JDC524236:JDQ524273 JMY524236:JNM524273 JWU524236:JXI524273 KGQ524236:KHE524273 KQM524236:KRA524273 LAI524236:LAW524273 LKE524236:LKS524273 LUA524236:LUO524273 MDW524236:MEK524273 MNS524236:MOG524273 MXO524236:MYC524273 NHK524236:NHY524273 NRG524236:NRU524273 OBC524236:OBQ524273 OKY524236:OLM524273 OUU524236:OVI524273 PEQ524236:PFE524273 POM524236:PPA524273 PYI524236:PYW524273 QIE524236:QIS524273 QSA524236:QSO524273 RBW524236:RCK524273 RLS524236:RMG524273 RVO524236:RWC524273 SFK524236:SFY524273 SPG524236:SPU524273 SZC524236:SZQ524273 TIY524236:TJM524273 TSU524236:TTI524273 UCQ524236:UDE524273 UMM524236:UNA524273 UWI524236:UWW524273 VGE524236:VGS524273 VQA524236:VQO524273 VZW524236:WAK524273 WJS524236:WKG524273 WTO524236:WUC524273 HC589772:HQ589809 QY589772:RM589809 AAU589772:ABI589809 AKQ589772:ALE589809 AUM589772:AVA589809 BEI589772:BEW589809 BOE589772:BOS589809 BYA589772:BYO589809 CHW589772:CIK589809 CRS589772:CSG589809 DBO589772:DCC589809 DLK589772:DLY589809 DVG589772:DVU589809 EFC589772:EFQ589809 EOY589772:EPM589809 EYU589772:EZI589809 FIQ589772:FJE589809 FSM589772:FTA589809 GCI589772:GCW589809 GME589772:GMS589809 GWA589772:GWO589809 HFW589772:HGK589809 HPS589772:HQG589809 HZO589772:IAC589809 IJK589772:IJY589809 ITG589772:ITU589809 JDC589772:JDQ589809 JMY589772:JNM589809 JWU589772:JXI589809 KGQ589772:KHE589809 KQM589772:KRA589809 LAI589772:LAW589809 LKE589772:LKS589809 LUA589772:LUO589809 MDW589772:MEK589809 MNS589772:MOG589809 MXO589772:MYC589809 NHK589772:NHY589809 NRG589772:NRU589809 OBC589772:OBQ589809 OKY589772:OLM589809 OUU589772:OVI589809 PEQ589772:PFE589809 POM589772:PPA589809 PYI589772:PYW589809 QIE589772:QIS589809 QSA589772:QSO589809 RBW589772:RCK589809 RLS589772:RMG589809 RVO589772:RWC589809 SFK589772:SFY589809 SPG589772:SPU589809 SZC589772:SZQ589809 TIY589772:TJM589809 TSU589772:TTI589809 UCQ589772:UDE589809 UMM589772:UNA589809 UWI589772:UWW589809 VGE589772:VGS589809 VQA589772:VQO589809 VZW589772:WAK589809 WJS589772:WKG589809 WTO589772:WUC589809 HC655308:HQ655345 QY655308:RM655345 AAU655308:ABI655345 AKQ655308:ALE655345 AUM655308:AVA655345 BEI655308:BEW655345 BOE655308:BOS655345 BYA655308:BYO655345 CHW655308:CIK655345 CRS655308:CSG655345 DBO655308:DCC655345 DLK655308:DLY655345 DVG655308:DVU655345 EFC655308:EFQ655345 EOY655308:EPM655345 EYU655308:EZI655345 FIQ655308:FJE655345 FSM655308:FTA655345 GCI655308:GCW655345 GME655308:GMS655345 GWA655308:GWO655345 HFW655308:HGK655345 HPS655308:HQG655345 HZO655308:IAC655345 IJK655308:IJY655345 ITG655308:ITU655345 JDC655308:JDQ655345 JMY655308:JNM655345 JWU655308:JXI655345 KGQ655308:KHE655345 KQM655308:KRA655345 LAI655308:LAW655345 LKE655308:LKS655345 LUA655308:LUO655345 MDW655308:MEK655345 MNS655308:MOG655345 MXO655308:MYC655345 NHK655308:NHY655345 NRG655308:NRU655345 OBC655308:OBQ655345 OKY655308:OLM655345 OUU655308:OVI655345 PEQ655308:PFE655345 POM655308:PPA655345 PYI655308:PYW655345 QIE655308:QIS655345 QSA655308:QSO655345 RBW655308:RCK655345 RLS655308:RMG655345 RVO655308:RWC655345 SFK655308:SFY655345 SPG655308:SPU655345 SZC655308:SZQ655345 TIY655308:TJM655345 TSU655308:TTI655345 UCQ655308:UDE655345 UMM655308:UNA655345 UWI655308:UWW655345 VGE655308:VGS655345 VQA655308:VQO655345 VZW655308:WAK655345 WJS655308:WKG655345 WTO655308:WUC655345 HC720844:HQ720881 QY720844:RM720881 AAU720844:ABI720881 AKQ720844:ALE720881 AUM720844:AVA720881 BEI720844:BEW720881 BOE720844:BOS720881 BYA720844:BYO720881 CHW720844:CIK720881 CRS720844:CSG720881 DBO720844:DCC720881 DLK720844:DLY720881 DVG720844:DVU720881 EFC720844:EFQ720881 EOY720844:EPM720881 EYU720844:EZI720881 FIQ720844:FJE720881 FSM720844:FTA720881 GCI720844:GCW720881 GME720844:GMS720881 GWA720844:GWO720881 HFW720844:HGK720881 HPS720844:HQG720881 HZO720844:IAC720881 IJK720844:IJY720881 ITG720844:ITU720881 JDC720844:JDQ720881 JMY720844:JNM720881 JWU720844:JXI720881 KGQ720844:KHE720881 KQM720844:KRA720881 LAI720844:LAW720881 LKE720844:LKS720881 LUA720844:LUO720881 MDW720844:MEK720881 MNS720844:MOG720881 MXO720844:MYC720881 NHK720844:NHY720881 NRG720844:NRU720881 OBC720844:OBQ720881 OKY720844:OLM720881 OUU720844:OVI720881 PEQ720844:PFE720881 POM720844:PPA720881 PYI720844:PYW720881 QIE720844:QIS720881 QSA720844:QSO720881 RBW720844:RCK720881 RLS720844:RMG720881 RVO720844:RWC720881 SFK720844:SFY720881 SPG720844:SPU720881 SZC720844:SZQ720881 TIY720844:TJM720881 TSU720844:TTI720881 UCQ720844:UDE720881 UMM720844:UNA720881 UWI720844:UWW720881 VGE720844:VGS720881 VQA720844:VQO720881 VZW720844:WAK720881 WJS720844:WKG720881 WTO720844:WUC720881 HC786380:HQ786417 QY786380:RM786417 AAU786380:ABI786417 AKQ786380:ALE786417 AUM786380:AVA786417 BEI786380:BEW786417 BOE786380:BOS786417 BYA786380:BYO786417 CHW786380:CIK786417 CRS786380:CSG786417 DBO786380:DCC786417 DLK786380:DLY786417 DVG786380:DVU786417 EFC786380:EFQ786417 EOY786380:EPM786417 EYU786380:EZI786417 FIQ786380:FJE786417 FSM786380:FTA786417 GCI786380:GCW786417 GME786380:GMS786417 GWA786380:GWO786417 HFW786380:HGK786417 HPS786380:HQG786417 HZO786380:IAC786417 IJK786380:IJY786417 ITG786380:ITU786417 JDC786380:JDQ786417 JMY786380:JNM786417 JWU786380:JXI786417 KGQ786380:KHE786417 KQM786380:KRA786417 LAI786380:LAW786417 LKE786380:LKS786417 LUA786380:LUO786417 MDW786380:MEK786417 MNS786380:MOG786417 MXO786380:MYC786417 NHK786380:NHY786417 NRG786380:NRU786417 OBC786380:OBQ786417 OKY786380:OLM786417 OUU786380:OVI786417 PEQ786380:PFE786417 POM786380:PPA786417 PYI786380:PYW786417 QIE786380:QIS786417 QSA786380:QSO786417 RBW786380:RCK786417 RLS786380:RMG786417 RVO786380:RWC786417 SFK786380:SFY786417 SPG786380:SPU786417 SZC786380:SZQ786417 TIY786380:TJM786417 TSU786380:TTI786417 UCQ786380:UDE786417 UMM786380:UNA786417 UWI786380:UWW786417 VGE786380:VGS786417 VQA786380:VQO786417 VZW786380:WAK786417 WJS786380:WKG786417 WTO786380:WUC786417 HC851916:HQ851953 QY851916:RM851953 AAU851916:ABI851953 AKQ851916:ALE851953 AUM851916:AVA851953 BEI851916:BEW851953 BOE851916:BOS851953 BYA851916:BYO851953 CHW851916:CIK851953 CRS851916:CSG851953 DBO851916:DCC851953 DLK851916:DLY851953 DVG851916:DVU851953 EFC851916:EFQ851953 EOY851916:EPM851953 EYU851916:EZI851953 FIQ851916:FJE851953 FSM851916:FTA851953 GCI851916:GCW851953 GME851916:GMS851953 GWA851916:GWO851953 HFW851916:HGK851953 HPS851916:HQG851953 HZO851916:IAC851953 IJK851916:IJY851953 ITG851916:ITU851953 JDC851916:JDQ851953 JMY851916:JNM851953 JWU851916:JXI851953 KGQ851916:KHE851953 KQM851916:KRA851953 LAI851916:LAW851953 LKE851916:LKS851953 LUA851916:LUO851953 MDW851916:MEK851953 MNS851916:MOG851953 MXO851916:MYC851953 NHK851916:NHY851953 NRG851916:NRU851953 OBC851916:OBQ851953 OKY851916:OLM851953 OUU851916:OVI851953 PEQ851916:PFE851953 POM851916:PPA851953 PYI851916:PYW851953 QIE851916:QIS851953 QSA851916:QSO851953 RBW851916:RCK851953 RLS851916:RMG851953 RVO851916:RWC851953 SFK851916:SFY851953 SPG851916:SPU851953 SZC851916:SZQ851953 TIY851916:TJM851953 TSU851916:TTI851953 UCQ851916:UDE851953 UMM851916:UNA851953 UWI851916:UWW851953 VGE851916:VGS851953 VQA851916:VQO851953 VZW851916:WAK851953 WJS851916:WKG851953 WTO851916:WUC851953 HC917452:HQ917489 QY917452:RM917489 AAU917452:ABI917489 AKQ917452:ALE917489 AUM917452:AVA917489 BEI917452:BEW917489 BOE917452:BOS917489 BYA917452:BYO917489 CHW917452:CIK917489 CRS917452:CSG917489 DBO917452:DCC917489 DLK917452:DLY917489 DVG917452:DVU917489 EFC917452:EFQ917489 EOY917452:EPM917489 EYU917452:EZI917489 FIQ917452:FJE917489 FSM917452:FTA917489 GCI917452:GCW917489 GME917452:GMS917489 GWA917452:GWO917489 HFW917452:HGK917489 HPS917452:HQG917489 HZO917452:IAC917489 IJK917452:IJY917489 ITG917452:ITU917489 JDC917452:JDQ917489 JMY917452:JNM917489 JWU917452:JXI917489 KGQ917452:KHE917489 KQM917452:KRA917489 LAI917452:LAW917489 LKE917452:LKS917489 LUA917452:LUO917489 MDW917452:MEK917489 MNS917452:MOG917489 MXO917452:MYC917489 NHK917452:NHY917489 NRG917452:NRU917489 OBC917452:OBQ917489 OKY917452:OLM917489 OUU917452:OVI917489 PEQ917452:PFE917489 POM917452:PPA917489 PYI917452:PYW917489 QIE917452:QIS917489 QSA917452:QSO917489 RBW917452:RCK917489 RLS917452:RMG917489 RVO917452:RWC917489 SFK917452:SFY917489 SPG917452:SPU917489 SZC917452:SZQ917489 TIY917452:TJM917489 TSU917452:TTI917489 UCQ917452:UDE917489 UMM917452:UNA917489 UWI917452:UWW917489 VGE917452:VGS917489 VQA917452:VQO917489 VZW917452:WAK917489 WJS917452:WKG917489 WTO917452:WUC917489 HC982988:HQ983025 QY982988:RM983025 AAU982988:ABI983025 AKQ982988:ALE983025 AUM982988:AVA983025 BEI982988:BEW983025 BOE982988:BOS983025 BYA982988:BYO983025 CHW982988:CIK983025 CRS982988:CSG983025 DBO982988:DCC983025 DLK982988:DLY983025 DVG982988:DVU983025 EFC982988:EFQ983025 EOY982988:EPM983025 EYU982988:EZI983025 FIQ982988:FJE983025 FSM982988:FTA983025 GCI982988:GCW983025 GME982988:GMS983025 GWA982988:GWO983025 HFW982988:HGK983025 HPS982988:HQG983025 HZO982988:IAC983025 IJK982988:IJY983025 ITG982988:ITU983025 JDC982988:JDQ983025 JMY982988:JNM983025 JWU982988:JXI983025 KGQ982988:KHE983025 KQM982988:KRA983025 LAI982988:LAW983025 LKE982988:LKS983025 LUA982988:LUO983025 MDW982988:MEK983025 MNS982988:MOG983025 MXO982988:MYC983025 NHK982988:NHY983025 NRG982988:NRU983025 OBC982988:OBQ983025 OKY982988:OLM983025 OUU982988:OVI983025 PEQ982988:PFE983025 POM982988:PPA983025 PYI982988:PYW983025 QIE982988:QIS983025 QSA982988:QSO983025 RBW982988:RCK983025 RLS982988:RMG983025 RVO982988:RWC983025 SFK982988:SFY983025 SPG982988:SPU983025 SZC982988:SZQ983025 TIY982988:TJM983025 TSU982988:TTI983025 UCQ982988:UDE983025 UMM982988:UNA983025 UWI982988:UWW983025 VGE982988:VGS983025 VQA982988:VQO983025 WJS5:WKG16 WTO982988:WUC983025" xr:uid="{C4ED132A-D8E6-4B24-B44A-430CE62F3BAA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="VZW982990:WAK983027 HC5:HQ18 QY5:RM18 AAU5:ABI18 AKQ5:ALE18 AUM5:AVA18 BEI5:BEW18 BOE5:BOS18 BYA5:BYO18 CHW5:CIK18 CRS5:CSG18 DBO5:DCC18 DLK5:DLY18 DVG5:DVU18 EFC5:EFQ18 EOY5:EPM18 EYU5:EZI18 FIQ5:FJE18 FSM5:FTA18 GCI5:GCW18 GME5:GMS18 GWA5:GWO18 HFW5:HGK18 HPS5:HQG18 HZO5:IAC18 IJK5:IJY18 ITG5:ITU18 JDC5:JDQ18 JMY5:JNM18 JWU5:JXI18 KGQ5:KHE18 KQM5:KRA18 LAI5:LAW18 LKE5:LKS18 LUA5:LUO18 MDW5:MEK18 MNS5:MOG18 MXO5:MYC18 NHK5:NHY18 NRG5:NRU18 OBC5:OBQ18 OKY5:OLM18 OUU5:OVI18 PEQ5:PFE18 POM5:PPA18 PYI5:PYW18 QIE5:QIS18 QSA5:QSO18 RBW5:RCK18 RLS5:RMG18 RVO5:RWC18 SFK5:SFY18 SPG5:SPU18 SZC5:SZQ18 TIY5:TJM18 TSU5:TTI18 UCQ5:UDE18 UMM5:UNA18 UWI5:UWW18 VGE5:VGS18 VQA5:VQO18 VZW5:WAK18 WTO5:WUC18 WJS982990:WKG983027 HC65486:HQ65523 QY65486:RM65523 AAU65486:ABI65523 AKQ65486:ALE65523 AUM65486:AVA65523 BEI65486:BEW65523 BOE65486:BOS65523 BYA65486:BYO65523 CHW65486:CIK65523 CRS65486:CSG65523 DBO65486:DCC65523 DLK65486:DLY65523 DVG65486:DVU65523 EFC65486:EFQ65523 EOY65486:EPM65523 EYU65486:EZI65523 FIQ65486:FJE65523 FSM65486:FTA65523 GCI65486:GCW65523 GME65486:GMS65523 GWA65486:GWO65523 HFW65486:HGK65523 HPS65486:HQG65523 HZO65486:IAC65523 IJK65486:IJY65523 ITG65486:ITU65523 JDC65486:JDQ65523 JMY65486:JNM65523 JWU65486:JXI65523 KGQ65486:KHE65523 KQM65486:KRA65523 LAI65486:LAW65523 LKE65486:LKS65523 LUA65486:LUO65523 MDW65486:MEK65523 MNS65486:MOG65523 MXO65486:MYC65523 NHK65486:NHY65523 NRG65486:NRU65523 OBC65486:OBQ65523 OKY65486:OLM65523 OUU65486:OVI65523 PEQ65486:PFE65523 POM65486:PPA65523 PYI65486:PYW65523 QIE65486:QIS65523 QSA65486:QSO65523 RBW65486:RCK65523 RLS65486:RMG65523 RVO65486:RWC65523 SFK65486:SFY65523 SPG65486:SPU65523 SZC65486:SZQ65523 TIY65486:TJM65523 TSU65486:TTI65523 UCQ65486:UDE65523 UMM65486:UNA65523 UWI65486:UWW65523 VGE65486:VGS65523 VQA65486:VQO65523 VZW65486:WAK65523 WJS65486:WKG65523 WTO65486:WUC65523 HC131022:HQ131059 QY131022:RM131059 AAU131022:ABI131059 AKQ131022:ALE131059 AUM131022:AVA131059 BEI131022:BEW131059 BOE131022:BOS131059 BYA131022:BYO131059 CHW131022:CIK131059 CRS131022:CSG131059 DBO131022:DCC131059 DLK131022:DLY131059 DVG131022:DVU131059 EFC131022:EFQ131059 EOY131022:EPM131059 EYU131022:EZI131059 FIQ131022:FJE131059 FSM131022:FTA131059 GCI131022:GCW131059 GME131022:GMS131059 GWA131022:GWO131059 HFW131022:HGK131059 HPS131022:HQG131059 HZO131022:IAC131059 IJK131022:IJY131059 ITG131022:ITU131059 JDC131022:JDQ131059 JMY131022:JNM131059 JWU131022:JXI131059 KGQ131022:KHE131059 KQM131022:KRA131059 LAI131022:LAW131059 LKE131022:LKS131059 LUA131022:LUO131059 MDW131022:MEK131059 MNS131022:MOG131059 MXO131022:MYC131059 NHK131022:NHY131059 NRG131022:NRU131059 OBC131022:OBQ131059 OKY131022:OLM131059 OUU131022:OVI131059 PEQ131022:PFE131059 POM131022:PPA131059 PYI131022:PYW131059 QIE131022:QIS131059 QSA131022:QSO131059 RBW131022:RCK131059 RLS131022:RMG131059 RVO131022:RWC131059 SFK131022:SFY131059 SPG131022:SPU131059 SZC131022:SZQ131059 TIY131022:TJM131059 TSU131022:TTI131059 UCQ131022:UDE131059 UMM131022:UNA131059 UWI131022:UWW131059 VGE131022:VGS131059 VQA131022:VQO131059 VZW131022:WAK131059 WJS131022:WKG131059 WTO131022:WUC131059 HC196558:HQ196595 QY196558:RM196595 AAU196558:ABI196595 AKQ196558:ALE196595 AUM196558:AVA196595 BEI196558:BEW196595 BOE196558:BOS196595 BYA196558:BYO196595 CHW196558:CIK196595 CRS196558:CSG196595 DBO196558:DCC196595 DLK196558:DLY196595 DVG196558:DVU196595 EFC196558:EFQ196595 EOY196558:EPM196595 EYU196558:EZI196595 FIQ196558:FJE196595 FSM196558:FTA196595 GCI196558:GCW196595 GME196558:GMS196595 GWA196558:GWO196595 HFW196558:HGK196595 HPS196558:HQG196595 HZO196558:IAC196595 IJK196558:IJY196595 ITG196558:ITU196595 JDC196558:JDQ196595 JMY196558:JNM196595 JWU196558:JXI196595 KGQ196558:KHE196595 KQM196558:KRA196595 LAI196558:LAW196595 LKE196558:LKS196595 LUA196558:LUO196595 MDW196558:MEK196595 MNS196558:MOG196595 MXO196558:MYC196595 NHK196558:NHY196595 NRG196558:NRU196595 OBC196558:OBQ196595 OKY196558:OLM196595 OUU196558:OVI196595 PEQ196558:PFE196595 POM196558:PPA196595 PYI196558:PYW196595 QIE196558:QIS196595 QSA196558:QSO196595 RBW196558:RCK196595 RLS196558:RMG196595 RVO196558:RWC196595 SFK196558:SFY196595 SPG196558:SPU196595 SZC196558:SZQ196595 TIY196558:TJM196595 TSU196558:TTI196595 UCQ196558:UDE196595 UMM196558:UNA196595 UWI196558:UWW196595 VGE196558:VGS196595 VQA196558:VQO196595 VZW196558:WAK196595 WJS196558:WKG196595 WTO196558:WUC196595 HC262094:HQ262131 QY262094:RM262131 AAU262094:ABI262131 AKQ262094:ALE262131 AUM262094:AVA262131 BEI262094:BEW262131 BOE262094:BOS262131 BYA262094:BYO262131 CHW262094:CIK262131 CRS262094:CSG262131 DBO262094:DCC262131 DLK262094:DLY262131 DVG262094:DVU262131 EFC262094:EFQ262131 EOY262094:EPM262131 EYU262094:EZI262131 FIQ262094:FJE262131 FSM262094:FTA262131 GCI262094:GCW262131 GME262094:GMS262131 GWA262094:GWO262131 HFW262094:HGK262131 HPS262094:HQG262131 HZO262094:IAC262131 IJK262094:IJY262131 ITG262094:ITU262131 JDC262094:JDQ262131 JMY262094:JNM262131 JWU262094:JXI262131 KGQ262094:KHE262131 KQM262094:KRA262131 LAI262094:LAW262131 LKE262094:LKS262131 LUA262094:LUO262131 MDW262094:MEK262131 MNS262094:MOG262131 MXO262094:MYC262131 NHK262094:NHY262131 NRG262094:NRU262131 OBC262094:OBQ262131 OKY262094:OLM262131 OUU262094:OVI262131 PEQ262094:PFE262131 POM262094:PPA262131 PYI262094:PYW262131 QIE262094:QIS262131 QSA262094:QSO262131 RBW262094:RCK262131 RLS262094:RMG262131 RVO262094:RWC262131 SFK262094:SFY262131 SPG262094:SPU262131 SZC262094:SZQ262131 TIY262094:TJM262131 TSU262094:TTI262131 UCQ262094:UDE262131 UMM262094:UNA262131 UWI262094:UWW262131 VGE262094:VGS262131 VQA262094:VQO262131 VZW262094:WAK262131 WJS262094:WKG262131 WTO262094:WUC262131 HC327630:HQ327667 QY327630:RM327667 AAU327630:ABI327667 AKQ327630:ALE327667 AUM327630:AVA327667 BEI327630:BEW327667 BOE327630:BOS327667 BYA327630:BYO327667 CHW327630:CIK327667 CRS327630:CSG327667 DBO327630:DCC327667 DLK327630:DLY327667 DVG327630:DVU327667 EFC327630:EFQ327667 EOY327630:EPM327667 EYU327630:EZI327667 FIQ327630:FJE327667 FSM327630:FTA327667 GCI327630:GCW327667 GME327630:GMS327667 GWA327630:GWO327667 HFW327630:HGK327667 HPS327630:HQG327667 HZO327630:IAC327667 IJK327630:IJY327667 ITG327630:ITU327667 JDC327630:JDQ327667 JMY327630:JNM327667 JWU327630:JXI327667 KGQ327630:KHE327667 KQM327630:KRA327667 LAI327630:LAW327667 LKE327630:LKS327667 LUA327630:LUO327667 MDW327630:MEK327667 MNS327630:MOG327667 MXO327630:MYC327667 NHK327630:NHY327667 NRG327630:NRU327667 OBC327630:OBQ327667 OKY327630:OLM327667 OUU327630:OVI327667 PEQ327630:PFE327667 POM327630:PPA327667 PYI327630:PYW327667 QIE327630:QIS327667 QSA327630:QSO327667 RBW327630:RCK327667 RLS327630:RMG327667 RVO327630:RWC327667 SFK327630:SFY327667 SPG327630:SPU327667 SZC327630:SZQ327667 TIY327630:TJM327667 TSU327630:TTI327667 UCQ327630:UDE327667 UMM327630:UNA327667 UWI327630:UWW327667 VGE327630:VGS327667 VQA327630:VQO327667 VZW327630:WAK327667 WJS327630:WKG327667 WTO327630:WUC327667 HC393166:HQ393203 QY393166:RM393203 AAU393166:ABI393203 AKQ393166:ALE393203 AUM393166:AVA393203 BEI393166:BEW393203 BOE393166:BOS393203 BYA393166:BYO393203 CHW393166:CIK393203 CRS393166:CSG393203 DBO393166:DCC393203 DLK393166:DLY393203 DVG393166:DVU393203 EFC393166:EFQ393203 EOY393166:EPM393203 EYU393166:EZI393203 FIQ393166:FJE393203 FSM393166:FTA393203 GCI393166:GCW393203 GME393166:GMS393203 GWA393166:GWO393203 HFW393166:HGK393203 HPS393166:HQG393203 HZO393166:IAC393203 IJK393166:IJY393203 ITG393166:ITU393203 JDC393166:JDQ393203 JMY393166:JNM393203 JWU393166:JXI393203 KGQ393166:KHE393203 KQM393166:KRA393203 LAI393166:LAW393203 LKE393166:LKS393203 LUA393166:LUO393203 MDW393166:MEK393203 MNS393166:MOG393203 MXO393166:MYC393203 NHK393166:NHY393203 NRG393166:NRU393203 OBC393166:OBQ393203 OKY393166:OLM393203 OUU393166:OVI393203 PEQ393166:PFE393203 POM393166:PPA393203 PYI393166:PYW393203 QIE393166:QIS393203 QSA393166:QSO393203 RBW393166:RCK393203 RLS393166:RMG393203 RVO393166:RWC393203 SFK393166:SFY393203 SPG393166:SPU393203 SZC393166:SZQ393203 TIY393166:TJM393203 TSU393166:TTI393203 UCQ393166:UDE393203 UMM393166:UNA393203 UWI393166:UWW393203 VGE393166:VGS393203 VQA393166:VQO393203 VZW393166:WAK393203 WJS393166:WKG393203 WTO393166:WUC393203 HC458702:HQ458739 QY458702:RM458739 AAU458702:ABI458739 AKQ458702:ALE458739 AUM458702:AVA458739 BEI458702:BEW458739 BOE458702:BOS458739 BYA458702:BYO458739 CHW458702:CIK458739 CRS458702:CSG458739 DBO458702:DCC458739 DLK458702:DLY458739 DVG458702:DVU458739 EFC458702:EFQ458739 EOY458702:EPM458739 EYU458702:EZI458739 FIQ458702:FJE458739 FSM458702:FTA458739 GCI458702:GCW458739 GME458702:GMS458739 GWA458702:GWO458739 HFW458702:HGK458739 HPS458702:HQG458739 HZO458702:IAC458739 IJK458702:IJY458739 ITG458702:ITU458739 JDC458702:JDQ458739 JMY458702:JNM458739 JWU458702:JXI458739 KGQ458702:KHE458739 KQM458702:KRA458739 LAI458702:LAW458739 LKE458702:LKS458739 LUA458702:LUO458739 MDW458702:MEK458739 MNS458702:MOG458739 MXO458702:MYC458739 NHK458702:NHY458739 NRG458702:NRU458739 OBC458702:OBQ458739 OKY458702:OLM458739 OUU458702:OVI458739 PEQ458702:PFE458739 POM458702:PPA458739 PYI458702:PYW458739 QIE458702:QIS458739 QSA458702:QSO458739 RBW458702:RCK458739 RLS458702:RMG458739 RVO458702:RWC458739 SFK458702:SFY458739 SPG458702:SPU458739 SZC458702:SZQ458739 TIY458702:TJM458739 TSU458702:TTI458739 UCQ458702:UDE458739 UMM458702:UNA458739 UWI458702:UWW458739 VGE458702:VGS458739 VQA458702:VQO458739 VZW458702:WAK458739 WJS458702:WKG458739 WTO458702:WUC458739 HC524238:HQ524275 QY524238:RM524275 AAU524238:ABI524275 AKQ524238:ALE524275 AUM524238:AVA524275 BEI524238:BEW524275 BOE524238:BOS524275 BYA524238:BYO524275 CHW524238:CIK524275 CRS524238:CSG524275 DBO524238:DCC524275 DLK524238:DLY524275 DVG524238:DVU524275 EFC524238:EFQ524275 EOY524238:EPM524275 EYU524238:EZI524275 FIQ524238:FJE524275 FSM524238:FTA524275 GCI524238:GCW524275 GME524238:GMS524275 GWA524238:GWO524275 HFW524238:HGK524275 HPS524238:HQG524275 HZO524238:IAC524275 IJK524238:IJY524275 ITG524238:ITU524275 JDC524238:JDQ524275 JMY524238:JNM524275 JWU524238:JXI524275 KGQ524238:KHE524275 KQM524238:KRA524275 LAI524238:LAW524275 LKE524238:LKS524275 LUA524238:LUO524275 MDW524238:MEK524275 MNS524238:MOG524275 MXO524238:MYC524275 NHK524238:NHY524275 NRG524238:NRU524275 OBC524238:OBQ524275 OKY524238:OLM524275 OUU524238:OVI524275 PEQ524238:PFE524275 POM524238:PPA524275 PYI524238:PYW524275 QIE524238:QIS524275 QSA524238:QSO524275 RBW524238:RCK524275 RLS524238:RMG524275 RVO524238:RWC524275 SFK524238:SFY524275 SPG524238:SPU524275 SZC524238:SZQ524275 TIY524238:TJM524275 TSU524238:TTI524275 UCQ524238:UDE524275 UMM524238:UNA524275 UWI524238:UWW524275 VGE524238:VGS524275 VQA524238:VQO524275 VZW524238:WAK524275 WJS524238:WKG524275 WTO524238:WUC524275 HC589774:HQ589811 QY589774:RM589811 AAU589774:ABI589811 AKQ589774:ALE589811 AUM589774:AVA589811 BEI589774:BEW589811 BOE589774:BOS589811 BYA589774:BYO589811 CHW589774:CIK589811 CRS589774:CSG589811 DBO589774:DCC589811 DLK589774:DLY589811 DVG589774:DVU589811 EFC589774:EFQ589811 EOY589774:EPM589811 EYU589774:EZI589811 FIQ589774:FJE589811 FSM589774:FTA589811 GCI589774:GCW589811 GME589774:GMS589811 GWA589774:GWO589811 HFW589774:HGK589811 HPS589774:HQG589811 HZO589774:IAC589811 IJK589774:IJY589811 ITG589774:ITU589811 JDC589774:JDQ589811 JMY589774:JNM589811 JWU589774:JXI589811 KGQ589774:KHE589811 KQM589774:KRA589811 LAI589774:LAW589811 LKE589774:LKS589811 LUA589774:LUO589811 MDW589774:MEK589811 MNS589774:MOG589811 MXO589774:MYC589811 NHK589774:NHY589811 NRG589774:NRU589811 OBC589774:OBQ589811 OKY589774:OLM589811 OUU589774:OVI589811 PEQ589774:PFE589811 POM589774:PPA589811 PYI589774:PYW589811 QIE589774:QIS589811 QSA589774:QSO589811 RBW589774:RCK589811 RLS589774:RMG589811 RVO589774:RWC589811 SFK589774:SFY589811 SPG589774:SPU589811 SZC589774:SZQ589811 TIY589774:TJM589811 TSU589774:TTI589811 UCQ589774:UDE589811 UMM589774:UNA589811 UWI589774:UWW589811 VGE589774:VGS589811 VQA589774:VQO589811 VZW589774:WAK589811 WJS589774:WKG589811 WTO589774:WUC589811 HC655310:HQ655347 QY655310:RM655347 AAU655310:ABI655347 AKQ655310:ALE655347 AUM655310:AVA655347 BEI655310:BEW655347 BOE655310:BOS655347 BYA655310:BYO655347 CHW655310:CIK655347 CRS655310:CSG655347 DBO655310:DCC655347 DLK655310:DLY655347 DVG655310:DVU655347 EFC655310:EFQ655347 EOY655310:EPM655347 EYU655310:EZI655347 FIQ655310:FJE655347 FSM655310:FTA655347 GCI655310:GCW655347 GME655310:GMS655347 GWA655310:GWO655347 HFW655310:HGK655347 HPS655310:HQG655347 HZO655310:IAC655347 IJK655310:IJY655347 ITG655310:ITU655347 JDC655310:JDQ655347 JMY655310:JNM655347 JWU655310:JXI655347 KGQ655310:KHE655347 KQM655310:KRA655347 LAI655310:LAW655347 LKE655310:LKS655347 LUA655310:LUO655347 MDW655310:MEK655347 MNS655310:MOG655347 MXO655310:MYC655347 NHK655310:NHY655347 NRG655310:NRU655347 OBC655310:OBQ655347 OKY655310:OLM655347 OUU655310:OVI655347 PEQ655310:PFE655347 POM655310:PPA655347 PYI655310:PYW655347 QIE655310:QIS655347 QSA655310:QSO655347 RBW655310:RCK655347 RLS655310:RMG655347 RVO655310:RWC655347 SFK655310:SFY655347 SPG655310:SPU655347 SZC655310:SZQ655347 TIY655310:TJM655347 TSU655310:TTI655347 UCQ655310:UDE655347 UMM655310:UNA655347 UWI655310:UWW655347 VGE655310:VGS655347 VQA655310:VQO655347 VZW655310:WAK655347 WJS655310:WKG655347 WTO655310:WUC655347 HC720846:HQ720883 QY720846:RM720883 AAU720846:ABI720883 AKQ720846:ALE720883 AUM720846:AVA720883 BEI720846:BEW720883 BOE720846:BOS720883 BYA720846:BYO720883 CHW720846:CIK720883 CRS720846:CSG720883 DBO720846:DCC720883 DLK720846:DLY720883 DVG720846:DVU720883 EFC720846:EFQ720883 EOY720846:EPM720883 EYU720846:EZI720883 FIQ720846:FJE720883 FSM720846:FTA720883 GCI720846:GCW720883 GME720846:GMS720883 GWA720846:GWO720883 HFW720846:HGK720883 HPS720846:HQG720883 HZO720846:IAC720883 IJK720846:IJY720883 ITG720846:ITU720883 JDC720846:JDQ720883 JMY720846:JNM720883 JWU720846:JXI720883 KGQ720846:KHE720883 KQM720846:KRA720883 LAI720846:LAW720883 LKE720846:LKS720883 LUA720846:LUO720883 MDW720846:MEK720883 MNS720846:MOG720883 MXO720846:MYC720883 NHK720846:NHY720883 NRG720846:NRU720883 OBC720846:OBQ720883 OKY720846:OLM720883 OUU720846:OVI720883 PEQ720846:PFE720883 POM720846:PPA720883 PYI720846:PYW720883 QIE720846:QIS720883 QSA720846:QSO720883 RBW720846:RCK720883 RLS720846:RMG720883 RVO720846:RWC720883 SFK720846:SFY720883 SPG720846:SPU720883 SZC720846:SZQ720883 TIY720846:TJM720883 TSU720846:TTI720883 UCQ720846:UDE720883 UMM720846:UNA720883 UWI720846:UWW720883 VGE720846:VGS720883 VQA720846:VQO720883 VZW720846:WAK720883 WJS720846:WKG720883 WTO720846:WUC720883 HC786382:HQ786419 QY786382:RM786419 AAU786382:ABI786419 AKQ786382:ALE786419 AUM786382:AVA786419 BEI786382:BEW786419 BOE786382:BOS786419 BYA786382:BYO786419 CHW786382:CIK786419 CRS786382:CSG786419 DBO786382:DCC786419 DLK786382:DLY786419 DVG786382:DVU786419 EFC786382:EFQ786419 EOY786382:EPM786419 EYU786382:EZI786419 FIQ786382:FJE786419 FSM786382:FTA786419 GCI786382:GCW786419 GME786382:GMS786419 GWA786382:GWO786419 HFW786382:HGK786419 HPS786382:HQG786419 HZO786382:IAC786419 IJK786382:IJY786419 ITG786382:ITU786419 JDC786382:JDQ786419 JMY786382:JNM786419 JWU786382:JXI786419 KGQ786382:KHE786419 KQM786382:KRA786419 LAI786382:LAW786419 LKE786382:LKS786419 LUA786382:LUO786419 MDW786382:MEK786419 MNS786382:MOG786419 MXO786382:MYC786419 NHK786382:NHY786419 NRG786382:NRU786419 OBC786382:OBQ786419 OKY786382:OLM786419 OUU786382:OVI786419 PEQ786382:PFE786419 POM786382:PPA786419 PYI786382:PYW786419 QIE786382:QIS786419 QSA786382:QSO786419 RBW786382:RCK786419 RLS786382:RMG786419 RVO786382:RWC786419 SFK786382:SFY786419 SPG786382:SPU786419 SZC786382:SZQ786419 TIY786382:TJM786419 TSU786382:TTI786419 UCQ786382:UDE786419 UMM786382:UNA786419 UWI786382:UWW786419 VGE786382:VGS786419 VQA786382:VQO786419 VZW786382:WAK786419 WJS786382:WKG786419 WTO786382:WUC786419 HC851918:HQ851955 QY851918:RM851955 AAU851918:ABI851955 AKQ851918:ALE851955 AUM851918:AVA851955 BEI851918:BEW851955 BOE851918:BOS851955 BYA851918:BYO851955 CHW851918:CIK851955 CRS851918:CSG851955 DBO851918:DCC851955 DLK851918:DLY851955 DVG851918:DVU851955 EFC851918:EFQ851955 EOY851918:EPM851955 EYU851918:EZI851955 FIQ851918:FJE851955 FSM851918:FTA851955 GCI851918:GCW851955 GME851918:GMS851955 GWA851918:GWO851955 HFW851918:HGK851955 HPS851918:HQG851955 HZO851918:IAC851955 IJK851918:IJY851955 ITG851918:ITU851955 JDC851918:JDQ851955 JMY851918:JNM851955 JWU851918:JXI851955 KGQ851918:KHE851955 KQM851918:KRA851955 LAI851918:LAW851955 LKE851918:LKS851955 LUA851918:LUO851955 MDW851918:MEK851955 MNS851918:MOG851955 MXO851918:MYC851955 NHK851918:NHY851955 NRG851918:NRU851955 OBC851918:OBQ851955 OKY851918:OLM851955 OUU851918:OVI851955 PEQ851918:PFE851955 POM851918:PPA851955 PYI851918:PYW851955 QIE851918:QIS851955 QSA851918:QSO851955 RBW851918:RCK851955 RLS851918:RMG851955 RVO851918:RWC851955 SFK851918:SFY851955 SPG851918:SPU851955 SZC851918:SZQ851955 TIY851918:TJM851955 TSU851918:TTI851955 UCQ851918:UDE851955 UMM851918:UNA851955 UWI851918:UWW851955 VGE851918:VGS851955 VQA851918:VQO851955 VZW851918:WAK851955 WJS851918:WKG851955 WTO851918:WUC851955 HC917454:HQ917491 QY917454:RM917491 AAU917454:ABI917491 AKQ917454:ALE917491 AUM917454:AVA917491 BEI917454:BEW917491 BOE917454:BOS917491 BYA917454:BYO917491 CHW917454:CIK917491 CRS917454:CSG917491 DBO917454:DCC917491 DLK917454:DLY917491 DVG917454:DVU917491 EFC917454:EFQ917491 EOY917454:EPM917491 EYU917454:EZI917491 FIQ917454:FJE917491 FSM917454:FTA917491 GCI917454:GCW917491 GME917454:GMS917491 GWA917454:GWO917491 HFW917454:HGK917491 HPS917454:HQG917491 HZO917454:IAC917491 IJK917454:IJY917491 ITG917454:ITU917491 JDC917454:JDQ917491 JMY917454:JNM917491 JWU917454:JXI917491 KGQ917454:KHE917491 KQM917454:KRA917491 LAI917454:LAW917491 LKE917454:LKS917491 LUA917454:LUO917491 MDW917454:MEK917491 MNS917454:MOG917491 MXO917454:MYC917491 NHK917454:NHY917491 NRG917454:NRU917491 OBC917454:OBQ917491 OKY917454:OLM917491 OUU917454:OVI917491 PEQ917454:PFE917491 POM917454:PPA917491 PYI917454:PYW917491 QIE917454:QIS917491 QSA917454:QSO917491 RBW917454:RCK917491 RLS917454:RMG917491 RVO917454:RWC917491 SFK917454:SFY917491 SPG917454:SPU917491 SZC917454:SZQ917491 TIY917454:TJM917491 TSU917454:TTI917491 UCQ917454:UDE917491 UMM917454:UNA917491 UWI917454:UWW917491 VGE917454:VGS917491 VQA917454:VQO917491 VZW917454:WAK917491 WJS917454:WKG917491 WTO917454:WUC917491 HC982990:HQ983027 QY982990:RM983027 AAU982990:ABI983027 AKQ982990:ALE983027 AUM982990:AVA983027 BEI982990:BEW983027 BOE982990:BOS983027 BYA982990:BYO983027 CHW982990:CIK983027 CRS982990:CSG983027 DBO982990:DCC983027 DLK982990:DLY983027 DVG982990:DVU983027 EFC982990:EFQ983027 EOY982990:EPM983027 EYU982990:EZI983027 FIQ982990:FJE983027 FSM982990:FTA983027 GCI982990:GCW983027 GME982990:GMS983027 GWA982990:GWO983027 HFW982990:HGK983027 HPS982990:HQG983027 HZO982990:IAC983027 IJK982990:IJY983027 ITG982990:ITU983027 JDC982990:JDQ983027 JMY982990:JNM983027 JWU982990:JXI983027 KGQ982990:KHE983027 KQM982990:KRA983027 LAI982990:LAW983027 LKE982990:LKS983027 LUA982990:LUO983027 MDW982990:MEK983027 MNS982990:MOG983027 MXO982990:MYC983027 NHK982990:NHY983027 NRG982990:NRU983027 OBC982990:OBQ983027 OKY982990:OLM983027 OUU982990:OVI983027 PEQ982990:PFE983027 POM982990:PPA983027 PYI982990:PYW983027 QIE982990:QIS983027 QSA982990:QSO983027 RBW982990:RCK983027 RLS982990:RMG983027 RVO982990:RWC983027 SFK982990:SFY983027 SPG982990:SPU983027 SZC982990:SZQ983027 TIY982990:TJM983027 TSU982990:TTI983027 UCQ982990:UDE983027 UMM982990:UNA983027 UWI982990:UWW983027 VGE982990:VGS983027 VQA982990:VQO983027 WJS5:WKG18 WTO982990:WUC983027" xr:uid="{C4ED132A-D8E6-4B24-B44A-430CE62F3BAA}">
       <formula1>#REF!</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="HQ983029:HX983034 RM983029:RT983034 ABI983029:ABP983034 ALE983029:ALL983034 AVA983029:AVH983034 BEW983029:BFD983034 BOS983029:BOZ983034 BYO983029:BYV983034 CIK983029:CIR983034 CSG983029:CSN983034 DCC983029:DCJ983034 DLY983029:DMF983034 DVU983029:DWB983034 EFQ983029:EFX983034 EPM983029:EPT983034 EZI983029:EZP983034 FJE983029:FJL983034 FTA983029:FTH983034 GCW983029:GDD983034 GMS983029:GMZ983034 GWO983029:GWV983034 HGK983029:HGR983034 HQG983029:HQN983034 IAC983029:IAJ983034 IJY983029:IKF983034 ITU983029:IUB983034 JDQ983029:JDX983034 JNM983029:JNT983034 JXI983029:JXP983034 KHE983029:KHL983034 KRA983029:KRH983034 LAW983029:LBD983034 LKS983029:LKZ983034 LUO983029:LUV983034 MEK983029:MER983034 MOG983029:MON983034 MYC983029:MYJ983034 NHY983029:NIF983034 NRU983029:NSB983034 OBQ983029:OBX983034 OLM983029:OLT983034 OVI983029:OVP983034 PFE983029:PFL983034 PPA983029:PPH983034 PYW983029:PZD983034 QIS983029:QIZ983034 QSO983029:QSV983034 RCK983029:RCR983034 RMG983029:RMN983034 RWC983029:RWJ983034 SFY983029:SGF983034 SPU983029:SQB983034 SZQ983029:SZX983034 TJM983029:TJT983034 TTI983029:TTP983034 UDE983029:UDL983034 UNA983029:UNH983034 UWW983029:UXD983034 VGS983029:VGZ983034 VQO983029:VQV983034 WAK983029:WAR983034 WKG983029:WKN983034 WUC983029:WUJ983034 HQ65525:HX65530 RM65525:RT65530 ABI65525:ABP65530 ALE65525:ALL65530 AVA65525:AVH65530 BEW65525:BFD65530 BOS65525:BOZ65530 BYO65525:BYV65530 CIK65525:CIR65530 CSG65525:CSN65530 DCC65525:DCJ65530 DLY65525:DMF65530 DVU65525:DWB65530 EFQ65525:EFX65530 EPM65525:EPT65530 EZI65525:EZP65530 FJE65525:FJL65530 FTA65525:FTH65530 GCW65525:GDD65530 GMS65525:GMZ65530 GWO65525:GWV65530 HGK65525:HGR65530 HQG65525:HQN65530 IAC65525:IAJ65530 IJY65525:IKF65530 ITU65525:IUB65530 JDQ65525:JDX65530 JNM65525:JNT65530 JXI65525:JXP65530 KHE65525:KHL65530 KRA65525:KRH65530 LAW65525:LBD65530 LKS65525:LKZ65530 LUO65525:LUV65530 MEK65525:MER65530 MOG65525:MON65530 MYC65525:MYJ65530 NHY65525:NIF65530 NRU65525:NSB65530 OBQ65525:OBX65530 OLM65525:OLT65530 OVI65525:OVP65530 PFE65525:PFL65530 PPA65525:PPH65530 PYW65525:PZD65530 QIS65525:QIZ65530 QSO65525:QSV65530 RCK65525:RCR65530 RMG65525:RMN65530 RWC65525:RWJ65530 SFY65525:SGF65530 SPU65525:SQB65530 SZQ65525:SZX65530 TJM65525:TJT65530 TTI65525:TTP65530 UDE65525:UDL65530 UNA65525:UNH65530 UWW65525:UXD65530 VGS65525:VGZ65530 VQO65525:VQV65530 WAK65525:WAR65530 WKG65525:WKN65530 WUC65525:WUJ65530 HQ131061:HX131066 RM131061:RT131066 ABI131061:ABP131066 ALE131061:ALL131066 AVA131061:AVH131066 BEW131061:BFD131066 BOS131061:BOZ131066 BYO131061:BYV131066 CIK131061:CIR131066 CSG131061:CSN131066 DCC131061:DCJ131066 DLY131061:DMF131066 DVU131061:DWB131066 EFQ131061:EFX131066 EPM131061:EPT131066 EZI131061:EZP131066 FJE131061:FJL131066 FTA131061:FTH131066 GCW131061:GDD131066 GMS131061:GMZ131066 GWO131061:GWV131066 HGK131061:HGR131066 HQG131061:HQN131066 IAC131061:IAJ131066 IJY131061:IKF131066 ITU131061:IUB131066 JDQ131061:JDX131066 JNM131061:JNT131066 JXI131061:JXP131066 KHE131061:KHL131066 KRA131061:KRH131066 LAW131061:LBD131066 LKS131061:LKZ131066 LUO131061:LUV131066 MEK131061:MER131066 MOG131061:MON131066 MYC131061:MYJ131066 NHY131061:NIF131066 NRU131061:NSB131066 OBQ131061:OBX131066 OLM131061:OLT131066 OVI131061:OVP131066 PFE131061:PFL131066 PPA131061:PPH131066 PYW131061:PZD131066 QIS131061:QIZ131066 QSO131061:QSV131066 RCK131061:RCR131066 RMG131061:RMN131066 RWC131061:RWJ131066 SFY131061:SGF131066 SPU131061:SQB131066 SZQ131061:SZX131066 TJM131061:TJT131066 TTI131061:TTP131066 UDE131061:UDL131066 UNA131061:UNH131066 UWW131061:UXD131066 VGS131061:VGZ131066 VQO131061:VQV131066 WAK131061:WAR131066 WKG131061:WKN131066 WUC131061:WUJ131066 HQ196597:HX196602 RM196597:RT196602 ABI196597:ABP196602 ALE196597:ALL196602 AVA196597:AVH196602 BEW196597:BFD196602 BOS196597:BOZ196602 BYO196597:BYV196602 CIK196597:CIR196602 CSG196597:CSN196602 DCC196597:DCJ196602 DLY196597:DMF196602 DVU196597:DWB196602 EFQ196597:EFX196602 EPM196597:EPT196602 EZI196597:EZP196602 FJE196597:FJL196602 FTA196597:FTH196602 GCW196597:GDD196602 GMS196597:GMZ196602 GWO196597:GWV196602 HGK196597:HGR196602 HQG196597:HQN196602 IAC196597:IAJ196602 IJY196597:IKF196602 ITU196597:IUB196602 JDQ196597:JDX196602 JNM196597:JNT196602 JXI196597:JXP196602 KHE196597:KHL196602 KRA196597:KRH196602 LAW196597:LBD196602 LKS196597:LKZ196602 LUO196597:LUV196602 MEK196597:MER196602 MOG196597:MON196602 MYC196597:MYJ196602 NHY196597:NIF196602 NRU196597:NSB196602 OBQ196597:OBX196602 OLM196597:OLT196602 OVI196597:OVP196602 PFE196597:PFL196602 PPA196597:PPH196602 PYW196597:PZD196602 QIS196597:QIZ196602 QSO196597:QSV196602 RCK196597:RCR196602 RMG196597:RMN196602 RWC196597:RWJ196602 SFY196597:SGF196602 SPU196597:SQB196602 SZQ196597:SZX196602 TJM196597:TJT196602 TTI196597:TTP196602 UDE196597:UDL196602 UNA196597:UNH196602 UWW196597:UXD196602 VGS196597:VGZ196602 VQO196597:VQV196602 WAK196597:WAR196602 WKG196597:WKN196602 WUC196597:WUJ196602 HQ262133:HX262138 RM262133:RT262138 ABI262133:ABP262138 ALE262133:ALL262138 AVA262133:AVH262138 BEW262133:BFD262138 BOS262133:BOZ262138 BYO262133:BYV262138 CIK262133:CIR262138 CSG262133:CSN262138 DCC262133:DCJ262138 DLY262133:DMF262138 DVU262133:DWB262138 EFQ262133:EFX262138 EPM262133:EPT262138 EZI262133:EZP262138 FJE262133:FJL262138 FTA262133:FTH262138 GCW262133:GDD262138 GMS262133:GMZ262138 GWO262133:GWV262138 HGK262133:HGR262138 HQG262133:HQN262138 IAC262133:IAJ262138 IJY262133:IKF262138 ITU262133:IUB262138 JDQ262133:JDX262138 JNM262133:JNT262138 JXI262133:JXP262138 KHE262133:KHL262138 KRA262133:KRH262138 LAW262133:LBD262138 LKS262133:LKZ262138 LUO262133:LUV262138 MEK262133:MER262138 MOG262133:MON262138 MYC262133:MYJ262138 NHY262133:NIF262138 NRU262133:NSB262138 OBQ262133:OBX262138 OLM262133:OLT262138 OVI262133:OVP262138 PFE262133:PFL262138 PPA262133:PPH262138 PYW262133:PZD262138 QIS262133:QIZ262138 QSO262133:QSV262138 RCK262133:RCR262138 RMG262133:RMN262138 RWC262133:RWJ262138 SFY262133:SGF262138 SPU262133:SQB262138 SZQ262133:SZX262138 TJM262133:TJT262138 TTI262133:TTP262138 UDE262133:UDL262138 UNA262133:UNH262138 UWW262133:UXD262138 VGS262133:VGZ262138 VQO262133:VQV262138 WAK262133:WAR262138 WKG262133:WKN262138 WUC262133:WUJ262138 HQ327669:HX327674 RM327669:RT327674 ABI327669:ABP327674 ALE327669:ALL327674 AVA327669:AVH327674 BEW327669:BFD327674 BOS327669:BOZ327674 BYO327669:BYV327674 CIK327669:CIR327674 CSG327669:CSN327674 DCC327669:DCJ327674 DLY327669:DMF327674 DVU327669:DWB327674 EFQ327669:EFX327674 EPM327669:EPT327674 EZI327669:EZP327674 FJE327669:FJL327674 FTA327669:FTH327674 GCW327669:GDD327674 GMS327669:GMZ327674 GWO327669:GWV327674 HGK327669:HGR327674 HQG327669:HQN327674 IAC327669:IAJ327674 IJY327669:IKF327674 ITU327669:IUB327674 JDQ327669:JDX327674 JNM327669:JNT327674 JXI327669:JXP327674 KHE327669:KHL327674 KRA327669:KRH327674 LAW327669:LBD327674 LKS327669:LKZ327674 LUO327669:LUV327674 MEK327669:MER327674 MOG327669:MON327674 MYC327669:MYJ327674 NHY327669:NIF327674 NRU327669:NSB327674 OBQ327669:OBX327674 OLM327669:OLT327674 OVI327669:OVP327674 PFE327669:PFL327674 PPA327669:PPH327674 PYW327669:PZD327674 QIS327669:QIZ327674 QSO327669:QSV327674 RCK327669:RCR327674 RMG327669:RMN327674 RWC327669:RWJ327674 SFY327669:SGF327674 SPU327669:SQB327674 SZQ327669:SZX327674 TJM327669:TJT327674 TTI327669:TTP327674 UDE327669:UDL327674 UNA327669:UNH327674 UWW327669:UXD327674 VGS327669:VGZ327674 VQO327669:VQV327674 WAK327669:WAR327674 WKG327669:WKN327674 WUC327669:WUJ327674 HQ393205:HX393210 RM393205:RT393210 ABI393205:ABP393210 ALE393205:ALL393210 AVA393205:AVH393210 BEW393205:BFD393210 BOS393205:BOZ393210 BYO393205:BYV393210 CIK393205:CIR393210 CSG393205:CSN393210 DCC393205:DCJ393210 DLY393205:DMF393210 DVU393205:DWB393210 EFQ393205:EFX393210 EPM393205:EPT393210 EZI393205:EZP393210 FJE393205:FJL393210 FTA393205:FTH393210 GCW393205:GDD393210 GMS393205:GMZ393210 GWO393205:GWV393210 HGK393205:HGR393210 HQG393205:HQN393210 IAC393205:IAJ393210 IJY393205:IKF393210 ITU393205:IUB393210 JDQ393205:JDX393210 JNM393205:JNT393210 JXI393205:JXP393210 KHE393205:KHL393210 KRA393205:KRH393210 LAW393205:LBD393210 LKS393205:LKZ393210 LUO393205:LUV393210 MEK393205:MER393210 MOG393205:MON393210 MYC393205:MYJ393210 NHY393205:NIF393210 NRU393205:NSB393210 OBQ393205:OBX393210 OLM393205:OLT393210 OVI393205:OVP393210 PFE393205:PFL393210 PPA393205:PPH393210 PYW393205:PZD393210 QIS393205:QIZ393210 QSO393205:QSV393210 RCK393205:RCR393210 RMG393205:RMN393210 RWC393205:RWJ393210 SFY393205:SGF393210 SPU393205:SQB393210 SZQ393205:SZX393210 TJM393205:TJT393210 TTI393205:TTP393210 UDE393205:UDL393210 UNA393205:UNH393210 UWW393205:UXD393210 VGS393205:VGZ393210 VQO393205:VQV393210 WAK393205:WAR393210 WKG393205:WKN393210 WUC393205:WUJ393210 HQ458741:HX458746 RM458741:RT458746 ABI458741:ABP458746 ALE458741:ALL458746 AVA458741:AVH458746 BEW458741:BFD458746 BOS458741:BOZ458746 BYO458741:BYV458746 CIK458741:CIR458746 CSG458741:CSN458746 DCC458741:DCJ458746 DLY458741:DMF458746 DVU458741:DWB458746 EFQ458741:EFX458746 EPM458741:EPT458746 EZI458741:EZP458746 FJE458741:FJL458746 FTA458741:FTH458746 GCW458741:GDD458746 GMS458741:GMZ458746 GWO458741:GWV458746 HGK458741:HGR458746 HQG458741:HQN458746 IAC458741:IAJ458746 IJY458741:IKF458746 ITU458741:IUB458746 JDQ458741:JDX458746 JNM458741:JNT458746 JXI458741:JXP458746 KHE458741:KHL458746 KRA458741:KRH458746 LAW458741:LBD458746 LKS458741:LKZ458746 LUO458741:LUV458746 MEK458741:MER458746 MOG458741:MON458746 MYC458741:MYJ458746 NHY458741:NIF458746 NRU458741:NSB458746 OBQ458741:OBX458746 OLM458741:OLT458746 OVI458741:OVP458746 PFE458741:PFL458746 PPA458741:PPH458746 PYW458741:PZD458746 QIS458741:QIZ458746 QSO458741:QSV458746 RCK458741:RCR458746 RMG458741:RMN458746 RWC458741:RWJ458746 SFY458741:SGF458746 SPU458741:SQB458746 SZQ458741:SZX458746 TJM458741:TJT458746 TTI458741:TTP458746 UDE458741:UDL458746 UNA458741:UNH458746 UWW458741:UXD458746 VGS458741:VGZ458746 VQO458741:VQV458746 WAK458741:WAR458746 WKG458741:WKN458746 WUC458741:WUJ458746 HQ524277:HX524282 RM524277:RT524282 ABI524277:ABP524282 ALE524277:ALL524282 AVA524277:AVH524282 BEW524277:BFD524282 BOS524277:BOZ524282 BYO524277:BYV524282 CIK524277:CIR524282 CSG524277:CSN524282 DCC524277:DCJ524282 DLY524277:DMF524282 DVU524277:DWB524282 EFQ524277:EFX524282 EPM524277:EPT524282 EZI524277:EZP524282 FJE524277:FJL524282 FTA524277:FTH524282 GCW524277:GDD524282 GMS524277:GMZ524282 GWO524277:GWV524282 HGK524277:HGR524282 HQG524277:HQN524282 IAC524277:IAJ524282 IJY524277:IKF524282 ITU524277:IUB524282 JDQ524277:JDX524282 JNM524277:JNT524282 JXI524277:JXP524282 KHE524277:KHL524282 KRA524277:KRH524282 LAW524277:LBD524282 LKS524277:LKZ524282 LUO524277:LUV524282 MEK524277:MER524282 MOG524277:MON524282 MYC524277:MYJ524282 NHY524277:NIF524282 NRU524277:NSB524282 OBQ524277:OBX524282 OLM524277:OLT524282 OVI524277:OVP524282 PFE524277:PFL524282 PPA524277:PPH524282 PYW524277:PZD524282 QIS524277:QIZ524282 QSO524277:QSV524282 RCK524277:RCR524282 RMG524277:RMN524282 RWC524277:RWJ524282 SFY524277:SGF524282 SPU524277:SQB524282 SZQ524277:SZX524282 TJM524277:TJT524282 TTI524277:TTP524282 UDE524277:UDL524282 UNA524277:UNH524282 UWW524277:UXD524282 VGS524277:VGZ524282 VQO524277:VQV524282 WAK524277:WAR524282 WKG524277:WKN524282 WUC524277:WUJ524282 HQ589813:HX589818 RM589813:RT589818 ABI589813:ABP589818 ALE589813:ALL589818 AVA589813:AVH589818 BEW589813:BFD589818 BOS589813:BOZ589818 BYO589813:BYV589818 CIK589813:CIR589818 CSG589813:CSN589818 DCC589813:DCJ589818 DLY589813:DMF589818 DVU589813:DWB589818 EFQ589813:EFX589818 EPM589813:EPT589818 EZI589813:EZP589818 FJE589813:FJL589818 FTA589813:FTH589818 GCW589813:GDD589818 GMS589813:GMZ589818 GWO589813:GWV589818 HGK589813:HGR589818 HQG589813:HQN589818 IAC589813:IAJ589818 IJY589813:IKF589818 ITU589813:IUB589818 JDQ589813:JDX589818 JNM589813:JNT589818 JXI589813:JXP589818 KHE589813:KHL589818 KRA589813:KRH589818 LAW589813:LBD589818 LKS589813:LKZ589818 LUO589813:LUV589818 MEK589813:MER589818 MOG589813:MON589818 MYC589813:MYJ589818 NHY589813:NIF589818 NRU589813:NSB589818 OBQ589813:OBX589818 OLM589813:OLT589818 OVI589813:OVP589818 PFE589813:PFL589818 PPA589813:PPH589818 PYW589813:PZD589818 QIS589813:QIZ589818 QSO589813:QSV589818 RCK589813:RCR589818 RMG589813:RMN589818 RWC589813:RWJ589818 SFY589813:SGF589818 SPU589813:SQB589818 SZQ589813:SZX589818 TJM589813:TJT589818 TTI589813:TTP589818 UDE589813:UDL589818 UNA589813:UNH589818 UWW589813:UXD589818 VGS589813:VGZ589818 VQO589813:VQV589818 WAK589813:WAR589818 WKG589813:WKN589818 WUC589813:WUJ589818 HQ655349:HX655354 RM655349:RT655354 ABI655349:ABP655354 ALE655349:ALL655354 AVA655349:AVH655354 BEW655349:BFD655354 BOS655349:BOZ655354 BYO655349:BYV655354 CIK655349:CIR655354 CSG655349:CSN655354 DCC655349:DCJ655354 DLY655349:DMF655354 DVU655349:DWB655354 EFQ655349:EFX655354 EPM655349:EPT655354 EZI655349:EZP655354 FJE655349:FJL655354 FTA655349:FTH655354 GCW655349:GDD655354 GMS655349:GMZ655354 GWO655349:GWV655354 HGK655349:HGR655354 HQG655349:HQN655354 IAC655349:IAJ655354 IJY655349:IKF655354 ITU655349:IUB655354 JDQ655349:JDX655354 JNM655349:JNT655354 JXI655349:JXP655354 KHE655349:KHL655354 KRA655349:KRH655354 LAW655349:LBD655354 LKS655349:LKZ655354 LUO655349:LUV655354 MEK655349:MER655354 MOG655349:MON655354 MYC655349:MYJ655354 NHY655349:NIF655354 NRU655349:NSB655354 OBQ655349:OBX655354 OLM655349:OLT655354 OVI655349:OVP655354 PFE655349:PFL655354 PPA655349:PPH655354 PYW655349:PZD655354 QIS655349:QIZ655354 QSO655349:QSV655354 RCK655349:RCR655354 RMG655349:RMN655354 RWC655349:RWJ655354 SFY655349:SGF655354 SPU655349:SQB655354 SZQ655349:SZX655354 TJM655349:TJT655354 TTI655349:TTP655354 UDE655349:UDL655354 UNA655349:UNH655354 UWW655349:UXD655354 VGS655349:VGZ655354 VQO655349:VQV655354 WAK655349:WAR655354 WKG655349:WKN655354 WUC655349:WUJ655354 HQ720885:HX720890 RM720885:RT720890 ABI720885:ABP720890 ALE720885:ALL720890 AVA720885:AVH720890 BEW720885:BFD720890 BOS720885:BOZ720890 BYO720885:BYV720890 CIK720885:CIR720890 CSG720885:CSN720890 DCC720885:DCJ720890 DLY720885:DMF720890 DVU720885:DWB720890 EFQ720885:EFX720890 EPM720885:EPT720890 EZI720885:EZP720890 FJE720885:FJL720890 FTA720885:FTH720890 GCW720885:GDD720890 GMS720885:GMZ720890 GWO720885:GWV720890 HGK720885:HGR720890 HQG720885:HQN720890 IAC720885:IAJ720890 IJY720885:IKF720890 ITU720885:IUB720890 JDQ720885:JDX720890 JNM720885:JNT720890 JXI720885:JXP720890 KHE720885:KHL720890 KRA720885:KRH720890 LAW720885:LBD720890 LKS720885:LKZ720890 LUO720885:LUV720890 MEK720885:MER720890 MOG720885:MON720890 MYC720885:MYJ720890 NHY720885:NIF720890 NRU720885:NSB720890 OBQ720885:OBX720890 OLM720885:OLT720890 OVI720885:OVP720890 PFE720885:PFL720890 PPA720885:PPH720890 PYW720885:PZD720890 QIS720885:QIZ720890 QSO720885:QSV720890 RCK720885:RCR720890 RMG720885:RMN720890 RWC720885:RWJ720890 SFY720885:SGF720890 SPU720885:SQB720890 SZQ720885:SZX720890 TJM720885:TJT720890 TTI720885:TTP720890 UDE720885:UDL720890 UNA720885:UNH720890 UWW720885:UXD720890 VGS720885:VGZ720890 VQO720885:VQV720890 WAK720885:WAR720890 WKG720885:WKN720890 WUC720885:WUJ720890 HQ786421:HX786426 RM786421:RT786426 ABI786421:ABP786426 ALE786421:ALL786426 AVA786421:AVH786426 BEW786421:BFD786426 BOS786421:BOZ786426 BYO786421:BYV786426 CIK786421:CIR786426 CSG786421:CSN786426 DCC786421:DCJ786426 DLY786421:DMF786426 DVU786421:DWB786426 EFQ786421:EFX786426 EPM786421:EPT786426 EZI786421:EZP786426 FJE786421:FJL786426 FTA786421:FTH786426 GCW786421:GDD786426 GMS786421:GMZ786426 GWO786421:GWV786426 HGK786421:HGR786426 HQG786421:HQN786426 IAC786421:IAJ786426 IJY786421:IKF786426 ITU786421:IUB786426 JDQ786421:JDX786426 JNM786421:JNT786426 JXI786421:JXP786426 KHE786421:KHL786426 KRA786421:KRH786426 LAW786421:LBD786426 LKS786421:LKZ786426 LUO786421:LUV786426 MEK786421:MER786426 MOG786421:MON786426 MYC786421:MYJ786426 NHY786421:NIF786426 NRU786421:NSB786426 OBQ786421:OBX786426 OLM786421:OLT786426 OVI786421:OVP786426 PFE786421:PFL786426 PPA786421:PPH786426 PYW786421:PZD786426 QIS786421:QIZ786426 QSO786421:QSV786426 RCK786421:RCR786426 RMG786421:RMN786426 RWC786421:RWJ786426 SFY786421:SGF786426 SPU786421:SQB786426 SZQ786421:SZX786426 TJM786421:TJT786426 TTI786421:TTP786426 UDE786421:UDL786426 UNA786421:UNH786426 UWW786421:UXD786426 VGS786421:VGZ786426 VQO786421:VQV786426 WAK786421:WAR786426 WKG786421:WKN786426 WUC786421:WUJ786426 HQ851957:HX851962 RM851957:RT851962 ABI851957:ABP851962 ALE851957:ALL851962 AVA851957:AVH851962 BEW851957:BFD851962 BOS851957:BOZ851962 BYO851957:BYV851962 CIK851957:CIR851962 CSG851957:CSN851962 DCC851957:DCJ851962 DLY851957:DMF851962 DVU851957:DWB851962 EFQ851957:EFX851962 EPM851957:EPT851962 EZI851957:EZP851962 FJE851957:FJL851962 FTA851957:FTH851962 GCW851957:GDD851962 GMS851957:GMZ851962 GWO851957:GWV851962 HGK851957:HGR851962 HQG851957:HQN851962 IAC851957:IAJ851962 IJY851957:IKF851962 ITU851957:IUB851962 JDQ851957:JDX851962 JNM851957:JNT851962 JXI851957:JXP851962 KHE851957:KHL851962 KRA851957:KRH851962 LAW851957:LBD851962 LKS851957:LKZ851962 LUO851957:LUV851962 MEK851957:MER851962 MOG851957:MON851962 MYC851957:MYJ851962 NHY851957:NIF851962 NRU851957:NSB851962 OBQ851957:OBX851962 OLM851957:OLT851962 OVI851957:OVP851962 PFE851957:PFL851962 PPA851957:PPH851962 PYW851957:PZD851962 QIS851957:QIZ851962 QSO851957:QSV851962 RCK851957:RCR851962 RMG851957:RMN851962 RWC851957:RWJ851962 SFY851957:SGF851962 SPU851957:SQB851962 SZQ851957:SZX851962 TJM851957:TJT851962 TTI851957:TTP851962 UDE851957:UDL851962 UNA851957:UNH851962 UWW851957:UXD851962 VGS851957:VGZ851962 VQO851957:VQV851962 WAK851957:WAR851962 WKG851957:WKN851962 WUC851957:WUJ851962 HQ917493:HX917498 RM917493:RT917498 ABI917493:ABP917498 ALE917493:ALL917498 AVA917493:AVH917498 BEW917493:BFD917498 BOS917493:BOZ917498 BYO917493:BYV917498 CIK917493:CIR917498 CSG917493:CSN917498 DCC917493:DCJ917498 DLY917493:DMF917498 DVU917493:DWB917498 EFQ917493:EFX917498 EPM917493:EPT917498 EZI917493:EZP917498 FJE917493:FJL917498 FTA917493:FTH917498 GCW917493:GDD917498 GMS917493:GMZ917498 GWO917493:GWV917498 HGK917493:HGR917498 HQG917493:HQN917498 IAC917493:IAJ917498 IJY917493:IKF917498 ITU917493:IUB917498 JDQ917493:JDX917498 JNM917493:JNT917498 JXI917493:JXP917498 KHE917493:KHL917498 KRA917493:KRH917498 LAW917493:LBD917498 LKS917493:LKZ917498 LUO917493:LUV917498 MEK917493:MER917498 MOG917493:MON917498 MYC917493:MYJ917498 NHY917493:NIF917498 NRU917493:NSB917498 OBQ917493:OBX917498 OLM917493:OLT917498 OVI917493:OVP917498 PFE917493:PFL917498 PPA917493:PPH917498 PYW917493:PZD917498 QIS917493:QIZ917498 QSO917493:QSV917498 RCK917493:RCR917498 RMG917493:RMN917498 RWC917493:RWJ917498 SFY917493:SGF917498 SPU917493:SQB917498 SZQ917493:SZX917498 TJM917493:TJT917498 TTI917493:TTP917498 UDE917493:UDL917498 UNA917493:UNH917498 UWW917493:UXD917498 VGS917493:VGZ917498 VQO917493:VQV917498 WAK917493:WAR917498 WKG917493:WKN917498 WUC917493:WUJ917498" xr:uid="{38E70801-6EC0-4CA3-9454-EC0ABF5F9215}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="HQ983031:HX983036 RM983031:RT983036 ABI983031:ABP983036 ALE983031:ALL983036 AVA983031:AVH983036 BEW983031:BFD983036 BOS983031:BOZ983036 BYO983031:BYV983036 CIK983031:CIR983036 CSG983031:CSN983036 DCC983031:DCJ983036 DLY983031:DMF983036 DVU983031:DWB983036 EFQ983031:EFX983036 EPM983031:EPT983036 EZI983031:EZP983036 FJE983031:FJL983036 FTA983031:FTH983036 GCW983031:GDD983036 GMS983031:GMZ983036 GWO983031:GWV983036 HGK983031:HGR983036 HQG983031:HQN983036 IAC983031:IAJ983036 IJY983031:IKF983036 ITU983031:IUB983036 JDQ983031:JDX983036 JNM983031:JNT983036 JXI983031:JXP983036 KHE983031:KHL983036 KRA983031:KRH983036 LAW983031:LBD983036 LKS983031:LKZ983036 LUO983031:LUV983036 MEK983031:MER983036 MOG983031:MON983036 MYC983031:MYJ983036 NHY983031:NIF983036 NRU983031:NSB983036 OBQ983031:OBX983036 OLM983031:OLT983036 OVI983031:OVP983036 PFE983031:PFL983036 PPA983031:PPH983036 PYW983031:PZD983036 QIS983031:QIZ983036 QSO983031:QSV983036 RCK983031:RCR983036 RMG983031:RMN983036 RWC983031:RWJ983036 SFY983031:SGF983036 SPU983031:SQB983036 SZQ983031:SZX983036 TJM983031:TJT983036 TTI983031:TTP983036 UDE983031:UDL983036 UNA983031:UNH983036 UWW983031:UXD983036 VGS983031:VGZ983036 VQO983031:VQV983036 WAK983031:WAR983036 WKG983031:WKN983036 WUC983031:WUJ983036 HQ65527:HX65532 RM65527:RT65532 ABI65527:ABP65532 ALE65527:ALL65532 AVA65527:AVH65532 BEW65527:BFD65532 BOS65527:BOZ65532 BYO65527:BYV65532 CIK65527:CIR65532 CSG65527:CSN65532 DCC65527:DCJ65532 DLY65527:DMF65532 DVU65527:DWB65532 EFQ65527:EFX65532 EPM65527:EPT65532 EZI65527:EZP65532 FJE65527:FJL65532 FTA65527:FTH65532 GCW65527:GDD65532 GMS65527:GMZ65532 GWO65527:GWV65532 HGK65527:HGR65532 HQG65527:HQN65532 IAC65527:IAJ65532 IJY65527:IKF65532 ITU65527:IUB65532 JDQ65527:JDX65532 JNM65527:JNT65532 JXI65527:JXP65532 KHE65527:KHL65532 KRA65527:KRH65532 LAW65527:LBD65532 LKS65527:LKZ65532 LUO65527:LUV65532 MEK65527:MER65532 MOG65527:MON65532 MYC65527:MYJ65532 NHY65527:NIF65532 NRU65527:NSB65532 OBQ65527:OBX65532 OLM65527:OLT65532 OVI65527:OVP65532 PFE65527:PFL65532 PPA65527:PPH65532 PYW65527:PZD65532 QIS65527:QIZ65532 QSO65527:QSV65532 RCK65527:RCR65532 RMG65527:RMN65532 RWC65527:RWJ65532 SFY65527:SGF65532 SPU65527:SQB65532 SZQ65527:SZX65532 TJM65527:TJT65532 TTI65527:TTP65532 UDE65527:UDL65532 UNA65527:UNH65532 UWW65527:UXD65532 VGS65527:VGZ65532 VQO65527:VQV65532 WAK65527:WAR65532 WKG65527:WKN65532 WUC65527:WUJ65532 HQ131063:HX131068 RM131063:RT131068 ABI131063:ABP131068 ALE131063:ALL131068 AVA131063:AVH131068 BEW131063:BFD131068 BOS131063:BOZ131068 BYO131063:BYV131068 CIK131063:CIR131068 CSG131063:CSN131068 DCC131063:DCJ131068 DLY131063:DMF131068 DVU131063:DWB131068 EFQ131063:EFX131068 EPM131063:EPT131068 EZI131063:EZP131068 FJE131063:FJL131068 FTA131063:FTH131068 GCW131063:GDD131068 GMS131063:GMZ131068 GWO131063:GWV131068 HGK131063:HGR131068 HQG131063:HQN131068 IAC131063:IAJ131068 IJY131063:IKF131068 ITU131063:IUB131068 JDQ131063:JDX131068 JNM131063:JNT131068 JXI131063:JXP131068 KHE131063:KHL131068 KRA131063:KRH131068 LAW131063:LBD131068 LKS131063:LKZ131068 LUO131063:LUV131068 MEK131063:MER131068 MOG131063:MON131068 MYC131063:MYJ131068 NHY131063:NIF131068 NRU131063:NSB131068 OBQ131063:OBX131068 OLM131063:OLT131068 OVI131063:OVP131068 PFE131063:PFL131068 PPA131063:PPH131068 PYW131063:PZD131068 QIS131063:QIZ131068 QSO131063:QSV131068 RCK131063:RCR131068 RMG131063:RMN131068 RWC131063:RWJ131068 SFY131063:SGF131068 SPU131063:SQB131068 SZQ131063:SZX131068 TJM131063:TJT131068 TTI131063:TTP131068 UDE131063:UDL131068 UNA131063:UNH131068 UWW131063:UXD131068 VGS131063:VGZ131068 VQO131063:VQV131068 WAK131063:WAR131068 WKG131063:WKN131068 WUC131063:WUJ131068 HQ196599:HX196604 RM196599:RT196604 ABI196599:ABP196604 ALE196599:ALL196604 AVA196599:AVH196604 BEW196599:BFD196604 BOS196599:BOZ196604 BYO196599:BYV196604 CIK196599:CIR196604 CSG196599:CSN196604 DCC196599:DCJ196604 DLY196599:DMF196604 DVU196599:DWB196604 EFQ196599:EFX196604 EPM196599:EPT196604 EZI196599:EZP196604 FJE196599:FJL196604 FTA196599:FTH196604 GCW196599:GDD196604 GMS196599:GMZ196604 GWO196599:GWV196604 HGK196599:HGR196604 HQG196599:HQN196604 IAC196599:IAJ196604 IJY196599:IKF196604 ITU196599:IUB196604 JDQ196599:JDX196604 JNM196599:JNT196604 JXI196599:JXP196604 KHE196599:KHL196604 KRA196599:KRH196604 LAW196599:LBD196604 LKS196599:LKZ196604 LUO196599:LUV196604 MEK196599:MER196604 MOG196599:MON196604 MYC196599:MYJ196604 NHY196599:NIF196604 NRU196599:NSB196604 OBQ196599:OBX196604 OLM196599:OLT196604 OVI196599:OVP196604 PFE196599:PFL196604 PPA196599:PPH196604 PYW196599:PZD196604 QIS196599:QIZ196604 QSO196599:QSV196604 RCK196599:RCR196604 RMG196599:RMN196604 RWC196599:RWJ196604 SFY196599:SGF196604 SPU196599:SQB196604 SZQ196599:SZX196604 TJM196599:TJT196604 TTI196599:TTP196604 UDE196599:UDL196604 UNA196599:UNH196604 UWW196599:UXD196604 VGS196599:VGZ196604 VQO196599:VQV196604 WAK196599:WAR196604 WKG196599:WKN196604 WUC196599:WUJ196604 HQ262135:HX262140 RM262135:RT262140 ABI262135:ABP262140 ALE262135:ALL262140 AVA262135:AVH262140 BEW262135:BFD262140 BOS262135:BOZ262140 BYO262135:BYV262140 CIK262135:CIR262140 CSG262135:CSN262140 DCC262135:DCJ262140 DLY262135:DMF262140 DVU262135:DWB262140 EFQ262135:EFX262140 EPM262135:EPT262140 EZI262135:EZP262140 FJE262135:FJL262140 FTA262135:FTH262140 GCW262135:GDD262140 GMS262135:GMZ262140 GWO262135:GWV262140 HGK262135:HGR262140 HQG262135:HQN262140 IAC262135:IAJ262140 IJY262135:IKF262140 ITU262135:IUB262140 JDQ262135:JDX262140 JNM262135:JNT262140 JXI262135:JXP262140 KHE262135:KHL262140 KRA262135:KRH262140 LAW262135:LBD262140 LKS262135:LKZ262140 LUO262135:LUV262140 MEK262135:MER262140 MOG262135:MON262140 MYC262135:MYJ262140 NHY262135:NIF262140 NRU262135:NSB262140 OBQ262135:OBX262140 OLM262135:OLT262140 OVI262135:OVP262140 PFE262135:PFL262140 PPA262135:PPH262140 PYW262135:PZD262140 QIS262135:QIZ262140 QSO262135:QSV262140 RCK262135:RCR262140 RMG262135:RMN262140 RWC262135:RWJ262140 SFY262135:SGF262140 SPU262135:SQB262140 SZQ262135:SZX262140 TJM262135:TJT262140 TTI262135:TTP262140 UDE262135:UDL262140 UNA262135:UNH262140 UWW262135:UXD262140 VGS262135:VGZ262140 VQO262135:VQV262140 WAK262135:WAR262140 WKG262135:WKN262140 WUC262135:WUJ262140 HQ327671:HX327676 RM327671:RT327676 ABI327671:ABP327676 ALE327671:ALL327676 AVA327671:AVH327676 BEW327671:BFD327676 BOS327671:BOZ327676 BYO327671:BYV327676 CIK327671:CIR327676 CSG327671:CSN327676 DCC327671:DCJ327676 DLY327671:DMF327676 DVU327671:DWB327676 EFQ327671:EFX327676 EPM327671:EPT327676 EZI327671:EZP327676 FJE327671:FJL327676 FTA327671:FTH327676 GCW327671:GDD327676 GMS327671:GMZ327676 GWO327671:GWV327676 HGK327671:HGR327676 HQG327671:HQN327676 IAC327671:IAJ327676 IJY327671:IKF327676 ITU327671:IUB327676 JDQ327671:JDX327676 JNM327671:JNT327676 JXI327671:JXP327676 KHE327671:KHL327676 KRA327671:KRH327676 LAW327671:LBD327676 LKS327671:LKZ327676 LUO327671:LUV327676 MEK327671:MER327676 MOG327671:MON327676 MYC327671:MYJ327676 NHY327671:NIF327676 NRU327671:NSB327676 OBQ327671:OBX327676 OLM327671:OLT327676 OVI327671:OVP327676 PFE327671:PFL327676 PPA327671:PPH327676 PYW327671:PZD327676 QIS327671:QIZ327676 QSO327671:QSV327676 RCK327671:RCR327676 RMG327671:RMN327676 RWC327671:RWJ327676 SFY327671:SGF327676 SPU327671:SQB327676 SZQ327671:SZX327676 TJM327671:TJT327676 TTI327671:TTP327676 UDE327671:UDL327676 UNA327671:UNH327676 UWW327671:UXD327676 VGS327671:VGZ327676 VQO327671:VQV327676 WAK327671:WAR327676 WKG327671:WKN327676 WUC327671:WUJ327676 HQ393207:HX393212 RM393207:RT393212 ABI393207:ABP393212 ALE393207:ALL393212 AVA393207:AVH393212 BEW393207:BFD393212 BOS393207:BOZ393212 BYO393207:BYV393212 CIK393207:CIR393212 CSG393207:CSN393212 DCC393207:DCJ393212 DLY393207:DMF393212 DVU393207:DWB393212 EFQ393207:EFX393212 EPM393207:EPT393212 EZI393207:EZP393212 FJE393207:FJL393212 FTA393207:FTH393212 GCW393207:GDD393212 GMS393207:GMZ393212 GWO393207:GWV393212 HGK393207:HGR393212 HQG393207:HQN393212 IAC393207:IAJ393212 IJY393207:IKF393212 ITU393207:IUB393212 JDQ393207:JDX393212 JNM393207:JNT393212 JXI393207:JXP393212 KHE393207:KHL393212 KRA393207:KRH393212 LAW393207:LBD393212 LKS393207:LKZ393212 LUO393207:LUV393212 MEK393207:MER393212 MOG393207:MON393212 MYC393207:MYJ393212 NHY393207:NIF393212 NRU393207:NSB393212 OBQ393207:OBX393212 OLM393207:OLT393212 OVI393207:OVP393212 PFE393207:PFL393212 PPA393207:PPH393212 PYW393207:PZD393212 QIS393207:QIZ393212 QSO393207:QSV393212 RCK393207:RCR393212 RMG393207:RMN393212 RWC393207:RWJ393212 SFY393207:SGF393212 SPU393207:SQB393212 SZQ393207:SZX393212 TJM393207:TJT393212 TTI393207:TTP393212 UDE393207:UDL393212 UNA393207:UNH393212 UWW393207:UXD393212 VGS393207:VGZ393212 VQO393207:VQV393212 WAK393207:WAR393212 WKG393207:WKN393212 WUC393207:WUJ393212 HQ458743:HX458748 RM458743:RT458748 ABI458743:ABP458748 ALE458743:ALL458748 AVA458743:AVH458748 BEW458743:BFD458748 BOS458743:BOZ458748 BYO458743:BYV458748 CIK458743:CIR458748 CSG458743:CSN458748 DCC458743:DCJ458748 DLY458743:DMF458748 DVU458743:DWB458748 EFQ458743:EFX458748 EPM458743:EPT458748 EZI458743:EZP458748 FJE458743:FJL458748 FTA458743:FTH458748 GCW458743:GDD458748 GMS458743:GMZ458748 GWO458743:GWV458748 HGK458743:HGR458748 HQG458743:HQN458748 IAC458743:IAJ458748 IJY458743:IKF458748 ITU458743:IUB458748 JDQ458743:JDX458748 JNM458743:JNT458748 JXI458743:JXP458748 KHE458743:KHL458748 KRA458743:KRH458748 LAW458743:LBD458748 LKS458743:LKZ458748 LUO458743:LUV458748 MEK458743:MER458748 MOG458743:MON458748 MYC458743:MYJ458748 NHY458743:NIF458748 NRU458743:NSB458748 OBQ458743:OBX458748 OLM458743:OLT458748 OVI458743:OVP458748 PFE458743:PFL458748 PPA458743:PPH458748 PYW458743:PZD458748 QIS458743:QIZ458748 QSO458743:QSV458748 RCK458743:RCR458748 RMG458743:RMN458748 RWC458743:RWJ458748 SFY458743:SGF458748 SPU458743:SQB458748 SZQ458743:SZX458748 TJM458743:TJT458748 TTI458743:TTP458748 UDE458743:UDL458748 UNA458743:UNH458748 UWW458743:UXD458748 VGS458743:VGZ458748 VQO458743:VQV458748 WAK458743:WAR458748 WKG458743:WKN458748 WUC458743:WUJ458748 HQ524279:HX524284 RM524279:RT524284 ABI524279:ABP524284 ALE524279:ALL524284 AVA524279:AVH524284 BEW524279:BFD524284 BOS524279:BOZ524284 BYO524279:BYV524284 CIK524279:CIR524284 CSG524279:CSN524284 DCC524279:DCJ524284 DLY524279:DMF524284 DVU524279:DWB524284 EFQ524279:EFX524284 EPM524279:EPT524284 EZI524279:EZP524284 FJE524279:FJL524284 FTA524279:FTH524284 GCW524279:GDD524284 GMS524279:GMZ524284 GWO524279:GWV524284 HGK524279:HGR524284 HQG524279:HQN524284 IAC524279:IAJ524284 IJY524279:IKF524284 ITU524279:IUB524284 JDQ524279:JDX524284 JNM524279:JNT524284 JXI524279:JXP524284 KHE524279:KHL524284 KRA524279:KRH524284 LAW524279:LBD524284 LKS524279:LKZ524284 LUO524279:LUV524284 MEK524279:MER524284 MOG524279:MON524284 MYC524279:MYJ524284 NHY524279:NIF524284 NRU524279:NSB524284 OBQ524279:OBX524284 OLM524279:OLT524284 OVI524279:OVP524284 PFE524279:PFL524284 PPA524279:PPH524284 PYW524279:PZD524284 QIS524279:QIZ524284 QSO524279:QSV524284 RCK524279:RCR524284 RMG524279:RMN524284 RWC524279:RWJ524284 SFY524279:SGF524284 SPU524279:SQB524284 SZQ524279:SZX524284 TJM524279:TJT524284 TTI524279:TTP524284 UDE524279:UDL524284 UNA524279:UNH524284 UWW524279:UXD524284 VGS524279:VGZ524284 VQO524279:VQV524284 WAK524279:WAR524284 WKG524279:WKN524284 WUC524279:WUJ524284 HQ589815:HX589820 RM589815:RT589820 ABI589815:ABP589820 ALE589815:ALL589820 AVA589815:AVH589820 BEW589815:BFD589820 BOS589815:BOZ589820 BYO589815:BYV589820 CIK589815:CIR589820 CSG589815:CSN589820 DCC589815:DCJ589820 DLY589815:DMF589820 DVU589815:DWB589820 EFQ589815:EFX589820 EPM589815:EPT589820 EZI589815:EZP589820 FJE589815:FJL589820 FTA589815:FTH589820 GCW589815:GDD589820 GMS589815:GMZ589820 GWO589815:GWV589820 HGK589815:HGR589820 HQG589815:HQN589820 IAC589815:IAJ589820 IJY589815:IKF589820 ITU589815:IUB589820 JDQ589815:JDX589820 JNM589815:JNT589820 JXI589815:JXP589820 KHE589815:KHL589820 KRA589815:KRH589820 LAW589815:LBD589820 LKS589815:LKZ589820 LUO589815:LUV589820 MEK589815:MER589820 MOG589815:MON589820 MYC589815:MYJ589820 NHY589815:NIF589820 NRU589815:NSB589820 OBQ589815:OBX589820 OLM589815:OLT589820 OVI589815:OVP589820 PFE589815:PFL589820 PPA589815:PPH589820 PYW589815:PZD589820 QIS589815:QIZ589820 QSO589815:QSV589820 RCK589815:RCR589820 RMG589815:RMN589820 RWC589815:RWJ589820 SFY589815:SGF589820 SPU589815:SQB589820 SZQ589815:SZX589820 TJM589815:TJT589820 TTI589815:TTP589820 UDE589815:UDL589820 UNA589815:UNH589820 UWW589815:UXD589820 VGS589815:VGZ589820 VQO589815:VQV589820 WAK589815:WAR589820 WKG589815:WKN589820 WUC589815:WUJ589820 HQ655351:HX655356 RM655351:RT655356 ABI655351:ABP655356 ALE655351:ALL655356 AVA655351:AVH655356 BEW655351:BFD655356 BOS655351:BOZ655356 BYO655351:BYV655356 CIK655351:CIR655356 CSG655351:CSN655356 DCC655351:DCJ655356 DLY655351:DMF655356 DVU655351:DWB655356 EFQ655351:EFX655356 EPM655351:EPT655356 EZI655351:EZP655356 FJE655351:FJL655356 FTA655351:FTH655356 GCW655351:GDD655356 GMS655351:GMZ655356 GWO655351:GWV655356 HGK655351:HGR655356 HQG655351:HQN655356 IAC655351:IAJ655356 IJY655351:IKF655356 ITU655351:IUB655356 JDQ655351:JDX655356 JNM655351:JNT655356 JXI655351:JXP655356 KHE655351:KHL655356 KRA655351:KRH655356 LAW655351:LBD655356 LKS655351:LKZ655356 LUO655351:LUV655356 MEK655351:MER655356 MOG655351:MON655356 MYC655351:MYJ655356 NHY655351:NIF655356 NRU655351:NSB655356 OBQ655351:OBX655356 OLM655351:OLT655356 OVI655351:OVP655356 PFE655351:PFL655356 PPA655351:PPH655356 PYW655351:PZD655356 QIS655351:QIZ655356 QSO655351:QSV655356 RCK655351:RCR655356 RMG655351:RMN655356 RWC655351:RWJ655356 SFY655351:SGF655356 SPU655351:SQB655356 SZQ655351:SZX655356 TJM655351:TJT655356 TTI655351:TTP655356 UDE655351:UDL655356 UNA655351:UNH655356 UWW655351:UXD655356 VGS655351:VGZ655356 VQO655351:VQV655356 WAK655351:WAR655356 WKG655351:WKN655356 WUC655351:WUJ655356 HQ720887:HX720892 RM720887:RT720892 ABI720887:ABP720892 ALE720887:ALL720892 AVA720887:AVH720892 BEW720887:BFD720892 BOS720887:BOZ720892 BYO720887:BYV720892 CIK720887:CIR720892 CSG720887:CSN720892 DCC720887:DCJ720892 DLY720887:DMF720892 DVU720887:DWB720892 EFQ720887:EFX720892 EPM720887:EPT720892 EZI720887:EZP720892 FJE720887:FJL720892 FTA720887:FTH720892 GCW720887:GDD720892 GMS720887:GMZ720892 GWO720887:GWV720892 HGK720887:HGR720892 HQG720887:HQN720892 IAC720887:IAJ720892 IJY720887:IKF720892 ITU720887:IUB720892 JDQ720887:JDX720892 JNM720887:JNT720892 JXI720887:JXP720892 KHE720887:KHL720892 KRA720887:KRH720892 LAW720887:LBD720892 LKS720887:LKZ720892 LUO720887:LUV720892 MEK720887:MER720892 MOG720887:MON720892 MYC720887:MYJ720892 NHY720887:NIF720892 NRU720887:NSB720892 OBQ720887:OBX720892 OLM720887:OLT720892 OVI720887:OVP720892 PFE720887:PFL720892 PPA720887:PPH720892 PYW720887:PZD720892 QIS720887:QIZ720892 QSO720887:QSV720892 RCK720887:RCR720892 RMG720887:RMN720892 RWC720887:RWJ720892 SFY720887:SGF720892 SPU720887:SQB720892 SZQ720887:SZX720892 TJM720887:TJT720892 TTI720887:TTP720892 UDE720887:UDL720892 UNA720887:UNH720892 UWW720887:UXD720892 VGS720887:VGZ720892 VQO720887:VQV720892 WAK720887:WAR720892 WKG720887:WKN720892 WUC720887:WUJ720892 HQ786423:HX786428 RM786423:RT786428 ABI786423:ABP786428 ALE786423:ALL786428 AVA786423:AVH786428 BEW786423:BFD786428 BOS786423:BOZ786428 BYO786423:BYV786428 CIK786423:CIR786428 CSG786423:CSN786428 DCC786423:DCJ786428 DLY786423:DMF786428 DVU786423:DWB786428 EFQ786423:EFX786428 EPM786423:EPT786428 EZI786423:EZP786428 FJE786423:FJL786428 FTA786423:FTH786428 GCW786423:GDD786428 GMS786423:GMZ786428 GWO786423:GWV786428 HGK786423:HGR786428 HQG786423:HQN786428 IAC786423:IAJ786428 IJY786423:IKF786428 ITU786423:IUB786428 JDQ786423:JDX786428 JNM786423:JNT786428 JXI786423:JXP786428 KHE786423:KHL786428 KRA786423:KRH786428 LAW786423:LBD786428 LKS786423:LKZ786428 LUO786423:LUV786428 MEK786423:MER786428 MOG786423:MON786428 MYC786423:MYJ786428 NHY786423:NIF786428 NRU786423:NSB786428 OBQ786423:OBX786428 OLM786423:OLT786428 OVI786423:OVP786428 PFE786423:PFL786428 PPA786423:PPH786428 PYW786423:PZD786428 QIS786423:QIZ786428 QSO786423:QSV786428 RCK786423:RCR786428 RMG786423:RMN786428 RWC786423:RWJ786428 SFY786423:SGF786428 SPU786423:SQB786428 SZQ786423:SZX786428 TJM786423:TJT786428 TTI786423:TTP786428 UDE786423:UDL786428 UNA786423:UNH786428 UWW786423:UXD786428 VGS786423:VGZ786428 VQO786423:VQV786428 WAK786423:WAR786428 WKG786423:WKN786428 WUC786423:WUJ786428 HQ851959:HX851964 RM851959:RT851964 ABI851959:ABP851964 ALE851959:ALL851964 AVA851959:AVH851964 BEW851959:BFD851964 BOS851959:BOZ851964 BYO851959:BYV851964 CIK851959:CIR851964 CSG851959:CSN851964 DCC851959:DCJ851964 DLY851959:DMF851964 DVU851959:DWB851964 EFQ851959:EFX851964 EPM851959:EPT851964 EZI851959:EZP851964 FJE851959:FJL851964 FTA851959:FTH851964 GCW851959:GDD851964 GMS851959:GMZ851964 GWO851959:GWV851964 HGK851959:HGR851964 HQG851959:HQN851964 IAC851959:IAJ851964 IJY851959:IKF851964 ITU851959:IUB851964 JDQ851959:JDX851964 JNM851959:JNT851964 JXI851959:JXP851964 KHE851959:KHL851964 KRA851959:KRH851964 LAW851959:LBD851964 LKS851959:LKZ851964 LUO851959:LUV851964 MEK851959:MER851964 MOG851959:MON851964 MYC851959:MYJ851964 NHY851959:NIF851964 NRU851959:NSB851964 OBQ851959:OBX851964 OLM851959:OLT851964 OVI851959:OVP851964 PFE851959:PFL851964 PPA851959:PPH851964 PYW851959:PZD851964 QIS851959:QIZ851964 QSO851959:QSV851964 RCK851959:RCR851964 RMG851959:RMN851964 RWC851959:RWJ851964 SFY851959:SGF851964 SPU851959:SQB851964 SZQ851959:SZX851964 TJM851959:TJT851964 TTI851959:TTP851964 UDE851959:UDL851964 UNA851959:UNH851964 UWW851959:UXD851964 VGS851959:VGZ851964 VQO851959:VQV851964 WAK851959:WAR851964 WKG851959:WKN851964 WUC851959:WUJ851964 HQ917495:HX917500 RM917495:RT917500 ABI917495:ABP917500 ALE917495:ALL917500 AVA917495:AVH917500 BEW917495:BFD917500 BOS917495:BOZ917500 BYO917495:BYV917500 CIK917495:CIR917500 CSG917495:CSN917500 DCC917495:DCJ917500 DLY917495:DMF917500 DVU917495:DWB917500 EFQ917495:EFX917500 EPM917495:EPT917500 EZI917495:EZP917500 FJE917495:FJL917500 FTA917495:FTH917500 GCW917495:GDD917500 GMS917495:GMZ917500 GWO917495:GWV917500 HGK917495:HGR917500 HQG917495:HQN917500 IAC917495:IAJ917500 IJY917495:IKF917500 ITU917495:IUB917500 JDQ917495:JDX917500 JNM917495:JNT917500 JXI917495:JXP917500 KHE917495:KHL917500 KRA917495:KRH917500 LAW917495:LBD917500 LKS917495:LKZ917500 LUO917495:LUV917500 MEK917495:MER917500 MOG917495:MON917500 MYC917495:MYJ917500 NHY917495:NIF917500 NRU917495:NSB917500 OBQ917495:OBX917500 OLM917495:OLT917500 OVI917495:OVP917500 PFE917495:PFL917500 PPA917495:PPH917500 PYW917495:PZD917500 QIS917495:QIZ917500 QSO917495:QSV917500 RCK917495:RCR917500 RMG917495:RMN917500 RWC917495:RWJ917500 SFY917495:SGF917500 SPU917495:SQB917500 SZQ917495:SZX917500 TJM917495:TJT917500 TTI917495:TTP917500 UDE917495:UDL917500 UNA917495:UNH917500 UWW917495:UXD917500 VGS917495:VGZ917500 VQO917495:VQV917500 WAK917495:WAR917500 WKG917495:WKN917500 WUC917495:WUJ917500" xr:uid="{38E70801-6EC0-4CA3-9454-EC0ABF5F9215}">
       <formula1>"サーバ,クライアント"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V65538:Y65541 IG65538:IJ65541 SC65538:SF65541 ABY65538:ACB65541 ALU65538:ALX65541 AVQ65538:AVT65541 BFM65538:BFP65541 BPI65538:BPL65541 BZE65538:BZH65541 CJA65538:CJD65541 CSW65538:CSZ65541 DCS65538:DCV65541 DMO65538:DMR65541 DWK65538:DWN65541 EGG65538:EGJ65541 EQC65538:EQF65541 EZY65538:FAB65541 FJU65538:FJX65541 FTQ65538:FTT65541 GDM65538:GDP65541 GNI65538:GNL65541 GXE65538:GXH65541 HHA65538:HHD65541 HQW65538:HQZ65541 IAS65538:IAV65541 IKO65538:IKR65541 IUK65538:IUN65541 JEG65538:JEJ65541 JOC65538:JOF65541 JXY65538:JYB65541 KHU65538:KHX65541 KRQ65538:KRT65541 LBM65538:LBP65541 LLI65538:LLL65541 LVE65538:LVH65541 MFA65538:MFD65541 MOW65538:MOZ65541 MYS65538:MYV65541 NIO65538:NIR65541 NSK65538:NSN65541 OCG65538:OCJ65541 OMC65538:OMF65541 OVY65538:OWB65541 PFU65538:PFX65541 PPQ65538:PPT65541 PZM65538:PZP65541 QJI65538:QJL65541 QTE65538:QTH65541 RDA65538:RDD65541 RMW65538:RMZ65541 RWS65538:RWV65541 SGO65538:SGR65541 SQK65538:SQN65541 TAG65538:TAJ65541 TKC65538:TKF65541 TTY65538:TUB65541 UDU65538:UDX65541 UNQ65538:UNT65541 UXM65538:UXP65541 VHI65538:VHL65541 VRE65538:VRH65541 WBA65538:WBD65541 WKW65538:WKZ65541 WUS65538:WUV65541 V131074:Y131077 IG131074:IJ131077 SC131074:SF131077 ABY131074:ACB131077 ALU131074:ALX131077 AVQ131074:AVT131077 BFM131074:BFP131077 BPI131074:BPL131077 BZE131074:BZH131077 CJA131074:CJD131077 CSW131074:CSZ131077 DCS131074:DCV131077 DMO131074:DMR131077 DWK131074:DWN131077 EGG131074:EGJ131077 EQC131074:EQF131077 EZY131074:FAB131077 FJU131074:FJX131077 FTQ131074:FTT131077 GDM131074:GDP131077 GNI131074:GNL131077 GXE131074:GXH131077 HHA131074:HHD131077 HQW131074:HQZ131077 IAS131074:IAV131077 IKO131074:IKR131077 IUK131074:IUN131077 JEG131074:JEJ131077 JOC131074:JOF131077 JXY131074:JYB131077 KHU131074:KHX131077 KRQ131074:KRT131077 LBM131074:LBP131077 LLI131074:LLL131077 LVE131074:LVH131077 MFA131074:MFD131077 MOW131074:MOZ131077 MYS131074:MYV131077 NIO131074:NIR131077 NSK131074:NSN131077 OCG131074:OCJ131077 OMC131074:OMF131077 OVY131074:OWB131077 PFU131074:PFX131077 PPQ131074:PPT131077 PZM131074:PZP131077 QJI131074:QJL131077 QTE131074:QTH131077 RDA131074:RDD131077 RMW131074:RMZ131077 RWS131074:RWV131077 SGO131074:SGR131077 SQK131074:SQN131077 TAG131074:TAJ131077 TKC131074:TKF131077 TTY131074:TUB131077 UDU131074:UDX131077 UNQ131074:UNT131077 UXM131074:UXP131077 VHI131074:VHL131077 VRE131074:VRH131077 WBA131074:WBD131077 WKW131074:WKZ131077 WUS131074:WUV131077 V196610:Y196613 IG196610:IJ196613 SC196610:SF196613 ABY196610:ACB196613 ALU196610:ALX196613 AVQ196610:AVT196613 BFM196610:BFP196613 BPI196610:BPL196613 BZE196610:BZH196613 CJA196610:CJD196613 CSW196610:CSZ196613 DCS196610:DCV196613 DMO196610:DMR196613 DWK196610:DWN196613 EGG196610:EGJ196613 EQC196610:EQF196613 EZY196610:FAB196613 FJU196610:FJX196613 FTQ196610:FTT196613 GDM196610:GDP196613 GNI196610:GNL196613 GXE196610:GXH196613 HHA196610:HHD196613 HQW196610:HQZ196613 IAS196610:IAV196613 IKO196610:IKR196613 IUK196610:IUN196613 JEG196610:JEJ196613 JOC196610:JOF196613 JXY196610:JYB196613 KHU196610:KHX196613 KRQ196610:KRT196613 LBM196610:LBP196613 LLI196610:LLL196613 LVE196610:LVH196613 MFA196610:MFD196613 MOW196610:MOZ196613 MYS196610:MYV196613 NIO196610:NIR196613 NSK196610:NSN196613 OCG196610:OCJ196613 OMC196610:OMF196613 OVY196610:OWB196613 PFU196610:PFX196613 PPQ196610:PPT196613 PZM196610:PZP196613 QJI196610:QJL196613 QTE196610:QTH196613 RDA196610:RDD196613 RMW196610:RMZ196613 RWS196610:RWV196613 SGO196610:SGR196613 SQK196610:SQN196613 TAG196610:TAJ196613 TKC196610:TKF196613 TTY196610:TUB196613 UDU196610:UDX196613 UNQ196610:UNT196613 UXM196610:UXP196613 VHI196610:VHL196613 VRE196610:VRH196613 WBA196610:WBD196613 WKW196610:WKZ196613 WUS196610:WUV196613 V262146:Y262149 IG262146:IJ262149 SC262146:SF262149 ABY262146:ACB262149 ALU262146:ALX262149 AVQ262146:AVT262149 BFM262146:BFP262149 BPI262146:BPL262149 BZE262146:BZH262149 CJA262146:CJD262149 CSW262146:CSZ262149 DCS262146:DCV262149 DMO262146:DMR262149 DWK262146:DWN262149 EGG262146:EGJ262149 EQC262146:EQF262149 EZY262146:FAB262149 FJU262146:FJX262149 FTQ262146:FTT262149 GDM262146:GDP262149 GNI262146:GNL262149 GXE262146:GXH262149 HHA262146:HHD262149 HQW262146:HQZ262149 IAS262146:IAV262149 IKO262146:IKR262149 IUK262146:IUN262149 JEG262146:JEJ262149 JOC262146:JOF262149 JXY262146:JYB262149 KHU262146:KHX262149 KRQ262146:KRT262149 LBM262146:LBP262149 LLI262146:LLL262149 LVE262146:LVH262149 MFA262146:MFD262149 MOW262146:MOZ262149 MYS262146:MYV262149 NIO262146:NIR262149 NSK262146:NSN262149 OCG262146:OCJ262149 OMC262146:OMF262149 OVY262146:OWB262149 PFU262146:PFX262149 PPQ262146:PPT262149 PZM262146:PZP262149 QJI262146:QJL262149 QTE262146:QTH262149 RDA262146:RDD262149 RMW262146:RMZ262149 RWS262146:RWV262149 SGO262146:SGR262149 SQK262146:SQN262149 TAG262146:TAJ262149 TKC262146:TKF262149 TTY262146:TUB262149 UDU262146:UDX262149 UNQ262146:UNT262149 UXM262146:UXP262149 VHI262146:VHL262149 VRE262146:VRH262149 WBA262146:WBD262149 WKW262146:WKZ262149 WUS262146:WUV262149 V327682:Y327685 IG327682:IJ327685 SC327682:SF327685 ABY327682:ACB327685 ALU327682:ALX327685 AVQ327682:AVT327685 BFM327682:BFP327685 BPI327682:BPL327685 BZE327682:BZH327685 CJA327682:CJD327685 CSW327682:CSZ327685 DCS327682:DCV327685 DMO327682:DMR327685 DWK327682:DWN327685 EGG327682:EGJ327685 EQC327682:EQF327685 EZY327682:FAB327685 FJU327682:FJX327685 FTQ327682:FTT327685 GDM327682:GDP327685 GNI327682:GNL327685 GXE327682:GXH327685 HHA327682:HHD327685 HQW327682:HQZ327685 IAS327682:IAV327685 IKO327682:IKR327685 IUK327682:IUN327685 JEG327682:JEJ327685 JOC327682:JOF327685 JXY327682:JYB327685 KHU327682:KHX327685 KRQ327682:KRT327685 LBM327682:LBP327685 LLI327682:LLL327685 LVE327682:LVH327685 MFA327682:MFD327685 MOW327682:MOZ327685 MYS327682:MYV327685 NIO327682:NIR327685 NSK327682:NSN327685 OCG327682:OCJ327685 OMC327682:OMF327685 OVY327682:OWB327685 PFU327682:PFX327685 PPQ327682:PPT327685 PZM327682:PZP327685 QJI327682:QJL327685 QTE327682:QTH327685 RDA327682:RDD327685 RMW327682:RMZ327685 RWS327682:RWV327685 SGO327682:SGR327685 SQK327682:SQN327685 TAG327682:TAJ327685 TKC327682:TKF327685 TTY327682:TUB327685 UDU327682:UDX327685 UNQ327682:UNT327685 UXM327682:UXP327685 VHI327682:VHL327685 VRE327682:VRH327685 WBA327682:WBD327685 WKW327682:WKZ327685 WUS327682:WUV327685 V393218:Y393221 IG393218:IJ393221 SC393218:SF393221 ABY393218:ACB393221 ALU393218:ALX393221 AVQ393218:AVT393221 BFM393218:BFP393221 BPI393218:BPL393221 BZE393218:BZH393221 CJA393218:CJD393221 CSW393218:CSZ393221 DCS393218:DCV393221 DMO393218:DMR393221 DWK393218:DWN393221 EGG393218:EGJ393221 EQC393218:EQF393221 EZY393218:FAB393221 FJU393218:FJX393221 FTQ393218:FTT393221 GDM393218:GDP393221 GNI393218:GNL393221 GXE393218:GXH393221 HHA393218:HHD393221 HQW393218:HQZ393221 IAS393218:IAV393221 IKO393218:IKR393221 IUK393218:IUN393221 JEG393218:JEJ393221 JOC393218:JOF393221 JXY393218:JYB393221 KHU393218:KHX393221 KRQ393218:KRT393221 LBM393218:LBP393221 LLI393218:LLL393221 LVE393218:LVH393221 MFA393218:MFD393221 MOW393218:MOZ393221 MYS393218:MYV393221 NIO393218:NIR393221 NSK393218:NSN393221 OCG393218:OCJ393221 OMC393218:OMF393221 OVY393218:OWB393221 PFU393218:PFX393221 PPQ393218:PPT393221 PZM393218:PZP393221 QJI393218:QJL393221 QTE393218:QTH393221 RDA393218:RDD393221 RMW393218:RMZ393221 RWS393218:RWV393221 SGO393218:SGR393221 SQK393218:SQN393221 TAG393218:TAJ393221 TKC393218:TKF393221 TTY393218:TUB393221 UDU393218:UDX393221 UNQ393218:UNT393221 UXM393218:UXP393221 VHI393218:VHL393221 VRE393218:VRH393221 WBA393218:WBD393221 WKW393218:WKZ393221 WUS393218:WUV393221 V458754:Y458757 IG458754:IJ458757 SC458754:SF458757 ABY458754:ACB458757 ALU458754:ALX458757 AVQ458754:AVT458757 BFM458754:BFP458757 BPI458754:BPL458757 BZE458754:BZH458757 CJA458754:CJD458757 CSW458754:CSZ458757 DCS458754:DCV458757 DMO458754:DMR458757 DWK458754:DWN458757 EGG458754:EGJ458757 EQC458754:EQF458757 EZY458754:FAB458757 FJU458754:FJX458757 FTQ458754:FTT458757 GDM458754:GDP458757 GNI458754:GNL458757 GXE458754:GXH458757 HHA458754:HHD458757 HQW458754:HQZ458757 IAS458754:IAV458757 IKO458754:IKR458757 IUK458754:IUN458757 JEG458754:JEJ458757 JOC458754:JOF458757 JXY458754:JYB458757 KHU458754:KHX458757 KRQ458754:KRT458757 LBM458754:LBP458757 LLI458754:LLL458757 LVE458754:LVH458757 MFA458754:MFD458757 MOW458754:MOZ458757 MYS458754:MYV458757 NIO458754:NIR458757 NSK458754:NSN458757 OCG458754:OCJ458757 OMC458754:OMF458757 OVY458754:OWB458757 PFU458754:PFX458757 PPQ458754:PPT458757 PZM458754:PZP458757 QJI458754:QJL458757 QTE458754:QTH458757 RDA458754:RDD458757 RMW458754:RMZ458757 RWS458754:RWV458757 SGO458754:SGR458757 SQK458754:SQN458757 TAG458754:TAJ458757 TKC458754:TKF458757 TTY458754:TUB458757 UDU458754:UDX458757 UNQ458754:UNT458757 UXM458754:UXP458757 VHI458754:VHL458757 VRE458754:VRH458757 WBA458754:WBD458757 WKW458754:WKZ458757 WUS458754:WUV458757 V524290:Y524293 IG524290:IJ524293 SC524290:SF524293 ABY524290:ACB524293 ALU524290:ALX524293 AVQ524290:AVT524293 BFM524290:BFP524293 BPI524290:BPL524293 BZE524290:BZH524293 CJA524290:CJD524293 CSW524290:CSZ524293 DCS524290:DCV524293 DMO524290:DMR524293 DWK524290:DWN524293 EGG524290:EGJ524293 EQC524290:EQF524293 EZY524290:FAB524293 FJU524290:FJX524293 FTQ524290:FTT524293 GDM524290:GDP524293 GNI524290:GNL524293 GXE524290:GXH524293 HHA524290:HHD524293 HQW524290:HQZ524293 IAS524290:IAV524293 IKO524290:IKR524293 IUK524290:IUN524293 JEG524290:JEJ524293 JOC524290:JOF524293 JXY524290:JYB524293 KHU524290:KHX524293 KRQ524290:KRT524293 LBM524290:LBP524293 LLI524290:LLL524293 LVE524290:LVH524293 MFA524290:MFD524293 MOW524290:MOZ524293 MYS524290:MYV524293 NIO524290:NIR524293 NSK524290:NSN524293 OCG524290:OCJ524293 OMC524290:OMF524293 OVY524290:OWB524293 PFU524290:PFX524293 PPQ524290:PPT524293 PZM524290:PZP524293 QJI524290:QJL524293 QTE524290:QTH524293 RDA524290:RDD524293 RMW524290:RMZ524293 RWS524290:RWV524293 SGO524290:SGR524293 SQK524290:SQN524293 TAG524290:TAJ524293 TKC524290:TKF524293 TTY524290:TUB524293 UDU524290:UDX524293 UNQ524290:UNT524293 UXM524290:UXP524293 VHI524290:VHL524293 VRE524290:VRH524293 WBA524290:WBD524293 WKW524290:WKZ524293 WUS524290:WUV524293 V589826:Y589829 IG589826:IJ589829 SC589826:SF589829 ABY589826:ACB589829 ALU589826:ALX589829 AVQ589826:AVT589829 BFM589826:BFP589829 BPI589826:BPL589829 BZE589826:BZH589829 CJA589826:CJD589829 CSW589826:CSZ589829 DCS589826:DCV589829 DMO589826:DMR589829 DWK589826:DWN589829 EGG589826:EGJ589829 EQC589826:EQF589829 EZY589826:FAB589829 FJU589826:FJX589829 FTQ589826:FTT589829 GDM589826:GDP589829 GNI589826:GNL589829 GXE589826:GXH589829 HHA589826:HHD589829 HQW589826:HQZ589829 IAS589826:IAV589829 IKO589826:IKR589829 IUK589826:IUN589829 JEG589826:JEJ589829 JOC589826:JOF589829 JXY589826:JYB589829 KHU589826:KHX589829 KRQ589826:KRT589829 LBM589826:LBP589829 LLI589826:LLL589829 LVE589826:LVH589829 MFA589826:MFD589829 MOW589826:MOZ589829 MYS589826:MYV589829 NIO589826:NIR589829 NSK589826:NSN589829 OCG589826:OCJ589829 OMC589826:OMF589829 OVY589826:OWB589829 PFU589826:PFX589829 PPQ589826:PPT589829 PZM589826:PZP589829 QJI589826:QJL589829 QTE589826:QTH589829 RDA589826:RDD589829 RMW589826:RMZ589829 RWS589826:RWV589829 SGO589826:SGR589829 SQK589826:SQN589829 TAG589826:TAJ589829 TKC589826:TKF589829 TTY589826:TUB589829 UDU589826:UDX589829 UNQ589826:UNT589829 UXM589826:UXP589829 VHI589826:VHL589829 VRE589826:VRH589829 WBA589826:WBD589829 WKW589826:WKZ589829 WUS589826:WUV589829 V655362:Y655365 IG655362:IJ655365 SC655362:SF655365 ABY655362:ACB655365 ALU655362:ALX655365 AVQ655362:AVT655365 BFM655362:BFP655365 BPI655362:BPL655365 BZE655362:BZH655365 CJA655362:CJD655365 CSW655362:CSZ655365 DCS655362:DCV655365 DMO655362:DMR655365 DWK655362:DWN655365 EGG655362:EGJ655365 EQC655362:EQF655365 EZY655362:FAB655365 FJU655362:FJX655365 FTQ655362:FTT655365 GDM655362:GDP655365 GNI655362:GNL655365 GXE655362:GXH655365 HHA655362:HHD655365 HQW655362:HQZ655365 IAS655362:IAV655365 IKO655362:IKR655365 IUK655362:IUN655365 JEG655362:JEJ655365 JOC655362:JOF655365 JXY655362:JYB655365 KHU655362:KHX655365 KRQ655362:KRT655365 LBM655362:LBP655365 LLI655362:LLL655365 LVE655362:LVH655365 MFA655362:MFD655365 MOW655362:MOZ655365 MYS655362:MYV655365 NIO655362:NIR655365 NSK655362:NSN655365 OCG655362:OCJ655365 OMC655362:OMF655365 OVY655362:OWB655365 PFU655362:PFX655365 PPQ655362:PPT655365 PZM655362:PZP655365 QJI655362:QJL655365 QTE655362:QTH655365 RDA655362:RDD655365 RMW655362:RMZ655365 RWS655362:RWV655365 SGO655362:SGR655365 SQK655362:SQN655365 TAG655362:TAJ655365 TKC655362:TKF655365 TTY655362:TUB655365 UDU655362:UDX655365 UNQ655362:UNT655365 UXM655362:UXP655365 VHI655362:VHL655365 VRE655362:VRH655365 WBA655362:WBD655365 WKW655362:WKZ655365 WUS655362:WUV655365 V720898:Y720901 IG720898:IJ720901 SC720898:SF720901 ABY720898:ACB720901 ALU720898:ALX720901 AVQ720898:AVT720901 BFM720898:BFP720901 BPI720898:BPL720901 BZE720898:BZH720901 CJA720898:CJD720901 CSW720898:CSZ720901 DCS720898:DCV720901 DMO720898:DMR720901 DWK720898:DWN720901 EGG720898:EGJ720901 EQC720898:EQF720901 EZY720898:FAB720901 FJU720898:FJX720901 FTQ720898:FTT720901 GDM720898:GDP720901 GNI720898:GNL720901 GXE720898:GXH720901 HHA720898:HHD720901 HQW720898:HQZ720901 IAS720898:IAV720901 IKO720898:IKR720901 IUK720898:IUN720901 JEG720898:JEJ720901 JOC720898:JOF720901 JXY720898:JYB720901 KHU720898:KHX720901 KRQ720898:KRT720901 LBM720898:LBP720901 LLI720898:LLL720901 LVE720898:LVH720901 MFA720898:MFD720901 MOW720898:MOZ720901 MYS720898:MYV720901 NIO720898:NIR720901 NSK720898:NSN720901 OCG720898:OCJ720901 OMC720898:OMF720901 OVY720898:OWB720901 PFU720898:PFX720901 PPQ720898:PPT720901 PZM720898:PZP720901 QJI720898:QJL720901 QTE720898:QTH720901 RDA720898:RDD720901 RMW720898:RMZ720901 RWS720898:RWV720901 SGO720898:SGR720901 SQK720898:SQN720901 TAG720898:TAJ720901 TKC720898:TKF720901 TTY720898:TUB720901 UDU720898:UDX720901 UNQ720898:UNT720901 UXM720898:UXP720901 VHI720898:VHL720901 VRE720898:VRH720901 WBA720898:WBD720901 WKW720898:WKZ720901 WUS720898:WUV720901 V786434:Y786437 IG786434:IJ786437 SC786434:SF786437 ABY786434:ACB786437 ALU786434:ALX786437 AVQ786434:AVT786437 BFM786434:BFP786437 BPI786434:BPL786437 BZE786434:BZH786437 CJA786434:CJD786437 CSW786434:CSZ786437 DCS786434:DCV786437 DMO786434:DMR786437 DWK786434:DWN786437 EGG786434:EGJ786437 EQC786434:EQF786437 EZY786434:FAB786437 FJU786434:FJX786437 FTQ786434:FTT786437 GDM786434:GDP786437 GNI786434:GNL786437 GXE786434:GXH786437 HHA786434:HHD786437 HQW786434:HQZ786437 IAS786434:IAV786437 IKO786434:IKR786437 IUK786434:IUN786437 JEG786434:JEJ786437 JOC786434:JOF786437 JXY786434:JYB786437 KHU786434:KHX786437 KRQ786434:KRT786437 LBM786434:LBP786437 LLI786434:LLL786437 LVE786434:LVH786437 MFA786434:MFD786437 MOW786434:MOZ786437 MYS786434:MYV786437 NIO786434:NIR786437 NSK786434:NSN786437 OCG786434:OCJ786437 OMC786434:OMF786437 OVY786434:OWB786437 PFU786434:PFX786437 PPQ786434:PPT786437 PZM786434:PZP786437 QJI786434:QJL786437 QTE786434:QTH786437 RDA786434:RDD786437 RMW786434:RMZ786437 RWS786434:RWV786437 SGO786434:SGR786437 SQK786434:SQN786437 TAG786434:TAJ786437 TKC786434:TKF786437 TTY786434:TUB786437 UDU786434:UDX786437 UNQ786434:UNT786437 UXM786434:UXP786437 VHI786434:VHL786437 VRE786434:VRH786437 WBA786434:WBD786437 WKW786434:WKZ786437 WUS786434:WUV786437 V851970:Y851973 IG851970:IJ851973 SC851970:SF851973 ABY851970:ACB851973 ALU851970:ALX851973 AVQ851970:AVT851973 BFM851970:BFP851973 BPI851970:BPL851973 BZE851970:BZH851973 CJA851970:CJD851973 CSW851970:CSZ851973 DCS851970:DCV851973 DMO851970:DMR851973 DWK851970:DWN851973 EGG851970:EGJ851973 EQC851970:EQF851973 EZY851970:FAB851973 FJU851970:FJX851973 FTQ851970:FTT851973 GDM851970:GDP851973 GNI851970:GNL851973 GXE851970:GXH851973 HHA851970:HHD851973 HQW851970:HQZ851973 IAS851970:IAV851973 IKO851970:IKR851973 IUK851970:IUN851973 JEG851970:JEJ851973 JOC851970:JOF851973 JXY851970:JYB851973 KHU851970:KHX851973 KRQ851970:KRT851973 LBM851970:LBP851973 LLI851970:LLL851973 LVE851970:LVH851973 MFA851970:MFD851973 MOW851970:MOZ851973 MYS851970:MYV851973 NIO851970:NIR851973 NSK851970:NSN851973 OCG851970:OCJ851973 OMC851970:OMF851973 OVY851970:OWB851973 PFU851970:PFX851973 PPQ851970:PPT851973 PZM851970:PZP851973 QJI851970:QJL851973 QTE851970:QTH851973 RDA851970:RDD851973 RMW851970:RMZ851973 RWS851970:RWV851973 SGO851970:SGR851973 SQK851970:SQN851973 TAG851970:TAJ851973 TKC851970:TKF851973 TTY851970:TUB851973 UDU851970:UDX851973 UNQ851970:UNT851973 UXM851970:UXP851973 VHI851970:VHL851973 VRE851970:VRH851973 WBA851970:WBD851973 WKW851970:WKZ851973 WUS851970:WUV851973 V917506:Y917509 IG917506:IJ917509 SC917506:SF917509 ABY917506:ACB917509 ALU917506:ALX917509 AVQ917506:AVT917509 BFM917506:BFP917509 BPI917506:BPL917509 BZE917506:BZH917509 CJA917506:CJD917509 CSW917506:CSZ917509 DCS917506:DCV917509 DMO917506:DMR917509 DWK917506:DWN917509 EGG917506:EGJ917509 EQC917506:EQF917509 EZY917506:FAB917509 FJU917506:FJX917509 FTQ917506:FTT917509 GDM917506:GDP917509 GNI917506:GNL917509 GXE917506:GXH917509 HHA917506:HHD917509 HQW917506:HQZ917509 IAS917506:IAV917509 IKO917506:IKR917509 IUK917506:IUN917509 JEG917506:JEJ917509 JOC917506:JOF917509 JXY917506:JYB917509 KHU917506:KHX917509 KRQ917506:KRT917509 LBM917506:LBP917509 LLI917506:LLL917509 LVE917506:LVH917509 MFA917506:MFD917509 MOW917506:MOZ917509 MYS917506:MYV917509 NIO917506:NIR917509 NSK917506:NSN917509 OCG917506:OCJ917509 OMC917506:OMF917509 OVY917506:OWB917509 PFU917506:PFX917509 PPQ917506:PPT917509 PZM917506:PZP917509 QJI917506:QJL917509 QTE917506:QTH917509 RDA917506:RDD917509 RMW917506:RMZ917509 RWS917506:RWV917509 SGO917506:SGR917509 SQK917506:SQN917509 TAG917506:TAJ917509 TKC917506:TKF917509 TTY917506:TUB917509 UDU917506:UDX917509 UNQ917506:UNT917509 UXM917506:UXP917509 VHI917506:VHL917509 VRE917506:VRH917509 WBA917506:WBD917509 WKW917506:WKZ917509 WUS917506:WUV917509 V983042:Y983045 IG983042:IJ983045 SC983042:SF983045 ABY983042:ACB983045 ALU983042:ALX983045 AVQ983042:AVT983045 BFM983042:BFP983045 BPI983042:BPL983045 BZE983042:BZH983045 CJA983042:CJD983045 CSW983042:CSZ983045 DCS983042:DCV983045 DMO983042:DMR983045 DWK983042:DWN983045 EGG983042:EGJ983045 EQC983042:EQF983045 EZY983042:FAB983045 FJU983042:FJX983045 FTQ983042:FTT983045 GDM983042:GDP983045 GNI983042:GNL983045 GXE983042:GXH983045 HHA983042:HHD983045 HQW983042:HQZ983045 IAS983042:IAV983045 IKO983042:IKR983045 IUK983042:IUN983045 JEG983042:JEJ983045 JOC983042:JOF983045 JXY983042:JYB983045 KHU983042:KHX983045 KRQ983042:KRT983045 LBM983042:LBP983045 LLI983042:LLL983045 LVE983042:LVH983045 MFA983042:MFD983045 MOW983042:MOZ983045 MYS983042:MYV983045 NIO983042:NIR983045 NSK983042:NSN983045 OCG983042:OCJ983045 OMC983042:OMF983045 OVY983042:OWB983045 PFU983042:PFX983045 PPQ983042:PPT983045 PZM983042:PZP983045 QJI983042:QJL983045 QTE983042:QTH983045 RDA983042:RDD983045 RMW983042:RMZ983045 RWS983042:RWV983045 SGO983042:SGR983045 SQK983042:SQN983045 TAG983042:TAJ983045 TKC983042:TKF983045 TTY983042:TUB983045 UDU983042:UDX983045 UNQ983042:UNT983045 UXM983042:UXP983045 VHI983042:VHL983045 VRE983042:VRH983045 WBA983042:WBD983045 WKW983042:WKZ983045 WUS983042:WUV983045 Q65532:T65532 IB65532:IE65532 RX65532:SA65532 ABT65532:ABW65532 ALP65532:ALS65532 AVL65532:AVO65532 BFH65532:BFK65532 BPD65532:BPG65532 BYZ65532:BZC65532 CIV65532:CIY65532 CSR65532:CSU65532 DCN65532:DCQ65532 DMJ65532:DMM65532 DWF65532:DWI65532 EGB65532:EGE65532 EPX65532:EQA65532 EZT65532:EZW65532 FJP65532:FJS65532 FTL65532:FTO65532 GDH65532:GDK65532 GND65532:GNG65532 GWZ65532:GXC65532 HGV65532:HGY65532 HQR65532:HQU65532 IAN65532:IAQ65532 IKJ65532:IKM65532 IUF65532:IUI65532 JEB65532:JEE65532 JNX65532:JOA65532 JXT65532:JXW65532 KHP65532:KHS65532 KRL65532:KRO65532 LBH65532:LBK65532 LLD65532:LLG65532 LUZ65532:LVC65532 MEV65532:MEY65532 MOR65532:MOU65532 MYN65532:MYQ65532 NIJ65532:NIM65532 NSF65532:NSI65532 OCB65532:OCE65532 OLX65532:OMA65532 OVT65532:OVW65532 PFP65532:PFS65532 PPL65532:PPO65532 PZH65532:PZK65532 QJD65532:QJG65532 QSZ65532:QTC65532 RCV65532:RCY65532 RMR65532:RMU65532 RWN65532:RWQ65532 SGJ65532:SGM65532 SQF65532:SQI65532 TAB65532:TAE65532 TJX65532:TKA65532 TTT65532:TTW65532 UDP65532:UDS65532 UNL65532:UNO65532 UXH65532:UXK65532 VHD65532:VHG65532 VQZ65532:VRC65532 WAV65532:WAY65532 WKR65532:WKU65532 WUN65532:WUQ65532 Q131068:T131068 IB131068:IE131068 RX131068:SA131068 ABT131068:ABW131068 ALP131068:ALS131068 AVL131068:AVO131068 BFH131068:BFK131068 BPD131068:BPG131068 BYZ131068:BZC131068 CIV131068:CIY131068 CSR131068:CSU131068 DCN131068:DCQ131068 DMJ131068:DMM131068 DWF131068:DWI131068 EGB131068:EGE131068 EPX131068:EQA131068 EZT131068:EZW131068 FJP131068:FJS131068 FTL131068:FTO131068 GDH131068:GDK131068 GND131068:GNG131068 GWZ131068:GXC131068 HGV131068:HGY131068 HQR131068:HQU131068 IAN131068:IAQ131068 IKJ131068:IKM131068 IUF131068:IUI131068 JEB131068:JEE131068 JNX131068:JOA131068 JXT131068:JXW131068 KHP131068:KHS131068 KRL131068:KRO131068 LBH131068:LBK131068 LLD131068:LLG131068 LUZ131068:LVC131068 MEV131068:MEY131068 MOR131068:MOU131068 MYN131068:MYQ131068 NIJ131068:NIM131068 NSF131068:NSI131068 OCB131068:OCE131068 OLX131068:OMA131068 OVT131068:OVW131068 PFP131068:PFS131068 PPL131068:PPO131068 PZH131068:PZK131068 QJD131068:QJG131068 QSZ131068:QTC131068 RCV131068:RCY131068 RMR131068:RMU131068 RWN131068:RWQ131068 SGJ131068:SGM131068 SQF131068:SQI131068 TAB131068:TAE131068 TJX131068:TKA131068 TTT131068:TTW131068 UDP131068:UDS131068 UNL131068:UNO131068 UXH131068:UXK131068 VHD131068:VHG131068 VQZ131068:VRC131068 WAV131068:WAY131068 WKR131068:WKU131068 WUN131068:WUQ131068 Q196604:T196604 IB196604:IE196604 RX196604:SA196604 ABT196604:ABW196604 ALP196604:ALS196604 AVL196604:AVO196604 BFH196604:BFK196604 BPD196604:BPG196604 BYZ196604:BZC196604 CIV196604:CIY196604 CSR196604:CSU196604 DCN196604:DCQ196604 DMJ196604:DMM196604 DWF196604:DWI196604 EGB196604:EGE196604 EPX196604:EQA196604 EZT196604:EZW196604 FJP196604:FJS196604 FTL196604:FTO196604 GDH196604:GDK196604 GND196604:GNG196604 GWZ196604:GXC196604 HGV196604:HGY196604 HQR196604:HQU196604 IAN196604:IAQ196604 IKJ196604:IKM196604 IUF196604:IUI196604 JEB196604:JEE196604 JNX196604:JOA196604 JXT196604:JXW196604 KHP196604:KHS196604 KRL196604:KRO196604 LBH196604:LBK196604 LLD196604:LLG196604 LUZ196604:LVC196604 MEV196604:MEY196604 MOR196604:MOU196604 MYN196604:MYQ196604 NIJ196604:NIM196604 NSF196604:NSI196604 OCB196604:OCE196604 OLX196604:OMA196604 OVT196604:OVW196604 PFP196604:PFS196604 PPL196604:PPO196604 PZH196604:PZK196604 QJD196604:QJG196604 QSZ196604:QTC196604 RCV196604:RCY196604 RMR196604:RMU196604 RWN196604:RWQ196604 SGJ196604:SGM196604 SQF196604:SQI196604 TAB196604:TAE196604 TJX196604:TKA196604 TTT196604:TTW196604 UDP196604:UDS196604 UNL196604:UNO196604 UXH196604:UXK196604 VHD196604:VHG196604 VQZ196604:VRC196604 WAV196604:WAY196604 WKR196604:WKU196604 WUN196604:WUQ196604 Q262140:T262140 IB262140:IE262140 RX262140:SA262140 ABT262140:ABW262140 ALP262140:ALS262140 AVL262140:AVO262140 BFH262140:BFK262140 BPD262140:BPG262140 BYZ262140:BZC262140 CIV262140:CIY262140 CSR262140:CSU262140 DCN262140:DCQ262140 DMJ262140:DMM262140 DWF262140:DWI262140 EGB262140:EGE262140 EPX262140:EQA262140 EZT262140:EZW262140 FJP262140:FJS262140 FTL262140:FTO262140 GDH262140:GDK262140 GND262140:GNG262140 GWZ262140:GXC262140 HGV262140:HGY262140 HQR262140:HQU262140 IAN262140:IAQ262140 IKJ262140:IKM262140 IUF262140:IUI262140 JEB262140:JEE262140 JNX262140:JOA262140 JXT262140:JXW262140 KHP262140:KHS262140 KRL262140:KRO262140 LBH262140:LBK262140 LLD262140:LLG262140 LUZ262140:LVC262140 MEV262140:MEY262140 MOR262140:MOU262140 MYN262140:MYQ262140 NIJ262140:NIM262140 NSF262140:NSI262140 OCB262140:OCE262140 OLX262140:OMA262140 OVT262140:OVW262140 PFP262140:PFS262140 PPL262140:PPO262140 PZH262140:PZK262140 QJD262140:QJG262140 QSZ262140:QTC262140 RCV262140:RCY262140 RMR262140:RMU262140 RWN262140:RWQ262140 SGJ262140:SGM262140 SQF262140:SQI262140 TAB262140:TAE262140 TJX262140:TKA262140 TTT262140:TTW262140 UDP262140:UDS262140 UNL262140:UNO262140 UXH262140:UXK262140 VHD262140:VHG262140 VQZ262140:VRC262140 WAV262140:WAY262140 WKR262140:WKU262140 WUN262140:WUQ262140 Q327676:T327676 IB327676:IE327676 RX327676:SA327676 ABT327676:ABW327676 ALP327676:ALS327676 AVL327676:AVO327676 BFH327676:BFK327676 BPD327676:BPG327676 BYZ327676:BZC327676 CIV327676:CIY327676 CSR327676:CSU327676 DCN327676:DCQ327676 DMJ327676:DMM327676 DWF327676:DWI327676 EGB327676:EGE327676 EPX327676:EQA327676 EZT327676:EZW327676 FJP327676:FJS327676 FTL327676:FTO327676 GDH327676:GDK327676 GND327676:GNG327676 GWZ327676:GXC327676 HGV327676:HGY327676 HQR327676:HQU327676 IAN327676:IAQ327676 IKJ327676:IKM327676 IUF327676:IUI327676 JEB327676:JEE327676 JNX327676:JOA327676 JXT327676:JXW327676 KHP327676:KHS327676 KRL327676:KRO327676 LBH327676:LBK327676 LLD327676:LLG327676 LUZ327676:LVC327676 MEV327676:MEY327676 MOR327676:MOU327676 MYN327676:MYQ327676 NIJ327676:NIM327676 NSF327676:NSI327676 OCB327676:OCE327676 OLX327676:OMA327676 OVT327676:OVW327676 PFP327676:PFS327676 PPL327676:PPO327676 PZH327676:PZK327676 QJD327676:QJG327676 QSZ327676:QTC327676 RCV327676:RCY327676 RMR327676:RMU327676 RWN327676:RWQ327676 SGJ327676:SGM327676 SQF327676:SQI327676 TAB327676:TAE327676 TJX327676:TKA327676 TTT327676:TTW327676 UDP327676:UDS327676 UNL327676:UNO327676 UXH327676:UXK327676 VHD327676:VHG327676 VQZ327676:VRC327676 WAV327676:WAY327676 WKR327676:WKU327676 WUN327676:WUQ327676 Q393212:T393212 IB393212:IE393212 RX393212:SA393212 ABT393212:ABW393212 ALP393212:ALS393212 AVL393212:AVO393212 BFH393212:BFK393212 BPD393212:BPG393212 BYZ393212:BZC393212 CIV393212:CIY393212 CSR393212:CSU393212 DCN393212:DCQ393212 DMJ393212:DMM393212 DWF393212:DWI393212 EGB393212:EGE393212 EPX393212:EQA393212 EZT393212:EZW393212 FJP393212:FJS393212 FTL393212:FTO393212 GDH393212:GDK393212 GND393212:GNG393212 GWZ393212:GXC393212 HGV393212:HGY393212 HQR393212:HQU393212 IAN393212:IAQ393212 IKJ393212:IKM393212 IUF393212:IUI393212 JEB393212:JEE393212 JNX393212:JOA393212 JXT393212:JXW393212 KHP393212:KHS393212 KRL393212:KRO393212 LBH393212:LBK393212 LLD393212:LLG393212 LUZ393212:LVC393212 MEV393212:MEY393212 MOR393212:MOU393212 MYN393212:MYQ393212 NIJ393212:NIM393212 NSF393212:NSI393212 OCB393212:OCE393212 OLX393212:OMA393212 OVT393212:OVW393212 PFP393212:PFS393212 PPL393212:PPO393212 PZH393212:PZK393212 QJD393212:QJG393212 QSZ393212:QTC393212 RCV393212:RCY393212 RMR393212:RMU393212 RWN393212:RWQ393212 SGJ393212:SGM393212 SQF393212:SQI393212 TAB393212:TAE393212 TJX393212:TKA393212 TTT393212:TTW393212 UDP393212:UDS393212 UNL393212:UNO393212 UXH393212:UXK393212 VHD393212:VHG393212 VQZ393212:VRC393212 WAV393212:WAY393212 WKR393212:WKU393212 WUN393212:WUQ393212 Q458748:T458748 IB458748:IE458748 RX458748:SA458748 ABT458748:ABW458748 ALP458748:ALS458748 AVL458748:AVO458748 BFH458748:BFK458748 BPD458748:BPG458748 BYZ458748:BZC458748 CIV458748:CIY458748 CSR458748:CSU458748 DCN458748:DCQ458748 DMJ458748:DMM458748 DWF458748:DWI458748 EGB458748:EGE458748 EPX458748:EQA458748 EZT458748:EZW458748 FJP458748:FJS458748 FTL458748:FTO458748 GDH458748:GDK458748 GND458748:GNG458748 GWZ458748:GXC458748 HGV458748:HGY458748 HQR458748:HQU458748 IAN458748:IAQ458748 IKJ458748:IKM458748 IUF458748:IUI458748 JEB458748:JEE458748 JNX458748:JOA458748 JXT458748:JXW458748 KHP458748:KHS458748 KRL458748:KRO458748 LBH458748:LBK458748 LLD458748:LLG458748 LUZ458748:LVC458748 MEV458748:MEY458748 MOR458748:MOU458748 MYN458748:MYQ458748 NIJ458748:NIM458748 NSF458748:NSI458748 OCB458748:OCE458748 OLX458748:OMA458748 OVT458748:OVW458748 PFP458748:PFS458748 PPL458748:PPO458748 PZH458748:PZK458748 QJD458748:QJG458748 QSZ458748:QTC458748 RCV458748:RCY458748 RMR458748:RMU458748 RWN458748:RWQ458748 SGJ458748:SGM458748 SQF458748:SQI458748 TAB458748:TAE458748 TJX458748:TKA458748 TTT458748:TTW458748 UDP458748:UDS458748 UNL458748:UNO458748 UXH458748:UXK458748 VHD458748:VHG458748 VQZ458748:VRC458748 WAV458748:WAY458748 WKR458748:WKU458748 WUN458748:WUQ458748 Q524284:T524284 IB524284:IE524284 RX524284:SA524284 ABT524284:ABW524284 ALP524284:ALS524284 AVL524284:AVO524284 BFH524284:BFK524284 BPD524284:BPG524284 BYZ524284:BZC524284 CIV524284:CIY524284 CSR524284:CSU524284 DCN524284:DCQ524284 DMJ524284:DMM524284 DWF524284:DWI524284 EGB524284:EGE524284 EPX524284:EQA524284 EZT524284:EZW524284 FJP524284:FJS524284 FTL524284:FTO524284 GDH524284:GDK524284 GND524284:GNG524284 GWZ524284:GXC524284 HGV524284:HGY524284 HQR524284:HQU524284 IAN524284:IAQ524284 IKJ524284:IKM524284 IUF524284:IUI524284 JEB524284:JEE524284 JNX524284:JOA524284 JXT524284:JXW524284 KHP524284:KHS524284 KRL524284:KRO524284 LBH524284:LBK524284 LLD524284:LLG524284 LUZ524284:LVC524284 MEV524284:MEY524284 MOR524284:MOU524284 MYN524284:MYQ524284 NIJ524284:NIM524284 NSF524284:NSI524284 OCB524284:OCE524284 OLX524284:OMA524284 OVT524284:OVW524284 PFP524284:PFS524284 PPL524284:PPO524284 PZH524284:PZK524284 QJD524284:QJG524284 QSZ524284:QTC524284 RCV524284:RCY524284 RMR524284:RMU524284 RWN524284:RWQ524284 SGJ524284:SGM524284 SQF524284:SQI524284 TAB524284:TAE524284 TJX524284:TKA524284 TTT524284:TTW524284 UDP524284:UDS524284 UNL524284:UNO524284 UXH524284:UXK524284 VHD524284:VHG524284 VQZ524284:VRC524284 WAV524284:WAY524284 WKR524284:WKU524284 WUN524284:WUQ524284 Q589820:T589820 IB589820:IE589820 RX589820:SA589820 ABT589820:ABW589820 ALP589820:ALS589820 AVL589820:AVO589820 BFH589820:BFK589820 BPD589820:BPG589820 BYZ589820:BZC589820 CIV589820:CIY589820 CSR589820:CSU589820 DCN589820:DCQ589820 DMJ589820:DMM589820 DWF589820:DWI589820 EGB589820:EGE589820 EPX589820:EQA589820 EZT589820:EZW589820 FJP589820:FJS589820 FTL589820:FTO589820 GDH589820:GDK589820 GND589820:GNG589820 GWZ589820:GXC589820 HGV589820:HGY589820 HQR589820:HQU589820 IAN589820:IAQ589820 IKJ589820:IKM589820 IUF589820:IUI589820 JEB589820:JEE589820 JNX589820:JOA589820 JXT589820:JXW589820 KHP589820:KHS589820 KRL589820:KRO589820 LBH589820:LBK589820 LLD589820:LLG589820 LUZ589820:LVC589820 MEV589820:MEY589820 MOR589820:MOU589820 MYN589820:MYQ589820 NIJ589820:NIM589820 NSF589820:NSI589820 OCB589820:OCE589820 OLX589820:OMA589820 OVT589820:OVW589820 PFP589820:PFS589820 PPL589820:PPO589820 PZH589820:PZK589820 QJD589820:QJG589820 QSZ589820:QTC589820 RCV589820:RCY589820 RMR589820:RMU589820 RWN589820:RWQ589820 SGJ589820:SGM589820 SQF589820:SQI589820 TAB589820:TAE589820 TJX589820:TKA589820 TTT589820:TTW589820 UDP589820:UDS589820 UNL589820:UNO589820 UXH589820:UXK589820 VHD589820:VHG589820 VQZ589820:VRC589820 WAV589820:WAY589820 WKR589820:WKU589820 WUN589820:WUQ589820 Q655356:T655356 IB655356:IE655356 RX655356:SA655356 ABT655356:ABW655356 ALP655356:ALS655356 AVL655356:AVO655356 BFH655356:BFK655356 BPD655356:BPG655356 BYZ655356:BZC655356 CIV655356:CIY655356 CSR655356:CSU655356 DCN655356:DCQ655356 DMJ655356:DMM655356 DWF655356:DWI655356 EGB655356:EGE655356 EPX655356:EQA655356 EZT655356:EZW655356 FJP655356:FJS655356 FTL655356:FTO655356 GDH655356:GDK655356 GND655356:GNG655356 GWZ655356:GXC655356 HGV655356:HGY655356 HQR655356:HQU655356 IAN655356:IAQ655356 IKJ655356:IKM655356 IUF655356:IUI655356 JEB655356:JEE655356 JNX655356:JOA655356 JXT655356:JXW655356 KHP655356:KHS655356 KRL655356:KRO655356 LBH655356:LBK655356 LLD655356:LLG655356 LUZ655356:LVC655356 MEV655356:MEY655356 MOR655356:MOU655356 MYN655356:MYQ655356 NIJ655356:NIM655356 NSF655356:NSI655356 OCB655356:OCE655356 OLX655356:OMA655356 OVT655356:OVW655356 PFP655356:PFS655356 PPL655356:PPO655356 PZH655356:PZK655356 QJD655356:QJG655356 QSZ655356:QTC655356 RCV655356:RCY655356 RMR655356:RMU655356 RWN655356:RWQ655356 SGJ655356:SGM655356 SQF655356:SQI655356 TAB655356:TAE655356 TJX655356:TKA655356 TTT655356:TTW655356 UDP655356:UDS655356 UNL655356:UNO655356 UXH655356:UXK655356 VHD655356:VHG655356 VQZ655356:VRC655356 WAV655356:WAY655356 WKR655356:WKU655356 WUN655356:WUQ655356 Q720892:T720892 IB720892:IE720892 RX720892:SA720892 ABT720892:ABW720892 ALP720892:ALS720892 AVL720892:AVO720892 BFH720892:BFK720892 BPD720892:BPG720892 BYZ720892:BZC720892 CIV720892:CIY720892 CSR720892:CSU720892 DCN720892:DCQ720892 DMJ720892:DMM720892 DWF720892:DWI720892 EGB720892:EGE720892 EPX720892:EQA720892 EZT720892:EZW720892 FJP720892:FJS720892 FTL720892:FTO720892 GDH720892:GDK720892 GND720892:GNG720892 GWZ720892:GXC720892 HGV720892:HGY720892 HQR720892:HQU720892 IAN720892:IAQ720892 IKJ720892:IKM720892 IUF720892:IUI720892 JEB720892:JEE720892 JNX720892:JOA720892 JXT720892:JXW720892 KHP720892:KHS720892 KRL720892:KRO720892 LBH720892:LBK720892 LLD720892:LLG720892 LUZ720892:LVC720892 MEV720892:MEY720892 MOR720892:MOU720892 MYN720892:MYQ720892 NIJ720892:NIM720892 NSF720892:NSI720892 OCB720892:OCE720892 OLX720892:OMA720892 OVT720892:OVW720892 PFP720892:PFS720892 PPL720892:PPO720892 PZH720892:PZK720892 QJD720892:QJG720892 QSZ720892:QTC720892 RCV720892:RCY720892 RMR720892:RMU720892 RWN720892:RWQ720892 SGJ720892:SGM720892 SQF720892:SQI720892 TAB720892:TAE720892 TJX720892:TKA720892 TTT720892:TTW720892 UDP720892:UDS720892 UNL720892:UNO720892 UXH720892:UXK720892 VHD720892:VHG720892 VQZ720892:VRC720892 WAV720892:WAY720892 WKR720892:WKU720892 WUN720892:WUQ720892 Q786428:T786428 IB786428:IE786428 RX786428:SA786428 ABT786428:ABW786428 ALP786428:ALS786428 AVL786428:AVO786428 BFH786428:BFK786428 BPD786428:BPG786428 BYZ786428:BZC786428 CIV786428:CIY786428 CSR786428:CSU786428 DCN786428:DCQ786428 DMJ786428:DMM786428 DWF786428:DWI786428 EGB786428:EGE786428 EPX786428:EQA786428 EZT786428:EZW786428 FJP786428:FJS786428 FTL786428:FTO786428 GDH786428:GDK786428 GND786428:GNG786428 GWZ786428:GXC786428 HGV786428:HGY786428 HQR786428:HQU786428 IAN786428:IAQ786428 IKJ786428:IKM786428 IUF786428:IUI786428 JEB786428:JEE786428 JNX786428:JOA786428 JXT786428:JXW786428 KHP786428:KHS786428 KRL786428:KRO786428 LBH786428:LBK786428 LLD786428:LLG786428 LUZ786428:LVC786428 MEV786428:MEY786428 MOR786428:MOU786428 MYN786428:MYQ786428 NIJ786428:NIM786428 NSF786428:NSI786428 OCB786428:OCE786428 OLX786428:OMA786428 OVT786428:OVW786428 PFP786428:PFS786428 PPL786428:PPO786428 PZH786428:PZK786428 QJD786428:QJG786428 QSZ786428:QTC786428 RCV786428:RCY786428 RMR786428:RMU786428 RWN786428:RWQ786428 SGJ786428:SGM786428 SQF786428:SQI786428 TAB786428:TAE786428 TJX786428:TKA786428 TTT786428:TTW786428 UDP786428:UDS786428 UNL786428:UNO786428 UXH786428:UXK786428 VHD786428:VHG786428 VQZ786428:VRC786428 WAV786428:WAY786428 WKR786428:WKU786428 WUN786428:WUQ786428 Q851964:T851964 IB851964:IE851964 RX851964:SA851964 ABT851964:ABW851964 ALP851964:ALS851964 AVL851964:AVO851964 BFH851964:BFK851964 BPD851964:BPG851964 BYZ851964:BZC851964 CIV851964:CIY851964 CSR851964:CSU851964 DCN851964:DCQ851964 DMJ851964:DMM851964 DWF851964:DWI851964 EGB851964:EGE851964 EPX851964:EQA851964 EZT851964:EZW851964 FJP851964:FJS851964 FTL851964:FTO851964 GDH851964:GDK851964 GND851964:GNG851964 GWZ851964:GXC851964 HGV851964:HGY851964 HQR851964:HQU851964 IAN851964:IAQ851964 IKJ851964:IKM851964 IUF851964:IUI851964 JEB851964:JEE851964 JNX851964:JOA851964 JXT851964:JXW851964 KHP851964:KHS851964 KRL851964:KRO851964 LBH851964:LBK851964 LLD851964:LLG851964 LUZ851964:LVC851964 MEV851964:MEY851964 MOR851964:MOU851964 MYN851964:MYQ851964 NIJ851964:NIM851964 NSF851964:NSI851964 OCB851964:OCE851964 OLX851964:OMA851964 OVT851964:OVW851964 PFP851964:PFS851964 PPL851964:PPO851964 PZH851964:PZK851964 QJD851964:QJG851964 QSZ851964:QTC851964 RCV851964:RCY851964 RMR851964:RMU851964 RWN851964:RWQ851964 SGJ851964:SGM851964 SQF851964:SQI851964 TAB851964:TAE851964 TJX851964:TKA851964 TTT851964:TTW851964 UDP851964:UDS851964 UNL851964:UNO851964 UXH851964:UXK851964 VHD851964:VHG851964 VQZ851964:VRC851964 WAV851964:WAY851964 WKR851964:WKU851964 WUN851964:WUQ851964 Q917500:T917500 IB917500:IE917500 RX917500:SA917500 ABT917500:ABW917500 ALP917500:ALS917500 AVL917500:AVO917500 BFH917500:BFK917500 BPD917500:BPG917500 BYZ917500:BZC917500 CIV917500:CIY917500 CSR917500:CSU917500 DCN917500:DCQ917500 DMJ917500:DMM917500 DWF917500:DWI917500 EGB917500:EGE917500 EPX917500:EQA917500 EZT917500:EZW917500 FJP917500:FJS917500 FTL917500:FTO917500 GDH917500:GDK917500 GND917500:GNG917500 GWZ917500:GXC917500 HGV917500:HGY917500 HQR917500:HQU917500 IAN917500:IAQ917500 IKJ917500:IKM917500 IUF917500:IUI917500 JEB917500:JEE917500 JNX917500:JOA917500 JXT917500:JXW917500 KHP917500:KHS917500 KRL917500:KRO917500 LBH917500:LBK917500 LLD917500:LLG917500 LUZ917500:LVC917500 MEV917500:MEY917500 MOR917500:MOU917500 MYN917500:MYQ917500 NIJ917500:NIM917500 NSF917500:NSI917500 OCB917500:OCE917500 OLX917500:OMA917500 OVT917500:OVW917500 PFP917500:PFS917500 PPL917500:PPO917500 PZH917500:PZK917500 QJD917500:QJG917500 QSZ917500:QTC917500 RCV917500:RCY917500 RMR917500:RMU917500 RWN917500:RWQ917500 SGJ917500:SGM917500 SQF917500:SQI917500 TAB917500:TAE917500 TJX917500:TKA917500 TTT917500:TTW917500 UDP917500:UDS917500 UNL917500:UNO917500 UXH917500:UXK917500 VHD917500:VHG917500 VQZ917500:VRC917500 WAV917500:WAY917500 WKR917500:WKU917500 WUN917500:WUQ917500 Q983036:T983036 IB983036:IE983036 RX983036:SA983036 ABT983036:ABW983036 ALP983036:ALS983036 AVL983036:AVO983036 BFH983036:BFK983036 BPD983036:BPG983036 BYZ983036:BZC983036 CIV983036:CIY983036 CSR983036:CSU983036 DCN983036:DCQ983036 DMJ983036:DMM983036 DWF983036:DWI983036 EGB983036:EGE983036 EPX983036:EQA983036 EZT983036:EZW983036 FJP983036:FJS983036 FTL983036:FTO983036 GDH983036:GDK983036 GND983036:GNG983036 GWZ983036:GXC983036 HGV983036:HGY983036 HQR983036:HQU983036 IAN983036:IAQ983036 IKJ983036:IKM983036 IUF983036:IUI983036 JEB983036:JEE983036 JNX983036:JOA983036 JXT983036:JXW983036 KHP983036:KHS983036 KRL983036:KRO983036 LBH983036:LBK983036 LLD983036:LLG983036 LUZ983036:LVC983036 MEV983036:MEY983036 MOR983036:MOU983036 MYN983036:MYQ983036 NIJ983036:NIM983036 NSF983036:NSI983036 OCB983036:OCE983036 OLX983036:OMA983036 OVT983036:OVW983036 PFP983036:PFS983036 PPL983036:PPO983036 PZH983036:PZK983036 QJD983036:QJG983036 QSZ983036:QTC983036 RCV983036:RCY983036 RMR983036:RMU983036 RWN983036:RWQ983036 SGJ983036:SGM983036 SQF983036:SQI983036 TAB983036:TAE983036 TJX983036:TKA983036 TTT983036:TTW983036 UDP983036:UDS983036 UNL983036:UNO983036 UXH983036:UXK983036 VHD983036:VHG983036 VQZ983036:VRC983036 WAV983036:WAY983036 WKR983036:WKU983036 WUN983036:WUQ983036 HW983035:HZ983035 RS983035:RV983035 ABO983035:ABR983035 ALK983035:ALN983035 AVG983035:AVJ983035 BFC983035:BFF983035 BOY983035:BPB983035 BYU983035:BYX983035 CIQ983035:CIT983035 CSM983035:CSP983035 DCI983035:DCL983035 DME983035:DMH983035 DWA983035:DWD983035 EFW983035:EFZ983035 EPS983035:EPV983035 EZO983035:EZR983035 FJK983035:FJN983035 FTG983035:FTJ983035 GDC983035:GDF983035 GMY983035:GNB983035 GWU983035:GWX983035 HGQ983035:HGT983035 HQM983035:HQP983035 IAI983035:IAL983035 IKE983035:IKH983035 IUA983035:IUD983035 JDW983035:JDZ983035 JNS983035:JNV983035 JXO983035:JXR983035 KHK983035:KHN983035 KRG983035:KRJ983035 LBC983035:LBF983035 LKY983035:LLB983035 LUU983035:LUX983035 MEQ983035:MET983035 MOM983035:MOP983035 MYI983035:MYL983035 NIE983035:NIH983035 NSA983035:NSD983035 OBW983035:OBZ983035 OLS983035:OLV983035 OVO983035:OVR983035 PFK983035:PFN983035 PPG983035:PPJ983035 PZC983035:PZF983035 QIY983035:QJB983035 QSU983035:QSX983035 RCQ983035:RCT983035 RMM983035:RMP983035 RWI983035:RWL983035 SGE983035:SGH983035 SQA983035:SQD983035 SZW983035:SZZ983035 TJS983035:TJV983035 TTO983035:TTR983035 UDK983035:UDN983035 UNG983035:UNJ983035 UXC983035:UXF983035 VGY983035:VHB983035 VQU983035:VQX983035 WAQ983035:WAT983035 WKM983035:WKP983035 WUI983035:WUL983035 HW65531:HZ65531 RS65531:RV65531 ABO65531:ABR65531 ALK65531:ALN65531 AVG65531:AVJ65531 BFC65531:BFF65531 BOY65531:BPB65531 BYU65531:BYX65531 CIQ65531:CIT65531 CSM65531:CSP65531 DCI65531:DCL65531 DME65531:DMH65531 DWA65531:DWD65531 EFW65531:EFZ65531 EPS65531:EPV65531 EZO65531:EZR65531 FJK65531:FJN65531 FTG65531:FTJ65531 GDC65531:GDF65531 GMY65531:GNB65531 GWU65531:GWX65531 HGQ65531:HGT65531 HQM65531:HQP65531 IAI65531:IAL65531 IKE65531:IKH65531 IUA65531:IUD65531 JDW65531:JDZ65531 JNS65531:JNV65531 JXO65531:JXR65531 KHK65531:KHN65531 KRG65531:KRJ65531 LBC65531:LBF65531 LKY65531:LLB65531 LUU65531:LUX65531 MEQ65531:MET65531 MOM65531:MOP65531 MYI65531:MYL65531 NIE65531:NIH65531 NSA65531:NSD65531 OBW65531:OBZ65531 OLS65531:OLV65531 OVO65531:OVR65531 PFK65531:PFN65531 PPG65531:PPJ65531 PZC65531:PZF65531 QIY65531:QJB65531 QSU65531:QSX65531 RCQ65531:RCT65531 RMM65531:RMP65531 RWI65531:RWL65531 SGE65531:SGH65531 SQA65531:SQD65531 SZW65531:SZZ65531 TJS65531:TJV65531 TTO65531:TTR65531 UDK65531:UDN65531 UNG65531:UNJ65531 UXC65531:UXF65531 VGY65531:VHB65531 VQU65531:VQX65531 WAQ65531:WAT65531 WKM65531:WKP65531 WUI65531:WUL65531 HW131067:HZ131067 RS131067:RV131067 ABO131067:ABR131067 ALK131067:ALN131067 AVG131067:AVJ131067 BFC131067:BFF131067 BOY131067:BPB131067 BYU131067:BYX131067 CIQ131067:CIT131067 CSM131067:CSP131067 DCI131067:DCL131067 DME131067:DMH131067 DWA131067:DWD131067 EFW131067:EFZ131067 EPS131067:EPV131067 EZO131067:EZR131067 FJK131067:FJN131067 FTG131067:FTJ131067 GDC131067:GDF131067 GMY131067:GNB131067 GWU131067:GWX131067 HGQ131067:HGT131067 HQM131067:HQP131067 IAI131067:IAL131067 IKE131067:IKH131067 IUA131067:IUD131067 JDW131067:JDZ131067 JNS131067:JNV131067 JXO131067:JXR131067 KHK131067:KHN131067 KRG131067:KRJ131067 LBC131067:LBF131067 LKY131067:LLB131067 LUU131067:LUX131067 MEQ131067:MET131067 MOM131067:MOP131067 MYI131067:MYL131067 NIE131067:NIH131067 NSA131067:NSD131067 OBW131067:OBZ131067 OLS131067:OLV131067 OVO131067:OVR131067 PFK131067:PFN131067 PPG131067:PPJ131067 PZC131067:PZF131067 QIY131067:QJB131067 QSU131067:QSX131067 RCQ131067:RCT131067 RMM131067:RMP131067 RWI131067:RWL131067 SGE131067:SGH131067 SQA131067:SQD131067 SZW131067:SZZ131067 TJS131067:TJV131067 TTO131067:TTR131067 UDK131067:UDN131067 UNG131067:UNJ131067 UXC131067:UXF131067 VGY131067:VHB131067 VQU131067:VQX131067 WAQ131067:WAT131067 WKM131067:WKP131067 WUI131067:WUL131067 HW196603:HZ196603 RS196603:RV196603 ABO196603:ABR196603 ALK196603:ALN196603 AVG196603:AVJ196603 BFC196603:BFF196603 BOY196603:BPB196603 BYU196603:BYX196603 CIQ196603:CIT196603 CSM196603:CSP196603 DCI196603:DCL196603 DME196603:DMH196603 DWA196603:DWD196603 EFW196603:EFZ196603 EPS196603:EPV196603 EZO196603:EZR196603 FJK196603:FJN196603 FTG196603:FTJ196603 GDC196603:GDF196603 GMY196603:GNB196603 GWU196603:GWX196603 HGQ196603:HGT196603 HQM196603:HQP196603 IAI196603:IAL196603 IKE196603:IKH196603 IUA196603:IUD196603 JDW196603:JDZ196603 JNS196603:JNV196603 JXO196603:JXR196603 KHK196603:KHN196603 KRG196603:KRJ196603 LBC196603:LBF196603 LKY196603:LLB196603 LUU196603:LUX196603 MEQ196603:MET196603 MOM196603:MOP196603 MYI196603:MYL196603 NIE196603:NIH196603 NSA196603:NSD196603 OBW196603:OBZ196603 OLS196603:OLV196603 OVO196603:OVR196603 PFK196603:PFN196603 PPG196603:PPJ196603 PZC196603:PZF196603 QIY196603:QJB196603 QSU196603:QSX196603 RCQ196603:RCT196603 RMM196603:RMP196603 RWI196603:RWL196603 SGE196603:SGH196603 SQA196603:SQD196603 SZW196603:SZZ196603 TJS196603:TJV196603 TTO196603:TTR196603 UDK196603:UDN196603 UNG196603:UNJ196603 UXC196603:UXF196603 VGY196603:VHB196603 VQU196603:VQX196603 WAQ196603:WAT196603 WKM196603:WKP196603 WUI196603:WUL196603 HW262139:HZ262139 RS262139:RV262139 ABO262139:ABR262139 ALK262139:ALN262139 AVG262139:AVJ262139 BFC262139:BFF262139 BOY262139:BPB262139 BYU262139:BYX262139 CIQ262139:CIT262139 CSM262139:CSP262139 DCI262139:DCL262139 DME262139:DMH262139 DWA262139:DWD262139 EFW262139:EFZ262139 EPS262139:EPV262139 EZO262139:EZR262139 FJK262139:FJN262139 FTG262139:FTJ262139 GDC262139:GDF262139 GMY262139:GNB262139 GWU262139:GWX262139 HGQ262139:HGT262139 HQM262139:HQP262139 IAI262139:IAL262139 IKE262139:IKH262139 IUA262139:IUD262139 JDW262139:JDZ262139 JNS262139:JNV262139 JXO262139:JXR262139 KHK262139:KHN262139 KRG262139:KRJ262139 LBC262139:LBF262139 LKY262139:LLB262139 LUU262139:LUX262139 MEQ262139:MET262139 MOM262139:MOP262139 MYI262139:MYL262139 NIE262139:NIH262139 NSA262139:NSD262139 OBW262139:OBZ262139 OLS262139:OLV262139 OVO262139:OVR262139 PFK262139:PFN262139 PPG262139:PPJ262139 PZC262139:PZF262139 QIY262139:QJB262139 QSU262139:QSX262139 RCQ262139:RCT262139 RMM262139:RMP262139 RWI262139:RWL262139 SGE262139:SGH262139 SQA262139:SQD262139 SZW262139:SZZ262139 TJS262139:TJV262139 TTO262139:TTR262139 UDK262139:UDN262139 UNG262139:UNJ262139 UXC262139:UXF262139 VGY262139:VHB262139 VQU262139:VQX262139 WAQ262139:WAT262139 WKM262139:WKP262139 WUI262139:WUL262139 HW327675:HZ327675 RS327675:RV327675 ABO327675:ABR327675 ALK327675:ALN327675 AVG327675:AVJ327675 BFC327675:BFF327675 BOY327675:BPB327675 BYU327675:BYX327675 CIQ327675:CIT327675 CSM327675:CSP327675 DCI327675:DCL327675 DME327675:DMH327675 DWA327675:DWD327675 EFW327675:EFZ327675 EPS327675:EPV327675 EZO327675:EZR327675 FJK327675:FJN327675 FTG327675:FTJ327675 GDC327675:GDF327675 GMY327675:GNB327675 GWU327675:GWX327675 HGQ327675:HGT327675 HQM327675:HQP327675 IAI327675:IAL327675 IKE327675:IKH327675 IUA327675:IUD327675 JDW327675:JDZ327675 JNS327675:JNV327675 JXO327675:JXR327675 KHK327675:KHN327675 KRG327675:KRJ327675 LBC327675:LBF327675 LKY327675:LLB327675 LUU327675:LUX327675 MEQ327675:MET327675 MOM327675:MOP327675 MYI327675:MYL327675 NIE327675:NIH327675 NSA327675:NSD327675 OBW327675:OBZ327675 OLS327675:OLV327675 OVO327675:OVR327675 PFK327675:PFN327675 PPG327675:PPJ327675 PZC327675:PZF327675 QIY327675:QJB327675 QSU327675:QSX327675 RCQ327675:RCT327675 RMM327675:RMP327675 RWI327675:RWL327675 SGE327675:SGH327675 SQA327675:SQD327675 SZW327675:SZZ327675 TJS327675:TJV327675 TTO327675:TTR327675 UDK327675:UDN327675 UNG327675:UNJ327675 UXC327675:UXF327675 VGY327675:VHB327675 VQU327675:VQX327675 WAQ327675:WAT327675 WKM327675:WKP327675 WUI327675:WUL327675 HW393211:HZ393211 RS393211:RV393211 ABO393211:ABR393211 ALK393211:ALN393211 AVG393211:AVJ393211 BFC393211:BFF393211 BOY393211:BPB393211 BYU393211:BYX393211 CIQ393211:CIT393211 CSM393211:CSP393211 DCI393211:DCL393211 DME393211:DMH393211 DWA393211:DWD393211 EFW393211:EFZ393211 EPS393211:EPV393211 EZO393211:EZR393211 FJK393211:FJN393211 FTG393211:FTJ393211 GDC393211:GDF393211 GMY393211:GNB393211 GWU393211:GWX393211 HGQ393211:HGT393211 HQM393211:HQP393211 IAI393211:IAL393211 IKE393211:IKH393211 IUA393211:IUD393211 JDW393211:JDZ393211 JNS393211:JNV393211 JXO393211:JXR393211 KHK393211:KHN393211 KRG393211:KRJ393211 LBC393211:LBF393211 LKY393211:LLB393211 LUU393211:LUX393211 MEQ393211:MET393211 MOM393211:MOP393211 MYI393211:MYL393211 NIE393211:NIH393211 NSA393211:NSD393211 OBW393211:OBZ393211 OLS393211:OLV393211 OVO393211:OVR393211 PFK393211:PFN393211 PPG393211:PPJ393211 PZC393211:PZF393211 QIY393211:QJB393211 QSU393211:QSX393211 RCQ393211:RCT393211 RMM393211:RMP393211 RWI393211:RWL393211 SGE393211:SGH393211 SQA393211:SQD393211 SZW393211:SZZ393211 TJS393211:TJV393211 TTO393211:TTR393211 UDK393211:UDN393211 UNG393211:UNJ393211 UXC393211:UXF393211 VGY393211:VHB393211 VQU393211:VQX393211 WAQ393211:WAT393211 WKM393211:WKP393211 WUI393211:WUL393211 HW458747:HZ458747 RS458747:RV458747 ABO458747:ABR458747 ALK458747:ALN458747 AVG458747:AVJ458747 BFC458747:BFF458747 BOY458747:BPB458747 BYU458747:BYX458747 CIQ458747:CIT458747 CSM458747:CSP458747 DCI458747:DCL458747 DME458747:DMH458747 DWA458747:DWD458747 EFW458747:EFZ458747 EPS458747:EPV458747 EZO458747:EZR458747 FJK458747:FJN458747 FTG458747:FTJ458747 GDC458747:GDF458747 GMY458747:GNB458747 GWU458747:GWX458747 HGQ458747:HGT458747 HQM458747:HQP458747 IAI458747:IAL458747 IKE458747:IKH458747 IUA458747:IUD458747 JDW458747:JDZ458747 JNS458747:JNV458747 JXO458747:JXR458747 KHK458747:KHN458747 KRG458747:KRJ458747 LBC458747:LBF458747 LKY458747:LLB458747 LUU458747:LUX458747 MEQ458747:MET458747 MOM458747:MOP458747 MYI458747:MYL458747 NIE458747:NIH458747 NSA458747:NSD458747 OBW458747:OBZ458747 OLS458747:OLV458747 OVO458747:OVR458747 PFK458747:PFN458747 PPG458747:PPJ458747 PZC458747:PZF458747 QIY458747:QJB458747 QSU458747:QSX458747 RCQ458747:RCT458747 RMM458747:RMP458747 RWI458747:RWL458747 SGE458747:SGH458747 SQA458747:SQD458747 SZW458747:SZZ458747 TJS458747:TJV458747 TTO458747:TTR458747 UDK458747:UDN458747 UNG458747:UNJ458747 UXC458747:UXF458747 VGY458747:VHB458747 VQU458747:VQX458747 WAQ458747:WAT458747 WKM458747:WKP458747 WUI458747:WUL458747 HW524283:HZ524283 RS524283:RV524283 ABO524283:ABR524283 ALK524283:ALN524283 AVG524283:AVJ524283 BFC524283:BFF524283 BOY524283:BPB524283 BYU524283:BYX524283 CIQ524283:CIT524283 CSM524283:CSP524283 DCI524283:DCL524283 DME524283:DMH524283 DWA524283:DWD524283 EFW524283:EFZ524283 EPS524283:EPV524283 EZO524283:EZR524283 FJK524283:FJN524283 FTG524283:FTJ524283 GDC524283:GDF524283 GMY524283:GNB524283 GWU524283:GWX524283 HGQ524283:HGT524283 HQM524283:HQP524283 IAI524283:IAL524283 IKE524283:IKH524283 IUA524283:IUD524283 JDW524283:JDZ524283 JNS524283:JNV524283 JXO524283:JXR524283 KHK524283:KHN524283 KRG524283:KRJ524283 LBC524283:LBF524283 LKY524283:LLB524283 LUU524283:LUX524283 MEQ524283:MET524283 MOM524283:MOP524283 MYI524283:MYL524283 NIE524283:NIH524283 NSA524283:NSD524283 OBW524283:OBZ524283 OLS524283:OLV524283 OVO524283:OVR524283 PFK524283:PFN524283 PPG524283:PPJ524283 PZC524283:PZF524283 QIY524283:QJB524283 QSU524283:QSX524283 RCQ524283:RCT524283 RMM524283:RMP524283 RWI524283:RWL524283 SGE524283:SGH524283 SQA524283:SQD524283 SZW524283:SZZ524283 TJS524283:TJV524283 TTO524283:TTR524283 UDK524283:UDN524283 UNG524283:UNJ524283 UXC524283:UXF524283 VGY524283:VHB524283 VQU524283:VQX524283 WAQ524283:WAT524283 WKM524283:WKP524283 WUI524283:WUL524283 HW589819:HZ589819 RS589819:RV589819 ABO589819:ABR589819 ALK589819:ALN589819 AVG589819:AVJ589819 BFC589819:BFF589819 BOY589819:BPB589819 BYU589819:BYX589819 CIQ589819:CIT589819 CSM589819:CSP589819 DCI589819:DCL589819 DME589819:DMH589819 DWA589819:DWD589819 EFW589819:EFZ589819 EPS589819:EPV589819 EZO589819:EZR589819 FJK589819:FJN589819 FTG589819:FTJ589819 GDC589819:GDF589819 GMY589819:GNB589819 GWU589819:GWX589819 HGQ589819:HGT589819 HQM589819:HQP589819 IAI589819:IAL589819 IKE589819:IKH589819 IUA589819:IUD589819 JDW589819:JDZ589819 JNS589819:JNV589819 JXO589819:JXR589819 KHK589819:KHN589819 KRG589819:KRJ589819 LBC589819:LBF589819 LKY589819:LLB589819 LUU589819:LUX589819 MEQ589819:MET589819 MOM589819:MOP589819 MYI589819:MYL589819 NIE589819:NIH589819 NSA589819:NSD589819 OBW589819:OBZ589819 OLS589819:OLV589819 OVO589819:OVR589819 PFK589819:PFN589819 PPG589819:PPJ589819 PZC589819:PZF589819 QIY589819:QJB589819 QSU589819:QSX589819 RCQ589819:RCT589819 RMM589819:RMP589819 RWI589819:RWL589819 SGE589819:SGH589819 SQA589819:SQD589819 SZW589819:SZZ589819 TJS589819:TJV589819 TTO589819:TTR589819 UDK589819:UDN589819 UNG589819:UNJ589819 UXC589819:UXF589819 VGY589819:VHB589819 VQU589819:VQX589819 WAQ589819:WAT589819 WKM589819:WKP589819 WUI589819:WUL589819 HW655355:HZ655355 RS655355:RV655355 ABO655355:ABR655355 ALK655355:ALN655355 AVG655355:AVJ655355 BFC655355:BFF655355 BOY655355:BPB655355 BYU655355:BYX655355 CIQ655355:CIT655355 CSM655355:CSP655355 DCI655355:DCL655355 DME655355:DMH655355 DWA655355:DWD655355 EFW655355:EFZ655355 EPS655355:EPV655355 EZO655355:EZR655355 FJK655355:FJN655355 FTG655355:FTJ655355 GDC655355:GDF655355 GMY655355:GNB655355 GWU655355:GWX655355 HGQ655355:HGT655355 HQM655355:HQP655355 IAI655355:IAL655355 IKE655355:IKH655355 IUA655355:IUD655355 JDW655355:JDZ655355 JNS655355:JNV655355 JXO655355:JXR655355 KHK655355:KHN655355 KRG655355:KRJ655355 LBC655355:LBF655355 LKY655355:LLB655355 LUU655355:LUX655355 MEQ655355:MET655355 MOM655355:MOP655355 MYI655355:MYL655355 NIE655355:NIH655355 NSA655355:NSD655355 OBW655355:OBZ655355 OLS655355:OLV655355 OVO655355:OVR655355 PFK655355:PFN655355 PPG655355:PPJ655355 PZC655355:PZF655355 QIY655355:QJB655355 QSU655355:QSX655355 RCQ655355:RCT655355 RMM655355:RMP655355 RWI655355:RWL655355 SGE655355:SGH655355 SQA655355:SQD655355 SZW655355:SZZ655355 TJS655355:TJV655355 TTO655355:TTR655355 UDK655355:UDN655355 UNG655355:UNJ655355 UXC655355:UXF655355 VGY655355:VHB655355 VQU655355:VQX655355 WAQ655355:WAT655355 WKM655355:WKP655355 WUI655355:WUL655355 HW720891:HZ720891 RS720891:RV720891 ABO720891:ABR720891 ALK720891:ALN720891 AVG720891:AVJ720891 BFC720891:BFF720891 BOY720891:BPB720891 BYU720891:BYX720891 CIQ720891:CIT720891 CSM720891:CSP720891 DCI720891:DCL720891 DME720891:DMH720891 DWA720891:DWD720891 EFW720891:EFZ720891 EPS720891:EPV720891 EZO720891:EZR720891 FJK720891:FJN720891 FTG720891:FTJ720891 GDC720891:GDF720891 GMY720891:GNB720891 GWU720891:GWX720891 HGQ720891:HGT720891 HQM720891:HQP720891 IAI720891:IAL720891 IKE720891:IKH720891 IUA720891:IUD720891 JDW720891:JDZ720891 JNS720891:JNV720891 JXO720891:JXR720891 KHK720891:KHN720891 KRG720891:KRJ720891 LBC720891:LBF720891 LKY720891:LLB720891 LUU720891:LUX720891 MEQ720891:MET720891 MOM720891:MOP720891 MYI720891:MYL720891 NIE720891:NIH720891 NSA720891:NSD720891 OBW720891:OBZ720891 OLS720891:OLV720891 OVO720891:OVR720891 PFK720891:PFN720891 PPG720891:PPJ720891 PZC720891:PZF720891 QIY720891:QJB720891 QSU720891:QSX720891 RCQ720891:RCT720891 RMM720891:RMP720891 RWI720891:RWL720891 SGE720891:SGH720891 SQA720891:SQD720891 SZW720891:SZZ720891 TJS720891:TJV720891 TTO720891:TTR720891 UDK720891:UDN720891 UNG720891:UNJ720891 UXC720891:UXF720891 VGY720891:VHB720891 VQU720891:VQX720891 WAQ720891:WAT720891 WKM720891:WKP720891 WUI720891:WUL720891 HW786427:HZ786427 RS786427:RV786427 ABO786427:ABR786427 ALK786427:ALN786427 AVG786427:AVJ786427 BFC786427:BFF786427 BOY786427:BPB786427 BYU786427:BYX786427 CIQ786427:CIT786427 CSM786427:CSP786427 DCI786427:DCL786427 DME786427:DMH786427 DWA786427:DWD786427 EFW786427:EFZ786427 EPS786427:EPV786427 EZO786427:EZR786427 FJK786427:FJN786427 FTG786427:FTJ786427 GDC786427:GDF786427 GMY786427:GNB786427 GWU786427:GWX786427 HGQ786427:HGT786427 HQM786427:HQP786427 IAI786427:IAL786427 IKE786427:IKH786427 IUA786427:IUD786427 JDW786427:JDZ786427 JNS786427:JNV786427 JXO786427:JXR786427 KHK786427:KHN786427 KRG786427:KRJ786427 LBC786427:LBF786427 LKY786427:LLB786427 LUU786427:LUX786427 MEQ786427:MET786427 MOM786427:MOP786427 MYI786427:MYL786427 NIE786427:NIH786427 NSA786427:NSD786427 OBW786427:OBZ786427 OLS786427:OLV786427 OVO786427:OVR786427 PFK786427:PFN786427 PPG786427:PPJ786427 PZC786427:PZF786427 QIY786427:QJB786427 QSU786427:QSX786427 RCQ786427:RCT786427 RMM786427:RMP786427 RWI786427:RWL786427 SGE786427:SGH786427 SQA786427:SQD786427 SZW786427:SZZ786427 TJS786427:TJV786427 TTO786427:TTR786427 UDK786427:UDN786427 UNG786427:UNJ786427 UXC786427:UXF786427 VGY786427:VHB786427 VQU786427:VQX786427 WAQ786427:WAT786427 WKM786427:WKP786427 WUI786427:WUL786427 HW851963:HZ851963 RS851963:RV851963 ABO851963:ABR851963 ALK851963:ALN851963 AVG851963:AVJ851963 BFC851963:BFF851963 BOY851963:BPB851963 BYU851963:BYX851963 CIQ851963:CIT851963 CSM851963:CSP851963 DCI851963:DCL851963 DME851963:DMH851963 DWA851963:DWD851963 EFW851963:EFZ851963 EPS851963:EPV851963 EZO851963:EZR851963 FJK851963:FJN851963 FTG851963:FTJ851963 GDC851963:GDF851963 GMY851963:GNB851963 GWU851963:GWX851963 HGQ851963:HGT851963 HQM851963:HQP851963 IAI851963:IAL851963 IKE851963:IKH851963 IUA851963:IUD851963 JDW851963:JDZ851963 JNS851963:JNV851963 JXO851963:JXR851963 KHK851963:KHN851963 KRG851963:KRJ851963 LBC851963:LBF851963 LKY851963:LLB851963 LUU851963:LUX851963 MEQ851963:MET851963 MOM851963:MOP851963 MYI851963:MYL851963 NIE851963:NIH851963 NSA851963:NSD851963 OBW851963:OBZ851963 OLS851963:OLV851963 OVO851963:OVR851963 PFK851963:PFN851963 PPG851963:PPJ851963 PZC851963:PZF851963 QIY851963:QJB851963 QSU851963:QSX851963 RCQ851963:RCT851963 RMM851963:RMP851963 RWI851963:RWL851963 SGE851963:SGH851963 SQA851963:SQD851963 SZW851963:SZZ851963 TJS851963:TJV851963 TTO851963:TTR851963 UDK851963:UDN851963 UNG851963:UNJ851963 UXC851963:UXF851963 VGY851963:VHB851963 VQU851963:VQX851963 WAQ851963:WAT851963 WKM851963:WKP851963 WUI851963:WUL851963 HW917499:HZ917499 RS917499:RV917499 ABO917499:ABR917499 ALK917499:ALN917499 AVG917499:AVJ917499 BFC917499:BFF917499 BOY917499:BPB917499 BYU917499:BYX917499 CIQ917499:CIT917499 CSM917499:CSP917499 DCI917499:DCL917499 DME917499:DMH917499 DWA917499:DWD917499 EFW917499:EFZ917499 EPS917499:EPV917499 EZO917499:EZR917499 FJK917499:FJN917499 FTG917499:FTJ917499 GDC917499:GDF917499 GMY917499:GNB917499 GWU917499:GWX917499 HGQ917499:HGT917499 HQM917499:HQP917499 IAI917499:IAL917499 IKE917499:IKH917499 IUA917499:IUD917499 JDW917499:JDZ917499 JNS917499:JNV917499 JXO917499:JXR917499 KHK917499:KHN917499 KRG917499:KRJ917499 LBC917499:LBF917499 LKY917499:LLB917499 LUU917499:LUX917499 MEQ917499:MET917499 MOM917499:MOP917499 MYI917499:MYL917499 NIE917499:NIH917499 NSA917499:NSD917499 OBW917499:OBZ917499 OLS917499:OLV917499 OVO917499:OVR917499 PFK917499:PFN917499 PPG917499:PPJ917499 PZC917499:PZF917499 QIY917499:QJB917499 QSU917499:QSX917499 RCQ917499:RCT917499 RMM917499:RMP917499 RWI917499:RWL917499 SGE917499:SGH917499 SQA917499:SQD917499 SZW917499:SZZ917499 TJS917499:TJV917499 TTO917499:TTR917499 UDK917499:UDN917499 UNG917499:UNJ917499 UXC917499:UXF917499 VGY917499:VHB917499 VQU917499:VQX917499 WAQ917499:WAT917499 WKM917499:WKP917499 WUI917499:WUL917499 AI65552:AJ65555 AI131088:AJ131091 AI196624:AJ196627 AI262160:AJ262163 AI327696:AJ327699 AI393232:AJ393235 AI458768:AJ458771 AI524304:AJ524307 AI589840:AJ589843 AI655376:AJ655379 AI720912:AJ720915 AI786448:AJ786451 AI851984:AJ851987 AI917520:AJ917523 AI983056:AJ983059 AG65546 AG131082 AG196618 AG262154 AG327690 AG393226 AG458762 AG524298 AG589834 AG655370 AG720906 AG786442 AG851978 AG917514 AB917514:AD917514 AB851978:AD851978 AB786442:AD786442 AB720906:AD720906 AB655370:AD655370 AB589834:AD589834 AB524298:AD524298 AB458762:AD458762 AB393226:AD393226 AB327690:AD327690 AB262154:AD262154 AB196618:AD196618 AB131082:AD131082 AB65546:AD65546 AB983050:AD983050 AG983050 AF65552:AF65555 AF131088:AF131091 AF196624:AF196627 AF262160:AF262163 AF327696:AF327699 AF393232:AF393235 AF458768:AF458771 AF524304:AF524307 AF589840:AF589843 AF655376:AF655379 AF720912:AF720915 AF786448:AF786451 AF851984:AF851987 AF917520:AF917523 AF983056:AF983059 AF19 AI19:AJ19" xr:uid="{BBC32FCA-F27E-4303-BEB1-085300B4CFF2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V65540:Y65543 IG65540:IJ65543 SC65540:SF65543 ABY65540:ACB65543 ALU65540:ALX65543 AVQ65540:AVT65543 BFM65540:BFP65543 BPI65540:BPL65543 BZE65540:BZH65543 CJA65540:CJD65543 CSW65540:CSZ65543 DCS65540:DCV65543 DMO65540:DMR65543 DWK65540:DWN65543 EGG65540:EGJ65543 EQC65540:EQF65543 EZY65540:FAB65543 FJU65540:FJX65543 FTQ65540:FTT65543 GDM65540:GDP65543 GNI65540:GNL65543 GXE65540:GXH65543 HHA65540:HHD65543 HQW65540:HQZ65543 IAS65540:IAV65543 IKO65540:IKR65543 IUK65540:IUN65543 JEG65540:JEJ65543 JOC65540:JOF65543 JXY65540:JYB65543 KHU65540:KHX65543 KRQ65540:KRT65543 LBM65540:LBP65543 LLI65540:LLL65543 LVE65540:LVH65543 MFA65540:MFD65543 MOW65540:MOZ65543 MYS65540:MYV65543 NIO65540:NIR65543 NSK65540:NSN65543 OCG65540:OCJ65543 OMC65540:OMF65543 OVY65540:OWB65543 PFU65540:PFX65543 PPQ65540:PPT65543 PZM65540:PZP65543 QJI65540:QJL65543 QTE65540:QTH65543 RDA65540:RDD65543 RMW65540:RMZ65543 RWS65540:RWV65543 SGO65540:SGR65543 SQK65540:SQN65543 TAG65540:TAJ65543 TKC65540:TKF65543 TTY65540:TUB65543 UDU65540:UDX65543 UNQ65540:UNT65543 UXM65540:UXP65543 VHI65540:VHL65543 VRE65540:VRH65543 WBA65540:WBD65543 WKW65540:WKZ65543 WUS65540:WUV65543 V131076:Y131079 IG131076:IJ131079 SC131076:SF131079 ABY131076:ACB131079 ALU131076:ALX131079 AVQ131076:AVT131079 BFM131076:BFP131079 BPI131076:BPL131079 BZE131076:BZH131079 CJA131076:CJD131079 CSW131076:CSZ131079 DCS131076:DCV131079 DMO131076:DMR131079 DWK131076:DWN131079 EGG131076:EGJ131079 EQC131076:EQF131079 EZY131076:FAB131079 FJU131076:FJX131079 FTQ131076:FTT131079 GDM131076:GDP131079 GNI131076:GNL131079 GXE131076:GXH131079 HHA131076:HHD131079 HQW131076:HQZ131079 IAS131076:IAV131079 IKO131076:IKR131079 IUK131076:IUN131079 JEG131076:JEJ131079 JOC131076:JOF131079 JXY131076:JYB131079 KHU131076:KHX131079 KRQ131076:KRT131079 LBM131076:LBP131079 LLI131076:LLL131079 LVE131076:LVH131079 MFA131076:MFD131079 MOW131076:MOZ131079 MYS131076:MYV131079 NIO131076:NIR131079 NSK131076:NSN131079 OCG131076:OCJ131079 OMC131076:OMF131079 OVY131076:OWB131079 PFU131076:PFX131079 PPQ131076:PPT131079 PZM131076:PZP131079 QJI131076:QJL131079 QTE131076:QTH131079 RDA131076:RDD131079 RMW131076:RMZ131079 RWS131076:RWV131079 SGO131076:SGR131079 SQK131076:SQN131079 TAG131076:TAJ131079 TKC131076:TKF131079 TTY131076:TUB131079 UDU131076:UDX131079 UNQ131076:UNT131079 UXM131076:UXP131079 VHI131076:VHL131079 VRE131076:VRH131079 WBA131076:WBD131079 WKW131076:WKZ131079 WUS131076:WUV131079 V196612:Y196615 IG196612:IJ196615 SC196612:SF196615 ABY196612:ACB196615 ALU196612:ALX196615 AVQ196612:AVT196615 BFM196612:BFP196615 BPI196612:BPL196615 BZE196612:BZH196615 CJA196612:CJD196615 CSW196612:CSZ196615 DCS196612:DCV196615 DMO196612:DMR196615 DWK196612:DWN196615 EGG196612:EGJ196615 EQC196612:EQF196615 EZY196612:FAB196615 FJU196612:FJX196615 FTQ196612:FTT196615 GDM196612:GDP196615 GNI196612:GNL196615 GXE196612:GXH196615 HHA196612:HHD196615 HQW196612:HQZ196615 IAS196612:IAV196615 IKO196612:IKR196615 IUK196612:IUN196615 JEG196612:JEJ196615 JOC196612:JOF196615 JXY196612:JYB196615 KHU196612:KHX196615 KRQ196612:KRT196615 LBM196612:LBP196615 LLI196612:LLL196615 LVE196612:LVH196615 MFA196612:MFD196615 MOW196612:MOZ196615 MYS196612:MYV196615 NIO196612:NIR196615 NSK196612:NSN196615 OCG196612:OCJ196615 OMC196612:OMF196615 OVY196612:OWB196615 PFU196612:PFX196615 PPQ196612:PPT196615 PZM196612:PZP196615 QJI196612:QJL196615 QTE196612:QTH196615 RDA196612:RDD196615 RMW196612:RMZ196615 RWS196612:RWV196615 SGO196612:SGR196615 SQK196612:SQN196615 TAG196612:TAJ196615 TKC196612:TKF196615 TTY196612:TUB196615 UDU196612:UDX196615 UNQ196612:UNT196615 UXM196612:UXP196615 VHI196612:VHL196615 VRE196612:VRH196615 WBA196612:WBD196615 WKW196612:WKZ196615 WUS196612:WUV196615 V262148:Y262151 IG262148:IJ262151 SC262148:SF262151 ABY262148:ACB262151 ALU262148:ALX262151 AVQ262148:AVT262151 BFM262148:BFP262151 BPI262148:BPL262151 BZE262148:BZH262151 CJA262148:CJD262151 CSW262148:CSZ262151 DCS262148:DCV262151 DMO262148:DMR262151 DWK262148:DWN262151 EGG262148:EGJ262151 EQC262148:EQF262151 EZY262148:FAB262151 FJU262148:FJX262151 FTQ262148:FTT262151 GDM262148:GDP262151 GNI262148:GNL262151 GXE262148:GXH262151 HHA262148:HHD262151 HQW262148:HQZ262151 IAS262148:IAV262151 IKO262148:IKR262151 IUK262148:IUN262151 JEG262148:JEJ262151 JOC262148:JOF262151 JXY262148:JYB262151 KHU262148:KHX262151 KRQ262148:KRT262151 LBM262148:LBP262151 LLI262148:LLL262151 LVE262148:LVH262151 MFA262148:MFD262151 MOW262148:MOZ262151 MYS262148:MYV262151 NIO262148:NIR262151 NSK262148:NSN262151 OCG262148:OCJ262151 OMC262148:OMF262151 OVY262148:OWB262151 PFU262148:PFX262151 PPQ262148:PPT262151 PZM262148:PZP262151 QJI262148:QJL262151 QTE262148:QTH262151 RDA262148:RDD262151 RMW262148:RMZ262151 RWS262148:RWV262151 SGO262148:SGR262151 SQK262148:SQN262151 TAG262148:TAJ262151 TKC262148:TKF262151 TTY262148:TUB262151 UDU262148:UDX262151 UNQ262148:UNT262151 UXM262148:UXP262151 VHI262148:VHL262151 VRE262148:VRH262151 WBA262148:WBD262151 WKW262148:WKZ262151 WUS262148:WUV262151 V327684:Y327687 IG327684:IJ327687 SC327684:SF327687 ABY327684:ACB327687 ALU327684:ALX327687 AVQ327684:AVT327687 BFM327684:BFP327687 BPI327684:BPL327687 BZE327684:BZH327687 CJA327684:CJD327687 CSW327684:CSZ327687 DCS327684:DCV327687 DMO327684:DMR327687 DWK327684:DWN327687 EGG327684:EGJ327687 EQC327684:EQF327687 EZY327684:FAB327687 FJU327684:FJX327687 FTQ327684:FTT327687 GDM327684:GDP327687 GNI327684:GNL327687 GXE327684:GXH327687 HHA327684:HHD327687 HQW327684:HQZ327687 IAS327684:IAV327687 IKO327684:IKR327687 IUK327684:IUN327687 JEG327684:JEJ327687 JOC327684:JOF327687 JXY327684:JYB327687 KHU327684:KHX327687 KRQ327684:KRT327687 LBM327684:LBP327687 LLI327684:LLL327687 LVE327684:LVH327687 MFA327684:MFD327687 MOW327684:MOZ327687 MYS327684:MYV327687 NIO327684:NIR327687 NSK327684:NSN327687 OCG327684:OCJ327687 OMC327684:OMF327687 OVY327684:OWB327687 PFU327684:PFX327687 PPQ327684:PPT327687 PZM327684:PZP327687 QJI327684:QJL327687 QTE327684:QTH327687 RDA327684:RDD327687 RMW327684:RMZ327687 RWS327684:RWV327687 SGO327684:SGR327687 SQK327684:SQN327687 TAG327684:TAJ327687 TKC327684:TKF327687 TTY327684:TUB327687 UDU327684:UDX327687 UNQ327684:UNT327687 UXM327684:UXP327687 VHI327684:VHL327687 VRE327684:VRH327687 WBA327684:WBD327687 WKW327684:WKZ327687 WUS327684:WUV327687 V393220:Y393223 IG393220:IJ393223 SC393220:SF393223 ABY393220:ACB393223 ALU393220:ALX393223 AVQ393220:AVT393223 BFM393220:BFP393223 BPI393220:BPL393223 BZE393220:BZH393223 CJA393220:CJD393223 CSW393220:CSZ393223 DCS393220:DCV393223 DMO393220:DMR393223 DWK393220:DWN393223 EGG393220:EGJ393223 EQC393220:EQF393223 EZY393220:FAB393223 FJU393220:FJX393223 FTQ393220:FTT393223 GDM393220:GDP393223 GNI393220:GNL393223 GXE393220:GXH393223 HHA393220:HHD393223 HQW393220:HQZ393223 IAS393220:IAV393223 IKO393220:IKR393223 IUK393220:IUN393223 JEG393220:JEJ393223 JOC393220:JOF393223 JXY393220:JYB393223 KHU393220:KHX393223 KRQ393220:KRT393223 LBM393220:LBP393223 LLI393220:LLL393223 LVE393220:LVH393223 MFA393220:MFD393223 MOW393220:MOZ393223 MYS393220:MYV393223 NIO393220:NIR393223 NSK393220:NSN393223 OCG393220:OCJ393223 OMC393220:OMF393223 OVY393220:OWB393223 PFU393220:PFX393223 PPQ393220:PPT393223 PZM393220:PZP393223 QJI393220:QJL393223 QTE393220:QTH393223 RDA393220:RDD393223 RMW393220:RMZ393223 RWS393220:RWV393223 SGO393220:SGR393223 SQK393220:SQN393223 TAG393220:TAJ393223 TKC393220:TKF393223 TTY393220:TUB393223 UDU393220:UDX393223 UNQ393220:UNT393223 UXM393220:UXP393223 VHI393220:VHL393223 VRE393220:VRH393223 WBA393220:WBD393223 WKW393220:WKZ393223 WUS393220:WUV393223 V458756:Y458759 IG458756:IJ458759 SC458756:SF458759 ABY458756:ACB458759 ALU458756:ALX458759 AVQ458756:AVT458759 BFM458756:BFP458759 BPI458756:BPL458759 BZE458756:BZH458759 CJA458756:CJD458759 CSW458756:CSZ458759 DCS458756:DCV458759 DMO458756:DMR458759 DWK458756:DWN458759 EGG458756:EGJ458759 EQC458756:EQF458759 EZY458756:FAB458759 FJU458756:FJX458759 FTQ458756:FTT458759 GDM458756:GDP458759 GNI458756:GNL458759 GXE458756:GXH458759 HHA458756:HHD458759 HQW458756:HQZ458759 IAS458756:IAV458759 IKO458756:IKR458759 IUK458756:IUN458759 JEG458756:JEJ458759 JOC458756:JOF458759 JXY458756:JYB458759 KHU458756:KHX458759 KRQ458756:KRT458759 LBM458756:LBP458759 LLI458756:LLL458759 LVE458756:LVH458759 MFA458756:MFD458759 MOW458756:MOZ458759 MYS458756:MYV458759 NIO458756:NIR458759 NSK458756:NSN458759 OCG458756:OCJ458759 OMC458756:OMF458759 OVY458756:OWB458759 PFU458756:PFX458759 PPQ458756:PPT458759 PZM458756:PZP458759 QJI458756:QJL458759 QTE458756:QTH458759 RDA458756:RDD458759 RMW458756:RMZ458759 RWS458756:RWV458759 SGO458756:SGR458759 SQK458756:SQN458759 TAG458756:TAJ458759 TKC458756:TKF458759 TTY458756:TUB458759 UDU458756:UDX458759 UNQ458756:UNT458759 UXM458756:UXP458759 VHI458756:VHL458759 VRE458756:VRH458759 WBA458756:WBD458759 WKW458756:WKZ458759 WUS458756:WUV458759 V524292:Y524295 IG524292:IJ524295 SC524292:SF524295 ABY524292:ACB524295 ALU524292:ALX524295 AVQ524292:AVT524295 BFM524292:BFP524295 BPI524292:BPL524295 BZE524292:BZH524295 CJA524292:CJD524295 CSW524292:CSZ524295 DCS524292:DCV524295 DMO524292:DMR524295 DWK524292:DWN524295 EGG524292:EGJ524295 EQC524292:EQF524295 EZY524292:FAB524295 FJU524292:FJX524295 FTQ524292:FTT524295 GDM524292:GDP524295 GNI524292:GNL524295 GXE524292:GXH524295 HHA524292:HHD524295 HQW524292:HQZ524295 IAS524292:IAV524295 IKO524292:IKR524295 IUK524292:IUN524295 JEG524292:JEJ524295 JOC524292:JOF524295 JXY524292:JYB524295 KHU524292:KHX524295 KRQ524292:KRT524295 LBM524292:LBP524295 LLI524292:LLL524295 LVE524292:LVH524295 MFA524292:MFD524295 MOW524292:MOZ524295 MYS524292:MYV524295 NIO524292:NIR524295 NSK524292:NSN524295 OCG524292:OCJ524295 OMC524292:OMF524295 OVY524292:OWB524295 PFU524292:PFX524295 PPQ524292:PPT524295 PZM524292:PZP524295 QJI524292:QJL524295 QTE524292:QTH524295 RDA524292:RDD524295 RMW524292:RMZ524295 RWS524292:RWV524295 SGO524292:SGR524295 SQK524292:SQN524295 TAG524292:TAJ524295 TKC524292:TKF524295 TTY524292:TUB524295 UDU524292:UDX524295 UNQ524292:UNT524295 UXM524292:UXP524295 VHI524292:VHL524295 VRE524292:VRH524295 WBA524292:WBD524295 WKW524292:WKZ524295 WUS524292:WUV524295 V589828:Y589831 IG589828:IJ589831 SC589828:SF589831 ABY589828:ACB589831 ALU589828:ALX589831 AVQ589828:AVT589831 BFM589828:BFP589831 BPI589828:BPL589831 BZE589828:BZH589831 CJA589828:CJD589831 CSW589828:CSZ589831 DCS589828:DCV589831 DMO589828:DMR589831 DWK589828:DWN589831 EGG589828:EGJ589831 EQC589828:EQF589831 EZY589828:FAB589831 FJU589828:FJX589831 FTQ589828:FTT589831 GDM589828:GDP589831 GNI589828:GNL589831 GXE589828:GXH589831 HHA589828:HHD589831 HQW589828:HQZ589831 IAS589828:IAV589831 IKO589828:IKR589831 IUK589828:IUN589831 JEG589828:JEJ589831 JOC589828:JOF589831 JXY589828:JYB589831 KHU589828:KHX589831 KRQ589828:KRT589831 LBM589828:LBP589831 LLI589828:LLL589831 LVE589828:LVH589831 MFA589828:MFD589831 MOW589828:MOZ589831 MYS589828:MYV589831 NIO589828:NIR589831 NSK589828:NSN589831 OCG589828:OCJ589831 OMC589828:OMF589831 OVY589828:OWB589831 PFU589828:PFX589831 PPQ589828:PPT589831 PZM589828:PZP589831 QJI589828:QJL589831 QTE589828:QTH589831 RDA589828:RDD589831 RMW589828:RMZ589831 RWS589828:RWV589831 SGO589828:SGR589831 SQK589828:SQN589831 TAG589828:TAJ589831 TKC589828:TKF589831 TTY589828:TUB589831 UDU589828:UDX589831 UNQ589828:UNT589831 UXM589828:UXP589831 VHI589828:VHL589831 VRE589828:VRH589831 WBA589828:WBD589831 WKW589828:WKZ589831 WUS589828:WUV589831 V655364:Y655367 IG655364:IJ655367 SC655364:SF655367 ABY655364:ACB655367 ALU655364:ALX655367 AVQ655364:AVT655367 BFM655364:BFP655367 BPI655364:BPL655367 BZE655364:BZH655367 CJA655364:CJD655367 CSW655364:CSZ655367 DCS655364:DCV655367 DMO655364:DMR655367 DWK655364:DWN655367 EGG655364:EGJ655367 EQC655364:EQF655367 EZY655364:FAB655367 FJU655364:FJX655367 FTQ655364:FTT655367 GDM655364:GDP655367 GNI655364:GNL655367 GXE655364:GXH655367 HHA655364:HHD655367 HQW655364:HQZ655367 IAS655364:IAV655367 IKO655364:IKR655367 IUK655364:IUN655367 JEG655364:JEJ655367 JOC655364:JOF655367 JXY655364:JYB655367 KHU655364:KHX655367 KRQ655364:KRT655367 LBM655364:LBP655367 LLI655364:LLL655367 LVE655364:LVH655367 MFA655364:MFD655367 MOW655364:MOZ655367 MYS655364:MYV655367 NIO655364:NIR655367 NSK655364:NSN655367 OCG655364:OCJ655367 OMC655364:OMF655367 OVY655364:OWB655367 PFU655364:PFX655367 PPQ655364:PPT655367 PZM655364:PZP655367 QJI655364:QJL655367 QTE655364:QTH655367 RDA655364:RDD655367 RMW655364:RMZ655367 RWS655364:RWV655367 SGO655364:SGR655367 SQK655364:SQN655367 TAG655364:TAJ655367 TKC655364:TKF655367 TTY655364:TUB655367 UDU655364:UDX655367 UNQ655364:UNT655367 UXM655364:UXP655367 VHI655364:VHL655367 VRE655364:VRH655367 WBA655364:WBD655367 WKW655364:WKZ655367 WUS655364:WUV655367 V720900:Y720903 IG720900:IJ720903 SC720900:SF720903 ABY720900:ACB720903 ALU720900:ALX720903 AVQ720900:AVT720903 BFM720900:BFP720903 BPI720900:BPL720903 BZE720900:BZH720903 CJA720900:CJD720903 CSW720900:CSZ720903 DCS720900:DCV720903 DMO720900:DMR720903 DWK720900:DWN720903 EGG720900:EGJ720903 EQC720900:EQF720903 EZY720900:FAB720903 FJU720900:FJX720903 FTQ720900:FTT720903 GDM720900:GDP720903 GNI720900:GNL720903 GXE720900:GXH720903 HHA720900:HHD720903 HQW720900:HQZ720903 IAS720900:IAV720903 IKO720900:IKR720903 IUK720900:IUN720903 JEG720900:JEJ720903 JOC720900:JOF720903 JXY720900:JYB720903 KHU720900:KHX720903 KRQ720900:KRT720903 LBM720900:LBP720903 LLI720900:LLL720903 LVE720900:LVH720903 MFA720900:MFD720903 MOW720900:MOZ720903 MYS720900:MYV720903 NIO720900:NIR720903 NSK720900:NSN720903 OCG720900:OCJ720903 OMC720900:OMF720903 OVY720900:OWB720903 PFU720900:PFX720903 PPQ720900:PPT720903 PZM720900:PZP720903 QJI720900:QJL720903 QTE720900:QTH720903 RDA720900:RDD720903 RMW720900:RMZ720903 RWS720900:RWV720903 SGO720900:SGR720903 SQK720900:SQN720903 TAG720900:TAJ720903 TKC720900:TKF720903 TTY720900:TUB720903 UDU720900:UDX720903 UNQ720900:UNT720903 UXM720900:UXP720903 VHI720900:VHL720903 VRE720900:VRH720903 WBA720900:WBD720903 WKW720900:WKZ720903 WUS720900:WUV720903 V786436:Y786439 IG786436:IJ786439 SC786436:SF786439 ABY786436:ACB786439 ALU786436:ALX786439 AVQ786436:AVT786439 BFM786436:BFP786439 BPI786436:BPL786439 BZE786436:BZH786439 CJA786436:CJD786439 CSW786436:CSZ786439 DCS786436:DCV786439 DMO786436:DMR786439 DWK786436:DWN786439 EGG786436:EGJ786439 EQC786436:EQF786439 EZY786436:FAB786439 FJU786436:FJX786439 FTQ786436:FTT786439 GDM786436:GDP786439 GNI786436:GNL786439 GXE786436:GXH786439 HHA786436:HHD786439 HQW786436:HQZ786439 IAS786436:IAV786439 IKO786436:IKR786439 IUK786436:IUN786439 JEG786436:JEJ786439 JOC786436:JOF786439 JXY786436:JYB786439 KHU786436:KHX786439 KRQ786436:KRT786439 LBM786436:LBP786439 LLI786436:LLL786439 LVE786436:LVH786439 MFA786436:MFD786439 MOW786436:MOZ786439 MYS786436:MYV786439 NIO786436:NIR786439 NSK786436:NSN786439 OCG786436:OCJ786439 OMC786436:OMF786439 OVY786436:OWB786439 PFU786436:PFX786439 PPQ786436:PPT786439 PZM786436:PZP786439 QJI786436:QJL786439 QTE786436:QTH786439 RDA786436:RDD786439 RMW786436:RMZ786439 RWS786436:RWV786439 SGO786436:SGR786439 SQK786436:SQN786439 TAG786436:TAJ786439 TKC786436:TKF786439 TTY786436:TUB786439 UDU786436:UDX786439 UNQ786436:UNT786439 UXM786436:UXP786439 VHI786436:VHL786439 VRE786436:VRH786439 WBA786436:WBD786439 WKW786436:WKZ786439 WUS786436:WUV786439 V851972:Y851975 IG851972:IJ851975 SC851972:SF851975 ABY851972:ACB851975 ALU851972:ALX851975 AVQ851972:AVT851975 BFM851972:BFP851975 BPI851972:BPL851975 BZE851972:BZH851975 CJA851972:CJD851975 CSW851972:CSZ851975 DCS851972:DCV851975 DMO851972:DMR851975 DWK851972:DWN851975 EGG851972:EGJ851975 EQC851972:EQF851975 EZY851972:FAB851975 FJU851972:FJX851975 FTQ851972:FTT851975 GDM851972:GDP851975 GNI851972:GNL851975 GXE851972:GXH851975 HHA851972:HHD851975 HQW851972:HQZ851975 IAS851972:IAV851975 IKO851972:IKR851975 IUK851972:IUN851975 JEG851972:JEJ851975 JOC851972:JOF851975 JXY851972:JYB851975 KHU851972:KHX851975 KRQ851972:KRT851975 LBM851972:LBP851975 LLI851972:LLL851975 LVE851972:LVH851975 MFA851972:MFD851975 MOW851972:MOZ851975 MYS851972:MYV851975 NIO851972:NIR851975 NSK851972:NSN851975 OCG851972:OCJ851975 OMC851972:OMF851975 OVY851972:OWB851975 PFU851972:PFX851975 PPQ851972:PPT851975 PZM851972:PZP851975 QJI851972:QJL851975 QTE851972:QTH851975 RDA851972:RDD851975 RMW851972:RMZ851975 RWS851972:RWV851975 SGO851972:SGR851975 SQK851972:SQN851975 TAG851972:TAJ851975 TKC851972:TKF851975 TTY851972:TUB851975 UDU851972:UDX851975 UNQ851972:UNT851975 UXM851972:UXP851975 VHI851972:VHL851975 VRE851972:VRH851975 WBA851972:WBD851975 WKW851972:WKZ851975 WUS851972:WUV851975 V917508:Y917511 IG917508:IJ917511 SC917508:SF917511 ABY917508:ACB917511 ALU917508:ALX917511 AVQ917508:AVT917511 BFM917508:BFP917511 BPI917508:BPL917511 BZE917508:BZH917511 CJA917508:CJD917511 CSW917508:CSZ917511 DCS917508:DCV917511 DMO917508:DMR917511 DWK917508:DWN917511 EGG917508:EGJ917511 EQC917508:EQF917511 EZY917508:FAB917511 FJU917508:FJX917511 FTQ917508:FTT917511 GDM917508:GDP917511 GNI917508:GNL917511 GXE917508:GXH917511 HHA917508:HHD917511 HQW917508:HQZ917511 IAS917508:IAV917511 IKO917508:IKR917511 IUK917508:IUN917511 JEG917508:JEJ917511 JOC917508:JOF917511 JXY917508:JYB917511 KHU917508:KHX917511 KRQ917508:KRT917511 LBM917508:LBP917511 LLI917508:LLL917511 LVE917508:LVH917511 MFA917508:MFD917511 MOW917508:MOZ917511 MYS917508:MYV917511 NIO917508:NIR917511 NSK917508:NSN917511 OCG917508:OCJ917511 OMC917508:OMF917511 OVY917508:OWB917511 PFU917508:PFX917511 PPQ917508:PPT917511 PZM917508:PZP917511 QJI917508:QJL917511 QTE917508:QTH917511 RDA917508:RDD917511 RMW917508:RMZ917511 RWS917508:RWV917511 SGO917508:SGR917511 SQK917508:SQN917511 TAG917508:TAJ917511 TKC917508:TKF917511 TTY917508:TUB917511 UDU917508:UDX917511 UNQ917508:UNT917511 UXM917508:UXP917511 VHI917508:VHL917511 VRE917508:VRH917511 WBA917508:WBD917511 WKW917508:WKZ917511 WUS917508:WUV917511 V983044:Y983047 IG983044:IJ983047 SC983044:SF983047 ABY983044:ACB983047 ALU983044:ALX983047 AVQ983044:AVT983047 BFM983044:BFP983047 BPI983044:BPL983047 BZE983044:BZH983047 CJA983044:CJD983047 CSW983044:CSZ983047 DCS983044:DCV983047 DMO983044:DMR983047 DWK983044:DWN983047 EGG983044:EGJ983047 EQC983044:EQF983047 EZY983044:FAB983047 FJU983044:FJX983047 FTQ983044:FTT983047 GDM983044:GDP983047 GNI983044:GNL983047 GXE983044:GXH983047 HHA983044:HHD983047 HQW983044:HQZ983047 IAS983044:IAV983047 IKO983044:IKR983047 IUK983044:IUN983047 JEG983044:JEJ983047 JOC983044:JOF983047 JXY983044:JYB983047 KHU983044:KHX983047 KRQ983044:KRT983047 LBM983044:LBP983047 LLI983044:LLL983047 LVE983044:LVH983047 MFA983044:MFD983047 MOW983044:MOZ983047 MYS983044:MYV983047 NIO983044:NIR983047 NSK983044:NSN983047 OCG983044:OCJ983047 OMC983044:OMF983047 OVY983044:OWB983047 PFU983044:PFX983047 PPQ983044:PPT983047 PZM983044:PZP983047 QJI983044:QJL983047 QTE983044:QTH983047 RDA983044:RDD983047 RMW983044:RMZ983047 RWS983044:RWV983047 SGO983044:SGR983047 SQK983044:SQN983047 TAG983044:TAJ983047 TKC983044:TKF983047 TTY983044:TUB983047 UDU983044:UDX983047 UNQ983044:UNT983047 UXM983044:UXP983047 VHI983044:VHL983047 VRE983044:VRH983047 WBA983044:WBD983047 WKW983044:WKZ983047 WUS983044:WUV983047 Q65534:T65534 IB65534:IE65534 RX65534:SA65534 ABT65534:ABW65534 ALP65534:ALS65534 AVL65534:AVO65534 BFH65534:BFK65534 BPD65534:BPG65534 BYZ65534:BZC65534 CIV65534:CIY65534 CSR65534:CSU65534 DCN65534:DCQ65534 DMJ65534:DMM65534 DWF65534:DWI65534 EGB65534:EGE65534 EPX65534:EQA65534 EZT65534:EZW65534 FJP65534:FJS65534 FTL65534:FTO65534 GDH65534:GDK65534 GND65534:GNG65534 GWZ65534:GXC65534 HGV65534:HGY65534 HQR65534:HQU65534 IAN65534:IAQ65534 IKJ65534:IKM65534 IUF65534:IUI65534 JEB65534:JEE65534 JNX65534:JOA65534 JXT65534:JXW65534 KHP65534:KHS65534 KRL65534:KRO65534 LBH65534:LBK65534 LLD65534:LLG65534 LUZ65534:LVC65534 MEV65534:MEY65534 MOR65534:MOU65534 MYN65534:MYQ65534 NIJ65534:NIM65534 NSF65534:NSI65534 OCB65534:OCE65534 OLX65534:OMA65534 OVT65534:OVW65534 PFP65534:PFS65534 PPL65534:PPO65534 PZH65534:PZK65534 QJD65534:QJG65534 QSZ65534:QTC65534 RCV65534:RCY65534 RMR65534:RMU65534 RWN65534:RWQ65534 SGJ65534:SGM65534 SQF65534:SQI65534 TAB65534:TAE65534 TJX65534:TKA65534 TTT65534:TTW65534 UDP65534:UDS65534 UNL65534:UNO65534 UXH65534:UXK65534 VHD65534:VHG65534 VQZ65534:VRC65534 WAV65534:WAY65534 WKR65534:WKU65534 WUN65534:WUQ65534 Q131070:T131070 IB131070:IE131070 RX131070:SA131070 ABT131070:ABW131070 ALP131070:ALS131070 AVL131070:AVO131070 BFH131070:BFK131070 BPD131070:BPG131070 BYZ131070:BZC131070 CIV131070:CIY131070 CSR131070:CSU131070 DCN131070:DCQ131070 DMJ131070:DMM131070 DWF131070:DWI131070 EGB131070:EGE131070 EPX131070:EQA131070 EZT131070:EZW131070 FJP131070:FJS131070 FTL131070:FTO131070 GDH131070:GDK131070 GND131070:GNG131070 GWZ131070:GXC131070 HGV131070:HGY131070 HQR131070:HQU131070 IAN131070:IAQ131070 IKJ131070:IKM131070 IUF131070:IUI131070 JEB131070:JEE131070 JNX131070:JOA131070 JXT131070:JXW131070 KHP131070:KHS131070 KRL131070:KRO131070 LBH131070:LBK131070 LLD131070:LLG131070 LUZ131070:LVC131070 MEV131070:MEY131070 MOR131070:MOU131070 MYN131070:MYQ131070 NIJ131070:NIM131070 NSF131070:NSI131070 OCB131070:OCE131070 OLX131070:OMA131070 OVT131070:OVW131070 PFP131070:PFS131070 PPL131070:PPO131070 PZH131070:PZK131070 QJD131070:QJG131070 QSZ131070:QTC131070 RCV131070:RCY131070 RMR131070:RMU131070 RWN131070:RWQ131070 SGJ131070:SGM131070 SQF131070:SQI131070 TAB131070:TAE131070 TJX131070:TKA131070 TTT131070:TTW131070 UDP131070:UDS131070 UNL131070:UNO131070 UXH131070:UXK131070 VHD131070:VHG131070 VQZ131070:VRC131070 WAV131070:WAY131070 WKR131070:WKU131070 WUN131070:WUQ131070 Q196606:T196606 IB196606:IE196606 RX196606:SA196606 ABT196606:ABW196606 ALP196606:ALS196606 AVL196606:AVO196606 BFH196606:BFK196606 BPD196606:BPG196606 BYZ196606:BZC196606 CIV196606:CIY196606 CSR196606:CSU196606 DCN196606:DCQ196606 DMJ196606:DMM196606 DWF196606:DWI196606 EGB196606:EGE196606 EPX196606:EQA196606 EZT196606:EZW196606 FJP196606:FJS196606 FTL196606:FTO196606 GDH196606:GDK196606 GND196606:GNG196606 GWZ196606:GXC196606 HGV196606:HGY196606 HQR196606:HQU196606 IAN196606:IAQ196606 IKJ196606:IKM196606 IUF196606:IUI196606 JEB196606:JEE196606 JNX196606:JOA196606 JXT196606:JXW196606 KHP196606:KHS196606 KRL196606:KRO196606 LBH196606:LBK196606 LLD196606:LLG196606 LUZ196606:LVC196606 MEV196606:MEY196606 MOR196606:MOU196606 MYN196606:MYQ196606 NIJ196606:NIM196606 NSF196606:NSI196606 OCB196606:OCE196606 OLX196606:OMA196606 OVT196606:OVW196606 PFP196606:PFS196606 PPL196606:PPO196606 PZH196606:PZK196606 QJD196606:QJG196606 QSZ196606:QTC196606 RCV196606:RCY196606 RMR196606:RMU196606 RWN196606:RWQ196606 SGJ196606:SGM196606 SQF196606:SQI196606 TAB196606:TAE196606 TJX196606:TKA196606 TTT196606:TTW196606 UDP196606:UDS196606 UNL196606:UNO196606 UXH196606:UXK196606 VHD196606:VHG196606 VQZ196606:VRC196606 WAV196606:WAY196606 WKR196606:WKU196606 WUN196606:WUQ196606 Q262142:T262142 IB262142:IE262142 RX262142:SA262142 ABT262142:ABW262142 ALP262142:ALS262142 AVL262142:AVO262142 BFH262142:BFK262142 BPD262142:BPG262142 BYZ262142:BZC262142 CIV262142:CIY262142 CSR262142:CSU262142 DCN262142:DCQ262142 DMJ262142:DMM262142 DWF262142:DWI262142 EGB262142:EGE262142 EPX262142:EQA262142 EZT262142:EZW262142 FJP262142:FJS262142 FTL262142:FTO262142 GDH262142:GDK262142 GND262142:GNG262142 GWZ262142:GXC262142 HGV262142:HGY262142 HQR262142:HQU262142 IAN262142:IAQ262142 IKJ262142:IKM262142 IUF262142:IUI262142 JEB262142:JEE262142 JNX262142:JOA262142 JXT262142:JXW262142 KHP262142:KHS262142 KRL262142:KRO262142 LBH262142:LBK262142 LLD262142:LLG262142 LUZ262142:LVC262142 MEV262142:MEY262142 MOR262142:MOU262142 MYN262142:MYQ262142 NIJ262142:NIM262142 NSF262142:NSI262142 OCB262142:OCE262142 OLX262142:OMA262142 OVT262142:OVW262142 PFP262142:PFS262142 PPL262142:PPO262142 PZH262142:PZK262142 QJD262142:QJG262142 QSZ262142:QTC262142 RCV262142:RCY262142 RMR262142:RMU262142 RWN262142:RWQ262142 SGJ262142:SGM262142 SQF262142:SQI262142 TAB262142:TAE262142 TJX262142:TKA262142 TTT262142:TTW262142 UDP262142:UDS262142 UNL262142:UNO262142 UXH262142:UXK262142 VHD262142:VHG262142 VQZ262142:VRC262142 WAV262142:WAY262142 WKR262142:WKU262142 WUN262142:WUQ262142 Q327678:T327678 IB327678:IE327678 RX327678:SA327678 ABT327678:ABW327678 ALP327678:ALS327678 AVL327678:AVO327678 BFH327678:BFK327678 BPD327678:BPG327678 BYZ327678:BZC327678 CIV327678:CIY327678 CSR327678:CSU327678 DCN327678:DCQ327678 DMJ327678:DMM327678 DWF327678:DWI327678 EGB327678:EGE327678 EPX327678:EQA327678 EZT327678:EZW327678 FJP327678:FJS327678 FTL327678:FTO327678 GDH327678:GDK327678 GND327678:GNG327678 GWZ327678:GXC327678 HGV327678:HGY327678 HQR327678:HQU327678 IAN327678:IAQ327678 IKJ327678:IKM327678 IUF327678:IUI327678 JEB327678:JEE327678 JNX327678:JOA327678 JXT327678:JXW327678 KHP327678:KHS327678 KRL327678:KRO327678 LBH327678:LBK327678 LLD327678:LLG327678 LUZ327678:LVC327678 MEV327678:MEY327678 MOR327678:MOU327678 MYN327678:MYQ327678 NIJ327678:NIM327678 NSF327678:NSI327678 OCB327678:OCE327678 OLX327678:OMA327678 OVT327678:OVW327678 PFP327678:PFS327678 PPL327678:PPO327678 PZH327678:PZK327678 QJD327678:QJG327678 QSZ327678:QTC327678 RCV327678:RCY327678 RMR327678:RMU327678 RWN327678:RWQ327678 SGJ327678:SGM327678 SQF327678:SQI327678 TAB327678:TAE327678 TJX327678:TKA327678 TTT327678:TTW327678 UDP327678:UDS327678 UNL327678:UNO327678 UXH327678:UXK327678 VHD327678:VHG327678 VQZ327678:VRC327678 WAV327678:WAY327678 WKR327678:WKU327678 WUN327678:WUQ327678 Q393214:T393214 IB393214:IE393214 RX393214:SA393214 ABT393214:ABW393214 ALP393214:ALS393214 AVL393214:AVO393214 BFH393214:BFK393214 BPD393214:BPG393214 BYZ393214:BZC393214 CIV393214:CIY393214 CSR393214:CSU393214 DCN393214:DCQ393214 DMJ393214:DMM393214 DWF393214:DWI393214 EGB393214:EGE393214 EPX393214:EQA393214 EZT393214:EZW393214 FJP393214:FJS393214 FTL393214:FTO393214 GDH393214:GDK393214 GND393214:GNG393214 GWZ393214:GXC393214 HGV393214:HGY393214 HQR393214:HQU393214 IAN393214:IAQ393214 IKJ393214:IKM393214 IUF393214:IUI393214 JEB393214:JEE393214 JNX393214:JOA393214 JXT393214:JXW393214 KHP393214:KHS393214 KRL393214:KRO393214 LBH393214:LBK393214 LLD393214:LLG393214 LUZ393214:LVC393214 MEV393214:MEY393214 MOR393214:MOU393214 MYN393214:MYQ393214 NIJ393214:NIM393214 NSF393214:NSI393214 OCB393214:OCE393214 OLX393214:OMA393214 OVT393214:OVW393214 PFP393214:PFS393214 PPL393214:PPO393214 PZH393214:PZK393214 QJD393214:QJG393214 QSZ393214:QTC393214 RCV393214:RCY393214 RMR393214:RMU393214 RWN393214:RWQ393214 SGJ393214:SGM393214 SQF393214:SQI393214 TAB393214:TAE393214 TJX393214:TKA393214 TTT393214:TTW393214 UDP393214:UDS393214 UNL393214:UNO393214 UXH393214:UXK393214 VHD393214:VHG393214 VQZ393214:VRC393214 WAV393214:WAY393214 WKR393214:WKU393214 WUN393214:WUQ393214 Q458750:T458750 IB458750:IE458750 RX458750:SA458750 ABT458750:ABW458750 ALP458750:ALS458750 AVL458750:AVO458750 BFH458750:BFK458750 BPD458750:BPG458750 BYZ458750:BZC458750 CIV458750:CIY458750 CSR458750:CSU458750 DCN458750:DCQ458750 DMJ458750:DMM458750 DWF458750:DWI458750 EGB458750:EGE458750 EPX458750:EQA458750 EZT458750:EZW458750 FJP458750:FJS458750 FTL458750:FTO458750 GDH458750:GDK458750 GND458750:GNG458750 GWZ458750:GXC458750 HGV458750:HGY458750 HQR458750:HQU458750 IAN458750:IAQ458750 IKJ458750:IKM458750 IUF458750:IUI458750 JEB458750:JEE458750 JNX458750:JOA458750 JXT458750:JXW458750 KHP458750:KHS458750 KRL458750:KRO458750 LBH458750:LBK458750 LLD458750:LLG458750 LUZ458750:LVC458750 MEV458750:MEY458750 MOR458750:MOU458750 MYN458750:MYQ458750 NIJ458750:NIM458750 NSF458750:NSI458750 OCB458750:OCE458750 OLX458750:OMA458750 OVT458750:OVW458750 PFP458750:PFS458750 PPL458750:PPO458750 PZH458750:PZK458750 QJD458750:QJG458750 QSZ458750:QTC458750 RCV458750:RCY458750 RMR458750:RMU458750 RWN458750:RWQ458750 SGJ458750:SGM458750 SQF458750:SQI458750 TAB458750:TAE458750 TJX458750:TKA458750 TTT458750:TTW458750 UDP458750:UDS458750 UNL458750:UNO458750 UXH458750:UXK458750 VHD458750:VHG458750 VQZ458750:VRC458750 WAV458750:WAY458750 WKR458750:WKU458750 WUN458750:WUQ458750 Q524286:T524286 IB524286:IE524286 RX524286:SA524286 ABT524286:ABW524286 ALP524286:ALS524286 AVL524286:AVO524286 BFH524286:BFK524286 BPD524286:BPG524286 BYZ524286:BZC524286 CIV524286:CIY524286 CSR524286:CSU524286 DCN524286:DCQ524286 DMJ524286:DMM524286 DWF524286:DWI524286 EGB524286:EGE524286 EPX524286:EQA524286 EZT524286:EZW524286 FJP524286:FJS524286 FTL524286:FTO524286 GDH524286:GDK524286 GND524286:GNG524286 GWZ524286:GXC524286 HGV524286:HGY524286 HQR524286:HQU524286 IAN524286:IAQ524286 IKJ524286:IKM524286 IUF524286:IUI524286 JEB524286:JEE524286 JNX524286:JOA524286 JXT524286:JXW524286 KHP524286:KHS524286 KRL524286:KRO524286 LBH524286:LBK524286 LLD524286:LLG524286 LUZ524286:LVC524286 MEV524286:MEY524286 MOR524286:MOU524286 MYN524286:MYQ524286 NIJ524286:NIM524286 NSF524286:NSI524286 OCB524286:OCE524286 OLX524286:OMA524286 OVT524286:OVW524286 PFP524286:PFS524286 PPL524286:PPO524286 PZH524286:PZK524286 QJD524286:QJG524286 QSZ524286:QTC524286 RCV524286:RCY524286 RMR524286:RMU524286 RWN524286:RWQ524286 SGJ524286:SGM524286 SQF524286:SQI524286 TAB524286:TAE524286 TJX524286:TKA524286 TTT524286:TTW524286 UDP524286:UDS524286 UNL524286:UNO524286 UXH524286:UXK524286 VHD524286:VHG524286 VQZ524286:VRC524286 WAV524286:WAY524286 WKR524286:WKU524286 WUN524286:WUQ524286 Q589822:T589822 IB589822:IE589822 RX589822:SA589822 ABT589822:ABW589822 ALP589822:ALS589822 AVL589822:AVO589822 BFH589822:BFK589822 BPD589822:BPG589822 BYZ589822:BZC589822 CIV589822:CIY589822 CSR589822:CSU589822 DCN589822:DCQ589822 DMJ589822:DMM589822 DWF589822:DWI589822 EGB589822:EGE589822 EPX589822:EQA589822 EZT589822:EZW589822 FJP589822:FJS589822 FTL589822:FTO589822 GDH589822:GDK589822 GND589822:GNG589822 GWZ589822:GXC589822 HGV589822:HGY589822 HQR589822:HQU589822 IAN589822:IAQ589822 IKJ589822:IKM589822 IUF589822:IUI589822 JEB589822:JEE589822 JNX589822:JOA589822 JXT589822:JXW589822 KHP589822:KHS589822 KRL589822:KRO589822 LBH589822:LBK589822 LLD589822:LLG589822 LUZ589822:LVC589822 MEV589822:MEY589822 MOR589822:MOU589822 MYN589822:MYQ589822 NIJ589822:NIM589822 NSF589822:NSI589822 OCB589822:OCE589822 OLX589822:OMA589822 OVT589822:OVW589822 PFP589822:PFS589822 PPL589822:PPO589822 PZH589822:PZK589822 QJD589822:QJG589822 QSZ589822:QTC589822 RCV589822:RCY589822 RMR589822:RMU589822 RWN589822:RWQ589822 SGJ589822:SGM589822 SQF589822:SQI589822 TAB589822:TAE589822 TJX589822:TKA589822 TTT589822:TTW589822 UDP589822:UDS589822 UNL589822:UNO589822 UXH589822:UXK589822 VHD589822:VHG589822 VQZ589822:VRC589822 WAV589822:WAY589822 WKR589822:WKU589822 WUN589822:WUQ589822 Q655358:T655358 IB655358:IE655358 RX655358:SA655358 ABT655358:ABW655358 ALP655358:ALS655358 AVL655358:AVO655358 BFH655358:BFK655358 BPD655358:BPG655358 BYZ655358:BZC655358 CIV655358:CIY655358 CSR655358:CSU655358 DCN655358:DCQ655358 DMJ655358:DMM655358 DWF655358:DWI655358 EGB655358:EGE655358 EPX655358:EQA655358 EZT655358:EZW655358 FJP655358:FJS655358 FTL655358:FTO655358 GDH655358:GDK655358 GND655358:GNG655358 GWZ655358:GXC655358 HGV655358:HGY655358 HQR655358:HQU655358 IAN655358:IAQ655358 IKJ655358:IKM655358 IUF655358:IUI655358 JEB655358:JEE655358 JNX655358:JOA655358 JXT655358:JXW655358 KHP655358:KHS655358 KRL655358:KRO655358 LBH655358:LBK655358 LLD655358:LLG655358 LUZ655358:LVC655358 MEV655358:MEY655358 MOR655358:MOU655358 MYN655358:MYQ655358 NIJ655358:NIM655358 NSF655358:NSI655358 OCB655358:OCE655358 OLX655358:OMA655358 OVT655358:OVW655358 PFP655358:PFS655358 PPL655358:PPO655358 PZH655358:PZK655358 QJD655358:QJG655358 QSZ655358:QTC655358 RCV655358:RCY655358 RMR655358:RMU655358 RWN655358:RWQ655358 SGJ655358:SGM655358 SQF655358:SQI655358 TAB655358:TAE655358 TJX655358:TKA655358 TTT655358:TTW655358 UDP655358:UDS655358 UNL655358:UNO655358 UXH655358:UXK655358 VHD655358:VHG655358 VQZ655358:VRC655358 WAV655358:WAY655358 WKR655358:WKU655358 WUN655358:WUQ655358 Q720894:T720894 IB720894:IE720894 RX720894:SA720894 ABT720894:ABW720894 ALP720894:ALS720894 AVL720894:AVO720894 BFH720894:BFK720894 BPD720894:BPG720894 BYZ720894:BZC720894 CIV720894:CIY720894 CSR720894:CSU720894 DCN720894:DCQ720894 DMJ720894:DMM720894 DWF720894:DWI720894 EGB720894:EGE720894 EPX720894:EQA720894 EZT720894:EZW720894 FJP720894:FJS720894 FTL720894:FTO720894 GDH720894:GDK720894 GND720894:GNG720894 GWZ720894:GXC720894 HGV720894:HGY720894 HQR720894:HQU720894 IAN720894:IAQ720894 IKJ720894:IKM720894 IUF720894:IUI720894 JEB720894:JEE720894 JNX720894:JOA720894 JXT720894:JXW720894 KHP720894:KHS720894 KRL720894:KRO720894 LBH720894:LBK720894 LLD720894:LLG720894 LUZ720894:LVC720894 MEV720894:MEY720894 MOR720894:MOU720894 MYN720894:MYQ720894 NIJ720894:NIM720894 NSF720894:NSI720894 OCB720894:OCE720894 OLX720894:OMA720894 OVT720894:OVW720894 PFP720894:PFS720894 PPL720894:PPO720894 PZH720894:PZK720894 QJD720894:QJG720894 QSZ720894:QTC720894 RCV720894:RCY720894 RMR720894:RMU720894 RWN720894:RWQ720894 SGJ720894:SGM720894 SQF720894:SQI720894 TAB720894:TAE720894 TJX720894:TKA720894 TTT720894:TTW720894 UDP720894:UDS720894 UNL720894:UNO720894 UXH720894:UXK720894 VHD720894:VHG720894 VQZ720894:VRC720894 WAV720894:WAY720894 WKR720894:WKU720894 WUN720894:WUQ720894 Q786430:T786430 IB786430:IE786430 RX786430:SA786430 ABT786430:ABW786430 ALP786430:ALS786430 AVL786430:AVO786430 BFH786430:BFK786430 BPD786430:BPG786430 BYZ786430:BZC786430 CIV786430:CIY786430 CSR786430:CSU786430 DCN786430:DCQ786430 DMJ786430:DMM786430 DWF786430:DWI786430 EGB786430:EGE786430 EPX786430:EQA786430 EZT786430:EZW786430 FJP786430:FJS786430 FTL786430:FTO786430 GDH786430:GDK786430 GND786430:GNG786430 GWZ786430:GXC786430 HGV786430:HGY786430 HQR786430:HQU786430 IAN786430:IAQ786430 IKJ786430:IKM786430 IUF786430:IUI786430 JEB786430:JEE786430 JNX786430:JOA786430 JXT786430:JXW786430 KHP786430:KHS786430 KRL786430:KRO786430 LBH786430:LBK786430 LLD786430:LLG786430 LUZ786430:LVC786430 MEV786430:MEY786430 MOR786430:MOU786430 MYN786430:MYQ786430 NIJ786430:NIM786430 NSF786430:NSI786430 OCB786430:OCE786430 OLX786430:OMA786430 OVT786430:OVW786430 PFP786430:PFS786430 PPL786430:PPO786430 PZH786430:PZK786430 QJD786430:QJG786430 QSZ786430:QTC786430 RCV786430:RCY786430 RMR786430:RMU786430 RWN786430:RWQ786430 SGJ786430:SGM786430 SQF786430:SQI786430 TAB786430:TAE786430 TJX786430:TKA786430 TTT786430:TTW786430 UDP786430:UDS786430 UNL786430:UNO786430 UXH786430:UXK786430 VHD786430:VHG786430 VQZ786430:VRC786430 WAV786430:WAY786430 WKR786430:WKU786430 WUN786430:WUQ786430 Q851966:T851966 IB851966:IE851966 RX851966:SA851966 ABT851966:ABW851966 ALP851966:ALS851966 AVL851966:AVO851966 BFH851966:BFK851966 BPD851966:BPG851966 BYZ851966:BZC851966 CIV851966:CIY851966 CSR851966:CSU851966 DCN851966:DCQ851966 DMJ851966:DMM851966 DWF851966:DWI851966 EGB851966:EGE851966 EPX851966:EQA851966 EZT851966:EZW851966 FJP851966:FJS851966 FTL851966:FTO851966 GDH851966:GDK851966 GND851966:GNG851966 GWZ851966:GXC851966 HGV851966:HGY851966 HQR851966:HQU851966 IAN851966:IAQ851966 IKJ851966:IKM851966 IUF851966:IUI851966 JEB851966:JEE851966 JNX851966:JOA851966 JXT851966:JXW851966 KHP851966:KHS851966 KRL851966:KRO851966 LBH851966:LBK851966 LLD851966:LLG851966 LUZ851966:LVC851966 MEV851966:MEY851966 MOR851966:MOU851966 MYN851966:MYQ851966 NIJ851966:NIM851966 NSF851966:NSI851966 OCB851966:OCE851966 OLX851966:OMA851966 OVT851966:OVW851966 PFP851966:PFS851966 PPL851966:PPO851966 PZH851966:PZK851966 QJD851966:QJG851966 QSZ851966:QTC851966 RCV851966:RCY851966 RMR851966:RMU851966 RWN851966:RWQ851966 SGJ851966:SGM851966 SQF851966:SQI851966 TAB851966:TAE851966 TJX851966:TKA851966 TTT851966:TTW851966 UDP851966:UDS851966 UNL851966:UNO851966 UXH851966:UXK851966 VHD851966:VHG851966 VQZ851966:VRC851966 WAV851966:WAY851966 WKR851966:WKU851966 WUN851966:WUQ851966 Q917502:T917502 IB917502:IE917502 RX917502:SA917502 ABT917502:ABW917502 ALP917502:ALS917502 AVL917502:AVO917502 BFH917502:BFK917502 BPD917502:BPG917502 BYZ917502:BZC917502 CIV917502:CIY917502 CSR917502:CSU917502 DCN917502:DCQ917502 DMJ917502:DMM917502 DWF917502:DWI917502 EGB917502:EGE917502 EPX917502:EQA917502 EZT917502:EZW917502 FJP917502:FJS917502 FTL917502:FTO917502 GDH917502:GDK917502 GND917502:GNG917502 GWZ917502:GXC917502 HGV917502:HGY917502 HQR917502:HQU917502 IAN917502:IAQ917502 IKJ917502:IKM917502 IUF917502:IUI917502 JEB917502:JEE917502 JNX917502:JOA917502 JXT917502:JXW917502 KHP917502:KHS917502 KRL917502:KRO917502 LBH917502:LBK917502 LLD917502:LLG917502 LUZ917502:LVC917502 MEV917502:MEY917502 MOR917502:MOU917502 MYN917502:MYQ917502 NIJ917502:NIM917502 NSF917502:NSI917502 OCB917502:OCE917502 OLX917502:OMA917502 OVT917502:OVW917502 PFP917502:PFS917502 PPL917502:PPO917502 PZH917502:PZK917502 QJD917502:QJG917502 QSZ917502:QTC917502 RCV917502:RCY917502 RMR917502:RMU917502 RWN917502:RWQ917502 SGJ917502:SGM917502 SQF917502:SQI917502 TAB917502:TAE917502 TJX917502:TKA917502 TTT917502:TTW917502 UDP917502:UDS917502 UNL917502:UNO917502 UXH917502:UXK917502 VHD917502:VHG917502 VQZ917502:VRC917502 WAV917502:WAY917502 WKR917502:WKU917502 WUN917502:WUQ917502 Q983038:T983038 IB983038:IE983038 RX983038:SA983038 ABT983038:ABW983038 ALP983038:ALS983038 AVL983038:AVO983038 BFH983038:BFK983038 BPD983038:BPG983038 BYZ983038:BZC983038 CIV983038:CIY983038 CSR983038:CSU983038 DCN983038:DCQ983038 DMJ983038:DMM983038 DWF983038:DWI983038 EGB983038:EGE983038 EPX983038:EQA983038 EZT983038:EZW983038 FJP983038:FJS983038 FTL983038:FTO983038 GDH983038:GDK983038 GND983038:GNG983038 GWZ983038:GXC983038 HGV983038:HGY983038 HQR983038:HQU983038 IAN983038:IAQ983038 IKJ983038:IKM983038 IUF983038:IUI983038 JEB983038:JEE983038 JNX983038:JOA983038 JXT983038:JXW983038 KHP983038:KHS983038 KRL983038:KRO983038 LBH983038:LBK983038 LLD983038:LLG983038 LUZ983038:LVC983038 MEV983038:MEY983038 MOR983038:MOU983038 MYN983038:MYQ983038 NIJ983038:NIM983038 NSF983038:NSI983038 OCB983038:OCE983038 OLX983038:OMA983038 OVT983038:OVW983038 PFP983038:PFS983038 PPL983038:PPO983038 PZH983038:PZK983038 QJD983038:QJG983038 QSZ983038:QTC983038 RCV983038:RCY983038 RMR983038:RMU983038 RWN983038:RWQ983038 SGJ983038:SGM983038 SQF983038:SQI983038 TAB983038:TAE983038 TJX983038:TKA983038 TTT983038:TTW983038 UDP983038:UDS983038 UNL983038:UNO983038 UXH983038:UXK983038 VHD983038:VHG983038 VQZ983038:VRC983038 WAV983038:WAY983038 WKR983038:WKU983038 WUN983038:WUQ983038 HW983037:HZ983037 RS983037:RV983037 ABO983037:ABR983037 ALK983037:ALN983037 AVG983037:AVJ983037 BFC983037:BFF983037 BOY983037:BPB983037 BYU983037:BYX983037 CIQ983037:CIT983037 CSM983037:CSP983037 DCI983037:DCL983037 DME983037:DMH983037 DWA983037:DWD983037 EFW983037:EFZ983037 EPS983037:EPV983037 EZO983037:EZR983037 FJK983037:FJN983037 FTG983037:FTJ983037 GDC983037:GDF983037 GMY983037:GNB983037 GWU983037:GWX983037 HGQ983037:HGT983037 HQM983037:HQP983037 IAI983037:IAL983037 IKE983037:IKH983037 IUA983037:IUD983037 JDW983037:JDZ983037 JNS983037:JNV983037 JXO983037:JXR983037 KHK983037:KHN983037 KRG983037:KRJ983037 LBC983037:LBF983037 LKY983037:LLB983037 LUU983037:LUX983037 MEQ983037:MET983037 MOM983037:MOP983037 MYI983037:MYL983037 NIE983037:NIH983037 NSA983037:NSD983037 OBW983037:OBZ983037 OLS983037:OLV983037 OVO983037:OVR983037 PFK983037:PFN983037 PPG983037:PPJ983037 PZC983037:PZF983037 QIY983037:QJB983037 QSU983037:QSX983037 RCQ983037:RCT983037 RMM983037:RMP983037 RWI983037:RWL983037 SGE983037:SGH983037 SQA983037:SQD983037 SZW983037:SZZ983037 TJS983037:TJV983037 TTO983037:TTR983037 UDK983037:UDN983037 UNG983037:UNJ983037 UXC983037:UXF983037 VGY983037:VHB983037 VQU983037:VQX983037 WAQ983037:WAT983037 WKM983037:WKP983037 WUI983037:WUL983037 HW65533:HZ65533 RS65533:RV65533 ABO65533:ABR65533 ALK65533:ALN65533 AVG65533:AVJ65533 BFC65533:BFF65533 BOY65533:BPB65533 BYU65533:BYX65533 CIQ65533:CIT65533 CSM65533:CSP65533 DCI65533:DCL65533 DME65533:DMH65533 DWA65533:DWD65533 EFW65533:EFZ65533 EPS65533:EPV65533 EZO65533:EZR65533 FJK65533:FJN65533 FTG65533:FTJ65533 GDC65533:GDF65533 GMY65533:GNB65533 GWU65533:GWX65533 HGQ65533:HGT65533 HQM65533:HQP65533 IAI65533:IAL65533 IKE65533:IKH65533 IUA65533:IUD65533 JDW65533:JDZ65533 JNS65533:JNV65533 JXO65533:JXR65533 KHK65533:KHN65533 KRG65533:KRJ65533 LBC65533:LBF65533 LKY65533:LLB65533 LUU65533:LUX65533 MEQ65533:MET65533 MOM65533:MOP65533 MYI65533:MYL65533 NIE65533:NIH65533 NSA65533:NSD65533 OBW65533:OBZ65533 OLS65533:OLV65533 OVO65533:OVR65533 PFK65533:PFN65533 PPG65533:PPJ65533 PZC65533:PZF65533 QIY65533:QJB65533 QSU65533:QSX65533 RCQ65533:RCT65533 RMM65533:RMP65533 RWI65533:RWL65533 SGE65533:SGH65533 SQA65533:SQD65533 SZW65533:SZZ65533 TJS65533:TJV65533 TTO65533:TTR65533 UDK65533:UDN65533 UNG65533:UNJ65533 UXC65533:UXF65533 VGY65533:VHB65533 VQU65533:VQX65533 WAQ65533:WAT65533 WKM65533:WKP65533 WUI65533:WUL65533 HW131069:HZ131069 RS131069:RV131069 ABO131069:ABR131069 ALK131069:ALN131069 AVG131069:AVJ131069 BFC131069:BFF131069 BOY131069:BPB131069 BYU131069:BYX131069 CIQ131069:CIT131069 CSM131069:CSP131069 DCI131069:DCL131069 DME131069:DMH131069 DWA131069:DWD131069 EFW131069:EFZ131069 EPS131069:EPV131069 EZO131069:EZR131069 FJK131069:FJN131069 FTG131069:FTJ131069 GDC131069:GDF131069 GMY131069:GNB131069 GWU131069:GWX131069 HGQ131069:HGT131069 HQM131069:HQP131069 IAI131069:IAL131069 IKE131069:IKH131069 IUA131069:IUD131069 JDW131069:JDZ131069 JNS131069:JNV131069 JXO131069:JXR131069 KHK131069:KHN131069 KRG131069:KRJ131069 LBC131069:LBF131069 LKY131069:LLB131069 LUU131069:LUX131069 MEQ131069:MET131069 MOM131069:MOP131069 MYI131069:MYL131069 NIE131069:NIH131069 NSA131069:NSD131069 OBW131069:OBZ131069 OLS131069:OLV131069 OVO131069:OVR131069 PFK131069:PFN131069 PPG131069:PPJ131069 PZC131069:PZF131069 QIY131069:QJB131069 QSU131069:QSX131069 RCQ131069:RCT131069 RMM131069:RMP131069 RWI131069:RWL131069 SGE131069:SGH131069 SQA131069:SQD131069 SZW131069:SZZ131069 TJS131069:TJV131069 TTO131069:TTR131069 UDK131069:UDN131069 UNG131069:UNJ131069 UXC131069:UXF131069 VGY131069:VHB131069 VQU131069:VQX131069 WAQ131069:WAT131069 WKM131069:WKP131069 WUI131069:WUL131069 HW196605:HZ196605 RS196605:RV196605 ABO196605:ABR196605 ALK196605:ALN196605 AVG196605:AVJ196605 BFC196605:BFF196605 BOY196605:BPB196605 BYU196605:BYX196605 CIQ196605:CIT196605 CSM196605:CSP196605 DCI196605:DCL196605 DME196605:DMH196605 DWA196605:DWD196605 EFW196605:EFZ196605 EPS196605:EPV196605 EZO196605:EZR196605 FJK196605:FJN196605 FTG196605:FTJ196605 GDC196605:GDF196605 GMY196605:GNB196605 GWU196605:GWX196605 HGQ196605:HGT196605 HQM196605:HQP196605 IAI196605:IAL196605 IKE196605:IKH196605 IUA196605:IUD196605 JDW196605:JDZ196605 JNS196605:JNV196605 JXO196605:JXR196605 KHK196605:KHN196605 KRG196605:KRJ196605 LBC196605:LBF196605 LKY196605:LLB196605 LUU196605:LUX196605 MEQ196605:MET196605 MOM196605:MOP196605 MYI196605:MYL196605 NIE196605:NIH196605 NSA196605:NSD196605 OBW196605:OBZ196605 OLS196605:OLV196605 OVO196605:OVR196605 PFK196605:PFN196605 PPG196605:PPJ196605 PZC196605:PZF196605 QIY196605:QJB196605 QSU196605:QSX196605 RCQ196605:RCT196605 RMM196605:RMP196605 RWI196605:RWL196605 SGE196605:SGH196605 SQA196605:SQD196605 SZW196605:SZZ196605 TJS196605:TJV196605 TTO196605:TTR196605 UDK196605:UDN196605 UNG196605:UNJ196605 UXC196605:UXF196605 VGY196605:VHB196605 VQU196605:VQX196605 WAQ196605:WAT196605 WKM196605:WKP196605 WUI196605:WUL196605 HW262141:HZ262141 RS262141:RV262141 ABO262141:ABR262141 ALK262141:ALN262141 AVG262141:AVJ262141 BFC262141:BFF262141 BOY262141:BPB262141 BYU262141:BYX262141 CIQ262141:CIT262141 CSM262141:CSP262141 DCI262141:DCL262141 DME262141:DMH262141 DWA262141:DWD262141 EFW262141:EFZ262141 EPS262141:EPV262141 EZO262141:EZR262141 FJK262141:FJN262141 FTG262141:FTJ262141 GDC262141:GDF262141 GMY262141:GNB262141 GWU262141:GWX262141 HGQ262141:HGT262141 HQM262141:HQP262141 IAI262141:IAL262141 IKE262141:IKH262141 IUA262141:IUD262141 JDW262141:JDZ262141 JNS262141:JNV262141 JXO262141:JXR262141 KHK262141:KHN262141 KRG262141:KRJ262141 LBC262141:LBF262141 LKY262141:LLB262141 LUU262141:LUX262141 MEQ262141:MET262141 MOM262141:MOP262141 MYI262141:MYL262141 NIE262141:NIH262141 NSA262141:NSD262141 OBW262141:OBZ262141 OLS262141:OLV262141 OVO262141:OVR262141 PFK262141:PFN262141 PPG262141:PPJ262141 PZC262141:PZF262141 QIY262141:QJB262141 QSU262141:QSX262141 RCQ262141:RCT262141 RMM262141:RMP262141 RWI262141:RWL262141 SGE262141:SGH262141 SQA262141:SQD262141 SZW262141:SZZ262141 TJS262141:TJV262141 TTO262141:TTR262141 UDK262141:UDN262141 UNG262141:UNJ262141 UXC262141:UXF262141 VGY262141:VHB262141 VQU262141:VQX262141 WAQ262141:WAT262141 WKM262141:WKP262141 WUI262141:WUL262141 HW327677:HZ327677 RS327677:RV327677 ABO327677:ABR327677 ALK327677:ALN327677 AVG327677:AVJ327677 BFC327677:BFF327677 BOY327677:BPB327677 BYU327677:BYX327677 CIQ327677:CIT327677 CSM327677:CSP327677 DCI327677:DCL327677 DME327677:DMH327677 DWA327677:DWD327677 EFW327677:EFZ327677 EPS327677:EPV327677 EZO327677:EZR327677 FJK327677:FJN327677 FTG327677:FTJ327677 GDC327677:GDF327677 GMY327677:GNB327677 GWU327677:GWX327677 HGQ327677:HGT327677 HQM327677:HQP327677 IAI327677:IAL327677 IKE327677:IKH327677 IUA327677:IUD327677 JDW327677:JDZ327677 JNS327677:JNV327677 JXO327677:JXR327677 KHK327677:KHN327677 KRG327677:KRJ327677 LBC327677:LBF327677 LKY327677:LLB327677 LUU327677:LUX327677 MEQ327677:MET327677 MOM327677:MOP327677 MYI327677:MYL327677 NIE327677:NIH327677 NSA327677:NSD327677 OBW327677:OBZ327677 OLS327677:OLV327677 OVO327677:OVR327677 PFK327677:PFN327677 PPG327677:PPJ327677 PZC327677:PZF327677 QIY327677:QJB327677 QSU327677:QSX327677 RCQ327677:RCT327677 RMM327677:RMP327677 RWI327677:RWL327677 SGE327677:SGH327677 SQA327677:SQD327677 SZW327677:SZZ327677 TJS327677:TJV327677 TTO327677:TTR327677 UDK327677:UDN327677 UNG327677:UNJ327677 UXC327677:UXF327677 VGY327677:VHB327677 VQU327677:VQX327677 WAQ327677:WAT327677 WKM327677:WKP327677 WUI327677:WUL327677 HW393213:HZ393213 RS393213:RV393213 ABO393213:ABR393213 ALK393213:ALN393213 AVG393213:AVJ393213 BFC393213:BFF393213 BOY393213:BPB393213 BYU393213:BYX393213 CIQ393213:CIT393213 CSM393213:CSP393213 DCI393213:DCL393213 DME393213:DMH393213 DWA393213:DWD393213 EFW393213:EFZ393213 EPS393213:EPV393213 EZO393213:EZR393213 FJK393213:FJN393213 FTG393213:FTJ393213 GDC393213:GDF393213 GMY393213:GNB393213 GWU393213:GWX393213 HGQ393213:HGT393213 HQM393213:HQP393213 IAI393213:IAL393213 IKE393213:IKH393213 IUA393213:IUD393213 JDW393213:JDZ393213 JNS393213:JNV393213 JXO393213:JXR393213 KHK393213:KHN393213 KRG393213:KRJ393213 LBC393213:LBF393213 LKY393213:LLB393213 LUU393213:LUX393213 MEQ393213:MET393213 MOM393213:MOP393213 MYI393213:MYL393213 NIE393213:NIH393213 NSA393213:NSD393213 OBW393213:OBZ393213 OLS393213:OLV393213 OVO393213:OVR393213 PFK393213:PFN393213 PPG393213:PPJ393213 PZC393213:PZF393213 QIY393213:QJB393213 QSU393213:QSX393213 RCQ393213:RCT393213 RMM393213:RMP393213 RWI393213:RWL393213 SGE393213:SGH393213 SQA393213:SQD393213 SZW393213:SZZ393213 TJS393213:TJV393213 TTO393213:TTR393213 UDK393213:UDN393213 UNG393213:UNJ393213 UXC393213:UXF393213 VGY393213:VHB393213 VQU393213:VQX393213 WAQ393213:WAT393213 WKM393213:WKP393213 WUI393213:WUL393213 HW458749:HZ458749 RS458749:RV458749 ABO458749:ABR458749 ALK458749:ALN458749 AVG458749:AVJ458749 BFC458749:BFF458749 BOY458749:BPB458749 BYU458749:BYX458749 CIQ458749:CIT458749 CSM458749:CSP458749 DCI458749:DCL458749 DME458749:DMH458749 DWA458749:DWD458749 EFW458749:EFZ458749 EPS458749:EPV458749 EZO458749:EZR458749 FJK458749:FJN458749 FTG458749:FTJ458749 GDC458749:GDF458749 GMY458749:GNB458749 GWU458749:GWX458749 HGQ458749:HGT458749 HQM458749:HQP458749 IAI458749:IAL458749 IKE458749:IKH458749 IUA458749:IUD458749 JDW458749:JDZ458749 JNS458749:JNV458749 JXO458749:JXR458749 KHK458749:KHN458749 KRG458749:KRJ458749 LBC458749:LBF458749 LKY458749:LLB458749 LUU458749:LUX458749 MEQ458749:MET458749 MOM458749:MOP458749 MYI458749:MYL458749 NIE458749:NIH458749 NSA458749:NSD458749 OBW458749:OBZ458749 OLS458749:OLV458749 OVO458749:OVR458749 PFK458749:PFN458749 PPG458749:PPJ458749 PZC458749:PZF458749 QIY458749:QJB458749 QSU458749:QSX458749 RCQ458749:RCT458749 RMM458749:RMP458749 RWI458749:RWL458749 SGE458749:SGH458749 SQA458749:SQD458749 SZW458749:SZZ458749 TJS458749:TJV458749 TTO458749:TTR458749 UDK458749:UDN458749 UNG458749:UNJ458749 UXC458749:UXF458749 VGY458749:VHB458749 VQU458749:VQX458749 WAQ458749:WAT458749 WKM458749:WKP458749 WUI458749:WUL458749 HW524285:HZ524285 RS524285:RV524285 ABO524285:ABR524285 ALK524285:ALN524285 AVG524285:AVJ524285 BFC524285:BFF524285 BOY524285:BPB524285 BYU524285:BYX524285 CIQ524285:CIT524285 CSM524285:CSP524285 DCI524285:DCL524285 DME524285:DMH524285 DWA524285:DWD524285 EFW524285:EFZ524285 EPS524285:EPV524285 EZO524285:EZR524285 FJK524285:FJN524285 FTG524285:FTJ524285 GDC524285:GDF524285 GMY524285:GNB524285 GWU524285:GWX524285 HGQ524285:HGT524285 HQM524285:HQP524285 IAI524285:IAL524285 IKE524285:IKH524285 IUA524285:IUD524285 JDW524285:JDZ524285 JNS524285:JNV524285 JXO524285:JXR524285 KHK524285:KHN524285 KRG524285:KRJ524285 LBC524285:LBF524285 LKY524285:LLB524285 LUU524285:LUX524285 MEQ524285:MET524285 MOM524285:MOP524285 MYI524285:MYL524285 NIE524285:NIH524285 NSA524285:NSD524285 OBW524285:OBZ524285 OLS524285:OLV524285 OVO524285:OVR524285 PFK524285:PFN524285 PPG524285:PPJ524285 PZC524285:PZF524285 QIY524285:QJB524285 QSU524285:QSX524285 RCQ524285:RCT524285 RMM524285:RMP524285 RWI524285:RWL524285 SGE524285:SGH524285 SQA524285:SQD524285 SZW524285:SZZ524285 TJS524285:TJV524285 TTO524285:TTR524285 UDK524285:UDN524285 UNG524285:UNJ524285 UXC524285:UXF524285 VGY524285:VHB524285 VQU524285:VQX524285 WAQ524285:WAT524285 WKM524285:WKP524285 WUI524285:WUL524285 HW589821:HZ589821 RS589821:RV589821 ABO589821:ABR589821 ALK589821:ALN589821 AVG589821:AVJ589821 BFC589821:BFF589821 BOY589821:BPB589821 BYU589821:BYX589821 CIQ589821:CIT589821 CSM589821:CSP589821 DCI589821:DCL589821 DME589821:DMH589821 DWA589821:DWD589821 EFW589821:EFZ589821 EPS589821:EPV589821 EZO589821:EZR589821 FJK589821:FJN589821 FTG589821:FTJ589821 GDC589821:GDF589821 GMY589821:GNB589821 GWU589821:GWX589821 HGQ589821:HGT589821 HQM589821:HQP589821 IAI589821:IAL589821 IKE589821:IKH589821 IUA589821:IUD589821 JDW589821:JDZ589821 JNS589821:JNV589821 JXO589821:JXR589821 KHK589821:KHN589821 KRG589821:KRJ589821 LBC589821:LBF589821 LKY589821:LLB589821 LUU589821:LUX589821 MEQ589821:MET589821 MOM589821:MOP589821 MYI589821:MYL589821 NIE589821:NIH589821 NSA589821:NSD589821 OBW589821:OBZ589821 OLS589821:OLV589821 OVO589821:OVR589821 PFK589821:PFN589821 PPG589821:PPJ589821 PZC589821:PZF589821 QIY589821:QJB589821 QSU589821:QSX589821 RCQ589821:RCT589821 RMM589821:RMP589821 RWI589821:RWL589821 SGE589821:SGH589821 SQA589821:SQD589821 SZW589821:SZZ589821 TJS589821:TJV589821 TTO589821:TTR589821 UDK589821:UDN589821 UNG589821:UNJ589821 UXC589821:UXF589821 VGY589821:VHB589821 VQU589821:VQX589821 WAQ589821:WAT589821 WKM589821:WKP589821 WUI589821:WUL589821 HW655357:HZ655357 RS655357:RV655357 ABO655357:ABR655357 ALK655357:ALN655357 AVG655357:AVJ655357 BFC655357:BFF655357 BOY655357:BPB655357 BYU655357:BYX655357 CIQ655357:CIT655357 CSM655357:CSP655357 DCI655357:DCL655357 DME655357:DMH655357 DWA655357:DWD655357 EFW655357:EFZ655357 EPS655357:EPV655357 EZO655357:EZR655357 FJK655357:FJN655357 FTG655357:FTJ655357 GDC655357:GDF655357 GMY655357:GNB655357 GWU655357:GWX655357 HGQ655357:HGT655357 HQM655357:HQP655357 IAI655357:IAL655357 IKE655357:IKH655357 IUA655357:IUD655357 JDW655357:JDZ655357 JNS655357:JNV655357 JXO655357:JXR655357 KHK655357:KHN655357 KRG655357:KRJ655357 LBC655357:LBF655357 LKY655357:LLB655357 LUU655357:LUX655357 MEQ655357:MET655357 MOM655357:MOP655357 MYI655357:MYL655357 NIE655357:NIH655357 NSA655357:NSD655357 OBW655357:OBZ655357 OLS655357:OLV655357 OVO655357:OVR655357 PFK655357:PFN655357 PPG655357:PPJ655357 PZC655357:PZF655357 QIY655357:QJB655357 QSU655357:QSX655357 RCQ655357:RCT655357 RMM655357:RMP655357 RWI655357:RWL655357 SGE655357:SGH655357 SQA655357:SQD655357 SZW655357:SZZ655357 TJS655357:TJV655357 TTO655357:TTR655357 UDK655357:UDN655357 UNG655357:UNJ655357 UXC655357:UXF655357 VGY655357:VHB655357 VQU655357:VQX655357 WAQ655357:WAT655357 WKM655357:WKP655357 WUI655357:WUL655357 HW720893:HZ720893 RS720893:RV720893 ABO720893:ABR720893 ALK720893:ALN720893 AVG720893:AVJ720893 BFC720893:BFF720893 BOY720893:BPB720893 BYU720893:BYX720893 CIQ720893:CIT720893 CSM720893:CSP720893 DCI720893:DCL720893 DME720893:DMH720893 DWA720893:DWD720893 EFW720893:EFZ720893 EPS720893:EPV720893 EZO720893:EZR720893 FJK720893:FJN720893 FTG720893:FTJ720893 GDC720893:GDF720893 GMY720893:GNB720893 GWU720893:GWX720893 HGQ720893:HGT720893 HQM720893:HQP720893 IAI720893:IAL720893 IKE720893:IKH720893 IUA720893:IUD720893 JDW720893:JDZ720893 JNS720893:JNV720893 JXO720893:JXR720893 KHK720893:KHN720893 KRG720893:KRJ720893 LBC720893:LBF720893 LKY720893:LLB720893 LUU720893:LUX720893 MEQ720893:MET720893 MOM720893:MOP720893 MYI720893:MYL720893 NIE720893:NIH720893 NSA720893:NSD720893 OBW720893:OBZ720893 OLS720893:OLV720893 OVO720893:OVR720893 PFK720893:PFN720893 PPG720893:PPJ720893 PZC720893:PZF720893 QIY720893:QJB720893 QSU720893:QSX720893 RCQ720893:RCT720893 RMM720893:RMP720893 RWI720893:RWL720893 SGE720893:SGH720893 SQA720893:SQD720893 SZW720893:SZZ720893 TJS720893:TJV720893 TTO720893:TTR720893 UDK720893:UDN720893 UNG720893:UNJ720893 UXC720893:UXF720893 VGY720893:VHB720893 VQU720893:VQX720893 WAQ720893:WAT720893 WKM720893:WKP720893 WUI720893:WUL720893 HW786429:HZ786429 RS786429:RV786429 ABO786429:ABR786429 ALK786429:ALN786429 AVG786429:AVJ786429 BFC786429:BFF786429 BOY786429:BPB786429 BYU786429:BYX786429 CIQ786429:CIT786429 CSM786429:CSP786429 DCI786429:DCL786429 DME786429:DMH786429 DWA786429:DWD786429 EFW786429:EFZ786429 EPS786429:EPV786429 EZO786429:EZR786429 FJK786429:FJN786429 FTG786429:FTJ786429 GDC786429:GDF786429 GMY786429:GNB786429 GWU786429:GWX786429 HGQ786429:HGT786429 HQM786429:HQP786429 IAI786429:IAL786429 IKE786429:IKH786429 IUA786429:IUD786429 JDW786429:JDZ786429 JNS786429:JNV786429 JXO786429:JXR786429 KHK786429:KHN786429 KRG786429:KRJ786429 LBC786429:LBF786429 LKY786429:LLB786429 LUU786429:LUX786429 MEQ786429:MET786429 MOM786429:MOP786429 MYI786429:MYL786429 NIE786429:NIH786429 NSA786429:NSD786429 OBW786429:OBZ786429 OLS786429:OLV786429 OVO786429:OVR786429 PFK786429:PFN786429 PPG786429:PPJ786429 PZC786429:PZF786429 QIY786429:QJB786429 QSU786429:QSX786429 RCQ786429:RCT786429 RMM786429:RMP786429 RWI786429:RWL786429 SGE786429:SGH786429 SQA786429:SQD786429 SZW786429:SZZ786429 TJS786429:TJV786429 TTO786429:TTR786429 UDK786429:UDN786429 UNG786429:UNJ786429 UXC786429:UXF786429 VGY786429:VHB786429 VQU786429:VQX786429 WAQ786429:WAT786429 WKM786429:WKP786429 WUI786429:WUL786429 HW851965:HZ851965 RS851965:RV851965 ABO851965:ABR851965 ALK851965:ALN851965 AVG851965:AVJ851965 BFC851965:BFF851965 BOY851965:BPB851965 BYU851965:BYX851965 CIQ851965:CIT851965 CSM851965:CSP851965 DCI851965:DCL851965 DME851965:DMH851965 DWA851965:DWD851965 EFW851965:EFZ851965 EPS851965:EPV851965 EZO851965:EZR851965 FJK851965:FJN851965 FTG851965:FTJ851965 GDC851965:GDF851965 GMY851965:GNB851965 GWU851965:GWX851965 HGQ851965:HGT851965 HQM851965:HQP851965 IAI851965:IAL851965 IKE851965:IKH851965 IUA851965:IUD851965 JDW851965:JDZ851965 JNS851965:JNV851965 JXO851965:JXR851965 KHK851965:KHN851965 KRG851965:KRJ851965 LBC851965:LBF851965 LKY851965:LLB851965 LUU851965:LUX851965 MEQ851965:MET851965 MOM851965:MOP851965 MYI851965:MYL851965 NIE851965:NIH851965 NSA851965:NSD851965 OBW851965:OBZ851965 OLS851965:OLV851965 OVO851965:OVR851965 PFK851965:PFN851965 PPG851965:PPJ851965 PZC851965:PZF851965 QIY851965:QJB851965 QSU851965:QSX851965 RCQ851965:RCT851965 RMM851965:RMP851965 RWI851965:RWL851965 SGE851965:SGH851965 SQA851965:SQD851965 SZW851965:SZZ851965 TJS851965:TJV851965 TTO851965:TTR851965 UDK851965:UDN851965 UNG851965:UNJ851965 UXC851965:UXF851965 VGY851965:VHB851965 VQU851965:VQX851965 WAQ851965:WAT851965 WKM851965:WKP851965 WUI851965:WUL851965 HW917501:HZ917501 RS917501:RV917501 ABO917501:ABR917501 ALK917501:ALN917501 AVG917501:AVJ917501 BFC917501:BFF917501 BOY917501:BPB917501 BYU917501:BYX917501 CIQ917501:CIT917501 CSM917501:CSP917501 DCI917501:DCL917501 DME917501:DMH917501 DWA917501:DWD917501 EFW917501:EFZ917501 EPS917501:EPV917501 EZO917501:EZR917501 FJK917501:FJN917501 FTG917501:FTJ917501 GDC917501:GDF917501 GMY917501:GNB917501 GWU917501:GWX917501 HGQ917501:HGT917501 HQM917501:HQP917501 IAI917501:IAL917501 IKE917501:IKH917501 IUA917501:IUD917501 JDW917501:JDZ917501 JNS917501:JNV917501 JXO917501:JXR917501 KHK917501:KHN917501 KRG917501:KRJ917501 LBC917501:LBF917501 LKY917501:LLB917501 LUU917501:LUX917501 MEQ917501:MET917501 MOM917501:MOP917501 MYI917501:MYL917501 NIE917501:NIH917501 NSA917501:NSD917501 OBW917501:OBZ917501 OLS917501:OLV917501 OVO917501:OVR917501 PFK917501:PFN917501 PPG917501:PPJ917501 PZC917501:PZF917501 QIY917501:QJB917501 QSU917501:QSX917501 RCQ917501:RCT917501 RMM917501:RMP917501 RWI917501:RWL917501 SGE917501:SGH917501 SQA917501:SQD917501 SZW917501:SZZ917501 TJS917501:TJV917501 TTO917501:TTR917501 UDK917501:UDN917501 UNG917501:UNJ917501 UXC917501:UXF917501 VGY917501:VHB917501 VQU917501:VQX917501 WAQ917501:WAT917501 WKM917501:WKP917501 WUI917501:WUL917501 AI65554:AJ65557 AI131090:AJ131093 AI196626:AJ196629 AI262162:AJ262165 AI327698:AJ327701 AI393234:AJ393237 AI458770:AJ458773 AI524306:AJ524309 AI589842:AJ589845 AI655378:AJ655381 AI720914:AJ720917 AI786450:AJ786453 AI851986:AJ851989 AI917522:AJ917525 AI983058:AJ983061 AG65548 AG131084 AG196620 AG262156 AG327692 AG393228 AG458764 AG524300 AG589836 AG655372 AG720908 AG786444 AG851980 AG917516 AB917516:AD917516 AB851980:AD851980 AB786444:AD786444 AB720908:AD720908 AB655372:AD655372 AB589836:AD589836 AB524300:AD524300 AB458764:AD458764 AB393228:AD393228 AB327692:AD327692 AB262156:AD262156 AB196620:AD196620 AB131084:AD131084 AB65548:AD65548 AB983052:AD983052 AG983052 AF65554:AF65557 AF131090:AF131093 AF196626:AF196629 AF262162:AF262165 AF327698:AF327701 AF393234:AF393237 AF458770:AF458773 AF524306:AF524309 AF589842:AF589845 AF655378:AF655381 AF720914:AF720917 AF786450:AF786453 AF851986:AF851989 AF917522:AF917525 AF983058:AF983061 AF21 AI21:AJ21" xr:uid="{BBC32FCA-F27E-4303-BEB1-085300B4CFF2}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U65532:X65532 IF65532:II65532 SB65532:SE65532 ABX65532:ACA65532 ALT65532:ALW65532 AVP65532:AVS65532 BFL65532:BFO65532 BPH65532:BPK65532 BZD65532:BZG65532 CIZ65532:CJC65532 CSV65532:CSY65532 DCR65532:DCU65532 DMN65532:DMQ65532 DWJ65532:DWM65532 EGF65532:EGI65532 EQB65532:EQE65532 EZX65532:FAA65532 FJT65532:FJW65532 FTP65532:FTS65532 GDL65532:GDO65532 GNH65532:GNK65532 GXD65532:GXG65532 HGZ65532:HHC65532 HQV65532:HQY65532 IAR65532:IAU65532 IKN65532:IKQ65532 IUJ65532:IUM65532 JEF65532:JEI65532 JOB65532:JOE65532 JXX65532:JYA65532 KHT65532:KHW65532 KRP65532:KRS65532 LBL65532:LBO65532 LLH65532:LLK65532 LVD65532:LVG65532 MEZ65532:MFC65532 MOV65532:MOY65532 MYR65532:MYU65532 NIN65532:NIQ65532 NSJ65532:NSM65532 OCF65532:OCI65532 OMB65532:OME65532 OVX65532:OWA65532 PFT65532:PFW65532 PPP65532:PPS65532 PZL65532:PZO65532 QJH65532:QJK65532 QTD65532:QTG65532 RCZ65532:RDC65532 RMV65532:RMY65532 RWR65532:RWU65532 SGN65532:SGQ65532 SQJ65532:SQM65532 TAF65532:TAI65532 TKB65532:TKE65532 TTX65532:TUA65532 UDT65532:UDW65532 UNP65532:UNS65532 UXL65532:UXO65532 VHH65532:VHK65532 VRD65532:VRG65532 WAZ65532:WBC65532 WKV65532:WKY65532 WUR65532:WUU65532 U131068:X131068 IF131068:II131068 SB131068:SE131068 ABX131068:ACA131068 ALT131068:ALW131068 AVP131068:AVS131068 BFL131068:BFO131068 BPH131068:BPK131068 BZD131068:BZG131068 CIZ131068:CJC131068 CSV131068:CSY131068 DCR131068:DCU131068 DMN131068:DMQ131068 DWJ131068:DWM131068 EGF131068:EGI131068 EQB131068:EQE131068 EZX131068:FAA131068 FJT131068:FJW131068 FTP131068:FTS131068 GDL131068:GDO131068 GNH131068:GNK131068 GXD131068:GXG131068 HGZ131068:HHC131068 HQV131068:HQY131068 IAR131068:IAU131068 IKN131068:IKQ131068 IUJ131068:IUM131068 JEF131068:JEI131068 JOB131068:JOE131068 JXX131068:JYA131068 KHT131068:KHW131068 KRP131068:KRS131068 LBL131068:LBO131068 LLH131068:LLK131068 LVD131068:LVG131068 MEZ131068:MFC131068 MOV131068:MOY131068 MYR131068:MYU131068 NIN131068:NIQ131068 NSJ131068:NSM131068 OCF131068:OCI131068 OMB131068:OME131068 OVX131068:OWA131068 PFT131068:PFW131068 PPP131068:PPS131068 PZL131068:PZO131068 QJH131068:QJK131068 QTD131068:QTG131068 RCZ131068:RDC131068 RMV131068:RMY131068 RWR131068:RWU131068 SGN131068:SGQ131068 SQJ131068:SQM131068 TAF131068:TAI131068 TKB131068:TKE131068 TTX131068:TUA131068 UDT131068:UDW131068 UNP131068:UNS131068 UXL131068:UXO131068 VHH131068:VHK131068 VRD131068:VRG131068 WAZ131068:WBC131068 WKV131068:WKY131068 WUR131068:WUU131068 U196604:X196604 IF196604:II196604 SB196604:SE196604 ABX196604:ACA196604 ALT196604:ALW196604 AVP196604:AVS196604 BFL196604:BFO196604 BPH196604:BPK196604 BZD196604:BZG196604 CIZ196604:CJC196604 CSV196604:CSY196604 DCR196604:DCU196604 DMN196604:DMQ196604 DWJ196604:DWM196604 EGF196604:EGI196604 EQB196604:EQE196604 EZX196604:FAA196604 FJT196604:FJW196604 FTP196604:FTS196604 GDL196604:GDO196604 GNH196604:GNK196604 GXD196604:GXG196604 HGZ196604:HHC196604 HQV196604:HQY196604 IAR196604:IAU196604 IKN196604:IKQ196604 IUJ196604:IUM196604 JEF196604:JEI196604 JOB196604:JOE196604 JXX196604:JYA196604 KHT196604:KHW196604 KRP196604:KRS196604 LBL196604:LBO196604 LLH196604:LLK196604 LVD196604:LVG196604 MEZ196604:MFC196604 MOV196604:MOY196604 MYR196604:MYU196604 NIN196604:NIQ196604 NSJ196604:NSM196604 OCF196604:OCI196604 OMB196604:OME196604 OVX196604:OWA196604 PFT196604:PFW196604 PPP196604:PPS196604 PZL196604:PZO196604 QJH196604:QJK196604 QTD196604:QTG196604 RCZ196604:RDC196604 RMV196604:RMY196604 RWR196604:RWU196604 SGN196604:SGQ196604 SQJ196604:SQM196604 TAF196604:TAI196604 TKB196604:TKE196604 TTX196604:TUA196604 UDT196604:UDW196604 UNP196604:UNS196604 UXL196604:UXO196604 VHH196604:VHK196604 VRD196604:VRG196604 WAZ196604:WBC196604 WKV196604:WKY196604 WUR196604:WUU196604 U262140:X262140 IF262140:II262140 SB262140:SE262140 ABX262140:ACA262140 ALT262140:ALW262140 AVP262140:AVS262140 BFL262140:BFO262140 BPH262140:BPK262140 BZD262140:BZG262140 CIZ262140:CJC262140 CSV262140:CSY262140 DCR262140:DCU262140 DMN262140:DMQ262140 DWJ262140:DWM262140 EGF262140:EGI262140 EQB262140:EQE262140 EZX262140:FAA262140 FJT262140:FJW262140 FTP262140:FTS262140 GDL262140:GDO262140 GNH262140:GNK262140 GXD262140:GXG262140 HGZ262140:HHC262140 HQV262140:HQY262140 IAR262140:IAU262140 IKN262140:IKQ262140 IUJ262140:IUM262140 JEF262140:JEI262140 JOB262140:JOE262140 JXX262140:JYA262140 KHT262140:KHW262140 KRP262140:KRS262140 LBL262140:LBO262140 LLH262140:LLK262140 LVD262140:LVG262140 MEZ262140:MFC262140 MOV262140:MOY262140 MYR262140:MYU262140 NIN262140:NIQ262140 NSJ262140:NSM262140 OCF262140:OCI262140 OMB262140:OME262140 OVX262140:OWA262140 PFT262140:PFW262140 PPP262140:PPS262140 PZL262140:PZO262140 QJH262140:QJK262140 QTD262140:QTG262140 RCZ262140:RDC262140 RMV262140:RMY262140 RWR262140:RWU262140 SGN262140:SGQ262140 SQJ262140:SQM262140 TAF262140:TAI262140 TKB262140:TKE262140 TTX262140:TUA262140 UDT262140:UDW262140 UNP262140:UNS262140 UXL262140:UXO262140 VHH262140:VHK262140 VRD262140:VRG262140 WAZ262140:WBC262140 WKV262140:WKY262140 WUR262140:WUU262140 U327676:X327676 IF327676:II327676 SB327676:SE327676 ABX327676:ACA327676 ALT327676:ALW327676 AVP327676:AVS327676 BFL327676:BFO327676 BPH327676:BPK327676 BZD327676:BZG327676 CIZ327676:CJC327676 CSV327676:CSY327676 DCR327676:DCU327676 DMN327676:DMQ327676 DWJ327676:DWM327676 EGF327676:EGI327676 EQB327676:EQE327676 EZX327676:FAA327676 FJT327676:FJW327676 FTP327676:FTS327676 GDL327676:GDO327676 GNH327676:GNK327676 GXD327676:GXG327676 HGZ327676:HHC327676 HQV327676:HQY327676 IAR327676:IAU327676 IKN327676:IKQ327676 IUJ327676:IUM327676 JEF327676:JEI327676 JOB327676:JOE327676 JXX327676:JYA327676 KHT327676:KHW327676 KRP327676:KRS327676 LBL327676:LBO327676 LLH327676:LLK327676 LVD327676:LVG327676 MEZ327676:MFC327676 MOV327676:MOY327676 MYR327676:MYU327676 NIN327676:NIQ327676 NSJ327676:NSM327676 OCF327676:OCI327676 OMB327676:OME327676 OVX327676:OWA327676 PFT327676:PFW327676 PPP327676:PPS327676 PZL327676:PZO327676 QJH327676:QJK327676 QTD327676:QTG327676 RCZ327676:RDC327676 RMV327676:RMY327676 RWR327676:RWU327676 SGN327676:SGQ327676 SQJ327676:SQM327676 TAF327676:TAI327676 TKB327676:TKE327676 TTX327676:TUA327676 UDT327676:UDW327676 UNP327676:UNS327676 UXL327676:UXO327676 VHH327676:VHK327676 VRD327676:VRG327676 WAZ327676:WBC327676 WKV327676:WKY327676 WUR327676:WUU327676 U393212:X393212 IF393212:II393212 SB393212:SE393212 ABX393212:ACA393212 ALT393212:ALW393212 AVP393212:AVS393212 BFL393212:BFO393212 BPH393212:BPK393212 BZD393212:BZG393212 CIZ393212:CJC393212 CSV393212:CSY393212 DCR393212:DCU393212 DMN393212:DMQ393212 DWJ393212:DWM393212 EGF393212:EGI393212 EQB393212:EQE393212 EZX393212:FAA393212 FJT393212:FJW393212 FTP393212:FTS393212 GDL393212:GDO393212 GNH393212:GNK393212 GXD393212:GXG393212 HGZ393212:HHC393212 HQV393212:HQY393212 IAR393212:IAU393212 IKN393212:IKQ393212 IUJ393212:IUM393212 JEF393212:JEI393212 JOB393212:JOE393212 JXX393212:JYA393212 KHT393212:KHW393212 KRP393212:KRS393212 LBL393212:LBO393212 LLH393212:LLK393212 LVD393212:LVG393212 MEZ393212:MFC393212 MOV393212:MOY393212 MYR393212:MYU393212 NIN393212:NIQ393212 NSJ393212:NSM393212 OCF393212:OCI393212 OMB393212:OME393212 OVX393212:OWA393212 PFT393212:PFW393212 PPP393212:PPS393212 PZL393212:PZO393212 QJH393212:QJK393212 QTD393212:QTG393212 RCZ393212:RDC393212 RMV393212:RMY393212 RWR393212:RWU393212 SGN393212:SGQ393212 SQJ393212:SQM393212 TAF393212:TAI393212 TKB393212:TKE393212 TTX393212:TUA393212 UDT393212:UDW393212 UNP393212:UNS393212 UXL393212:UXO393212 VHH393212:VHK393212 VRD393212:VRG393212 WAZ393212:WBC393212 WKV393212:WKY393212 WUR393212:WUU393212 U458748:X458748 IF458748:II458748 SB458748:SE458748 ABX458748:ACA458748 ALT458748:ALW458748 AVP458748:AVS458748 BFL458748:BFO458748 BPH458748:BPK458748 BZD458748:BZG458748 CIZ458748:CJC458748 CSV458748:CSY458748 DCR458748:DCU458748 DMN458748:DMQ458748 DWJ458748:DWM458748 EGF458748:EGI458748 EQB458748:EQE458748 EZX458748:FAA458748 FJT458748:FJW458748 FTP458748:FTS458748 GDL458748:GDO458748 GNH458748:GNK458748 GXD458748:GXG458748 HGZ458748:HHC458748 HQV458748:HQY458748 IAR458748:IAU458748 IKN458748:IKQ458748 IUJ458748:IUM458748 JEF458748:JEI458748 JOB458748:JOE458748 JXX458748:JYA458748 KHT458748:KHW458748 KRP458748:KRS458748 LBL458748:LBO458748 LLH458748:LLK458748 LVD458748:LVG458748 MEZ458748:MFC458748 MOV458748:MOY458748 MYR458748:MYU458748 NIN458748:NIQ458748 NSJ458748:NSM458748 OCF458748:OCI458748 OMB458748:OME458748 OVX458748:OWA458748 PFT458748:PFW458748 PPP458748:PPS458748 PZL458748:PZO458748 QJH458748:QJK458748 QTD458748:QTG458748 RCZ458748:RDC458748 RMV458748:RMY458748 RWR458748:RWU458748 SGN458748:SGQ458748 SQJ458748:SQM458748 TAF458748:TAI458748 TKB458748:TKE458748 TTX458748:TUA458748 UDT458748:UDW458748 UNP458748:UNS458748 UXL458748:UXO458748 VHH458748:VHK458748 VRD458748:VRG458748 WAZ458748:WBC458748 WKV458748:WKY458748 WUR458748:WUU458748 U524284:X524284 IF524284:II524284 SB524284:SE524284 ABX524284:ACA524284 ALT524284:ALW524284 AVP524284:AVS524284 BFL524284:BFO524284 BPH524284:BPK524284 BZD524284:BZG524284 CIZ524284:CJC524284 CSV524284:CSY524284 DCR524284:DCU524284 DMN524284:DMQ524284 DWJ524284:DWM524284 EGF524284:EGI524284 EQB524284:EQE524284 EZX524284:FAA524284 FJT524284:FJW524284 FTP524284:FTS524284 GDL524284:GDO524284 GNH524284:GNK524284 GXD524284:GXG524284 HGZ524284:HHC524284 HQV524284:HQY524284 IAR524284:IAU524284 IKN524284:IKQ524284 IUJ524284:IUM524284 JEF524284:JEI524284 JOB524284:JOE524284 JXX524284:JYA524284 KHT524284:KHW524284 KRP524284:KRS524284 LBL524284:LBO524284 LLH524284:LLK524284 LVD524284:LVG524284 MEZ524284:MFC524284 MOV524284:MOY524284 MYR524284:MYU524284 NIN524284:NIQ524284 NSJ524284:NSM524284 OCF524284:OCI524284 OMB524284:OME524284 OVX524284:OWA524284 PFT524284:PFW524284 PPP524284:PPS524284 PZL524284:PZO524284 QJH524284:QJK524284 QTD524284:QTG524284 RCZ524284:RDC524284 RMV524284:RMY524284 RWR524284:RWU524284 SGN524284:SGQ524284 SQJ524284:SQM524284 TAF524284:TAI524284 TKB524284:TKE524284 TTX524284:TUA524284 UDT524284:UDW524284 UNP524284:UNS524284 UXL524284:UXO524284 VHH524284:VHK524284 VRD524284:VRG524284 WAZ524284:WBC524284 WKV524284:WKY524284 WUR524284:WUU524284 U589820:X589820 IF589820:II589820 SB589820:SE589820 ABX589820:ACA589820 ALT589820:ALW589820 AVP589820:AVS589820 BFL589820:BFO589820 BPH589820:BPK589820 BZD589820:BZG589820 CIZ589820:CJC589820 CSV589820:CSY589820 DCR589820:DCU589820 DMN589820:DMQ589820 DWJ589820:DWM589820 EGF589820:EGI589820 EQB589820:EQE589820 EZX589820:FAA589820 FJT589820:FJW589820 FTP589820:FTS589820 GDL589820:GDO589820 GNH589820:GNK589820 GXD589820:GXG589820 HGZ589820:HHC589820 HQV589820:HQY589820 IAR589820:IAU589820 IKN589820:IKQ589820 IUJ589820:IUM589820 JEF589820:JEI589820 JOB589820:JOE589820 JXX589820:JYA589820 KHT589820:KHW589820 KRP589820:KRS589820 LBL589820:LBO589820 LLH589820:LLK589820 LVD589820:LVG589820 MEZ589820:MFC589820 MOV589820:MOY589820 MYR589820:MYU589820 NIN589820:NIQ589820 NSJ589820:NSM589820 OCF589820:OCI589820 OMB589820:OME589820 OVX589820:OWA589820 PFT589820:PFW589820 PPP589820:PPS589820 PZL589820:PZO589820 QJH589820:QJK589820 QTD589820:QTG589820 RCZ589820:RDC589820 RMV589820:RMY589820 RWR589820:RWU589820 SGN589820:SGQ589820 SQJ589820:SQM589820 TAF589820:TAI589820 TKB589820:TKE589820 TTX589820:TUA589820 UDT589820:UDW589820 UNP589820:UNS589820 UXL589820:UXO589820 VHH589820:VHK589820 VRD589820:VRG589820 WAZ589820:WBC589820 WKV589820:WKY589820 WUR589820:WUU589820 U655356:X655356 IF655356:II655356 SB655356:SE655356 ABX655356:ACA655356 ALT655356:ALW655356 AVP655356:AVS655356 BFL655356:BFO655356 BPH655356:BPK655356 BZD655356:BZG655356 CIZ655356:CJC655356 CSV655356:CSY655356 DCR655356:DCU655356 DMN655356:DMQ655356 DWJ655356:DWM655356 EGF655356:EGI655356 EQB655356:EQE655356 EZX655356:FAA655356 FJT655356:FJW655356 FTP655356:FTS655356 GDL655356:GDO655356 GNH655356:GNK655356 GXD655356:GXG655356 HGZ655356:HHC655356 HQV655356:HQY655356 IAR655356:IAU655356 IKN655356:IKQ655356 IUJ655356:IUM655356 JEF655356:JEI655356 JOB655356:JOE655356 JXX655356:JYA655356 KHT655356:KHW655356 KRP655356:KRS655356 LBL655356:LBO655356 LLH655356:LLK655356 LVD655356:LVG655356 MEZ655356:MFC655356 MOV655356:MOY655356 MYR655356:MYU655356 NIN655356:NIQ655356 NSJ655356:NSM655356 OCF655356:OCI655356 OMB655356:OME655356 OVX655356:OWA655356 PFT655356:PFW655356 PPP655356:PPS655356 PZL655356:PZO655356 QJH655356:QJK655356 QTD655356:QTG655356 RCZ655356:RDC655356 RMV655356:RMY655356 RWR655356:RWU655356 SGN655356:SGQ655356 SQJ655356:SQM655356 TAF655356:TAI655356 TKB655356:TKE655356 TTX655356:TUA655356 UDT655356:UDW655356 UNP655356:UNS655356 UXL655356:UXO655356 VHH655356:VHK655356 VRD655356:VRG655356 WAZ655356:WBC655356 WKV655356:WKY655356 WUR655356:WUU655356 U720892:X720892 IF720892:II720892 SB720892:SE720892 ABX720892:ACA720892 ALT720892:ALW720892 AVP720892:AVS720892 BFL720892:BFO720892 BPH720892:BPK720892 BZD720892:BZG720892 CIZ720892:CJC720892 CSV720892:CSY720892 DCR720892:DCU720892 DMN720892:DMQ720892 DWJ720892:DWM720892 EGF720892:EGI720892 EQB720892:EQE720892 EZX720892:FAA720892 FJT720892:FJW720892 FTP720892:FTS720892 GDL720892:GDO720892 GNH720892:GNK720892 GXD720892:GXG720892 HGZ720892:HHC720892 HQV720892:HQY720892 IAR720892:IAU720892 IKN720892:IKQ720892 IUJ720892:IUM720892 JEF720892:JEI720892 JOB720892:JOE720892 JXX720892:JYA720892 KHT720892:KHW720892 KRP720892:KRS720892 LBL720892:LBO720892 LLH720892:LLK720892 LVD720892:LVG720892 MEZ720892:MFC720892 MOV720892:MOY720892 MYR720892:MYU720892 NIN720892:NIQ720892 NSJ720892:NSM720892 OCF720892:OCI720892 OMB720892:OME720892 OVX720892:OWA720892 PFT720892:PFW720892 PPP720892:PPS720892 PZL720892:PZO720892 QJH720892:QJK720892 QTD720892:QTG720892 RCZ720892:RDC720892 RMV720892:RMY720892 RWR720892:RWU720892 SGN720892:SGQ720892 SQJ720892:SQM720892 TAF720892:TAI720892 TKB720892:TKE720892 TTX720892:TUA720892 UDT720892:UDW720892 UNP720892:UNS720892 UXL720892:UXO720892 VHH720892:VHK720892 VRD720892:VRG720892 WAZ720892:WBC720892 WKV720892:WKY720892 WUR720892:WUU720892 U786428:X786428 IF786428:II786428 SB786428:SE786428 ABX786428:ACA786428 ALT786428:ALW786428 AVP786428:AVS786428 BFL786428:BFO786428 BPH786428:BPK786428 BZD786428:BZG786428 CIZ786428:CJC786428 CSV786428:CSY786428 DCR786428:DCU786428 DMN786428:DMQ786428 DWJ786428:DWM786428 EGF786428:EGI786428 EQB786428:EQE786428 EZX786428:FAA786428 FJT786428:FJW786428 FTP786428:FTS786428 GDL786428:GDO786428 GNH786428:GNK786428 GXD786428:GXG786428 HGZ786428:HHC786428 HQV786428:HQY786428 IAR786428:IAU786428 IKN786428:IKQ786428 IUJ786428:IUM786428 JEF786428:JEI786428 JOB786428:JOE786428 JXX786428:JYA786428 KHT786428:KHW786428 KRP786428:KRS786428 LBL786428:LBO786428 LLH786428:LLK786428 LVD786428:LVG786428 MEZ786428:MFC786428 MOV786428:MOY786428 MYR786428:MYU786428 NIN786428:NIQ786428 NSJ786428:NSM786428 OCF786428:OCI786428 OMB786428:OME786428 OVX786428:OWA786428 PFT786428:PFW786428 PPP786428:PPS786428 PZL786428:PZO786428 QJH786428:QJK786428 QTD786428:QTG786428 RCZ786428:RDC786428 RMV786428:RMY786428 RWR786428:RWU786428 SGN786428:SGQ786428 SQJ786428:SQM786428 TAF786428:TAI786428 TKB786428:TKE786428 TTX786428:TUA786428 UDT786428:UDW786428 UNP786428:UNS786428 UXL786428:UXO786428 VHH786428:VHK786428 VRD786428:VRG786428 WAZ786428:WBC786428 WKV786428:WKY786428 WUR786428:WUU786428 U851964:X851964 IF851964:II851964 SB851964:SE851964 ABX851964:ACA851964 ALT851964:ALW851964 AVP851964:AVS851964 BFL851964:BFO851964 BPH851964:BPK851964 BZD851964:BZG851964 CIZ851964:CJC851964 CSV851964:CSY851964 DCR851964:DCU851964 DMN851964:DMQ851964 DWJ851964:DWM851964 EGF851964:EGI851964 EQB851964:EQE851964 EZX851964:FAA851964 FJT851964:FJW851964 FTP851964:FTS851964 GDL851964:GDO851964 GNH851964:GNK851964 GXD851964:GXG851964 HGZ851964:HHC851964 HQV851964:HQY851964 IAR851964:IAU851964 IKN851964:IKQ851964 IUJ851964:IUM851964 JEF851964:JEI851964 JOB851964:JOE851964 JXX851964:JYA851964 KHT851964:KHW851964 KRP851964:KRS851964 LBL851964:LBO851964 LLH851964:LLK851964 LVD851964:LVG851964 MEZ851964:MFC851964 MOV851964:MOY851964 MYR851964:MYU851964 NIN851964:NIQ851964 NSJ851964:NSM851964 OCF851964:OCI851964 OMB851964:OME851964 OVX851964:OWA851964 PFT851964:PFW851964 PPP851964:PPS851964 PZL851964:PZO851964 QJH851964:QJK851964 QTD851964:QTG851964 RCZ851964:RDC851964 RMV851964:RMY851964 RWR851964:RWU851964 SGN851964:SGQ851964 SQJ851964:SQM851964 TAF851964:TAI851964 TKB851964:TKE851964 TTX851964:TUA851964 UDT851964:UDW851964 UNP851964:UNS851964 UXL851964:UXO851964 VHH851964:VHK851964 VRD851964:VRG851964 WAZ851964:WBC851964 WKV851964:WKY851964 WUR851964:WUU851964 U917500:X917500 IF917500:II917500 SB917500:SE917500 ABX917500:ACA917500 ALT917500:ALW917500 AVP917500:AVS917500 BFL917500:BFO917500 BPH917500:BPK917500 BZD917500:BZG917500 CIZ917500:CJC917500 CSV917500:CSY917500 DCR917500:DCU917500 DMN917500:DMQ917500 DWJ917500:DWM917500 EGF917500:EGI917500 EQB917500:EQE917500 EZX917500:FAA917500 FJT917500:FJW917500 FTP917500:FTS917500 GDL917500:GDO917500 GNH917500:GNK917500 GXD917500:GXG917500 HGZ917500:HHC917500 HQV917500:HQY917500 IAR917500:IAU917500 IKN917500:IKQ917500 IUJ917500:IUM917500 JEF917500:JEI917500 JOB917500:JOE917500 JXX917500:JYA917500 KHT917500:KHW917500 KRP917500:KRS917500 LBL917500:LBO917500 LLH917500:LLK917500 LVD917500:LVG917500 MEZ917500:MFC917500 MOV917500:MOY917500 MYR917500:MYU917500 NIN917500:NIQ917500 NSJ917500:NSM917500 OCF917500:OCI917500 OMB917500:OME917500 OVX917500:OWA917500 PFT917500:PFW917500 PPP917500:PPS917500 PZL917500:PZO917500 QJH917500:QJK917500 QTD917500:QTG917500 RCZ917500:RDC917500 RMV917500:RMY917500 RWR917500:RWU917500 SGN917500:SGQ917500 SQJ917500:SQM917500 TAF917500:TAI917500 TKB917500:TKE917500 TTX917500:TUA917500 UDT917500:UDW917500 UNP917500:UNS917500 UXL917500:UXO917500 VHH917500:VHK917500 VRD917500:VRG917500 WAZ917500:WBC917500 WKV917500:WKY917500 WUR917500:WUU917500 U983036:X983036 IF983036:II983036 SB983036:SE983036 ABX983036:ACA983036 ALT983036:ALW983036 AVP983036:AVS983036 BFL983036:BFO983036 BPH983036:BPK983036 BZD983036:BZG983036 CIZ983036:CJC983036 CSV983036:CSY983036 DCR983036:DCU983036 DMN983036:DMQ983036 DWJ983036:DWM983036 EGF983036:EGI983036 EQB983036:EQE983036 EZX983036:FAA983036 FJT983036:FJW983036 FTP983036:FTS983036 GDL983036:GDO983036 GNH983036:GNK983036 GXD983036:GXG983036 HGZ983036:HHC983036 HQV983036:HQY983036 IAR983036:IAU983036 IKN983036:IKQ983036 IUJ983036:IUM983036 JEF983036:JEI983036 JOB983036:JOE983036 JXX983036:JYA983036 KHT983036:KHW983036 KRP983036:KRS983036 LBL983036:LBO983036 LLH983036:LLK983036 LVD983036:LVG983036 MEZ983036:MFC983036 MOV983036:MOY983036 MYR983036:MYU983036 NIN983036:NIQ983036 NSJ983036:NSM983036 OCF983036:OCI983036 OMB983036:OME983036 OVX983036:OWA983036 PFT983036:PFW983036 PPP983036:PPS983036 PZL983036:PZO983036 QJH983036:QJK983036 QTD983036:QTG983036 RCZ983036:RDC983036 RMV983036:RMY983036 RWR983036:RWU983036 SGN983036:SGQ983036 SQJ983036:SQM983036 TAF983036:TAI983036 TKB983036:TKE983036 TTX983036:TUA983036 UDT983036:UDW983036 UNP983036:UNS983036 UXL983036:UXO983036 VHH983036:VHK983036 VRD983036:VRG983036 WAZ983036:WBC983036 WKV983036:WKY983036 WUR983036:WUU983036 IA983035:ID983035 RW983035:RZ983035 ABS983035:ABV983035 ALO983035:ALR983035 AVK983035:AVN983035 BFG983035:BFJ983035 BPC983035:BPF983035 BYY983035:BZB983035 CIU983035:CIX983035 CSQ983035:CST983035 DCM983035:DCP983035 DMI983035:DML983035 DWE983035:DWH983035 EGA983035:EGD983035 EPW983035:EPZ983035 EZS983035:EZV983035 FJO983035:FJR983035 FTK983035:FTN983035 GDG983035:GDJ983035 GNC983035:GNF983035 GWY983035:GXB983035 HGU983035:HGX983035 HQQ983035:HQT983035 IAM983035:IAP983035 IKI983035:IKL983035 IUE983035:IUH983035 JEA983035:JED983035 JNW983035:JNZ983035 JXS983035:JXV983035 KHO983035:KHR983035 KRK983035:KRN983035 LBG983035:LBJ983035 LLC983035:LLF983035 LUY983035:LVB983035 MEU983035:MEX983035 MOQ983035:MOT983035 MYM983035:MYP983035 NII983035:NIL983035 NSE983035:NSH983035 OCA983035:OCD983035 OLW983035:OLZ983035 OVS983035:OVV983035 PFO983035:PFR983035 PPK983035:PPN983035 PZG983035:PZJ983035 QJC983035:QJF983035 QSY983035:QTB983035 RCU983035:RCX983035 RMQ983035:RMT983035 RWM983035:RWP983035 SGI983035:SGL983035 SQE983035:SQH983035 TAA983035:TAD983035 TJW983035:TJZ983035 TTS983035:TTV983035 UDO983035:UDR983035 UNK983035:UNN983035 UXG983035:UXJ983035 VHC983035:VHF983035 VQY983035:VRB983035 WAU983035:WAX983035 WKQ983035:WKT983035 WUM983035:WUP983035 IA65531:ID65531 RW65531:RZ65531 ABS65531:ABV65531 ALO65531:ALR65531 AVK65531:AVN65531 BFG65531:BFJ65531 BPC65531:BPF65531 BYY65531:BZB65531 CIU65531:CIX65531 CSQ65531:CST65531 DCM65531:DCP65531 DMI65531:DML65531 DWE65531:DWH65531 EGA65531:EGD65531 EPW65531:EPZ65531 EZS65531:EZV65531 FJO65531:FJR65531 FTK65531:FTN65531 GDG65531:GDJ65531 GNC65531:GNF65531 GWY65531:GXB65531 HGU65531:HGX65531 HQQ65531:HQT65531 IAM65531:IAP65531 IKI65531:IKL65531 IUE65531:IUH65531 JEA65531:JED65531 JNW65531:JNZ65531 JXS65531:JXV65531 KHO65531:KHR65531 KRK65531:KRN65531 LBG65531:LBJ65531 LLC65531:LLF65531 LUY65531:LVB65531 MEU65531:MEX65531 MOQ65531:MOT65531 MYM65531:MYP65531 NII65531:NIL65531 NSE65531:NSH65531 OCA65531:OCD65531 OLW65531:OLZ65531 OVS65531:OVV65531 PFO65531:PFR65531 PPK65531:PPN65531 PZG65531:PZJ65531 QJC65531:QJF65531 QSY65531:QTB65531 RCU65531:RCX65531 RMQ65531:RMT65531 RWM65531:RWP65531 SGI65531:SGL65531 SQE65531:SQH65531 TAA65531:TAD65531 TJW65531:TJZ65531 TTS65531:TTV65531 UDO65531:UDR65531 UNK65531:UNN65531 UXG65531:UXJ65531 VHC65531:VHF65531 VQY65531:VRB65531 WAU65531:WAX65531 WKQ65531:WKT65531 WUM65531:WUP65531 IA131067:ID131067 RW131067:RZ131067 ABS131067:ABV131067 ALO131067:ALR131067 AVK131067:AVN131067 BFG131067:BFJ131067 BPC131067:BPF131067 BYY131067:BZB131067 CIU131067:CIX131067 CSQ131067:CST131067 DCM131067:DCP131067 DMI131067:DML131067 DWE131067:DWH131067 EGA131067:EGD131067 EPW131067:EPZ131067 EZS131067:EZV131067 FJO131067:FJR131067 FTK131067:FTN131067 GDG131067:GDJ131067 GNC131067:GNF131067 GWY131067:GXB131067 HGU131067:HGX131067 HQQ131067:HQT131067 IAM131067:IAP131067 IKI131067:IKL131067 IUE131067:IUH131067 JEA131067:JED131067 JNW131067:JNZ131067 JXS131067:JXV131067 KHO131067:KHR131067 KRK131067:KRN131067 LBG131067:LBJ131067 LLC131067:LLF131067 LUY131067:LVB131067 MEU131067:MEX131067 MOQ131067:MOT131067 MYM131067:MYP131067 NII131067:NIL131067 NSE131067:NSH131067 OCA131067:OCD131067 OLW131067:OLZ131067 OVS131067:OVV131067 PFO131067:PFR131067 PPK131067:PPN131067 PZG131067:PZJ131067 QJC131067:QJF131067 QSY131067:QTB131067 RCU131067:RCX131067 RMQ131067:RMT131067 RWM131067:RWP131067 SGI131067:SGL131067 SQE131067:SQH131067 TAA131067:TAD131067 TJW131067:TJZ131067 TTS131067:TTV131067 UDO131067:UDR131067 UNK131067:UNN131067 UXG131067:UXJ131067 VHC131067:VHF131067 VQY131067:VRB131067 WAU131067:WAX131067 WKQ131067:WKT131067 WUM131067:WUP131067 IA196603:ID196603 RW196603:RZ196603 ABS196603:ABV196603 ALO196603:ALR196603 AVK196603:AVN196603 BFG196603:BFJ196603 BPC196603:BPF196603 BYY196603:BZB196603 CIU196603:CIX196603 CSQ196603:CST196603 DCM196603:DCP196603 DMI196603:DML196603 DWE196603:DWH196603 EGA196603:EGD196603 EPW196603:EPZ196603 EZS196603:EZV196603 FJO196603:FJR196603 FTK196603:FTN196603 GDG196603:GDJ196603 GNC196603:GNF196603 GWY196603:GXB196603 HGU196603:HGX196603 HQQ196603:HQT196603 IAM196603:IAP196603 IKI196603:IKL196603 IUE196603:IUH196603 JEA196603:JED196603 JNW196603:JNZ196603 JXS196603:JXV196603 KHO196603:KHR196603 KRK196603:KRN196603 LBG196603:LBJ196603 LLC196603:LLF196603 LUY196603:LVB196603 MEU196603:MEX196603 MOQ196603:MOT196603 MYM196603:MYP196603 NII196603:NIL196603 NSE196603:NSH196603 OCA196603:OCD196603 OLW196603:OLZ196603 OVS196603:OVV196603 PFO196603:PFR196603 PPK196603:PPN196603 PZG196603:PZJ196603 QJC196603:QJF196603 QSY196603:QTB196603 RCU196603:RCX196603 RMQ196603:RMT196603 RWM196603:RWP196603 SGI196603:SGL196603 SQE196603:SQH196603 TAA196603:TAD196603 TJW196603:TJZ196603 TTS196603:TTV196603 UDO196603:UDR196603 UNK196603:UNN196603 UXG196603:UXJ196603 VHC196603:VHF196603 VQY196603:VRB196603 WAU196603:WAX196603 WKQ196603:WKT196603 WUM196603:WUP196603 IA262139:ID262139 RW262139:RZ262139 ABS262139:ABV262139 ALO262139:ALR262139 AVK262139:AVN262139 BFG262139:BFJ262139 BPC262139:BPF262139 BYY262139:BZB262139 CIU262139:CIX262139 CSQ262139:CST262139 DCM262139:DCP262139 DMI262139:DML262139 DWE262139:DWH262139 EGA262139:EGD262139 EPW262139:EPZ262139 EZS262139:EZV262139 FJO262139:FJR262139 FTK262139:FTN262139 GDG262139:GDJ262139 GNC262139:GNF262139 GWY262139:GXB262139 HGU262139:HGX262139 HQQ262139:HQT262139 IAM262139:IAP262139 IKI262139:IKL262139 IUE262139:IUH262139 JEA262139:JED262139 JNW262139:JNZ262139 JXS262139:JXV262139 KHO262139:KHR262139 KRK262139:KRN262139 LBG262139:LBJ262139 LLC262139:LLF262139 LUY262139:LVB262139 MEU262139:MEX262139 MOQ262139:MOT262139 MYM262139:MYP262139 NII262139:NIL262139 NSE262139:NSH262139 OCA262139:OCD262139 OLW262139:OLZ262139 OVS262139:OVV262139 PFO262139:PFR262139 PPK262139:PPN262139 PZG262139:PZJ262139 QJC262139:QJF262139 QSY262139:QTB262139 RCU262139:RCX262139 RMQ262139:RMT262139 RWM262139:RWP262139 SGI262139:SGL262139 SQE262139:SQH262139 TAA262139:TAD262139 TJW262139:TJZ262139 TTS262139:TTV262139 UDO262139:UDR262139 UNK262139:UNN262139 UXG262139:UXJ262139 VHC262139:VHF262139 VQY262139:VRB262139 WAU262139:WAX262139 WKQ262139:WKT262139 WUM262139:WUP262139 IA327675:ID327675 RW327675:RZ327675 ABS327675:ABV327675 ALO327675:ALR327675 AVK327675:AVN327675 BFG327675:BFJ327675 BPC327675:BPF327675 BYY327675:BZB327675 CIU327675:CIX327675 CSQ327675:CST327675 DCM327675:DCP327675 DMI327675:DML327675 DWE327675:DWH327675 EGA327675:EGD327675 EPW327675:EPZ327675 EZS327675:EZV327675 FJO327675:FJR327675 FTK327675:FTN327675 GDG327675:GDJ327675 GNC327675:GNF327675 GWY327675:GXB327675 HGU327675:HGX327675 HQQ327675:HQT327675 IAM327675:IAP327675 IKI327675:IKL327675 IUE327675:IUH327675 JEA327675:JED327675 JNW327675:JNZ327675 JXS327675:JXV327675 KHO327675:KHR327675 KRK327675:KRN327675 LBG327675:LBJ327675 LLC327675:LLF327675 LUY327675:LVB327675 MEU327675:MEX327675 MOQ327675:MOT327675 MYM327675:MYP327675 NII327675:NIL327675 NSE327675:NSH327675 OCA327675:OCD327675 OLW327675:OLZ327675 OVS327675:OVV327675 PFO327675:PFR327675 PPK327675:PPN327675 PZG327675:PZJ327675 QJC327675:QJF327675 QSY327675:QTB327675 RCU327675:RCX327675 RMQ327675:RMT327675 RWM327675:RWP327675 SGI327675:SGL327675 SQE327675:SQH327675 TAA327675:TAD327675 TJW327675:TJZ327675 TTS327675:TTV327675 UDO327675:UDR327675 UNK327675:UNN327675 UXG327675:UXJ327675 VHC327675:VHF327675 VQY327675:VRB327675 WAU327675:WAX327675 WKQ327675:WKT327675 WUM327675:WUP327675 IA393211:ID393211 RW393211:RZ393211 ABS393211:ABV393211 ALO393211:ALR393211 AVK393211:AVN393211 BFG393211:BFJ393211 BPC393211:BPF393211 BYY393211:BZB393211 CIU393211:CIX393211 CSQ393211:CST393211 DCM393211:DCP393211 DMI393211:DML393211 DWE393211:DWH393211 EGA393211:EGD393211 EPW393211:EPZ393211 EZS393211:EZV393211 FJO393211:FJR393211 FTK393211:FTN393211 GDG393211:GDJ393211 GNC393211:GNF393211 GWY393211:GXB393211 HGU393211:HGX393211 HQQ393211:HQT393211 IAM393211:IAP393211 IKI393211:IKL393211 IUE393211:IUH393211 JEA393211:JED393211 JNW393211:JNZ393211 JXS393211:JXV393211 KHO393211:KHR393211 KRK393211:KRN393211 LBG393211:LBJ393211 LLC393211:LLF393211 LUY393211:LVB393211 MEU393211:MEX393211 MOQ393211:MOT393211 MYM393211:MYP393211 NII393211:NIL393211 NSE393211:NSH393211 OCA393211:OCD393211 OLW393211:OLZ393211 OVS393211:OVV393211 PFO393211:PFR393211 PPK393211:PPN393211 PZG393211:PZJ393211 QJC393211:QJF393211 QSY393211:QTB393211 RCU393211:RCX393211 RMQ393211:RMT393211 RWM393211:RWP393211 SGI393211:SGL393211 SQE393211:SQH393211 TAA393211:TAD393211 TJW393211:TJZ393211 TTS393211:TTV393211 UDO393211:UDR393211 UNK393211:UNN393211 UXG393211:UXJ393211 VHC393211:VHF393211 VQY393211:VRB393211 WAU393211:WAX393211 WKQ393211:WKT393211 WUM393211:WUP393211 IA458747:ID458747 RW458747:RZ458747 ABS458747:ABV458747 ALO458747:ALR458747 AVK458747:AVN458747 BFG458747:BFJ458747 BPC458747:BPF458747 BYY458747:BZB458747 CIU458747:CIX458747 CSQ458747:CST458747 DCM458747:DCP458747 DMI458747:DML458747 DWE458747:DWH458747 EGA458747:EGD458747 EPW458747:EPZ458747 EZS458747:EZV458747 FJO458747:FJR458747 FTK458747:FTN458747 GDG458747:GDJ458747 GNC458747:GNF458747 GWY458747:GXB458747 HGU458747:HGX458747 HQQ458747:HQT458747 IAM458747:IAP458747 IKI458747:IKL458747 IUE458747:IUH458747 JEA458747:JED458747 JNW458747:JNZ458747 JXS458747:JXV458747 KHO458747:KHR458747 KRK458747:KRN458747 LBG458747:LBJ458747 LLC458747:LLF458747 LUY458747:LVB458747 MEU458747:MEX458747 MOQ458747:MOT458747 MYM458747:MYP458747 NII458747:NIL458747 NSE458747:NSH458747 OCA458747:OCD458747 OLW458747:OLZ458747 OVS458747:OVV458747 PFO458747:PFR458747 PPK458747:PPN458747 PZG458747:PZJ458747 QJC458747:QJF458747 QSY458747:QTB458747 RCU458747:RCX458747 RMQ458747:RMT458747 RWM458747:RWP458747 SGI458747:SGL458747 SQE458747:SQH458747 TAA458747:TAD458747 TJW458747:TJZ458747 TTS458747:TTV458747 UDO458747:UDR458747 UNK458747:UNN458747 UXG458747:UXJ458747 VHC458747:VHF458747 VQY458747:VRB458747 WAU458747:WAX458747 WKQ458747:WKT458747 WUM458747:WUP458747 IA524283:ID524283 RW524283:RZ524283 ABS524283:ABV524283 ALO524283:ALR524283 AVK524283:AVN524283 BFG524283:BFJ524283 BPC524283:BPF524283 BYY524283:BZB524283 CIU524283:CIX524283 CSQ524283:CST524283 DCM524283:DCP524283 DMI524283:DML524283 DWE524283:DWH524283 EGA524283:EGD524283 EPW524283:EPZ524283 EZS524283:EZV524283 FJO524283:FJR524283 FTK524283:FTN524283 GDG524283:GDJ524283 GNC524283:GNF524283 GWY524283:GXB524283 HGU524283:HGX524283 HQQ524283:HQT524283 IAM524283:IAP524283 IKI524283:IKL524283 IUE524283:IUH524283 JEA524283:JED524283 JNW524283:JNZ524283 JXS524283:JXV524283 KHO524283:KHR524283 KRK524283:KRN524283 LBG524283:LBJ524283 LLC524283:LLF524283 LUY524283:LVB524283 MEU524283:MEX524283 MOQ524283:MOT524283 MYM524283:MYP524283 NII524283:NIL524283 NSE524283:NSH524283 OCA524283:OCD524283 OLW524283:OLZ524283 OVS524283:OVV524283 PFO524283:PFR524283 PPK524283:PPN524283 PZG524283:PZJ524283 QJC524283:QJF524283 QSY524283:QTB524283 RCU524283:RCX524283 RMQ524283:RMT524283 RWM524283:RWP524283 SGI524283:SGL524283 SQE524283:SQH524283 TAA524283:TAD524283 TJW524283:TJZ524283 TTS524283:TTV524283 UDO524283:UDR524283 UNK524283:UNN524283 UXG524283:UXJ524283 VHC524283:VHF524283 VQY524283:VRB524283 WAU524283:WAX524283 WKQ524283:WKT524283 WUM524283:WUP524283 IA589819:ID589819 RW589819:RZ589819 ABS589819:ABV589819 ALO589819:ALR589819 AVK589819:AVN589819 BFG589819:BFJ589819 BPC589819:BPF589819 BYY589819:BZB589819 CIU589819:CIX589819 CSQ589819:CST589819 DCM589819:DCP589819 DMI589819:DML589819 DWE589819:DWH589819 EGA589819:EGD589819 EPW589819:EPZ589819 EZS589819:EZV589819 FJO589819:FJR589819 FTK589819:FTN589819 GDG589819:GDJ589819 GNC589819:GNF589819 GWY589819:GXB589819 HGU589819:HGX589819 HQQ589819:HQT589819 IAM589819:IAP589819 IKI589819:IKL589819 IUE589819:IUH589819 JEA589819:JED589819 JNW589819:JNZ589819 JXS589819:JXV589819 KHO589819:KHR589819 KRK589819:KRN589819 LBG589819:LBJ589819 LLC589819:LLF589819 LUY589819:LVB589819 MEU589819:MEX589819 MOQ589819:MOT589819 MYM589819:MYP589819 NII589819:NIL589819 NSE589819:NSH589819 OCA589819:OCD589819 OLW589819:OLZ589819 OVS589819:OVV589819 PFO589819:PFR589819 PPK589819:PPN589819 PZG589819:PZJ589819 QJC589819:QJF589819 QSY589819:QTB589819 RCU589819:RCX589819 RMQ589819:RMT589819 RWM589819:RWP589819 SGI589819:SGL589819 SQE589819:SQH589819 TAA589819:TAD589819 TJW589819:TJZ589819 TTS589819:TTV589819 UDO589819:UDR589819 UNK589819:UNN589819 UXG589819:UXJ589819 VHC589819:VHF589819 VQY589819:VRB589819 WAU589819:WAX589819 WKQ589819:WKT589819 WUM589819:WUP589819 IA655355:ID655355 RW655355:RZ655355 ABS655355:ABV655355 ALO655355:ALR655355 AVK655355:AVN655355 BFG655355:BFJ655355 BPC655355:BPF655355 BYY655355:BZB655355 CIU655355:CIX655355 CSQ655355:CST655355 DCM655355:DCP655355 DMI655355:DML655355 DWE655355:DWH655355 EGA655355:EGD655355 EPW655355:EPZ655355 EZS655355:EZV655355 FJO655355:FJR655355 FTK655355:FTN655355 GDG655355:GDJ655355 GNC655355:GNF655355 GWY655355:GXB655355 HGU655355:HGX655355 HQQ655355:HQT655355 IAM655355:IAP655355 IKI655355:IKL655355 IUE655355:IUH655355 JEA655355:JED655355 JNW655355:JNZ655355 JXS655355:JXV655355 KHO655355:KHR655355 KRK655355:KRN655355 LBG655355:LBJ655355 LLC655355:LLF655355 LUY655355:LVB655355 MEU655355:MEX655355 MOQ655355:MOT655355 MYM655355:MYP655355 NII655355:NIL655355 NSE655355:NSH655355 OCA655355:OCD655355 OLW655355:OLZ655355 OVS655355:OVV655355 PFO655355:PFR655355 PPK655355:PPN655355 PZG655355:PZJ655355 QJC655355:QJF655355 QSY655355:QTB655355 RCU655355:RCX655355 RMQ655355:RMT655355 RWM655355:RWP655355 SGI655355:SGL655355 SQE655355:SQH655355 TAA655355:TAD655355 TJW655355:TJZ655355 TTS655355:TTV655355 UDO655355:UDR655355 UNK655355:UNN655355 UXG655355:UXJ655355 VHC655355:VHF655355 VQY655355:VRB655355 WAU655355:WAX655355 WKQ655355:WKT655355 WUM655355:WUP655355 IA720891:ID720891 RW720891:RZ720891 ABS720891:ABV720891 ALO720891:ALR720891 AVK720891:AVN720891 BFG720891:BFJ720891 BPC720891:BPF720891 BYY720891:BZB720891 CIU720891:CIX720891 CSQ720891:CST720891 DCM720891:DCP720891 DMI720891:DML720891 DWE720891:DWH720891 EGA720891:EGD720891 EPW720891:EPZ720891 EZS720891:EZV720891 FJO720891:FJR720891 FTK720891:FTN720891 GDG720891:GDJ720891 GNC720891:GNF720891 GWY720891:GXB720891 HGU720891:HGX720891 HQQ720891:HQT720891 IAM720891:IAP720891 IKI720891:IKL720891 IUE720891:IUH720891 JEA720891:JED720891 JNW720891:JNZ720891 JXS720891:JXV720891 KHO720891:KHR720891 KRK720891:KRN720891 LBG720891:LBJ720891 LLC720891:LLF720891 LUY720891:LVB720891 MEU720891:MEX720891 MOQ720891:MOT720891 MYM720891:MYP720891 NII720891:NIL720891 NSE720891:NSH720891 OCA720891:OCD720891 OLW720891:OLZ720891 OVS720891:OVV720891 PFO720891:PFR720891 PPK720891:PPN720891 PZG720891:PZJ720891 QJC720891:QJF720891 QSY720891:QTB720891 RCU720891:RCX720891 RMQ720891:RMT720891 RWM720891:RWP720891 SGI720891:SGL720891 SQE720891:SQH720891 TAA720891:TAD720891 TJW720891:TJZ720891 TTS720891:TTV720891 UDO720891:UDR720891 UNK720891:UNN720891 UXG720891:UXJ720891 VHC720891:VHF720891 VQY720891:VRB720891 WAU720891:WAX720891 WKQ720891:WKT720891 WUM720891:WUP720891 IA786427:ID786427 RW786427:RZ786427 ABS786427:ABV786427 ALO786427:ALR786427 AVK786427:AVN786427 BFG786427:BFJ786427 BPC786427:BPF786427 BYY786427:BZB786427 CIU786427:CIX786427 CSQ786427:CST786427 DCM786427:DCP786427 DMI786427:DML786427 DWE786427:DWH786427 EGA786427:EGD786427 EPW786427:EPZ786427 EZS786427:EZV786427 FJO786427:FJR786427 FTK786427:FTN786427 GDG786427:GDJ786427 GNC786427:GNF786427 GWY786427:GXB786427 HGU786427:HGX786427 HQQ786427:HQT786427 IAM786427:IAP786427 IKI786427:IKL786427 IUE786427:IUH786427 JEA786427:JED786427 JNW786427:JNZ786427 JXS786427:JXV786427 KHO786427:KHR786427 KRK786427:KRN786427 LBG786427:LBJ786427 LLC786427:LLF786427 LUY786427:LVB786427 MEU786427:MEX786427 MOQ786427:MOT786427 MYM786427:MYP786427 NII786427:NIL786427 NSE786427:NSH786427 OCA786427:OCD786427 OLW786427:OLZ786427 OVS786427:OVV786427 PFO786427:PFR786427 PPK786427:PPN786427 PZG786427:PZJ786427 QJC786427:QJF786427 QSY786427:QTB786427 RCU786427:RCX786427 RMQ786427:RMT786427 RWM786427:RWP786427 SGI786427:SGL786427 SQE786427:SQH786427 TAA786427:TAD786427 TJW786427:TJZ786427 TTS786427:TTV786427 UDO786427:UDR786427 UNK786427:UNN786427 UXG786427:UXJ786427 VHC786427:VHF786427 VQY786427:VRB786427 WAU786427:WAX786427 WKQ786427:WKT786427 WUM786427:WUP786427 IA851963:ID851963 RW851963:RZ851963 ABS851963:ABV851963 ALO851963:ALR851963 AVK851963:AVN851963 BFG851963:BFJ851963 BPC851963:BPF851963 BYY851963:BZB851963 CIU851963:CIX851963 CSQ851963:CST851963 DCM851963:DCP851963 DMI851963:DML851963 DWE851963:DWH851963 EGA851963:EGD851963 EPW851963:EPZ851963 EZS851963:EZV851963 FJO851963:FJR851963 FTK851963:FTN851963 GDG851963:GDJ851963 GNC851963:GNF851963 GWY851963:GXB851963 HGU851963:HGX851963 HQQ851963:HQT851963 IAM851963:IAP851963 IKI851963:IKL851963 IUE851963:IUH851963 JEA851963:JED851963 JNW851963:JNZ851963 JXS851963:JXV851963 KHO851963:KHR851963 KRK851963:KRN851963 LBG851963:LBJ851963 LLC851963:LLF851963 LUY851963:LVB851963 MEU851963:MEX851963 MOQ851963:MOT851963 MYM851963:MYP851963 NII851963:NIL851963 NSE851963:NSH851963 OCA851963:OCD851963 OLW851963:OLZ851963 OVS851963:OVV851963 PFO851963:PFR851963 PPK851963:PPN851963 PZG851963:PZJ851963 QJC851963:QJF851963 QSY851963:QTB851963 RCU851963:RCX851963 RMQ851963:RMT851963 RWM851963:RWP851963 SGI851963:SGL851963 SQE851963:SQH851963 TAA851963:TAD851963 TJW851963:TJZ851963 TTS851963:TTV851963 UDO851963:UDR851963 UNK851963:UNN851963 UXG851963:UXJ851963 VHC851963:VHF851963 VQY851963:VRB851963 WAU851963:WAX851963 WKQ851963:WKT851963 WUM851963:WUP851963 IA917499:ID917499 RW917499:RZ917499 ABS917499:ABV917499 ALO917499:ALR917499 AVK917499:AVN917499 BFG917499:BFJ917499 BPC917499:BPF917499 BYY917499:BZB917499 CIU917499:CIX917499 CSQ917499:CST917499 DCM917499:DCP917499 DMI917499:DML917499 DWE917499:DWH917499 EGA917499:EGD917499 EPW917499:EPZ917499 EZS917499:EZV917499 FJO917499:FJR917499 FTK917499:FTN917499 GDG917499:GDJ917499 GNC917499:GNF917499 GWY917499:GXB917499 HGU917499:HGX917499 HQQ917499:HQT917499 IAM917499:IAP917499 IKI917499:IKL917499 IUE917499:IUH917499 JEA917499:JED917499 JNW917499:JNZ917499 JXS917499:JXV917499 KHO917499:KHR917499 KRK917499:KRN917499 LBG917499:LBJ917499 LLC917499:LLF917499 LUY917499:LVB917499 MEU917499:MEX917499 MOQ917499:MOT917499 MYM917499:MYP917499 NII917499:NIL917499 NSE917499:NSH917499 OCA917499:OCD917499 OLW917499:OLZ917499 OVS917499:OVV917499 PFO917499:PFR917499 PPK917499:PPN917499 PZG917499:PZJ917499 QJC917499:QJF917499 QSY917499:QTB917499 RCU917499:RCX917499 RMQ917499:RMT917499 RWM917499:RWP917499 SGI917499:SGL917499 SQE917499:SQH917499 TAA917499:TAD917499 TJW917499:TJZ917499 TTS917499:TTV917499 UDO917499:UDR917499 UNK917499:UNN917499 UXG917499:UXJ917499 VHC917499:VHF917499 VQY917499:VRB917499 WAU917499:WAX917499 WKQ917499:WKT917499 WUM917499:WUP917499 AH131082:AJ131082 AH196618:AJ196618 AH262154:AJ262154 AH327690:AJ327690 AH393226:AJ393226 AH458762:AJ458762 AH524298:AJ524298 AH589834:AJ589834 AH655370:AJ655370 AH720906:AJ720906 AH786442:AJ786442 AH851978:AJ851978 AH917514:AJ917514 AH983050:AJ983050 AB917513:AD917513 AB851977:AD851977 AB786441:AD786441 AB720905:AD720905 AB655369:AD655369 AB589833:AD589833 AB524297:AD524297 AB458761:AD458761 AB393225:AD393225 AB327689:AD327689 AB262153:AD262153 AB196617:AD196617 AB131081:AD131081 AB65545:AD65545 AH65546:AJ65546 AB983049:AD983049 AE131082:AF131082 AE196618:AF196618 AE262154:AF262154 AE327690:AF327690 AE393226:AF393226 AE458762:AF458762 AE524298:AF524298 AE589834:AF589834 AE655370:AF655370 AE720906:AF720906 AE786442:AF786442 AE851978:AF851978 AE917514:AF917514 AE983050:AF983050 AE65546:AF65546 Q917499:S917499 Q851963:S851963 Q786427:S786427 Q720891:S720891 Q655355:S655355 Q589819:S589819 Q524283:S524283 Q458747:S458747 Q393211:S393211 Q327675:S327675 Q262139:S262139 Q196603:S196603 Q131067:S131067 Q65531:S65531 Q983035:S983035" xr:uid="{53C29DC1-0999-47B9-9B02-82B124C1E4C2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U65534:X65534 IF65534:II65534 SB65534:SE65534 ABX65534:ACA65534 ALT65534:ALW65534 AVP65534:AVS65534 BFL65534:BFO65534 BPH65534:BPK65534 BZD65534:BZG65534 CIZ65534:CJC65534 CSV65534:CSY65534 DCR65534:DCU65534 DMN65534:DMQ65534 DWJ65534:DWM65534 EGF65534:EGI65534 EQB65534:EQE65534 EZX65534:FAA65534 FJT65534:FJW65534 FTP65534:FTS65534 GDL65534:GDO65534 GNH65534:GNK65534 GXD65534:GXG65534 HGZ65534:HHC65534 HQV65534:HQY65534 IAR65534:IAU65534 IKN65534:IKQ65534 IUJ65534:IUM65534 JEF65534:JEI65534 JOB65534:JOE65534 JXX65534:JYA65534 KHT65534:KHW65534 KRP65534:KRS65534 LBL65534:LBO65534 LLH65534:LLK65534 LVD65534:LVG65534 MEZ65534:MFC65534 MOV65534:MOY65534 MYR65534:MYU65534 NIN65534:NIQ65534 NSJ65534:NSM65534 OCF65534:OCI65534 OMB65534:OME65534 OVX65534:OWA65534 PFT65534:PFW65534 PPP65534:PPS65534 PZL65534:PZO65534 QJH65534:QJK65534 QTD65534:QTG65534 RCZ65534:RDC65534 RMV65534:RMY65534 RWR65534:RWU65534 SGN65534:SGQ65534 SQJ65534:SQM65534 TAF65534:TAI65534 TKB65534:TKE65534 TTX65534:TUA65534 UDT65534:UDW65534 UNP65534:UNS65534 UXL65534:UXO65534 VHH65534:VHK65534 VRD65534:VRG65534 WAZ65534:WBC65534 WKV65534:WKY65534 WUR65534:WUU65534 U131070:X131070 IF131070:II131070 SB131070:SE131070 ABX131070:ACA131070 ALT131070:ALW131070 AVP131070:AVS131070 BFL131070:BFO131070 BPH131070:BPK131070 BZD131070:BZG131070 CIZ131070:CJC131070 CSV131070:CSY131070 DCR131070:DCU131070 DMN131070:DMQ131070 DWJ131070:DWM131070 EGF131070:EGI131070 EQB131070:EQE131070 EZX131070:FAA131070 FJT131070:FJW131070 FTP131070:FTS131070 GDL131070:GDO131070 GNH131070:GNK131070 GXD131070:GXG131070 HGZ131070:HHC131070 HQV131070:HQY131070 IAR131070:IAU131070 IKN131070:IKQ131070 IUJ131070:IUM131070 JEF131070:JEI131070 JOB131070:JOE131070 JXX131070:JYA131070 KHT131070:KHW131070 KRP131070:KRS131070 LBL131070:LBO131070 LLH131070:LLK131070 LVD131070:LVG131070 MEZ131070:MFC131070 MOV131070:MOY131070 MYR131070:MYU131070 NIN131070:NIQ131070 NSJ131070:NSM131070 OCF131070:OCI131070 OMB131070:OME131070 OVX131070:OWA131070 PFT131070:PFW131070 PPP131070:PPS131070 PZL131070:PZO131070 QJH131070:QJK131070 QTD131070:QTG131070 RCZ131070:RDC131070 RMV131070:RMY131070 RWR131070:RWU131070 SGN131070:SGQ131070 SQJ131070:SQM131070 TAF131070:TAI131070 TKB131070:TKE131070 TTX131070:TUA131070 UDT131070:UDW131070 UNP131070:UNS131070 UXL131070:UXO131070 VHH131070:VHK131070 VRD131070:VRG131070 WAZ131070:WBC131070 WKV131070:WKY131070 WUR131070:WUU131070 U196606:X196606 IF196606:II196606 SB196606:SE196606 ABX196606:ACA196606 ALT196606:ALW196606 AVP196606:AVS196606 BFL196606:BFO196606 BPH196606:BPK196606 BZD196606:BZG196606 CIZ196606:CJC196606 CSV196606:CSY196606 DCR196606:DCU196606 DMN196606:DMQ196606 DWJ196606:DWM196606 EGF196606:EGI196606 EQB196606:EQE196606 EZX196606:FAA196606 FJT196606:FJW196606 FTP196606:FTS196606 GDL196606:GDO196606 GNH196606:GNK196606 GXD196606:GXG196606 HGZ196606:HHC196606 HQV196606:HQY196606 IAR196606:IAU196606 IKN196606:IKQ196606 IUJ196606:IUM196606 JEF196606:JEI196606 JOB196606:JOE196606 JXX196606:JYA196606 KHT196606:KHW196606 KRP196606:KRS196606 LBL196606:LBO196606 LLH196606:LLK196606 LVD196606:LVG196606 MEZ196606:MFC196606 MOV196606:MOY196606 MYR196606:MYU196606 NIN196606:NIQ196606 NSJ196606:NSM196606 OCF196606:OCI196606 OMB196606:OME196606 OVX196606:OWA196606 PFT196606:PFW196606 PPP196606:PPS196606 PZL196606:PZO196606 QJH196606:QJK196606 QTD196606:QTG196606 RCZ196606:RDC196606 RMV196606:RMY196606 RWR196606:RWU196606 SGN196606:SGQ196606 SQJ196606:SQM196606 TAF196606:TAI196606 TKB196606:TKE196606 TTX196606:TUA196606 UDT196606:UDW196606 UNP196606:UNS196606 UXL196606:UXO196606 VHH196606:VHK196606 VRD196606:VRG196606 WAZ196606:WBC196606 WKV196606:WKY196606 WUR196606:WUU196606 U262142:X262142 IF262142:II262142 SB262142:SE262142 ABX262142:ACA262142 ALT262142:ALW262142 AVP262142:AVS262142 BFL262142:BFO262142 BPH262142:BPK262142 BZD262142:BZG262142 CIZ262142:CJC262142 CSV262142:CSY262142 DCR262142:DCU262142 DMN262142:DMQ262142 DWJ262142:DWM262142 EGF262142:EGI262142 EQB262142:EQE262142 EZX262142:FAA262142 FJT262142:FJW262142 FTP262142:FTS262142 GDL262142:GDO262142 GNH262142:GNK262142 GXD262142:GXG262142 HGZ262142:HHC262142 HQV262142:HQY262142 IAR262142:IAU262142 IKN262142:IKQ262142 IUJ262142:IUM262142 JEF262142:JEI262142 JOB262142:JOE262142 JXX262142:JYA262142 KHT262142:KHW262142 KRP262142:KRS262142 LBL262142:LBO262142 LLH262142:LLK262142 LVD262142:LVG262142 MEZ262142:MFC262142 MOV262142:MOY262142 MYR262142:MYU262142 NIN262142:NIQ262142 NSJ262142:NSM262142 OCF262142:OCI262142 OMB262142:OME262142 OVX262142:OWA262142 PFT262142:PFW262142 PPP262142:PPS262142 PZL262142:PZO262142 QJH262142:QJK262142 QTD262142:QTG262142 RCZ262142:RDC262142 RMV262142:RMY262142 RWR262142:RWU262142 SGN262142:SGQ262142 SQJ262142:SQM262142 TAF262142:TAI262142 TKB262142:TKE262142 TTX262142:TUA262142 UDT262142:UDW262142 UNP262142:UNS262142 UXL262142:UXO262142 VHH262142:VHK262142 VRD262142:VRG262142 WAZ262142:WBC262142 WKV262142:WKY262142 WUR262142:WUU262142 U327678:X327678 IF327678:II327678 SB327678:SE327678 ABX327678:ACA327678 ALT327678:ALW327678 AVP327678:AVS327678 BFL327678:BFO327678 BPH327678:BPK327678 BZD327678:BZG327678 CIZ327678:CJC327678 CSV327678:CSY327678 DCR327678:DCU327678 DMN327678:DMQ327678 DWJ327678:DWM327678 EGF327678:EGI327678 EQB327678:EQE327678 EZX327678:FAA327678 FJT327678:FJW327678 FTP327678:FTS327678 GDL327678:GDO327678 GNH327678:GNK327678 GXD327678:GXG327678 HGZ327678:HHC327678 HQV327678:HQY327678 IAR327678:IAU327678 IKN327678:IKQ327678 IUJ327678:IUM327678 JEF327678:JEI327678 JOB327678:JOE327678 JXX327678:JYA327678 KHT327678:KHW327678 KRP327678:KRS327678 LBL327678:LBO327678 LLH327678:LLK327678 LVD327678:LVG327678 MEZ327678:MFC327678 MOV327678:MOY327678 MYR327678:MYU327678 NIN327678:NIQ327678 NSJ327678:NSM327678 OCF327678:OCI327678 OMB327678:OME327678 OVX327678:OWA327678 PFT327678:PFW327678 PPP327678:PPS327678 PZL327678:PZO327678 QJH327678:QJK327678 QTD327678:QTG327678 RCZ327678:RDC327678 RMV327678:RMY327678 RWR327678:RWU327678 SGN327678:SGQ327678 SQJ327678:SQM327678 TAF327678:TAI327678 TKB327678:TKE327678 TTX327678:TUA327678 UDT327678:UDW327678 UNP327678:UNS327678 UXL327678:UXO327678 VHH327678:VHK327678 VRD327678:VRG327678 WAZ327678:WBC327678 WKV327678:WKY327678 WUR327678:WUU327678 U393214:X393214 IF393214:II393214 SB393214:SE393214 ABX393214:ACA393214 ALT393214:ALW393214 AVP393214:AVS393214 BFL393214:BFO393214 BPH393214:BPK393214 BZD393214:BZG393214 CIZ393214:CJC393214 CSV393214:CSY393214 DCR393214:DCU393214 DMN393214:DMQ393214 DWJ393214:DWM393214 EGF393214:EGI393214 EQB393214:EQE393214 EZX393214:FAA393214 FJT393214:FJW393214 FTP393214:FTS393214 GDL393214:GDO393214 GNH393214:GNK393214 GXD393214:GXG393214 HGZ393214:HHC393214 HQV393214:HQY393214 IAR393214:IAU393214 IKN393214:IKQ393214 IUJ393214:IUM393214 JEF393214:JEI393214 JOB393214:JOE393214 JXX393214:JYA393214 KHT393214:KHW393214 KRP393214:KRS393214 LBL393214:LBO393214 LLH393214:LLK393214 LVD393214:LVG393214 MEZ393214:MFC393214 MOV393214:MOY393214 MYR393214:MYU393214 NIN393214:NIQ393214 NSJ393214:NSM393214 OCF393214:OCI393214 OMB393214:OME393214 OVX393214:OWA393214 PFT393214:PFW393214 PPP393214:PPS393214 PZL393214:PZO393214 QJH393214:QJK393214 QTD393214:QTG393214 RCZ393214:RDC393214 RMV393214:RMY393214 RWR393214:RWU393214 SGN393214:SGQ393214 SQJ393214:SQM393214 TAF393214:TAI393214 TKB393214:TKE393214 TTX393214:TUA393214 UDT393214:UDW393214 UNP393214:UNS393214 UXL393214:UXO393214 VHH393214:VHK393214 VRD393214:VRG393214 WAZ393214:WBC393214 WKV393214:WKY393214 WUR393214:WUU393214 U458750:X458750 IF458750:II458750 SB458750:SE458750 ABX458750:ACA458750 ALT458750:ALW458750 AVP458750:AVS458750 BFL458750:BFO458750 BPH458750:BPK458750 BZD458750:BZG458750 CIZ458750:CJC458750 CSV458750:CSY458750 DCR458750:DCU458750 DMN458750:DMQ458750 DWJ458750:DWM458750 EGF458750:EGI458750 EQB458750:EQE458750 EZX458750:FAA458750 FJT458750:FJW458750 FTP458750:FTS458750 GDL458750:GDO458750 GNH458750:GNK458750 GXD458750:GXG458750 HGZ458750:HHC458750 HQV458750:HQY458750 IAR458750:IAU458750 IKN458750:IKQ458750 IUJ458750:IUM458750 JEF458750:JEI458750 JOB458750:JOE458750 JXX458750:JYA458750 KHT458750:KHW458750 KRP458750:KRS458750 LBL458750:LBO458750 LLH458750:LLK458750 LVD458750:LVG458750 MEZ458750:MFC458750 MOV458750:MOY458750 MYR458750:MYU458750 NIN458750:NIQ458750 NSJ458750:NSM458750 OCF458750:OCI458750 OMB458750:OME458750 OVX458750:OWA458750 PFT458750:PFW458750 PPP458750:PPS458750 PZL458750:PZO458750 QJH458750:QJK458750 QTD458750:QTG458750 RCZ458750:RDC458750 RMV458750:RMY458750 RWR458750:RWU458750 SGN458750:SGQ458750 SQJ458750:SQM458750 TAF458750:TAI458750 TKB458750:TKE458750 TTX458750:TUA458750 UDT458750:UDW458750 UNP458750:UNS458750 UXL458750:UXO458750 VHH458750:VHK458750 VRD458750:VRG458750 WAZ458750:WBC458750 WKV458750:WKY458750 WUR458750:WUU458750 U524286:X524286 IF524286:II524286 SB524286:SE524286 ABX524286:ACA524286 ALT524286:ALW524286 AVP524286:AVS524286 BFL524286:BFO524286 BPH524286:BPK524286 BZD524286:BZG524286 CIZ524286:CJC524286 CSV524286:CSY524286 DCR524286:DCU524286 DMN524286:DMQ524286 DWJ524286:DWM524286 EGF524286:EGI524286 EQB524286:EQE524286 EZX524286:FAA524286 FJT524286:FJW524286 FTP524286:FTS524286 GDL524286:GDO524286 GNH524286:GNK524286 GXD524286:GXG524286 HGZ524286:HHC524286 HQV524286:HQY524286 IAR524286:IAU524286 IKN524286:IKQ524286 IUJ524286:IUM524286 JEF524286:JEI524286 JOB524286:JOE524286 JXX524286:JYA524286 KHT524286:KHW524286 KRP524286:KRS524286 LBL524286:LBO524286 LLH524286:LLK524286 LVD524286:LVG524286 MEZ524286:MFC524286 MOV524286:MOY524286 MYR524286:MYU524286 NIN524286:NIQ524286 NSJ524286:NSM524286 OCF524286:OCI524286 OMB524286:OME524286 OVX524286:OWA524286 PFT524286:PFW524286 PPP524286:PPS524286 PZL524286:PZO524286 QJH524286:QJK524286 QTD524286:QTG524286 RCZ524286:RDC524286 RMV524286:RMY524286 RWR524286:RWU524286 SGN524286:SGQ524286 SQJ524286:SQM524286 TAF524286:TAI524286 TKB524286:TKE524286 TTX524286:TUA524286 UDT524286:UDW524286 UNP524286:UNS524286 UXL524286:UXO524286 VHH524286:VHK524286 VRD524286:VRG524286 WAZ524286:WBC524286 WKV524286:WKY524286 WUR524286:WUU524286 U589822:X589822 IF589822:II589822 SB589822:SE589822 ABX589822:ACA589822 ALT589822:ALW589822 AVP589822:AVS589822 BFL589822:BFO589822 BPH589822:BPK589822 BZD589822:BZG589822 CIZ589822:CJC589822 CSV589822:CSY589822 DCR589822:DCU589822 DMN589822:DMQ589822 DWJ589822:DWM589822 EGF589822:EGI589822 EQB589822:EQE589822 EZX589822:FAA589822 FJT589822:FJW589822 FTP589822:FTS589822 GDL589822:GDO589822 GNH589822:GNK589822 GXD589822:GXG589822 HGZ589822:HHC589822 HQV589822:HQY589822 IAR589822:IAU589822 IKN589822:IKQ589822 IUJ589822:IUM589822 JEF589822:JEI589822 JOB589822:JOE589822 JXX589822:JYA589822 KHT589822:KHW589822 KRP589822:KRS589822 LBL589822:LBO589822 LLH589822:LLK589822 LVD589822:LVG589822 MEZ589822:MFC589822 MOV589822:MOY589822 MYR589822:MYU589822 NIN589822:NIQ589822 NSJ589822:NSM589822 OCF589822:OCI589822 OMB589822:OME589822 OVX589822:OWA589822 PFT589822:PFW589822 PPP589822:PPS589822 PZL589822:PZO589822 QJH589822:QJK589822 QTD589822:QTG589822 RCZ589822:RDC589822 RMV589822:RMY589822 RWR589822:RWU589822 SGN589822:SGQ589822 SQJ589822:SQM589822 TAF589822:TAI589822 TKB589822:TKE589822 TTX589822:TUA589822 UDT589822:UDW589822 UNP589822:UNS589822 UXL589822:UXO589822 VHH589822:VHK589822 VRD589822:VRG589822 WAZ589822:WBC589822 WKV589822:WKY589822 WUR589822:WUU589822 U655358:X655358 IF655358:II655358 SB655358:SE655358 ABX655358:ACA655358 ALT655358:ALW655358 AVP655358:AVS655358 BFL655358:BFO655358 BPH655358:BPK655358 BZD655358:BZG655358 CIZ655358:CJC655358 CSV655358:CSY655358 DCR655358:DCU655358 DMN655358:DMQ655358 DWJ655358:DWM655358 EGF655358:EGI655358 EQB655358:EQE655358 EZX655358:FAA655358 FJT655358:FJW655358 FTP655358:FTS655358 GDL655358:GDO655358 GNH655358:GNK655358 GXD655358:GXG655358 HGZ655358:HHC655358 HQV655358:HQY655358 IAR655358:IAU655358 IKN655358:IKQ655358 IUJ655358:IUM655358 JEF655358:JEI655358 JOB655358:JOE655358 JXX655358:JYA655358 KHT655358:KHW655358 KRP655358:KRS655358 LBL655358:LBO655358 LLH655358:LLK655358 LVD655358:LVG655358 MEZ655358:MFC655358 MOV655358:MOY655358 MYR655358:MYU655358 NIN655358:NIQ655358 NSJ655358:NSM655358 OCF655358:OCI655358 OMB655358:OME655358 OVX655358:OWA655358 PFT655358:PFW655358 PPP655358:PPS655358 PZL655358:PZO655358 QJH655358:QJK655358 QTD655358:QTG655358 RCZ655358:RDC655358 RMV655358:RMY655358 RWR655358:RWU655358 SGN655358:SGQ655358 SQJ655358:SQM655358 TAF655358:TAI655358 TKB655358:TKE655358 TTX655358:TUA655358 UDT655358:UDW655358 UNP655358:UNS655358 UXL655358:UXO655358 VHH655358:VHK655358 VRD655358:VRG655358 WAZ655358:WBC655358 WKV655358:WKY655358 WUR655358:WUU655358 U720894:X720894 IF720894:II720894 SB720894:SE720894 ABX720894:ACA720894 ALT720894:ALW720894 AVP720894:AVS720894 BFL720894:BFO720894 BPH720894:BPK720894 BZD720894:BZG720894 CIZ720894:CJC720894 CSV720894:CSY720894 DCR720894:DCU720894 DMN720894:DMQ720894 DWJ720894:DWM720894 EGF720894:EGI720894 EQB720894:EQE720894 EZX720894:FAA720894 FJT720894:FJW720894 FTP720894:FTS720894 GDL720894:GDO720894 GNH720894:GNK720894 GXD720894:GXG720894 HGZ720894:HHC720894 HQV720894:HQY720894 IAR720894:IAU720894 IKN720894:IKQ720894 IUJ720894:IUM720894 JEF720894:JEI720894 JOB720894:JOE720894 JXX720894:JYA720894 KHT720894:KHW720894 KRP720894:KRS720894 LBL720894:LBO720894 LLH720894:LLK720894 LVD720894:LVG720894 MEZ720894:MFC720894 MOV720894:MOY720894 MYR720894:MYU720894 NIN720894:NIQ720894 NSJ720894:NSM720894 OCF720894:OCI720894 OMB720894:OME720894 OVX720894:OWA720894 PFT720894:PFW720894 PPP720894:PPS720894 PZL720894:PZO720894 QJH720894:QJK720894 QTD720894:QTG720894 RCZ720894:RDC720894 RMV720894:RMY720894 RWR720894:RWU720894 SGN720894:SGQ720894 SQJ720894:SQM720894 TAF720894:TAI720894 TKB720894:TKE720894 TTX720894:TUA720894 UDT720894:UDW720894 UNP720894:UNS720894 UXL720894:UXO720894 VHH720894:VHK720894 VRD720894:VRG720894 WAZ720894:WBC720894 WKV720894:WKY720894 WUR720894:WUU720894 U786430:X786430 IF786430:II786430 SB786430:SE786430 ABX786430:ACA786430 ALT786430:ALW786430 AVP786430:AVS786430 BFL786430:BFO786430 BPH786430:BPK786430 BZD786430:BZG786430 CIZ786430:CJC786430 CSV786430:CSY786430 DCR786430:DCU786430 DMN786430:DMQ786430 DWJ786430:DWM786430 EGF786430:EGI786430 EQB786430:EQE786430 EZX786430:FAA786430 FJT786430:FJW786430 FTP786430:FTS786430 GDL786430:GDO786430 GNH786430:GNK786430 GXD786430:GXG786430 HGZ786430:HHC786430 HQV786430:HQY786430 IAR786430:IAU786430 IKN786430:IKQ786430 IUJ786430:IUM786430 JEF786430:JEI786430 JOB786430:JOE786430 JXX786430:JYA786430 KHT786430:KHW786430 KRP786430:KRS786430 LBL786430:LBO786430 LLH786430:LLK786430 LVD786430:LVG786430 MEZ786430:MFC786430 MOV786430:MOY786430 MYR786430:MYU786430 NIN786430:NIQ786430 NSJ786430:NSM786430 OCF786430:OCI786430 OMB786430:OME786430 OVX786430:OWA786430 PFT786430:PFW786430 PPP786430:PPS786430 PZL786430:PZO786430 QJH786430:QJK786430 QTD786430:QTG786430 RCZ786430:RDC786430 RMV786430:RMY786430 RWR786430:RWU786430 SGN786430:SGQ786430 SQJ786430:SQM786430 TAF786430:TAI786430 TKB786430:TKE786430 TTX786430:TUA786430 UDT786430:UDW786430 UNP786430:UNS786430 UXL786430:UXO786430 VHH786430:VHK786430 VRD786430:VRG786430 WAZ786430:WBC786430 WKV786430:WKY786430 WUR786430:WUU786430 U851966:X851966 IF851966:II851966 SB851966:SE851966 ABX851966:ACA851966 ALT851966:ALW851966 AVP851966:AVS851966 BFL851966:BFO851966 BPH851966:BPK851966 BZD851966:BZG851966 CIZ851966:CJC851966 CSV851966:CSY851966 DCR851966:DCU851966 DMN851966:DMQ851966 DWJ851966:DWM851966 EGF851966:EGI851966 EQB851966:EQE851966 EZX851966:FAA851966 FJT851966:FJW851966 FTP851966:FTS851966 GDL851966:GDO851966 GNH851966:GNK851966 GXD851966:GXG851966 HGZ851966:HHC851966 HQV851966:HQY851966 IAR851966:IAU851966 IKN851966:IKQ851966 IUJ851966:IUM851966 JEF851966:JEI851966 JOB851966:JOE851966 JXX851966:JYA851966 KHT851966:KHW851966 KRP851966:KRS851966 LBL851966:LBO851966 LLH851966:LLK851966 LVD851966:LVG851966 MEZ851966:MFC851966 MOV851966:MOY851966 MYR851966:MYU851966 NIN851966:NIQ851966 NSJ851966:NSM851966 OCF851966:OCI851966 OMB851966:OME851966 OVX851966:OWA851966 PFT851966:PFW851966 PPP851966:PPS851966 PZL851966:PZO851966 QJH851966:QJK851966 QTD851966:QTG851966 RCZ851966:RDC851966 RMV851966:RMY851966 RWR851966:RWU851966 SGN851966:SGQ851966 SQJ851966:SQM851966 TAF851966:TAI851966 TKB851966:TKE851966 TTX851966:TUA851966 UDT851966:UDW851966 UNP851966:UNS851966 UXL851966:UXO851966 VHH851966:VHK851966 VRD851966:VRG851966 WAZ851966:WBC851966 WKV851966:WKY851966 WUR851966:WUU851966 U917502:X917502 IF917502:II917502 SB917502:SE917502 ABX917502:ACA917502 ALT917502:ALW917502 AVP917502:AVS917502 BFL917502:BFO917502 BPH917502:BPK917502 BZD917502:BZG917502 CIZ917502:CJC917502 CSV917502:CSY917502 DCR917502:DCU917502 DMN917502:DMQ917502 DWJ917502:DWM917502 EGF917502:EGI917502 EQB917502:EQE917502 EZX917502:FAA917502 FJT917502:FJW917502 FTP917502:FTS917502 GDL917502:GDO917502 GNH917502:GNK917502 GXD917502:GXG917502 HGZ917502:HHC917502 HQV917502:HQY917502 IAR917502:IAU917502 IKN917502:IKQ917502 IUJ917502:IUM917502 JEF917502:JEI917502 JOB917502:JOE917502 JXX917502:JYA917502 KHT917502:KHW917502 KRP917502:KRS917502 LBL917502:LBO917502 LLH917502:LLK917502 LVD917502:LVG917502 MEZ917502:MFC917502 MOV917502:MOY917502 MYR917502:MYU917502 NIN917502:NIQ917502 NSJ917502:NSM917502 OCF917502:OCI917502 OMB917502:OME917502 OVX917502:OWA917502 PFT917502:PFW917502 PPP917502:PPS917502 PZL917502:PZO917502 QJH917502:QJK917502 QTD917502:QTG917502 RCZ917502:RDC917502 RMV917502:RMY917502 RWR917502:RWU917502 SGN917502:SGQ917502 SQJ917502:SQM917502 TAF917502:TAI917502 TKB917502:TKE917502 TTX917502:TUA917502 UDT917502:UDW917502 UNP917502:UNS917502 UXL917502:UXO917502 VHH917502:VHK917502 VRD917502:VRG917502 WAZ917502:WBC917502 WKV917502:WKY917502 WUR917502:WUU917502 U983038:X983038 IF983038:II983038 SB983038:SE983038 ABX983038:ACA983038 ALT983038:ALW983038 AVP983038:AVS983038 BFL983038:BFO983038 BPH983038:BPK983038 BZD983038:BZG983038 CIZ983038:CJC983038 CSV983038:CSY983038 DCR983038:DCU983038 DMN983038:DMQ983038 DWJ983038:DWM983038 EGF983038:EGI983038 EQB983038:EQE983038 EZX983038:FAA983038 FJT983038:FJW983038 FTP983038:FTS983038 GDL983038:GDO983038 GNH983038:GNK983038 GXD983038:GXG983038 HGZ983038:HHC983038 HQV983038:HQY983038 IAR983038:IAU983038 IKN983038:IKQ983038 IUJ983038:IUM983038 JEF983038:JEI983038 JOB983038:JOE983038 JXX983038:JYA983038 KHT983038:KHW983038 KRP983038:KRS983038 LBL983038:LBO983038 LLH983038:LLK983038 LVD983038:LVG983038 MEZ983038:MFC983038 MOV983038:MOY983038 MYR983038:MYU983038 NIN983038:NIQ983038 NSJ983038:NSM983038 OCF983038:OCI983038 OMB983038:OME983038 OVX983038:OWA983038 PFT983038:PFW983038 PPP983038:PPS983038 PZL983038:PZO983038 QJH983038:QJK983038 QTD983038:QTG983038 RCZ983038:RDC983038 RMV983038:RMY983038 RWR983038:RWU983038 SGN983038:SGQ983038 SQJ983038:SQM983038 TAF983038:TAI983038 TKB983038:TKE983038 TTX983038:TUA983038 UDT983038:UDW983038 UNP983038:UNS983038 UXL983038:UXO983038 VHH983038:VHK983038 VRD983038:VRG983038 WAZ983038:WBC983038 WKV983038:WKY983038 WUR983038:WUU983038 IA983037:ID983037 RW983037:RZ983037 ABS983037:ABV983037 ALO983037:ALR983037 AVK983037:AVN983037 BFG983037:BFJ983037 BPC983037:BPF983037 BYY983037:BZB983037 CIU983037:CIX983037 CSQ983037:CST983037 DCM983037:DCP983037 DMI983037:DML983037 DWE983037:DWH983037 EGA983037:EGD983037 EPW983037:EPZ983037 EZS983037:EZV983037 FJO983037:FJR983037 FTK983037:FTN983037 GDG983037:GDJ983037 GNC983037:GNF983037 GWY983037:GXB983037 HGU983037:HGX983037 HQQ983037:HQT983037 IAM983037:IAP983037 IKI983037:IKL983037 IUE983037:IUH983037 JEA983037:JED983037 JNW983037:JNZ983037 JXS983037:JXV983037 KHO983037:KHR983037 KRK983037:KRN983037 LBG983037:LBJ983037 LLC983037:LLF983037 LUY983037:LVB983037 MEU983037:MEX983037 MOQ983037:MOT983037 MYM983037:MYP983037 NII983037:NIL983037 NSE983037:NSH983037 OCA983037:OCD983037 OLW983037:OLZ983037 OVS983037:OVV983037 PFO983037:PFR983037 PPK983037:PPN983037 PZG983037:PZJ983037 QJC983037:QJF983037 QSY983037:QTB983037 RCU983037:RCX983037 RMQ983037:RMT983037 RWM983037:RWP983037 SGI983037:SGL983037 SQE983037:SQH983037 TAA983037:TAD983037 TJW983037:TJZ983037 TTS983037:TTV983037 UDO983037:UDR983037 UNK983037:UNN983037 UXG983037:UXJ983037 VHC983037:VHF983037 VQY983037:VRB983037 WAU983037:WAX983037 WKQ983037:WKT983037 WUM983037:WUP983037 IA65533:ID65533 RW65533:RZ65533 ABS65533:ABV65533 ALO65533:ALR65533 AVK65533:AVN65533 BFG65533:BFJ65533 BPC65533:BPF65533 BYY65533:BZB65533 CIU65533:CIX65533 CSQ65533:CST65533 DCM65533:DCP65533 DMI65533:DML65533 DWE65533:DWH65533 EGA65533:EGD65533 EPW65533:EPZ65533 EZS65533:EZV65533 FJO65533:FJR65533 FTK65533:FTN65533 GDG65533:GDJ65533 GNC65533:GNF65533 GWY65533:GXB65533 HGU65533:HGX65533 HQQ65533:HQT65533 IAM65533:IAP65533 IKI65533:IKL65533 IUE65533:IUH65533 JEA65533:JED65533 JNW65533:JNZ65533 JXS65533:JXV65533 KHO65533:KHR65533 KRK65533:KRN65533 LBG65533:LBJ65533 LLC65533:LLF65533 LUY65533:LVB65533 MEU65533:MEX65533 MOQ65533:MOT65533 MYM65533:MYP65533 NII65533:NIL65533 NSE65533:NSH65533 OCA65533:OCD65533 OLW65533:OLZ65533 OVS65533:OVV65533 PFO65533:PFR65533 PPK65533:PPN65533 PZG65533:PZJ65533 QJC65533:QJF65533 QSY65533:QTB65533 RCU65533:RCX65533 RMQ65533:RMT65533 RWM65533:RWP65533 SGI65533:SGL65533 SQE65533:SQH65533 TAA65533:TAD65533 TJW65533:TJZ65533 TTS65533:TTV65533 UDO65533:UDR65533 UNK65533:UNN65533 UXG65533:UXJ65533 VHC65533:VHF65533 VQY65533:VRB65533 WAU65533:WAX65533 WKQ65533:WKT65533 WUM65533:WUP65533 IA131069:ID131069 RW131069:RZ131069 ABS131069:ABV131069 ALO131069:ALR131069 AVK131069:AVN131069 BFG131069:BFJ131069 BPC131069:BPF131069 BYY131069:BZB131069 CIU131069:CIX131069 CSQ131069:CST131069 DCM131069:DCP131069 DMI131069:DML131069 DWE131069:DWH131069 EGA131069:EGD131069 EPW131069:EPZ131069 EZS131069:EZV131069 FJO131069:FJR131069 FTK131069:FTN131069 GDG131069:GDJ131069 GNC131069:GNF131069 GWY131069:GXB131069 HGU131069:HGX131069 HQQ131069:HQT131069 IAM131069:IAP131069 IKI131069:IKL131069 IUE131069:IUH131069 JEA131069:JED131069 JNW131069:JNZ131069 JXS131069:JXV131069 KHO131069:KHR131069 KRK131069:KRN131069 LBG131069:LBJ131069 LLC131069:LLF131069 LUY131069:LVB131069 MEU131069:MEX131069 MOQ131069:MOT131069 MYM131069:MYP131069 NII131069:NIL131069 NSE131069:NSH131069 OCA131069:OCD131069 OLW131069:OLZ131069 OVS131069:OVV131069 PFO131069:PFR131069 PPK131069:PPN131069 PZG131069:PZJ131069 QJC131069:QJF131069 QSY131069:QTB131069 RCU131069:RCX131069 RMQ131069:RMT131069 RWM131069:RWP131069 SGI131069:SGL131069 SQE131069:SQH131069 TAA131069:TAD131069 TJW131069:TJZ131069 TTS131069:TTV131069 UDO131069:UDR131069 UNK131069:UNN131069 UXG131069:UXJ131069 VHC131069:VHF131069 VQY131069:VRB131069 WAU131069:WAX131069 WKQ131069:WKT131069 WUM131069:WUP131069 IA196605:ID196605 RW196605:RZ196605 ABS196605:ABV196605 ALO196605:ALR196605 AVK196605:AVN196605 BFG196605:BFJ196605 BPC196605:BPF196605 BYY196605:BZB196605 CIU196605:CIX196605 CSQ196605:CST196605 DCM196605:DCP196605 DMI196605:DML196605 DWE196605:DWH196605 EGA196605:EGD196605 EPW196605:EPZ196605 EZS196605:EZV196605 FJO196605:FJR196605 FTK196605:FTN196605 GDG196605:GDJ196605 GNC196605:GNF196605 GWY196605:GXB196605 HGU196605:HGX196605 HQQ196605:HQT196605 IAM196605:IAP196605 IKI196605:IKL196605 IUE196605:IUH196605 JEA196605:JED196605 JNW196605:JNZ196605 JXS196605:JXV196605 KHO196605:KHR196605 KRK196605:KRN196605 LBG196605:LBJ196605 LLC196605:LLF196605 LUY196605:LVB196605 MEU196605:MEX196605 MOQ196605:MOT196605 MYM196605:MYP196605 NII196605:NIL196605 NSE196605:NSH196605 OCA196605:OCD196605 OLW196605:OLZ196605 OVS196605:OVV196605 PFO196605:PFR196605 PPK196605:PPN196605 PZG196605:PZJ196605 QJC196605:QJF196605 QSY196605:QTB196605 RCU196605:RCX196605 RMQ196605:RMT196605 RWM196605:RWP196605 SGI196605:SGL196605 SQE196605:SQH196605 TAA196605:TAD196605 TJW196605:TJZ196605 TTS196605:TTV196605 UDO196605:UDR196605 UNK196605:UNN196605 UXG196605:UXJ196605 VHC196605:VHF196605 VQY196605:VRB196605 WAU196605:WAX196605 WKQ196605:WKT196605 WUM196605:WUP196605 IA262141:ID262141 RW262141:RZ262141 ABS262141:ABV262141 ALO262141:ALR262141 AVK262141:AVN262141 BFG262141:BFJ262141 BPC262141:BPF262141 BYY262141:BZB262141 CIU262141:CIX262141 CSQ262141:CST262141 DCM262141:DCP262141 DMI262141:DML262141 DWE262141:DWH262141 EGA262141:EGD262141 EPW262141:EPZ262141 EZS262141:EZV262141 FJO262141:FJR262141 FTK262141:FTN262141 GDG262141:GDJ262141 GNC262141:GNF262141 GWY262141:GXB262141 HGU262141:HGX262141 HQQ262141:HQT262141 IAM262141:IAP262141 IKI262141:IKL262141 IUE262141:IUH262141 JEA262141:JED262141 JNW262141:JNZ262141 JXS262141:JXV262141 KHO262141:KHR262141 KRK262141:KRN262141 LBG262141:LBJ262141 LLC262141:LLF262141 LUY262141:LVB262141 MEU262141:MEX262141 MOQ262141:MOT262141 MYM262141:MYP262141 NII262141:NIL262141 NSE262141:NSH262141 OCA262141:OCD262141 OLW262141:OLZ262141 OVS262141:OVV262141 PFO262141:PFR262141 PPK262141:PPN262141 PZG262141:PZJ262141 QJC262141:QJF262141 QSY262141:QTB262141 RCU262141:RCX262141 RMQ262141:RMT262141 RWM262141:RWP262141 SGI262141:SGL262141 SQE262141:SQH262141 TAA262141:TAD262141 TJW262141:TJZ262141 TTS262141:TTV262141 UDO262141:UDR262141 UNK262141:UNN262141 UXG262141:UXJ262141 VHC262141:VHF262141 VQY262141:VRB262141 WAU262141:WAX262141 WKQ262141:WKT262141 WUM262141:WUP262141 IA327677:ID327677 RW327677:RZ327677 ABS327677:ABV327677 ALO327677:ALR327677 AVK327677:AVN327677 BFG327677:BFJ327677 BPC327677:BPF327677 BYY327677:BZB327677 CIU327677:CIX327677 CSQ327677:CST327677 DCM327677:DCP327677 DMI327677:DML327677 DWE327677:DWH327677 EGA327677:EGD327677 EPW327677:EPZ327677 EZS327677:EZV327677 FJO327677:FJR327677 FTK327677:FTN327677 GDG327677:GDJ327677 GNC327677:GNF327677 GWY327677:GXB327677 HGU327677:HGX327677 HQQ327677:HQT327677 IAM327677:IAP327677 IKI327677:IKL327677 IUE327677:IUH327677 JEA327677:JED327677 JNW327677:JNZ327677 JXS327677:JXV327677 KHO327677:KHR327677 KRK327677:KRN327677 LBG327677:LBJ327677 LLC327677:LLF327677 LUY327677:LVB327677 MEU327677:MEX327677 MOQ327677:MOT327677 MYM327677:MYP327677 NII327677:NIL327677 NSE327677:NSH327677 OCA327677:OCD327677 OLW327677:OLZ327677 OVS327677:OVV327677 PFO327677:PFR327677 PPK327677:PPN327677 PZG327677:PZJ327677 QJC327677:QJF327677 QSY327677:QTB327677 RCU327677:RCX327677 RMQ327677:RMT327677 RWM327677:RWP327677 SGI327677:SGL327677 SQE327677:SQH327677 TAA327677:TAD327677 TJW327677:TJZ327677 TTS327677:TTV327677 UDO327677:UDR327677 UNK327677:UNN327677 UXG327677:UXJ327677 VHC327677:VHF327677 VQY327677:VRB327677 WAU327677:WAX327677 WKQ327677:WKT327677 WUM327677:WUP327677 IA393213:ID393213 RW393213:RZ393213 ABS393213:ABV393213 ALO393213:ALR393213 AVK393213:AVN393213 BFG393213:BFJ393213 BPC393213:BPF393213 BYY393213:BZB393213 CIU393213:CIX393213 CSQ393213:CST393213 DCM393213:DCP393213 DMI393213:DML393213 DWE393213:DWH393213 EGA393213:EGD393213 EPW393213:EPZ393213 EZS393213:EZV393213 FJO393213:FJR393213 FTK393213:FTN393213 GDG393213:GDJ393213 GNC393213:GNF393213 GWY393213:GXB393213 HGU393213:HGX393213 HQQ393213:HQT393213 IAM393213:IAP393213 IKI393213:IKL393213 IUE393213:IUH393213 JEA393213:JED393213 JNW393213:JNZ393213 JXS393213:JXV393213 KHO393213:KHR393213 KRK393213:KRN393213 LBG393213:LBJ393213 LLC393213:LLF393213 LUY393213:LVB393213 MEU393213:MEX393213 MOQ393213:MOT393213 MYM393213:MYP393213 NII393213:NIL393213 NSE393213:NSH393213 OCA393213:OCD393213 OLW393213:OLZ393213 OVS393213:OVV393213 PFO393213:PFR393213 PPK393213:PPN393213 PZG393213:PZJ393213 QJC393213:QJF393213 QSY393213:QTB393213 RCU393213:RCX393213 RMQ393213:RMT393213 RWM393213:RWP393213 SGI393213:SGL393213 SQE393213:SQH393213 TAA393213:TAD393213 TJW393213:TJZ393213 TTS393213:TTV393213 UDO393213:UDR393213 UNK393213:UNN393213 UXG393213:UXJ393213 VHC393213:VHF393213 VQY393213:VRB393213 WAU393213:WAX393213 WKQ393213:WKT393213 WUM393213:WUP393213 IA458749:ID458749 RW458749:RZ458749 ABS458749:ABV458749 ALO458749:ALR458749 AVK458749:AVN458749 BFG458749:BFJ458749 BPC458749:BPF458749 BYY458749:BZB458749 CIU458749:CIX458749 CSQ458749:CST458749 DCM458749:DCP458749 DMI458749:DML458749 DWE458749:DWH458749 EGA458749:EGD458749 EPW458749:EPZ458749 EZS458749:EZV458749 FJO458749:FJR458749 FTK458749:FTN458749 GDG458749:GDJ458749 GNC458749:GNF458749 GWY458749:GXB458749 HGU458749:HGX458749 HQQ458749:HQT458749 IAM458749:IAP458749 IKI458749:IKL458749 IUE458749:IUH458749 JEA458749:JED458749 JNW458749:JNZ458749 JXS458749:JXV458749 KHO458749:KHR458749 KRK458749:KRN458749 LBG458749:LBJ458749 LLC458749:LLF458749 LUY458749:LVB458749 MEU458749:MEX458749 MOQ458749:MOT458749 MYM458749:MYP458749 NII458749:NIL458749 NSE458749:NSH458749 OCA458749:OCD458749 OLW458749:OLZ458749 OVS458749:OVV458749 PFO458749:PFR458749 PPK458749:PPN458749 PZG458749:PZJ458749 QJC458749:QJF458749 QSY458749:QTB458749 RCU458749:RCX458749 RMQ458749:RMT458749 RWM458749:RWP458749 SGI458749:SGL458749 SQE458749:SQH458749 TAA458749:TAD458749 TJW458749:TJZ458749 TTS458749:TTV458749 UDO458749:UDR458749 UNK458749:UNN458749 UXG458749:UXJ458749 VHC458749:VHF458749 VQY458749:VRB458749 WAU458749:WAX458749 WKQ458749:WKT458749 WUM458749:WUP458749 IA524285:ID524285 RW524285:RZ524285 ABS524285:ABV524285 ALO524285:ALR524285 AVK524285:AVN524285 BFG524285:BFJ524285 BPC524285:BPF524285 BYY524285:BZB524285 CIU524285:CIX524285 CSQ524285:CST524285 DCM524285:DCP524285 DMI524285:DML524285 DWE524285:DWH524285 EGA524285:EGD524285 EPW524285:EPZ524285 EZS524285:EZV524285 FJO524285:FJR524285 FTK524285:FTN524285 GDG524285:GDJ524285 GNC524285:GNF524285 GWY524285:GXB524285 HGU524285:HGX524285 HQQ524285:HQT524285 IAM524285:IAP524285 IKI524285:IKL524285 IUE524285:IUH524285 JEA524285:JED524285 JNW524285:JNZ524285 JXS524285:JXV524285 KHO524285:KHR524285 KRK524285:KRN524285 LBG524285:LBJ524285 LLC524285:LLF524285 LUY524285:LVB524285 MEU524285:MEX524285 MOQ524285:MOT524285 MYM524285:MYP524285 NII524285:NIL524285 NSE524285:NSH524285 OCA524285:OCD524285 OLW524285:OLZ524285 OVS524285:OVV524285 PFO524285:PFR524285 PPK524285:PPN524285 PZG524285:PZJ524285 QJC524285:QJF524285 QSY524285:QTB524285 RCU524285:RCX524285 RMQ524285:RMT524285 RWM524285:RWP524285 SGI524285:SGL524285 SQE524285:SQH524285 TAA524285:TAD524285 TJW524285:TJZ524285 TTS524285:TTV524285 UDO524285:UDR524285 UNK524285:UNN524285 UXG524285:UXJ524285 VHC524285:VHF524285 VQY524285:VRB524285 WAU524285:WAX524285 WKQ524285:WKT524285 WUM524285:WUP524285 IA589821:ID589821 RW589821:RZ589821 ABS589821:ABV589821 ALO589821:ALR589821 AVK589821:AVN589821 BFG589821:BFJ589821 BPC589821:BPF589821 BYY589821:BZB589821 CIU589821:CIX589821 CSQ589821:CST589821 DCM589821:DCP589821 DMI589821:DML589821 DWE589821:DWH589821 EGA589821:EGD589821 EPW589821:EPZ589821 EZS589821:EZV589821 FJO589821:FJR589821 FTK589821:FTN589821 GDG589821:GDJ589821 GNC589821:GNF589821 GWY589821:GXB589821 HGU589821:HGX589821 HQQ589821:HQT589821 IAM589821:IAP589821 IKI589821:IKL589821 IUE589821:IUH589821 JEA589821:JED589821 JNW589821:JNZ589821 JXS589821:JXV589821 KHO589821:KHR589821 KRK589821:KRN589821 LBG589821:LBJ589821 LLC589821:LLF589821 LUY589821:LVB589821 MEU589821:MEX589821 MOQ589821:MOT589821 MYM589821:MYP589821 NII589821:NIL589821 NSE589821:NSH589821 OCA589821:OCD589821 OLW589821:OLZ589821 OVS589821:OVV589821 PFO589821:PFR589821 PPK589821:PPN589821 PZG589821:PZJ589821 QJC589821:QJF589821 QSY589821:QTB589821 RCU589821:RCX589821 RMQ589821:RMT589821 RWM589821:RWP589821 SGI589821:SGL589821 SQE589821:SQH589821 TAA589821:TAD589821 TJW589821:TJZ589821 TTS589821:TTV589821 UDO589821:UDR589821 UNK589821:UNN589821 UXG589821:UXJ589821 VHC589821:VHF589821 VQY589821:VRB589821 WAU589821:WAX589821 WKQ589821:WKT589821 WUM589821:WUP589821 IA655357:ID655357 RW655357:RZ655357 ABS655357:ABV655357 ALO655357:ALR655357 AVK655357:AVN655357 BFG655357:BFJ655357 BPC655357:BPF655357 BYY655357:BZB655357 CIU655357:CIX655357 CSQ655357:CST655357 DCM655357:DCP655357 DMI655357:DML655357 DWE655357:DWH655357 EGA655357:EGD655357 EPW655357:EPZ655357 EZS655357:EZV655357 FJO655357:FJR655357 FTK655357:FTN655357 GDG655357:GDJ655357 GNC655357:GNF655357 GWY655357:GXB655357 HGU655357:HGX655357 HQQ655357:HQT655357 IAM655357:IAP655357 IKI655357:IKL655357 IUE655357:IUH655357 JEA655357:JED655357 JNW655357:JNZ655357 JXS655357:JXV655357 KHO655357:KHR655357 KRK655357:KRN655357 LBG655357:LBJ655357 LLC655357:LLF655357 LUY655357:LVB655357 MEU655357:MEX655357 MOQ655357:MOT655357 MYM655357:MYP655357 NII655357:NIL655357 NSE655357:NSH655357 OCA655357:OCD655357 OLW655357:OLZ655357 OVS655357:OVV655357 PFO655357:PFR655357 PPK655357:PPN655357 PZG655357:PZJ655357 QJC655357:QJF655357 QSY655357:QTB655357 RCU655357:RCX655357 RMQ655357:RMT655357 RWM655357:RWP655357 SGI655357:SGL655357 SQE655357:SQH655357 TAA655357:TAD655357 TJW655357:TJZ655357 TTS655357:TTV655357 UDO655357:UDR655357 UNK655357:UNN655357 UXG655357:UXJ655357 VHC655357:VHF655357 VQY655357:VRB655357 WAU655357:WAX655357 WKQ655357:WKT655357 WUM655357:WUP655357 IA720893:ID720893 RW720893:RZ720893 ABS720893:ABV720893 ALO720893:ALR720893 AVK720893:AVN720893 BFG720893:BFJ720893 BPC720893:BPF720893 BYY720893:BZB720893 CIU720893:CIX720893 CSQ720893:CST720893 DCM720893:DCP720893 DMI720893:DML720893 DWE720893:DWH720893 EGA720893:EGD720893 EPW720893:EPZ720893 EZS720893:EZV720893 FJO720893:FJR720893 FTK720893:FTN720893 GDG720893:GDJ720893 GNC720893:GNF720893 GWY720893:GXB720893 HGU720893:HGX720893 HQQ720893:HQT720893 IAM720893:IAP720893 IKI720893:IKL720893 IUE720893:IUH720893 JEA720893:JED720893 JNW720893:JNZ720893 JXS720893:JXV720893 KHO720893:KHR720893 KRK720893:KRN720893 LBG720893:LBJ720893 LLC720893:LLF720893 LUY720893:LVB720893 MEU720893:MEX720893 MOQ720893:MOT720893 MYM720893:MYP720893 NII720893:NIL720893 NSE720893:NSH720893 OCA720893:OCD720893 OLW720893:OLZ720893 OVS720893:OVV720893 PFO720893:PFR720893 PPK720893:PPN720893 PZG720893:PZJ720893 QJC720893:QJF720893 QSY720893:QTB720893 RCU720893:RCX720893 RMQ720893:RMT720893 RWM720893:RWP720893 SGI720893:SGL720893 SQE720893:SQH720893 TAA720893:TAD720893 TJW720893:TJZ720893 TTS720893:TTV720893 UDO720893:UDR720893 UNK720893:UNN720893 UXG720893:UXJ720893 VHC720893:VHF720893 VQY720893:VRB720893 WAU720893:WAX720893 WKQ720893:WKT720893 WUM720893:WUP720893 IA786429:ID786429 RW786429:RZ786429 ABS786429:ABV786429 ALO786429:ALR786429 AVK786429:AVN786429 BFG786429:BFJ786429 BPC786429:BPF786429 BYY786429:BZB786429 CIU786429:CIX786429 CSQ786429:CST786429 DCM786429:DCP786429 DMI786429:DML786429 DWE786429:DWH786429 EGA786429:EGD786429 EPW786429:EPZ786429 EZS786429:EZV786429 FJO786429:FJR786429 FTK786429:FTN786429 GDG786429:GDJ786429 GNC786429:GNF786429 GWY786429:GXB786429 HGU786429:HGX786429 HQQ786429:HQT786429 IAM786429:IAP786429 IKI786429:IKL786429 IUE786429:IUH786429 JEA786429:JED786429 JNW786429:JNZ786429 JXS786429:JXV786429 KHO786429:KHR786429 KRK786429:KRN786429 LBG786429:LBJ786429 LLC786429:LLF786429 LUY786429:LVB786429 MEU786429:MEX786429 MOQ786429:MOT786429 MYM786429:MYP786429 NII786429:NIL786429 NSE786429:NSH786429 OCA786429:OCD786429 OLW786429:OLZ786429 OVS786429:OVV786429 PFO786429:PFR786429 PPK786429:PPN786429 PZG786429:PZJ786429 QJC786429:QJF786429 QSY786429:QTB786429 RCU786429:RCX786429 RMQ786429:RMT786429 RWM786429:RWP786429 SGI786429:SGL786429 SQE786429:SQH786429 TAA786429:TAD786429 TJW786429:TJZ786429 TTS786429:TTV786429 UDO786429:UDR786429 UNK786429:UNN786429 UXG786429:UXJ786429 VHC786429:VHF786429 VQY786429:VRB786429 WAU786429:WAX786429 WKQ786429:WKT786429 WUM786429:WUP786429 IA851965:ID851965 RW851965:RZ851965 ABS851965:ABV851965 ALO851965:ALR851965 AVK851965:AVN851965 BFG851965:BFJ851965 BPC851965:BPF851965 BYY851965:BZB851965 CIU851965:CIX851965 CSQ851965:CST851965 DCM851965:DCP851965 DMI851965:DML851965 DWE851965:DWH851965 EGA851965:EGD851965 EPW851965:EPZ851965 EZS851965:EZV851965 FJO851965:FJR851965 FTK851965:FTN851965 GDG851965:GDJ851965 GNC851965:GNF851965 GWY851965:GXB851965 HGU851965:HGX851965 HQQ851965:HQT851965 IAM851965:IAP851965 IKI851965:IKL851965 IUE851965:IUH851965 JEA851965:JED851965 JNW851965:JNZ851965 JXS851965:JXV851965 KHO851965:KHR851965 KRK851965:KRN851965 LBG851965:LBJ851965 LLC851965:LLF851965 LUY851965:LVB851965 MEU851965:MEX851965 MOQ851965:MOT851965 MYM851965:MYP851965 NII851965:NIL851965 NSE851965:NSH851965 OCA851965:OCD851965 OLW851965:OLZ851965 OVS851965:OVV851965 PFO851965:PFR851965 PPK851965:PPN851965 PZG851965:PZJ851965 QJC851965:QJF851965 QSY851965:QTB851965 RCU851965:RCX851965 RMQ851965:RMT851965 RWM851965:RWP851965 SGI851965:SGL851965 SQE851965:SQH851965 TAA851965:TAD851965 TJW851965:TJZ851965 TTS851965:TTV851965 UDO851965:UDR851965 UNK851965:UNN851965 UXG851965:UXJ851965 VHC851965:VHF851965 VQY851965:VRB851965 WAU851965:WAX851965 WKQ851965:WKT851965 WUM851965:WUP851965 IA917501:ID917501 RW917501:RZ917501 ABS917501:ABV917501 ALO917501:ALR917501 AVK917501:AVN917501 BFG917501:BFJ917501 BPC917501:BPF917501 BYY917501:BZB917501 CIU917501:CIX917501 CSQ917501:CST917501 DCM917501:DCP917501 DMI917501:DML917501 DWE917501:DWH917501 EGA917501:EGD917501 EPW917501:EPZ917501 EZS917501:EZV917501 FJO917501:FJR917501 FTK917501:FTN917501 GDG917501:GDJ917501 GNC917501:GNF917501 GWY917501:GXB917501 HGU917501:HGX917501 HQQ917501:HQT917501 IAM917501:IAP917501 IKI917501:IKL917501 IUE917501:IUH917501 JEA917501:JED917501 JNW917501:JNZ917501 JXS917501:JXV917501 KHO917501:KHR917501 KRK917501:KRN917501 LBG917501:LBJ917501 LLC917501:LLF917501 LUY917501:LVB917501 MEU917501:MEX917501 MOQ917501:MOT917501 MYM917501:MYP917501 NII917501:NIL917501 NSE917501:NSH917501 OCA917501:OCD917501 OLW917501:OLZ917501 OVS917501:OVV917501 PFO917501:PFR917501 PPK917501:PPN917501 PZG917501:PZJ917501 QJC917501:QJF917501 QSY917501:QTB917501 RCU917501:RCX917501 RMQ917501:RMT917501 RWM917501:RWP917501 SGI917501:SGL917501 SQE917501:SQH917501 TAA917501:TAD917501 TJW917501:TJZ917501 TTS917501:TTV917501 UDO917501:UDR917501 UNK917501:UNN917501 UXG917501:UXJ917501 VHC917501:VHF917501 VQY917501:VRB917501 WAU917501:WAX917501 WKQ917501:WKT917501 WUM917501:WUP917501 AH131084:AJ131084 AH196620:AJ196620 AH262156:AJ262156 AH327692:AJ327692 AH393228:AJ393228 AH458764:AJ458764 AH524300:AJ524300 AH589836:AJ589836 AH655372:AJ655372 AH720908:AJ720908 AH786444:AJ786444 AH851980:AJ851980 AH917516:AJ917516 AH983052:AJ983052 AB917515:AD917515 AB851979:AD851979 AB786443:AD786443 AB720907:AD720907 AB655371:AD655371 AB589835:AD589835 AB524299:AD524299 AB458763:AD458763 AB393227:AD393227 AB327691:AD327691 AB262155:AD262155 AB196619:AD196619 AB131083:AD131083 AB65547:AD65547 AH65548:AJ65548 AB983051:AD983051 AE131084:AF131084 AE196620:AF196620 AE262156:AF262156 AE327692:AF327692 AE393228:AF393228 AE458764:AF458764 AE524300:AF524300 AE589836:AF589836 AE655372:AF655372 AE720908:AF720908 AE786444:AF786444 AE851980:AF851980 AE917516:AF917516 AE983052:AF983052 AE65548:AF65548 Q917501:S917501 Q851965:S851965 Q786429:S786429 Q720893:S720893 Q655357:S655357 Q589821:S589821 Q524285:S524285 Q458749:S458749 Q393213:S393213 Q327677:S327677 Q262141:S262141 Q196605:S196605 Q131069:S131069 Q65533:S65533 Q983037:S983037" xr:uid="{53C29DC1-0999-47B9-9B02-82B124C1E4C2}">
       <formula1>"○, ○（オンライン処理設計書なし）"</formula1>
     </dataValidation>
   </dataValidations>
@@ -28322,21 +28905,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:85" ht="13.75" customHeight="1">
-      <c r="A1" s="304" t="s">
+      <c r="A1" s="312" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="304"/>
-      <c r="C1" s="304"/>
-      <c r="D1" s="304"/>
-      <c r="E1" s="304"/>
-      <c r="F1" s="304"/>
-      <c r="G1" s="304"/>
-      <c r="H1" s="304"/>
-      <c r="I1" s="304"/>
-      <c r="J1" s="304"/>
-      <c r="K1" s="304"/>
-      <c r="L1" s="304"/>
-      <c r="M1" s="304"/>
+      <c r="B1" s="312"/>
+      <c r="C1" s="312"/>
+      <c r="D1" s="312"/>
+      <c r="E1" s="312"/>
+      <c r="F1" s="312"/>
+      <c r="G1" s="312"/>
+      <c r="H1" s="312"/>
+      <c r="I1" s="312"/>
+      <c r="J1" s="312"/>
+      <c r="K1" s="312"/>
+      <c r="L1" s="312"/>
+      <c r="M1" s="312"/>
     </row>
     <row r="2" spans="1:85" ht="13.75" customHeight="1">
       <c r="A2" s="169"/>
@@ -28687,15 +29270,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:76" ht="13.75" customHeight="1">
-      <c r="A1" s="307" t="s">
+      <c r="A1" s="315" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="307"/>
-      <c r="C1" s="307"/>
-      <c r="D1" s="307"/>
-      <c r="E1" s="307"/>
-      <c r="F1" s="307"/>
-      <c r="G1" s="307"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
+      <c r="F1" s="315"/>
+      <c r="G1" s="315"/>
       <c r="H1" s="142"/>
       <c r="I1" s="142"/>
       <c r="J1" s="142"/>
@@ -28767,57 +29350,57 @@
       <c r="BX1" s="143"/>
     </row>
     <row r="2" spans="1:76" ht="13.75" customHeight="1">
-      <c r="A2" s="305" t="s">
+      <c r="A2" s="313" t="s">
         <v>49</v>
       </c>
-      <c r="B2" s="306"/>
-      <c r="C2" s="308" t="s">
+      <c r="B2" s="314"/>
+      <c r="C2" s="316" t="s">
         <v>81</v>
       </c>
-      <c r="D2" s="309"/>
-      <c r="E2" s="309"/>
-      <c r="F2" s="309"/>
-      <c r="G2" s="309"/>
-      <c r="H2" s="309"/>
-      <c r="I2" s="310"/>
-      <c r="J2" s="305" t="s">
+      <c r="D2" s="317"/>
+      <c r="E2" s="317"/>
+      <c r="F2" s="317"/>
+      <c r="G2" s="317"/>
+      <c r="H2" s="317"/>
+      <c r="I2" s="318"/>
+      <c r="J2" s="313" t="s">
         <v>82</v>
       </c>
-      <c r="K2" s="306"/>
-      <c r="L2" s="306"/>
-      <c r="M2" s="306"/>
-      <c r="N2" s="306"/>
-      <c r="O2" s="306"/>
-      <c r="P2" s="305" t="s">
+      <c r="K2" s="314"/>
+      <c r="L2" s="314"/>
+      <c r="M2" s="314"/>
+      <c r="N2" s="314"/>
+      <c r="O2" s="314"/>
+      <c r="P2" s="313" t="s">
         <v>83</v>
       </c>
-      <c r="Q2" s="306"/>
-      <c r="R2" s="306"/>
-      <c r="S2" s="306"/>
-      <c r="T2" s="306"/>
-      <c r="U2" s="306"/>
-      <c r="V2" s="306"/>
-      <c r="W2" s="306"/>
-      <c r="X2" s="305" t="s">
+      <c r="Q2" s="314"/>
+      <c r="R2" s="314"/>
+      <c r="S2" s="314"/>
+      <c r="T2" s="314"/>
+      <c r="U2" s="314"/>
+      <c r="V2" s="314"/>
+      <c r="W2" s="314"/>
+      <c r="X2" s="313" t="s">
         <v>146</v>
       </c>
-      <c r="Y2" s="306"/>
-      <c r="Z2" s="306"/>
-      <c r="AA2" s="306"/>
-      <c r="AB2" s="306"/>
-      <c r="AC2" s="306"/>
-      <c r="AD2" s="306"/>
-      <c r="AE2" s="306"/>
-      <c r="AF2" s="305" t="s">
+      <c r="Y2" s="314"/>
+      <c r="Z2" s="314"/>
+      <c r="AA2" s="314"/>
+      <c r="AB2" s="314"/>
+      <c r="AC2" s="314"/>
+      <c r="AD2" s="314"/>
+      <c r="AE2" s="314"/>
+      <c r="AF2" s="313" t="s">
         <v>40</v>
       </c>
-      <c r="AG2" s="306"/>
-      <c r="AH2" s="306"/>
-      <c r="AI2" s="306"/>
-      <c r="AJ2" s="306"/>
-      <c r="AK2" s="306"/>
-      <c r="AL2" s="306"/>
-      <c r="AM2" s="306"/>
+      <c r="AG2" s="314"/>
+      <c r="AH2" s="314"/>
+      <c r="AI2" s="314"/>
+      <c r="AJ2" s="314"/>
+      <c r="AK2" s="314"/>
+      <c r="AL2" s="314"/>
+      <c r="AM2" s="314"/>
       <c r="AN2" s="143"/>
       <c r="AO2" s="143"/>
       <c r="AP2" s="143"/>
@@ -28857,45 +29440,45 @@
       <c r="BX2" s="143"/>
     </row>
     <row r="3" spans="1:76" ht="48.75" customHeight="1">
-      <c r="A3" s="306"/>
-      <c r="B3" s="306"/>
-      <c r="C3" s="311"/>
-      <c r="D3" s="312"/>
-      <c r="E3" s="312"/>
-      <c r="F3" s="312"/>
-      <c r="G3" s="312"/>
-      <c r="H3" s="312"/>
-      <c r="I3" s="313"/>
-      <c r="J3" s="306"/>
-      <c r="K3" s="306"/>
-      <c r="L3" s="306"/>
-      <c r="M3" s="306"/>
-      <c r="N3" s="306"/>
-      <c r="O3" s="306"/>
-      <c r="P3" s="306"/>
-      <c r="Q3" s="306"/>
-      <c r="R3" s="306"/>
-      <c r="S3" s="306"/>
-      <c r="T3" s="306"/>
-      <c r="U3" s="306"/>
-      <c r="V3" s="306"/>
-      <c r="W3" s="306"/>
-      <c r="X3" s="306"/>
-      <c r="Y3" s="306"/>
-      <c r="Z3" s="306"/>
-      <c r="AA3" s="306"/>
-      <c r="AB3" s="306"/>
-      <c r="AC3" s="306"/>
-      <c r="AD3" s="306"/>
-      <c r="AE3" s="306"/>
-      <c r="AF3" s="306"/>
-      <c r="AG3" s="306"/>
-      <c r="AH3" s="306"/>
-      <c r="AI3" s="306"/>
-      <c r="AJ3" s="306"/>
-      <c r="AK3" s="306"/>
-      <c r="AL3" s="306"/>
-      <c r="AM3" s="306"/>
+      <c r="A3" s="314"/>
+      <c r="B3" s="314"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="320"/>
+      <c r="E3" s="320"/>
+      <c r="F3" s="320"/>
+      <c r="G3" s="320"/>
+      <c r="H3" s="320"/>
+      <c r="I3" s="321"/>
+      <c r="J3" s="314"/>
+      <c r="K3" s="314"/>
+      <c r="L3" s="314"/>
+      <c r="M3" s="314"/>
+      <c r="N3" s="314"/>
+      <c r="O3" s="314"/>
+      <c r="P3" s="314"/>
+      <c r="Q3" s="314"/>
+      <c r="R3" s="314"/>
+      <c r="S3" s="314"/>
+      <c r="T3" s="314"/>
+      <c r="U3" s="314"/>
+      <c r="V3" s="314"/>
+      <c r="W3" s="314"/>
+      <c r="X3" s="314"/>
+      <c r="Y3" s="314"/>
+      <c r="Z3" s="314"/>
+      <c r="AA3" s="314"/>
+      <c r="AB3" s="314"/>
+      <c r="AC3" s="314"/>
+      <c r="AD3" s="314"/>
+      <c r="AE3" s="314"/>
+      <c r="AF3" s="314"/>
+      <c r="AG3" s="314"/>
+      <c r="AH3" s="314"/>
+      <c r="AI3" s="314"/>
+      <c r="AJ3" s="314"/>
+      <c r="AK3" s="314"/>
+      <c r="AL3" s="314"/>
+      <c r="AM3" s="314"/>
       <c r="AN3" s="143"/>
       <c r="AO3" s="143"/>
       <c r="AP3" s="143"/>
@@ -28935,57 +29518,57 @@
       <c r="BX3" s="143"/>
     </row>
     <row r="4" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A4" s="339">
+      <c r="A4" s="347">
         <v>1</v>
       </c>
-      <c r="B4" s="340"/>
-      <c r="C4" s="333" t="s">
+      <c r="B4" s="348"/>
+      <c r="C4" s="341" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="334"/>
-      <c r="E4" s="334"/>
-      <c r="F4" s="334"/>
-      <c r="G4" s="334"/>
-      <c r="H4" s="334"/>
-      <c r="I4" s="335"/>
-      <c r="J4" s="315" t="s">
+      <c r="D4" s="342"/>
+      <c r="E4" s="342"/>
+      <c r="F4" s="342"/>
+      <c r="G4" s="342"/>
+      <c r="H4" s="342"/>
+      <c r="I4" s="343"/>
+      <c r="J4" s="323" t="s">
         <v>84</v>
       </c>
-      <c r="K4" s="315"/>
-      <c r="L4" s="315"/>
-      <c r="M4" s="315"/>
-      <c r="N4" s="315"/>
-      <c r="O4" s="315"/>
-      <c r="P4" s="321" t="s">
+      <c r="K4" s="323"/>
+      <c r="L4" s="323"/>
+      <c r="M4" s="323"/>
+      <c r="N4" s="323"/>
+      <c r="O4" s="323"/>
+      <c r="P4" s="329" t="s">
         <v>34</v>
       </c>
-      <c r="Q4" s="321"/>
-      <c r="R4" s="321"/>
-      <c r="S4" s="321"/>
-      <c r="T4" s="321"/>
-      <c r="U4" s="322" t="s">
+      <c r="Q4" s="329"/>
+      <c r="R4" s="329"/>
+      <c r="S4" s="329"/>
+      <c r="T4" s="329"/>
+      <c r="U4" s="330" t="s">
         <v>34</v>
       </c>
-      <c r="V4" s="322"/>
-      <c r="W4" s="322"/>
-      <c r="X4" s="318" t="s">
+      <c r="V4" s="330"/>
+      <c r="W4" s="330"/>
+      <c r="X4" s="326" t="s">
         <v>149</v>
       </c>
-      <c r="Y4" s="319"/>
-      <c r="Z4" s="319"/>
-      <c r="AA4" s="319"/>
-      <c r="AB4" s="319"/>
-      <c r="AC4" s="319"/>
-      <c r="AD4" s="319"/>
-      <c r="AE4" s="320"/>
-      <c r="AF4" s="314"/>
-      <c r="AG4" s="314"/>
-      <c r="AH4" s="314"/>
-      <c r="AI4" s="314"/>
-      <c r="AJ4" s="314"/>
-      <c r="AK4" s="314"/>
-      <c r="AL4" s="314"/>
-      <c r="AM4" s="314"/>
+      <c r="Y4" s="327"/>
+      <c r="Z4" s="327"/>
+      <c r="AA4" s="327"/>
+      <c r="AB4" s="327"/>
+      <c r="AC4" s="327"/>
+      <c r="AD4" s="327"/>
+      <c r="AE4" s="328"/>
+      <c r="AF4" s="322"/>
+      <c r="AG4" s="322"/>
+      <c r="AH4" s="322"/>
+      <c r="AI4" s="322"/>
+      <c r="AJ4" s="322"/>
+      <c r="AK4" s="322"/>
+      <c r="AL4" s="322"/>
+      <c r="AM4" s="322"/>
       <c r="AN4" s="145"/>
       <c r="AO4" s="145"/>
       <c r="AP4" s="145"/>
@@ -29025,53 +29608,53 @@
       <c r="BX4" s="145"/>
     </row>
     <row r="5" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A5" s="341"/>
-      <c r="B5" s="342"/>
-      <c r="C5" s="336"/>
-      <c r="D5" s="337"/>
-      <c r="E5" s="337"/>
-      <c r="F5" s="337"/>
-      <c r="G5" s="337"/>
-      <c r="H5" s="337"/>
-      <c r="I5" s="338"/>
-      <c r="J5" s="315" t="s">
+      <c r="A5" s="349"/>
+      <c r="B5" s="350"/>
+      <c r="C5" s="344"/>
+      <c r="D5" s="345"/>
+      <c r="E5" s="345"/>
+      <c r="F5" s="345"/>
+      <c r="G5" s="345"/>
+      <c r="H5" s="345"/>
+      <c r="I5" s="346"/>
+      <c r="J5" s="323" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="315"/>
-      <c r="L5" s="315"/>
-      <c r="M5" s="315"/>
-      <c r="N5" s="315"/>
-      <c r="O5" s="315"/>
-      <c r="P5" s="316" t="s">
+      <c r="K5" s="323"/>
+      <c r="L5" s="323"/>
+      <c r="M5" s="323"/>
+      <c r="N5" s="323"/>
+      <c r="O5" s="323"/>
+      <c r="P5" s="324" t="s">
         <v>87</v>
       </c>
-      <c r="Q5" s="316"/>
-      <c r="R5" s="316"/>
-      <c r="S5" s="316"/>
-      <c r="T5" s="316"/>
-      <c r="U5" s="317">
+      <c r="Q5" s="324"/>
+      <c r="R5" s="324"/>
+      <c r="S5" s="324"/>
+      <c r="T5" s="324"/>
+      <c r="U5" s="325">
         <v>255</v>
       </c>
-      <c r="V5" s="317"/>
-      <c r="W5" s="317"/>
-      <c r="X5" s="318" t="s">
+      <c r="V5" s="325"/>
+      <c r="W5" s="325"/>
+      <c r="X5" s="326" t="s">
         <v>147</v>
       </c>
-      <c r="Y5" s="319"/>
-      <c r="Z5" s="319"/>
-      <c r="AA5" s="319"/>
-      <c r="AB5" s="319"/>
-      <c r="AC5" s="319"/>
-      <c r="AD5" s="319"/>
-      <c r="AE5" s="320"/>
-      <c r="AF5" s="314"/>
-      <c r="AG5" s="314"/>
-      <c r="AH5" s="314"/>
-      <c r="AI5" s="314"/>
-      <c r="AJ5" s="314"/>
-      <c r="AK5" s="314"/>
-      <c r="AL5" s="314"/>
-      <c r="AM5" s="314"/>
+      <c r="Y5" s="327"/>
+      <c r="Z5" s="327"/>
+      <c r="AA5" s="327"/>
+      <c r="AB5" s="327"/>
+      <c r="AC5" s="327"/>
+      <c r="AD5" s="327"/>
+      <c r="AE5" s="328"/>
+      <c r="AF5" s="322"/>
+      <c r="AG5" s="322"/>
+      <c r="AH5" s="322"/>
+      <c r="AI5" s="322"/>
+      <c r="AJ5" s="322"/>
+      <c r="AK5" s="322"/>
+      <c r="AL5" s="322"/>
+      <c r="AM5" s="322"/>
       <c r="AN5" s="145"/>
       <c r="AO5" s="145"/>
       <c r="AP5" s="145"/>
@@ -29111,57 +29694,57 @@
       <c r="BX5" s="145"/>
     </row>
     <row r="6" spans="1:76" ht="27" customHeight="1">
-      <c r="A6" s="323">
+      <c r="A6" s="331">
         <v>2</v>
       </c>
-      <c r="B6" s="323"/>
-      <c r="C6" s="324" t="s">
+      <c r="B6" s="331"/>
+      <c r="C6" s="332" t="s">
         <v>47</v>
       </c>
-      <c r="D6" s="325"/>
-      <c r="E6" s="325"/>
-      <c r="F6" s="325"/>
-      <c r="G6" s="325"/>
-      <c r="H6" s="325"/>
-      <c r="I6" s="326"/>
-      <c r="J6" s="315" t="s">
+      <c r="D6" s="333"/>
+      <c r="E6" s="333"/>
+      <c r="F6" s="333"/>
+      <c r="G6" s="333"/>
+      <c r="H6" s="333"/>
+      <c r="I6" s="334"/>
+      <c r="J6" s="323" t="s">
         <v>86</v>
       </c>
-      <c r="K6" s="315"/>
-      <c r="L6" s="315"/>
-      <c r="M6" s="315"/>
-      <c r="N6" s="315"/>
-      <c r="O6" s="315"/>
-      <c r="P6" s="316" t="s">
+      <c r="K6" s="323"/>
+      <c r="L6" s="323"/>
+      <c r="M6" s="323"/>
+      <c r="N6" s="323"/>
+      <c r="O6" s="323"/>
+      <c r="P6" s="324" t="s">
         <v>87</v>
       </c>
-      <c r="Q6" s="316"/>
-      <c r="R6" s="316"/>
-      <c r="S6" s="316"/>
-      <c r="T6" s="316"/>
-      <c r="U6" s="327">
+      <c r="Q6" s="324"/>
+      <c r="R6" s="324"/>
+      <c r="S6" s="324"/>
+      <c r="T6" s="324"/>
+      <c r="U6" s="335">
         <v>100</v>
       </c>
-      <c r="V6" s="327"/>
-      <c r="W6" s="327"/>
-      <c r="X6" s="318" t="s">
+      <c r="V6" s="335"/>
+      <c r="W6" s="335"/>
+      <c r="X6" s="326" t="s">
         <v>148</v>
       </c>
-      <c r="Y6" s="319"/>
-      <c r="Z6" s="319"/>
-      <c r="AA6" s="319"/>
-      <c r="AB6" s="319"/>
-      <c r="AC6" s="319"/>
-      <c r="AD6" s="319"/>
-      <c r="AE6" s="320"/>
-      <c r="AF6" s="323"/>
-      <c r="AG6" s="323"/>
-      <c r="AH6" s="323"/>
-      <c r="AI6" s="323"/>
-      <c r="AJ6" s="323"/>
-      <c r="AK6" s="323"/>
-      <c r="AL6" s="323"/>
-      <c r="AM6" s="323"/>
+      <c r="Y6" s="327"/>
+      <c r="Z6" s="327"/>
+      <c r="AA6" s="327"/>
+      <c r="AB6" s="327"/>
+      <c r="AC6" s="327"/>
+      <c r="AD6" s="327"/>
+      <c r="AE6" s="328"/>
+      <c r="AF6" s="331"/>
+      <c r="AG6" s="331"/>
+      <c r="AH6" s="331"/>
+      <c r="AI6" s="331"/>
+      <c r="AJ6" s="331"/>
+      <c r="AK6" s="331"/>
+      <c r="AL6" s="331"/>
+      <c r="AM6" s="331"/>
       <c r="AN6" s="143"/>
       <c r="AO6" s="143"/>
       <c r="AP6" s="143"/>
@@ -29201,57 +29784,57 @@
       <c r="BX6" s="143"/>
     </row>
     <row r="7" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A7" s="339">
+      <c r="A7" s="347">
         <v>3</v>
       </c>
-      <c r="B7" s="340"/>
-      <c r="C7" s="324" t="s">
+      <c r="B7" s="348"/>
+      <c r="C7" s="332" t="s">
         <v>71</v>
       </c>
-      <c r="D7" s="325"/>
-      <c r="E7" s="325"/>
-      <c r="F7" s="325"/>
-      <c r="G7" s="325"/>
-      <c r="H7" s="325"/>
-      <c r="I7" s="326"/>
-      <c r="J7" s="315" t="s">
+      <c r="D7" s="333"/>
+      <c r="E7" s="333"/>
+      <c r="F7" s="333"/>
+      <c r="G7" s="333"/>
+      <c r="H7" s="333"/>
+      <c r="I7" s="334"/>
+      <c r="J7" s="323" t="s">
         <v>84</v>
       </c>
-      <c r="K7" s="315"/>
-      <c r="L7" s="315"/>
-      <c r="M7" s="315"/>
-      <c r="N7" s="315"/>
-      <c r="O7" s="315"/>
-      <c r="P7" s="321" t="s">
+      <c r="K7" s="323"/>
+      <c r="L7" s="323"/>
+      <c r="M7" s="323"/>
+      <c r="N7" s="323"/>
+      <c r="O7" s="323"/>
+      <c r="P7" s="329" t="s">
         <v>34</v>
       </c>
-      <c r="Q7" s="321"/>
-      <c r="R7" s="321"/>
-      <c r="S7" s="321"/>
-      <c r="T7" s="321"/>
-      <c r="U7" s="322" t="s">
+      <c r="Q7" s="329"/>
+      <c r="R7" s="329"/>
+      <c r="S7" s="329"/>
+      <c r="T7" s="329"/>
+      <c r="U7" s="330" t="s">
         <v>34</v>
       </c>
-      <c r="V7" s="322"/>
-      <c r="W7" s="322"/>
-      <c r="X7" s="318" t="s">
+      <c r="V7" s="330"/>
+      <c r="W7" s="330"/>
+      <c r="X7" s="326" t="s">
         <v>150</v>
       </c>
-      <c r="Y7" s="319"/>
-      <c r="Z7" s="319"/>
-      <c r="AA7" s="319"/>
-      <c r="AB7" s="319"/>
-      <c r="AC7" s="319"/>
-      <c r="AD7" s="319"/>
-      <c r="AE7" s="320"/>
-      <c r="AF7" s="328"/>
-      <c r="AG7" s="328"/>
-      <c r="AH7" s="328"/>
-      <c r="AI7" s="328"/>
-      <c r="AJ7" s="328"/>
-      <c r="AK7" s="328"/>
-      <c r="AL7" s="328"/>
-      <c r="AM7" s="328"/>
+      <c r="Y7" s="327"/>
+      <c r="Z7" s="327"/>
+      <c r="AA7" s="327"/>
+      <c r="AB7" s="327"/>
+      <c r="AC7" s="327"/>
+      <c r="AD7" s="327"/>
+      <c r="AE7" s="328"/>
+      <c r="AF7" s="336"/>
+      <c r="AG7" s="336"/>
+      <c r="AH7" s="336"/>
+      <c r="AI7" s="336"/>
+      <c r="AJ7" s="336"/>
+      <c r="AK7" s="336"/>
+      <c r="AL7" s="336"/>
+      <c r="AM7" s="336"/>
       <c r="AN7" s="147"/>
       <c r="AO7" s="147"/>
       <c r="AP7" s="147"/>
@@ -29291,55 +29874,55 @@
       <c r="BX7" s="145"/>
     </row>
     <row r="8" spans="1:76" s="146" customFormat="1" ht="26" customHeight="1">
-      <c r="A8" s="343"/>
-      <c r="B8" s="344"/>
-      <c r="C8" s="324" t="s">
+      <c r="A8" s="351"/>
+      <c r="B8" s="352"/>
+      <c r="C8" s="332" t="s">
         <v>71</v>
       </c>
-      <c r="D8" s="325"/>
-      <c r="E8" s="325"/>
-      <c r="F8" s="325"/>
-      <c r="G8" s="325"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="326"/>
-      <c r="J8" s="315" t="s">
+      <c r="D8" s="333"/>
+      <c r="E8" s="333"/>
+      <c r="F8" s="333"/>
+      <c r="G8" s="333"/>
+      <c r="H8" s="333"/>
+      <c r="I8" s="334"/>
+      <c r="J8" s="323" t="s">
         <v>88</v>
       </c>
-      <c r="K8" s="315"/>
-      <c r="L8" s="315"/>
-      <c r="M8" s="315"/>
-      <c r="N8" s="315"/>
-      <c r="O8" s="315"/>
-      <c r="P8" s="316" t="s">
+      <c r="K8" s="323"/>
+      <c r="L8" s="323"/>
+      <c r="M8" s="323"/>
+      <c r="N8" s="323"/>
+      <c r="O8" s="323"/>
+      <c r="P8" s="324" t="s">
         <v>85</v>
       </c>
-      <c r="Q8" s="316"/>
-      <c r="R8" s="316"/>
-      <c r="S8" s="316"/>
-      <c r="T8" s="316"/>
-      <c r="U8" s="322" t="s">
+      <c r="Q8" s="324"/>
+      <c r="R8" s="324"/>
+      <c r="S8" s="324"/>
+      <c r="T8" s="324"/>
+      <c r="U8" s="330" t="s">
         <v>34</v>
       </c>
-      <c r="V8" s="322"/>
-      <c r="W8" s="322"/>
-      <c r="X8" s="318" t="s">
+      <c r="V8" s="330"/>
+      <c r="W8" s="330"/>
+      <c r="X8" s="326" t="s">
         <v>151</v>
       </c>
-      <c r="Y8" s="319"/>
-      <c r="Z8" s="319"/>
-      <c r="AA8" s="319"/>
-      <c r="AB8" s="319"/>
-      <c r="AC8" s="319"/>
-      <c r="AD8" s="319"/>
-      <c r="AE8" s="320"/>
-      <c r="AF8" s="323"/>
-      <c r="AG8" s="328"/>
-      <c r="AH8" s="328"/>
-      <c r="AI8" s="328"/>
-      <c r="AJ8" s="328"/>
-      <c r="AK8" s="328"/>
-      <c r="AL8" s="328"/>
-      <c r="AM8" s="328"/>
+      <c r="Y8" s="327"/>
+      <c r="Z8" s="327"/>
+      <c r="AA8" s="327"/>
+      <c r="AB8" s="327"/>
+      <c r="AC8" s="327"/>
+      <c r="AD8" s="327"/>
+      <c r="AE8" s="328"/>
+      <c r="AF8" s="331"/>
+      <c r="AG8" s="336"/>
+      <c r="AH8" s="336"/>
+      <c r="AI8" s="336"/>
+      <c r="AJ8" s="336"/>
+      <c r="AK8" s="336"/>
+      <c r="AL8" s="336"/>
+      <c r="AM8" s="336"/>
       <c r="AN8" s="147"/>
       <c r="AO8" s="147"/>
       <c r="AP8" s="147"/>
@@ -29379,55 +29962,55 @@
       <c r="BX8" s="145"/>
     </row>
     <row r="9" spans="1:76" s="146" customFormat="1" ht="30.25" customHeight="1">
-      <c r="A9" s="341"/>
-      <c r="B9" s="342"/>
-      <c r="C9" s="324" t="s">
+      <c r="A9" s="349"/>
+      <c r="B9" s="350"/>
+      <c r="C9" s="332" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="325"/>
-      <c r="E9" s="325"/>
-      <c r="F9" s="325"/>
-      <c r="G9" s="325"/>
-      <c r="H9" s="325"/>
-      <c r="I9" s="326"/>
-      <c r="J9" s="315" t="s">
+      <c r="D9" s="333"/>
+      <c r="E9" s="333"/>
+      <c r="F9" s="333"/>
+      <c r="G9" s="333"/>
+      <c r="H9" s="333"/>
+      <c r="I9" s="334"/>
+      <c r="J9" s="323" t="s">
         <v>86</v>
       </c>
-      <c r="K9" s="315"/>
-      <c r="L9" s="315"/>
-      <c r="M9" s="315"/>
-      <c r="N9" s="315"/>
-      <c r="O9" s="315"/>
-      <c r="P9" s="316" t="s">
+      <c r="K9" s="323"/>
+      <c r="L9" s="323"/>
+      <c r="M9" s="323"/>
+      <c r="N9" s="323"/>
+      <c r="O9" s="323"/>
+      <c r="P9" s="324" t="s">
         <v>87</v>
       </c>
-      <c r="Q9" s="316"/>
-      <c r="R9" s="316"/>
-      <c r="S9" s="316"/>
-      <c r="T9" s="316"/>
-      <c r="U9" s="329">
+      <c r="Q9" s="324"/>
+      <c r="R9" s="324"/>
+      <c r="S9" s="324"/>
+      <c r="T9" s="324"/>
+      <c r="U9" s="337">
         <v>3000</v>
       </c>
-      <c r="V9" s="329"/>
-      <c r="W9" s="329"/>
-      <c r="X9" s="318" t="s">
+      <c r="V9" s="337"/>
+      <c r="W9" s="337"/>
+      <c r="X9" s="326" t="s">
         <v>152</v>
       </c>
-      <c r="Y9" s="319"/>
-      <c r="Z9" s="319"/>
-      <c r="AA9" s="319"/>
-      <c r="AB9" s="319"/>
-      <c r="AC9" s="319"/>
-      <c r="AD9" s="319"/>
-      <c r="AE9" s="320"/>
-      <c r="AF9" s="328"/>
-      <c r="AG9" s="328"/>
-      <c r="AH9" s="328"/>
-      <c r="AI9" s="328"/>
-      <c r="AJ9" s="328"/>
-      <c r="AK9" s="328"/>
-      <c r="AL9" s="328"/>
-      <c r="AM9" s="328"/>
+      <c r="Y9" s="327"/>
+      <c r="Z9" s="327"/>
+      <c r="AA9" s="327"/>
+      <c r="AB9" s="327"/>
+      <c r="AC9" s="327"/>
+      <c r="AD9" s="327"/>
+      <c r="AE9" s="328"/>
+      <c r="AF9" s="336"/>
+      <c r="AG9" s="336"/>
+      <c r="AH9" s="336"/>
+      <c r="AI9" s="336"/>
+      <c r="AJ9" s="336"/>
+      <c r="AK9" s="336"/>
+      <c r="AL9" s="336"/>
+      <c r="AM9" s="336"/>
       <c r="AN9" s="147"/>
       <c r="AO9" s="147"/>
       <c r="AP9" s="147"/>
@@ -29467,59 +30050,59 @@
       <c r="BX9" s="145"/>
     </row>
     <row r="10" spans="1:76" ht="81" customHeight="1">
-      <c r="A10" s="323">
+      <c r="A10" s="331">
         <v>4</v>
       </c>
-      <c r="B10" s="323"/>
-      <c r="C10" s="324" t="s">
+      <c r="B10" s="331"/>
+      <c r="C10" s="332" t="s">
         <v>72</v>
       </c>
-      <c r="D10" s="325"/>
-      <c r="E10" s="325"/>
-      <c r="F10" s="325"/>
-      <c r="G10" s="325"/>
-      <c r="H10" s="325"/>
-      <c r="I10" s="326"/>
-      <c r="J10" s="330" t="s">
+      <c r="D10" s="333"/>
+      <c r="E10" s="333"/>
+      <c r="F10" s="333"/>
+      <c r="G10" s="333"/>
+      <c r="H10" s="333"/>
+      <c r="I10" s="334"/>
+      <c r="J10" s="338" t="s">
         <v>89</v>
       </c>
-      <c r="K10" s="331"/>
-      <c r="L10" s="331"/>
-      <c r="M10" s="331"/>
-      <c r="N10" s="331"/>
-      <c r="O10" s="332"/>
-      <c r="P10" s="316" t="s">
+      <c r="K10" s="339"/>
+      <c r="L10" s="339"/>
+      <c r="M10" s="339"/>
+      <c r="N10" s="339"/>
+      <c r="O10" s="340"/>
+      <c r="P10" s="324" t="s">
         <v>90</v>
       </c>
-      <c r="Q10" s="316"/>
-      <c r="R10" s="316"/>
-      <c r="S10" s="316"/>
-      <c r="T10" s="316"/>
-      <c r="U10" s="322" t="s">
+      <c r="Q10" s="324"/>
+      <c r="R10" s="324"/>
+      <c r="S10" s="324"/>
+      <c r="T10" s="324"/>
+      <c r="U10" s="330" t="s">
         <v>34</v>
       </c>
-      <c r="V10" s="322"/>
-      <c r="W10" s="322"/>
-      <c r="X10" s="318" t="s">
+      <c r="V10" s="330"/>
+      <c r="W10" s="330"/>
+      <c r="X10" s="326" t="s">
         <v>153</v>
       </c>
-      <c r="Y10" s="319"/>
-      <c r="Z10" s="319"/>
-      <c r="AA10" s="319"/>
-      <c r="AB10" s="319"/>
-      <c r="AC10" s="319"/>
-      <c r="AD10" s="319"/>
-      <c r="AE10" s="320"/>
-      <c r="AF10" s="323" t="s">
+      <c r="Y10" s="327"/>
+      <c r="Z10" s="327"/>
+      <c r="AA10" s="327"/>
+      <c r="AB10" s="327"/>
+      <c r="AC10" s="327"/>
+      <c r="AD10" s="327"/>
+      <c r="AE10" s="328"/>
+      <c r="AF10" s="331" t="s">
         <v>91</v>
       </c>
-      <c r="AG10" s="323"/>
-      <c r="AH10" s="323"/>
-      <c r="AI10" s="323"/>
-      <c r="AJ10" s="323"/>
-      <c r="AK10" s="323"/>
-      <c r="AL10" s="323"/>
-      <c r="AM10" s="323"/>
+      <c r="AG10" s="331"/>
+      <c r="AH10" s="331"/>
+      <c r="AI10" s="331"/>
+      <c r="AJ10" s="331"/>
+      <c r="AK10" s="331"/>
+      <c r="AL10" s="331"/>
+      <c r="AM10" s="331"/>
       <c r="AN10" s="143"/>
       <c r="AO10" s="143"/>
       <c r="AP10" s="143"/>
@@ -29559,59 +30142,59 @@
       <c r="BX10" s="143"/>
     </row>
     <row r="11" spans="1:76" ht="27.75" customHeight="1">
-      <c r="A11" s="346" t="s">
+      <c r="A11" s="354" t="s">
         <v>155</v>
       </c>
-      <c r="B11" s="347"/>
-      <c r="C11" s="324" t="s">
+      <c r="B11" s="355"/>
+      <c r="C11" s="332" t="s">
         <v>143</v>
       </c>
-      <c r="D11" s="325"/>
-      <c r="E11" s="325"/>
-      <c r="F11" s="325"/>
-      <c r="G11" s="325"/>
-      <c r="H11" s="325"/>
-      <c r="I11" s="326"/>
-      <c r="J11" s="315" t="s">
+      <c r="D11" s="333"/>
+      <c r="E11" s="333"/>
+      <c r="F11" s="333"/>
+      <c r="G11" s="333"/>
+      <c r="H11" s="333"/>
+      <c r="I11" s="334"/>
+      <c r="J11" s="323" t="s">
         <v>144</v>
       </c>
-      <c r="K11" s="315"/>
-      <c r="L11" s="315"/>
-      <c r="M11" s="315"/>
-      <c r="N11" s="315"/>
-      <c r="O11" s="315"/>
-      <c r="P11" s="316" t="s">
+      <c r="K11" s="323"/>
+      <c r="L11" s="323"/>
+      <c r="M11" s="323"/>
+      <c r="N11" s="323"/>
+      <c r="O11" s="323"/>
+      <c r="P11" s="324" t="s">
         <v>145</v>
       </c>
-      <c r="Q11" s="316"/>
-      <c r="R11" s="316"/>
-      <c r="S11" s="316"/>
-      <c r="T11" s="316"/>
-      <c r="U11" s="327">
+      <c r="Q11" s="324"/>
+      <c r="R11" s="324"/>
+      <c r="S11" s="324"/>
+      <c r="T11" s="324"/>
+      <c r="U11" s="335">
         <v>100</v>
       </c>
-      <c r="V11" s="327"/>
-      <c r="W11" s="327"/>
-      <c r="X11" s="318" t="s">
+      <c r="V11" s="335"/>
+      <c r="W11" s="335"/>
+      <c r="X11" s="326" t="s">
         <v>156</v>
       </c>
-      <c r="Y11" s="319"/>
-      <c r="Z11" s="319"/>
-      <c r="AA11" s="319"/>
-      <c r="AB11" s="319"/>
-      <c r="AC11" s="319"/>
-      <c r="AD11" s="319"/>
-      <c r="AE11" s="320"/>
-      <c r="AF11" s="323" t="s">
+      <c r="Y11" s="327"/>
+      <c r="Z11" s="327"/>
+      <c r="AA11" s="327"/>
+      <c r="AB11" s="327"/>
+      <c r="AC11" s="327"/>
+      <c r="AD11" s="327"/>
+      <c r="AE11" s="328"/>
+      <c r="AF11" s="331" t="s">
         <v>154</v>
       </c>
-      <c r="AG11" s="323"/>
-      <c r="AH11" s="323"/>
-      <c r="AI11" s="323"/>
-      <c r="AJ11" s="323"/>
-      <c r="AK11" s="323"/>
-      <c r="AL11" s="323"/>
-      <c r="AM11" s="323"/>
+      <c r="AG11" s="331"/>
+      <c r="AH11" s="331"/>
+      <c r="AI11" s="331"/>
+      <c r="AJ11" s="331"/>
+      <c r="AK11" s="331"/>
+      <c r="AL11" s="331"/>
+      <c r="AM11" s="331"/>
       <c r="AN11" s="143"/>
       <c r="AO11" s="143"/>
       <c r="AP11" s="143"/>
@@ -29651,45 +30234,45 @@
       <c r="BX11" s="143"/>
     </row>
     <row r="12" spans="1:76" ht="27.75" customHeight="1">
-      <c r="A12" s="345"/>
-      <c r="B12" s="323"/>
-      <c r="C12" s="324"/>
-      <c r="D12" s="325"/>
-      <c r="E12" s="325"/>
-      <c r="F12" s="325"/>
-      <c r="G12" s="325"/>
-      <c r="H12" s="325"/>
-      <c r="I12" s="326"/>
-      <c r="J12" s="315"/>
-      <c r="K12" s="315"/>
-      <c r="L12" s="315"/>
-      <c r="M12" s="315"/>
-      <c r="N12" s="315"/>
-      <c r="O12" s="315"/>
-      <c r="P12" s="316"/>
-      <c r="Q12" s="316"/>
-      <c r="R12" s="316"/>
-      <c r="S12" s="316"/>
-      <c r="T12" s="316"/>
-      <c r="U12" s="327"/>
-      <c r="V12" s="327"/>
-      <c r="W12" s="327"/>
-      <c r="X12" s="318"/>
-      <c r="Y12" s="319"/>
-      <c r="Z12" s="319"/>
-      <c r="AA12" s="319"/>
-      <c r="AB12" s="319"/>
-      <c r="AC12" s="319"/>
-      <c r="AD12" s="319"/>
-      <c r="AE12" s="320"/>
-      <c r="AF12" s="323"/>
-      <c r="AG12" s="323"/>
-      <c r="AH12" s="323"/>
-      <c r="AI12" s="323"/>
-      <c r="AJ12" s="323"/>
-      <c r="AK12" s="323"/>
-      <c r="AL12" s="323"/>
-      <c r="AM12" s="323"/>
+      <c r="A12" s="353"/>
+      <c r="B12" s="331"/>
+      <c r="C12" s="332"/>
+      <c r="D12" s="333"/>
+      <c r="E12" s="333"/>
+      <c r="F12" s="333"/>
+      <c r="G12" s="333"/>
+      <c r="H12" s="333"/>
+      <c r="I12" s="334"/>
+      <c r="J12" s="323"/>
+      <c r="K12" s="323"/>
+      <c r="L12" s="323"/>
+      <c r="M12" s="323"/>
+      <c r="N12" s="323"/>
+      <c r="O12" s="323"/>
+      <c r="P12" s="324"/>
+      <c r="Q12" s="324"/>
+      <c r="R12" s="324"/>
+      <c r="S12" s="324"/>
+      <c r="T12" s="324"/>
+      <c r="U12" s="335"/>
+      <c r="V12" s="335"/>
+      <c r="W12" s="335"/>
+      <c r="X12" s="326"/>
+      <c r="Y12" s="327"/>
+      <c r="Z12" s="327"/>
+      <c r="AA12" s="327"/>
+      <c r="AB12" s="327"/>
+      <c r="AC12" s="327"/>
+      <c r="AD12" s="327"/>
+      <c r="AE12" s="328"/>
+      <c r="AF12" s="331"/>
+      <c r="AG12" s="331"/>
+      <c r="AH12" s="331"/>
+      <c r="AI12" s="331"/>
+      <c r="AJ12" s="331"/>
+      <c r="AK12" s="331"/>
+      <c r="AL12" s="331"/>
+      <c r="AM12" s="331"/>
       <c r="AN12" s="143"/>
       <c r="AO12" s="143"/>
       <c r="AP12" s="143"/>

--- a/20_設計書/化学物質データ申請画面.xlsx
+++ b/20_設計書/化学物質データ申請画面.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AMA1040\Documents\古竹作成\基本設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1539BE-3199-4C84-938B-3CD503DC01C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EA05BB0-B1CA-4A28-8472-4AB95D3DD298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29370" yWindow="570" windowWidth="16245" windowHeight="10095" tabRatio="859" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -250,7 +250,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="172">
   <si>
     <t>HRS殿</t>
     <rPh sb="3" eb="4">
@@ -1661,22 +1661,6 @@
     <phoneticPr fontId="56"/>
   </si>
   <si>
-    <t>リンクを押下すると「化学物質データ」画面に遷移する</t>
-    <rPh sb="4" eb="6">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="10" eb="14">
-      <t>カガクブッシツ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="56"/>
-  </si>
-  <si>
     <t>お知らせテーブル データバージョン情報(日本語・HTML)/データバージョン情報(英語・HTML)</t>
     <rPh sb="1" eb="2">
       <t>シ</t>
@@ -1732,6 +1716,27 @@
     </rPh>
     <rPh sb="10" eb="12">
       <t>イコウ</t>
+    </rPh>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>ホーム画面: ホーム (リンクなし)</t>
+    <phoneticPr fontId="56"/>
+  </si>
+  <si>
+    <t>dr1.5</t>
+    <phoneticPr fontId="52"/>
+  </si>
+  <si>
+    <t>課題リストの回答をもとに修正</t>
+    <rPh sb="0" eb="2">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>カイトウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>シュウセイ</t>
     </rPh>
     <phoneticPr fontId="52"/>
   </si>
@@ -8002,7 +8007,7 @@
     <row r="22" spans="2:8" ht="14.25" customHeight="1">
       <c r="B22" s="177" t="str">
         <f ca="1">TEXT(変更来歴!AT2,"yyyy年 mm月 dd日") &amp; " " &amp; 変更来歴!AT3</f>
-        <v>2026年 06月 11日 dr1.4</v>
+        <v>2026年 06月 17日 dr1.5</v>
       </c>
       <c r="C22" s="178"/>
       <c r="D22" s="178"/>
@@ -9019,7 +9024,7 @@
     </row>
     <row r="2" spans="1:53">
       <c r="A2" s="207" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B2" s="207"/>
       <c r="C2" s="207"/>
@@ -9035,7 +9040,7 @@
       <c r="K2" s="208"/>
       <c r="L2" s="208"/>
       <c r="M2" s="209" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="N2" s="210"/>
       <c r="O2" s="210"/>
@@ -9076,7 +9081,7 @@
       <c r="AR2" s="212"/>
       <c r="AS2" s="212"/>
       <c r="AT2" s="215">
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AU2" s="215"/>
       <c r="AV2" s="215"/>
@@ -9146,7 +9151,7 @@
       <c r="AS3" s="212"/>
       <c r="AT3" s="228" t="str">
         <f ca="1">INDIRECT("A" &amp; COUNTA(A7:A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AU3" s="228"/>
       <c r="AV3" s="228"/>
@@ -9563,7 +9568,7 @@
       <c r="O11" s="201"/>
       <c r="P11" s="202"/>
       <c r="Q11" s="186" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="R11" s="185"/>
       <c r="S11" s="185"/>
@@ -9607,23 +9612,29 @@
       <c r="BA11" s="185"/>
     </row>
     <row r="12" spans="1:53">
-      <c r="A12" s="184"/>
-      <c r="B12" s="184"/>
-      <c r="C12" s="185"/>
-      <c r="D12" s="185"/>
-      <c r="E12" s="185"/>
-      <c r="F12" s="185"/>
-      <c r="G12" s="185"/>
-      <c r="H12" s="185"/>
-      <c r="I12" s="185"/>
-      <c r="J12" s="185"/>
-      <c r="K12" s="185"/>
-      <c r="L12" s="185"/>
-      <c r="M12" s="185"/>
-      <c r="N12" s="185"/>
-      <c r="O12" s="185"/>
-      <c r="P12" s="185"/>
-      <c r="Q12" s="185"/>
+      <c r="A12" s="199" t="s">
+        <v>170</v>
+      </c>
+      <c r="B12" s="200"/>
+      <c r="C12" s="186" t="s">
+        <v>162</v>
+      </c>
+      <c r="D12" s="201"/>
+      <c r="E12" s="201"/>
+      <c r="F12" s="201"/>
+      <c r="G12" s="201"/>
+      <c r="H12" s="201"/>
+      <c r="I12" s="201"/>
+      <c r="J12" s="201"/>
+      <c r="K12" s="201"/>
+      <c r="L12" s="201"/>
+      <c r="M12" s="201"/>
+      <c r="N12" s="201"/>
+      <c r="O12" s="201"/>
+      <c r="P12" s="202"/>
+      <c r="Q12" s="185" t="s">
+        <v>171</v>
+      </c>
       <c r="R12" s="185"/>
       <c r="S12" s="185"/>
       <c r="T12" s="185"/>
@@ -9644,11 +9655,15 @@
       <c r="AI12" s="185"/>
       <c r="AJ12" s="185"/>
       <c r="AK12" s="185"/>
-      <c r="AL12" s="183"/>
+      <c r="AL12" s="183">
+        <v>46190</v>
+      </c>
       <c r="AM12" s="184"/>
       <c r="AN12" s="184"/>
       <c r="AO12" s="184"/>
-      <c r="AP12" s="185"/>
+      <c r="AP12" s="185" t="s">
+        <v>29</v>
+      </c>
       <c r="AQ12" s="185"/>
       <c r="AR12" s="185"/>
       <c r="AS12" s="185"/>
@@ -11273,7 +11288,7 @@
       <c r="AU2" s="212"/>
       <c r="AV2" s="215">
         <f ca="1">INDIRECT("変更来歴!AL" &amp; COUNTA(変更来歴!AL7:'変更来歴'!AL39) + 6)</f>
-        <v>46184</v>
+        <v>46190</v>
       </c>
       <c r="AW2" s="228"/>
       <c r="AX2" s="228"/>
@@ -11325,7 +11340,7 @@
       <c r="Z3" s="208"/>
       <c r="AA3" s="224" t="str">
         <f ca="1">MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename"))) &amp; "画面"</f>
-        <v>変更来歴画面</v>
+        <v>表紙画面</v>
       </c>
       <c r="AB3" s="224"/>
       <c r="AC3" s="224"/>
@@ -11351,7 +11366,7 @@
       <c r="AU3" s="212"/>
       <c r="AV3" s="228" t="str">
         <f ca="1">INDIRECT("変更来歴!A" &amp; COUNTA(変更来歴!A7:'変更来歴'!A39) + 6)</f>
-        <v>dr1.4</v>
+        <v>dr1.5</v>
       </c>
       <c r="AW3" s="228"/>
       <c r="AX3" s="228"/>
@@ -11365,7 +11380,7 @@
     <row r="5" spans="1:75" ht="13.5" customHeight="1">
       <c r="A5" s="234" t="str">
         <f ca="1">"画面レイアウト"&amp;"("&amp;MID(CELL("filename"),FIND("]",CELL("filename"))+1,LEN(CELL("filename")))&amp;")"</f>
-        <v>画面レイアウト(変更来歴)</v>
+        <v>画面レイアウト(表紙)</v>
       </c>
       <c r="B5" s="235"/>
       <c r="C5" s="235"/>
@@ -27967,7 +27982,7 @@
       <c r="AI8" s="255"/>
       <c r="AJ8" s="255"/>
       <c r="AK8" s="256" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AL8" s="255"/>
       <c r="AM8" s="255"/>
@@ -28438,7 +28453,7 @@
       <c r="Z14" s="294"/>
       <c r="AA14" s="295"/>
       <c r="AB14" s="296" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC14" s="297"/>
       <c r="AD14" s="297"/>
